--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44561909-5B32-DF41-ACAD-7037741CCA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C416EF-5D12-3849-AC2C-B866AF844443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{43BB2B61-81EB-3E4F-80D2-4E0A494C28E2}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{CDD22C7D-C6D9-7745-8F49-E2DB3D3FB05F}">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{DB1964DB-DAAE-5346-9520-97EA509EE5D8}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{EF544127-57E7-A843-956A-C3C40445D16D}">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{322E20F9-9988-D646-A6E8-7DC5480BFCA4}">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{E059F785-A631-6D40-98D9-742410D7E103}">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{384B2756-ADFE-EC45-B204-F5CE249C3DC7}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{661829BD-C86A-EF4C-9EA3-BFBCC8668404}">
       <text>
         <r>
           <rPr>
@@ -170,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{3AC934E5-A173-1549-AC2F-85AE3473677B}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{42C4D978-CBDF-9948-B435-C6907ECACA12}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{5BD5FC0C-F81E-0842-A731-BCC72F940F86}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{5F5A1961-83C7-0341-B44F-7E204CB74176}">
       <text>
         <r>
           <rPr>
@@ -234,7 +234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{1DB22D9C-6D47-904D-9027-135DD4207EBE}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{8D59DAA3-3300-E24E-826D-A61604037479}">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{5B216B1C-026F-874C-95B4-4665479D8309}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{6276D97B-D52C-CB40-9833-A93F36452632}">
       <text>
         <r>
           <rPr>
@@ -295,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{5FC140B9-BEC7-194F-B717-F22EFFB79970}">
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{3C61B88D-6CE0-D043-B8DC-B831ABF96F2A}">
       <text>
         <r>
           <rPr>
@@ -326,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{D5DA6462-2725-D24F-BF4C-3BE9B828F782}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{41398352-4BCD-C149-BAA9-F17F098CBED6}">
       <text>
         <r>
           <rPr>
@@ -357,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{88A8B099-698A-7849-A020-9E9996FA89AE}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{EBFC085A-7B53-2242-BC54-2A1844A17032}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{41A25DAA-DC5C-9B4E-8868-5EF95FBE8EEF}">
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{3526B851-1B0F-DA4F-9A7E-BCC2FBB1452F}">
       <text>
         <r>
           <rPr>
@@ -418,7 +418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{2EECE204-4157-9C45-B9B4-65034F2F21E8}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{24FF9647-BCDF-6743-9013-6CED273B6AC5}">
       <text>
         <r>
           <rPr>
@@ -449,7 +449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{2F06137C-3449-004E-B48B-A5B7C4D9704D}">
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{1EADB207-E9FC-2F44-9666-48229A450E8C}">
       <text>
         <r>
           <rPr>
@@ -480,7 +480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{2928A72D-2B02-344F-A784-02B043660CDB}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{478C9BE9-28F4-3149-B199-A03F06DC8F9D}">
       <text>
         <r>
           <rPr>
@@ -511,7 +511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{A64A29DB-B633-D54B-BF46-B89ACE8E6333}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{8AA31053-55F0-D64D-A119-58F7B5191DB5}">
       <text>
         <r>
           <rPr>
@@ -542,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{88910E92-A75A-3248-92DE-FD418C7CEFDF}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{A8326152-1B6E-794D-B1EE-1CC9E3401C66}">
       <text>
         <r>
           <rPr>
@@ -573,7 +573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{D0384561-9A5B-F14C-8612-E9BDF8AEC105}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{21DA9BBB-6D5C-1C46-A07F-1E32CACF57D0}">
       <text>
         <r>
           <rPr>
@@ -604,7 +604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{7536B58B-2597-EA40-A2DD-A697D2B8E37B}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{8E751289-9040-6848-95AE-BE9D3E14FC3E}">
       <text>
         <r>
           <rPr>
@@ -622,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{0DB6387C-99F0-8241-82E8-65539ED21A7C}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{7BB84E63-E182-1848-8DBE-709F5722C925}">
       <text>
         <r>
           <rPr>
@@ -640,7 +640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{EE069BBC-7AB8-BF44-8E56-C49C8ECC0C44}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{C2E796CE-AA58-D54D-940F-482AB821EFB2}">
       <text>
         <r>
           <rPr>
@@ -657,7 +657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{7874D7B2-A04E-624D-ABD3-6969E28C7F31}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{D00A7CF9-D215-6948-8B44-C17D20520474}">
       <text>
         <r>
           <rPr>
@@ -674,7 +674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{887FD518-605C-1646-98D0-A39F411B247F}">
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{DB5ADE94-33CF-1F42-A53D-D48880CA3BD2}">
       <text>
         <r>
           <rPr>
@@ -690,7 +690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{853D4058-E31B-C34C-98A5-E28909998164}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{607BBBA5-9346-EA47-829E-336B7C2F4EB4}">
       <text>
         <r>
           <rPr>
@@ -714,7 +714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{2B001AE7-05CA-5D45-BC40-370C74BF370B}">
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{55987714-60FF-3241-B469-A896D8402F62}">
       <text>
         <r>
           <rPr>
@@ -732,7 +732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{91756FD5-E362-0146-A417-FC16DCF40C45}">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{EFE54D89-369D-B046-8624-15E4EB00C256}">
       <text>
         <r>
           <rPr>
@@ -748,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{D2B381FE-203D-E644-804A-43654EB6D11F}">
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{6A7B9A75-AA96-B04D-9036-5CDCC6F00CF7}">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{1AF4B732-4C42-4E49-AA84-C71033CD4917}">
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{55BA5F4E-AA3A-AF4C-855F-6C8AC3DA868D}">
       <text>
         <r>
           <rPr>
@@ -793,7 +793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{ECACD1B5-1D74-084B-92C8-D1B3ACF0A50B}">
+    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{278D7B77-26FF-C647-9F19-F8A9C9D1BF50}">
       <text>
         <r>
           <rPr>
@@ -822,7 +822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{97BAE94B-BA1C-6849-9890-165352A7C389}">
+    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{3EC989FC-8241-3340-9D87-47ED64253461}">
       <text>
         <r>
           <rPr>
@@ -851,7 +851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{CF80C856-C377-924A-9AEB-8BB231E37AFB}">
+    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{D35F49B4-E8E8-7C47-A198-8358EB33D912}">
       <text>
         <r>
           <rPr>
@@ -875,7 +875,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{EBE04974-7DDD-F844-8BD0-713BDDF65DCA}">
+    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{863AFA52-27A9-FF4C-8E52-310F489E19E7}">
       <text>
         <r>
           <rPr>
@@ -891,7 +891,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{A1A5EFF5-83A1-BE43-8CDA-649B69B682F4}">
+    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{6A60425C-9662-F845-BDC3-D01FB079B67A}">
       <text>
         <r>
           <rPr>
@@ -920,7 +920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{FB60222D-37BA-CD4D-8A18-14176DB77908}">
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{7F66BE82-BB1B-1442-9A24-78B380B8EA58}">
       <text>
         <r>
           <rPr>
@@ -937,7 +937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{10C10BD3-0531-8446-A2F0-1BBF16B8DCD7}">
+    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{711E3ADC-137E-0542-925B-B418584D018A}">
       <text>
         <r>
           <rPr>
@@ -966,7 +966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{CC6E27A9-E22F-A640-A9A3-00A0D52EB759}">
+    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{BE892862-11C9-354A-BED4-F177484F03D9}">
       <text>
         <r>
           <rPr>
@@ -982,7 +982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{A0FCA332-EAAD-8146-99D9-EBD5DE79E4EA}">
+    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{0D72B90B-522C-E64E-8986-0FA60F2F6785}">
       <text>
         <r>
           <rPr>
@@ -1008,7 +1008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{89870D82-2AD0-DC43-B5BF-8634698487BC}">
+    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{03C38B03-C811-134D-A46C-EF7C1A0166E0}">
       <text>
         <r>
           <rPr>
@@ -1024,7 +1024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I40" authorId="0" shapeId="0" xr:uid="{16B3F79C-28A2-7540-B3DC-5970775A5E28}">
+    <comment ref="I40" authorId="0" shapeId="0" xr:uid="{3365C4A4-E947-DF43-8BE6-0254A4C6C631}">
       <text>
         <r>
           <rPr>
@@ -1040,7 +1040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{F2A8C3E5-164D-7549-89B6-B11D1B6A53FA}">
+    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{FC4F312D-09DF-A543-9970-8AFA51C1618C}">
       <text>
         <r>
           <rPr>
@@ -1057,7 +1057,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{E1721375-AC00-4145-8158-4CD787DA1C5F}">
+    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{222C5458-9DD7-BC4B-9720-B917803ECBC0}">
       <text>
         <r>
           <rPr>
@@ -1073,7 +1073,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{D3649271-CA04-A34D-93F1-2E9E1F34CE05}">
+    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{AB4BC33A-C0DC-3D44-A661-6BAD5B9030C8}">
       <text>
         <r>
           <rPr>
@@ -1089,7 +1089,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I44" authorId="0" shapeId="0" xr:uid="{30EE3800-66FA-0240-AD68-254B54D392EB}">
+    <comment ref="I44" authorId="0" shapeId="0" xr:uid="{D66E1DA4-F59F-274E-9183-5FDD9AD08D08}">
       <text>
         <r>
           <rPr>
@@ -1105,7 +1105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I45" authorId="0" shapeId="0" xr:uid="{68E1437C-A1C9-654E-ACD7-B42491171798}">
+    <comment ref="I45" authorId="0" shapeId="0" xr:uid="{9E980415-DCF2-C841-B61B-E832BB434694}">
       <text>
         <r>
           <rPr>
@@ -1132,7 +1132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I46" authorId="0" shapeId="0" xr:uid="{C61FF840-9C5E-9944-BA3A-115265951118}">
+    <comment ref="I46" authorId="0" shapeId="0" xr:uid="{AB6F152C-77D6-0243-A1BE-E2DB6F532274}">
       <text>
         <r>
           <rPr>
@@ -1161,7 +1161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{F4235F20-7622-7744-A30A-D53A6CF18DBC}">
+    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{BD86983B-D2DD-6348-99C8-4453C3E15B9D}">
       <text>
         <r>
           <rPr>
@@ -1177,7 +1177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{5AA5B8C7-FBBC-8A4C-AE3E-1D9CCA72BD9C}">
+    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{E9E74E13-BCC8-D34C-BDF0-BF7E83880F00}">
       <text>
         <r>
           <rPr>
@@ -1193,7 +1193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{E80C5181-0F6E-6642-8ED1-2EE5E2AF170B}">
+    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{311C40F2-B185-A247-8F13-86FDFCDBA7C3}">
       <text>
         <r>
           <rPr>
@@ -1208,7 +1208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{CB3106AB-1B1A-F84B-BF90-C3D0DD06F47D}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{CED9D70B-E13E-4A41-973C-D21814AAC3E2}">
       <text>
         <r>
           <rPr>
@@ -1235,7 +1235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{6678592D-C48D-2C4A-A682-2E9E2637EBB1}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{F45C7C05-C8F5-1149-A2A4-8F83533302DF}">
       <text>
         <r>
           <rPr>
@@ -1251,7 +1251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{DDDCDFAF-8B03-744C-A415-13DF0DDDFCBE}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{63D182F5-CD2F-FE42-9402-A507424E7844}">
       <text>
         <r>
           <rPr>
@@ -1267,7 +1267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{5DA19F55-0222-7643-B2E5-BB67C44E1823}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{568D71AC-9CDC-ED45-AA81-C0DB40244ADF}">
       <text>
         <r>
           <rPr>
@@ -1291,7 +1291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I54" authorId="0" shapeId="0" xr:uid="{437F4776-7A20-E043-9059-C6C03EF9EE17}">
+    <comment ref="I54" authorId="0" shapeId="0" xr:uid="{57AFF0C9-E338-194A-9577-132D4FCE698B}">
       <text>
         <r>
           <rPr>
@@ -1307,7 +1307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I55" authorId="0" shapeId="0" xr:uid="{69717D1E-818A-ED49-B814-66F7C822D6F0}">
+    <comment ref="I55" authorId="0" shapeId="0" xr:uid="{B3565069-5D34-7440-86A9-AF44CFB23D1D}">
       <text>
         <r>
           <rPr>
@@ -1323,7 +1323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{C45FED00-A37A-4943-A0C7-55B43A888D54}">
+    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{B1BA0472-2E26-7845-B6FF-3A21BB735207}">
       <text>
         <r>
           <rPr>
@@ -1348,7 +1348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I57" authorId="0" shapeId="0" xr:uid="{9CBF805D-0E15-344B-850A-8420FE04C8E1}">
+    <comment ref="I57" authorId="0" shapeId="0" xr:uid="{4784C6E1-B1AD-C541-A5B2-7C5005DF3DB6}">
       <text>
         <r>
           <rPr>
@@ -1373,7 +1373,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{B67AD2D7-1A7F-8345-A351-0EEAF68AFCCC}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{5120F521-CFF5-674A-9A24-2C3298C73790}">
       <text>
         <r>
           <rPr>
@@ -1393,7 +1393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{CBDE7E76-D14B-2546-8CB3-18906CAD89FB}">
+    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{6302E5F4-768A-E84E-84CA-6C1B780F1F24}">
       <text>
         <r>
           <rPr>
@@ -1408,7 +1408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I60" authorId="0" shapeId="0" xr:uid="{0A733D18-F99F-A047-979D-A91C7D170644}">
+    <comment ref="I60" authorId="0" shapeId="0" xr:uid="{CA1981A4-AEB2-0444-B0A7-3985B91BBDE9}">
       <text>
         <r>
           <rPr>
@@ -1428,7 +1428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I61" authorId="0" shapeId="0" xr:uid="{9723F380-CBA8-8E4F-B2D1-D33622CB9CCF}">
+    <comment ref="I61" authorId="0" shapeId="0" xr:uid="{BB460848-7DA5-684B-93F7-7E8021DC8EB1}">
       <text>
         <r>
           <rPr>
@@ -1444,7 +1444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I62" authorId="0" shapeId="0" xr:uid="{EAF8B9A6-48F3-1F4D-8DFE-7BF0D13C3537}">
+    <comment ref="I62" authorId="0" shapeId="0" xr:uid="{06426C9A-1836-1D49-A1B0-7755DAAB7F2D}">
       <text>
         <r>
           <rPr>
@@ -1460,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I63" authorId="0" shapeId="0" xr:uid="{9D721D3E-64C4-CC41-8FC4-2807656DFBB9}">
+    <comment ref="I63" authorId="0" shapeId="0" xr:uid="{250A7F06-B88D-0F4F-A4C2-138026A9E516}">
       <text>
         <r>
           <rPr>
@@ -1475,7 +1475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I64" authorId="0" shapeId="0" xr:uid="{A497EBE9-2F66-554C-A9E8-04DB31EC61DC}">
+    <comment ref="I64" authorId="0" shapeId="0" xr:uid="{34B159C3-295D-F94B-BC63-7DBF4DB96663}">
       <text>
         <r>
           <rPr>
@@ -1491,7 +1491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I65" authorId="0" shapeId="0" xr:uid="{22A77367-CC98-1541-B06B-60B6D5B3BB2D}">
+    <comment ref="I65" authorId="0" shapeId="0" xr:uid="{CA1A74E0-25A4-FF4D-A980-56B36838BF41}">
       <text>
         <r>
           <rPr>
@@ -1520,7 +1520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I66" authorId="0" shapeId="0" xr:uid="{ADDF5059-CB6C-1340-AC96-87A01BA3FDB2}">
+    <comment ref="I66" authorId="0" shapeId="0" xr:uid="{69F63B8F-DA4C-E342-8BAC-162BDDE64E23}">
       <text>
         <r>
           <rPr>
@@ -1535,7 +1535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{7BBB78F6-0DA5-A44C-B303-95DB381DB0F5}">
+    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{32C47C9C-93FC-924E-8D7C-4D48C3995241}">
       <text>
         <r>
           <rPr>
@@ -1555,7 +1555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{7FBCE7DB-2272-3444-B33E-F6F760C01E79}">
+    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{60A606A5-7446-794D-BA98-0DEE3F486CBC}">
       <text>
         <r>
           <rPr>
@@ -1575,7 +1575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{8E455C54-7F69-384C-A85B-0B4585627971}">
+    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{DFEE89FE-1FC3-AF48-8C02-23FE4D87FF41}">
       <text>
         <r>
           <rPr>
@@ -1595,7 +1595,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I70" authorId="0" shapeId="0" xr:uid="{821A9618-9DEE-AB44-AC26-BC62EC6B6202}">
+    <comment ref="I70" authorId="0" shapeId="0" xr:uid="{E5093DA3-9896-6341-B31C-7CC7C46FF6C0}">
       <text>
         <r>
           <rPr>
@@ -1618,7 +1618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I71" authorId="0" shapeId="0" xr:uid="{B88FA29E-EA6A-AC44-8700-8CEA5776B742}">
+    <comment ref="I71" authorId="0" shapeId="0" xr:uid="{945BDABC-1EE3-7B48-8C9C-7069310A72B6}">
       <text>
         <r>
           <rPr>
@@ -1634,7 +1634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{27AB7A14-3835-2547-BFAD-BDA84EB9FE49}">
+    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{A3EC5891-72C7-9D4B-9E31-637BE31575E7}">
       <text>
         <r>
           <rPr>
@@ -1663,7 +1663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I73" authorId="0" shapeId="0" xr:uid="{564E591A-373A-7E48-A0FA-D86D9D31E555}">
+    <comment ref="I73" authorId="0" shapeId="0" xr:uid="{8E223EBD-B04E-094F-A5F6-CF5EF8AA5D15}">
       <text>
         <r>
           <rPr>
@@ -1678,7 +1678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I74" authorId="0" shapeId="0" xr:uid="{064EE0B9-EF27-6344-ACDF-3C37532ECAB3}">
+    <comment ref="I74" authorId="0" shapeId="0" xr:uid="{53093360-1BAC-6B4C-B611-205E05773696}">
       <text>
         <r>
           <rPr>
@@ -1698,7 +1698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I75" authorId="0" shapeId="0" xr:uid="{834049B3-1087-CA4D-A52A-C2F0671C2CFD}">
+    <comment ref="I75" authorId="0" shapeId="0" xr:uid="{E3498F08-9835-FA40-AEA2-FFB9AD25BD4C}">
       <text>
         <r>
           <rPr>
@@ -1718,7 +1718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I76" authorId="0" shapeId="0" xr:uid="{A330070F-6361-9148-B274-94806936EE26}">
+    <comment ref="I76" authorId="0" shapeId="0" xr:uid="{E1C031D8-A441-FD4B-8E20-937901B99546}">
       <text>
         <r>
           <rPr>
@@ -1738,7 +1738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I77" authorId="0" shapeId="0" xr:uid="{5A4A995C-4B6E-4945-A831-840B62457151}">
+    <comment ref="I77" authorId="0" shapeId="0" xr:uid="{61B7FE4A-436D-0546-BC7C-A6307EDDBA42}">
       <text>
         <r>
           <rPr>
@@ -1758,7 +1758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I78" authorId="0" shapeId="0" xr:uid="{C06E31E7-45F8-8645-988C-20D7BC672476}">
+    <comment ref="I78" authorId="0" shapeId="0" xr:uid="{2CFA145E-78C9-C64A-B39C-1EADF9137806}">
       <text>
         <r>
           <rPr>
@@ -1774,7 +1774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I79" authorId="0" shapeId="0" xr:uid="{48073F28-762A-E748-8378-58FF5C3E70F8}">
+    <comment ref="I79" authorId="0" shapeId="0" xr:uid="{2C2DA30E-596A-5D44-803A-84750681ECD4}">
       <text>
         <r>
           <rPr>
@@ -1789,7 +1789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I80" authorId="0" shapeId="0" xr:uid="{78D37E4B-D834-4B4F-875F-947D1ED58358}">
+    <comment ref="I80" authorId="0" shapeId="0" xr:uid="{31FDD1E7-56B3-BE49-B8E2-A55CBC1D03B8}">
       <text>
         <r>
           <rPr>
@@ -1809,7 +1809,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I81" authorId="0" shapeId="0" xr:uid="{22CE11A6-BAF3-CC4E-B401-32B86CE686F0}">
+    <comment ref="I81" authorId="0" shapeId="0" xr:uid="{E8ED0BBB-E824-124D-BE7D-B35BF23EA0B2}">
       <text>
         <r>
           <rPr>
@@ -1829,7 +1829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I82" authorId="0" shapeId="0" xr:uid="{0C30A2C4-CC8B-D44F-8CC7-3F240CE83116}">
+    <comment ref="I82" authorId="0" shapeId="0" xr:uid="{2A9C6C65-92ED-F740-92BB-0F36A84A4734}">
       <text>
         <r>
           <rPr>
@@ -1856,7 +1856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I83" authorId="0" shapeId="0" xr:uid="{77CBD89A-B47F-4E45-AA88-9F79C402CAAF}">
+    <comment ref="I83" authorId="0" shapeId="0" xr:uid="{BA93BD8E-86CF-F649-B2D8-8013A5DB8D91}">
       <text>
         <r>
           <rPr>
@@ -1874,7 +1874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I84" authorId="0" shapeId="0" xr:uid="{28A17E66-BFFA-1746-8DEA-8A78E22C319D}">
+    <comment ref="I84" authorId="0" shapeId="0" xr:uid="{8CA3B1F6-ED31-4A45-AD72-DCC22129C589}">
       <text>
         <r>
           <rPr>
@@ -1903,7 +1903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{8142070D-B69D-DB48-979F-D40512140FDD}">
+    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{EC7991BE-2CB6-4D49-B4C6-31DE5BF08C87}">
       <text>
         <r>
           <rPr>
@@ -1923,7 +1923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{013BC4EB-84B7-224B-B44D-FE925CBA1241}">
+    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{9763A51D-C5FC-A140-A128-231A8588C56B}">
       <text>
         <r>
           <rPr>
@@ -1938,7 +1938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{5028700A-2341-F843-9A06-E766159AD054}">
+    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{F62FFB5E-79F2-EA4E-94AA-4D07F5DA3AF2}">
       <text>
         <r>
           <rPr>
@@ -1954,7 +1954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{698EB9CF-D006-6C46-ACA9-C9313E9F3CED}">
+    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{CEFDAD3B-646F-FB47-8117-04A500AD30DB}">
       <text>
         <r>
           <rPr>
@@ -1972,7 +1972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{760B6320-5962-AC43-9BFC-408885AD7EB5}">
+    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{D1907C2B-4C33-0A4A-B884-37DAB993939D}">
       <text>
         <r>
           <rPr>
@@ -1991,7 +1991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{02CA6117-C4D7-5745-896B-480DD63BE6A1}">
+    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{5FABE4D9-3D28-2F49-BC65-70D2D2C88449}">
       <text>
         <r>
           <rPr>
@@ -2011,7 +2011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I91" authorId="0" shapeId="0" xr:uid="{452D3753-EC28-4A4E-B1BB-5AB51A732980}">
+    <comment ref="I91" authorId="0" shapeId="0" xr:uid="{F58AE13D-692D-AE4C-A6BC-BF6390C126CF}">
       <text>
         <r>
           <rPr>
@@ -2039,7 +2039,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I92" authorId="0" shapeId="0" xr:uid="{35488184-377F-F24C-8B08-F3E42FB1ABD7}">
+    <comment ref="I92" authorId="0" shapeId="0" xr:uid="{1E416B00-7685-3646-BD4D-8FBC35462593}">
       <text>
         <r>
           <rPr>
@@ -2054,7 +2054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I93" authorId="0" shapeId="0" xr:uid="{09906888-374A-664F-B3C2-6FDEB955205F}">
+    <comment ref="I93" authorId="0" shapeId="0" xr:uid="{2BC3AE11-3565-FA4D-82F2-0EA159544242}">
       <text>
         <r>
           <rPr>
@@ -2069,7 +2069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I94" authorId="0" shapeId="0" xr:uid="{2C97D463-78CB-2248-ADB6-4011C7CD2D34}">
+    <comment ref="I94" authorId="0" shapeId="0" xr:uid="{2F75E7AD-4725-8B41-AA1D-1675621578A5}">
       <text>
         <r>
           <rPr>
@@ -2085,7 +2085,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I95" authorId="0" shapeId="0" xr:uid="{9BA45FE4-35AC-B649-97C0-DA4178E405B1}">
+    <comment ref="I95" authorId="0" shapeId="0" xr:uid="{E166480C-4650-504D-9AA2-F68FF571B597}">
       <text>
         <r>
           <rPr>
@@ -2114,7 +2114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I96" authorId="0" shapeId="0" xr:uid="{DB6E78C3-79CA-AC4E-9D5D-08173D7687DB}">
+    <comment ref="I96" authorId="0" shapeId="0" xr:uid="{E31365FC-F7B3-D545-96AA-BE92B2474012}">
       <text>
         <r>
           <rPr>
@@ -2134,7 +2134,26 @@
         </r>
       </text>
     </comment>
-    <comment ref="I97" authorId="0" shapeId="0" xr:uid="{554DF9D0-6ED8-6246-A522-34AE8652864E}">
+    <comment ref="I97" authorId="0" shapeId="0" xr:uid="{B2CED603-1065-9B4E-A134-055A3B9FBEF4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>줄리: 이지수
+폴: 송유택
+나폴레옹: 김지민
+장: 안두호
+파리시장: 김아영
+예술가 대표: 허만</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I98" authorId="0" shapeId="0" xr:uid="{A573D570-9D04-1740-B68F-6E465D1F2E4E}">
       <text>
         <r>
           <rPr>
@@ -2154,7 +2173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I98" authorId="0" shapeId="0" xr:uid="{04A24BC8-84AD-2A44-8A53-B014A769BAA0}">
+    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{421554E7-0279-8A45-A58F-B48BBB9086FD}">
       <text>
         <r>
           <rPr>
@@ -2174,7 +2193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{9858D150-76D7-2B47-82D2-A095718EEA55}">
+    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{EFF7D8FE-6754-BB41-85B5-10E7642978DE}">
       <text>
         <r>
           <rPr>
@@ -2189,7 +2208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{385D2C40-D8A4-A74D-A114-822D28EE5386}">
+    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{81818C18-87F4-DF44-9B3F-A508E33402AF}">
       <text>
         <r>
           <rPr>
@@ -2218,7 +2237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{6C648FB0-3197-F941-9404-B7E41E1670AF}">
+    <comment ref="I102" authorId="0" shapeId="0" xr:uid="{56BAE108-6347-A442-810C-DAAC2833AF99}">
       <text>
         <r>
           <rPr>
@@ -2236,7 +2255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I102" authorId="0" shapeId="0" xr:uid="{CEA417D8-F70A-5444-9945-02822EA0246D}">
+    <comment ref="I103" authorId="0" shapeId="0" xr:uid="{FE5FE1A2-F209-6746-A60B-FA6D94429263}">
       <text>
         <r>
           <rPr>
@@ -2256,7 +2275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I103" authorId="0" shapeId="0" xr:uid="{7092F872-FADA-B74A-8AB9-E18F8E87C787}">
+    <comment ref="I104" authorId="0" shapeId="0" xr:uid="{E518287F-D224-514F-B526-B3CEE3F130E0}">
       <text>
         <r>
           <rPr>
@@ -2274,7 +2293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I104" authorId="0" shapeId="0" xr:uid="{6BC66DA3-37DD-6742-BE9C-9C6082BCE992}">
+    <comment ref="I105" authorId="0" shapeId="0" xr:uid="{1D7FD9D8-9352-8A48-B9FC-A1481E60BA0B}">
       <text>
         <r>
           <rPr>
@@ -2292,7 +2311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I105" authorId="0" shapeId="0" xr:uid="{0430E9A5-9A02-5D49-8A5C-5298E4757963}">
+    <comment ref="I106" authorId="0" shapeId="0" xr:uid="{EBBA18E0-4D1F-DC4F-945E-63144B49CDE2}">
       <text>
         <r>
           <rPr>
@@ -2312,7 +2331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I106" authorId="0" shapeId="0" xr:uid="{83D93102-8EAE-0D4D-982C-FEB7A9DA5DD4}">
+    <comment ref="I107" authorId="0" shapeId="0" xr:uid="{D4975286-B2E7-6140-BFFA-2F2A390682A1}">
       <text>
         <r>
           <rPr>
@@ -2327,7 +2346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I107" authorId="0" shapeId="0" xr:uid="{61DDED02-90ED-EB49-98DF-A15637DC6EA1}">
+    <comment ref="I108" authorId="0" shapeId="0" xr:uid="{D1316BE1-DA0A-BD4D-9A15-60661DB9203F}">
       <text>
         <r>
           <rPr>
@@ -2350,7 +2369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I108" authorId="0" shapeId="0" xr:uid="{EC60228D-BA2D-B14B-8506-D8690E0970B2}">
+    <comment ref="I109" authorId="0" shapeId="0" xr:uid="{EEE034F3-66FA-1A4C-8524-85B854610408}">
       <text>
         <r>
           <rPr>
@@ -2365,7 +2384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I109" authorId="0" shapeId="0" xr:uid="{4EB11D2B-43BC-A443-BAFD-30108A3091FF}">
+    <comment ref="I110" authorId="0" shapeId="0" xr:uid="{7AB2ED47-7A8B-5F43-90C6-FF1FEB0A99F0}">
       <text>
         <r>
           <rPr>
@@ -2380,7 +2399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I110" authorId="0" shapeId="0" xr:uid="{47A7EAAD-ACE1-9842-8496-36DE2E0CB9D2}">
+    <comment ref="I111" authorId="0" shapeId="0" xr:uid="{D927A0AC-C5DA-FF46-A2A1-8D1B6A851373}">
       <text>
         <r>
           <rPr>
@@ -2395,7 +2414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I111" authorId="0" shapeId="0" xr:uid="{688C6FDE-6EB9-B243-9882-FC65CA5EE91C}">
+    <comment ref="I112" authorId="0" shapeId="0" xr:uid="{DD7E1723-A48A-7249-8AFA-CB000E04949B}">
       <text>
         <r>
           <rPr>
@@ -2416,7 +2435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I112" authorId="0" shapeId="0" xr:uid="{42836E5B-8B2E-CC4F-B2AE-1DBE861F27A8}">
+    <comment ref="I113" authorId="0" shapeId="0" xr:uid="{BAC1104E-F19D-F045-AB76-5732761A7871}">
       <text>
         <r>
           <rPr>
@@ -2433,7 +2452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I113" authorId="0" shapeId="0" xr:uid="{786174C6-BC91-4943-A0B2-8B089BD2231B}">
+    <comment ref="I114" authorId="0" shapeId="0" xr:uid="{C765A7CA-A8A8-8944-8D53-C4A4073FD19C}">
       <text>
         <r>
           <rPr>
@@ -2448,26 +2467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I114" authorId="0" shapeId="0" xr:uid="{89181F40-37AC-9344-94D3-A690497EAD4C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>줄리: 이지수
-폴: 송유택
-나폴레옹: 김지민
-장: 안두호
-파리시장: 김아영
-예술가 대표: 허만</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I115" authorId="0" shapeId="0" xr:uid="{6F38EC56-C5D5-5842-9E46-B8D8AF115A0F}">
+    <comment ref="I115" authorId="0" shapeId="0" xr:uid="{51539A1E-87CB-1541-B86C-FD3859EF80CA}">
       <text>
         <r>
           <rPr>
@@ -2486,7 +2486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I116" authorId="0" shapeId="0" xr:uid="{D927FBAB-BDF9-A24C-86E8-7D38D2E88FEC}">
+    <comment ref="I116" authorId="0" shapeId="0" xr:uid="{C39AF620-7F96-6747-A1A4-EB74AD91C72C}">
       <text>
         <r>
           <rPr>
@@ -2503,7 +2503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I117" authorId="0" shapeId="0" xr:uid="{2F4663C6-1349-9246-834E-B8008E815E34}">
+    <comment ref="I117" authorId="0" shapeId="0" xr:uid="{C41654E3-A9C7-424E-95A0-E61057AEE435}">
       <text>
         <r>
           <rPr>
@@ -2529,7 +2529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I118" authorId="0" shapeId="0" xr:uid="{DECA7CA5-D192-9D49-BD64-8FFB8E6F0B0A}">
+    <comment ref="I118" authorId="0" shapeId="0" xr:uid="{CE7EA601-520B-9B43-BF02-99E189D5B579}">
       <text>
         <r>
           <rPr>
@@ -2546,7 +2546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I119" authorId="0" shapeId="0" xr:uid="{D1A24305-7666-B34F-B721-621F43B092F8}">
+    <comment ref="I119" authorId="0" shapeId="0" xr:uid="{3889F7FF-FF94-8E4D-B3D4-8987AAB11F0F}">
       <text>
         <r>
           <rPr>
@@ -2574,7 +2574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I120" authorId="0" shapeId="0" xr:uid="{E25887C0-BFA9-4748-9698-3B4CBD1B8ED4}">
+    <comment ref="I120" authorId="0" shapeId="0" xr:uid="{BB5A9008-50AB-B545-AB2D-F7315284065F}">
       <text>
         <r>
           <rPr>
@@ -2590,7 +2590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I121" authorId="0" shapeId="0" xr:uid="{9AE5BC78-11B4-954A-881B-59CC86FE6838}">
+    <comment ref="I121" authorId="0" shapeId="0" xr:uid="{FC363B1D-B247-EE4A-8997-8E513747754A}">
       <text>
         <r>
           <rPr>
@@ -2607,7 +2607,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I122" authorId="0" shapeId="0" xr:uid="{4CE2A148-F83A-7044-9761-4CB867388B93}">
+    <comment ref="I122" authorId="0" shapeId="0" xr:uid="{0FD67D6C-F4F2-4048-87B1-DB3E07E36581}">
       <text>
         <r>
           <rPr>
@@ -2623,7 +2623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I123" authorId="0" shapeId="0" xr:uid="{438FC682-F352-B245-99B7-315D53BC034A}">
+    <comment ref="I123" authorId="0" shapeId="0" xr:uid="{147CE88B-2A72-D24A-8512-25D126A32BAB}">
       <text>
         <r>
           <rPr>
@@ -2640,7 +2640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I124" authorId="0" shapeId="0" xr:uid="{351EED06-DA31-194D-8D6F-02ABEDCD9104}">
+    <comment ref="I124" authorId="0" shapeId="0" xr:uid="{ECC530B1-B8C9-094A-8946-2CE06D75F3D4}">
       <text>
         <r>
           <rPr>
@@ -2672,7 +2672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I125" authorId="0" shapeId="0" xr:uid="{5DEA4DCD-6A3D-F548-AB4E-D4989936A359}">
+    <comment ref="I125" authorId="0" shapeId="0" xr:uid="{67CE107F-291B-9A4E-9E9D-2FB7996674FF}">
       <text>
         <r>
           <rPr>
@@ -2691,7 +2691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I126" authorId="0" shapeId="0" xr:uid="{4DD775CB-CE02-5240-B9E3-D2260AB38F78}">
+    <comment ref="I126" authorId="0" shapeId="0" xr:uid="{86F6084E-52A6-7A47-BA27-0B79D5C19B19}">
       <text>
         <r>
           <rPr>
@@ -2709,7 +2709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I127" authorId="0" shapeId="0" xr:uid="{E0AC6CCE-64EA-3644-B4D5-AA0FAEFD13DB}">
+    <comment ref="I127" authorId="0" shapeId="0" xr:uid="{5980DF08-6106-8742-9DB3-84854E9BBBC0}">
       <text>
         <r>
           <rPr>
@@ -2724,7 +2724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I128" authorId="0" shapeId="0" xr:uid="{4E4B8D3A-36E3-134F-9CC2-078C8D0A8811}">
+    <comment ref="I128" authorId="0" shapeId="0" xr:uid="{674FC521-49C7-9D4A-956D-40898B9F5D93}">
       <text>
         <r>
           <rPr>
@@ -2741,7 +2741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I129" authorId="0" shapeId="0" xr:uid="{13BB3FA9-0CEE-D947-8708-B7FA58FF783F}">
+    <comment ref="I129" authorId="0" shapeId="0" xr:uid="{B13EFDF5-D849-C043-9148-A04590E387B3}">
       <text>
         <r>
           <rPr>
@@ -2758,7 +2758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I130" authorId="0" shapeId="0" xr:uid="{F5FEB7E7-6AE3-9F48-8C28-FC7BA852A75F}">
+    <comment ref="I130" authorId="0" shapeId="0" xr:uid="{B8F39F20-F2CF-FE4A-B27C-DED5AC061175}">
       <text>
         <r>
           <rPr>
@@ -2773,7 +2773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I131" authorId="0" shapeId="0" xr:uid="{A11358BF-2496-B248-AF84-719F45BA6A5D}">
+    <comment ref="I131" authorId="0" shapeId="0" xr:uid="{46E2FA38-5B8B-5E46-8E7F-D794C56CCCFB}">
       <text>
         <r>
           <rPr>
@@ -2792,7 +2792,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I132" authorId="0" shapeId="0" xr:uid="{9E9B5EAD-56DA-9A4F-BA45-3FD513A06506}">
+    <comment ref="I132" authorId="0" shapeId="0" xr:uid="{7CBFDA46-85C2-6643-968E-B00237057164}">
       <text>
         <r>
           <rPr>
@@ -2811,7 +2811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I133" authorId="0" shapeId="0" xr:uid="{06F965C0-AB3D-3547-84EC-E529E6C34F22}">
+    <comment ref="I133" authorId="0" shapeId="0" xr:uid="{32544447-79D9-0745-87AD-9BE84C33295F}">
       <text>
         <r>
           <rPr>
@@ -2828,7 +2828,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I134" authorId="0" shapeId="0" xr:uid="{28BC4A6A-E0D2-BD4D-9BB0-3AA310FA32EB}">
+    <comment ref="I134" authorId="0" shapeId="0" xr:uid="{19AF820A-66F8-FF4F-AB25-C22A556D319B}">
       <text>
         <r>
           <rPr>
@@ -2843,7 +2843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I135" authorId="0" shapeId="0" xr:uid="{CEB0FBCE-A125-0043-B3E7-738FCA90D81E}">
+    <comment ref="I135" authorId="0" shapeId="0" xr:uid="{C7EBA187-7E07-FA46-9F97-B72D34396F0C}">
       <text>
         <r>
           <rPr>
@@ -2859,7 +2859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I136" authorId="0" shapeId="0" xr:uid="{C3E8CF21-EBD7-7A41-AF43-CF16FCCB01AA}">
+    <comment ref="I136" authorId="0" shapeId="0" xr:uid="{42EACD4F-2BEC-9C46-B628-437C956D7A08}">
       <text>
         <r>
           <rPr>
@@ -2876,7 +2876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I137" authorId="0" shapeId="0" xr:uid="{D4FC8DF4-B3F4-3A42-8984-A6088A567F96}">
+    <comment ref="I137" authorId="0" shapeId="0" xr:uid="{6A875D1F-202F-314B-8A97-D6E68BFB4FC7}">
       <text>
         <r>
           <rPr>
@@ -2904,7 +2904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I138" authorId="0" shapeId="0" xr:uid="{01B8E751-752A-F14E-85C2-4DDFAF675C60}">
+    <comment ref="I138" authorId="0" shapeId="0" xr:uid="{80856D44-2EE2-D641-A813-0E994340826E}">
       <text>
         <r>
           <rPr>
@@ -2921,7 +2921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I139" authorId="0" shapeId="0" xr:uid="{539F12EA-4BED-3347-8D6E-3CD7B78F1D70}">
+    <comment ref="I139" authorId="0" shapeId="0" xr:uid="{54FE72E8-4F4C-D74F-9640-6A1CDDB51177}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I140" authorId="0" shapeId="0" xr:uid="{411AA7D5-A48C-0D44-BC4C-36A32A76CABF}">
+    <comment ref="I140" authorId="0" shapeId="0" xr:uid="{BECA2A22-FE05-2E4F-B803-1B9846ABAFA4}">
       <text>
         <r>
           <rPr>
@@ -2953,7 +2953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I141" authorId="0" shapeId="0" xr:uid="{2549CA9B-D035-D54B-9412-F93754BD8D8B}">
+    <comment ref="I141" authorId="0" shapeId="0" xr:uid="{E061FE7D-EF10-A246-9C9C-B9BB5EE9BA57}">
       <text>
         <r>
           <rPr>
@@ -2971,7 +2971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I142" authorId="0" shapeId="0" xr:uid="{18D0C71A-8BEE-D445-AB04-FA13F953B7E2}">
+    <comment ref="I142" authorId="0" shapeId="0" xr:uid="{C45CE467-09E1-2549-A2B4-3D823F415E99}">
       <text>
         <r>
           <rPr>
@@ -2989,7 +2989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I143" authorId="0" shapeId="0" xr:uid="{3B726C1E-CD55-AD45-8DD1-03A736160FFA}">
+    <comment ref="I143" authorId="0" shapeId="0" xr:uid="{A021A58D-4988-154F-B341-DD02DE236F21}">
       <text>
         <r>
           <rPr>
@@ -3005,7 +3005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I144" authorId="0" shapeId="0" xr:uid="{223733AC-2CE0-8242-AE42-F5E570E5918C}">
+    <comment ref="I144" authorId="0" shapeId="0" xr:uid="{9227589E-FFCE-284A-8492-619868DEBE19}">
       <text>
         <r>
           <rPr>
@@ -3022,7 +3022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I145" authorId="0" shapeId="0" xr:uid="{13151A57-60DF-E341-A739-BE629DCA16E7}">
+    <comment ref="I145" authorId="0" shapeId="0" xr:uid="{85109B89-3BF6-5546-BF3F-CD51B752BDAE}">
       <text>
         <r>
           <rPr>
@@ -3038,7 +3038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I146" authorId="0" shapeId="0" xr:uid="{3669B953-0FAF-FA49-91AB-727C101EBA50}">
+    <comment ref="I146" authorId="0" shapeId="0" xr:uid="{3CB4E5CC-B258-FD49-B641-BFB11012B5A8}">
       <text>
         <r>
           <rPr>
@@ -3055,7 +3055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I147" authorId="0" shapeId="0" xr:uid="{6044C59E-2B01-4544-962E-75ECCA54AE96}">
+    <comment ref="I147" authorId="0" shapeId="0" xr:uid="{E950008B-840D-C149-9450-E3924DB1C4A6}">
       <text>
         <r>
           <rPr>
@@ -3075,7 +3075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I148" authorId="0" shapeId="0" xr:uid="{6F1F8897-12A8-494E-A5F6-8EAFEECF5683}">
+    <comment ref="I148" authorId="0" shapeId="0" xr:uid="{8D25F71D-3575-4141-8344-47C45CB26205}">
       <text>
         <r>
           <rPr>
@@ -3110,7 +3110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I149" authorId="0" shapeId="0" xr:uid="{11E38DCE-B7A1-8246-8379-3949F9488DF9}">
+    <comment ref="I149" authorId="0" shapeId="0" xr:uid="{2E4000A1-E919-BB4C-BCC6-EB6D07BF38FC}">
       <text>
         <r>
           <rPr>
@@ -3126,7 +3126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I150" authorId="0" shapeId="0" xr:uid="{9A056C04-33A0-4844-B998-6B996830DBB7}">
+    <comment ref="I150" authorId="0" shapeId="0" xr:uid="{3947EEAA-A995-8B41-BEB1-A0FD30234CDA}">
       <text>
         <r>
           <rPr>
@@ -3148,7 +3148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I151" authorId="0" shapeId="0" xr:uid="{EC9A3410-43E8-EF49-95D0-2922801A0B53}">
+    <comment ref="I151" authorId="0" shapeId="0" xr:uid="{48642573-20DE-D34A-BD5D-F7F3EA6C81B6}">
       <text>
         <r>
           <rPr>
@@ -3172,7 +3172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I152" authorId="0" shapeId="0" xr:uid="{0FCBB893-13FF-7F43-8B14-6EA0EA6690F9}">
+    <comment ref="I152" authorId="0" shapeId="0" xr:uid="{BFC4FA42-9C9F-0B4C-9594-B3B96FF14160}">
       <text>
         <r>
           <rPr>
@@ -3190,7 +3190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I153" authorId="0" shapeId="0" xr:uid="{EEF72ED7-562C-214D-9763-45424171E510}">
+    <comment ref="I153" authorId="0" shapeId="0" xr:uid="{1BB3B919-5FB6-774B-94F1-B002B0F3C2A0}">
       <text>
         <r>
           <rPr>
@@ -3206,7 +3206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I154" authorId="0" shapeId="0" xr:uid="{D2676800-BA4A-8349-B7DC-902D09A0DEA6}">
+    <comment ref="I154" authorId="0" shapeId="0" xr:uid="{7C2016A5-A6EA-1244-BE29-ED9810917E4C}">
       <text>
         <r>
           <rPr>
@@ -3230,7 +3230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I155" authorId="0" shapeId="0" xr:uid="{BCBB97AF-204A-ED49-841C-B09F3C163E45}">
+    <comment ref="I155" authorId="0" shapeId="0" xr:uid="{4FDF1B6A-14B8-C940-8D1F-1F7BE89790E4}">
       <text>
         <r>
           <rPr>
@@ -3249,7 +3249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I156" authorId="0" shapeId="0" xr:uid="{160056C2-4CCE-154C-996F-CBC925435CAC}">
+    <comment ref="I156" authorId="0" shapeId="0" xr:uid="{DE4C174E-7C10-AC45-BE4A-FB0E68B24413}">
       <text>
         <r>
           <rPr>
@@ -3269,7 +3269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I157" authorId="0" shapeId="0" xr:uid="{CC7556D6-D56B-A440-A95D-46832582AB86}">
+    <comment ref="I157" authorId="0" shapeId="0" xr:uid="{4D4E3027-EF71-E440-872D-EDCADE1B9803}">
       <text>
         <r>
           <rPr>
@@ -3289,7 +3289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I158" authorId="0" shapeId="0" xr:uid="{15576226-79CE-4249-9C0F-F5369EF2F489}">
+    <comment ref="I158" authorId="0" shapeId="0" xr:uid="{08384CBE-E23C-3A40-811D-E1A0AE1CD9BE}">
       <text>
         <r>
           <rPr>
@@ -3309,7 +3309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I159" authorId="0" shapeId="0" xr:uid="{5F24F883-4C4C-1044-90D2-CCBEB4BD1A79}">
+    <comment ref="I159" authorId="0" shapeId="0" xr:uid="{D04D4256-68B9-684E-BAB4-EC281EE73E88}">
       <text>
         <r>
           <rPr>
@@ -3325,7 +3325,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I160" authorId="0" shapeId="0" xr:uid="{98009C0E-0427-2A49-988D-0ED8608032F6}">
+    <comment ref="I160" authorId="0" shapeId="0" xr:uid="{D7B03296-77DA-D94A-BCA7-48968460DD9A}">
       <text>
         <r>
           <rPr>
@@ -3349,7 +3349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I161" authorId="0" shapeId="0" xr:uid="{633373FA-7F67-B04C-A763-13D2A343F208}">
+    <comment ref="I161" authorId="0" shapeId="0" xr:uid="{CE921F55-8A34-7B44-95B2-10F737E8EB4D}">
       <text>
         <r>
           <rPr>
@@ -3373,7 +3373,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I162" authorId="0" shapeId="0" xr:uid="{74854367-C5B4-2849-9EE6-147F1EF35FD7}">
+    <comment ref="I162" authorId="0" shapeId="0" xr:uid="{29A6B29A-B823-5944-AB83-5C166F4750A1}">
       <text>
         <r>
           <rPr>
@@ -3397,7 +3397,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I163" authorId="0" shapeId="0" xr:uid="{20A56CD0-5ED5-DF42-827B-59C07AFB4871}">
+    <comment ref="I163" authorId="0" shapeId="0" xr:uid="{3A055752-9CE2-5040-83D6-2BEFB92FC86B}">
       <text>
         <r>
           <rPr>
@@ -3415,7 +3415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I164" authorId="0" shapeId="0" xr:uid="{1F40B8C0-6B3F-E244-B2E8-BF47BD5DAE50}">
+    <comment ref="I164" authorId="0" shapeId="0" xr:uid="{95BD731A-8093-FF48-AAEF-3A8FB7C8450E}">
       <text>
         <r>
           <rPr>
@@ -3437,7 +3437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I165" authorId="0" shapeId="0" xr:uid="{8BA7A651-6D2C-4D46-A810-A1649B062A54}">
+    <comment ref="I165" authorId="0" shapeId="0" xr:uid="{CBDD24E8-AA98-D74E-81AF-5180F66744FE}">
       <text>
         <r>
           <rPr>
@@ -3455,7 +3455,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I166" authorId="0" shapeId="0" xr:uid="{BF1F54F7-E857-524E-B194-31E431BA8E00}">
+    <comment ref="I166" authorId="0" shapeId="0" xr:uid="{F9565A2C-5159-BF49-BA3C-87FCEB856D79}">
       <text>
         <r>
           <rPr>
@@ -3471,7 +3471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I167" authorId="0" shapeId="0" xr:uid="{2619F29C-01E0-D14C-B507-D1BBCDDE981D}">
+    <comment ref="I167" authorId="0" shapeId="0" xr:uid="{4C5BD747-F694-5541-9982-3FA0ED9CA703}">
       <text>
         <r>
           <rPr>
@@ -3494,7 +3494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I168" authorId="0" shapeId="0" xr:uid="{645A7C6E-7D0E-654C-BF84-6175D5A6E024}">
+    <comment ref="I168" authorId="0" shapeId="0" xr:uid="{D316A72A-C247-3C48-BCA1-AB02A3CEC391}">
       <text>
         <r>
           <rPr>
@@ -3515,7 +3515,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I169" authorId="0" shapeId="0" xr:uid="{77CE9E23-E3CE-BB45-9080-B1168D313BF3}">
+    <comment ref="I169" authorId="0" shapeId="0" xr:uid="{8B9EE1E6-7E7E-8946-BD27-2BF350F64766}">
       <text>
         <r>
           <rPr>
@@ -3539,7 +3539,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I170" authorId="0" shapeId="0" xr:uid="{9CD0EFF4-6E84-2B4D-A4FA-6F75670F6830}">
+    <comment ref="I170" authorId="0" shapeId="0" xr:uid="{13A37E6A-7D19-C34F-BE24-B8CA42224F1C}">
       <text>
         <r>
           <rPr>
@@ -3559,7 +3559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I171" authorId="0" shapeId="0" xr:uid="{C985C666-763A-9C4B-AAF7-7CF4CFA0D487}">
+    <comment ref="I171" authorId="0" shapeId="0" xr:uid="{5F2573C9-825C-564D-A501-19C0E37B1787}">
       <text>
         <r>
           <rPr>
@@ -3574,7 +3574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I172" authorId="0" shapeId="0" xr:uid="{4326A905-DA00-5C42-A191-1D3B06BFF6E0}">
+    <comment ref="I172" authorId="0" shapeId="0" xr:uid="{31A91EF6-BAFC-9A48-9831-F4B1A56A8A99}">
       <text>
         <r>
           <rPr>
@@ -3589,7 +3589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I173" authorId="0" shapeId="0" xr:uid="{E9028E42-D9C3-C34E-99A8-D8C06E86C992}">
+    <comment ref="I173" authorId="0" shapeId="0" xr:uid="{22519804-8BCD-C34E-BC58-74BEDAE2E16E}">
       <text>
         <r>
           <rPr>
@@ -3605,7 +3605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I174" authorId="0" shapeId="0" xr:uid="{615AB082-7FDB-A243-BA25-57F968C85B3B}">
+    <comment ref="I174" authorId="0" shapeId="0" xr:uid="{071057B3-0EAA-8547-ADBF-6A4C35E00584}">
       <text>
         <r>
           <rPr>
@@ -3624,7 +3624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I175" authorId="0" shapeId="0" xr:uid="{CA074C9C-0A80-EB40-B974-C1573A07E8DF}">
+    <comment ref="I175" authorId="0" shapeId="0" xr:uid="{C1C105F0-2E66-6049-BBAB-A0B11E23E931}">
       <text>
         <r>
           <rPr>
@@ -3648,7 +3648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I176" authorId="0" shapeId="0" xr:uid="{9D00916D-DD97-194F-9C37-D906085ABA22}">
+    <comment ref="I176" authorId="0" shapeId="0" xr:uid="{BB5EDC35-9866-834F-A13A-644C116A9B76}">
       <text>
         <r>
           <rPr>
@@ -3666,7 +3666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I177" authorId="0" shapeId="0" xr:uid="{CA4E7BD7-3C29-824E-B7CD-BC18D956CEE4}">
+    <comment ref="I177" authorId="0" shapeId="0" xr:uid="{5B84EF85-448C-9D41-8203-B6C3661F2445}">
       <text>
         <r>
           <rPr>
@@ -3684,7 +3684,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I178" authorId="0" shapeId="0" xr:uid="{60B39967-1B56-9942-AB35-82C21CB46585}">
+    <comment ref="I178" authorId="0" shapeId="0" xr:uid="{164B0177-89C6-BD49-BCF8-9B858208A3D1}">
       <text>
         <r>
           <rPr>
@@ -3701,7 +3701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I179" authorId="0" shapeId="0" xr:uid="{79C160AB-ACC7-BF4B-9EB1-C94F22B5A894}">
+    <comment ref="I179" authorId="0" shapeId="0" xr:uid="{436AA8E6-B6CE-DB4D-B228-0988A39F7013}">
       <text>
         <r>
           <rPr>
@@ -3720,7 +3720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I180" authorId="0" shapeId="0" xr:uid="{56F8B40C-6F9A-EF45-93C3-6B5DA485629A}">
+    <comment ref="I180" authorId="0" shapeId="0" xr:uid="{A0B287DD-B256-0E42-9BEC-EA41DC73BF11}">
       <text>
         <r>
           <rPr>
@@ -3744,7 +3744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I181" authorId="0" shapeId="0" xr:uid="{AC97B8EA-FCA6-604C-924D-DDAAF0A3431A}">
+    <comment ref="I181" authorId="0" shapeId="0" xr:uid="{1F4A572A-2F76-664C-9F5D-F2F556C87D1C}">
       <text>
         <r>
           <rPr>
@@ -3779,7 +3779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I182" authorId="0" shapeId="0" xr:uid="{4A6C1F9E-D7D1-F24D-868B-0445C2FC72DC}">
+    <comment ref="I182" authorId="0" shapeId="0" xr:uid="{117D5AF1-AD9D-774A-96AB-0A92037B5B5F}">
       <text>
         <r>
           <rPr>
@@ -3794,7 +3794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I183" authorId="0" shapeId="0" xr:uid="{E59A70B0-1319-C04E-BBA5-FE42B454070E}">
+    <comment ref="I183" authorId="0" shapeId="0" xr:uid="{4D90051B-6820-C14E-A62D-CDE18E208691}">
       <text>
         <r>
           <rPr>
@@ -3809,7 +3809,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I184" authorId="0" shapeId="0" xr:uid="{91424D1C-4309-9349-9D32-D6FC8A3B52E8}">
+    <comment ref="I184" authorId="0" shapeId="0" xr:uid="{E7F5D5E2-799C-9044-81D8-4623F692AB8F}">
       <text>
         <r>
           <rPr>
@@ -3824,7 +3824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I185" authorId="0" shapeId="0" xr:uid="{FE97C994-A19B-8E44-A50A-AFA8FBC386ED}">
+    <comment ref="I185" authorId="0" shapeId="0" xr:uid="{EB02DD58-EC0D-3F4F-862E-EC9C52BD8513}">
       <text>
         <r>
           <rPr>
@@ -3839,7 +3839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I186" authorId="0" shapeId="0" xr:uid="{9984FC5E-196E-1C4D-8B30-EA457B3C839C}">
+    <comment ref="I186" authorId="0" shapeId="0" xr:uid="{0B7C1016-01EB-2845-8C7C-2DA10A957AF3}">
       <text>
         <r>
           <rPr>
@@ -3859,7 +3859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I187" authorId="0" shapeId="0" xr:uid="{E8C29792-56DF-5A47-9113-8B18C645BC61}">
+    <comment ref="I187" authorId="0" shapeId="0" xr:uid="{89C2EAD9-5633-AF4C-8659-3288C83CC6FF}">
       <text>
         <r>
           <rPr>
@@ -3879,7 +3879,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I188" authorId="0" shapeId="0" xr:uid="{A0D43A14-6136-B541-A950-C752F139F061}">
+    <comment ref="I188" authorId="0" shapeId="0" xr:uid="{FCFD5F23-6F3D-E548-8A9B-90F1E97FB114}">
       <text>
         <r>
           <rPr>
@@ -3912,7 +3912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I189" authorId="0" shapeId="0" xr:uid="{3A178F90-3197-F440-BE71-F3652C6C8017}">
+    <comment ref="I189" authorId="0" shapeId="0" xr:uid="{9125247B-F766-074F-AD57-D1CB85990309}">
       <text>
         <r>
           <rPr>
@@ -3928,7 +3928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I190" authorId="0" shapeId="0" xr:uid="{223FA533-58F0-CB44-92D3-37EB17835345}">
+    <comment ref="I190" authorId="0" shapeId="0" xr:uid="{6E72403C-0C8B-2248-A1CD-7FF2D67A7D08}">
       <text>
         <r>
           <rPr>
@@ -3943,7 +3943,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I191" authorId="0" shapeId="0" xr:uid="{A27BA0CA-13F8-3F48-922D-3B9385B6C5BC}">
+    <comment ref="I191" authorId="0" shapeId="0" xr:uid="{A5FAE39A-1B38-B045-A748-52D7B9325F2F}">
       <text>
         <r>
           <rPr>
@@ -3958,7 +3958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I192" authorId="0" shapeId="0" xr:uid="{B85111F4-6B59-3A4B-B694-F051FD0194FB}">
+    <comment ref="I192" authorId="0" shapeId="0" xr:uid="{8FB5DB90-7AD5-9241-B33A-80732DDF2528}">
       <text>
         <r>
           <rPr>
@@ -3973,7 +3973,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I193" authorId="0" shapeId="0" xr:uid="{70572FCD-A432-CF4F-9025-060046FB087B}">
+    <comment ref="I193" authorId="0" shapeId="0" xr:uid="{EDB8F71F-2A7E-5646-BC03-FBA030E501A3}">
       <text>
         <r>
           <rPr>
@@ -3989,7 +3989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I194" authorId="0" shapeId="0" xr:uid="{6661265D-7F9A-B541-87B4-3D2FFE54B519}">
+    <comment ref="I194" authorId="0" shapeId="0" xr:uid="{D4333EB8-E360-A443-B235-A8C934B18F6D}">
       <text>
         <r>
           <rPr>
@@ -4004,7 +4004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I195" authorId="0" shapeId="0" xr:uid="{B7F54D7C-35D4-E048-AAE3-DE71A8619C9A}">
+    <comment ref="I195" authorId="0" shapeId="0" xr:uid="{F04AEBEA-390C-0F48-9D0D-619F98ABD9F4}">
       <text>
         <r>
           <rPr>
@@ -4020,7 +4020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I196" authorId="0" shapeId="0" xr:uid="{CE733703-E23C-C244-8197-6695A94E47F9}">
+    <comment ref="I196" authorId="0" shapeId="0" xr:uid="{5A683168-70D3-4640-8DB4-FD40942C4EA4}">
       <text>
         <r>
           <rPr>
@@ -4041,7 +4041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I197" authorId="0" shapeId="0" xr:uid="{8AC80EE1-E2EA-9A49-AD05-A6E1145B5C31}">
+    <comment ref="I197" authorId="0" shapeId="0" xr:uid="{B5216970-205E-FA43-ACFE-CA2A389723B4}">
       <text>
         <r>
           <rPr>
@@ -4059,7 +4059,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I198" authorId="0" shapeId="0" xr:uid="{A1286D2D-D037-324B-A29E-EEE145BFDFCC}">
+    <comment ref="I198" authorId="0" shapeId="0" xr:uid="{EA9B0E80-22D2-624E-A228-734980C72D7E}">
       <text>
         <r>
           <rPr>
@@ -4077,7 +4077,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I199" authorId="0" shapeId="0" xr:uid="{3156D56E-F488-824F-BE00-4029403A932C}">
+    <comment ref="I199" authorId="0" shapeId="0" xr:uid="{CDB17DA3-8378-A244-90C1-02E8AB9AAED4}">
       <text>
         <r>
           <rPr>
@@ -4098,27 +4098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I200" authorId="0" shapeId="0" xr:uid="{B79D007E-0141-894C-95F7-7457828CEEDB}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>원류환: 백승렬
-리해랑: 박준후
-리해진: 김지온
-란&amp;순임: 박채원
-김태원: 서승원
-서수혁/조두석: 정휘욱
-국정원: 박시윤, 이진우(은)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I201" authorId="0" shapeId="0" xr:uid="{7E53F753-0A8E-2948-836E-3446F310B9F3}">
+    <comment ref="I200" authorId="0" shapeId="0" xr:uid="{B468284B-0992-A34B-A450-E96EDBFDE9B5}">
       <text>
         <r>
           <rPr>
@@ -4133,7 +4113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I202" authorId="0" shapeId="0" xr:uid="{7868AD6D-D823-3C41-9257-A0C6E6612A6B}">
+    <comment ref="I201" authorId="0" shapeId="0" xr:uid="{92452682-12D5-254B-A74B-D7430C0AA186}">
       <text>
         <r>
           <rPr>
@@ -4161,7 +4141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I203" authorId="0" shapeId="0" xr:uid="{2E4D0485-4F82-FB4F-9C14-65BCBA6F05E2}">
+    <comment ref="I202" authorId="0" shapeId="0" xr:uid="{812F7FBE-1F98-CB44-AEE2-99B0565226E5}">
       <text>
         <r>
           <rPr>
@@ -4178,7 +4158,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="I204" authorId="0" shapeId="0" xr:uid="{F694A8FE-0542-764B-A677-06A66B205A73}">
+    <comment ref="I203" authorId="0" shapeId="0" xr:uid="{47E9B674-E4C6-FF4D-9D17-1AD3C69E1996}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>원류환: 백승렬
+리해랑: 박준후
+리해진: 김지온
+란&amp;순임: 박채원
+김태원: 서승원
+서수혁/조두석: 정휘욱
+국정원: 박시윤, 이진우(은)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I204" authorId="0" shapeId="0" xr:uid="{839F06B0-F249-BE4B-85B1-9A710E8114E4}">
       <text>
         <r>
           <rPr>
@@ -4194,7 +4194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I205" authorId="0" shapeId="0" xr:uid="{26C481DA-86DE-8443-86B5-E25524C0E319}">
+    <comment ref="I205" authorId="0" shapeId="0" xr:uid="{1B259CFC-3E3E-3D40-BA15-6F04E2873B6D}">
       <text>
         <r>
           <rPr>
@@ -4210,7 +4210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I206" authorId="0" shapeId="0" xr:uid="{2F874602-B2F6-684D-9176-67BC0AEC00BB}">
+    <comment ref="I206" authorId="0" shapeId="0" xr:uid="{81AAA624-E704-D549-B2F6-056F075F8DB2}">
       <text>
         <r>
           <rPr>
@@ -4235,7 +4235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I207" authorId="0" shapeId="0" xr:uid="{4FEEA9FB-7BB7-3944-AB9E-3186A702FC6C}">
+    <comment ref="I207" authorId="0" shapeId="0" xr:uid="{C0944842-3122-1344-AA7E-D02508641087}">
       <text>
         <r>
           <rPr>
@@ -4254,7 +4254,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I208" authorId="0" shapeId="0" xr:uid="{A69C39ED-2DB1-1C44-A2B1-B7259712DD3C}">
+    <comment ref="I208" authorId="0" shapeId="0" xr:uid="{6EA7E5F6-4789-F547-8A8C-2566D1310F88}">
       <text>
         <r>
           <rPr>
@@ -4273,7 +4273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I209" authorId="0" shapeId="0" xr:uid="{F3F6EE42-94DB-6A49-8DC2-E0D49A53D05E}">
+    <comment ref="I209" authorId="0" shapeId="0" xr:uid="{F35979FA-3961-E44B-B5C1-135DC2F1CCF6}">
       <text>
         <r>
           <rPr>
@@ -4290,7 +4290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I210" authorId="0" shapeId="0" xr:uid="{3D682493-3D70-C243-82C0-0D6B7CB19544}">
+    <comment ref="I210" authorId="0" shapeId="0" xr:uid="{14221F75-B92B-014D-AC28-689AED83B2D7}">
       <text>
         <r>
           <rPr>
@@ -4310,7 +4310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I211" authorId="0" shapeId="0" xr:uid="{F5A6F1EB-CDA3-8842-86E0-1AACB90147E1}">
+    <comment ref="I211" authorId="0" shapeId="0" xr:uid="{1AFF5738-6116-9743-99EA-0374CC182309}">
       <text>
         <r>
           <rPr>
@@ -4332,7 +4332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I212" authorId="0" shapeId="0" xr:uid="{0E3C114D-20BD-BB4D-83F8-FB30201BA20C}">
+    <comment ref="I212" authorId="0" shapeId="0" xr:uid="{86A6294D-4859-6043-8585-56AB21CA61BA}">
       <text>
         <r>
           <rPr>
@@ -4348,7 +4348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I213" authorId="0" shapeId="0" xr:uid="{750893C4-ADCA-D844-9693-897B00B3A67D}">
+    <comment ref="I213" authorId="0" shapeId="0" xr:uid="{49890B61-8C18-0E41-B4F8-9A0FAB7B611C}">
       <text>
         <r>
           <rPr>
@@ -4364,7 +4364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I214" authorId="0" shapeId="0" xr:uid="{2228C4E0-10EB-1649-870A-9DF6B22D330F}">
+    <comment ref="I214" authorId="0" shapeId="0" xr:uid="{269A437A-3917-2940-BA9A-29F1B12DA4BA}">
       <text>
         <r>
           <rPr>
@@ -4386,7 +4386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I215" authorId="0" shapeId="0" xr:uid="{A33BCC86-0252-B149-B9C5-E9BC0537E168}">
+    <comment ref="I215" authorId="0" shapeId="0" xr:uid="{96237709-ECB9-8847-B521-F1FAE429DA77}">
       <text>
         <r>
           <rPr>
@@ -4406,7 +4406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I216" authorId="0" shapeId="0" xr:uid="{37E1D306-4565-1C45-B17B-151D40795A9B}">
+    <comment ref="I216" authorId="0" shapeId="0" xr:uid="{85DC2582-390C-FB45-8186-7509F0CA5628}">
       <text>
         <r>
           <rPr>
@@ -4422,7 +4422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I217" authorId="0" shapeId="0" xr:uid="{F6EB4693-A0CB-BC42-AE12-D44633FBFFA6}">
+    <comment ref="I217" authorId="0" shapeId="0" xr:uid="{89D65983-C25F-4943-BFEE-03B733A96E1B}">
       <text>
         <r>
           <rPr>
@@ -4439,7 +4439,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I218" authorId="0" shapeId="0" xr:uid="{F9C093ED-0B00-6848-933C-36B96D8B5A3F}">
+    <comment ref="I218" authorId="0" shapeId="0" xr:uid="{ED3F166D-5560-8049-9F6C-E04D028DA181}">
       <text>
         <r>
           <rPr>
@@ -4459,7 +4459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I219" authorId="0" shapeId="0" xr:uid="{22A58E15-959B-3E4C-9524-197B0796AAAA}">
+    <comment ref="I219" authorId="0" shapeId="0" xr:uid="{EE0365F7-547A-8642-A2B0-6802BBEE6428}">
       <text>
         <r>
           <rPr>
@@ -4474,7 +4474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I220" authorId="0" shapeId="0" xr:uid="{98BE51C9-6374-3D46-A73A-B1AEA2F08A32}">
+    <comment ref="I220" authorId="0" shapeId="0" xr:uid="{CC51C6C1-8492-624C-AD86-CA85BAB1ABE2}">
       <text>
         <r>
           <rPr>
@@ -4496,7 +4496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I221" authorId="0" shapeId="0" xr:uid="{F98FD835-E0A5-2A4C-A2D7-94A240FC2122}">
+    <comment ref="I221" authorId="0" shapeId="0" xr:uid="{DC59DD29-EDD5-5D47-8E1B-0CF5FAC0FE84}">
       <text>
         <r>
           <rPr>
@@ -4518,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I222" authorId="0" shapeId="0" xr:uid="{FE6B1FBE-794F-C24C-8693-75C37B878C50}">
+    <comment ref="I222" authorId="0" shapeId="0" xr:uid="{4D224EF0-CEB4-5B45-9790-81D72F4EBB60}">
       <text>
         <r>
           <rPr>
@@ -4551,7 +4551,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I223" authorId="0" shapeId="0" xr:uid="{01CC7921-3E4B-2F4A-B712-179559E0DC2D}">
+    <comment ref="I223" authorId="0" shapeId="0" xr:uid="{A71C6DD6-C5AA-944F-84C5-907821A5E125}">
       <text>
         <r>
           <rPr>
@@ -4581,7 +4581,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I224" authorId="0" shapeId="0" xr:uid="{8AB8BD0B-EC9E-CE49-9074-775613A7A1E1}">
+    <comment ref="I224" authorId="0" shapeId="0" xr:uid="{C2D07236-DB59-D841-AE27-A0AE8ED91FAF}">
       <text>
         <r>
           <rPr>
@@ -4596,7 +4596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I225" authorId="0" shapeId="0" xr:uid="{F11F8BB8-23F0-1A44-8A01-04349690DA79}">
+    <comment ref="I225" authorId="0" shapeId="0" xr:uid="{AF9630B9-68F5-B040-AF9F-AB3B9482BC6C}">
       <text>
         <r>
           <rPr>
@@ -4615,7 +4615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I226" authorId="0" shapeId="0" xr:uid="{84DE76C6-F9E4-794A-977A-DCEAC712087C}">
+    <comment ref="I226" authorId="0" shapeId="0" xr:uid="{99590F93-0EF6-544F-B67B-9EB2A62E38D2}">
       <text>
         <r>
           <rPr>
@@ -4633,7 +4633,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I227" authorId="0" shapeId="0" xr:uid="{F9E049CB-CE60-1B49-8B82-B9DB9E24332D}">
+    <comment ref="I227" authorId="0" shapeId="0" xr:uid="{9544A8CD-1F0B-1D46-A509-F38A7586FA2F}">
       <text>
         <r>
           <rPr>
@@ -4660,7 +4660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I228" authorId="0" shapeId="0" xr:uid="{3DEEFF4F-7737-F343-9FA7-D7532AFABAEF}">
+    <comment ref="I228" authorId="0" shapeId="0" xr:uid="{C17103A1-4D38-8746-8FDC-FD0BEB34E4BF}">
       <text>
         <r>
           <rPr>
@@ -4675,7 +4675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I229" authorId="0" shapeId="0" xr:uid="{DDCD001A-D1D5-2E45-A962-E9799F7627D2}">
+    <comment ref="I229" authorId="0" shapeId="0" xr:uid="{EA5D666F-E335-384A-BB06-52F0E3EF6314}">
       <text>
         <r>
           <rPr>
@@ -4694,7 +4694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I230" authorId="0" shapeId="0" xr:uid="{F2DF7E15-E636-4147-9B0C-8952B1D3282B}">
+    <comment ref="I230" authorId="0" shapeId="0" xr:uid="{B0AD2759-17C1-2A49-8889-F252247A51BD}">
       <text>
         <r>
           <rPr>
@@ -4710,7 +4710,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I231" authorId="0" shapeId="0" xr:uid="{18B2209A-D24F-6147-84A7-5BE91C9E24B8}">
+    <comment ref="I231" authorId="0" shapeId="0" xr:uid="{957265A3-AC30-6E49-95F3-F635D7D07162}">
       <text>
         <r>
           <rPr>
@@ -4738,7 +4738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I232" authorId="0" shapeId="0" xr:uid="{4169A6EF-FC4A-1A49-84DC-DFA71FCD8D8D}">
+    <comment ref="I232" authorId="0" shapeId="0" xr:uid="{8300C6B5-DC99-7848-8BD3-43F4C8421A53}">
       <text>
         <r>
           <rPr>
@@ -4758,7 +4758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I233" authorId="0" shapeId="0" xr:uid="{BDD6A7C0-76D1-3443-B3D5-BF31ADA12064}">
+    <comment ref="I233" authorId="0" shapeId="0" xr:uid="{73607A05-07D3-7B4D-B855-3B7798B1F1B1}">
       <text>
         <r>
           <rPr>
@@ -4783,7 +4783,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I234" authorId="0" shapeId="0" xr:uid="{986EFFAE-5591-3345-A47F-9741111C9E7D}">
+    <comment ref="I234" authorId="0" shapeId="0" xr:uid="{C4F58FE0-C8F7-2C40-8496-875971400199}">
       <text>
         <r>
           <rPr>
@@ -4799,7 +4799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I235" authorId="0" shapeId="0" xr:uid="{3FA396EC-5EE5-2C4B-8ABD-82CE0A59FCD1}">
+    <comment ref="I235" authorId="0" shapeId="0" xr:uid="{A2E780F8-0CE9-3844-8B29-56E8FD485C4C}">
       <text>
         <r>
           <rPr>
@@ -4815,7 +4815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I236" authorId="0" shapeId="0" xr:uid="{A4644E5E-CC62-5B4B-8E07-4F495CE858FF}">
+    <comment ref="I236" authorId="0" shapeId="0" xr:uid="{8ABD1331-8495-1844-BD9C-B8682A53282A}">
       <text>
         <r>
           <rPr>
@@ -4831,7 +4831,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I237" authorId="0" shapeId="0" xr:uid="{E5DFD759-3DEA-2944-95F7-03E0851EEDC3}">
+    <comment ref="I237" authorId="0" shapeId="0" xr:uid="{6CFD5E53-E3F9-344E-8E42-CDAA1AAADAAC}">
       <text>
         <r>
           <rPr>
@@ -4850,7 +4850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I238" authorId="0" shapeId="0" xr:uid="{0018C6F7-4D3C-AE4F-816A-F6FA335D4A77}">
+    <comment ref="I238" authorId="0" shapeId="0" xr:uid="{8C79D6B3-1268-2B44-9F33-07E502B3E778}">
       <text>
         <r>
           <rPr>
@@ -4865,7 +4865,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I239" authorId="0" shapeId="0" xr:uid="{626366B8-C1E2-8347-A1F6-879C7B19FE74}">
+    <comment ref="I239" authorId="0" shapeId="0" xr:uid="{CE807C49-A316-7047-A0BF-CC26F3401AE9}">
       <text>
         <r>
           <rPr>
@@ -4887,7 +4887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I240" authorId="0" shapeId="0" xr:uid="{6A4C9809-7D30-9442-BD6F-FDF4F58F3E7C}">
+    <comment ref="I240" authorId="0" shapeId="0" xr:uid="{1AF20C0E-43C5-EB43-903D-B3F24C074477}">
       <text>
         <r>
           <rPr>
@@ -4903,7 +4903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I241" authorId="0" shapeId="0" xr:uid="{0CFCF291-1D85-A347-91AA-04FCC6EC3C37}">
+    <comment ref="I241" authorId="0" shapeId="0" xr:uid="{C8A08F2A-C818-724B-B087-08400DCCB90B}">
       <text>
         <r>
           <rPr>
@@ -4921,7 +4921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I242" authorId="0" shapeId="0" xr:uid="{6FFDAEFF-0978-5C40-BD83-A331ADBA67E3}">
+    <comment ref="I242" authorId="0" shapeId="0" xr:uid="{4F9AC0AD-5B95-6D4C-9126-8AA6E0C341F7}">
       <text>
         <r>
           <rPr>
@@ -4937,7 +4937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I243" authorId="0" shapeId="0" xr:uid="{4838D205-F2DC-A943-A973-DE0EEEE53516}">
+    <comment ref="I243" authorId="0" shapeId="0" xr:uid="{431213A2-AE3D-7544-B810-1F6DC760CCC2}">
       <text>
         <r>
           <rPr>
@@ -4953,7 +4953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I244" authorId="0" shapeId="0" xr:uid="{292C7902-5F86-1A49-8877-4837D5CF07D3}">
+    <comment ref="I244" authorId="0" shapeId="0" xr:uid="{1C619983-8028-5543-86D0-1946447DC08B}">
       <text>
         <r>
           <rPr>
@@ -4969,7 +4969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I245" authorId="0" shapeId="0" xr:uid="{EF13EC48-B3E4-C54F-B7B4-502F1B761675}">
+    <comment ref="I245" authorId="0" shapeId="0" xr:uid="{1D2F427C-0BCF-3C4E-A8D8-8AA9741170C1}">
       <text>
         <r>
           <rPr>
@@ -4985,7 +4985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I246" authorId="0" shapeId="0" xr:uid="{F51AA0E3-E628-2342-B700-9E175992977B}">
+    <comment ref="I246" authorId="0" shapeId="0" xr:uid="{E7ABA0AC-24F7-3044-B733-7F1DCDB0288B}">
       <text>
         <r>
           <rPr>
@@ -5000,7 +5000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I247" authorId="0" shapeId="0" xr:uid="{85A65FE1-C8A8-9F49-9533-271963148EEF}">
+    <comment ref="I247" authorId="0" shapeId="0" xr:uid="{76C01643-7F34-DD47-9732-BC158D88F82A}">
       <text>
         <r>
           <rPr>
@@ -5016,7 +5016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I248" authorId="0" shapeId="0" xr:uid="{D2018D53-66D8-0F47-ADBC-4AF0FC57DA3A}">
+    <comment ref="I248" authorId="0" shapeId="0" xr:uid="{EA929610-5460-4041-8761-08825E8C622C}">
       <text>
         <r>
           <rPr>
@@ -5031,7 +5031,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I249" authorId="0" shapeId="0" xr:uid="{42EA8B0B-BCC2-9446-99A2-2FB4DC9AD21D}">
+    <comment ref="I249" authorId="0" shapeId="0" xr:uid="{1199F00C-01BB-7249-B244-011DA3DAF041}">
       <text>
         <r>
           <rPr>
@@ -5050,7 +5050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I250" authorId="0" shapeId="0" xr:uid="{B27B8CC8-F4BD-4D47-B5EB-37EFEC4E32DF}">
+    <comment ref="I250" authorId="0" shapeId="0" xr:uid="{945D763F-1948-8846-9C4C-87ABEA1921C5}">
       <text>
         <r>
           <rPr>
@@ -5066,7 +5066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I251" authorId="0" shapeId="0" xr:uid="{A3D0FFAC-4DC7-1F4C-9FF2-5E0E0D7AA155}">
+    <comment ref="I251" authorId="0" shapeId="0" xr:uid="{16F0DF82-F1EF-7240-A407-AAD0B87B2B4D}">
       <text>
         <r>
           <rPr>
@@ -5085,7 +5085,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I252" authorId="0" shapeId="0" xr:uid="{0AC219BF-3D79-A741-9C3A-F5A6D7C3F7BA}">
+    <comment ref="I252" authorId="0" shapeId="0" xr:uid="{58E97A43-73E7-2741-A445-E932617AE992}">
       <text>
         <r>
           <rPr>
@@ -5113,7 +5113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I253" authorId="0" shapeId="0" xr:uid="{72A6FE97-3ACA-B84D-9BED-EACAEC850B05}">
+    <comment ref="I253" authorId="0" shapeId="0" xr:uid="{E0DBAC3C-D555-4845-90DC-FB5F3DB841B2}">
       <text>
         <r>
           <rPr>
@@ -5129,7 +5129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I254" authorId="0" shapeId="0" xr:uid="{4F460B72-89EF-5245-BC03-3613FC91E42F}">
+    <comment ref="I254" authorId="0" shapeId="0" xr:uid="{AE9D47E5-D105-0D49-BE13-3C03680F8920}">
       <text>
         <r>
           <rPr>
@@ -5156,7 +5156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I255" authorId="0" shapeId="0" xr:uid="{02D2F2DC-5BF0-154B-81B7-31E907EFFD50}">
+    <comment ref="I255" authorId="0" shapeId="0" xr:uid="{43E17A9A-994E-DB42-A50E-3DA30DD8AD6B}">
       <text>
         <r>
           <rPr>
@@ -5172,7 +5172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I256" authorId="0" shapeId="0" xr:uid="{3C9A3135-A866-8743-AE98-69E5DFBCF6E4}">
+    <comment ref="I256" authorId="0" shapeId="0" xr:uid="{1BCA1835-4BE2-9040-BFF6-FDF9DD5C29BE}">
       <text>
         <r>
           <rPr>
@@ -5187,7 +5187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I257" authorId="0" shapeId="0" xr:uid="{3E9DA68E-DC9D-BD4D-8C20-364A58B429BE}">
+    <comment ref="I257" authorId="0" shapeId="0" xr:uid="{39A132FD-A010-D948-AB73-588C65BA73BE}">
       <text>
         <r>
           <rPr>
@@ -5203,7 +5203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I258" authorId="0" shapeId="0" xr:uid="{E7A3D9FB-38FD-CC41-B343-46786FD3BBA1}">
+    <comment ref="I258" authorId="0" shapeId="0" xr:uid="{912D9B8C-A855-3441-8906-EF4F83C000D2}">
       <text>
         <r>
           <rPr>
@@ -5222,7 +5222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I259" authorId="0" shapeId="0" xr:uid="{B8F37015-5940-B047-A9FF-C012CDECF528}">
+    <comment ref="I259" authorId="0" shapeId="0" xr:uid="{3E8246A5-8112-0643-8C26-6E84E4E91A09}">
       <text>
         <r>
           <rPr>
@@ -5237,7 +5237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I260" authorId="0" shapeId="0" xr:uid="{288E69D0-D8AA-CD4A-9054-5CED728BEFDB}">
+    <comment ref="I260" authorId="0" shapeId="0" xr:uid="{054FBA84-E5CB-A941-9608-B43D29CC1469}">
       <text>
         <r>
           <rPr>
@@ -5253,7 +5253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I261" authorId="0" shapeId="0" xr:uid="{3877BBC3-E3EE-844E-AD98-B68FEFB5FEF1}">
+    <comment ref="I261" authorId="0" shapeId="0" xr:uid="{240FC08D-E48F-BB4A-9239-513B5309EF91}">
       <text>
         <r>
           <rPr>
@@ -5271,7 +5271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I262" authorId="0" shapeId="0" xr:uid="{FC5A8A96-56CE-A94C-A28B-9E9B6AD52C76}">
+    <comment ref="I262" authorId="0" shapeId="0" xr:uid="{E15A5941-DC42-4B4B-A598-D9589698430A}">
       <text>
         <r>
           <rPr>
@@ -5287,7 +5287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I263" authorId="0" shapeId="0" xr:uid="{07BF76DC-7398-1543-8EE9-F9CEE66AB5E2}">
+    <comment ref="I263" authorId="0" shapeId="0" xr:uid="{3733C530-92E3-2746-92E3-C6F2050D0247}">
       <text>
         <r>
           <rPr>
@@ -5306,7 +5306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I264" authorId="0" shapeId="0" xr:uid="{3C5807E6-3998-A948-B09F-0787B35D906A}">
+    <comment ref="I264" authorId="0" shapeId="0" xr:uid="{C5E37D09-42B6-124F-9B5B-F8D6FC6B0CB1}">
       <text>
         <r>
           <rPr>
@@ -5322,7 +5322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I265" authorId="0" shapeId="0" xr:uid="{6C3B961F-AB63-5B40-9C29-BBAE1B7AD78D}">
+    <comment ref="I265" authorId="0" shapeId="0" xr:uid="{47517282-36D9-D641-82EC-1CED2AB212F4}">
       <text>
         <r>
           <rPr>
@@ -5340,7 +5340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I266" authorId="0" shapeId="0" xr:uid="{0E53366E-1FC0-7F41-859E-C456042FFEA8}">
+    <comment ref="I266" authorId="0" shapeId="0" xr:uid="{3C71BDF8-D897-DA46-A09E-85390415B281}">
       <text>
         <r>
           <rPr>
@@ -5358,7 +5358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I267" authorId="0" shapeId="0" xr:uid="{96B71664-5AE9-8545-AB28-2B7B4E36FCDE}">
+    <comment ref="I267" authorId="0" shapeId="0" xr:uid="{7DE5CDC8-1FBF-6F46-AD40-4C6A3D27B52A}">
       <text>
         <r>
           <rPr>
@@ -5376,7 +5376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I268" authorId="0" shapeId="0" xr:uid="{0E539068-1A86-0E44-B915-5D968E60F598}">
+    <comment ref="I268" authorId="0" shapeId="0" xr:uid="{530F2B7A-B68B-EB4F-B4FF-45FC50A574B8}">
       <text>
         <r>
           <rPr>
@@ -5391,7 +5391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I269" authorId="0" shapeId="0" xr:uid="{826F2D43-B644-A941-B891-33F479B36F11}">
+    <comment ref="I269" authorId="0" shapeId="0" xr:uid="{36E682A9-1E70-9E4C-BD12-E4D111EDC3C5}">
       <text>
         <r>
           <rPr>
@@ -5410,7 +5410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I270" authorId="0" shapeId="0" xr:uid="{E1A454D7-5EF8-5C42-87F1-C2C4E142EF6D}">
+    <comment ref="I270" authorId="0" shapeId="0" xr:uid="{9ED5BCD5-97A5-C340-BBF1-5D8E78DF1775}">
       <text>
         <r>
           <rPr>
@@ -5426,7 +5426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I271" authorId="0" shapeId="0" xr:uid="{FC917A25-4785-BC4F-85E8-4ED9ED3AAD3E}">
+    <comment ref="I271" authorId="0" shapeId="0" xr:uid="{2071FD22-4DFC-3449-895E-CC6B45E0386D}">
       <text>
         <r>
           <rPr>
@@ -5444,7 +5444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I272" authorId="0" shapeId="0" xr:uid="{D6333E44-50BA-CF43-B3D9-8E9D2B76D9C9}">
+    <comment ref="I272" authorId="0" shapeId="0" xr:uid="{306C747A-F5EE-2E4B-8C75-4C4D9794CEFB}">
       <text>
         <r>
           <rPr>
@@ -5460,356 +5460,42 @@
         </r>
       </text>
     </comment>
-    <comment ref="I273" authorId="0" shapeId="0" xr:uid="{D52C1F81-49FD-B441-B1D6-1D054732415A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루크</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윤형렬</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>테오</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김산호</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>존</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루키페르</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최민철</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>헤이든</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>허혜진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>엠마</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김명희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>사일러스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>조환지</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I274" authorId="0" shapeId="0" xr:uid="{9E3F812F-506C-4846-A51B-2B66143B4394}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>동현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박건</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>봉수</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박정원</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>수아</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박란주</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I275" authorId="0" shapeId="0" xr:uid="{4B3BEC3C-BD36-9C4B-99FE-FE5539A8661E}">
+    <comment ref="I273" authorId="0" shapeId="0" xr:uid="{13BE408C-30E9-2241-BD90-763797FB11FC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>루크: 윤형렬
+테오: 김산호
+존 루키페르: 최민철
+헤이든: 허혜진
+엠마: 김명희
+사일러스: 조환지</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I274" authorId="0" shapeId="0" xr:uid="{61AE0156-5C9B-7C4F-932D-6F440BCEC2E4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>동현: 박건
+봉수: 박정원
+수아: 박란주</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I275" authorId="0" shapeId="0" xr:uid="{25A24806-E75C-7A44-9096-10AF7C8C3054}">
       <text>
         <r>
           <rPr>
@@ -5825,7 +5511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I276" authorId="0" shapeId="0" xr:uid="{15D7D9AF-E469-9648-94DC-D00F56A04568}">
+    <comment ref="I276" authorId="0" shapeId="0" xr:uid="{9FDE8277-4D60-A440-8AD2-82B78AECCC3C}">
       <text>
         <r>
           <rPr>
@@ -5843,7 +5529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I277" authorId="0" shapeId="0" xr:uid="{C583BC55-D256-2E47-A54B-FA44CBECDA35}">
+    <comment ref="I277" authorId="0" shapeId="0" xr:uid="{4E0D29C9-625C-5E4B-9F52-E0CF957DD3B4}">
       <text>
         <r>
           <rPr>
@@ -5859,7 +5545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I278" authorId="0" shapeId="0" xr:uid="{6ADDFCD1-4E5E-4241-A3E9-6620B08C6FCE}">
+    <comment ref="I278" authorId="0" shapeId="0" xr:uid="{320F90CF-B8BD-F340-B2B8-41114F0CE218}">
       <text>
         <r>
           <rPr>
@@ -5875,7 +5561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I279" authorId="0" shapeId="0" xr:uid="{B95DD247-24DB-7E43-87CC-0EAFCA8A1979}">
+    <comment ref="I279" authorId="0" shapeId="0" xr:uid="{443BD892-6FD8-6C4F-BA41-379420F2282C}">
       <text>
         <r>
           <rPr>
@@ -5891,7 +5577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I280" authorId="0" shapeId="0" xr:uid="{10BF1BEC-448A-1147-899D-8CC14ADE4E4F}">
+    <comment ref="I280" authorId="0" shapeId="0" xr:uid="{FB6C4B3C-D634-0D4D-8881-F24AF6810F81}">
       <text>
         <r>
           <rPr>
@@ -5911,7 +5597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I281" authorId="0" shapeId="0" xr:uid="{2E130BBA-872F-3E46-8718-FAC625D8FCBC}">
+    <comment ref="I281" authorId="0" shapeId="0" xr:uid="{653D7051-3174-7046-AE04-DA1961777C4C}">
       <text>
         <r>
           <rPr>
@@ -5929,7 +5615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I282" authorId="0" shapeId="0" xr:uid="{904433A7-1B43-4F46-ADBA-C14A04B32306}">
+    <comment ref="I282" authorId="0" shapeId="0" xr:uid="{479F1A90-8098-2B4D-9C4B-CAB40F643252}">
       <text>
         <r>
           <rPr>
@@ -5957,7 +5643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I283" authorId="0" shapeId="0" xr:uid="{AA013361-E562-AA4C-AA1D-443ED17A2850}">
+    <comment ref="I283" authorId="0" shapeId="0" xr:uid="{98D304F0-7E25-5E49-BCD8-DE33AB49E013}">
       <text>
         <r>
           <rPr>
@@ -5986,7 +5672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I284" authorId="0" shapeId="0" xr:uid="{C6F2989C-8EDD-8341-9DFF-EBCD86424ADA}">
+    <comment ref="I284" authorId="0" shapeId="0" xr:uid="{DC868158-FAB0-CC45-90B5-8FF830FFA42F}">
       <text>
         <r>
           <rPr>
@@ -6003,7 +5689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I285" authorId="0" shapeId="0" xr:uid="{2734F423-93E6-D840-892D-137929FE813A}">
+    <comment ref="I285" authorId="0" shapeId="0" xr:uid="{4197B7BC-C491-C84E-9BD0-D5D8723FD449}">
       <text>
         <r>
           <rPr>
@@ -6032,7 +5718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I286" authorId="0" shapeId="0" xr:uid="{F67F8060-F111-AE4C-9BD9-BE462BC3D4F0}">
+    <comment ref="I286" authorId="0" shapeId="0" xr:uid="{0677DD71-2C17-6940-85DE-3116511AC56F}">
       <text>
         <r>
           <rPr>
@@ -6061,7 +5747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I287" authorId="0" shapeId="0" xr:uid="{805E1C8E-1B2F-B840-8147-ED3ECC5DA8B2}">
+    <comment ref="I287" authorId="0" shapeId="0" xr:uid="{46E713B9-25CB-304C-B98D-797F5A072023}">
       <text>
         <r>
           <rPr>
@@ -6076,7 +5762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I288" authorId="0" shapeId="0" xr:uid="{7537E550-6BE5-5849-813D-506989695A68}">
+    <comment ref="I288" authorId="0" shapeId="0" xr:uid="{303E517C-BFF3-8447-9AAF-40F8C9206275}">
       <text>
         <r>
           <rPr>
@@ -6094,7 +5780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I289" authorId="0" shapeId="0" xr:uid="{EB8A12C0-92E5-0F4B-904F-66D42F3864C0}">
+    <comment ref="I289" authorId="0" shapeId="0" xr:uid="{4054B581-DB83-5347-9254-3C354111A43A}">
       <text>
         <r>
           <rPr>
@@ -6114,7 +5800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I290" authorId="0" shapeId="0" xr:uid="{3D4BB729-692C-1B4E-AD6A-7BE99C281E16}">
+    <comment ref="I290" authorId="0" shapeId="0" xr:uid="{170122FD-FD24-F54B-AA15-D02B5DF55A4C}">
       <text>
         <r>
           <rPr>
@@ -6133,7 +5819,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I291" authorId="0" shapeId="0" xr:uid="{25969FFF-9C06-444F-973B-98766258524E}">
+    <comment ref="I291" authorId="0" shapeId="0" xr:uid="{9664C157-459F-E74D-BC5C-55AC04EC14AA}">
       <text>
         <r>
           <rPr>
@@ -6152,7 +5838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I292" authorId="0" shapeId="0" xr:uid="{6D46C832-DBE3-644E-9A99-3B3939532B55}">
+    <comment ref="I292" authorId="0" shapeId="0" xr:uid="{57403BF4-E18B-5940-9826-B87EFCAF5CD9}">
       <text>
         <r>
           <rPr>
@@ -6172,7 +5858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I293" authorId="0" shapeId="0" xr:uid="{A0008E36-4F8A-C24B-B7D5-2E6E73E93CAE}">
+    <comment ref="I293" authorId="0" shapeId="0" xr:uid="{6A269C11-10D7-824B-856D-2C56D93ABDFE}">
       <text>
         <r>
           <rPr>
@@ -6201,7 +5887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I294" authorId="0" shapeId="0" xr:uid="{E636E26F-38F1-2346-B0DA-E276DFB0391E}">
+    <comment ref="I294" authorId="0" shapeId="0" xr:uid="{E9C469C7-5000-6043-95FB-81EC33F30C9B}">
       <text>
         <r>
           <rPr>
@@ -6222,7 +5908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I295" authorId="0" shapeId="0" xr:uid="{0A956A22-A1BF-2E49-9F6D-9DAB251532FF}">
+    <comment ref="I295" authorId="0" shapeId="0" xr:uid="{33C765A5-7FFF-DE4B-B494-29C2FCE1D380}">
       <text>
         <r>
           <rPr>
@@ -6237,7 +5923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I296" authorId="0" shapeId="0" xr:uid="{69593958-BB5F-064F-8387-D212520D0480}">
+    <comment ref="I296" authorId="0" shapeId="0" xr:uid="{2F2F54FE-46DF-E941-A1D1-FEF5066E7BAE}">
       <text>
         <r>
           <rPr>
@@ -6257,7 +5943,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I297" authorId="0" shapeId="0" xr:uid="{624058BE-B732-5943-B561-4FB8DEC72875}">
+    <comment ref="I297" authorId="0" shapeId="0" xr:uid="{425B7B3D-0935-BC4D-B9A9-1BA7DE467C7E}">
       <text>
         <r>
           <rPr>
@@ -6276,7 +5962,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I298" authorId="0" shapeId="0" xr:uid="{A0948F9A-04AE-FE48-8181-D703BBA9A6D6}">
+    <comment ref="I298" authorId="0" shapeId="0" xr:uid="{045F37F8-386D-0E48-8D53-91508779BF8E}">
       <text>
         <r>
           <rPr>
@@ -6296,7 +5982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I299" authorId="0" shapeId="0" xr:uid="{69FF2FF8-043F-5A41-9A82-C097AF081C81}">
+    <comment ref="I299" authorId="0" shapeId="0" xr:uid="{1B07E960-DCED-F148-8328-BFFD07DF6447}">
       <text>
         <r>
           <rPr>
@@ -6320,7 +6006,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I300" authorId="0" shapeId="0" xr:uid="{D0ED955B-9516-7F45-86CF-98D172CCFD83}">
+    <comment ref="I300" authorId="0" shapeId="0" xr:uid="{5B14C1B4-4918-D146-8936-8E52FED70536}">
       <text>
         <r>
           <rPr>
@@ -6335,7 +6021,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I301" authorId="0" shapeId="0" xr:uid="{EE991912-ADD8-4F42-ADCC-E8208144CD8B}">
+    <comment ref="I301" authorId="0" shapeId="0" xr:uid="{80104E09-6F07-A143-B211-4A7B833FD613}">
       <text>
         <r>
           <rPr>
@@ -6351,7 +6037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I302" authorId="0" shapeId="0" xr:uid="{67049F97-31DF-AA48-9B63-BDB8DA1A9FD8}">
+    <comment ref="I302" authorId="0" shapeId="0" xr:uid="{2C8AFCAD-53F2-D141-9CC6-10FFE19DE82B}">
       <text>
         <r>
           <rPr>
@@ -6367,7 +6053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I303" authorId="0" shapeId="0" xr:uid="{CA7B003A-4706-814E-8F2D-EA5906ED0ECC}">
+    <comment ref="I303" authorId="0" shapeId="0" xr:uid="{99F23C23-BF4D-EF4E-8AB0-BE2787D11180}">
       <text>
         <r>
           <rPr>
@@ -6385,7 +6071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I304" authorId="0" shapeId="0" xr:uid="{A21A4C88-B50B-FB4A-A3E1-9877AB7E3D0F}">
+    <comment ref="I304" authorId="0" shapeId="0" xr:uid="{E89F8FD4-8C36-7D4C-9B49-0EF9AD511ED5}">
       <text>
         <r>
           <rPr>
@@ -6402,7 +6088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I305" authorId="0" shapeId="0" xr:uid="{65F7D4D2-0ABB-3742-9BA5-C80987CFE516}">
+    <comment ref="I305" authorId="0" shapeId="0" xr:uid="{9149E73A-8B3E-4C46-A2E6-35B876400526}">
       <text>
         <r>
           <rPr>
@@ -6418,7 +6104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I306" authorId="0" shapeId="0" xr:uid="{B6F83A09-8EF1-8346-BC13-8F5F185CE2BC}">
+    <comment ref="I306" authorId="0" shapeId="0" xr:uid="{13956EF2-956C-8940-87D8-09D87DF9EB91}">
       <text>
         <r>
           <rPr>
@@ -6434,7 +6120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I307" authorId="0" shapeId="0" xr:uid="{033382B4-396A-8043-B9D8-A33263E62586}">
+    <comment ref="I307" authorId="0" shapeId="0" xr:uid="{F92F764C-E4CB-4E44-A454-DC38A402D510}">
       <text>
         <r>
           <rPr>
@@ -6456,7 +6142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I308" authorId="0" shapeId="0" xr:uid="{54A78CDA-F7CE-E543-8F06-3EF9DE8F76E9}">
+    <comment ref="I308" authorId="0" shapeId="0" xr:uid="{57AB9FC4-D9C2-E440-9A2C-D587141D877C}">
       <text>
         <r>
           <rPr>
@@ -6472,7 +6158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I309" authorId="0" shapeId="0" xr:uid="{80CD6549-AA13-F44E-AB7A-A538638FF677}">
+    <comment ref="I309" authorId="0" shapeId="0" xr:uid="{18AFFB46-789A-9344-B852-A68695BF40E2}">
       <text>
         <r>
           <rPr>
@@ -6488,7 +6174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I310" authorId="0" shapeId="0" xr:uid="{3E712D55-EAA3-9844-B5E6-7EAA4AA39305}">
+    <comment ref="I310" authorId="0" shapeId="0" xr:uid="{CCDF638F-4D3B-C648-99A7-E9A8F1900B02}">
       <text>
         <r>
           <rPr>
@@ -6508,7 +6194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I311" authorId="0" shapeId="0" xr:uid="{333651B5-B8DD-9F43-9476-93F39CB8A22A}">
+    <comment ref="I311" authorId="0" shapeId="0" xr:uid="{CBC6CE85-B915-2B43-B485-78100AE062BE}">
       <text>
         <r>
           <rPr>
@@ -6532,7 +6218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I312" authorId="0" shapeId="0" xr:uid="{0C23B41E-5CF2-6C4D-A118-1D7E0A427E50}">
+    <comment ref="I312" authorId="0" shapeId="0" xr:uid="{3407E634-EAA9-6A4C-914E-3A8C7F41149D}">
       <text>
         <r>
           <rPr>
@@ -6554,7 +6240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I313" authorId="0" shapeId="0" xr:uid="{657B4A4E-F20F-5045-8D0A-71F2C1725DF2}">
+    <comment ref="I313" authorId="0" shapeId="0" xr:uid="{8603BFC1-0BF4-534A-84BF-2943E9C243DD}">
       <text>
         <r>
           <rPr>
@@ -6576,7 +6262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I314" authorId="0" shapeId="0" xr:uid="{68897667-582D-A648-8B8A-C59AC8BB5E17}">
+    <comment ref="I314" authorId="0" shapeId="0" xr:uid="{4A5F29F6-CCB7-464F-9DFF-E90B12944B5B}">
       <text>
         <r>
           <rPr>
@@ -6604,7 +6290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I315" authorId="0" shapeId="0" xr:uid="{0BF9E2A9-AF55-234C-88DF-23E2E881153C}">
+    <comment ref="I315" authorId="0" shapeId="0" xr:uid="{36DA388C-A78A-F042-906A-1B72E8046237}">
       <text>
         <r>
           <rPr>
@@ -6623,7 +6309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I316" authorId="0" shapeId="0" xr:uid="{344C4CB7-26E5-E54D-A3DF-3CB6CDA42A50}">
+    <comment ref="I316" authorId="0" shapeId="0" xr:uid="{D866AA3B-7705-974A-9D4B-728C210BB362}">
       <text>
         <r>
           <rPr>
@@ -6643,7 +6329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I317" authorId="0" shapeId="0" xr:uid="{73D9A563-EC00-8F49-A285-0A8F5BDCED82}">
+    <comment ref="I317" authorId="0" shapeId="0" xr:uid="{7046F90B-7F17-7140-B1E2-BF418B82E8CA}">
       <text>
         <r>
           <rPr>
@@ -6661,7 +6347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I318" authorId="0" shapeId="0" xr:uid="{1FF4BA75-F118-3A4A-A743-1299C953A037}">
+    <comment ref="I318" authorId="0" shapeId="0" xr:uid="{9354BD52-26DE-7C40-AD9B-F717B9D6A918}">
       <text>
         <r>
           <rPr>
@@ -6676,7 +6362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I319" authorId="0" shapeId="0" xr:uid="{F0455B80-6485-2A42-88D0-F6A2AAE77F78}">
+    <comment ref="I319" authorId="0" shapeId="0" xr:uid="{7742E9BA-D876-D341-B552-EF0831934FF7}">
       <text>
         <r>
           <rPr>
@@ -6700,7 +6386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I320" authorId="0" shapeId="0" xr:uid="{DA7F4540-14C2-F849-92CF-5A0C5F6C6B4C}">
+    <comment ref="I320" authorId="0" shapeId="0" xr:uid="{A32CBF57-A05A-E342-8280-449B22829933}">
       <text>
         <r>
           <rPr>
@@ -6719,7 +6405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I321" authorId="0" shapeId="0" xr:uid="{DB7D7A62-B258-D649-B9A3-C09B2C15C885}">
+    <comment ref="I321" authorId="0" shapeId="0" xr:uid="{2181A94B-D61F-4844-878D-D31E45487245}">
       <text>
         <r>
           <rPr>
@@ -6735,7 +6421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I322" authorId="0" shapeId="0" xr:uid="{F9E97B89-BED0-5849-8570-8D919A7DFBF0}">
+    <comment ref="I322" authorId="0" shapeId="0" xr:uid="{D6826589-BD2C-524B-A05E-0329A47FDA0F}">
       <text>
         <r>
           <rPr>
@@ -6753,7 +6439,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I323" authorId="0" shapeId="0" xr:uid="{A7B42D22-10ED-3547-AC3F-BD657A793B7D}">
+    <comment ref="I323" authorId="0" shapeId="0" xr:uid="{2A38A67D-A007-074B-BF71-565B6A7BB776}">
       <text>
         <r>
           <rPr>
@@ -6768,7 +6454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I324" authorId="0" shapeId="0" xr:uid="{5C7527D2-0898-384E-8188-9757EE73B00E}">
+    <comment ref="I324" authorId="0" shapeId="0" xr:uid="{460E51B5-0BDA-7C4E-B9B8-C222947D5BD2}">
       <text>
         <r>
           <rPr>
@@ -6787,7 +6473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I325" authorId="0" shapeId="0" xr:uid="{4443B86F-3CC2-DA4C-A1CF-FD89513FCF46}">
+    <comment ref="I325" authorId="0" shapeId="0" xr:uid="{6A4BA6AB-89E6-7946-8E01-3C1AB6323BEC}">
       <text>
         <r>
           <rPr>
@@ -6816,7 +6502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I326" authorId="0" shapeId="0" xr:uid="{49366975-E314-ED4F-991D-D31E46E66579}">
+    <comment ref="I326" authorId="0" shapeId="0" xr:uid="{F1C3DFF7-78D0-4E48-AE08-C9DDEBC57A38}">
       <text>
         <r>
           <rPr>
@@ -6834,7 +6520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I327" authorId="0" shapeId="0" xr:uid="{0E1F8648-935A-F949-A0DD-03BACCC06593}">
+    <comment ref="I327" authorId="0" shapeId="0" xr:uid="{723B8F4D-32CB-6A46-94FA-E54D5B085584}">
       <text>
         <r>
           <rPr>
@@ -6863,7 +6549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I328" authorId="0" shapeId="0" xr:uid="{3EC98616-64CE-0844-A6F7-C5487B56E4F2}">
+    <comment ref="I328" authorId="0" shapeId="0" xr:uid="{5118DAB1-C09A-C840-ADC1-3482F048FEA1}">
       <text>
         <r>
           <rPr>
@@ -6879,7 +6565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I329" authorId="0" shapeId="0" xr:uid="{F27A83D2-9FB0-9547-B41F-DEF5E4F480A7}">
+    <comment ref="I329" authorId="0" shapeId="0" xr:uid="{F7DC6F45-B70F-434D-80CA-9CDEEDBE8BCD}">
       <text>
         <r>
           <rPr>
@@ -6895,7 +6581,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I330" authorId="0" shapeId="0" xr:uid="{931106A5-7BAF-6B4D-A218-D68C96F30A87}">
+    <comment ref="I330" authorId="0" shapeId="0" xr:uid="{F2EB90E9-1181-6B45-80F3-D9BABAB775B6}">
       <text>
         <r>
           <rPr>
@@ -6924,7 +6610,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I331" authorId="0" shapeId="0" xr:uid="{17FE5F58-C84F-7642-96B9-BA1731B8DD78}">
+    <comment ref="I331" authorId="0" shapeId="0" xr:uid="{767ACCE9-2F74-B640-B5F4-10CE8DF714EE}">
       <text>
         <r>
           <rPr>
@@ -6949,7 +6635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I332" authorId="0" shapeId="0" xr:uid="{8E0359DC-1AA4-344B-B7CF-03419C47539F}">
+    <comment ref="I332" authorId="0" shapeId="0" xr:uid="{DBC1AF16-5D66-0644-B206-581CD34634B4}">
       <text>
         <r>
           <rPr>
@@ -6968,7 +6654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I333" authorId="0" shapeId="0" xr:uid="{E3AAE53C-163E-C44A-8A43-87EC6EB9FD7A}">
+    <comment ref="I333" authorId="0" shapeId="0" xr:uid="{6091B03F-7085-854E-B809-B0F7FF7D211A}">
       <text>
         <r>
           <rPr>
@@ -6992,7 +6678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I334" authorId="0" shapeId="0" xr:uid="{3FD492FB-ED8D-AF47-A874-6DFE124A35E6}">
+    <comment ref="I334" authorId="0" shapeId="0" xr:uid="{88022390-F21F-8541-B41B-5FD224F5D2AB}">
       <text>
         <r>
           <rPr>
@@ -7011,7 +6697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I335" authorId="0" shapeId="0" xr:uid="{9B0CAADE-5268-E943-AFDF-74B6E0C444E0}">
+    <comment ref="I335" authorId="0" shapeId="0" xr:uid="{67482332-231E-BE42-9967-F268DCF7C143}">
       <text>
         <r>
           <rPr>
@@ -7030,7 +6716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I336" authorId="0" shapeId="0" xr:uid="{C3F6D60A-72F8-A54F-B507-C73C20E6A3E7}">
+    <comment ref="I336" authorId="0" shapeId="0" xr:uid="{FBDA71C9-BAC4-CA44-B415-91D6643F6885}">
       <text>
         <r>
           <rPr>
@@ -7049,7 +6735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I337" authorId="0" shapeId="0" xr:uid="{E8541B6F-CC6D-DD4B-A5D6-C9DE297D4B61}">
+    <comment ref="I337" authorId="0" shapeId="0" xr:uid="{E1B503B8-E287-8949-A04B-835D2AC87494}">
       <text>
         <r>
           <rPr>
@@ -7077,7 +6763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I338" authorId="0" shapeId="0" xr:uid="{05F23B0A-DBD2-DD47-B1BB-BC36A4916460}">
+    <comment ref="I338" authorId="0" shapeId="0" xr:uid="{268501E4-05E5-AA45-A96E-F141E0F837D5}">
       <text>
         <r>
           <rPr>
@@ -7096,7 +6782,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I339" authorId="0" shapeId="0" xr:uid="{48168E33-FAF5-2444-BE2F-412B6127E1EB}">
+    <comment ref="I339" authorId="0" shapeId="0" xr:uid="{244F7B4F-4E33-EE44-ACD8-6D01AD38F813}">
       <text>
         <r>
           <rPr>
@@ -7126,7 +6812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I340" authorId="0" shapeId="0" xr:uid="{1436ABA3-27E7-AB40-AFB1-05455AA18281}">
+    <comment ref="I340" authorId="0" shapeId="0" xr:uid="{F698B1C8-3326-2247-BDF7-61A03D68BDFC}">
       <text>
         <r>
           <rPr>
@@ -7145,7 +6831,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I341" authorId="0" shapeId="0" xr:uid="{4C9C0130-5ED5-2F45-9738-B56C949C0625}">
+    <comment ref="I341" authorId="0" shapeId="0" xr:uid="{DAE5529D-7456-034A-87AB-84A5C52953BB}">
       <text>
         <r>
           <rPr>
@@ -7161,7 +6847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I342" authorId="0" shapeId="0" xr:uid="{0F7FBCD8-EB14-C042-B9B6-5025F4908225}">
+    <comment ref="I342" authorId="0" shapeId="0" xr:uid="{D7EF43F4-22FE-CE4E-8F0B-A6C0A1FBE834}">
       <text>
         <r>
           <rPr>
@@ -7180,7 +6866,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I343" authorId="0" shapeId="0" xr:uid="{DFC752DC-AFB1-4148-BD00-B2A167043E8A}">
+    <comment ref="I343" authorId="0" shapeId="0" xr:uid="{7D605807-0DFD-AE42-BC22-67948077E539}">
       <text>
         <r>
           <rPr>
@@ -7209,7 +6895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I344" authorId="0" shapeId="0" xr:uid="{938D9148-3A11-7D4B-926A-A11CEE6FB747}">
+    <comment ref="I344" authorId="0" shapeId="0" xr:uid="{750FEC8F-C41E-CA40-881C-BB1DF4758C2A}">
       <text>
         <r>
           <rPr>
@@ -7228,7 +6914,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I345" authorId="0" shapeId="0" xr:uid="{AD772456-4B9D-CB44-9091-34D19EA1DE3F}">
+    <comment ref="I345" authorId="0" shapeId="0" xr:uid="{56101BBE-0D21-324E-BC6A-8CADDF23C29F}">
       <text>
         <r>
           <rPr>
@@ -7244,7 +6930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I346" authorId="0" shapeId="0" xr:uid="{09AE361A-D01D-BA40-B234-5E2B47130BDF}">
+    <comment ref="I346" authorId="0" shapeId="0" xr:uid="{A9ADBF38-8673-A942-928D-94DBA029CD74}">
       <text>
         <r>
           <rPr>
@@ -7263,7 +6949,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I347" authorId="0" shapeId="0" xr:uid="{47B986ED-5902-BC4A-AF1B-42C4AE411732}">
+    <comment ref="I347" authorId="0" shapeId="0" xr:uid="{7A0D7284-8CB4-6E48-8F8F-524CA0B9AD9E}">
       <text>
         <r>
           <rPr>
@@ -7292,7 +6978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I348" authorId="0" shapeId="0" xr:uid="{4880EF11-AB30-CC43-8F09-BFFB45B9722D}">
+    <comment ref="I348" authorId="0" shapeId="0" xr:uid="{DEFB0991-2F75-7948-BFC9-E41FC099296A}">
       <text>
         <r>
           <rPr>
@@ -7308,7 +6994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I349" authorId="0" shapeId="0" xr:uid="{C89A00A7-6917-3F45-AF19-5E077FF7799B}">
+    <comment ref="I349" authorId="0" shapeId="0" xr:uid="{7579ACF3-4301-8B47-811D-0C5156988AD6}">
       <text>
         <r>
           <rPr>
@@ -7323,7 +7009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I350" authorId="0" shapeId="0" xr:uid="{B42B35DB-DDBF-8245-85BD-B9C4849FC8D6}">
+    <comment ref="I350" authorId="0" shapeId="0" xr:uid="{058327BB-18ED-E245-8D56-A05E8341A91D}">
       <text>
         <r>
           <rPr>
@@ -7342,7 +7028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I351" authorId="0" shapeId="0" xr:uid="{6960BD71-7F7C-3C46-9DB3-B9D9E39A3D1A}">
+    <comment ref="I351" authorId="0" shapeId="0" xr:uid="{86F87F61-F97D-094C-BAEB-A347FC28C8DB}">
       <text>
         <r>
           <rPr>
@@ -7361,7 +7047,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I352" authorId="0" shapeId="0" xr:uid="{D386D542-103B-4041-8069-46400A184679}">
+    <comment ref="I352" authorId="0" shapeId="0" xr:uid="{EA4CA7E2-51BC-C849-9942-9210F81A8254}">
       <text>
         <r>
           <rPr>
@@ -7382,7 +7068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I353" authorId="0" shapeId="0" xr:uid="{1AEE2CBB-C618-1348-85A0-4EEAB6C68970}">
+    <comment ref="I353" authorId="0" shapeId="0" xr:uid="{93F4717B-FEE7-A849-BE48-B3BA1499EF54}">
       <text>
         <r>
           <rPr>
@@ -7397,7 +7083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I354" authorId="0" shapeId="0" xr:uid="{B7FE3987-E377-0B46-9E5B-ABBF9B4A79FC}">
+    <comment ref="I354" authorId="0" shapeId="0" xr:uid="{D69FCC35-6404-EE4B-BBD3-297771459BA3}">
       <text>
         <r>
           <rPr>
@@ -7413,7 +7099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I355" authorId="0" shapeId="0" xr:uid="{B0B5F8A4-3FCA-6A4E-96EC-318794772A64}">
+    <comment ref="I355" authorId="0" shapeId="0" xr:uid="{CC467F42-BF0D-DE43-A735-9C386194A963}">
       <text>
         <r>
           <rPr>
@@ -7430,7 +7116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I356" authorId="0" shapeId="0" xr:uid="{B1DCCBE8-29CE-4347-984B-249125B02B65}">
+    <comment ref="I356" authorId="0" shapeId="0" xr:uid="{C4EDEC99-1339-B947-AD77-E9CC38469298}">
       <text>
         <r>
           <rPr>
@@ -7446,7 +7132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I357" authorId="0" shapeId="0" xr:uid="{6414BC94-755F-9349-B38F-318A07B5AFD4}">
+    <comment ref="I357" authorId="0" shapeId="0" xr:uid="{52B78EBB-A232-944B-A4B6-AD4BF968C4D4}">
       <text>
         <r>
           <rPr>
@@ -7465,7 +7151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I358" authorId="0" shapeId="0" xr:uid="{03D62225-6351-2D4B-A5CD-EA7C9CD9BEFD}">
+    <comment ref="I358" authorId="0" shapeId="0" xr:uid="{9A3B07F4-C778-0047-B2AC-69F617580F5D}">
       <text>
         <r>
           <rPr>
@@ -7482,7 +7168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I359" authorId="0" shapeId="0" xr:uid="{72B0BB32-7ECC-3E43-B400-6674B097E659}">
+    <comment ref="I359" authorId="0" shapeId="0" xr:uid="{489D368D-900F-764D-BBA2-726782C0C0DC}">
       <text>
         <r>
           <rPr>
@@ -7501,7 +7187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I360" authorId="0" shapeId="0" xr:uid="{ADBA38E4-ABEC-E94B-91BB-13748003BEB7}">
+    <comment ref="I360" authorId="0" shapeId="0" xr:uid="{44DE0BD4-8F74-7647-A98F-B78F646B4B1F}">
       <text>
         <r>
           <rPr>
@@ -7518,7 +7204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I361" authorId="0" shapeId="0" xr:uid="{2BA2E77D-F4BF-1744-A87F-0DF4BF03C6C4}">
+    <comment ref="I361" authorId="0" shapeId="0" xr:uid="{68164627-067C-F04E-8B20-235B44A61706}">
       <text>
         <r>
           <rPr>
@@ -7535,7 +7221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I362" authorId="0" shapeId="0" xr:uid="{FBFCDD1C-1438-4E47-9B9F-CA876F786C3A}">
+    <comment ref="I362" authorId="0" shapeId="0" xr:uid="{08E3FA41-F5ED-2F45-8FD5-851424452E9E}">
       <text>
         <r>
           <rPr>
@@ -7552,7 +7238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I363" authorId="0" shapeId="0" xr:uid="{C79C88DA-BF84-5F46-A057-81CA37C765DC}">
+    <comment ref="I363" authorId="0" shapeId="0" xr:uid="{8EB945E8-8F13-004D-A560-78BC50B2A4C9}">
       <text>
         <r>
           <rPr>
@@ -7577,7 +7263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I364" authorId="0" shapeId="0" xr:uid="{BB03377C-4AA2-DD48-A0CD-78F099C4E581}">
+    <comment ref="I364" authorId="0" shapeId="0" xr:uid="{9E45BDA3-2D18-6243-A14B-E1B2743BE9C2}">
       <text>
         <r>
           <rPr>
@@ -7594,7 +7280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I365" authorId="0" shapeId="0" xr:uid="{54D90951-06DF-4249-875B-230A4867F8BF}">
+    <comment ref="I365" authorId="0" shapeId="0" xr:uid="{D1E82712-0158-2F44-8517-A8EE5C3C6950}">
       <text>
         <r>
           <rPr>
@@ -7611,7 +7297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I366" authorId="0" shapeId="0" xr:uid="{95170730-B2F6-5E4F-A21B-69F9DEDA1093}">
+    <comment ref="I366" authorId="0" shapeId="0" xr:uid="{741984A5-77EE-404F-9414-8597FC62A54B}">
       <text>
         <r>
           <rPr>
@@ -7628,7 +7314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I367" authorId="0" shapeId="0" xr:uid="{A871CB49-1A52-9544-BB13-20D45FA17922}">
+    <comment ref="I367" authorId="0" shapeId="0" xr:uid="{D05D560C-A6ED-104E-A22D-35B842225139}">
       <text>
         <r>
           <rPr>
@@ -7645,7 +7331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I368" authorId="0" shapeId="0" xr:uid="{7E3D3C32-E220-A74E-A238-877774D02135}">
+    <comment ref="I368" authorId="0" shapeId="0" xr:uid="{454F6E8D-7A56-5144-A841-D4D627D093C7}">
       <text>
         <r>
           <rPr>
@@ -7662,7 +7348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I369" authorId="0" shapeId="0" xr:uid="{DDFF2EA3-94D3-EF46-9975-ADBB5808BBF4}">
+    <comment ref="I369" authorId="0" shapeId="0" xr:uid="{BCDE1AE5-7183-0945-AC17-5EA7E86C030F}">
       <text>
         <r>
           <rPr>
@@ -7680,7 +7366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I370" authorId="0" shapeId="0" xr:uid="{1E9A4A84-E38F-0E47-9287-359D88880D22}">
+    <comment ref="I370" authorId="0" shapeId="0" xr:uid="{05B76244-0782-1148-A3AC-8F9587B832E6}">
       <text>
         <r>
           <rPr>
@@ -7697,7 +7383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I371" authorId="0" shapeId="0" xr:uid="{8F9C07FB-4656-7140-9D95-987EF86B61C3}">
+    <comment ref="I371" authorId="0" shapeId="0" xr:uid="{D4546F59-328E-C148-B5AF-793561C9930F}">
       <text>
         <r>
           <rPr>
@@ -7715,7 +7401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I372" authorId="0" shapeId="0" xr:uid="{1D7E63FC-6453-4741-80BB-C729908827A7}">
+    <comment ref="I372" authorId="0" shapeId="0" xr:uid="{6D470ED5-0562-8245-9C63-20BD31DDDA2F}">
       <text>
         <r>
           <rPr>
@@ -7739,7 +7425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I373" authorId="0" shapeId="0" xr:uid="{FBD6021E-A3C9-2246-88FA-9228C783C7E7}">
+    <comment ref="I373" authorId="0" shapeId="0" xr:uid="{0BE69191-A6FB-C04A-B4E7-C0845E29AAED}">
       <text>
         <r>
           <rPr>
@@ -7758,7 +7444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I374" authorId="0" shapeId="0" xr:uid="{DA44C6B3-FEE9-674D-8992-831C3BBD1B46}">
+    <comment ref="I374" authorId="0" shapeId="0" xr:uid="{B6754F02-FE93-204F-9CE4-B92732E9EB2C}">
       <text>
         <r>
           <rPr>
@@ -7776,7 +7462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I375" authorId="0" shapeId="0" xr:uid="{BD90CBE8-390E-7345-8582-4512F0469A8E}">
+    <comment ref="I375" authorId="0" shapeId="0" xr:uid="{51CB2BF9-625D-5340-ACEC-31BDFD26E5AF}">
       <text>
         <r>
           <rPr>
@@ -7793,7 +7479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I376" authorId="0" shapeId="0" xr:uid="{7D906E69-8D7B-FD4E-93A7-B6009CCFFC3F}">
+    <comment ref="I376" authorId="0" shapeId="0" xr:uid="{46962926-7394-5B4B-8E3B-5539CDA20DA4}">
       <text>
         <r>
           <rPr>
@@ -7810,7 +7496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I377" authorId="0" shapeId="0" xr:uid="{548D3BE7-D621-F84D-BDEE-70FED91AE6F0}">
+    <comment ref="I377" authorId="0" shapeId="0" xr:uid="{AB4157BD-F864-A142-8D91-B95E0BB9D255}">
       <text>
         <r>
           <rPr>
@@ -7827,7 +7513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I378" authorId="0" shapeId="0" xr:uid="{68587AFD-F055-7E41-9115-1F56112E9A74}">
+    <comment ref="I378" authorId="0" shapeId="0" xr:uid="{7261E552-9F2C-7349-9BEC-59C00973838C}">
       <text>
         <r>
           <rPr>
@@ -7847,7 +7533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I379" authorId="0" shapeId="0" xr:uid="{FFA9A3FD-BA77-9F47-8EDB-2A98971F96A5}">
+    <comment ref="I379" authorId="0" shapeId="0" xr:uid="{62002B78-A192-CF4B-A45D-8CCE19C52854}">
       <text>
         <r>
           <rPr>
@@ -7864,7 +7550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I380" authorId="0" shapeId="0" xr:uid="{90A0FA87-31A4-DC46-B2A2-1A45B25CCA6F}">
+    <comment ref="I380" authorId="0" shapeId="0" xr:uid="{0ACD802A-3013-0D49-9E54-9937CA28A26C}">
       <text>
         <r>
           <rPr>
@@ -7881,7 +7567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I381" authorId="0" shapeId="0" xr:uid="{D76D339F-08FA-A648-98FA-10BA57ABE39C}">
+    <comment ref="I381" authorId="0" shapeId="0" xr:uid="{DCF41749-E01E-6749-8894-3D252F048C82}">
       <text>
         <r>
           <rPr>
@@ -7898,7 +7584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I382" authorId="0" shapeId="0" xr:uid="{13228006-554E-344B-97F4-6C1D033A3492}">
+    <comment ref="I382" authorId="0" shapeId="0" xr:uid="{17BB7120-78FB-C644-B443-7DB187FB8012}">
       <text>
         <r>
           <rPr>
@@ -7915,7 +7601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I383" authorId="0" shapeId="0" xr:uid="{603BF8EB-E8F4-114A-8D80-63B2AFE5290D}">
+    <comment ref="I383" authorId="0" shapeId="0" xr:uid="{7693A19E-F1BD-EC4B-BBB8-65130FDFC85C}">
       <text>
         <r>
           <rPr>
@@ -7932,7 +7618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I384" authorId="0" shapeId="0" xr:uid="{3CC841F2-4415-B24B-B237-66A6C3FA9521}">
+    <comment ref="I384" authorId="0" shapeId="0" xr:uid="{BCEDC80E-8DA7-3844-8354-DEB3249D1CBC}">
       <text>
         <r>
           <rPr>
@@ -7949,7 +7635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I385" authorId="0" shapeId="0" xr:uid="{BA659A06-114B-4C4E-B03F-846A8CDBC1C5}">
+    <comment ref="I385" authorId="0" shapeId="0" xr:uid="{F01F22D4-7788-1C44-9213-4FDB54E96DCE}">
       <text>
         <r>
           <rPr>
@@ -7982,7 +7668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I386" authorId="0" shapeId="0" xr:uid="{9F960D9D-C024-9E44-AF0A-11EEF9418704}">
+    <comment ref="I386" authorId="0" shapeId="0" xr:uid="{DA8FD3EE-91D3-ED4F-80B5-DCD9E5DCC313}">
       <text>
         <r>
           <rPr>
@@ -7997,7 +7683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I387" authorId="0" shapeId="0" xr:uid="{9A3B00F3-C052-6E45-B2D8-B0597DE486D2}">
+    <comment ref="I387" authorId="0" shapeId="0" xr:uid="{F60987A0-C83E-2B4F-8DF0-2F05481BEC93}">
       <text>
         <r>
           <rPr>
@@ -8017,7 +7703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I388" authorId="0" shapeId="0" xr:uid="{2E36D6E3-684B-AF42-86CD-AC2E4642FD04}">
+    <comment ref="I388" authorId="0" shapeId="0" xr:uid="{48AE76D8-2D02-A945-A39C-F63AB4B0AAFC}">
       <text>
         <r>
           <rPr>
@@ -8037,7 +7723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I389" authorId="0" shapeId="0" xr:uid="{3B18DBFC-3A6B-6D4A-A1E9-882071B4F29B}">
+    <comment ref="I389" authorId="0" shapeId="0" xr:uid="{0D5648B1-DD1E-6B4E-8AB9-C05389D2D22D}">
       <text>
         <r>
           <rPr>
@@ -8055,7 +7741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I390" authorId="0" shapeId="0" xr:uid="{0F4E21FC-948C-BA4D-89A3-F6C99B5AFC2C}">
+    <comment ref="I390" authorId="0" shapeId="0" xr:uid="{57336D90-FAA3-214F-96B7-E5E0FF2BDB2D}">
       <text>
         <r>
           <rPr>
@@ -8073,7 +7759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I391" authorId="0" shapeId="0" xr:uid="{352B1969-C4C6-4240-A263-7A2E148AFAB1}">
+    <comment ref="I391" authorId="0" shapeId="0" xr:uid="{0D3B9BAA-E25F-BC4B-818A-0E59C94C35D7}">
       <text>
         <r>
           <rPr>
@@ -8090,7 +7776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I392" authorId="0" shapeId="0" xr:uid="{7DF13299-3528-1E4E-818A-BD69CCAA0E41}">
+    <comment ref="I392" authorId="0" shapeId="0" xr:uid="{073AE840-A049-4348-8F9B-92FB4B085846}">
       <text>
         <r>
           <rPr>
@@ -8107,7 +7793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I393" authorId="0" shapeId="0" xr:uid="{54F96A80-1D2E-8545-BF01-F9803B30172B}">
+    <comment ref="I393" authorId="0" shapeId="0" xr:uid="{29760F6E-A672-F748-9418-5B66223D46CE}">
       <text>
         <r>
           <rPr>
@@ -8136,7 +7822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I394" authorId="0" shapeId="0" xr:uid="{BB521832-7811-A147-8F32-56CBA683F00F}">
+    <comment ref="I394" authorId="0" shapeId="0" xr:uid="{E2933A66-5C4C-F04B-B83C-5A888C6899F3}">
       <text>
         <r>
           <rPr>
@@ -8158,7 +7844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I395" authorId="0" shapeId="0" xr:uid="{B64BF979-2208-6545-9D39-C0FF2ADECF22}">
+    <comment ref="I395" authorId="0" shapeId="0" xr:uid="{33A50B01-B6CB-F14F-B73E-A70AD1799C11}">
       <text>
         <r>
           <rPr>
@@ -8174,7 +7860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I396" authorId="0" shapeId="0" xr:uid="{BF38074B-1156-AA48-9C53-99A406ED38DC}">
+    <comment ref="I396" authorId="0" shapeId="0" xr:uid="{A73FA908-3F38-7F43-95D1-0E8F547E6374}">
       <text>
         <r>
           <rPr>
@@ -8193,7 +7879,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I397" authorId="0" shapeId="0" xr:uid="{BA8F7005-0CFB-0B41-ACF2-01B31DBEC98F}">
+    <comment ref="I397" authorId="0" shapeId="0" xr:uid="{B7D5293E-A6A1-DA41-AE7E-412F9788BFA0}">
       <text>
         <r>
           <rPr>
@@ -8215,7 +7901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I398" authorId="0" shapeId="0" xr:uid="{3BFFA45A-F375-5D4D-A392-556A0964A036}">
+    <comment ref="I398" authorId="0" shapeId="0" xr:uid="{67C4148B-A428-1945-B221-52F1DF753989}">
       <text>
         <r>
           <rPr>
@@ -8233,7 +7919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I399" authorId="0" shapeId="0" xr:uid="{54355A06-DE2C-3748-8867-38C1765F6E4B}">
+    <comment ref="I399" authorId="0" shapeId="0" xr:uid="{679EED08-78EB-864C-A1AE-1652C529217A}">
       <text>
         <r>
           <rPr>
@@ -8251,7 +7937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I400" authorId="0" shapeId="0" xr:uid="{E2B2A7E7-824F-8040-A5FF-DF6D1AC356F7}">
+    <comment ref="I400" authorId="0" shapeId="0" xr:uid="{EFADC7B2-0684-DF4D-BC10-A093ACC85ABE}">
       <text>
         <r>
           <rPr>
@@ -8267,7 +7953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I401" authorId="0" shapeId="0" xr:uid="{5F9D1796-2721-1944-AEF0-E6EF206F6D05}">
+    <comment ref="I401" authorId="0" shapeId="0" xr:uid="{2F5A8723-D0CF-AB41-887E-C6CB36536840}">
       <text>
         <r>
           <rPr>
@@ -8290,7 +7976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I402" authorId="0" shapeId="0" xr:uid="{2704CCC6-3694-8947-973F-1240D09020EE}">
+    <comment ref="I402" authorId="0" shapeId="0" xr:uid="{31A04D42-25C1-2442-AD1A-D93A1DE4C22B}">
       <text>
         <r>
           <rPr>
@@ -8308,7 +7994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I403" authorId="0" shapeId="0" xr:uid="{A925A6E2-E097-424E-8739-73604F3B59AC}">
+    <comment ref="I403" authorId="0" shapeId="0" xr:uid="{2269088A-53D8-BC49-8F90-40DCCEE09406}">
       <text>
         <r>
           <rPr>
@@ -8326,7 +8012,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I404" authorId="0" shapeId="0" xr:uid="{3058D0AD-42C7-DD40-BCB1-752C3F2A06F5}">
+    <comment ref="I404" authorId="0" shapeId="0" xr:uid="{9823EB9D-AAEE-A846-9347-6E0D537106F5}">
       <text>
         <r>
           <rPr>
@@ -8344,7 +8030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I405" authorId="0" shapeId="0" xr:uid="{235DDE43-0FB2-7B44-B183-E6A89A20DD10}">
+    <comment ref="I405" authorId="0" shapeId="0" xr:uid="{B6A19C48-7451-2A43-951E-25074C616411}">
       <text>
         <r>
           <rPr>
@@ -8367,7 +8053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I406" authorId="0" shapeId="0" xr:uid="{D57AC267-80BD-BA43-B6B2-EFE1CC490A1E}">
+    <comment ref="I406" authorId="0" shapeId="0" xr:uid="{ABEED6F8-9D06-F441-B536-5511401FD07A}">
       <text>
         <r>
           <rPr>
@@ -8385,7 +8071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I407" authorId="0" shapeId="0" xr:uid="{9A41F5C3-80BC-AB4B-ADBF-95D822E2C050}">
+    <comment ref="I407" authorId="0" shapeId="0" xr:uid="{0F6F16D2-D1FC-4346-A795-47C400A6A09C}">
       <text>
         <r>
           <rPr>
@@ -8408,7 +8094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I408" authorId="0" shapeId="0" xr:uid="{A08DF12D-39DA-474E-B81C-8048E4FEA12F}">
+    <comment ref="I408" authorId="0" shapeId="0" xr:uid="{1EFD6AAC-D64B-5B4C-A664-2F522EE5569B}">
       <text>
         <r>
           <rPr>
@@ -8426,7 +8112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I409" authorId="0" shapeId="0" xr:uid="{E682B874-8796-824A-83DF-6E82ED03078F}">
+    <comment ref="I409" authorId="0" shapeId="0" xr:uid="{0048E24A-276E-9B46-8875-79EAB87A4BD1}">
       <text>
         <r>
           <rPr>
@@ -8444,7 +8130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I410" authorId="0" shapeId="0" xr:uid="{FAA02CB1-86A1-1645-A082-3FE18CEF813B}">
+    <comment ref="I410" authorId="0" shapeId="0" xr:uid="{56D4574C-D0A8-C945-A611-B5A99726BADB}">
       <text>
         <r>
           <rPr>
@@ -8463,7 +8149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I411" authorId="0" shapeId="0" xr:uid="{5EA11A1B-A8F7-C648-8B67-130DE1020E72}">
+    <comment ref="I411" authorId="0" shapeId="0" xr:uid="{E44D948F-243C-9943-A487-8F70F8F2BE5F}">
       <text>
         <r>
           <rPr>
@@ -8486,7 +8172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I412" authorId="0" shapeId="0" xr:uid="{9543E67F-5041-4B4F-9904-4BEDD82D7CA2}">
+    <comment ref="I412" authorId="0" shapeId="0" xr:uid="{87EC8CC8-731C-6948-832A-78C73C0CF093}">
       <text>
         <r>
           <rPr>
@@ -8504,7 +8190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I413" authorId="0" shapeId="0" xr:uid="{1B27E4D5-0110-994A-A610-08694DE4BD8F}">
+    <comment ref="I413" authorId="0" shapeId="0" xr:uid="{ABF747E1-5613-9B4B-8331-5E6D1C0D85BF}">
       <text>
         <r>
           <rPr>
@@ -8520,7 +8206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I414" authorId="0" shapeId="0" xr:uid="{EE9A6462-3190-1B44-B52D-CADEC779701A}">
+    <comment ref="I414" authorId="0" shapeId="0" xr:uid="{83C907C8-7A9A-3C40-A52D-697785DCA6A5}">
       <text>
         <r>
           <rPr>
@@ -8543,7 +8229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I415" authorId="0" shapeId="0" xr:uid="{ED6F7222-3C94-544F-8B02-2F757A2050FD}">
+    <comment ref="I415" authorId="0" shapeId="0" xr:uid="{2141937E-DFE3-4C4E-935D-489CB300020C}">
       <text>
         <r>
           <rPr>
@@ -8561,7 +8247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I416" authorId="0" shapeId="0" xr:uid="{C56B3B23-8300-B145-8D4B-C0D5C932DFBE}">
+    <comment ref="I416" authorId="0" shapeId="0" xr:uid="{64983DBA-A380-4F43-AC6D-E0FB412907E3}">
       <text>
         <r>
           <rPr>
@@ -8576,7 +8262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I417" authorId="0" shapeId="0" xr:uid="{3B171BCF-3386-3746-9464-135B6B6A1F7A}">
+    <comment ref="I417" authorId="0" shapeId="0" xr:uid="{B069F428-7D66-4D42-89CF-F902B2156B43}">
       <text>
         <r>
           <rPr>
@@ -8599,7 +8285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I418" authorId="0" shapeId="0" xr:uid="{E449C6CC-FBCF-0242-8C59-CB1FE7CFAE95}">
+    <comment ref="I418" authorId="0" shapeId="0" xr:uid="{1E996D62-5407-3045-BFE6-4EC3FFF39DBB}">
       <text>
         <r>
           <rPr>
@@ -8618,7 +8304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I419" authorId="0" shapeId="0" xr:uid="{4F1C6E23-1AE3-0A4E-BAE4-E983CCD128C3}">
+    <comment ref="I419" authorId="0" shapeId="0" xr:uid="{F9942EF7-AF82-5F45-B196-590923C0AF48}">
       <text>
         <r>
           <rPr>
@@ -8641,7 +8327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I420" authorId="0" shapeId="0" xr:uid="{8F7F4E7E-2760-3C4B-9178-A713C6CB5257}">
+    <comment ref="I420" authorId="0" shapeId="0" xr:uid="{0DAAAFA5-09C5-D541-8E83-A15CC49518E5}">
       <text>
         <r>
           <rPr>
@@ -8659,7 +8345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I421" authorId="0" shapeId="0" xr:uid="{68B9E8EA-4DA2-1D42-BC48-7FF7C8E16AF4}">
+    <comment ref="I421" authorId="0" shapeId="0" xr:uid="{EB2A7015-066A-F34C-8C0F-8DF922FA8E54}">
       <text>
         <r>
           <rPr>
@@ -8682,7 +8368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I422" authorId="0" shapeId="0" xr:uid="{E782F098-8FA5-DF4E-9606-7795D0AA7F3D}">
+    <comment ref="I422" authorId="0" shapeId="0" xr:uid="{8453B8CD-5B0B-A840-84B2-F71DE28FBB66}">
       <text>
         <r>
           <rPr>
@@ -8705,7 +8391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I423" authorId="0" shapeId="0" xr:uid="{2CF7DB4D-BB87-DC42-9F0A-8DD47031A4C0}">
+    <comment ref="I423" authorId="0" shapeId="0" xr:uid="{7920431C-0BE8-7946-9FDB-9632497681AF}">
       <text>
         <r>
           <rPr>
@@ -8728,7 +8414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I424" authorId="0" shapeId="0" xr:uid="{C1069590-5EB1-7540-8976-E6ECFBC26134}">
+    <comment ref="I424" authorId="0" shapeId="0" xr:uid="{5B93172F-C7DD-394F-9C30-800302921D84}">
       <text>
         <r>
           <rPr>
@@ -8751,7 +8437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I425" authorId="0" shapeId="0" xr:uid="{4F0F1324-0C1D-3C4A-81FF-867B9390F3E3}">
+    <comment ref="I425" authorId="0" shapeId="0" xr:uid="{39CAE622-1B6E-7A4C-9CCD-F4E60AD49FD4}">
       <text>
         <r>
           <rPr>
@@ -8769,7 +8455,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I426" authorId="0" shapeId="0" xr:uid="{E3B6EED4-EE4E-0749-BCFC-36E0E555B19E}">
+    <comment ref="I426" authorId="0" shapeId="0" xr:uid="{B601B7BC-8FDA-7E41-ADAD-8F018103383B}">
       <text>
         <r>
           <rPr>
@@ -8792,7 +8478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I427" authorId="0" shapeId="0" xr:uid="{72BFDB9F-A100-4B4B-A86E-3FA046D38A87}">
+    <comment ref="I427" authorId="0" shapeId="0" xr:uid="{CB11FDAD-47B3-8D40-BF6A-A4440E8138B5}">
       <text>
         <r>
           <rPr>
@@ -8815,7 +8501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I428" authorId="0" shapeId="0" xr:uid="{9521B9DB-81CC-AB45-98E6-DF2FCD631FAB}">
+    <comment ref="I428" authorId="0" shapeId="0" xr:uid="{F8178035-8B28-FC4C-8A9A-C809F2A1D5E2}">
       <text>
         <r>
           <rPr>
@@ -8838,7 +8524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I429" authorId="0" shapeId="0" xr:uid="{A9B45FE3-B7F5-F74C-9AB8-D78C99A27E54}">
+    <comment ref="I429" authorId="0" shapeId="0" xr:uid="{2D9F56AE-2414-3545-88EB-ADC77C0FEEE4}">
       <text>
         <r>
           <rPr>
@@ -8861,7 +8547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I430" authorId="0" shapeId="0" xr:uid="{C533C382-D0D2-3C4D-A057-8AE403417825}">
+    <comment ref="I430" authorId="0" shapeId="0" xr:uid="{92E34430-7EE3-DC44-ADF1-D39CF433DC1A}">
       <text>
         <r>
           <rPr>
@@ -8884,7 +8570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I431" authorId="0" shapeId="0" xr:uid="{AD05A55C-3D55-EC45-B8EE-8FC305D4C8C8}">
+    <comment ref="I431" authorId="0" shapeId="0" xr:uid="{B3E008AB-2329-7E46-82EE-101CFBE0E5AC}">
       <text>
         <r>
           <rPr>
@@ -8907,7 +8593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I432" authorId="0" shapeId="0" xr:uid="{0EE4BBF8-B39E-9E46-945B-09B6467571CA}">
+    <comment ref="I432" authorId="0" shapeId="0" xr:uid="{81EA0314-FE13-1741-A22E-64307DE09847}">
       <text>
         <r>
           <rPr>
@@ -8922,7 +8608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I433" authorId="0" shapeId="0" xr:uid="{7C34C43B-7899-AD41-B509-540709C2EEA1}">
+    <comment ref="I433" authorId="0" shapeId="0" xr:uid="{83236F2A-97EB-6B48-B0B4-D42459D3CFE2}">
       <text>
         <r>
           <rPr>
@@ -8952,7 +8638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I434" authorId="0" shapeId="0" xr:uid="{D0210CE1-9596-A541-B80C-176E298775B0}">
+    <comment ref="I434" authorId="0" shapeId="0" xr:uid="{71976B8A-FEDA-084B-8D11-F1FC59032049}">
       <text>
         <r>
           <rPr>
@@ -8981,7 +8667,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I435" authorId="0" shapeId="0" xr:uid="{3F6BCBB2-D23B-FD4F-8143-8F6222377B1A}">
+    <comment ref="I435" authorId="0" shapeId="0" xr:uid="{F4A224DD-000F-AC41-8E4F-CDAB2FAE7568}">
       <text>
         <r>
           <rPr>
@@ -8997,7 +8683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I436" authorId="0" shapeId="0" xr:uid="{F64CA08B-1C2D-844D-95F1-4B48ECD6A4C4}">
+    <comment ref="I436" authorId="0" shapeId="0" xr:uid="{6F78EAF5-9EA5-824A-B677-9D3200C3D64F}">
       <text>
         <r>
           <rPr>
@@ -9016,7 +8702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I437" authorId="0" shapeId="0" xr:uid="{510813E6-8BB8-4744-B2FD-9025378ADA8A}">
+    <comment ref="I437" authorId="0" shapeId="0" xr:uid="{46848CA9-C76B-7E49-882D-4C871700F353}">
       <text>
         <r>
           <rPr>
@@ -9036,7 +8722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I438" authorId="0" shapeId="0" xr:uid="{09A84459-DD26-8649-9CB7-C53636A7065E}">
+    <comment ref="I438" authorId="0" shapeId="0" xr:uid="{2F4210F1-E5C7-B04D-8AD7-DA1F0A355FCE}">
       <text>
         <r>
           <rPr>
@@ -9056,7 +8742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I439" authorId="0" shapeId="0" xr:uid="{8A3559E0-D871-8B42-AC8D-F9C6103F8837}">
+    <comment ref="I439" authorId="0" shapeId="0" xr:uid="{A572B2A5-D4DC-2047-9642-73EED272074C}">
       <text>
         <r>
           <rPr>
@@ -9072,7 +8758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I440" authorId="0" shapeId="0" xr:uid="{1AA2CE29-5894-E043-8E1A-197780E530B4}">
+    <comment ref="I440" authorId="0" shapeId="0" xr:uid="{3BD302B6-48DF-9248-8C8D-BD59311656CB}">
       <text>
         <r>
           <rPr>
@@ -9092,7 +8778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I441" authorId="0" shapeId="0" xr:uid="{73D4C8FA-A8A8-C845-9C9E-8C8137584A6B}">
+    <comment ref="I441" authorId="0" shapeId="0" xr:uid="{1786BFBA-8D40-0748-BCDD-335F23F92090}">
       <text>
         <r>
           <rPr>
@@ -9111,7 +8797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I442" authorId="0" shapeId="0" xr:uid="{59B986E2-0716-2940-8AC8-5DAE23462756}">
+    <comment ref="I442" authorId="0" shapeId="0" xr:uid="{5632AD48-A3A0-FB44-BEC8-6B841F9F9F86}">
       <text>
         <r>
           <rPr>
@@ -9131,7 +8817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I443" authorId="0" shapeId="0" xr:uid="{2BDD7F33-724F-7A49-99C2-2E18A72715D1}">
+    <comment ref="I443" authorId="0" shapeId="0" xr:uid="{BB5C400E-697D-3642-83A2-0FEC69ACFF79}">
       <text>
         <r>
           <rPr>
@@ -9151,7 +8837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I444" authorId="0" shapeId="0" xr:uid="{633C48F8-01D5-FF4E-B5EB-EE0770DEDABF}">
+    <comment ref="I444" authorId="0" shapeId="0" xr:uid="{FB92A8CC-085C-CC4D-9FC2-13543A361D14}">
       <text>
         <r>
           <rPr>
@@ -9170,7 +8856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I445" authorId="0" shapeId="0" xr:uid="{02A5D606-CBCE-6B41-99ED-5500EEF790CB}">
+    <comment ref="I445" authorId="0" shapeId="0" xr:uid="{F1047010-EC1F-CE40-92F8-2F9412A8AAE8}">
       <text>
         <r>
           <rPr>
@@ -9196,7 +8882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I446" authorId="0" shapeId="0" xr:uid="{0C114A63-0222-DE4F-AD3C-34BFBB26AABA}">
+    <comment ref="I446" authorId="0" shapeId="0" xr:uid="{AFE6922E-ECBB-C24C-B845-D20A9549B6B9}">
       <text>
         <r>
           <rPr>
@@ -9222,7 +8908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I447" authorId="0" shapeId="0" xr:uid="{577800C7-BC6F-474E-B366-DE86A0C95553}">
+    <comment ref="I447" authorId="0" shapeId="0" xr:uid="{F1B41643-EAD8-0E4D-9C00-E0B1F3C44B59}">
       <text>
         <r>
           <rPr>
@@ -9248,7 +8934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I448" authorId="0" shapeId="0" xr:uid="{E619D671-3E09-6E4B-BE3B-7E3B78616673}">
+    <comment ref="I448" authorId="0" shapeId="0" xr:uid="{1E5BC150-402D-2847-8DFB-03484DC109B0}">
       <text>
         <r>
           <rPr>
@@ -9268,7 +8954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I449" authorId="0" shapeId="0" xr:uid="{245BDAF8-B7EC-3A43-B44F-636FD5F34AA0}">
+    <comment ref="I449" authorId="0" shapeId="0" xr:uid="{6A1576E8-C981-E348-A0C9-D08E8C8CC494}">
       <text>
         <r>
           <rPr>
@@ -9291,7 +8977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I450" authorId="0" shapeId="0" xr:uid="{D52EBC8E-8F1A-0C44-A752-EB774EBE74DA}">
+    <comment ref="I450" authorId="0" shapeId="0" xr:uid="{2599275A-8B77-4943-B254-43E1F08790F5}">
       <text>
         <r>
           <rPr>
@@ -9317,7 +9003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I451" authorId="0" shapeId="0" xr:uid="{65F1B010-A700-584C-9205-9E380AC302F3}">
+    <comment ref="I451" authorId="0" shapeId="0" xr:uid="{64DE6CAB-8927-1340-9391-FE49AA19CA05}">
       <text>
         <r>
           <rPr>
@@ -9337,7 +9023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I452" authorId="0" shapeId="0" xr:uid="{0061E806-8EEB-B64E-8FE9-42082D3094F3}">
+    <comment ref="I452" authorId="0" shapeId="0" xr:uid="{4B1CAFE1-D0F2-A142-8103-898C9AECD3C9}">
       <text>
         <r>
           <rPr>
@@ -9363,7 +9049,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I453" authorId="0" shapeId="0" xr:uid="{A389E82D-8FD9-4841-8B0D-21B2E247D1CF}">
+    <comment ref="I453" authorId="0" shapeId="0" xr:uid="{9CC1F3EC-EDA6-004E-BE1D-CC280EC6E185}">
       <text>
         <r>
           <rPr>
@@ -9389,7 +9075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I454" authorId="0" shapeId="0" xr:uid="{AD76A3EE-7FED-CF45-8608-6AF3EFD6F381}">
+    <comment ref="I454" authorId="0" shapeId="0" xr:uid="{239BFBAC-5B63-4842-A80C-3C57B7153465}">
       <text>
         <r>
           <rPr>
@@ -9409,7 +9095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I455" authorId="0" shapeId="0" xr:uid="{C872AC36-9A8A-E646-A778-1D8968A02DE5}">
+    <comment ref="I455" authorId="0" shapeId="0" xr:uid="{F150B38C-29D2-024C-A43D-973DDAB9A49A}">
       <text>
         <r>
           <rPr>
@@ -9432,7 +9118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I456" authorId="0" shapeId="0" xr:uid="{E45B1860-B49D-A343-8B8A-1CCE324E0E6B}">
+    <comment ref="I456" authorId="0" shapeId="0" xr:uid="{889EDB02-7C22-174C-9C2E-3338EC2C26D1}">
       <text>
         <r>
           <rPr>
@@ -9455,7 +9141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I457" authorId="0" shapeId="0" xr:uid="{F37C19B0-CD49-974F-8E30-70B99DC94F2F}">
+    <comment ref="I457" authorId="0" shapeId="0" xr:uid="{9ABB48BF-1A6E-4948-9D25-A127231C6F17}">
       <text>
         <r>
           <rPr>
@@ -9475,7 +9161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I458" authorId="0" shapeId="0" xr:uid="{CB0AEB2D-2758-3B4A-83E5-B872F2168D7B}">
+    <comment ref="I458" authorId="0" shapeId="0" xr:uid="{97D83A3F-219B-6A45-A6B2-CF4B0CA6D2AC}">
       <text>
         <r>
           <rPr>
@@ -9501,7 +9187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I459" authorId="0" shapeId="0" xr:uid="{7FA7296F-6437-2A4F-8694-D7FC0895184C}">
+    <comment ref="I459" authorId="0" shapeId="0" xr:uid="{9F6C5975-D5E1-0F46-900F-5C9A483A2BB5}">
       <text>
         <r>
           <rPr>
@@ -9521,7 +9207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I460" authorId="0" shapeId="0" xr:uid="{13D0C532-B2CF-FA44-840A-0BD2FE250BF8}">
+    <comment ref="I460" authorId="0" shapeId="0" xr:uid="{2D36A44F-1910-4041-AEF0-07C3BCA97A87}">
       <text>
         <r>
           <rPr>
@@ -9541,7 +9227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I461" authorId="0" shapeId="0" xr:uid="{9292FE93-6C28-C94C-BB1E-785C97EAC107}">
+    <comment ref="I461" authorId="0" shapeId="0" xr:uid="{0674856F-88BC-B745-BA4E-5667C0673987}">
       <text>
         <r>
           <rPr>
@@ -9567,7 +9253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I462" authorId="0" shapeId="0" xr:uid="{E9467411-BCAA-9747-8FC5-8375DB5D5DD5}">
+    <comment ref="I462" authorId="0" shapeId="0" xr:uid="{6A8FE243-2904-324C-9F1F-F4ABC0429C06}">
       <text>
         <r>
           <rPr>
@@ -9587,7 +9273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I463" authorId="0" shapeId="0" xr:uid="{BDF8D165-10FE-2641-8903-4DAC40BB1DE0}">
+    <comment ref="I463" authorId="0" shapeId="0" xr:uid="{BD09926B-DDA1-5E46-86DA-A830377EA301}">
       <text>
         <r>
           <rPr>
@@ -9613,7 +9299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I464" authorId="0" shapeId="0" xr:uid="{72583AFA-253D-8C49-A8C7-FC527CCBEF85}">
+    <comment ref="I464" authorId="0" shapeId="0" xr:uid="{A36DF166-08FF-ED44-B72B-7E128CB4AF08}">
       <text>
         <r>
           <rPr>
@@ -9639,7 +9325,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I465" authorId="0" shapeId="0" xr:uid="{3BDE9841-6030-D544-B80E-568F36050E6F}">
+    <comment ref="I465" authorId="0" shapeId="0" xr:uid="{4BAB56CB-E182-284F-9608-8CF75E7610CC}">
       <text>
         <r>
           <rPr>
@@ -9659,7 +9345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I466" authorId="0" shapeId="0" xr:uid="{D7A33128-5957-654F-AFA9-5EDB0E0F9AD8}">
+    <comment ref="I466" authorId="0" shapeId="0" xr:uid="{A78759C0-313E-7B46-BAC8-42B0DC9FEC88}">
       <text>
         <r>
           <rPr>
@@ -9679,7 +9365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I467" authorId="0" shapeId="0" xr:uid="{FAA8CB03-1136-2644-AAA0-A989C0B1771D}">
+    <comment ref="I467" authorId="0" shapeId="0" xr:uid="{58C44264-B038-3A40-B0AE-B1091CCB879B}">
       <text>
         <r>
           <rPr>
@@ -9705,7 +9391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I468" authorId="0" shapeId="0" xr:uid="{34FBF9A3-CEAE-EA47-AE9E-A8240B45E9F3}">
+    <comment ref="I468" authorId="0" shapeId="0" xr:uid="{D9C70C58-320A-C84E-A350-F19B62FBD9AA}">
       <text>
         <r>
           <rPr>
@@ -9725,7 +9411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I469" authorId="0" shapeId="0" xr:uid="{007CD779-A302-154F-8C67-E4CDFFF00297}">
+    <comment ref="I469" authorId="0" shapeId="0" xr:uid="{D1B888DE-DA0E-344D-A227-EF476E589733}">
       <text>
         <r>
           <rPr>
@@ -9751,7 +9437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I470" authorId="0" shapeId="0" xr:uid="{2086157A-F6DC-0C40-A496-86D65556D9FE}">
+    <comment ref="I470" authorId="0" shapeId="0" xr:uid="{E22B31EF-5101-8E4F-A84C-15CDD93AB88D}">
       <text>
         <r>
           <rPr>
@@ -9777,7 +9463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I471" authorId="0" shapeId="0" xr:uid="{4507447A-F9FC-614D-8512-2AF2D4A4E807}">
+    <comment ref="I471" authorId="0" shapeId="0" xr:uid="{A1B9F4E3-7968-C041-85FE-6D9542E7750F}">
       <text>
         <r>
           <rPr>
@@ -9797,7 +9483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I472" authorId="0" shapeId="0" xr:uid="{FD9BF689-F925-E74B-80C6-F682505EAAC7}">
+    <comment ref="I472" authorId="0" shapeId="0" xr:uid="{28002D5C-2BAA-8F44-BF88-E547A48A574F}">
       <text>
         <r>
           <rPr>
@@ -9815,7 +9501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I473" authorId="0" shapeId="0" xr:uid="{36269952-A8B2-BD4A-A70E-2F847ADCD309}">
+    <comment ref="I473" authorId="0" shapeId="0" xr:uid="{B5381041-A0E6-7F44-87A3-B3BF3D96EE4E}">
       <text>
         <r>
           <rPr>
@@ -9844,7 +9530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I474" authorId="0" shapeId="0" xr:uid="{95FEB3DC-D110-A740-9FC0-F313170AF079}">
+    <comment ref="I474" authorId="0" shapeId="0" xr:uid="{7AD2F74A-7756-5444-A1AE-5E49D5233F03}">
       <text>
         <r>
           <rPr>
@@ -9860,7 +9546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I475" authorId="0" shapeId="0" xr:uid="{7FCD2AF5-12FC-8B49-90B9-8B0A4A81E6F7}">
+    <comment ref="I475" authorId="0" shapeId="0" xr:uid="{16D88C07-3CBE-574F-BD0F-6070E4F04EEC}">
       <text>
         <r>
           <rPr>
@@ -9876,7 +9562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I476" authorId="0" shapeId="0" xr:uid="{09A4E637-D637-7343-8CC9-FCF8646C5865}">
+    <comment ref="I476" authorId="0" shapeId="0" xr:uid="{753CC93C-700B-5942-8586-5626D2347784}">
       <text>
         <r>
           <rPr>
@@ -9896,7 +9582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I477" authorId="0" shapeId="0" xr:uid="{277A1653-9AA0-0344-9332-10FA63807441}">
+    <comment ref="I477" authorId="0" shapeId="0" xr:uid="{EE9C849F-F8C5-FA4C-A57B-D52910A95838}">
       <text>
         <r>
           <rPr>
@@ -9922,7 +9608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I478" authorId="0" shapeId="0" xr:uid="{FA7244A3-CB14-9040-BAF8-C9B8F188AC70}">
+    <comment ref="I478" authorId="0" shapeId="0" xr:uid="{1B3351C0-87CE-FE42-9DD6-24BE2435DCC7}">
       <text>
         <r>
           <rPr>
@@ -9938,7 +9624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I479" authorId="0" shapeId="0" xr:uid="{DA8384B2-ED3F-414D-BD4C-6D40BA8C42AA}">
+    <comment ref="I479" authorId="0" shapeId="0" xr:uid="{F90F4016-D228-C049-9650-0C6C435C6222}">
       <text>
         <r>
           <rPr>
@@ -9958,7 +9644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I480" authorId="0" shapeId="0" xr:uid="{5DAD2FE0-10B5-504D-9FB9-A3F7C2CF0F42}">
+    <comment ref="I480" authorId="0" shapeId="0" xr:uid="{6587FD28-9D70-E34E-BF22-BB5A6553D47F}">
       <text>
         <r>
           <rPr>
@@ -9974,7 +9660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I481" authorId="0" shapeId="0" xr:uid="{C9E92591-9877-104A-9EF3-CBCB6D7EFE96}">
+    <comment ref="I481" authorId="0" shapeId="0" xr:uid="{CF92EEFF-812D-3C42-8EDC-50FF980684AA}">
       <text>
         <r>
           <rPr>
@@ -10000,7 +9686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I482" authorId="0" shapeId="0" xr:uid="{AB52E704-0F37-324A-AFA8-CF93C76B1AB2}">
+    <comment ref="I482" authorId="0" shapeId="0" xr:uid="{D030D2CC-F49F-D54E-B9A4-3264C9F9AAB7}">
       <text>
         <r>
           <rPr>
@@ -10023,7 +9709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I483" authorId="0" shapeId="0" xr:uid="{EE965D98-BC32-B244-8BF6-5390D7777DBD}">
+    <comment ref="I483" authorId="0" shapeId="0" xr:uid="{46F9EEE2-0598-EA47-9C08-4040A407ED80}">
       <text>
         <r>
           <rPr>
@@ -10043,7 +9729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I484" authorId="0" shapeId="0" xr:uid="{4B8E983A-6887-6D46-BC7D-CB5448311369}">
+    <comment ref="I484" authorId="0" shapeId="0" xr:uid="{8B54B42F-0317-9049-8E73-ED0CD354F482}">
       <text>
         <r>
           <rPr>
@@ -10059,7 +9745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I485" authorId="0" shapeId="0" xr:uid="{32369092-DE70-354F-BA0A-45CD22312B47}">
+    <comment ref="I485" authorId="0" shapeId="0" xr:uid="{F5E0361E-ECAA-F243-9D49-B47CA58D86E2}">
       <text>
         <r>
           <rPr>
@@ -10085,7 +9771,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I486" authorId="0" shapeId="0" xr:uid="{05523DEE-2F17-6B45-B02B-9481F5B603A4}">
+    <comment ref="I486" authorId="0" shapeId="0" xr:uid="{16CE1DDA-8ECD-6849-8ED1-B5C6F724B20D}">
       <text>
         <r>
           <rPr>
@@ -10101,7 +9787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I487" authorId="0" shapeId="0" xr:uid="{A47B267C-4BAF-9C45-916D-6FEA729A9C59}">
+    <comment ref="I487" authorId="0" shapeId="0" xr:uid="{74BA0A57-F67F-2640-AC6E-1BE3C77D7120}">
       <text>
         <r>
           <rPr>
@@ -10121,7 +9807,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I488" authorId="0" shapeId="0" xr:uid="{C8EBD242-E498-AA40-9A99-16296C465790}">
+    <comment ref="I488" authorId="0" shapeId="0" xr:uid="{EB8DBB7C-433B-0647-8D2B-9E67080ADF94}">
       <text>
         <r>
           <rPr>
@@ -10141,7 +9827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I489" authorId="0" shapeId="0" xr:uid="{7041B9CC-6260-DB4E-AC89-82A6722A5671}">
+    <comment ref="I489" authorId="0" shapeId="0" xr:uid="{EA7EC97F-7566-8F42-8C65-583874D4708C}">
       <text>
         <r>
           <rPr>
@@ -10161,7 +9847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I490" authorId="0" shapeId="0" xr:uid="{9D1A80B9-6152-6F41-9187-3F06BBFB19DD}">
+    <comment ref="I490" authorId="0" shapeId="0" xr:uid="{8ED986DC-62B0-6045-BEE7-0DCE39681AEE}">
       <text>
         <r>
           <rPr>
@@ -10181,7 +9867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I491" authorId="0" shapeId="0" xr:uid="{EB84F0B6-9668-1740-BDE0-900E312F812F}">
+    <comment ref="I491" authorId="0" shapeId="0" xr:uid="{ACC92907-9ECF-494A-9E84-ACAE3EAEAF7A}">
       <text>
         <r>
           <rPr>
@@ -10207,7 +9893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I492" authorId="0" shapeId="0" xr:uid="{BFA4D0A6-7117-4547-91AC-24AFCD0CAC65}">
+    <comment ref="I492" authorId="0" shapeId="0" xr:uid="{FB3332A7-E9BA-A840-8AC5-744AE10626AD}">
       <text>
         <r>
           <rPr>
@@ -10230,7 +9916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I493" authorId="0" shapeId="0" xr:uid="{260E11ED-6B45-9F4D-9336-DF1AE2F5883A}">
+    <comment ref="I493" authorId="0" shapeId="0" xr:uid="{77300F20-42B1-A846-8431-3656789CCA46}">
       <text>
         <r>
           <rPr>
@@ -10256,7 +9942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I494" authorId="0" shapeId="0" xr:uid="{F6404631-0CBB-DC4B-88FB-E49AFD11BE1A}">
+    <comment ref="I494" authorId="0" shapeId="0" xr:uid="{7536A48C-6AF6-684C-878C-31C27637ECF0}">
       <text>
         <r>
           <rPr>
@@ -10276,7 +9962,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I495" authorId="0" shapeId="0" xr:uid="{8AAF288B-5561-144D-8491-1828A31415AB}">
+    <comment ref="I495" authorId="0" shapeId="0" xr:uid="{5C1FE8CE-7A2B-554A-AF25-46FCC56C0C17}">
       <text>
         <r>
           <rPr>
@@ -10296,7 +9982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I496" authorId="0" shapeId="0" xr:uid="{4B3868EC-86AE-6540-98A0-C885A5541735}">
+    <comment ref="I496" authorId="0" shapeId="0" xr:uid="{98AC7E58-F71F-8140-839C-7CD64D7A5FE3}">
       <text>
         <r>
           <rPr>
@@ -10316,7 +10002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I497" authorId="0" shapeId="0" xr:uid="{6476C6FE-9259-9741-B032-6BDC25ACDFEF}">
+    <comment ref="I497" authorId="0" shapeId="0" xr:uid="{76E05A25-DD1F-734C-9C55-30742D5A9977}">
       <text>
         <r>
           <rPr>
@@ -10336,7 +10022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I498" authorId="0" shapeId="0" xr:uid="{9224F6F2-C924-7541-B1A4-C5762049A254}">
+    <comment ref="I498" authorId="0" shapeId="0" xr:uid="{0B12B6D3-073A-A941-8CC7-45FA66828174}">
       <text>
         <r>
           <rPr>
@@ -10356,7 +10042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I499" authorId="0" shapeId="0" xr:uid="{ECCDC75E-BAA3-F44D-9CDC-5C93B5389D3A}">
+    <comment ref="I499" authorId="0" shapeId="0" xr:uid="{791FFA24-DD54-7F43-9EA4-9DF2014DE795}">
       <text>
         <r>
           <rPr>
@@ -10377,7 +10063,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I500" authorId="0" shapeId="0" xr:uid="{F4129668-7A62-4D45-B703-F0BE77C4757D}">
+    <comment ref="I500" authorId="0" shapeId="0" xr:uid="{176DDFC8-82B3-E540-8397-58992D81E4D2}">
       <text>
         <r>
           <rPr>
@@ -10397,7 +10083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I501" authorId="0" shapeId="0" xr:uid="{4B047E37-B5FA-FF49-B71C-EA527C1927EC}">
+    <comment ref="I501" authorId="0" shapeId="0" xr:uid="{5C66508F-A482-764F-9487-0BC413E65CB0}">
       <text>
         <r>
           <rPr>
@@ -10415,7 +10101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I502" authorId="0" shapeId="0" xr:uid="{2834D3DA-A67E-CC49-94A7-469B3C355550}">
+    <comment ref="I502" authorId="0" shapeId="0" xr:uid="{EA5571C3-3019-884B-8BC4-0A077E820328}">
       <text>
         <r>
           <rPr>
@@ -10435,7 +10121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I503" authorId="0" shapeId="0" xr:uid="{6D3561E3-5982-0347-B93D-383D64ED27CA}">
+    <comment ref="I503" authorId="0" shapeId="0" xr:uid="{1E1DBB94-5B39-9946-B18F-074148C3532A}">
       <text>
         <r>
           <rPr>
@@ -10450,7 +10136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I504" authorId="0" shapeId="0" xr:uid="{019FB08D-74A4-8345-B054-84BD69370A1D}">
+    <comment ref="I504" authorId="0" shapeId="0" xr:uid="{A652A91F-D488-264B-A532-CB0D36B2AC3C}">
       <text>
         <r>
           <rPr>
@@ -10470,7 +10156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I505" authorId="0" shapeId="0" xr:uid="{AEE1DFB0-A4EB-C142-8E7E-F9557C8141AB}">
+    <comment ref="I505" authorId="0" shapeId="0" xr:uid="{E4F09544-7611-DD41-B196-226B27A0725A}">
       <text>
         <r>
           <rPr>
@@ -10490,7 +10176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I506" authorId="0" shapeId="0" xr:uid="{8BCEADF0-AA32-F842-920D-11FF8C3339BC}">
+    <comment ref="I506" authorId="0" shapeId="0" xr:uid="{6F714C4F-375A-AD47-A411-491207FB27C0}">
       <text>
         <r>
           <rPr>
@@ -10510,7 +10196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I507" authorId="0" shapeId="0" xr:uid="{84706AC3-BF58-3447-AC2C-A666C2D870D4}">
+    <comment ref="I507" authorId="0" shapeId="0" xr:uid="{9BD42531-5D95-E54C-BDF4-F2BFF5FC7147}">
       <text>
         <r>
           <rPr>
@@ -10530,7 +10216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I508" authorId="0" shapeId="0" xr:uid="{08BA6F24-04BB-C740-9864-D303DD23C4ED}">
+    <comment ref="I508" authorId="0" shapeId="0" xr:uid="{CA502012-7D21-BE49-A5E6-165E9AA00A78}">
       <text>
         <r>
           <rPr>
@@ -10547,7 +10233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I509" authorId="0" shapeId="0" xr:uid="{90B6345C-754E-4B40-B1F7-220ED270815D}">
+    <comment ref="I509" authorId="0" shapeId="0" xr:uid="{5B3816F1-D0D2-7A4D-A1B7-D6B78765759E}">
       <text>
         <r>
           <rPr>
@@ -10567,7 +10253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I510" authorId="0" shapeId="0" xr:uid="{E4E10CD0-F545-0247-B225-7C80C6B4FCC1}">
+    <comment ref="I510" authorId="0" shapeId="0" xr:uid="{9F003BAB-6F52-0746-9036-A5C2F91EB48C}">
       <text>
         <r>
           <rPr>
@@ -10587,7 +10273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I511" authorId="0" shapeId="0" xr:uid="{AA7B6689-70C7-454C-8690-4A3F3DAD6405}">
+    <comment ref="I511" authorId="0" shapeId="0" xr:uid="{2D48E2F2-E82E-E743-ABD4-EEB09AC68E1E}">
       <text>
         <r>
           <rPr>
@@ -10605,7 +10291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I512" authorId="0" shapeId="0" xr:uid="{BA9DBFCB-9993-1848-BBC8-EAAD21E0ABA0}">
+    <comment ref="I512" authorId="0" shapeId="0" xr:uid="{52D51A54-5F42-8D4A-94AC-C93E5B48E9E7}">
       <text>
         <r>
           <rPr>
@@ -10628,7 +10314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I513" authorId="0" shapeId="0" xr:uid="{5411165D-FA61-C542-A0F9-19A1D91DBF33}">
+    <comment ref="I513" authorId="0" shapeId="0" xr:uid="{6765F8F5-4A1C-B24A-9AFF-BBCC4491DF3C}">
       <text>
         <r>
           <rPr>
@@ -10644,7 +10330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I514" authorId="0" shapeId="0" xr:uid="{5D9288C1-877E-3049-9AEA-3C369D7EA415}">
+    <comment ref="I514" authorId="0" shapeId="0" xr:uid="{1CC9EF7D-1D9E-FD4B-B8A2-00D1F28AFDA5}">
       <text>
         <r>
           <rPr>
@@ -10670,7 +10356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I515" authorId="0" shapeId="0" xr:uid="{369BEA79-629D-0B44-8ED8-711050035749}">
+    <comment ref="I515" authorId="0" shapeId="0" xr:uid="{6E683BBD-BE85-AB40-8155-04047A8023EB}">
       <text>
         <r>
           <rPr>
@@ -10696,7 +10382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I516" authorId="0" shapeId="0" xr:uid="{CD5B3B7D-E88B-FE47-A4FF-8C4FCADB03FC}">
+    <comment ref="I516" authorId="0" shapeId="0" xr:uid="{BFAD919D-CE82-6A45-85B7-4AA66448178A}">
       <text>
         <r>
           <rPr>
@@ -10712,7 +10398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I517" authorId="0" shapeId="0" xr:uid="{4F4B10ED-2263-A54A-A44C-E0436D494F92}">
+    <comment ref="I517" authorId="0" shapeId="0" xr:uid="{681F7330-CB70-564E-AB56-3BAE6A5325BD}">
       <text>
         <r>
           <rPr>
@@ -10728,7 +10414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I518" authorId="0" shapeId="0" xr:uid="{9727E616-1731-604D-8D8E-C97BD4F2F09E}">
+    <comment ref="I518" authorId="0" shapeId="0" xr:uid="{D7C9CDE3-EB66-CF48-8D94-CE3923E05B74}">
       <text>
         <r>
           <rPr>
@@ -10744,7 +10430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I519" authorId="0" shapeId="0" xr:uid="{ACC422D8-9DAE-0C49-9E8D-29694A4C0BCE}">
+    <comment ref="I519" authorId="0" shapeId="0" xr:uid="{78C85B42-E728-C445-8981-57F255B1760D}">
       <text>
         <r>
           <rPr>
@@ -10761,7 +10447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I520" authorId="0" shapeId="0" xr:uid="{CF65934B-0B28-284E-916B-6BED3A5E6A21}">
+    <comment ref="I520" authorId="0" shapeId="0" xr:uid="{780CFEAB-53A9-3E4F-ADD8-7CC916D65BE4}">
       <text>
         <r>
           <rPr>
@@ -10778,7 +10464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I521" authorId="0" shapeId="0" xr:uid="{E95A4DAC-6D2F-3E41-B361-1C097F8DB467}">
+    <comment ref="I521" authorId="0" shapeId="0" xr:uid="{676D8409-D562-194A-8F0E-D9F49E31BC37}">
       <text>
         <r>
           <rPr>
@@ -10797,7 +10483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I522" authorId="0" shapeId="0" xr:uid="{21E13F95-CB05-CF47-9FFE-AC76F33B10FC}">
+    <comment ref="I522" authorId="0" shapeId="0" xr:uid="{EDF2BFC6-EF0E-A040-BE67-62069594136E}">
       <text>
         <r>
           <rPr>
@@ -10817,7 +10503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I523" authorId="0" shapeId="0" xr:uid="{1598F9E0-EAC3-4842-9E3E-81E771DD959B}">
+    <comment ref="I523" authorId="0" shapeId="0" xr:uid="{5E383E2B-0AAE-804F-B6C1-BB4C50B240A0}">
       <text>
         <r>
           <rPr>
@@ -10833,7 +10519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I524" authorId="0" shapeId="0" xr:uid="{36C58F28-6BDE-404C-AE76-CD868B83B3FC}">
+    <comment ref="I524" authorId="0" shapeId="0" xr:uid="{5FA3C409-0A50-7D40-BFFE-CEFFCD4E2B86}">
       <text>
         <r>
           <rPr>
@@ -10849,7 +10535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I525" authorId="0" shapeId="0" xr:uid="{A0B4AA11-2EE7-4C4D-98D3-0C7B52AE2328}">
+    <comment ref="I525" authorId="0" shapeId="0" xr:uid="{BBA7682F-6E57-8B47-9011-646E6E308121}">
       <text>
         <r>
           <rPr>
@@ -10866,7 +10552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I526" authorId="0" shapeId="0" xr:uid="{79757B5D-BC54-7A42-BE8D-36755D11F0F5}">
+    <comment ref="I526" authorId="0" shapeId="0" xr:uid="{2BBEA9E6-A048-634A-B248-F30AFCCE65DE}">
       <text>
         <r>
           <rPr>
@@ -10882,7 +10568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I527" authorId="0" shapeId="0" xr:uid="{7CC2CD22-7FA9-AF4B-8AF9-8BCDD8BBD787}">
+    <comment ref="I527" authorId="0" shapeId="0" xr:uid="{8381EEB4-11B8-D945-8BE3-60185B523C7E}">
       <text>
         <r>
           <rPr>
@@ -10899,7 +10585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I528" authorId="0" shapeId="0" xr:uid="{C7EF6162-8591-EC44-9A6F-79B5D4CA0F21}">
+    <comment ref="I528" authorId="0" shapeId="0" xr:uid="{B6E26837-3F2A-494E-B3E6-1A19141EB457}">
       <text>
         <r>
           <rPr>
@@ -10919,7 +10605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I529" authorId="0" shapeId="0" xr:uid="{6047703F-7C6D-5449-B182-F951F498E76C}">
+    <comment ref="I529" authorId="0" shapeId="0" xr:uid="{13C6D24D-3E49-9142-878B-F93D630CCDF8}">
       <text>
         <r>
           <rPr>
@@ -10935,7 +10621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I530" authorId="0" shapeId="0" xr:uid="{9CC84E9B-357C-D044-81FD-D33FFDBA06AB}">
+    <comment ref="I530" authorId="0" shapeId="0" xr:uid="{CF57F7A5-DF9F-5A48-9D52-7F7DE965409F}">
       <text>
         <r>
           <rPr>
@@ -10951,7 +10637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I531" authorId="0" shapeId="0" xr:uid="{164677F7-5CD0-6A43-A992-72E467DA23E7}">
+    <comment ref="I531" authorId="0" shapeId="0" xr:uid="{909CC0D3-C381-5B48-9D41-410811C68DE2}">
       <text>
         <r>
           <rPr>
@@ -10968,7 +10654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I532" authorId="0" shapeId="0" xr:uid="{B7EDF41B-3AF1-B743-BAB9-E81DF619C895}">
+    <comment ref="I532" authorId="0" shapeId="0" xr:uid="{74B952FE-628E-5144-AAF9-B5E4F98110DD}">
       <text>
         <r>
           <rPr>
@@ -10984,7 +10670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I533" authorId="0" shapeId="0" xr:uid="{B2D73947-BCD3-E046-805B-F171B8585350}">
+    <comment ref="I533" authorId="0" shapeId="0" xr:uid="{A548B08E-2FFD-6146-8BC1-2B1E05C9134D}">
       <text>
         <r>
           <rPr>
@@ -11003,7 +10689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I534" authorId="0" shapeId="0" xr:uid="{334D436D-655C-3148-A0A2-C17EE266DBFD}">
+    <comment ref="I534" authorId="0" shapeId="0" xr:uid="{0FB43C50-3DD9-544C-AEDB-63F59ADF41AE}">
       <text>
         <r>
           <rPr>
@@ -11020,7 +10706,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I535" authorId="0" shapeId="0" xr:uid="{5209E3A4-A090-AF48-991E-CAA234530320}">
+    <comment ref="I535" authorId="0" shapeId="0" xr:uid="{707D7E45-7987-5A44-8890-6CEE773DD6E6}">
       <text>
         <r>
           <rPr>
@@ -11036,7 +10722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I536" authorId="0" shapeId="0" xr:uid="{897BCACE-B8F1-764A-8CB5-0D75779180BF}">
+    <comment ref="I536" authorId="0" shapeId="0" xr:uid="{AC73353E-448A-8B4B-99D2-48A13759970D}">
       <text>
         <r>
           <rPr>
@@ -11052,7 +10738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I537" authorId="0" shapeId="0" xr:uid="{EF042221-E72F-8140-9D7D-16FE77BC32CB}">
+    <comment ref="I537" authorId="0" shapeId="0" xr:uid="{515707D8-7C9D-704A-80FB-45AA34C61F62}">
       <text>
         <r>
           <rPr>
@@ -11068,7 +10754,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I538" authorId="0" shapeId="0" xr:uid="{0179E54E-DAAB-4548-BFBE-8D18143C7A44}">
+    <comment ref="I538" authorId="0" shapeId="0" xr:uid="{A8C6C7E9-E7BF-C348-AA0E-85F7DBD80972}">
       <text>
         <r>
           <rPr>
@@ -11087,7 +10773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I539" authorId="0" shapeId="0" xr:uid="{16CB1E0A-E782-D946-80A2-3443C652412F}">
+    <comment ref="I539" authorId="0" shapeId="0" xr:uid="{33DD77DD-2916-E848-B5AA-76F72645540C}">
       <text>
         <r>
           <rPr>
@@ -11103,7 +10789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I540" authorId="0" shapeId="0" xr:uid="{DAC55648-56BD-5F4B-9C46-0433E97423B5}">
+    <comment ref="I540" authorId="0" shapeId="0" xr:uid="{5DD21ED7-F488-2544-87DE-F2C48D8914BA}">
       <text>
         <r>
           <rPr>
@@ -11118,7 +10804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I541" authorId="0" shapeId="0" xr:uid="{80A6BFDC-788C-3047-AABB-95CB27ACA9E3}">
+    <comment ref="I541" authorId="0" shapeId="0" xr:uid="{F1440A22-A283-9145-8DFA-F14839DC674B}">
       <text>
         <r>
           <rPr>
@@ -11142,7 +10828,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I542" authorId="0" shapeId="0" xr:uid="{6D4CFC12-D1DD-654E-A627-636388F96D5C}">
+    <comment ref="I542" authorId="0" shapeId="0" xr:uid="{68446397-BAC6-764F-B102-CEE128653207}">
       <text>
         <r>
           <rPr>
@@ -11158,7 +10844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I543" authorId="0" shapeId="0" xr:uid="{DB73C7E0-A6D1-1647-88EA-B79FB3E555D5}">
+    <comment ref="I543" authorId="0" shapeId="0" xr:uid="{BE17A39B-D4EC-E54D-AE9A-903DC93C1FF7}">
       <text>
         <r>
           <rPr>
@@ -11175,7 +10861,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I544" authorId="0" shapeId="0" xr:uid="{1AD7C857-36CA-E448-9395-6838704A7112}">
+    <comment ref="I544" authorId="0" shapeId="0" xr:uid="{2F583025-717D-9947-AF48-EDBFBA1A35C1}">
       <text>
         <r>
           <rPr>
@@ -11191,7 +10877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I545" authorId="0" shapeId="0" xr:uid="{F386DCB5-A07C-0A47-95D1-4E67877ED8D2}">
+    <comment ref="I545" authorId="0" shapeId="0" xr:uid="{6D1BD5BF-CCEE-8A4D-970C-4CD33DB61A87}">
       <text>
         <r>
           <rPr>
@@ -11207,7 +10893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I546" authorId="0" shapeId="0" xr:uid="{4083C9AA-4678-B947-9FB3-74EB8EAFD4DC}">
+    <comment ref="I546" authorId="0" shapeId="0" xr:uid="{D154767A-F3B4-6244-8BF3-257DBB9A7E94}">
       <text>
         <r>
           <rPr>
@@ -11223,7 +10909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I547" authorId="0" shapeId="0" xr:uid="{16A9AD2E-BF88-BB44-A8F8-D364CE9ACCDA}">
+    <comment ref="I547" authorId="0" shapeId="0" xr:uid="{CB668841-5504-5C44-91BB-690333F944C3}">
       <text>
         <r>
           <rPr>
@@ -11237,7 +10923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I548" authorId="0" shapeId="0" xr:uid="{E1AE874D-7E56-184B-816A-EEA45EC5316D}">
+    <comment ref="I548" authorId="0" shapeId="0" xr:uid="{1490F5EA-1C0F-554C-9F43-70692682434A}">
       <text>
         <r>
           <rPr>
@@ -11253,7 +10939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I549" authorId="0" shapeId="0" xr:uid="{A2C213E2-FD17-6543-8F4D-CF6285E88490}">
+    <comment ref="I549" authorId="0" shapeId="0" xr:uid="{0D2D6AA8-E053-384A-881B-9B9D66BFEA43}">
       <text>
         <r>
           <rPr>
@@ -11268,7 +10954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I550" authorId="0" shapeId="0" xr:uid="{8E7B0F9B-A489-FA4A-B465-221345CEAC36}">
+    <comment ref="I550" authorId="0" shapeId="0" xr:uid="{7E8C25A3-7812-1E4C-A3F1-CC84601337EE}">
       <text>
         <r>
           <rPr>
@@ -11284,7 +10970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I551" authorId="0" shapeId="0" xr:uid="{55C127E6-E6D4-EC44-8AB6-ECCBDD0B949B}">
+    <comment ref="I551" authorId="0" shapeId="0" xr:uid="{5B68A462-149D-A14C-8F6C-3ECEABE36FE6}">
       <text>
         <r>
           <rPr>
@@ -11300,7 +10986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I552" authorId="0" shapeId="0" xr:uid="{0467ADE0-28EC-4749-B595-2813398C8527}">
+    <comment ref="I552" authorId="0" shapeId="0" xr:uid="{032A0970-D76F-A24F-A799-83B660EFD24B}">
       <text>
         <r>
           <rPr>
@@ -11329,7 +11015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I553" authorId="0" shapeId="0" xr:uid="{8F6CD27C-F565-BF49-B531-503837B30BD5}">
+    <comment ref="I553" authorId="0" shapeId="0" xr:uid="{B8FD917D-015D-9344-9AEF-1369FB6C5E1B}">
       <text>
         <r>
           <rPr>
@@ -11344,7 +11030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I554" authorId="0" shapeId="0" xr:uid="{25FC4F26-B7B8-DA46-98F1-2575C508542B}">
+    <comment ref="I554" authorId="0" shapeId="0" xr:uid="{CB6D3D0B-566B-6B43-BF7A-EC7EFED912FF}">
       <text>
         <r>
           <rPr>
@@ -11359,7 +11045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I555" authorId="0" shapeId="0" xr:uid="{CD38DE19-F915-5B44-ABAB-636BFED176B3}">
+    <comment ref="I555" authorId="0" shapeId="0" xr:uid="{06F781E3-E9C0-BE47-AECB-C6E99DFF3518}">
       <text>
         <r>
           <rPr>
@@ -11376,7 +11062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I556" authorId="0" shapeId="0" xr:uid="{4DA95CFE-B7E0-0945-9BF7-9CDCB4132180}">
+    <comment ref="I556" authorId="0" shapeId="0" xr:uid="{2BC18427-CEF7-DC44-A283-C692CA751034}">
       <text>
         <r>
           <rPr>
@@ -11395,7 +11081,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I557" authorId="0" shapeId="0" xr:uid="{00A5235E-A816-AF4D-9355-CBB90CFE6CD0}">
+    <comment ref="I557" authorId="0" shapeId="0" xr:uid="{74EE0F0A-C84E-0F42-BC77-7ACC8FDA6D41}">
       <text>
         <r>
           <rPr>
@@ -11414,7 +11100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I558" authorId="0" shapeId="0" xr:uid="{0D8CB814-7026-4D44-A360-3E66F622F138}">
+    <comment ref="I558" authorId="0" shapeId="0" xr:uid="{6090096D-4038-3D4B-AC69-4DAD7410D804}">
       <text>
         <r>
           <rPr>
@@ -11433,7 +11119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I559" authorId="0" shapeId="0" xr:uid="{9BC94CE3-37F8-0540-8B36-E1B3374146BF}">
+    <comment ref="I559" authorId="0" shapeId="0" xr:uid="{491A6F1B-41B5-B74B-925D-DFC18D9C4668}">
       <text>
         <r>
           <rPr>
@@ -11452,7 +11138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I560" authorId="0" shapeId="0" xr:uid="{CAC868CF-E58B-CD48-84A9-16A897DF53C6}">
+    <comment ref="I560" authorId="0" shapeId="0" xr:uid="{3D8A4AB6-EA5A-4F4B-99F2-31948E5729C6}">
       <text>
         <r>
           <rPr>
@@ -11471,7 +11157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I561" authorId="0" shapeId="0" xr:uid="{61D0822B-90ED-8E44-A71D-18636826D7FC}">
+    <comment ref="I561" authorId="0" shapeId="0" xr:uid="{5D615E57-DEEC-164E-B599-B891AA3FE384}">
       <text>
         <r>
           <rPr>
@@ -11486,7 +11172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I562" authorId="0" shapeId="0" xr:uid="{71D16E7F-DF59-F242-B525-F87E30A6025C}">
+    <comment ref="I562" authorId="0" shapeId="0" xr:uid="{52A60689-D5B7-0044-8EF5-8051A02453EC}">
       <text>
         <r>
           <rPr>
@@ -11505,7 +11191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I563" authorId="0" shapeId="0" xr:uid="{31834F96-3A85-1C40-9AF3-9277AF3B9664}">
+    <comment ref="I563" authorId="0" shapeId="0" xr:uid="{B157EDD1-5F72-D045-9F41-2F494E39338A}">
       <text>
         <r>
           <rPr>
@@ -11522,7 +11208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I564" authorId="0" shapeId="0" xr:uid="{9CCD0E51-1D8B-C64D-899C-68A4D1FFF9A9}">
+    <comment ref="I564" authorId="0" shapeId="0" xr:uid="{FAF263F9-07F7-0D41-B560-D158B2BA7CBA}">
       <text>
         <r>
           <rPr>
@@ -11541,7 +11227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I565" authorId="0" shapeId="0" xr:uid="{164CD640-C3E6-4942-8081-1C5D769D5435}">
+    <comment ref="I565" authorId="0" shapeId="0" xr:uid="{C1BE22A7-30CD-5B4B-AA48-5D6E40A5D1D4}">
       <text>
         <r>
           <rPr>
@@ -11560,7 +11246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I566" authorId="0" shapeId="0" xr:uid="{02196F6A-C82B-3E4A-97C3-12CA49774768}">
+    <comment ref="I566" authorId="0" shapeId="0" xr:uid="{F06CAC7D-FE4A-354B-BF83-46E740E13A1F}">
       <text>
         <r>
           <rPr>
@@ -11578,7 +11264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I567" authorId="0" shapeId="0" xr:uid="{F42A6607-97C6-A047-8FE1-EC9DD2414B3C}">
+    <comment ref="I567" authorId="0" shapeId="0" xr:uid="{FADEC02E-FF34-144B-842F-556900106329}">
       <text>
         <r>
           <rPr>
@@ -11608,7 +11294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I568" authorId="0" shapeId="0" xr:uid="{E0B8C51C-8F83-F943-9E85-5C0744B5F1CB}">
+    <comment ref="I568" authorId="0" shapeId="0" xr:uid="{1A4E92D4-B873-7449-BC40-8D6F0442402A}">
       <text>
         <r>
           <rPr>
@@ -11627,7 +11313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I569" authorId="0" shapeId="0" xr:uid="{F90AAF07-8E84-9F49-9AB8-7A0D2A42A4B8}">
+    <comment ref="I569" authorId="0" shapeId="0" xr:uid="{1490B07D-0D30-954F-A099-9E74499DCBCD}">
       <text>
         <r>
           <rPr>
@@ -11646,7 +11332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I570" authorId="0" shapeId="0" xr:uid="{35EE82B4-A995-7644-A49E-9BA4936EF62C}">
+    <comment ref="I570" authorId="0" shapeId="0" xr:uid="{AE8C1507-9387-3348-8424-CF03CA5D8BC4}">
       <text>
         <r>
           <rPr>
@@ -11665,7 +11351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I571" authorId="0" shapeId="0" xr:uid="{2914BBA0-A652-774E-94B4-167F87EB3926}">
+    <comment ref="I571" authorId="0" shapeId="0" xr:uid="{5D0B0C07-23A8-404D-A7EC-0D93EC9ED03C}">
       <text>
         <r>
           <rPr>
@@ -11695,7 +11381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I572" authorId="0" shapeId="0" xr:uid="{7FC3AB59-EBC2-C644-BF64-0D0647631646}">
+    <comment ref="I572" authorId="0" shapeId="0" xr:uid="{06E584DA-09D8-E64D-BBC8-CC25BE97D44F}">
       <text>
         <r>
           <rPr>
@@ -11711,7 +11397,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I573" authorId="0" shapeId="0" xr:uid="{7FB708DC-682D-4C44-B3AC-5261A8E6FC1F}">
+    <comment ref="I573" authorId="0" shapeId="0" xr:uid="{885804E3-DD4C-EF42-B9A4-4E15DA637E3D}">
       <text>
         <r>
           <rPr>
@@ -11730,7 +11416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I574" authorId="0" shapeId="0" xr:uid="{02BEC98E-642D-B243-A0B8-4474362A515A}">
+    <comment ref="I574" authorId="0" shapeId="0" xr:uid="{B26F0754-623A-5044-848F-73F2240ACA7A}">
       <text>
         <r>
           <rPr>
@@ -11760,7 +11446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I575" authorId="0" shapeId="0" xr:uid="{3AB0CFC8-FC43-0A43-93C3-4514607FC2E4}">
+    <comment ref="I575" authorId="0" shapeId="0" xr:uid="{833F33B8-E023-D248-AF0A-3F88918AD32B}">
       <text>
         <r>
           <rPr>
@@ -11779,7 +11465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I576" authorId="0" shapeId="0" xr:uid="{4CF4972C-61CA-8F40-82AE-711B0C0A6758}">
+    <comment ref="I576" authorId="0" shapeId="0" xr:uid="{60621DD6-C240-9649-A590-7D7652765897}">
       <text>
         <r>
           <rPr>
@@ -11795,7 +11481,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I577" authorId="0" shapeId="0" xr:uid="{493595A1-B01E-544D-BE62-F37004FA8169}">
+    <comment ref="I577" authorId="0" shapeId="0" xr:uid="{CD5FE3C8-59E4-5646-9E87-1A8FD0753484}">
       <text>
         <r>
           <rPr>
@@ -11814,7 +11500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I578" authorId="0" shapeId="0" xr:uid="{C97671E2-95A0-E24E-ACA5-EAD85AF74BDF}">
+    <comment ref="I578" authorId="0" shapeId="0" xr:uid="{CA6DDB0A-770B-0E4C-BE66-3BAF9476519A}">
       <text>
         <r>
           <rPr>
@@ -11844,7 +11530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I579" authorId="0" shapeId="0" xr:uid="{81618A8E-2C85-004E-9559-732DABF73273}">
+    <comment ref="I579" authorId="0" shapeId="0" xr:uid="{3C2665BC-0981-AB47-AE0D-BD82C016EFFC}">
       <text>
         <r>
           <rPr>
@@ -11863,7 +11549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I580" authorId="0" shapeId="0" xr:uid="{888B08A3-0079-2A45-88A2-6158585C7571}">
+    <comment ref="I580" authorId="0" shapeId="0" xr:uid="{62B9AAC8-EE11-FE44-8A67-F5D64F6EF5C9}">
       <text>
         <r>
           <rPr>
@@ -11882,7 +11568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I581" authorId="0" shapeId="0" xr:uid="{ECC3E955-17B6-A94E-BFB6-0998C9B8828B}">
+    <comment ref="I581" authorId="0" shapeId="0" xr:uid="{EF200FB0-44ED-0044-B30A-F305C26971A0}">
       <text>
         <r>
           <rPr>
@@ -11901,7 +11587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I582" authorId="0" shapeId="0" xr:uid="{0C4EE351-7D0D-4542-B4D2-5697AEB2BC76}">
+    <comment ref="I582" authorId="0" shapeId="0" xr:uid="{5DBDF89A-88B2-604C-A62A-65988A6D7A4B}">
       <text>
         <r>
           <rPr>
@@ -11920,7 +11606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I583" authorId="0" shapeId="0" xr:uid="{AE340974-10AC-9F48-953D-5390C79521FA}">
+    <comment ref="I583" authorId="0" shapeId="0" xr:uid="{A48E172B-9953-724C-9F0D-549739B9139B}">
       <text>
         <r>
           <rPr>
@@ -11952,7 +11638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I584" authorId="0" shapeId="0" xr:uid="{6612F8DE-6B08-B240-B519-47ACD13D66AD}">
+    <comment ref="I584" authorId="0" shapeId="0" xr:uid="{77FCE538-A8C4-2745-B7A7-D660A35E3CA3}">
       <text>
         <r>
           <rPr>
@@ -11969,7 +11655,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I585" authorId="0" shapeId="0" xr:uid="{D37C0F53-C58F-0E43-AE16-49E4F6B688BE}">
+    <comment ref="I585" authorId="0" shapeId="0" xr:uid="{4FA0B0EB-F32E-AB44-80C5-352D5057134C}">
       <text>
         <r>
           <rPr>
@@ -11999,7 +11685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I586" authorId="0" shapeId="0" xr:uid="{456FEDF9-5FF2-4C4F-968C-6DD75F4E23F7}">
+    <comment ref="I586" authorId="0" shapeId="0" xr:uid="{E13CBA0E-74A3-6247-B44E-E614FCB7F597}">
       <text>
         <r>
           <rPr>
@@ -12027,7 +11713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I587" authorId="0" shapeId="0" xr:uid="{5577A95D-5861-C94B-82CB-F2FFA6662FE8}">
+    <comment ref="I587" authorId="0" shapeId="0" xr:uid="{DF95D13E-BA8B-6142-9EE1-566423ACDD04}">
       <text>
         <r>
           <rPr>
@@ -12048,7 +11734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I588" authorId="0" shapeId="0" xr:uid="{D7D44F5F-7BBF-FE44-BA67-7A13352E0398}">
+    <comment ref="I588" authorId="0" shapeId="0" xr:uid="{34D29F08-5EE0-F744-9D32-9E1F4E232739}">
       <text>
         <r>
           <rPr>
@@ -12076,7 +11762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I589" authorId="0" shapeId="0" xr:uid="{E48F789B-30C1-3C46-973D-12805CE5FBAE}">
+    <comment ref="I589" authorId="0" shapeId="0" xr:uid="{4780FE2C-F2A0-9F4A-B710-D00B2E3BAC0A}">
       <text>
         <r>
           <rPr>
@@ -12093,7 +11779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I590" authorId="0" shapeId="0" xr:uid="{6BE71BB0-0C47-604C-8901-5C2E4F142F05}">
+    <comment ref="I590" authorId="0" shapeId="0" xr:uid="{12E11D8A-4C6C-6142-A730-7258C16D5E27}">
       <text>
         <r>
           <rPr>
@@ -12113,7 +11799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I591" authorId="0" shapeId="0" xr:uid="{60F56389-74ED-5B4B-B824-5D62B2069775}">
+    <comment ref="I591" authorId="0" shapeId="0" xr:uid="{A2F58F2E-31DB-7F4D-8670-15E8C3C02B9A}">
       <text>
         <r>
           <rPr>
@@ -12135,7 +11821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I592" authorId="0" shapeId="0" xr:uid="{67CDD586-A935-2041-9824-4C12080CE994}">
+    <comment ref="I592" authorId="0" shapeId="0" xr:uid="{55115EDD-10B7-6442-9101-D19C9F6589D6}">
       <text>
         <r>
           <rPr>
@@ -12152,7 +11838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I593" authorId="0" shapeId="0" xr:uid="{E8DF95FC-520C-A442-A92B-FD2CA6B87908}">
+    <comment ref="I593" authorId="0" shapeId="0" xr:uid="{5676D461-0A53-F34A-9F30-9B800CE24FD0}">
       <text>
         <r>
           <rPr>
@@ -12168,7 +11854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I594" authorId="0" shapeId="0" xr:uid="{96E74BE8-EE01-F244-8DCC-757ABD0A8073}">
+    <comment ref="I594" authorId="0" shapeId="0" xr:uid="{E334E02D-EF89-BB41-AC14-709CA2832C86}">
       <text>
         <r>
           <rPr>
@@ -12191,7 +11877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I595" authorId="0" shapeId="0" xr:uid="{735A8CFB-93F5-4E47-B5F1-F15D2CF224EB}">
+    <comment ref="I595" authorId="0" shapeId="0" xr:uid="{1156037C-235F-7F4F-ABAE-32E676AF1E23}">
       <text>
         <r>
           <rPr>
@@ -12222,7 +11908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I596" authorId="0" shapeId="0" xr:uid="{CF5A4E40-4DAF-FB48-943D-08618CD28C2C}">
+    <comment ref="I596" authorId="0" shapeId="0" xr:uid="{F1E33ED1-9239-2A47-BCB4-7F3E303E2BEC}">
       <text>
         <r>
           <rPr>
@@ -12263,7 +11949,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I597" authorId="0" shapeId="0" xr:uid="{4F4D584F-0783-C341-8F5E-8B0467C18A2C}">
+    <comment ref="I597" authorId="0" shapeId="0" xr:uid="{1310A2F6-14CA-D643-8C7B-76D0CBED45D7}">
       <text>
         <r>
           <rPr>
@@ -12283,7 +11969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I598" authorId="0" shapeId="0" xr:uid="{3A457B5D-43A3-7745-AC9E-6E2F790FAC49}">
+    <comment ref="I598" authorId="0" shapeId="0" xr:uid="{B7B08C42-EA87-5C4F-ACCC-A004E3B0B6F2}">
       <text>
         <r>
           <rPr>
@@ -12323,7 +12009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I599" authorId="0" shapeId="0" xr:uid="{FE95374C-E9AE-8740-9772-FEA444692030}">
+    <comment ref="I599" authorId="0" shapeId="0" xr:uid="{2A2773FB-2805-F641-996C-876C59121250}">
       <text>
         <r>
           <rPr>
@@ -12363,7 +12049,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I600" authorId="0" shapeId="0" xr:uid="{83E3DB38-3252-F948-9FB5-B8EDD27F9E92}">
+    <comment ref="I600" authorId="0" shapeId="0" xr:uid="{8B8D1C2F-9A9D-A44B-AA14-7407014479FD}">
       <text>
         <r>
           <rPr>
@@ -12390,7 +12076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I601" authorId="0" shapeId="0" xr:uid="{35F7EDF5-3324-8E40-9B04-3CA03E8DAE7D}">
+    <comment ref="I601" authorId="0" shapeId="0" xr:uid="{D214ED83-7023-3E49-84B2-45B25792DF50}">
       <text>
         <r>
           <rPr>
@@ -12419,7 +12105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I602" authorId="0" shapeId="0" xr:uid="{77AD5D2F-B683-6740-8359-9AF1D4FDC945}">
+    <comment ref="I602" authorId="0" shapeId="0" xr:uid="{2AAE6B71-0006-F346-95F0-0C3D5393B235}">
       <text>
         <r>
           <rPr>
@@ -12435,7 +12121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I603" authorId="0" shapeId="0" xr:uid="{526D553D-3A0E-A24C-A305-F73877F6BFEF}">
+    <comment ref="I603" authorId="0" shapeId="0" xr:uid="{FD326AB3-9936-E64A-81B6-EDE3D3C4BEC2}">
       <text>
         <r>
           <rPr>
@@ -12458,7 +12144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I604" authorId="0" shapeId="0" xr:uid="{E56ADBF7-7B0F-F843-9E93-D7C7A1849534}">
+    <comment ref="I604" authorId="0" shapeId="0" xr:uid="{7F303C41-9C05-8A48-BECD-E42BBE173D81}">
       <text>
         <r>
           <rPr>
@@ -12483,7 +12169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I605" authorId="0" shapeId="0" xr:uid="{108E5D84-DC15-4548-94C7-7EEB04593D33}">
+    <comment ref="I605" authorId="0" shapeId="0" xr:uid="{8B1C6210-B143-EC47-9AA5-4E25569A036D}">
       <text>
         <r>
           <rPr>
@@ -12515,7 +12201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I606" authorId="0" shapeId="0" xr:uid="{A676A460-F3B3-0F4F-9E53-E43B39005C30}">
+    <comment ref="I606" authorId="0" shapeId="0" xr:uid="{505F527B-9123-C64D-90DE-B97AD6921131}">
       <text>
         <r>
           <rPr>
@@ -12550,7 +12236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I607" authorId="0" shapeId="0" xr:uid="{492F08F6-33E0-5341-8F72-4B310D04AADC}">
+    <comment ref="I607" authorId="0" shapeId="0" xr:uid="{DB52E1E7-48F6-714E-8311-2315A8EBBC4A}">
       <text>
         <r>
           <rPr>
@@ -12572,7 +12258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I608" authorId="0" shapeId="0" xr:uid="{9DBBC74F-D0E0-7646-A4C8-697F433637A2}">
+    <comment ref="I608" authorId="0" shapeId="0" xr:uid="{64A6EC5B-73C4-8740-94C8-E04445C2F152}">
       <text>
         <r>
           <rPr>
@@ -12602,7 +12288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I609" authorId="0" shapeId="0" xr:uid="{B6B0E80E-C187-A44A-8F0D-2B82014542BA}">
+    <comment ref="I609" authorId="0" shapeId="0" xr:uid="{94428467-25C9-0644-8A5C-126DD192F70C}">
       <text>
         <r>
           <rPr>
@@ -12617,7 +12303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I610" authorId="0" shapeId="0" xr:uid="{7AE4A028-CE77-384D-B315-1EB3D8C5B53E}">
+    <comment ref="I610" authorId="0" shapeId="0" xr:uid="{D2E4A929-1C9D-AE4D-B5DC-01BDE1B84C09}">
       <text>
         <r>
           <rPr>
@@ -12645,7 +12331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I611" authorId="0" shapeId="0" xr:uid="{B22938E4-1305-144A-8291-E4EB20F32B49}">
+    <comment ref="I611" authorId="0" shapeId="0" xr:uid="{BB9FC801-66D1-8240-91B8-623FE384D795}">
       <text>
         <r>
           <rPr>
@@ -12666,7 +12352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I612" authorId="0" shapeId="0" xr:uid="{C2B50641-2C98-AF47-8F64-EF68DB302739}">
+    <comment ref="I612" authorId="0" shapeId="0" xr:uid="{F7D8537F-D8B5-674D-97C5-913DE4682C70}">
       <text>
         <r>
           <rPr>
@@ -12707,7 +12393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I613" authorId="0" shapeId="0" xr:uid="{48880FF9-E79C-8144-94CB-3F7E5E03C5EE}">
+    <comment ref="I613" authorId="0" shapeId="0" xr:uid="{5E64F688-3C7C-9D48-9E1F-C656D29712FD}">
       <text>
         <r>
           <rPr>
@@ -12748,7 +12434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I614" authorId="0" shapeId="0" xr:uid="{8BCE32F6-C309-F649-8967-0E9661835654}">
+    <comment ref="I614" authorId="0" shapeId="0" xr:uid="{B6CBABB6-A1FF-CF42-AF67-508F8F00F76A}">
       <text>
         <r>
           <rPr>
@@ -12780,7 +12466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I615" authorId="0" shapeId="0" xr:uid="{29B8AD4E-65F6-A04A-B907-3DB109287D74}">
+    <comment ref="I615" authorId="0" shapeId="0" xr:uid="{BAA2D136-573F-614A-8505-AFE21652B85D}">
       <text>
         <r>
           <rPr>
@@ -12799,7 +12485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I616" authorId="0" shapeId="0" xr:uid="{EC8B4192-23D1-C14B-B438-A46D73539D11}">
+    <comment ref="I616" authorId="0" shapeId="0" xr:uid="{8A6F9A19-675E-4546-BE4C-0114F41D6238}">
       <text>
         <r>
           <rPr>
@@ -12815,7 +12501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I617" authorId="0" shapeId="0" xr:uid="{975912BF-A19F-2544-8036-8A273B79E174}">
+    <comment ref="I617" authorId="0" shapeId="0" xr:uid="{A1968FC3-BC24-5B42-A40E-B12400F44D43}">
       <text>
         <r>
           <rPr>
@@ -12834,7 +12520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I618" authorId="0" shapeId="0" xr:uid="{F78754B6-769C-7B40-A40D-CE707C747DFB}">
+    <comment ref="I618" authorId="0" shapeId="0" xr:uid="{71D6F7E7-410F-254E-B6F2-5F13C04A002D}">
       <text>
         <r>
           <rPr>
@@ -12873,7 +12559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I619" authorId="0" shapeId="0" xr:uid="{1049D513-46EA-5A40-A224-D4392946D7F3}">
+    <comment ref="I619" authorId="0" shapeId="0" xr:uid="{FEC94F2C-6C30-3D46-9F72-DE7EA5FC9B16}">
       <text>
         <r>
           <rPr>
@@ -12900,7 +12586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I620" authorId="0" shapeId="0" xr:uid="{4627DBF6-FAEA-874B-98A1-D35443F29525}">
+    <comment ref="I620" authorId="0" shapeId="0" xr:uid="{9813582A-4337-904B-B214-1536F13CBDDE}">
       <text>
         <r>
           <rPr>
@@ -12929,7 +12615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I621" authorId="0" shapeId="0" xr:uid="{969E7CAC-E5F9-A04F-9397-140BF148ACCD}">
+    <comment ref="I621" authorId="0" shapeId="0" xr:uid="{5308C4A5-8C52-C644-95E2-E015B379C48C}">
       <text>
         <r>
           <rPr>
@@ -12968,7 +12654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I622" authorId="0" shapeId="0" xr:uid="{D95AB5FD-2BE6-D040-9A35-13CBC09065FD}">
+    <comment ref="I622" authorId="0" shapeId="0" xr:uid="{8AB68296-418F-E64A-B33A-AB079250F4AA}">
       <text>
         <r>
           <rPr>
@@ -12995,7 +12681,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I623" authorId="0" shapeId="0" xr:uid="{2B09875D-F616-8E4E-845B-1C853F7A90BF}">
+    <comment ref="I623" authorId="0" shapeId="0" xr:uid="{046F060E-E3E8-9649-AD47-1CF1242F500B}">
       <text>
         <r>
           <rPr>
@@ -13022,7 +12708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I624" authorId="0" shapeId="0" xr:uid="{E1CC4141-BA84-B643-9E5D-9A429B9BA137}">
+    <comment ref="I624" authorId="0" shapeId="0" xr:uid="{49D55F10-81C9-FC45-BB03-92C0A3F67F46}">
       <text>
         <r>
           <rPr>
@@ -13063,7 +12749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I625" authorId="0" shapeId="0" xr:uid="{A065C919-74BB-D342-918F-5F4167BEA48F}">
+    <comment ref="I625" authorId="0" shapeId="0" xr:uid="{DFBE1752-8012-7A4B-8F9D-3DEB7DDA8DEE}">
       <text>
         <r>
           <rPr>
@@ -13104,7 +12790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I626" authorId="0" shapeId="0" xr:uid="{D8E5465E-A35A-064E-AD09-AADEA9482EA6}">
+    <comment ref="I626" authorId="0" shapeId="0" xr:uid="{980E6836-1652-D246-B8C4-0CF4E5D7D69C}">
       <text>
         <r>
           <rPr>
@@ -13127,7 +12813,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I627" authorId="0" shapeId="0" xr:uid="{19AF65ED-7DB0-2445-A331-C77D0AC8BB83}">
+    <comment ref="I627" authorId="0" shapeId="0" xr:uid="{B25E8F73-34A7-AB45-9AFC-2FB444D04CB3}">
       <text>
         <r>
           <rPr>
@@ -13154,7 +12840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I628" authorId="0" shapeId="0" xr:uid="{7508F6E9-A829-594F-9487-7BF55EC42FB6}">
+    <comment ref="I628" authorId="0" shapeId="0" xr:uid="{325D84AC-7F1E-D342-BA27-1EAA695C9DE7}">
       <text>
         <r>
           <rPr>
@@ -13181,7 +12867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I629" authorId="0" shapeId="0" xr:uid="{9E3B99BB-8E5C-054B-A8F5-C91535C39ED8}">
+    <comment ref="I629" authorId="0" shapeId="0" xr:uid="{9BE1FB8C-B0F5-DA48-BDE7-7195508DFC6F}">
       <text>
         <r>
           <rPr>
@@ -13214,7 +12900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I630" authorId="0" shapeId="0" xr:uid="{FC909450-BFEE-CE4B-9792-1759530BA3A5}">
+    <comment ref="I630" authorId="0" shapeId="0" xr:uid="{130AC034-18E5-B544-A83C-506AAA93A287}">
       <text>
         <r>
           <rPr>
@@ -13233,7 +12919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I631" authorId="0" shapeId="0" xr:uid="{4B0B97CC-47B8-E84B-9E5F-30E278DAB5C5}">
+    <comment ref="I631" authorId="0" shapeId="0" xr:uid="{9FB0C9F8-5075-6744-96AE-D86A0AA2691F}">
       <text>
         <r>
           <rPr>
@@ -13269,7 +12955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I632" authorId="0" shapeId="0" xr:uid="{52CD9D11-76C9-AB45-8CBB-7B100385DEDC}">
+    <comment ref="I632" authorId="0" shapeId="0" xr:uid="{2FFC7008-58D0-9F4A-988C-55B3D1B987FE}">
       <text>
         <r>
           <rPr>
@@ -13310,7 +12996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I633" authorId="0" shapeId="0" xr:uid="{37DC7E63-EA77-594C-87FD-9BA461BBBBA9}">
+    <comment ref="I633" authorId="0" shapeId="0" xr:uid="{81466AB1-3CA1-6045-B39F-D663C9E1AEDD}">
       <text>
         <r>
           <rPr>
@@ -13342,7 +13028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I634" authorId="0" shapeId="0" xr:uid="{4F1A6F48-3B74-054A-B1A6-1B0502E391CC}">
+    <comment ref="I634" authorId="0" shapeId="0" xr:uid="{B854F7CF-DB37-5A48-B028-C0EB90362326}">
       <text>
         <r>
           <rPr>
@@ -13383,7 +13069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I635" authorId="0" shapeId="0" xr:uid="{F45E96D8-603D-5544-891C-A1E8F4972CCA}">
+    <comment ref="I635" authorId="0" shapeId="0" xr:uid="{B11621F5-8462-EE4D-9805-002B36165C47}">
       <text>
         <r>
           <rPr>
@@ -13424,7 +13110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I636" authorId="0" shapeId="0" xr:uid="{0E2887A9-2A09-CE4D-8DCB-4195D595EC63}">
+    <comment ref="I636" authorId="0" shapeId="0" xr:uid="{85201442-B94D-0F41-BA2C-5AA96CEEEE22}">
       <text>
         <r>
           <rPr>
@@ -13465,7 +13151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I637" authorId="0" shapeId="0" xr:uid="{DEEFB690-0023-8B44-AAD1-B29A7309EB93}">
+    <comment ref="I637" authorId="0" shapeId="0" xr:uid="{7C533473-5751-6740-B886-01995F21B2E8}">
       <text>
         <r>
           <rPr>
@@ -13497,7 +13183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I638" authorId="0" shapeId="0" xr:uid="{D7240F32-40BA-5246-ABD7-1FC2F1304360}">
+    <comment ref="I638" authorId="0" shapeId="0" xr:uid="{1FA87843-3773-3141-8AC8-6BD8F07F13D7}">
       <text>
         <r>
           <rPr>
@@ -13523,7 +13209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I639" authorId="0" shapeId="0" xr:uid="{9034F70F-67E3-234B-8AE5-EBB33584E0E0}">
+    <comment ref="I639" authorId="0" shapeId="0" xr:uid="{226E9339-AB0C-6247-B370-7A3299C420FA}">
       <text>
         <r>
           <rPr>
@@ -13556,7 +13242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I640" authorId="0" shapeId="0" xr:uid="{FB2C8FB5-1C16-0C48-946B-586231208D17}">
+    <comment ref="I640" authorId="0" shapeId="0" xr:uid="{2735B273-649E-4247-B6A9-4D346BF95E43}">
       <text>
         <r>
           <rPr>
@@ -13597,7 +13283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I641" authorId="0" shapeId="0" xr:uid="{83A83888-7355-A14D-B7B9-735EC52BFB84}">
+    <comment ref="I641" authorId="0" shapeId="0" xr:uid="{C8DF0C2E-D360-BD45-9469-6A81198D303A}">
       <text>
         <r>
           <rPr>
@@ -13614,7 +13300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I642" authorId="0" shapeId="0" xr:uid="{AD846000-EBA1-C548-9759-5C9327004582}">
+    <comment ref="I642" authorId="0" shapeId="0" xr:uid="{6AC8B01F-3136-AB47-8801-24DD9231C82D}">
       <text>
         <r>
           <rPr>
@@ -13644,7 +13330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I643" authorId="0" shapeId="0" xr:uid="{2A8B70FC-6583-5C4F-91D2-B27691CE982D}">
+    <comment ref="I643" authorId="0" shapeId="0" xr:uid="{77F0A14E-0699-5541-9639-EE65AABCF84C}">
       <text>
         <r>
           <rPr>
@@ -13660,7 +13346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I644" authorId="0" shapeId="0" xr:uid="{0090B2B0-1642-D645-967B-56E33C93A865}">
+    <comment ref="I644" authorId="0" shapeId="0" xr:uid="{DFB6066E-E7F4-6347-A6F1-D41A863DB0A9}">
       <text>
         <r>
           <rPr>
@@ -13681,7 +13367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I645" authorId="0" shapeId="0" xr:uid="{5DA9C0B8-461E-D04D-9191-C9AA1DC77174}">
+    <comment ref="I645" authorId="0" shapeId="0" xr:uid="{4DF75E07-4E7F-E343-B685-1F4440BAF2F6}">
       <text>
         <r>
           <rPr>
@@ -13698,7 +13384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I646" authorId="0" shapeId="0" xr:uid="{133184A3-4BBC-9542-B2BA-AC628A7A905F}">
+    <comment ref="I646" authorId="0" shapeId="0" xr:uid="{F1BFE95B-CA39-1C43-B432-3FA941DB8F30}">
       <text>
         <r>
           <rPr>
@@ -13726,7 +13412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I647" authorId="0" shapeId="0" xr:uid="{154A8D5E-8FBA-E747-AEB4-9EBB35B2659B}">
+    <comment ref="I647" authorId="0" shapeId="0" xr:uid="{8D76F4FA-CA4A-1F45-AA54-D2046AB546CF}">
       <text>
         <r>
           <rPr>
@@ -13754,7 +13440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I648" authorId="0" shapeId="0" xr:uid="{370C2592-7CA0-254C-ACB0-5B7D0848D3A5}">
+    <comment ref="I648" authorId="0" shapeId="0" xr:uid="{15845FC3-137E-7546-9BF1-D9B5439670E0}">
       <text>
         <r>
           <rPr>
@@ -13771,7 +13457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I649" authorId="0" shapeId="0" xr:uid="{378B8E47-042D-3940-A0F2-0318D17B8545}">
+    <comment ref="I649" authorId="0" shapeId="0" xr:uid="{A2648DB6-AD41-5745-8693-7B7BA61B46EE}">
       <text>
         <r>
           <rPr>
@@ -13786,7 +13472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I650" authorId="0" shapeId="0" xr:uid="{52760F8A-3450-7543-B0F6-F3921BFC2466}">
+    <comment ref="I650" authorId="0" shapeId="0" xr:uid="{FD500496-5FA0-2E4D-82FA-B5D232A677A1}">
       <text>
         <r>
           <rPr>
@@ -13806,7 +13492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I651" authorId="0" shapeId="0" xr:uid="{CA58AB97-79BB-1245-8654-2F080673D922}">
+    <comment ref="I651" authorId="0" shapeId="0" xr:uid="{A3159CC4-BD2A-1F42-B88D-86A0CA983B94}">
       <text>
         <r>
           <rPr>
@@ -13828,7 +13514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I652" authorId="0" shapeId="0" xr:uid="{30CEBEE9-9F84-C44E-A173-14729A8F7AD0}">
+    <comment ref="I652" authorId="0" shapeId="0" xr:uid="{EFCC521E-AB3B-634C-8E30-C1377C990F6F}">
       <text>
         <r>
           <rPr>
@@ -13850,7 +13536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I653" authorId="0" shapeId="0" xr:uid="{82820C02-5A84-8A4D-AF08-95CAC67E156C}">
+    <comment ref="I653" authorId="0" shapeId="0" xr:uid="{CBE15B19-DD13-1045-B5F3-63B9314D4FA3}">
       <text>
         <r>
           <rPr>
@@ -13866,7 +13552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I654" authorId="0" shapeId="0" xr:uid="{241D1EC0-1B66-3044-ADC9-C25D3622983F}">
+    <comment ref="I654" authorId="0" shapeId="0" xr:uid="{450BAED8-6CB0-574A-8717-04C3E013C100}">
       <text>
         <r>
           <rPr>
@@ -13882,7 +13568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I655" authorId="0" shapeId="0" xr:uid="{F1E33196-BE05-B847-979C-5526B5E5BFD7}">
+    <comment ref="I655" authorId="0" shapeId="0" xr:uid="{B3F86C48-AA0B-F84B-ABE1-E1EE7E007411}">
       <text>
         <r>
           <rPr>
@@ -13900,7 +13586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I656" authorId="0" shapeId="0" xr:uid="{FFB16B36-BDE3-FB41-BB97-A4657343139B}">
+    <comment ref="I656" authorId="0" shapeId="0" xr:uid="{4712BAC2-2092-0344-9162-4A391642E0F7}">
       <text>
         <r>
           <rPr>
@@ -13916,7 +13602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I657" authorId="0" shapeId="0" xr:uid="{0A3CF6A5-0967-5747-90AC-B860F5B2FB87}">
+    <comment ref="I657" authorId="0" shapeId="0" xr:uid="{33228E45-5ED1-5C40-A981-19A84D7124E8}">
       <text>
         <r>
           <rPr>
@@ -13934,7 +13620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I658" authorId="0" shapeId="0" xr:uid="{4BBF8E16-3FF7-9E48-A255-EE459DBE2A07}">
+    <comment ref="I658" authorId="0" shapeId="0" xr:uid="{F8400392-1BCE-F649-A249-5EA71C426DA4}">
       <text>
         <r>
           <rPr>
@@ -13956,7 +13642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I659" authorId="0" shapeId="0" xr:uid="{D65F0C12-927A-AE42-BA40-CCA1AF47926B}">
+    <comment ref="I659" authorId="0" shapeId="0" xr:uid="{B2B04104-EABC-BD42-83EF-955F8EF2B735}">
       <text>
         <r>
           <rPr>
@@ -13980,7 +13666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I660" authorId="0" shapeId="0" xr:uid="{6AFDE9E2-B86A-0B41-9A60-1896FBB3934A}">
+    <comment ref="I660" authorId="0" shapeId="0" xr:uid="{9F2D991F-9D6E-E644-80C2-15CE7AA6BB72}">
       <text>
         <r>
           <rPr>
@@ -13998,7 +13684,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I661" authorId="0" shapeId="0" xr:uid="{199F2860-E91A-944D-ABA2-6D55E724E0C9}">
+    <comment ref="I661" authorId="0" shapeId="0" xr:uid="{8EA17980-32F6-B247-B597-238D76C84E56}">
       <text>
         <r>
           <rPr>
@@ -14022,7 +13708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I662" authorId="0" shapeId="0" xr:uid="{2BE718B0-4BD5-094A-91A8-66A1EC08C73A}">
+    <comment ref="I662" authorId="0" shapeId="0" xr:uid="{A42F7FBB-B026-EC44-B2F5-CF63C59DD47A}">
       <text>
         <r>
           <rPr>
@@ -14038,7 +13724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I663" authorId="0" shapeId="0" xr:uid="{4E89374D-2C21-374A-8253-9445B66DC51F}">
+    <comment ref="I663" authorId="0" shapeId="0" xr:uid="{29A28AE9-7110-D141-B206-062D06617994}">
       <text>
         <r>
           <rPr>
@@ -14054,7 +13740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I664" authorId="0" shapeId="0" xr:uid="{93413257-C1BF-954C-A221-44C9D57D283E}">
+    <comment ref="I664" authorId="0" shapeId="0" xr:uid="{D01EB10C-5C2D-234D-8E4C-E4462A0D1243}">
       <text>
         <r>
           <rPr>
@@ -14070,7 +13756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I665" authorId="0" shapeId="0" xr:uid="{1DCFC453-5718-5B4B-B95C-C47C2D433D76}">
+    <comment ref="I665" authorId="0" shapeId="0" xr:uid="{13173E55-E960-814B-B77D-B20E6DB6AD44}">
       <text>
         <r>
           <rPr>
@@ -14086,7 +13772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I666" authorId="0" shapeId="0" xr:uid="{7973A2BC-BFC5-FF42-873D-AC292B3699D3}">
+    <comment ref="I666" authorId="0" shapeId="0" xr:uid="{E4034BD2-619D-7E41-AF59-BBEBEDC163A5}">
       <text>
         <r>
           <rPr>
@@ -14115,7 +13801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I667" authorId="0" shapeId="0" xr:uid="{D7EAA582-28FD-3247-9334-AA440ECCBAFA}">
+    <comment ref="I667" authorId="0" shapeId="0" xr:uid="{F4775D20-F124-B844-AFD7-C6905EFEF87A}">
       <text>
         <r>
           <rPr>
@@ -14132,7 +13818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I668" authorId="0" shapeId="0" xr:uid="{410DB59D-CD1E-3B45-B298-3CFBF8E1A25F}">
+    <comment ref="I668" authorId="0" shapeId="0" xr:uid="{40DB271E-2F43-4D4F-B451-00137495A8EC}">
       <text>
         <r>
           <rPr>
@@ -14147,7 +13833,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I669" authorId="0" shapeId="0" xr:uid="{91F2A3C4-198D-274D-B5B6-314B160306AD}">
+    <comment ref="I669" authorId="0" shapeId="0" xr:uid="{9E4A9F91-4569-2B46-9B35-22CB6B7DFFF9}">
       <text>
         <r>
           <rPr>
@@ -14162,7 +13848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I670" authorId="0" shapeId="0" xr:uid="{71493C10-1FEA-2946-AA60-3D23F7C6C8E6}">
+    <comment ref="I670" authorId="0" shapeId="0" xr:uid="{F731C76B-A37E-AF48-AA9E-2ECBA7545996}">
       <text>
         <r>
           <rPr>
@@ -14178,7 +13864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I671" authorId="0" shapeId="0" xr:uid="{BF8ECC04-5594-D944-A6C3-6AA56A496F49}">
+    <comment ref="I671" authorId="0" shapeId="0" xr:uid="{0A79DDBE-77C2-F742-9E25-C66A2C60FD8F}">
       <text>
         <r>
           <rPr>
@@ -14207,7 +13893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I672" authorId="0" shapeId="0" xr:uid="{B0625BF8-00BC-CF45-B18A-675A80AFA188}">
+    <comment ref="I672" authorId="0" shapeId="0" xr:uid="{4517B323-B06A-A24A-A7C2-AA8A74DE8291}">
       <text>
         <r>
           <rPr>
@@ -14236,7 +13922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I673" authorId="0" shapeId="0" xr:uid="{E40000D6-79D5-E74A-A3D9-C21FC146B83A}">
+    <comment ref="I673" authorId="0" shapeId="0" xr:uid="{D5ED0A45-D3B2-824D-A9D1-5E20AB2D7708}">
       <text>
         <r>
           <rPr>
@@ -14260,7 +13946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I674" authorId="0" shapeId="0" xr:uid="{33A2028B-9664-AA48-9719-09788356D8C2}">
+    <comment ref="I674" authorId="0" shapeId="0" xr:uid="{E1499AD9-49CA-834E-B02A-B96BF21F22BE}">
       <text>
         <r>
           <rPr>
@@ -14277,7 +13963,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I675" authorId="0" shapeId="0" xr:uid="{E4D1FA89-5AA0-224F-90C1-EB9EBACCAC6C}">
+    <comment ref="I675" authorId="0" shapeId="0" xr:uid="{0BA3FC4B-C36A-A043-89B8-FE116CFCBDE8}">
       <text>
         <r>
           <rPr>
@@ -14306,7 +13992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I676" authorId="0" shapeId="0" xr:uid="{699D3239-DB78-514A-A0BD-73757ED1D065}">
+    <comment ref="I676" authorId="0" shapeId="0" xr:uid="{316E4311-81FD-F646-BA14-864B590865E0}">
       <text>
         <r>
           <rPr>
@@ -14342,1184 +14028,57 @@
         </r>
       </text>
     </comment>
-    <comment ref="I677" authorId="0" shapeId="0" xr:uid="{F351A2BA-6AAD-8D44-B2F0-00213F003982}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>엘리자벳</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>옥주현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>죽음</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이해준</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루케니</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이지훈</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>요제프</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>길병민</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>소피</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>주아</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루돌프</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>장윤석</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>막스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>공작</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>문성혁</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>볼프</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>부인</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김지선</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>에스터하지</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>백작부인</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>유신</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>헬레네</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박선정</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>황실</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>세력가들</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>공민섭</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>제병진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>신재희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>나현수</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>장윤호</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윤보경</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>앙상블</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이수현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>손의완</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>전선진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>채성욱</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>지원선</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>서은혜</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정태진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>오태희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김한결</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>전주일</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임다현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스윙</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정원일</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이강</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정은지</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>강수민</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>죽음의</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>천사들</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김동하</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김경일</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최낙권</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이선우</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정상효</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박신형</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스윙</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임종우</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I678" authorId="0" shapeId="0" xr:uid="{E4856D12-C49E-F04F-B627-5575070F161D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>마크</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정성일</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>싱어</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최석진</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I679" authorId="0" shapeId="0" xr:uid="{F488E32F-B6BB-D24D-94E5-D0E11360686D}">
+    <comment ref="I677" authorId="0" shapeId="0" xr:uid="{E376A43B-A630-9044-9443-D8756F34EB12}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>엘리자벳: 옥주현
+죽음: 이해준
+루케니: 이지훈
+요제프: 길병민
+소피: 주아
+루돌프: 장윤석
+막스 공작: 문성혁
+볼프 부인: 김지선
+에스터하지 백작부인: 유신
+헬레네: 박선정
+황실 세력가들: 
+공민섭 제병진 신재희 
+나현수 장윤호 윤보경
+앙상블: 
+이수현 손의완 전선진 채성욱 
+지원선 서은혜 정태진 오태희 
+김한결 전주일 임다현
+스윙: 
+정원일 이강 정은지 강수민
+죽음의 천사들: 
+김동하 김경일 최낙권 이선우 
+정상효 박신형 (스윙: 임종우)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I678" authorId="0" shapeId="0" xr:uid="{74F657FE-15C6-F94A-B6B6-2FA12525A012}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 정성일
+싱어: 최석진</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I679" authorId="0" shapeId="0" xr:uid="{5B56118E-0F39-6942-8B63-D3EB9C3F0669}">
       <text>
         <r>
           <rPr>
@@ -15537,7 +14096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I680" authorId="0" shapeId="0" xr:uid="{BE9149ED-F1DB-A745-AB3E-D1EFA535B06C}">
+    <comment ref="I680" authorId="0" shapeId="0" xr:uid="{BB1516AD-9AC4-0142-A228-2DFAC4F21209}">
       <text>
         <r>
           <rPr>
@@ -15552,213 +14111,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="I681" authorId="0" shapeId="0" xr:uid="{266E3621-CF22-934D-B8BD-D19C930222C9}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>서정인</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>홍나현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윤석영</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>홍승안</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>강재호</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김석환</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김만중</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김지훈</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이복자</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이선주</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>그</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I682" authorId="0" shapeId="0" xr:uid="{9BF527C7-2DF9-D04B-9A93-CE4FAE47E432}">
+    <comment ref="I681" authorId="0" shapeId="0" xr:uid="{539C3B37-1AA1-6D4D-9F19-5E014F430646}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>서정인: 홍나현
+윤석영: 홍승안
+강재호: 김석환
+김만중: 김지훈
+이복자: 이선주(그)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I682" authorId="0" shapeId="0" xr:uid="{7A6C9023-53E5-C845-8818-F7E473432744}">
       <text>
         <r>
           <rPr>
@@ -15775,7 +14146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I683" authorId="0" shapeId="0" xr:uid="{A235258B-955A-3D4C-A6BB-B79F9C4185E4}">
+    <comment ref="I683" authorId="0" shapeId="0" xr:uid="{3F3CDB65-1061-BB48-88D3-647E1A1FBD08}">
       <text>
         <r>
           <rPr>
@@ -15791,23 +14162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I684" authorId="0" shapeId="0" xr:uid="{0D78E005-8D48-1E4A-85C0-7E2F2F09575C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>티볼트: 박정복
-머큐쇼: 신주협
-플레이어: 조성윤</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I685" authorId="0" shapeId="0" xr:uid="{9213C35F-8F1F-C241-8384-2608086D8CA2}">
+    <comment ref="I684" authorId="0" shapeId="0" xr:uid="{2804BDB3-6D94-F94A-834F-6701FAC0BB9E}">
       <text>
         <r>
           <rPr>
@@ -15816,7 +14171,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>준희</t>
+          <t>티볼트</t>
         </r>
         <r>
           <rPr>
@@ -15834,7 +14189,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>강병훈</t>
+          <t>박정복</t>
         </r>
         <r>
           <rPr>
@@ -15853,7 +14208,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>정우</t>
+          <t>머큐쇼</t>
         </r>
         <r>
           <rPr>
@@ -15871,7 +14226,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>이석준</t>
+          <t>신주협</t>
         </r>
         <r>
           <rPr>
@@ -15880,7 +14235,8 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>(</t>
+          <t xml:space="preserve">
+</t>
         </r>
         <r>
           <rPr>
@@ -15889,7 +14245,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>풍</t>
+          <t>플레이어</t>
         </r>
         <r>
           <rPr>
@@ -15898,8 +14254,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">)
-</t>
+          <t xml:space="preserve">: </t>
         </r>
         <r>
           <rPr>
@@ -15908,29 +14263,27 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>연희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임하윤</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I686" authorId="0" shapeId="0" xr:uid="{F851B4C5-13A8-E840-A310-7FF5FE10181E}">
+          <t>조성윤</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I685" authorId="0" shapeId="0" xr:uid="{3AFBB8EC-1586-0A4D-AD91-D36281C8B605}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>준희: 강병훈
+정우: 이석준(풍)
+연희: 임하윤</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I686" authorId="0" shapeId="0" xr:uid="{15F624F2-3951-664C-AAAD-68F9C907D5C7}">
       <text>
         <r>
           <rPr>
@@ -15950,7 +14303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I687" authorId="0" shapeId="0" xr:uid="{20FA8872-4C5C-7E4C-ACAB-4749A5182B46}">
+    <comment ref="I687" authorId="0" shapeId="0" xr:uid="{A0F31E08-FBF8-8A4F-ADDA-3CA6F609A742}">
       <text>
         <r>
           <rPr>
@@ -15968,7 +14321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I688" authorId="0" shapeId="0" xr:uid="{E7751E25-B3D0-1546-9CFF-2128B543A262}">
+    <comment ref="I688" authorId="0" shapeId="0" xr:uid="{EE6EF0AB-72EA-DB4C-B5FB-A671B6F5192E}">
       <text>
         <r>
           <rPr>
@@ -15985,21 +14338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I689" authorId="0" shapeId="0" xr:uid="{61BF73E4-404F-7C4D-975B-03F982A3A50B}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>퍼포머: 고훈정</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I690" authorId="0" shapeId="0" xr:uid="{75F70A93-943C-DF47-9265-9383461684D1}">
+    <comment ref="I689" authorId="0" shapeId="0" xr:uid="{A7A6061C-13BB-0944-BDE6-5D59ED18F037}">
       <text>
         <r>
           <rPr>
@@ -16008,7 +14347,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>폴</t>
+          <t>퍼포머</t>
         </r>
         <r>
           <rPr>
@@ -16026,159 +14365,29 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>황두현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>왓슨</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박은미</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루시</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>송영미</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>니콜라이</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김대현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>기욤</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>장두환</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I691" authorId="0" shapeId="0" xr:uid="{D38DC41D-F222-1346-8C33-1E30F545F764}">
+          <t>고훈정</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I690" authorId="0" shapeId="0" xr:uid="{DC47FF4E-DCDA-284E-AF40-23247D35CE3E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>폴: 황두현
+왓슨: 박은미
+루시: 송영미
+니콜라이: 김대현
+기욤: 장두환</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I691" authorId="0" shapeId="0" xr:uid="{2916889E-6DF1-C144-9FCF-06D4DE25542B}">
       <text>
         <r>
           <rPr>
@@ -16196,7 +14405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I692" authorId="0" shapeId="0" xr:uid="{199D9A08-9F39-7144-9360-2CC16E2884FB}">
+    <comment ref="I692" authorId="0" shapeId="0" xr:uid="{17F02FA4-2134-7541-B212-69CB020F5881}">
       <text>
         <r>
           <rPr>
@@ -16214,7 +14423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I693" authorId="0" shapeId="0" xr:uid="{A6BEC186-5363-194B-A33C-CE1A8AE8C038}">
+    <comment ref="I693" authorId="0" shapeId="0" xr:uid="{5705ECB4-709F-F94F-8FC4-01BD672F2192}">
       <text>
         <r>
           <rPr>
@@ -16234,149 +14443,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="I694" authorId="0" shapeId="0" xr:uid="{38EE38E3-ACB2-094B-B9E4-5B17CFD70B7C}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>필립</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이형훈</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>올리버</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김이준</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>실비아</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김수연</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>남자</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박성현</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I695" authorId="0" shapeId="0" xr:uid="{28E0871A-DF43-744D-933B-4F02988B20CE}">
+    <comment ref="I694" authorId="0" shapeId="0" xr:uid="{2610E0F0-A287-734A-A56E-0F3A2011F50B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>필립: 이형훈
+올리버: 김이준
+실비아: 김수연
+남자: 박성현</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I695" authorId="0" shapeId="0" xr:uid="{8C81823A-FCF0-F04B-A38F-BD06E3344F9E}">
       <text>
         <r>
           <rPr>
@@ -16393,7 +14477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I696" authorId="0" shapeId="0" xr:uid="{C77E296D-6134-6147-A8E5-7E15FBE9F745}">
+    <comment ref="I696" authorId="0" shapeId="0" xr:uid="{927C0DA7-B0AE-4847-95F6-E6387F7DA11A}">
       <text>
         <r>
           <rPr>
@@ -16410,7 +14494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I697" authorId="0" shapeId="0" xr:uid="{0C5F3FBF-91FC-5648-B1EE-43CD62D31305}">
+    <comment ref="I697" authorId="0" shapeId="0" xr:uid="{367AA438-8510-5042-8BC2-9B8AFFA2244E}">
       <text>
         <r>
           <rPr>
@@ -16430,7 +14514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I698" authorId="0" shapeId="0" xr:uid="{0C5C2DE8-D4CD-F446-95E2-30494992FBAB}">
+    <comment ref="I698" authorId="0" shapeId="0" xr:uid="{F9A3B408-00C8-1047-A923-8EA539FC936B}">
       <text>
         <r>
           <rPr>
@@ -16448,7 +14532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I699" authorId="0" shapeId="0" xr:uid="{C07103F6-3FE9-D744-9338-03BD9D9DECCE}">
+    <comment ref="I699" authorId="0" shapeId="0" xr:uid="{A7D8411F-5B7C-0348-B1B1-EC14CF94E0F4}">
       <text>
         <r>
           <rPr>
@@ -16464,7 +14548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I700" authorId="0" shapeId="0" xr:uid="{7C8A5966-A29E-B341-BFD0-692387D8CFDB}">
+    <comment ref="I700" authorId="0" shapeId="0" xr:uid="{97271644-6ADA-F240-B3CB-6CABA32BF851}">
       <text>
         <r>
           <rPr>
@@ -16482,7 +14566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I701" authorId="0" shapeId="0" xr:uid="{4207D938-BFC2-6648-97FA-73F07DF4BD54}">
+    <comment ref="I701" authorId="0" shapeId="0" xr:uid="{E3F868AF-E82B-464F-B604-BC05FC229C69}">
       <text>
         <r>
           <rPr>
@@ -16501,75 +14585,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="I702" authorId="0" shapeId="0" xr:uid="{C441BF05-A9A1-5547-9E47-8E40C44E6D35}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>양희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이봄소리</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>해준</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윤은오</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I703" authorId="0" shapeId="0" xr:uid="{5A26CC17-E545-AD46-9A5C-6529AE1B2B91}">
+    <comment ref="I702" authorId="0" shapeId="0" xr:uid="{3A7B9C56-7F4B-9F46-82D4-C0470FBD5692}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>양희: 이봄소리
+해준: 윤은오</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I703" authorId="0" shapeId="0" xr:uid="{641019D0-7258-DA48-AAB3-27922009C955}">
       <text>
         <r>
           <rPr>
@@ -16587,7 +14618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I704" authorId="0" shapeId="0" xr:uid="{D006482A-941D-134E-A523-CB604EF56E15}">
+    <comment ref="I704" authorId="0" shapeId="0" xr:uid="{BF711E08-2B87-0E49-BDFE-84306BF99155}">
       <text>
         <r>
           <rPr>
@@ -16614,7 +14645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I705" authorId="0" shapeId="0" xr:uid="{5423095D-F9A9-2B44-AD05-6261AF4A9FCD}">
+    <comment ref="I705" authorId="0" shapeId="0" xr:uid="{DB67DA79-EDBA-CA45-B755-9B254226CAF5}">
       <text>
         <r>
           <rPr>
@@ -16630,7 +14661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I706" authorId="0" shapeId="0" xr:uid="{59383DDC-B332-0944-9A9F-21DA4CF01540}">
+    <comment ref="I706" authorId="0" shapeId="0" xr:uid="{10A606E3-6ED2-D046-8B04-15E68CE19565}">
       <text>
         <r>
           <rPr>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C416EF-5D12-3849-AC2C-B866AF844443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844F475D-5BEC-0849-9F06-6E278E4B6D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -1996,18 +1996,251 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>한영범: 조성윤
-류순호: 정휘
-이창섭: 차용학
-신석구: 안지환
-조동현: 김대웅
-변주화: 손유동
-여신: 이지숙</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>한영범</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조성윤</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>류순호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정휘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이창섭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>차용학</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신석구</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>안지환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조동현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김대웅</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>변주화</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>손유동</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>여신</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이지숙</t>
         </r>
       </text>
     </comment>
@@ -14134,15 +14367,176 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>이방인/자크: 현석준
-카트린/루시: 안유진
-앙리: 김우성
-샤를로트: 장예원</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이방인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>자크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>현석준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>카트린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>안유진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앙리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김우성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>샤를로트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장예원</t>
         </r>
       </text>
     </comment>
@@ -24908,9 +25302,6 @@
     <t>https://pbs.twimg.com/media/Eng80_UUwAALCHD?format=jpg&amp;name=large</t>
   </si>
   <si>
-    <t>https://pbs.twimg.com/media/ExKnKiVVgAMlaud?format=jpg&amp;name=large</t>
-  </si>
-  <si>
     <t>https://pbs.twimg.com/media/E5riWU3VIAIQauK?format=jpg&amp;name=large</t>
   </si>
   <si>
@@ -25634,9 +26025,6 @@
     <t>https://pbs.twimg.com/media/Eu_sV_RVcAIP99C?format=jpg&amp;name=large</t>
   </si>
   <si>
-    <t>https://pbs.twimg.com/media/ExPvaqcXEAUQVX1?format=jpg&amp;name=large</t>
-  </si>
-  <si>
     <t>https://pbs.twimg.com/media/ExjBeL3VcAQJ7QI?format=jpg&amp;name=large</t>
   </si>
   <si>
@@ -26565,6 +26953,12 @@
   </si>
   <si>
     <t>https://pbs.twimg.com/media/F_ouLkgWQAEJXga?format=jpg&amp;name=large</t>
+  </si>
+  <si>
+    <t>https://pbs.twimg.com/media/ExKnKiVVgAMWHrg?format=jpg&amp;name=large</t>
+  </si>
+  <si>
+    <t>https://pbs.twimg.com/media/ExPvaqcXEAUAMdI?format=jpg&amp;name=large</t>
   </si>
 </sst>
 </file>
@@ -28463,7 +28857,7 @@
         <v>2985</v>
       </c>
       <c r="P7" s="62" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="17" customHeight="1">
@@ -28514,7 +28908,7 @@
         <v>2986</v>
       </c>
       <c r="P8" s="62" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="17" customHeight="1">
@@ -28565,7 +28959,7 @@
         <v>2987</v>
       </c>
       <c r="P9" s="62" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="17" customHeight="1">
@@ -28616,7 +29010,7 @@
         <v>2988</v>
       </c>
       <c r="P10" s="62" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="17" customHeight="1">
@@ -28667,7 +29061,7 @@
         <v>2989</v>
       </c>
       <c r="P11" s="62" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="17" customHeight="1">
@@ -28718,7 +29112,7 @@
         <v>2990</v>
       </c>
       <c r="P12" s="62" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="17" customHeight="1">
@@ -28769,7 +29163,7 @@
         <v>2991</v>
       </c>
       <c r="P13" s="62" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="17" customHeight="1">
@@ -28820,7 +29214,7 @@
         <v>2992</v>
       </c>
       <c r="P14" s="62" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="17" customHeight="1">
@@ -28871,7 +29265,7 @@
         <v>2993</v>
       </c>
       <c r="P15" s="62" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="17" customHeight="1">
@@ -28922,7 +29316,7 @@
         <v>2994</v>
       </c>
       <c r="P16" s="62" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="17" customHeight="1">
@@ -28973,7 +29367,7 @@
         <v>2995</v>
       </c>
       <c r="P17" s="62" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="17" customHeight="1">
@@ -29024,7 +29418,7 @@
         <v>2996</v>
       </c>
       <c r="P18" s="62" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="17" customHeight="1">
@@ -29075,7 +29469,7 @@
         <v>2997</v>
       </c>
       <c r="P19" s="62" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="17" customHeight="1">
@@ -29120,10 +29514,10 @@
         <v>1255</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>16</v>
+        <v>2998</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>2998</v>
+        <v>16</v>
       </c>
       <c r="P20" s="62" t="s">
         <v>3390</v>
@@ -29171,13 +29565,13 @@
         <v>1257</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>16</v>
+        <v>2999</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>2999</v>
+        <v>16</v>
       </c>
       <c r="P21" s="62" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="17" customHeight="1">
@@ -29222,13 +29616,13 @@
         <v>1259</v>
       </c>
       <c r="N22" s="46" t="s">
-        <v>16</v>
+        <v>3000</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>3000</v>
+        <v>16</v>
       </c>
       <c r="P22" s="62" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="17" customHeight="1">
@@ -29273,13 +29667,13 @@
         <v>1261</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>16</v>
+        <v>3001</v>
       </c>
       <c r="O23" s="47" t="s">
-        <v>3001</v>
+        <v>16</v>
       </c>
       <c r="P23" s="62" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="17" customHeight="1">
@@ -29324,13 +29718,13 @@
         <v>1263</v>
       </c>
       <c r="N24" s="46" t="s">
-        <v>16</v>
+        <v>3002</v>
       </c>
       <c r="O24" s="47" t="s">
-        <v>3002</v>
+        <v>16</v>
       </c>
       <c r="P24" s="62" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="17" customHeight="1">
@@ -29375,13 +29769,13 @@
         <v>1265</v>
       </c>
       <c r="N25" s="46" t="s">
-        <v>16</v>
+        <v>3003</v>
       </c>
       <c r="O25" s="47" t="s">
-        <v>3003</v>
+        <v>16</v>
       </c>
       <c r="P25" s="62" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="17" customHeight="1">
@@ -29426,13 +29820,13 @@
         <v>1267</v>
       </c>
       <c r="N26" s="46" t="s">
-        <v>16</v>
+        <v>3004</v>
       </c>
       <c r="O26" s="47" t="s">
-        <v>3004</v>
+        <v>16</v>
       </c>
       <c r="P26" s="62" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="17" customHeight="1">
@@ -29477,10 +29871,10 @@
         <v>1269</v>
       </c>
       <c r="N27" s="46" t="s">
-        <v>16</v>
+        <v>3005</v>
       </c>
       <c r="O27" s="47" t="s">
-        <v>3005</v>
+        <v>16</v>
       </c>
       <c r="P27" s="62" t="s">
         <v>3258</v>
@@ -29579,10 +29973,10 @@
         <v>1273</v>
       </c>
       <c r="N29" s="46" t="s">
-        <v>16</v>
+        <v>3007</v>
       </c>
       <c r="O29" s="47" t="s">
-        <v>3007</v>
+        <v>16</v>
       </c>
       <c r="P29" s="62" t="s">
         <v>3259</v>
@@ -29732,13 +30126,13 @@
         <v>1279</v>
       </c>
       <c r="N32" s="46" t="s">
-        <v>16</v>
+        <v>3010</v>
       </c>
       <c r="O32" s="47" t="s">
-        <v>3010</v>
+        <v>16</v>
       </c>
       <c r="P32" s="62" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="17" customHeight="1">
@@ -29783,13 +30177,13 @@
         <v>1281</v>
       </c>
       <c r="N33" s="46" t="s">
-        <v>16</v>
+        <v>3011</v>
       </c>
       <c r="O33" s="47" t="s">
-        <v>3011</v>
+        <v>16</v>
       </c>
       <c r="P33" s="62" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="17" customHeight="1">
@@ -29885,13 +30279,13 @@
         <v>1285</v>
       </c>
       <c r="N35" s="46" t="s">
-        <v>16</v>
+        <v>3013</v>
       </c>
       <c r="O35" s="47" t="s">
-        <v>3013</v>
+        <v>16</v>
       </c>
       <c r="P35" s="62" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="17" customHeight="1">
@@ -29987,13 +30381,13 @@
         <v>1289</v>
       </c>
       <c r="N37" s="46" t="s">
-        <v>16</v>
+        <v>3015</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>3015</v>
+        <v>16</v>
       </c>
       <c r="P37" s="62" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="17" customHeight="1">
@@ -30044,7 +30438,7 @@
         <v>3016</v>
       </c>
       <c r="P38" s="62" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="17" customHeight="1">
@@ -30089,13 +30483,13 @@
         <v>1293</v>
       </c>
       <c r="N39" s="46" t="s">
-        <v>16</v>
+        <v>3017</v>
       </c>
       <c r="O39" s="47" t="s">
-        <v>3017</v>
+        <v>16</v>
       </c>
       <c r="P39" s="62" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="17" customHeight="1">
@@ -30140,13 +30534,13 @@
         <v>1295</v>
       </c>
       <c r="N40" s="46" t="s">
-        <v>16</v>
+        <v>3018</v>
       </c>
       <c r="O40" s="47" t="s">
-        <v>3018</v>
+        <v>16</v>
       </c>
       <c r="P40" s="62" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="17" customHeight="1">
@@ -30197,7 +30591,7 @@
         <v>3019</v>
       </c>
       <c r="P41" s="62" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="17" customHeight="1">
@@ -30242,13 +30636,13 @@
         <v>1299</v>
       </c>
       <c r="N42" s="46" t="s">
-        <v>16</v>
+        <v>3020</v>
       </c>
       <c r="O42" s="47" t="s">
-        <v>3020</v>
+        <v>16</v>
       </c>
       <c r="P42" s="62" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="17" customHeight="1">
@@ -30293,13 +30687,13 @@
         <v>1301</v>
       </c>
       <c r="N43" s="46" t="s">
-        <v>16</v>
+        <v>3021</v>
       </c>
       <c r="O43" s="47" t="s">
-        <v>3021</v>
+        <v>16</v>
       </c>
       <c r="P43" s="62" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="17" customHeight="1">
@@ -30344,13 +30738,13 @@
         <v>1303</v>
       </c>
       <c r="N44" s="46" t="s">
-        <v>16</v>
+        <v>3022</v>
       </c>
       <c r="O44" s="47" t="s">
-        <v>3022</v>
+        <v>16</v>
       </c>
       <c r="P44" s="62" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="17" customHeight="1">
@@ -30401,7 +30795,7 @@
         <v>3023</v>
       </c>
       <c r="P45" s="62" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="17" customHeight="1">
@@ -30497,13 +30891,13 @@
         <v>1309</v>
       </c>
       <c r="N47" s="46" t="s">
-        <v>16</v>
+        <v>3025</v>
       </c>
       <c r="O47" s="47" t="s">
-        <v>3025</v>
+        <v>16</v>
       </c>
       <c r="P47" s="62" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="17" customHeight="1">
@@ -30548,13 +30942,13 @@
         <v>1311</v>
       </c>
       <c r="N48" s="46" t="s">
-        <v>16</v>
+        <v>3026</v>
       </c>
       <c r="O48" s="47" t="s">
-        <v>3026</v>
+        <v>16</v>
       </c>
       <c r="P48" s="62" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="17" customHeight="1">
@@ -30605,7 +30999,7 @@
         <v>3027</v>
       </c>
       <c r="P49" s="62" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="17" customHeight="1">
@@ -30656,7 +31050,7 @@
         <v>3028</v>
       </c>
       <c r="P50" s="62" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="17" customHeight="1">
@@ -30701,13 +31095,13 @@
         <v>1317</v>
       </c>
       <c r="N51" s="46" t="s">
-        <v>16</v>
+        <v>3029</v>
       </c>
       <c r="O51" s="47" t="s">
-        <v>3029</v>
+        <v>16</v>
       </c>
       <c r="P51" s="62" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="17" customHeight="1">
@@ -30752,10 +31146,10 @@
         <v>1319</v>
       </c>
       <c r="N52" s="46" t="s">
-        <v>16</v>
+        <v>3030</v>
       </c>
       <c r="O52" s="47" t="s">
-        <v>3030</v>
+        <v>16</v>
       </c>
       <c r="P52" s="62" t="s">
         <v>3260</v>
@@ -30803,13 +31197,13 @@
         <v>1321</v>
       </c>
       <c r="N53" s="46" t="s">
-        <v>16</v>
+        <v>3031</v>
       </c>
       <c r="O53" s="47" t="s">
-        <v>3031</v>
+        <v>16</v>
       </c>
       <c r="P53" s="62" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="17" customHeight="1">
@@ -30854,13 +31248,13 @@
         <v>1323</v>
       </c>
       <c r="N54" s="46" t="s">
-        <v>16</v>
+        <v>3032</v>
       </c>
       <c r="O54" s="47" t="s">
-        <v>3032</v>
+        <v>16</v>
       </c>
       <c r="P54" s="62" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="17" customHeight="1">
@@ -30905,13 +31299,13 @@
         <v>1325</v>
       </c>
       <c r="N55" s="46" t="s">
-        <v>16</v>
+        <v>3033</v>
       </c>
       <c r="O55" s="47" t="s">
-        <v>3033</v>
+        <v>16</v>
       </c>
       <c r="P55" s="62" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="17" customHeight="1">
@@ -31058,10 +31452,10 @@
         <v>1331</v>
       </c>
       <c r="N58" s="46" t="s">
-        <v>16</v>
+        <v>3035</v>
       </c>
       <c r="O58" s="47" t="s">
-        <v>3035</v>
+        <v>16</v>
       </c>
       <c r="P58" s="62" t="s">
         <v>3261</v>
@@ -31115,7 +31509,7 @@
         <v>16</v>
       </c>
       <c r="P59" s="62" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="17" customHeight="1">
@@ -31160,10 +31554,10 @@
         <v>1335</v>
       </c>
       <c r="N60" s="46" t="s">
-        <v>16</v>
+        <v>3036</v>
       </c>
       <c r="O60" s="47" t="s">
-        <v>3036</v>
+        <v>16</v>
       </c>
       <c r="P60" s="62" t="s">
         <v>3262</v>
@@ -31211,13 +31605,13 @@
         <v>1337</v>
       </c>
       <c r="N61" s="46" t="s">
-        <v>16</v>
+        <v>3037</v>
       </c>
       <c r="O61" s="47" t="s">
-        <v>3037</v>
+        <v>16</v>
       </c>
       <c r="P61" s="62" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="17" customHeight="1">
@@ -31262,13 +31656,13 @@
         <v>1339</v>
       </c>
       <c r="N62" s="46" t="s">
-        <v>16</v>
+        <v>3038</v>
       </c>
       <c r="O62" s="47" t="s">
-        <v>3038</v>
+        <v>16</v>
       </c>
       <c r="P62" s="62" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="17" customHeight="1">
@@ -31313,10 +31707,10 @@
         <v>1341</v>
       </c>
       <c r="N63" s="46" t="s">
-        <v>16</v>
+        <v>3039</v>
       </c>
       <c r="O63" s="47" t="s">
-        <v>3039</v>
+        <v>16</v>
       </c>
       <c r="P63" s="62" t="s">
         <v>3263</v>
@@ -31364,13 +31758,13 @@
         <v>1343</v>
       </c>
       <c r="N64" s="46" t="s">
-        <v>16</v>
+        <v>3040</v>
       </c>
       <c r="O64" s="47" t="s">
-        <v>3040</v>
+        <v>16</v>
       </c>
       <c r="P64" s="62" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="17" customHeight="1">
@@ -31421,7 +31815,7 @@
         <v>16</v>
       </c>
       <c r="P65" s="62" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="17" customHeight="1">
@@ -31466,10 +31860,10 @@
         <v>1347</v>
       </c>
       <c r="N66" s="46" t="s">
-        <v>16</v>
+        <v>3041</v>
       </c>
       <c r="O66" s="47" t="s">
-        <v>3041</v>
+        <v>16</v>
       </c>
       <c r="P66" s="62" t="s">
         <v>3399</v>
@@ -31517,10 +31911,10 @@
         <v>1349</v>
       </c>
       <c r="N67" s="46" t="s">
-        <v>16</v>
+        <v>3042</v>
       </c>
       <c r="O67" s="47" t="s">
-        <v>3042</v>
+        <v>16</v>
       </c>
       <c r="P67" s="62" t="s">
         <v>3264</v>
@@ -31568,10 +31962,10 @@
         <v>1351</v>
       </c>
       <c r="N68" s="46" t="s">
-        <v>16</v>
+        <v>3043</v>
       </c>
       <c r="O68" s="47" t="s">
-        <v>3043</v>
+        <v>16</v>
       </c>
       <c r="P68" s="62" t="s">
         <v>3265</v>
@@ -31619,10 +32013,10 @@
         <v>1353</v>
       </c>
       <c r="N69" s="46" t="s">
-        <v>16</v>
+        <v>3044</v>
       </c>
       <c r="O69" s="47" t="s">
-        <v>3044</v>
+        <v>16</v>
       </c>
       <c r="P69" s="62" t="s">
         <v>3266</v>
@@ -31676,7 +32070,7 @@
         <v>3045</v>
       </c>
       <c r="P70" s="62" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="17" customHeight="1">
@@ -31721,10 +32115,10 @@
         <v>1357</v>
       </c>
       <c r="N71" s="46" t="s">
-        <v>16</v>
+        <v>3046</v>
       </c>
       <c r="O71" s="47" t="s">
-        <v>3046</v>
+        <v>16</v>
       </c>
       <c r="P71" s="62" t="s">
         <v>3267</v>
@@ -31778,7 +32172,7 @@
         <v>3047</v>
       </c>
       <c r="P72" s="62" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="17" customHeight="1">
@@ -31823,10 +32217,10 @@
         <v>1361</v>
       </c>
       <c r="N73" s="46" t="s">
-        <v>16</v>
+        <v>3048</v>
       </c>
       <c r="O73" s="47" t="s">
-        <v>3048</v>
+        <v>16</v>
       </c>
       <c r="P73" s="62" t="s">
         <v>3400</v>
@@ -31874,10 +32268,10 @@
         <v>1363</v>
       </c>
       <c r="N74" s="46" t="s">
-        <v>16</v>
+        <v>3049</v>
       </c>
       <c r="O74" s="47" t="s">
-        <v>3049</v>
+        <v>16</v>
       </c>
       <c r="P74" s="62" t="s">
         <v>3268</v>
@@ -31925,10 +32319,10 @@
         <v>1365</v>
       </c>
       <c r="N75" s="46" t="s">
-        <v>16</v>
+        <v>3050</v>
       </c>
       <c r="O75" s="47" t="s">
-        <v>3050</v>
+        <v>16</v>
       </c>
       <c r="P75" s="62" t="s">
         <v>3269</v>
@@ -31976,13 +32370,13 @@
         <v>1367</v>
       </c>
       <c r="N76" s="46" t="s">
-        <v>16</v>
+        <v>3051</v>
       </c>
       <c r="O76" s="47" t="s">
-        <v>3051</v>
+        <v>16</v>
       </c>
       <c r="P76" s="62" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="17" customHeight="1">
@@ -32078,10 +32472,10 @@
         <v>1371</v>
       </c>
       <c r="N78" s="46" t="s">
-        <v>16</v>
+        <v>3053</v>
       </c>
       <c r="O78" s="47" t="s">
-        <v>3053</v>
+        <v>16</v>
       </c>
       <c r="P78" s="62" t="s">
         <v>3270</v>
@@ -32129,13 +32523,13 @@
         <v>1373</v>
       </c>
       <c r="N79" s="46" t="s">
-        <v>16</v>
+        <v>3054</v>
       </c>
       <c r="O79" s="47" t="s">
-        <v>3054</v>
+        <v>16</v>
       </c>
       <c r="P79" s="62" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="17" customHeight="1">
@@ -32180,13 +32574,13 @@
         <v>1375</v>
       </c>
       <c r="N80" s="46" t="s">
-        <v>16</v>
+        <v>3055</v>
       </c>
       <c r="O80" s="47" t="s">
-        <v>3055</v>
+        <v>16</v>
       </c>
       <c r="P80" s="62" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="17" customHeight="1">
@@ -32237,7 +32631,7 @@
         <v>3056</v>
       </c>
       <c r="P81" s="62" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="17" customHeight="1">
@@ -32288,7 +32682,7 @@
         <v>3057</v>
       </c>
       <c r="P82" s="62" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="17" customHeight="1">
@@ -32333,13 +32727,13 @@
         <v>1381</v>
       </c>
       <c r="N83" s="46" t="s">
-        <v>16</v>
+        <v>3058</v>
       </c>
       <c r="O83" s="47" t="s">
-        <v>3058</v>
+        <v>16</v>
       </c>
       <c r="P83" s="62" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="17" customHeight="1">
@@ -32390,7 +32784,7 @@
         <v>16</v>
       </c>
       <c r="P84" s="62" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="17" customHeight="1">
@@ -32435,13 +32829,13 @@
         <v>1385</v>
       </c>
       <c r="N85" s="46" t="s">
-        <v>16</v>
+        <v>3059</v>
       </c>
       <c r="O85" s="47" t="s">
-        <v>3059</v>
+        <v>16</v>
       </c>
       <c r="P85" s="62" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="17" customHeight="1">
@@ -32486,13 +32880,13 @@
         <v>1387</v>
       </c>
       <c r="N86" s="46" t="s">
-        <v>16</v>
+        <v>3060</v>
       </c>
       <c r="O86" s="47" t="s">
-        <v>3060</v>
+        <v>16</v>
       </c>
       <c r="P86" s="62" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="17" customHeight="1">
@@ -32537,13 +32931,13 @@
         <v>1389</v>
       </c>
       <c r="N87" s="46" t="s">
-        <v>16</v>
+        <v>3061</v>
       </c>
       <c r="O87" s="47" t="s">
-        <v>3061</v>
+        <v>16</v>
       </c>
       <c r="P87" s="62" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="17" customHeight="1">
@@ -32588,13 +32982,13 @@
         <v>1391</v>
       </c>
       <c r="N88" s="46" t="s">
-        <v>16</v>
+        <v>3062</v>
       </c>
       <c r="O88" s="47" t="s">
-        <v>3062</v>
+        <v>16</v>
       </c>
       <c r="P88" s="62" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="17" customHeight="1">
@@ -32639,10 +33033,10 @@
         <v>1393</v>
       </c>
       <c r="N89" s="46" t="s">
-        <v>16</v>
+        <v>3063</v>
       </c>
       <c r="O89" s="47" t="s">
-        <v>3063</v>
+        <v>16</v>
       </c>
       <c r="P89" s="62" t="s">
         <v>3271</v>
@@ -32690,10 +33084,10 @@
         <v>1395</v>
       </c>
       <c r="N90" s="46" t="s">
-        <v>16</v>
+        <v>3064</v>
       </c>
       <c r="O90" s="47" t="s">
-        <v>3064</v>
+        <v>16</v>
       </c>
       <c r="P90" s="62" t="s">
         <v>3272</v>
@@ -32747,7 +33141,7 @@
         <v>16</v>
       </c>
       <c r="P91" s="62" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="17" customHeight="1">
@@ -32792,13 +33186,13 @@
         <v>1399</v>
       </c>
       <c r="N92" s="46" t="s">
-        <v>16</v>
+        <v>3065</v>
       </c>
       <c r="O92" s="47" t="s">
-        <v>3065</v>
+        <v>16</v>
       </c>
       <c r="P92" s="62" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="17" customHeight="1">
@@ -32843,13 +33237,13 @@
         <v>1401</v>
       </c>
       <c r="N93" s="46" t="s">
-        <v>16</v>
+        <v>3066</v>
       </c>
       <c r="O93" s="47" t="s">
-        <v>3066</v>
+        <v>16</v>
       </c>
       <c r="P93" s="62" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="17" customHeight="1">
@@ -32894,13 +33288,13 @@
         <v>1403</v>
       </c>
       <c r="N94" s="46" t="s">
-        <v>16</v>
+        <v>3067</v>
       </c>
       <c r="O94" s="47" t="s">
-        <v>3067</v>
+        <v>16</v>
       </c>
       <c r="P94" s="62" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="17" customHeight="1">
@@ -32951,7 +33345,7 @@
         <v>3068</v>
       </c>
       <c r="P95" s="62" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="17" customHeight="1">
@@ -32996,13 +33390,13 @@
         <v>1407</v>
       </c>
       <c r="N96" s="46" t="s">
-        <v>16</v>
+        <v>3069</v>
       </c>
       <c r="O96" s="47" t="s">
-        <v>3069</v>
+        <v>16</v>
       </c>
       <c r="P96" s="62" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="17" customHeight="1">
@@ -33047,13 +33441,13 @@
         <v>1443</v>
       </c>
       <c r="N97" s="65" t="s">
-        <v>16</v>
+        <v>3087</v>
       </c>
       <c r="O97" s="66" t="s">
-        <v>3087</v>
+        <v>16</v>
       </c>
       <c r="P97" s="67" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="17" customHeight="1">
@@ -33098,10 +33492,10 @@
         <v>1409</v>
       </c>
       <c r="N98" s="46" t="s">
-        <v>16</v>
+        <v>3070</v>
       </c>
       <c r="O98" s="47" t="s">
-        <v>3070</v>
+        <v>16</v>
       </c>
       <c r="P98" s="62" t="s">
         <v>3273</v>
@@ -33149,13 +33543,13 @@
         <v>1411</v>
       </c>
       <c r="N99" s="46" t="s">
-        <v>16</v>
+        <v>3071</v>
       </c>
       <c r="O99" s="47" t="s">
-        <v>3071</v>
+        <v>16</v>
       </c>
       <c r="P99" s="62" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="17" customHeight="1">
@@ -33200,13 +33594,13 @@
         <v>1413</v>
       </c>
       <c r="N100" s="46" t="s">
-        <v>16</v>
+        <v>3072</v>
       </c>
       <c r="O100" s="47" t="s">
-        <v>3072</v>
+        <v>16</v>
       </c>
       <c r="P100" s="62" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="17" customHeight="1">
@@ -33251,13 +33645,13 @@
         <v>1415</v>
       </c>
       <c r="N101" s="46" t="s">
-        <v>16</v>
+        <v>3073</v>
       </c>
       <c r="O101" s="47" t="s">
-        <v>3073</v>
+        <v>16</v>
       </c>
       <c r="P101" s="62" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="17" customHeight="1">
@@ -33302,10 +33696,10 @@
         <v>1417</v>
       </c>
       <c r="N102" s="46" t="s">
-        <v>16</v>
+        <v>3074</v>
       </c>
       <c r="O102" s="47" t="s">
-        <v>3074</v>
+        <v>16</v>
       </c>
       <c r="P102" s="62" t="s">
         <v>3274</v>
@@ -33353,10 +33747,10 @@
         <v>1419</v>
       </c>
       <c r="N103" s="46" t="s">
-        <v>16</v>
+        <v>3075</v>
       </c>
       <c r="O103" s="47" t="s">
-        <v>3075</v>
+        <v>16</v>
       </c>
       <c r="P103" s="62" t="s">
         <v>3275</v>
@@ -33404,10 +33798,10 @@
         <v>1421</v>
       </c>
       <c r="N104" s="46" t="s">
-        <v>16</v>
+        <v>3076</v>
       </c>
       <c r="O104" s="47" t="s">
-        <v>3076</v>
+        <v>16</v>
       </c>
       <c r="P104" s="62" t="s">
         <v>3276</v>
@@ -33455,10 +33849,10 @@
         <v>1423</v>
       </c>
       <c r="N105" s="46" t="s">
-        <v>16</v>
+        <v>3077</v>
       </c>
       <c r="O105" s="47" t="s">
-        <v>3077</v>
+        <v>16</v>
       </c>
       <c r="P105" s="62" t="s">
         <v>3277</v>
@@ -33506,10 +33900,10 @@
         <v>1425</v>
       </c>
       <c r="N106" s="46" t="s">
-        <v>16</v>
+        <v>3078</v>
       </c>
       <c r="O106" s="47" t="s">
-        <v>3078</v>
+        <v>16</v>
       </c>
       <c r="P106" s="62" t="s">
         <v>3278</v>
@@ -33557,13 +33951,13 @@
         <v>1427</v>
       </c>
       <c r="N107" s="46" t="s">
-        <v>16</v>
+        <v>3079</v>
       </c>
       <c r="O107" s="47" t="s">
-        <v>3079</v>
+        <v>16</v>
       </c>
       <c r="P107" s="62" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="17" customHeight="1">
@@ -33608,13 +34002,13 @@
         <v>1429</v>
       </c>
       <c r="N108" s="46" t="s">
-        <v>16</v>
+        <v>3080</v>
       </c>
       <c r="O108" s="47" t="s">
-        <v>3080</v>
+        <v>16</v>
       </c>
       <c r="P108" s="62" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="17" customHeight="1">
@@ -33659,13 +34053,13 @@
         <v>1431</v>
       </c>
       <c r="N109" s="46" t="s">
-        <v>16</v>
+        <v>3081</v>
       </c>
       <c r="O109" s="47" t="s">
-        <v>3081</v>
+        <v>16</v>
       </c>
       <c r="P109" s="62" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="17" customHeight="1">
@@ -33710,13 +34104,13 @@
         <v>1433</v>
       </c>
       <c r="N110" s="46" t="s">
-        <v>16</v>
+        <v>3082</v>
       </c>
       <c r="O110" s="47" t="s">
-        <v>3082</v>
+        <v>16</v>
       </c>
       <c r="P110" s="62" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="17" customHeight="1">
@@ -33761,13 +34155,13 @@
         <v>1435</v>
       </c>
       <c r="N111" s="46" t="s">
-        <v>16</v>
+        <v>3083</v>
       </c>
       <c r="O111" s="47" t="s">
-        <v>3083</v>
+        <v>16</v>
       </c>
       <c r="P111" s="62" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="17" customHeight="1">
@@ -33812,13 +34206,13 @@
         <v>1437</v>
       </c>
       <c r="N112" s="46" t="s">
-        <v>16</v>
+        <v>3084</v>
       </c>
       <c r="O112" s="47" t="s">
-        <v>3084</v>
+        <v>16</v>
       </c>
       <c r="P112" s="62" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="17" customHeight="1">
@@ -33863,13 +34257,13 @@
         <v>1439</v>
       </c>
       <c r="N113" s="46" t="s">
-        <v>16</v>
+        <v>3085</v>
       </c>
       <c r="O113" s="47" t="s">
-        <v>3085</v>
+        <v>16</v>
       </c>
       <c r="P113" s="62" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="17" customHeight="1">
@@ -33914,13 +34308,13 @@
         <v>1441</v>
       </c>
       <c r="N114" s="46" t="s">
-        <v>16</v>
+        <v>3086</v>
       </c>
       <c r="O114" s="47" t="s">
-        <v>3086</v>
+        <v>16</v>
       </c>
       <c r="P114" s="62" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="17" customHeight="1">
@@ -33965,13 +34359,13 @@
         <v>1445</v>
       </c>
       <c r="N115" s="46" t="s">
-        <v>16</v>
+        <v>3088</v>
       </c>
       <c r="O115" s="47" t="s">
-        <v>3088</v>
+        <v>16</v>
       </c>
       <c r="P115" s="62" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="17" customHeight="1">
@@ -34016,13 +34410,13 @@
         <v>1447</v>
       </c>
       <c r="N116" s="46" t="s">
-        <v>16</v>
+        <v>3089</v>
       </c>
       <c r="O116" s="47" t="s">
-        <v>3089</v>
+        <v>16</v>
       </c>
       <c r="P116" s="62" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="17" customHeight="1">
@@ -34073,7 +34467,7 @@
         <v>3090</v>
       </c>
       <c r="P117" s="62" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="17" customHeight="1">
@@ -34118,13 +34512,13 @@
         <v>1451</v>
       </c>
       <c r="N118" s="46" t="s">
-        <v>16</v>
+        <v>3091</v>
       </c>
       <c r="O118" s="47" t="s">
-        <v>3091</v>
+        <v>16</v>
       </c>
       <c r="P118" s="62" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="17" customHeight="1">
@@ -34175,7 +34569,7 @@
         <v>3092</v>
       </c>
       <c r="P119" s="62" t="s">
-        <v>3950</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="17" customHeight="1">
@@ -34220,13 +34614,13 @@
         <v>1455</v>
       </c>
       <c r="N120" s="46" t="s">
-        <v>16</v>
+        <v>3093</v>
       </c>
       <c r="O120" s="47" t="s">
-        <v>3093</v>
+        <v>16</v>
       </c>
       <c r="P120" s="62" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="17" customHeight="1">
@@ -34271,13 +34665,13 @@
         <v>1457</v>
       </c>
       <c r="N121" s="46" t="s">
-        <v>16</v>
+        <v>3094</v>
       </c>
       <c r="O121" s="47" t="s">
-        <v>3094</v>
+        <v>16</v>
       </c>
       <c r="P121" s="62" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="17" customHeight="1">
@@ -34322,13 +34716,13 @@
         <v>1459</v>
       </c>
       <c r="N122" s="46" t="s">
-        <v>16</v>
+        <v>3095</v>
       </c>
       <c r="O122" s="47" t="s">
-        <v>3095</v>
+        <v>16</v>
       </c>
       <c r="P122" s="62" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="17" customHeight="1">
@@ -34373,13 +34767,13 @@
         <v>1461</v>
       </c>
       <c r="N123" s="46" t="s">
-        <v>16</v>
+        <v>3096</v>
       </c>
       <c r="O123" s="47" t="s">
-        <v>3096</v>
+        <v>16</v>
       </c>
       <c r="P123" s="62" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="17" customHeight="1">
@@ -34424,13 +34818,13 @@
         <v>1463</v>
       </c>
       <c r="N124" s="46" t="s">
-        <v>16</v>
+        <v>3097</v>
       </c>
       <c r="O124" s="47" t="s">
-        <v>3097</v>
+        <v>16</v>
       </c>
       <c r="P124" s="62" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="17" customHeight="1">
@@ -34481,7 +34875,7 @@
         <v>16</v>
       </c>
       <c r="P125" s="62" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="17" customHeight="1">
@@ -34532,7 +34926,7 @@
         <v>3098</v>
       </c>
       <c r="P126" s="62" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="17" customHeight="1">
@@ -34577,10 +34971,10 @@
         <v>1469</v>
       </c>
       <c r="N127" s="46" t="s">
-        <v>16</v>
+        <v>3099</v>
       </c>
       <c r="O127" s="47" t="s">
-        <v>3099</v>
+        <v>16</v>
       </c>
       <c r="P127" s="62" t="s">
         <v>3279</v>
@@ -34628,13 +35022,13 @@
         <v>1471</v>
       </c>
       <c r="N128" s="46" t="s">
-        <v>16</v>
+        <v>3100</v>
       </c>
       <c r="O128" s="47" t="s">
-        <v>3100</v>
+        <v>16</v>
       </c>
       <c r="P128" s="62" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="17" customHeight="1">
@@ -34685,7 +35079,7 @@
         <v>16</v>
       </c>
       <c r="P129" s="62" t="s">
-        <v>3951</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="17" customHeight="1">
@@ -34730,13 +35124,13 @@
         <v>1475</v>
       </c>
       <c r="N130" s="46" t="s">
-        <v>16</v>
+        <v>3101</v>
       </c>
       <c r="O130" s="47" t="s">
-        <v>3101</v>
+        <v>16</v>
       </c>
       <c r="P130" s="62" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="17" customHeight="1">
@@ -34781,13 +35175,13 @@
         <v>1477</v>
       </c>
       <c r="N131" s="46" t="s">
-        <v>16</v>
+        <v>3102</v>
       </c>
       <c r="O131" s="47" t="s">
-        <v>3102</v>
+        <v>16</v>
       </c>
       <c r="P131" s="62" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="17" customHeight="1">
@@ -34832,13 +35226,13 @@
         <v>1479</v>
       </c>
       <c r="N132" s="46" t="s">
-        <v>16</v>
+        <v>3103</v>
       </c>
       <c r="O132" s="47" t="s">
-        <v>3103</v>
+        <v>16</v>
       </c>
       <c r="P132" s="62" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="17" customHeight="1">
@@ -34883,13 +35277,13 @@
         <v>1481</v>
       </c>
       <c r="N133" s="46" t="s">
-        <v>16</v>
+        <v>3104</v>
       </c>
       <c r="O133" s="47" t="s">
-        <v>3104</v>
+        <v>16</v>
       </c>
       <c r="P133" s="67" t="s">
-        <v>3952</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="17" customHeight="1">
@@ -34934,10 +35328,10 @@
         <v>1483</v>
       </c>
       <c r="N134" s="46" t="s">
-        <v>16</v>
+        <v>3105</v>
       </c>
       <c r="O134" s="47" t="s">
-        <v>3105</v>
+        <v>16</v>
       </c>
       <c r="P134" s="62" t="s">
         <v>3280</v>
@@ -34985,13 +35379,13 @@
         <v>1485</v>
       </c>
       <c r="N135" s="46" t="s">
-        <v>16</v>
+        <v>3106</v>
       </c>
       <c r="O135" s="47" t="s">
-        <v>3106</v>
+        <v>16</v>
       </c>
       <c r="P135" s="62" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="136" spans="1:16" ht="17" customHeight="1">
@@ -35036,13 +35430,13 @@
         <v>1487</v>
       </c>
       <c r="N136" s="46" t="s">
-        <v>16</v>
+        <v>3107</v>
       </c>
       <c r="O136" s="47" t="s">
-        <v>3107</v>
+        <v>16</v>
       </c>
       <c r="P136" s="62" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="17" customHeight="1">
@@ -35093,7 +35487,7 @@
         <v>3108</v>
       </c>
       <c r="P137" s="62" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="138" spans="1:16" ht="17" customHeight="1">
@@ -35138,13 +35532,13 @@
         <v>1491</v>
       </c>
       <c r="N138" s="46" t="s">
-        <v>16</v>
+        <v>3109</v>
       </c>
       <c r="O138" s="47" t="s">
-        <v>3109</v>
+        <v>16</v>
       </c>
       <c r="P138" s="62" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="17" customHeight="1">
@@ -35189,13 +35583,13 @@
         <v>1493</v>
       </c>
       <c r="N139" s="46" t="s">
-        <v>16</v>
+        <v>3110</v>
       </c>
       <c r="O139" s="47" t="s">
-        <v>3110</v>
+        <v>16</v>
       </c>
       <c r="P139" s="62" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="140" spans="1:16" ht="17" customHeight="1">
@@ -35240,13 +35634,13 @@
         <v>1495</v>
       </c>
       <c r="N140" s="46" t="s">
-        <v>16</v>
+        <v>3111</v>
       </c>
       <c r="O140" s="47" t="s">
-        <v>3111</v>
+        <v>16</v>
       </c>
       <c r="P140" s="62" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="141" spans="1:16" ht="17" customHeight="1">
@@ -35291,13 +35685,13 @@
         <v>1497</v>
       </c>
       <c r="N141" s="46" t="s">
-        <v>16</v>
+        <v>3112</v>
       </c>
       <c r="O141" s="47" t="s">
-        <v>3112</v>
+        <v>16</v>
       </c>
       <c r="P141" s="62" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="17" customHeight="1">
@@ -35342,13 +35736,13 @@
         <v>1499</v>
       </c>
       <c r="N142" s="46" t="s">
-        <v>16</v>
+        <v>3113</v>
       </c>
       <c r="O142" s="47" t="s">
-        <v>3113</v>
+        <v>16</v>
       </c>
       <c r="P142" s="62" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="17" customHeight="1">
@@ -35393,13 +35787,13 @@
         <v>1501</v>
       </c>
       <c r="N143" s="46" t="s">
-        <v>16</v>
+        <v>3114</v>
       </c>
       <c r="O143" s="47" t="s">
-        <v>3114</v>
+        <v>16</v>
       </c>
       <c r="P143" s="62" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="144" spans="1:16" ht="17" customHeight="1">
@@ -35444,13 +35838,13 @@
         <v>1503</v>
       </c>
       <c r="N144" s="46" t="s">
-        <v>16</v>
+        <v>3115</v>
       </c>
       <c r="O144" s="47" t="s">
-        <v>3115</v>
+        <v>16</v>
       </c>
       <c r="P144" s="67" t="s">
-        <v>3953</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="145" spans="1:16" ht="17" customHeight="1">
@@ -35495,13 +35889,13 @@
         <v>1505</v>
       </c>
       <c r="N145" s="46" t="s">
-        <v>16</v>
+        <v>3116</v>
       </c>
       <c r="O145" s="47" t="s">
-        <v>3116</v>
+        <v>16</v>
       </c>
       <c r="P145" s="62" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="17" customHeight="1">
@@ -35552,7 +35946,7 @@
         <v>16</v>
       </c>
       <c r="P146" s="62" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="17" customHeight="1">
@@ -35597,13 +35991,13 @@
         <v>1509</v>
       </c>
       <c r="N147" s="46" t="s">
-        <v>16</v>
+        <v>3117</v>
       </c>
       <c r="O147" s="47" t="s">
-        <v>3117</v>
+        <v>16</v>
       </c>
       <c r="P147" s="62" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="17" customHeight="1">
@@ -35654,7 +36048,7 @@
         <v>16</v>
       </c>
       <c r="P148" s="62" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="17" customHeight="1">
@@ -35699,13 +36093,13 @@
         <v>1513</v>
       </c>
       <c r="N149" s="46" t="s">
-        <v>16</v>
+        <v>2962</v>
       </c>
       <c r="O149" s="47" t="s">
-        <v>2962</v>
+        <v>16</v>
       </c>
       <c r="P149" s="62" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="150" spans="1:16" ht="17" customHeight="1">
@@ -35750,13 +36144,13 @@
         <v>1515</v>
       </c>
       <c r="N150" s="46" t="s">
-        <v>16</v>
+        <v>3118</v>
       </c>
       <c r="O150" s="47" t="s">
-        <v>3118</v>
+        <v>16</v>
       </c>
       <c r="P150" s="62" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="151" spans="1:16" ht="17" customHeight="1">
@@ -35801,13 +36195,13 @@
         <v>1517</v>
       </c>
       <c r="N151" s="46" t="s">
-        <v>16</v>
+        <v>3119</v>
       </c>
       <c r="O151" s="47" t="s">
-        <v>3119</v>
+        <v>16</v>
       </c>
       <c r="P151" s="62" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="17" customHeight="1">
@@ -35852,10 +36246,10 @@
         <v>1519</v>
       </c>
       <c r="N152" s="46" t="s">
-        <v>16</v>
+        <v>3120</v>
       </c>
       <c r="O152" s="47" t="s">
-        <v>3120</v>
+        <v>16</v>
       </c>
       <c r="P152" s="62" t="s">
         <v>3281</v>
@@ -35903,10 +36297,10 @@
         <v>1521</v>
       </c>
       <c r="N153" s="46" t="s">
-        <v>16</v>
+        <v>3121</v>
       </c>
       <c r="O153" s="47" t="s">
-        <v>3121</v>
+        <v>16</v>
       </c>
       <c r="P153" s="62" t="s">
         <v>3282</v>
@@ -35954,10 +36348,10 @@
         <v>1523</v>
       </c>
       <c r="N154" s="46" t="s">
-        <v>16</v>
+        <v>3122</v>
       </c>
       <c r="O154" s="47" t="s">
-        <v>3122</v>
+        <v>16</v>
       </c>
       <c r="P154" s="62" t="s">
         <v>3283</v>
@@ -36005,10 +36399,10 @@
         <v>1525</v>
       </c>
       <c r="N155" s="46" t="s">
-        <v>16</v>
+        <v>2965</v>
       </c>
       <c r="O155" s="47" t="s">
-        <v>2965</v>
+        <v>16</v>
       </c>
       <c r="P155" s="62" t="s">
         <v>3284</v>
@@ -36056,10 +36450,10 @@
         <v>1527</v>
       </c>
       <c r="N156" s="46" t="s">
-        <v>16</v>
+        <v>2966</v>
       </c>
       <c r="O156" s="47" t="s">
-        <v>2966</v>
+        <v>16</v>
       </c>
       <c r="P156" s="62" t="s">
         <v>3285</v>
@@ -36107,10 +36501,10 @@
         <v>1529</v>
       </c>
       <c r="N157" s="46" t="s">
-        <v>16</v>
+        <v>2967</v>
       </c>
       <c r="O157" s="47" t="s">
-        <v>2967</v>
+        <v>16</v>
       </c>
       <c r="P157" s="62" t="s">
         <v>3286</v>
@@ -36158,10 +36552,10 @@
         <v>1531</v>
       </c>
       <c r="N158" s="46" t="s">
-        <v>16</v>
+        <v>1532</v>
       </c>
       <c r="O158" s="47" t="s">
-        <v>1532</v>
+        <v>16</v>
       </c>
       <c r="P158" s="62" t="s">
         <v>3287</v>
@@ -36209,13 +36603,13 @@
         <v>1534</v>
       </c>
       <c r="N159" s="46" t="s">
-        <v>16</v>
+        <v>2968</v>
       </c>
       <c r="O159" s="47" t="s">
-        <v>2968</v>
+        <v>16</v>
       </c>
       <c r="P159" s="62" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="17" customHeight="1">
@@ -36260,13 +36654,13 @@
         <v>1536</v>
       </c>
       <c r="N160" s="46" t="s">
-        <v>16</v>
+        <v>2969</v>
       </c>
       <c r="O160" s="47" t="s">
-        <v>2969</v>
+        <v>16</v>
       </c>
       <c r="P160" s="62" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="17" customHeight="1">
@@ -36311,13 +36705,13 @@
         <v>1538</v>
       </c>
       <c r="N161" s="46" t="s">
-        <v>16</v>
+        <v>2982</v>
       </c>
       <c r="O161" s="47" t="s">
-        <v>2982</v>
+        <v>16</v>
       </c>
       <c r="P161" s="62" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="162" spans="1:16" ht="17" customHeight="1">
@@ -36362,13 +36756,13 @@
         <v>1540</v>
       </c>
       <c r="N162" s="46" t="s">
-        <v>16</v>
+        <v>2981</v>
       </c>
       <c r="O162" s="47" t="s">
-        <v>2981</v>
+        <v>16</v>
       </c>
       <c r="P162" s="62" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="163" spans="1:16" ht="17" customHeight="1">
@@ -36413,10 +36807,10 @@
         <v>1542</v>
       </c>
       <c r="N163" s="46" t="s">
-        <v>16</v>
+        <v>2964</v>
       </c>
       <c r="O163" s="47" t="s">
-        <v>2964</v>
+        <v>16</v>
       </c>
       <c r="P163" s="62" t="s">
         <v>3402</v>
@@ -36464,13 +36858,13 @@
         <v>1544</v>
       </c>
       <c r="N164" s="46" t="s">
-        <v>16</v>
+        <v>2963</v>
       </c>
       <c r="O164" s="47" t="s">
-        <v>2963</v>
+        <v>16</v>
       </c>
       <c r="P164" s="62" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="165" spans="1:16" ht="17" customHeight="1">
@@ -36515,13 +36909,13 @@
         <v>1546</v>
       </c>
       <c r="N165" s="46" t="s">
-        <v>16</v>
+        <v>1547</v>
       </c>
       <c r="O165" s="47" t="s">
-        <v>1547</v>
+        <v>16</v>
       </c>
       <c r="P165" s="62" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="166" spans="1:16" ht="17" customHeight="1">
@@ -36566,13 +36960,13 @@
         <v>1549</v>
       </c>
       <c r="N166" s="46" t="s">
-        <v>16</v>
+        <v>1550</v>
       </c>
       <c r="O166" s="47" t="s">
-        <v>1550</v>
+        <v>16</v>
       </c>
       <c r="P166" s="62" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="17" customHeight="1">
@@ -36617,13 +37011,13 @@
         <v>1552</v>
       </c>
       <c r="N167" s="46" t="s">
-        <v>16</v>
+        <v>1553</v>
       </c>
       <c r="O167" s="47" t="s">
-        <v>1553</v>
+        <v>16</v>
       </c>
       <c r="P167" s="62" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="168" spans="1:16" ht="17" customHeight="1">
@@ -36674,7 +37068,7 @@
         <v>1557</v>
       </c>
       <c r="P168" s="62" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="169" spans="1:16" ht="17" customHeight="1">
@@ -36719,13 +37113,13 @@
         <v>1559</v>
       </c>
       <c r="N169" s="46" t="s">
-        <v>16</v>
+        <v>2980</v>
       </c>
       <c r="O169" s="47" t="s">
-        <v>2980</v>
+        <v>16</v>
       </c>
       <c r="P169" s="62" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="170" spans="1:16" ht="17" customHeight="1">
@@ -36770,13 +37164,13 @@
         <v>1561</v>
       </c>
       <c r="N170" s="46" t="s">
-        <v>16</v>
+        <v>1562</v>
       </c>
       <c r="O170" s="47" t="s">
-        <v>1562</v>
+        <v>16</v>
       </c>
       <c r="P170" s="62" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="17" customHeight="1">
@@ -36821,13 +37215,13 @@
         <v>1564</v>
       </c>
       <c r="N171" s="46" t="s">
-        <v>16</v>
+        <v>2979</v>
       </c>
       <c r="O171" s="47" t="s">
-        <v>2979</v>
+        <v>16</v>
       </c>
       <c r="P171" s="62" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="172" spans="1:16" ht="17" customHeight="1">
@@ -36872,13 +37266,13 @@
         <v>1566</v>
       </c>
       <c r="N172" s="46" t="s">
-        <v>16</v>
+        <v>1567</v>
       </c>
       <c r="O172" s="47" t="s">
-        <v>1567</v>
+        <v>16</v>
       </c>
       <c r="P172" s="62" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="173" spans="1:16" ht="17" customHeight="1">
@@ -36929,7 +37323,7 @@
         <v>16</v>
       </c>
       <c r="P173" s="62" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="174" spans="1:16" ht="17" customHeight="1">
@@ -36974,13 +37368,13 @@
         <v>1571</v>
       </c>
       <c r="N174" s="46" t="s">
-        <v>16</v>
+        <v>2978</v>
       </c>
       <c r="O174" s="47" t="s">
-        <v>2978</v>
+        <v>16</v>
       </c>
       <c r="P174" s="62" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="175" spans="1:16" ht="17" customHeight="1">
@@ -37076,10 +37470,10 @@
         <v>1575</v>
       </c>
       <c r="N176" s="46" t="s">
-        <v>16</v>
+        <v>2976</v>
       </c>
       <c r="O176" s="47" t="s">
-        <v>2976</v>
+        <v>16</v>
       </c>
       <c r="P176" s="62" t="s">
         <v>3404</v>
@@ -37127,13 +37521,13 @@
         <v>1577</v>
       </c>
       <c r="N177" s="46" t="s">
-        <v>16</v>
+        <v>1578</v>
       </c>
       <c r="O177" s="47" t="s">
-        <v>1578</v>
+        <v>16</v>
       </c>
       <c r="P177" s="62" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="17" customHeight="1">
@@ -37178,13 +37572,13 @@
         <v>1580</v>
       </c>
       <c r="N178" s="46" t="s">
-        <v>16</v>
+        <v>1581</v>
       </c>
       <c r="O178" s="47" t="s">
-        <v>1581</v>
+        <v>16</v>
       </c>
       <c r="P178" s="62" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="179" spans="1:16" ht="17" customHeight="1">
@@ -37229,13 +37623,13 @@
         <v>1583</v>
       </c>
       <c r="N179" s="46" t="s">
-        <v>16</v>
+        <v>1584</v>
       </c>
       <c r="O179" s="47" t="s">
-        <v>1584</v>
+        <v>16</v>
       </c>
       <c r="P179" s="62" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="17" customHeight="1">
@@ -37280,13 +37674,13 @@
         <v>1586</v>
       </c>
       <c r="N180" s="46" t="s">
-        <v>16</v>
+        <v>1587</v>
       </c>
       <c r="O180" s="47" t="s">
-        <v>1587</v>
+        <v>16</v>
       </c>
       <c r="P180" s="62" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="17" customHeight="1">
@@ -37331,13 +37725,13 @@
         <v>1589</v>
       </c>
       <c r="N181" s="46" t="s">
-        <v>16</v>
+        <v>3123</v>
       </c>
       <c r="O181" s="47" t="s">
-        <v>3123</v>
+        <v>16</v>
       </c>
       <c r="P181" s="62" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="182" spans="1:16" ht="17" customHeight="1">
@@ -37388,7 +37782,7 @@
         <v>16</v>
       </c>
       <c r="P182" s="62" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="183" spans="1:16" ht="17" customHeight="1">
@@ -37439,7 +37833,7 @@
         <v>16</v>
       </c>
       <c r="P183" s="62" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="184" spans="1:16" ht="17" customHeight="1">
@@ -37484,13 +37878,13 @@
         <v>1595</v>
       </c>
       <c r="N184" s="46" t="s">
-        <v>16</v>
+        <v>1596</v>
       </c>
       <c r="O184" s="47" t="s">
-        <v>1596</v>
+        <v>16</v>
       </c>
       <c r="P184" s="62" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="17" customHeight="1">
@@ -37535,13 +37929,13 @@
         <v>1598</v>
       </c>
       <c r="N185" s="46" t="s">
-        <v>16</v>
+        <v>1599</v>
       </c>
       <c r="O185" s="47" t="s">
-        <v>1599</v>
+        <v>16</v>
       </c>
       <c r="P185" s="62" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="186" spans="1:16" ht="17" customHeight="1">
@@ -37586,13 +37980,13 @@
         <v>1601</v>
       </c>
       <c r="N186" s="46" t="s">
-        <v>16</v>
+        <v>3124</v>
       </c>
       <c r="O186" s="47" t="s">
-        <v>3124</v>
+        <v>16</v>
       </c>
       <c r="P186" s="62" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="17" customHeight="1">
@@ -37643,7 +38037,7 @@
         <v>3125</v>
       </c>
       <c r="P187" s="62" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="17" customHeight="1">
@@ -37688,13 +38082,13 @@
         <v>1605</v>
       </c>
       <c r="N188" s="46" t="s">
-        <v>16</v>
+        <v>3126</v>
       </c>
       <c r="O188" s="47" t="s">
-        <v>3126</v>
+        <v>16</v>
       </c>
       <c r="P188" s="62" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="189" spans="1:16" ht="17" customHeight="1">
@@ -37739,13 +38133,13 @@
         <v>1607</v>
       </c>
       <c r="N189" s="46" t="s">
-        <v>16</v>
+        <v>3127</v>
       </c>
       <c r="O189" s="47" t="s">
-        <v>3127</v>
+        <v>16</v>
       </c>
       <c r="P189" s="62" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="190" spans="1:16" ht="17" customHeight="1">
@@ -37790,13 +38184,13 @@
         <v>1609</v>
       </c>
       <c r="N190" s="46" t="s">
-        <v>16</v>
+        <v>2975</v>
       </c>
       <c r="O190" s="47" t="s">
-        <v>2975</v>
+        <v>16</v>
       </c>
       <c r="P190" s="62" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="191" spans="1:16" ht="17" customHeight="1">
@@ -37841,13 +38235,13 @@
         <v>1611</v>
       </c>
       <c r="N191" s="46" t="s">
-        <v>16</v>
+        <v>1612</v>
       </c>
       <c r="O191" s="47" t="s">
-        <v>1612</v>
+        <v>16</v>
       </c>
       <c r="P191" s="62" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="192" spans="1:16" ht="17" customHeight="1">
@@ -37892,10 +38286,10 @@
         <v>1614</v>
       </c>
       <c r="N192" s="46" t="s">
-        <v>16</v>
+        <v>1615</v>
       </c>
       <c r="O192" s="47" t="s">
-        <v>1615</v>
+        <v>16</v>
       </c>
       <c r="P192" s="62" t="s">
         <v>3288</v>
@@ -37943,13 +38337,13 @@
         <v>1617</v>
       </c>
       <c r="N193" s="46" t="s">
-        <v>16</v>
+        <v>2974</v>
       </c>
       <c r="O193" s="47" t="s">
-        <v>2974</v>
+        <v>16</v>
       </c>
       <c r="P193" s="62" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="17" customHeight="1">
@@ -37994,10 +38388,10 @@
         <v>1619</v>
       </c>
       <c r="N194" s="46" t="s">
-        <v>16</v>
+        <v>1620</v>
       </c>
       <c r="O194" s="47" t="s">
-        <v>1620</v>
+        <v>16</v>
       </c>
       <c r="P194" s="62" t="s">
         <v>3289</v>
@@ -38045,13 +38439,13 @@
         <v>1622</v>
       </c>
       <c r="N195" s="46" t="s">
-        <v>16</v>
+        <v>1623</v>
       </c>
       <c r="O195" s="47" t="s">
-        <v>1623</v>
+        <v>16</v>
       </c>
       <c r="P195" s="62" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="196" spans="1:16" ht="17" customHeight="1">
@@ -38096,13 +38490,13 @@
         <v>1625</v>
       </c>
       <c r="N196" s="46" t="s">
-        <v>16</v>
+        <v>1626</v>
       </c>
       <c r="O196" s="47" t="s">
-        <v>1626</v>
+        <v>16</v>
       </c>
       <c r="P196" s="62" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="17" customHeight="1">
@@ -38147,13 +38541,13 @@
         <v>1628</v>
       </c>
       <c r="N197" s="46" t="s">
-        <v>16</v>
+        <v>1629</v>
       </c>
       <c r="O197" s="47" t="s">
-        <v>1629</v>
+        <v>16</v>
       </c>
       <c r="P197" s="62" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="198" spans="1:16" ht="17" customHeight="1">
@@ -38198,13 +38592,13 @@
         <v>1631</v>
       </c>
       <c r="N198" s="46" t="s">
-        <v>16</v>
+        <v>1632</v>
       </c>
       <c r="O198" s="47" t="s">
-        <v>1632</v>
+        <v>16</v>
       </c>
       <c r="P198" s="62" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="199" spans="1:16" ht="17" customHeight="1">
@@ -38249,13 +38643,13 @@
         <v>1634</v>
       </c>
       <c r="N199" s="46" t="s">
-        <v>16</v>
+        <v>1635</v>
       </c>
       <c r="O199" s="47" t="s">
-        <v>1635</v>
+        <v>16</v>
       </c>
       <c r="P199" s="62" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="17" customHeight="1">
@@ -38300,10 +38694,10 @@
         <v>1640</v>
       </c>
       <c r="N200" s="46" t="s">
-        <v>16</v>
+        <v>1641</v>
       </c>
       <c r="O200" s="47" t="s">
-        <v>1641</v>
+        <v>16</v>
       </c>
       <c r="P200" s="62" t="s">
         <v>3290</v>
@@ -38402,13 +38796,13 @@
         <v>1647</v>
       </c>
       <c r="N202" s="46" t="s">
-        <v>16</v>
+        <v>1648</v>
       </c>
       <c r="O202" s="47" t="s">
-        <v>1648</v>
+        <v>16</v>
       </c>
       <c r="P202" s="62" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="203" spans="1:16" ht="17" customHeight="1">
@@ -38453,13 +38847,13 @@
         <v>1637</v>
       </c>
       <c r="N203" s="65" t="s">
-        <v>16</v>
+        <v>1638</v>
       </c>
       <c r="O203" s="66" t="s">
-        <v>1638</v>
+        <v>16</v>
       </c>
       <c r="P203" s="67" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="204" spans="1:16" ht="17" customHeight="1">
@@ -38504,13 +38898,13 @@
         <v>1650</v>
       </c>
       <c r="N204" s="46" t="s">
-        <v>16</v>
+        <v>1651</v>
       </c>
       <c r="O204" s="47" t="s">
-        <v>1651</v>
+        <v>16</v>
       </c>
       <c r="P204" s="62" t="s">
-        <v>3954</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="17" customHeight="1">
@@ -38555,13 +38949,13 @@
         <v>1653</v>
       </c>
       <c r="N205" s="46" t="s">
-        <v>16</v>
+        <v>1654</v>
       </c>
       <c r="O205" s="47" t="s">
-        <v>1654</v>
+        <v>16</v>
       </c>
       <c r="P205" s="62" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="206" spans="1:16" ht="17" customHeight="1">
@@ -38657,13 +39051,13 @@
         <v>1660</v>
       </c>
       <c r="N207" s="46" t="s">
-        <v>16</v>
+        <v>1661</v>
       </c>
       <c r="O207" s="47" t="s">
-        <v>1661</v>
+        <v>16</v>
       </c>
       <c r="P207" s="62" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="17" customHeight="1">
@@ -38708,13 +39102,13 @@
         <v>1663</v>
       </c>
       <c r="N208" s="46" t="s">
-        <v>16</v>
+        <v>3128</v>
       </c>
       <c r="O208" s="47" t="s">
-        <v>3128</v>
+        <v>16</v>
       </c>
       <c r="P208" s="62" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="17" customHeight="1">
@@ -38759,13 +39153,13 @@
         <v>1665</v>
       </c>
       <c r="N209" s="46" t="s">
-        <v>16</v>
+        <v>3129</v>
       </c>
       <c r="O209" s="47" t="s">
-        <v>3129</v>
+        <v>16</v>
       </c>
       <c r="P209" s="62" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="210" spans="1:16" ht="17" customHeight="1">
@@ -38810,13 +39204,13 @@
         <v>1667</v>
       </c>
       <c r="N210" s="46" t="s">
-        <v>16</v>
+        <v>1668</v>
       </c>
       <c r="O210" s="47" t="s">
-        <v>1668</v>
+        <v>16</v>
       </c>
       <c r="P210" s="62" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="211" spans="1:16" ht="17" customHeight="1">
@@ -38861,13 +39255,13 @@
         <v>1670</v>
       </c>
       <c r="N211" s="46" t="s">
-        <v>16</v>
+        <v>3130</v>
       </c>
       <c r="O211" s="47" t="s">
-        <v>3130</v>
+        <v>16</v>
       </c>
       <c r="P211" s="62" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="17" customHeight="1">
@@ -38918,7 +39312,7 @@
         <v>16</v>
       </c>
       <c r="P212" s="62" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="17" customHeight="1">
@@ -38963,10 +39357,10 @@
         <v>1674</v>
       </c>
       <c r="N213" s="46" t="s">
-        <v>16</v>
+        <v>1675</v>
       </c>
       <c r="O213" s="47" t="s">
-        <v>1675</v>
+        <v>16</v>
       </c>
       <c r="P213" s="62" t="s">
         <v>3291</v>
@@ -39020,7 +39414,7 @@
         <v>1679</v>
       </c>
       <c r="P214" s="62" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="215" spans="1:16" ht="17" customHeight="1">
@@ -39071,7 +39465,7 @@
         <v>16</v>
       </c>
       <c r="P215" s="62" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="17" customHeight="1">
@@ -39116,10 +39510,10 @@
         <v>1683</v>
       </c>
       <c r="N216" s="46" t="s">
-        <v>16</v>
+        <v>3131</v>
       </c>
       <c r="O216" s="47" t="s">
-        <v>3131</v>
+        <v>16</v>
       </c>
       <c r="P216" s="62" t="s">
         <v>3407</v>
@@ -39167,13 +39561,13 @@
         <v>1685</v>
       </c>
       <c r="N217" s="46" t="s">
-        <v>16</v>
+        <v>3132</v>
       </c>
       <c r="O217" s="47" t="s">
-        <v>3132</v>
+        <v>16</v>
       </c>
       <c r="P217" s="62" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="218" spans="1:16" ht="17" customHeight="1">
@@ -39218,13 +39612,13 @@
         <v>1687</v>
       </c>
       <c r="N218" s="46" t="s">
-        <v>16</v>
+        <v>1688</v>
       </c>
       <c r="O218" s="47" t="s">
-        <v>1688</v>
+        <v>16</v>
       </c>
       <c r="P218" s="62" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="219" spans="1:16" ht="17" customHeight="1">
@@ -39269,13 +39663,13 @@
         <v>1690</v>
       </c>
       <c r="N219" s="46" t="s">
-        <v>16</v>
+        <v>3133</v>
       </c>
       <c r="O219" s="47" t="s">
-        <v>3133</v>
+        <v>16</v>
       </c>
       <c r="P219" s="62" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="17" customHeight="1">
@@ -39320,13 +39714,13 @@
         <v>1692</v>
       </c>
       <c r="N220" s="46" t="s">
-        <v>16</v>
+        <v>3134</v>
       </c>
       <c r="O220" s="47" t="s">
-        <v>3134</v>
+        <v>16</v>
       </c>
       <c r="P220" s="62" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="17" customHeight="1">
@@ -39371,13 +39765,13 @@
         <v>1694</v>
       </c>
       <c r="N221" s="46" t="s">
-        <v>16</v>
+        <v>3135</v>
       </c>
       <c r="O221" s="47" t="s">
-        <v>3135</v>
+        <v>16</v>
       </c>
       <c r="P221" s="62" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="222" spans="1:16" ht="17" customHeight="1">
@@ -39422,13 +39816,13 @@
         <v>1696</v>
       </c>
       <c r="N222" s="46" t="s">
-        <v>16</v>
+        <v>3136</v>
       </c>
       <c r="O222" s="47" t="s">
-        <v>3136</v>
+        <v>16</v>
       </c>
       <c r="P222" s="62" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="223" spans="1:16" ht="17" customHeight="1">
@@ -39479,7 +39873,7 @@
         <v>16</v>
       </c>
       <c r="P223" s="62" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="17" customHeight="1">
@@ -39524,13 +39918,13 @@
         <v>1700</v>
       </c>
       <c r="N224" s="46" t="s">
-        <v>16</v>
+        <v>1701</v>
       </c>
       <c r="O224" s="47" t="s">
-        <v>1701</v>
+        <v>16</v>
       </c>
       <c r="P224" s="62" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="225" spans="1:16" ht="17" customHeight="1">
@@ -39575,13 +39969,13 @@
         <v>1703</v>
       </c>
       <c r="N225" s="46" t="s">
-        <v>16</v>
+        <v>1704</v>
       </c>
       <c r="O225" s="47" t="s">
-        <v>1704</v>
+        <v>16</v>
       </c>
       <c r="P225" s="62" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="17" customHeight="1">
@@ -39626,13 +40020,13 @@
         <v>1706</v>
       </c>
       <c r="N226" s="46" t="s">
-        <v>16</v>
+        <v>1707</v>
       </c>
       <c r="O226" s="47" t="s">
-        <v>1707</v>
+        <v>16</v>
       </c>
       <c r="P226" s="62" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="17" customHeight="1">
@@ -39677,13 +40071,13 @@
         <v>1709</v>
       </c>
       <c r="N227" s="46" t="s">
-        <v>16</v>
+        <v>1710</v>
       </c>
       <c r="O227" s="47" t="s">
-        <v>1710</v>
+        <v>16</v>
       </c>
       <c r="P227" s="62" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="228" spans="1:16" ht="17" customHeight="1">
@@ -39728,13 +40122,13 @@
         <v>1712</v>
       </c>
       <c r="N228" s="46" t="s">
-        <v>16</v>
+        <v>1713</v>
       </c>
       <c r="O228" s="47" t="s">
-        <v>1713</v>
+        <v>16</v>
       </c>
       <c r="P228" s="62" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="229" spans="1:16" ht="17" customHeight="1">
@@ -39785,7 +40179,7 @@
         <v>16</v>
       </c>
       <c r="P229" s="62" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="17" customHeight="1">
@@ -39830,10 +40224,10 @@
         <v>1717</v>
       </c>
       <c r="N230" s="46" t="s">
-        <v>16</v>
+        <v>1718</v>
       </c>
       <c r="O230" s="47" t="s">
-        <v>1718</v>
+        <v>16</v>
       </c>
       <c r="P230" s="62" t="s">
         <v>3292</v>
@@ -39887,7 +40281,7 @@
         <v>16</v>
       </c>
       <c r="P231" s="62" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="232" spans="1:16" ht="17" customHeight="1">
@@ -39932,13 +40326,13 @@
         <v>1722</v>
       </c>
       <c r="N232" s="46" t="s">
-        <v>16</v>
+        <v>3137</v>
       </c>
       <c r="O232" s="47" t="s">
-        <v>3137</v>
+        <v>16</v>
       </c>
       <c r="P232" s="62" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="233" spans="1:16" ht="17" customHeight="1">
@@ -39983,13 +40377,13 @@
         <v>1724</v>
       </c>
       <c r="N233" s="46" t="s">
-        <v>16</v>
+        <v>3138</v>
       </c>
       <c r="O233" s="47" t="s">
-        <v>3138</v>
+        <v>16</v>
       </c>
       <c r="P233" s="62" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="17" customHeight="1">
@@ -40040,7 +40434,7 @@
         <v>16</v>
       </c>
       <c r="P234" s="62" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="235" spans="1:16" ht="17" customHeight="1">
@@ -40085,13 +40479,13 @@
         <v>1728</v>
       </c>
       <c r="N235" s="46" t="s">
-        <v>16</v>
+        <v>3139</v>
       </c>
       <c r="O235" s="47" t="s">
-        <v>3139</v>
+        <v>16</v>
       </c>
       <c r="P235" s="62" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="236" spans="1:16" ht="17" customHeight="1">
@@ -40136,13 +40530,13 @@
         <v>1730</v>
       </c>
       <c r="N236" s="46" t="s">
-        <v>16</v>
+        <v>1731</v>
       </c>
       <c r="O236" s="47" t="s">
-        <v>1731</v>
+        <v>16</v>
       </c>
       <c r="P236" s="62" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="17" customHeight="1">
@@ -40187,13 +40581,13 @@
         <v>1733</v>
       </c>
       <c r="N237" s="46" t="s">
-        <v>16</v>
+        <v>1734</v>
       </c>
       <c r="O237" s="47" t="s">
-        <v>1734</v>
+        <v>16</v>
       </c>
       <c r="P237" s="62" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="238" spans="1:16" ht="17" customHeight="1">
@@ -40244,7 +40638,7 @@
         <v>16</v>
       </c>
       <c r="P238" s="62" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="239" spans="1:16" ht="17" customHeight="1">
@@ -40289,10 +40683,10 @@
         <v>1738</v>
       </c>
       <c r="N239" s="46" t="s">
-        <v>16</v>
+        <v>1739</v>
       </c>
       <c r="O239" s="47" t="s">
-        <v>1739</v>
+        <v>16</v>
       </c>
       <c r="P239" s="62" t="s">
         <v>3293</v>
@@ -40340,10 +40734,10 @@
         <v>1741</v>
       </c>
       <c r="N240" s="46" t="s">
-        <v>16</v>
+        <v>1742</v>
       </c>
       <c r="O240" s="47" t="s">
-        <v>1742</v>
+        <v>16</v>
       </c>
       <c r="P240" s="62" t="s">
         <v>3294</v>
@@ -40391,13 +40785,13 @@
         <v>1744</v>
       </c>
       <c r="N241" s="46" t="s">
-        <v>16</v>
+        <v>1745</v>
       </c>
       <c r="O241" s="47" t="s">
-        <v>1745</v>
+        <v>16</v>
       </c>
       <c r="P241" s="62" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="242" spans="1:16" ht="17" customHeight="1">
@@ -40448,7 +40842,7 @@
         <v>16</v>
       </c>
       <c r="P242" s="62" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="243" spans="1:16" ht="17" customHeight="1">
@@ -40493,13 +40887,13 @@
         <v>1749</v>
       </c>
       <c r="N243" s="46" t="s">
-        <v>16</v>
+        <v>1750</v>
       </c>
       <c r="O243" s="47" t="s">
-        <v>1750</v>
+        <v>16</v>
       </c>
       <c r="P243" s="62" t="s">
-        <v>3955</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="17" customHeight="1">
@@ -40544,10 +40938,10 @@
         <v>1752</v>
       </c>
       <c r="N244" s="46" t="s">
-        <v>16</v>
+        <v>1753</v>
       </c>
       <c r="O244" s="47" t="s">
-        <v>1753</v>
+        <v>16</v>
       </c>
       <c r="P244" s="62" t="s">
         <v>3295</v>
@@ -40595,10 +40989,10 @@
         <v>1755</v>
       </c>
       <c r="N245" s="46" t="s">
-        <v>16</v>
+        <v>1756</v>
       </c>
       <c r="O245" s="47" t="s">
-        <v>1756</v>
+        <v>16</v>
       </c>
       <c r="P245" s="62" t="s">
         <v>3296</v>
@@ -40652,7 +41046,7 @@
         <v>16</v>
       </c>
       <c r="P246" s="62" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="17" customHeight="1">
@@ -40697,13 +41091,13 @@
         <v>1760</v>
       </c>
       <c r="N247" s="46" t="s">
-        <v>16</v>
+        <v>1761</v>
       </c>
       <c r="O247" s="47" t="s">
-        <v>1761</v>
+        <v>16</v>
       </c>
       <c r="P247" s="62" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="248" spans="1:16" ht="17" customHeight="1">
@@ -40748,13 +41142,13 @@
         <v>1763</v>
       </c>
       <c r="N248" s="46" t="s">
-        <v>16</v>
+        <v>1764</v>
       </c>
       <c r="O248" s="47" t="s">
-        <v>1764</v>
+        <v>16</v>
       </c>
       <c r="P248" s="62" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="249" spans="1:16" ht="17" customHeight="1">
@@ -40799,13 +41193,13 @@
         <v>1766</v>
       </c>
       <c r="N249" s="46" t="s">
-        <v>16</v>
+        <v>1767</v>
       </c>
       <c r="O249" s="47" t="s">
-        <v>1767</v>
+        <v>16</v>
       </c>
       <c r="P249" s="62" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="250" spans="1:16" ht="17" customHeight="1">
@@ -40850,13 +41244,13 @@
         <v>1769</v>
       </c>
       <c r="N250" s="46" t="s">
-        <v>16</v>
+        <v>1770</v>
       </c>
       <c r="O250" s="47" t="s">
-        <v>1770</v>
+        <v>16</v>
       </c>
       <c r="P250" s="62" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="251" spans="1:16" ht="17" customHeight="1">
@@ -40907,7 +41301,7 @@
         <v>16</v>
       </c>
       <c r="P251" s="62" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="17" customHeight="1">
@@ -40958,7 +41352,7 @@
         <v>16</v>
       </c>
       <c r="P252" s="62" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="253" spans="1:16" ht="17" customHeight="1">
@@ -41003,10 +41397,10 @@
         <v>1776</v>
       </c>
       <c r="N253" s="46" t="s">
-        <v>16</v>
+        <v>1777</v>
       </c>
       <c r="O253" s="47" t="s">
-        <v>1777</v>
+        <v>16</v>
       </c>
       <c r="P253" s="62" t="s">
         <v>3297</v>
@@ -41060,7 +41454,7 @@
         <v>1781</v>
       </c>
       <c r="P254" s="62" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="255" spans="1:16" ht="17" customHeight="1">
@@ -41105,10 +41499,10 @@
         <v>1783</v>
       </c>
       <c r="N255" s="46" t="s">
-        <v>16</v>
+        <v>1784</v>
       </c>
       <c r="O255" s="47" t="s">
-        <v>1784</v>
+        <v>16</v>
       </c>
       <c r="P255" s="62" t="s">
         <v>3298</v>
@@ -41156,13 +41550,13 @@
         <v>1786</v>
       </c>
       <c r="N256" s="46" t="s">
-        <v>16</v>
+        <v>1787</v>
       </c>
       <c r="O256" s="47" t="s">
-        <v>1787</v>
+        <v>16</v>
       </c>
       <c r="P256" s="62" t="s">
-        <v>3408</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="257" spans="1:16" ht="17" customHeight="1">
@@ -41213,7 +41607,7 @@
         <v>16</v>
       </c>
       <c r="P257" s="62" t="s">
-        <v>3650</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="17" customHeight="1">
@@ -41258,10 +41652,10 @@
         <v>1791</v>
       </c>
       <c r="N258" s="46" t="s">
-        <v>16</v>
+        <v>1792</v>
       </c>
       <c r="O258" s="47" t="s">
-        <v>1792</v>
+        <v>16</v>
       </c>
       <c r="P258" s="62" t="s">
         <v>3299</v>
@@ -41309,13 +41703,13 @@
         <v>1794</v>
       </c>
       <c r="N259" s="46" t="s">
-        <v>16</v>
+        <v>1795</v>
       </c>
       <c r="O259" s="47" t="s">
-        <v>1795</v>
+        <v>16</v>
       </c>
       <c r="P259" s="62" t="s">
-        <v>3651</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="17" customHeight="1">
@@ -41360,13 +41754,13 @@
         <v>1797</v>
       </c>
       <c r="N260" s="46" t="s">
-        <v>16</v>
+        <v>1798</v>
       </c>
       <c r="O260" s="47" t="s">
-        <v>1798</v>
+        <v>16</v>
       </c>
       <c r="P260" s="62" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="261" spans="1:16" ht="17" customHeight="1">
@@ -41411,10 +41805,10 @@
         <v>1800</v>
       </c>
       <c r="N261" s="46" t="s">
-        <v>16</v>
+        <v>1801</v>
       </c>
       <c r="O261" s="47" t="s">
-        <v>1801</v>
+        <v>16</v>
       </c>
       <c r="P261" s="62" t="s">
         <v>3300</v>
@@ -41468,7 +41862,7 @@
         <v>16</v>
       </c>
       <c r="P262" s="62" t="s">
-        <v>3652</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="263" spans="1:16" ht="17" customHeight="1">
@@ -41513,10 +41907,10 @@
         <v>1805</v>
       </c>
       <c r="N263" s="46" t="s">
-        <v>16</v>
+        <v>3140</v>
       </c>
       <c r="O263" s="47" t="s">
-        <v>3140</v>
+        <v>16</v>
       </c>
       <c r="P263" s="62" t="s">
         <v>3301</v>
@@ -41564,13 +41958,13 @@
         <v>1807</v>
       </c>
       <c r="N264" s="46" t="s">
-        <v>16</v>
+        <v>1808</v>
       </c>
       <c r="O264" s="47" t="s">
-        <v>1808</v>
+        <v>16</v>
       </c>
       <c r="P264" s="62" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="17" customHeight="1">
@@ -41615,10 +42009,10 @@
         <v>1810</v>
       </c>
       <c r="N265" s="46" t="s">
-        <v>16</v>
+        <v>1811</v>
       </c>
       <c r="O265" s="47" t="s">
-        <v>1811</v>
+        <v>16</v>
       </c>
       <c r="P265" s="62" t="s">
         <v>3302</v>
@@ -41666,10 +42060,10 @@
         <v>1813</v>
       </c>
       <c r="N266" s="46" t="s">
-        <v>16</v>
+        <v>1814</v>
       </c>
       <c r="O266" s="47" t="s">
-        <v>1814</v>
+        <v>16</v>
       </c>
       <c r="P266" s="62" t="s">
         <v>3303</v>
@@ -41717,13 +42111,13 @@
         <v>1816</v>
       </c>
       <c r="N267" s="46" t="s">
-        <v>16</v>
+        <v>3141</v>
       </c>
       <c r="O267" s="47" t="s">
-        <v>3141</v>
+        <v>16</v>
       </c>
       <c r="P267" s="62" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="17" customHeight="1">
@@ -41768,13 +42162,13 @@
         <v>1818</v>
       </c>
       <c r="N268" s="46" t="s">
-        <v>16</v>
+        <v>3142</v>
       </c>
       <c r="O268" s="47" t="s">
-        <v>3142</v>
+        <v>16</v>
       </c>
       <c r="P268" s="62" t="s">
-        <v>3655</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="17" customHeight="1">
@@ -41819,10 +42213,10 @@
         <v>1820</v>
       </c>
       <c r="N269" s="46" t="s">
-        <v>16</v>
+        <v>1821</v>
       </c>
       <c r="O269" s="47" t="s">
-        <v>1821</v>
+        <v>16</v>
       </c>
       <c r="P269" s="62" t="s">
         <v>3304</v>
@@ -41876,7 +42270,7 @@
         <v>16</v>
       </c>
       <c r="P270" s="62" t="s">
-        <v>3656</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="271" spans="1:16" ht="17" customHeight="1">
@@ -41921,10 +42315,10 @@
         <v>1825</v>
       </c>
       <c r="N271" s="46" t="s">
-        <v>16</v>
+        <v>1826</v>
       </c>
       <c r="O271" s="47" t="s">
-        <v>1826</v>
+        <v>16</v>
       </c>
       <c r="P271" s="62" t="s">
         <v>3305</v>
@@ -41972,13 +42366,13 @@
         <v>1828</v>
       </c>
       <c r="N272" s="46" t="s">
-        <v>16</v>
+        <v>3143</v>
       </c>
       <c r="O272" s="47" t="s">
-        <v>3143</v>
+        <v>16</v>
       </c>
       <c r="P272" s="62" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="17" customHeight="1">
@@ -42029,7 +42423,7 @@
         <v>16</v>
       </c>
       <c r="P273" s="62" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="274" spans="1:16" ht="17" customHeight="1">
@@ -42074,13 +42468,13 @@
         <v>1832</v>
       </c>
       <c r="N274" s="46" t="s">
-        <v>16</v>
+        <v>3144</v>
       </c>
       <c r="O274" s="47" t="s">
-        <v>3144</v>
+        <v>16</v>
       </c>
       <c r="P274" s="62" t="s">
-        <v>3659</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="275" spans="1:16" ht="17" customHeight="1">
@@ -42125,13 +42519,13 @@
         <v>1834</v>
       </c>
       <c r="N275" s="46" t="s">
-        <v>16</v>
+        <v>1835</v>
       </c>
       <c r="O275" s="47" t="s">
-        <v>1835</v>
+        <v>16</v>
       </c>
       <c r="P275" s="62" t="s">
-        <v>3660</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="17" customHeight="1">
@@ -42182,7 +42576,7 @@
         <v>16</v>
       </c>
       <c r="P276" s="62" t="s">
-        <v>3661</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="277" spans="1:16" ht="17" customHeight="1">
@@ -42227,13 +42621,13 @@
         <v>1839</v>
       </c>
       <c r="N277" s="46" t="s">
-        <v>16</v>
+        <v>1840</v>
       </c>
       <c r="O277" s="47" t="s">
-        <v>1840</v>
+        <v>16</v>
       </c>
       <c r="P277" s="62" t="s">
-        <v>3662</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="278" spans="1:16" ht="17" customHeight="1">
@@ -42278,13 +42672,13 @@
         <v>1842</v>
       </c>
       <c r="N278" s="46" t="s">
-        <v>16</v>
+        <v>1843</v>
       </c>
       <c r="O278" s="47" t="s">
-        <v>1843</v>
+        <v>16</v>
       </c>
       <c r="P278" s="62" t="s">
-        <v>3663</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="279" spans="1:16" ht="17" customHeight="1">
@@ -42329,13 +42723,13 @@
         <v>1845</v>
       </c>
       <c r="N279" s="46" t="s">
-        <v>16</v>
+        <v>1846</v>
       </c>
       <c r="O279" s="47" t="s">
-        <v>1846</v>
+        <v>16</v>
       </c>
       <c r="P279" s="62" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="17" customHeight="1">
@@ -42386,7 +42780,7 @@
         <v>16</v>
       </c>
       <c r="P280" s="62" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="17" customHeight="1">
@@ -42431,13 +42825,13 @@
         <v>1850</v>
       </c>
       <c r="N281" s="46" t="s">
-        <v>16</v>
+        <v>1851</v>
       </c>
       <c r="O281" s="47" t="s">
-        <v>1851</v>
+        <v>16</v>
       </c>
       <c r="P281" s="62" t="s">
-        <v>3666</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="17" customHeight="1">
@@ -42488,7 +42882,7 @@
         <v>1855</v>
       </c>
       <c r="P282" s="62" t="s">
-        <v>3667</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="283" spans="1:16" ht="17" customHeight="1">
@@ -42539,7 +42933,7 @@
         <v>3145</v>
       </c>
       <c r="P283" s="62" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="284" spans="1:16" ht="17" customHeight="1">
@@ -42584,13 +42978,13 @@
         <v>1860</v>
       </c>
       <c r="N284" s="46" t="s">
-        <v>16</v>
+        <v>1861</v>
       </c>
       <c r="O284" s="47" t="s">
-        <v>1861</v>
+        <v>16</v>
       </c>
       <c r="P284" s="62" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="17" customHeight="1">
@@ -42641,7 +43035,7 @@
         <v>1865</v>
       </c>
       <c r="P285" s="62" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="17" customHeight="1">
@@ -42692,7 +43086,7 @@
         <v>1869</v>
       </c>
       <c r="P286" s="62" t="s">
-        <v>3668</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="287" spans="1:16" ht="17" customHeight="1">
@@ -42737,13 +43131,13 @@
         <v>1871</v>
       </c>
       <c r="N287" s="46" t="s">
-        <v>16</v>
+        <v>1872</v>
       </c>
       <c r="O287" s="47" t="s">
-        <v>1872</v>
+        <v>16</v>
       </c>
       <c r="P287" s="62" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="288" spans="1:16" ht="17" customHeight="1">
@@ -42788,13 +43182,13 @@
         <v>1874</v>
       </c>
       <c r="N288" s="46" t="s">
-        <v>16</v>
+        <v>1875</v>
       </c>
       <c r="O288" s="47" t="s">
-        <v>1875</v>
+        <v>16</v>
       </c>
       <c r="P288" s="62" t="s">
-        <v>3669</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="289" spans="1:16" ht="17" customHeight="1">
@@ -42839,13 +43233,13 @@
         <v>1877</v>
       </c>
       <c r="N289" s="46" t="s">
-        <v>16</v>
+        <v>3146</v>
       </c>
       <c r="O289" s="47" t="s">
-        <v>3146</v>
+        <v>16</v>
       </c>
       <c r="P289" s="62" t="s">
-        <v>3670</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="290" spans="1:16" ht="17" customHeight="1">
@@ -42947,7 +43341,7 @@
         <v>16</v>
       </c>
       <c r="P291" s="62" t="s">
-        <v>3671</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="17" customHeight="1">
@@ -42992,13 +43386,13 @@
         <v>1885</v>
       </c>
       <c r="N292" s="46" t="s">
-        <v>16</v>
+        <v>1886</v>
       </c>
       <c r="O292" s="47" t="s">
-        <v>1886</v>
+        <v>16</v>
       </c>
       <c r="P292" s="62" t="s">
-        <v>3672</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="293" spans="1:16" ht="17" customHeight="1">
@@ -43049,7 +43443,7 @@
         <v>1890</v>
       </c>
       <c r="P293" s="62" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="294" spans="1:16" ht="17" customHeight="1">
@@ -43100,7 +43494,7 @@
         <v>16</v>
       </c>
       <c r="P294" s="62" t="s">
-        <v>3674</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="295" spans="1:16" ht="17" customHeight="1">
@@ -43145,13 +43539,13 @@
         <v>1894</v>
       </c>
       <c r="N295" s="46" t="s">
-        <v>16</v>
+        <v>3147</v>
       </c>
       <c r="O295" s="47" t="s">
-        <v>3147</v>
+        <v>16</v>
       </c>
       <c r="P295" s="62" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="296" spans="1:16" ht="17" customHeight="1">
@@ -43196,13 +43590,13 @@
         <v>1896</v>
       </c>
       <c r="N296" s="46" t="s">
-        <v>16</v>
+        <v>1897</v>
       </c>
       <c r="O296" s="47" t="s">
-        <v>1897</v>
+        <v>16</v>
       </c>
       <c r="P296" s="62" t="s">
-        <v>3676</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="297" spans="1:16" ht="17" customHeight="1">
@@ -43247,13 +43641,13 @@
         <v>1899</v>
       </c>
       <c r="N297" s="46" t="s">
-        <v>16</v>
+        <v>1900</v>
       </c>
       <c r="O297" s="47" t="s">
-        <v>1900</v>
+        <v>16</v>
       </c>
       <c r="P297" s="62" t="s">
-        <v>3677</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="298" spans="1:16" ht="17" customHeight="1">
@@ -43298,13 +43692,13 @@
         <v>1902</v>
       </c>
       <c r="N298" s="46" t="s">
-        <v>16</v>
+        <v>3148</v>
       </c>
       <c r="O298" s="47" t="s">
-        <v>3148</v>
+        <v>16</v>
       </c>
       <c r="P298" s="62" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="17" customHeight="1">
@@ -43355,7 +43749,7 @@
         <v>3149</v>
       </c>
       <c r="P299" s="62" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="300" spans="1:16" ht="17" customHeight="1">
@@ -43400,13 +43794,13 @@
         <v>1906</v>
       </c>
       <c r="N300" s="46" t="s">
-        <v>16</v>
+        <v>1907</v>
       </c>
       <c r="O300" s="47" t="s">
-        <v>1907</v>
+        <v>16</v>
       </c>
       <c r="P300" s="62" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
     </row>
     <row r="301" spans="1:16" ht="17" customHeight="1">
@@ -43451,13 +43845,13 @@
         <v>1909</v>
       </c>
       <c r="N301" s="46" t="s">
-        <v>16</v>
+        <v>1910</v>
       </c>
       <c r="O301" s="47" t="s">
-        <v>1910</v>
+        <v>16</v>
       </c>
       <c r="P301" s="62" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="302" spans="1:16" ht="17" customHeight="1">
@@ -43508,7 +43902,7 @@
         <v>16</v>
       </c>
       <c r="P302" s="62" t="s">
-        <v>3682</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="303" spans="1:16" ht="17" customHeight="1">
@@ -43553,13 +43947,13 @@
         <v>1914</v>
       </c>
       <c r="N303" s="46" t="s">
-        <v>16</v>
+        <v>1915</v>
       </c>
       <c r="O303" s="47" t="s">
-        <v>1915</v>
+        <v>16</v>
       </c>
       <c r="P303" s="62" t="s">
-        <v>3683</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="17" customHeight="1">
@@ -43604,13 +43998,13 @@
         <v>1917</v>
       </c>
       <c r="N304" s="46" t="s">
-        <v>16</v>
+        <v>3150</v>
       </c>
       <c r="O304" s="47" t="s">
-        <v>3150</v>
+        <v>16</v>
       </c>
       <c r="P304" s="62" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="305" spans="1:16" ht="17" customHeight="1">
@@ -43655,13 +44049,13 @@
         <v>1919</v>
       </c>
       <c r="N305" s="46" t="s">
-        <v>16</v>
+        <v>1920</v>
       </c>
       <c r="O305" s="47" t="s">
-        <v>1920</v>
+        <v>16</v>
       </c>
       <c r="P305" s="62" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="17" customHeight="1">
@@ -43706,13 +44100,13 @@
         <v>1922</v>
       </c>
       <c r="N306" s="46" t="s">
-        <v>16</v>
+        <v>1923</v>
       </c>
       <c r="O306" s="47" t="s">
-        <v>1923</v>
+        <v>16</v>
       </c>
       <c r="P306" s="62" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="307" spans="1:16" ht="17" customHeight="1">
@@ -43757,13 +44151,13 @@
         <v>1925</v>
       </c>
       <c r="N307" s="46" t="s">
-        <v>16</v>
+        <v>1926</v>
       </c>
       <c r="O307" s="47" t="s">
-        <v>1926</v>
+        <v>16</v>
       </c>
       <c r="P307" s="62" t="s">
-        <v>3686</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="17" customHeight="1">
@@ -43808,13 +44202,13 @@
         <v>1928</v>
       </c>
       <c r="N308" s="46" t="s">
-        <v>16</v>
+        <v>3151</v>
       </c>
       <c r="O308" s="47" t="s">
-        <v>3151</v>
+        <v>16</v>
       </c>
       <c r="P308" s="62" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="17" customHeight="1">
@@ -43859,13 +44253,13 @@
         <v>1930</v>
       </c>
       <c r="N309" s="46" t="s">
-        <v>16</v>
+        <v>1931</v>
       </c>
       <c r="O309" s="47" t="s">
-        <v>1931</v>
+        <v>16</v>
       </c>
       <c r="P309" s="62" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="17" customHeight="1">
@@ -43910,13 +44304,13 @@
         <v>1933</v>
       </c>
       <c r="N310" s="46" t="s">
-        <v>16</v>
+        <v>1934</v>
       </c>
       <c r="O310" s="47" t="s">
-        <v>1934</v>
+        <v>16</v>
       </c>
       <c r="P310" s="62" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="311" spans="1:16" ht="17" customHeight="1">
@@ -43967,7 +44361,7 @@
         <v>16</v>
       </c>
       <c r="P311" s="62" t="s">
-        <v>3690</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="312" spans="1:16" ht="17" customHeight="1">
@@ -44012,13 +44406,13 @@
         <v>1938</v>
       </c>
       <c r="N312" s="46" t="s">
-        <v>16</v>
+        <v>1939</v>
       </c>
       <c r="O312" s="47" t="s">
-        <v>1939</v>
+        <v>16</v>
       </c>
       <c r="P312" s="62" t="s">
-        <v>3691</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="313" spans="1:16" ht="17" customHeight="1">
@@ -44063,10 +44457,10 @@
         <v>1941</v>
       </c>
       <c r="N313" s="46" t="s">
-        <v>16</v>
+        <v>1942</v>
       </c>
       <c r="O313" s="47" t="s">
-        <v>1942</v>
+        <v>16</v>
       </c>
       <c r="P313" s="62" t="s">
         <v>3307</v>
@@ -44114,13 +44508,13 @@
         <v>1944</v>
       </c>
       <c r="N314" s="46" t="s">
-        <v>16</v>
+        <v>3152</v>
       </c>
       <c r="O314" s="47" t="s">
-        <v>3152</v>
+        <v>16</v>
       </c>
       <c r="P314" s="62" t="s">
-        <v>3692</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="315" spans="1:16" ht="17" customHeight="1">
@@ -44165,13 +44559,13 @@
         <v>1946</v>
       </c>
       <c r="N315" s="46" t="s">
-        <v>16</v>
+        <v>3153</v>
       </c>
       <c r="O315" s="47" t="s">
-        <v>3153</v>
+        <v>16</v>
       </c>
       <c r="P315" s="62" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="316" spans="1:16" ht="17" customHeight="1">
@@ -44216,13 +44610,13 @@
         <v>1948</v>
       </c>
       <c r="N316" s="46" t="s">
-        <v>16</v>
+        <v>1949</v>
       </c>
       <c r="O316" s="47" t="s">
-        <v>1949</v>
+        <v>16</v>
       </c>
       <c r="P316" s="62" t="s">
-        <v>3693</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="317" spans="1:16" ht="17" customHeight="1">
@@ -44267,13 +44661,13 @@
         <v>1951</v>
       </c>
       <c r="N317" s="46" t="s">
-        <v>16</v>
+        <v>1952</v>
       </c>
       <c r="O317" s="47" t="s">
-        <v>1952</v>
+        <v>16</v>
       </c>
       <c r="P317" s="62" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="318" spans="1:16" ht="17" customHeight="1">
@@ -44324,7 +44718,7 @@
         <v>16</v>
       </c>
       <c r="P318" s="62" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="319" spans="1:16" ht="17" customHeight="1">
@@ -44375,7 +44769,7 @@
         <v>1958</v>
       </c>
       <c r="P319" s="62" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="320" spans="1:16" ht="17" customHeight="1">
@@ -44471,13 +44865,13 @@
         <v>1962</v>
       </c>
       <c r="N321" s="46" t="s">
-        <v>16</v>
+        <v>1963</v>
       </c>
       <c r="O321" s="47" t="s">
-        <v>1963</v>
+        <v>16</v>
       </c>
       <c r="P321" s="62" t="s">
-        <v>3695</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="322" spans="1:16" ht="17" customHeight="1">
@@ -44522,13 +44916,13 @@
         <v>1965</v>
       </c>
       <c r="N322" s="46" t="s">
-        <v>16</v>
+        <v>1966</v>
       </c>
       <c r="O322" s="47" t="s">
-        <v>1966</v>
+        <v>16</v>
       </c>
       <c r="P322" s="62" t="s">
-        <v>3696</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="323" spans="1:16" ht="17" customHeight="1">
@@ -44573,13 +44967,13 @@
         <v>1968</v>
       </c>
       <c r="N323" s="46" t="s">
-        <v>16</v>
+        <v>1969</v>
       </c>
       <c r="O323" s="47" t="s">
-        <v>1969</v>
+        <v>16</v>
       </c>
       <c r="P323" s="62" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="324" spans="1:16" ht="17" customHeight="1">
@@ -44630,7 +45024,7 @@
         <v>16</v>
       </c>
       <c r="P324" s="62" t="s">
-        <v>3697</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="17" customHeight="1">
@@ -44675,13 +45069,13 @@
         <v>1973</v>
       </c>
       <c r="N325" s="46" t="s">
-        <v>16</v>
+        <v>1974</v>
       </c>
       <c r="O325" s="47" t="s">
-        <v>1974</v>
+        <v>16</v>
       </c>
       <c r="P325" s="62" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="326" spans="1:16" ht="17" customHeight="1">
@@ -44726,13 +45120,13 @@
         <v>1976</v>
       </c>
       <c r="N326" s="46" t="s">
-        <v>16</v>
+        <v>3154</v>
       </c>
       <c r="O326" s="47" t="s">
-        <v>3154</v>
+        <v>16</v>
       </c>
       <c r="P326" s="62" t="s">
-        <v>3698</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="17" customHeight="1">
@@ -44783,7 +45177,7 @@
         <v>1980</v>
       </c>
       <c r="P327" s="62" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="328" spans="1:16" ht="17" customHeight="1">
@@ -44828,13 +45222,13 @@
         <v>1982</v>
       </c>
       <c r="N328" s="46" t="s">
-        <v>16</v>
+        <v>1983</v>
       </c>
       <c r="O328" s="47" t="s">
-        <v>1983</v>
+        <v>16</v>
       </c>
       <c r="P328" s="62" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="17" customHeight="1">
@@ -44879,13 +45273,13 @@
         <v>1985</v>
       </c>
       <c r="N329" s="46" t="s">
-        <v>16</v>
+        <v>1986</v>
       </c>
       <c r="O329" s="47" t="s">
-        <v>1986</v>
+        <v>16</v>
       </c>
       <c r="P329" s="62" t="s">
-        <v>3699</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="330" spans="1:16" ht="17" customHeight="1">
@@ -44936,7 +45330,7 @@
         <v>1990</v>
       </c>
       <c r="P330" s="62" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="331" spans="1:16" ht="17" customHeight="1">
@@ -44987,7 +45381,7 @@
         <v>16</v>
       </c>
       <c r="P331" s="62" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="332" spans="1:16" ht="17" customHeight="1">
@@ -45038,7 +45432,7 @@
         <v>16</v>
       </c>
       <c r="P332" s="62" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="333" spans="1:16" ht="17" customHeight="1">
@@ -45083,13 +45477,13 @@
         <v>1996</v>
       </c>
       <c r="N333" s="46" t="s">
-        <v>16</v>
+        <v>3155</v>
       </c>
       <c r="O333" s="47" t="s">
-        <v>3155</v>
+        <v>16</v>
       </c>
       <c r="P333" s="62" t="s">
-        <v>3700</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="334" spans="1:16" ht="17" customHeight="1">
@@ -45134,13 +45528,13 @@
         <v>1998</v>
       </c>
       <c r="N334" s="46" t="s">
-        <v>16</v>
+        <v>1999</v>
       </c>
       <c r="O334" s="47" t="s">
-        <v>1999</v>
+        <v>16</v>
       </c>
       <c r="P334" s="62" t="s">
-        <v>3701</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="17" customHeight="1">
@@ -45191,7 +45585,7 @@
         <v>16</v>
       </c>
       <c r="P335" s="62" t="s">
-        <v>3702</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="17" customHeight="1">
@@ -45236,13 +45630,13 @@
         <v>2003</v>
       </c>
       <c r="N336" s="46" t="s">
-        <v>16</v>
+        <v>3156</v>
       </c>
       <c r="O336" s="47" t="s">
-        <v>3156</v>
+        <v>16</v>
       </c>
       <c r="P336" s="62" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="17" customHeight="1">
@@ -45287,13 +45681,13 @@
         <v>2005</v>
       </c>
       <c r="N337" s="46" t="s">
-        <v>16</v>
+        <v>2006</v>
       </c>
       <c r="O337" s="47" t="s">
-        <v>2006</v>
+        <v>16</v>
       </c>
       <c r="P337" s="62" t="s">
-        <v>3703</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="338" spans="1:16" ht="17" customHeight="1">
@@ -45344,7 +45738,7 @@
         <v>16</v>
       </c>
       <c r="P338" s="62" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="339" spans="1:16" ht="17" customHeight="1">
@@ -45395,7 +45789,7 @@
         <v>16</v>
       </c>
       <c r="P339" s="62" t="s">
-        <v>3704</v>
+        <v>3702</v>
       </c>
     </row>
     <row r="340" spans="1:16" ht="17" customHeight="1">
@@ -45446,7 +45840,7 @@
         <v>16</v>
       </c>
       <c r="P340" s="62" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="17" customHeight="1">
@@ -45491,13 +45885,13 @@
         <v>2014</v>
       </c>
       <c r="N341" s="46" t="s">
-        <v>16</v>
+        <v>2015</v>
       </c>
       <c r="O341" s="47" t="s">
-        <v>2015</v>
+        <v>16</v>
       </c>
       <c r="P341" s="62" t="s">
-        <v>3705</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="17" customHeight="1">
@@ -45542,13 +45936,13 @@
         <v>2017</v>
       </c>
       <c r="N342" s="46" t="s">
-        <v>16</v>
+        <v>3157</v>
       </c>
       <c r="O342" s="47" t="s">
-        <v>3157</v>
+        <v>16</v>
       </c>
       <c r="P342" s="62" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="17" customHeight="1">
@@ -45593,13 +45987,13 @@
         <v>2019</v>
       </c>
       <c r="N343" s="46" t="s">
-        <v>16</v>
+        <v>2020</v>
       </c>
       <c r="O343" s="47" t="s">
-        <v>2020</v>
+        <v>16</v>
       </c>
       <c r="P343" s="62" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="344" spans="1:16" ht="17" customHeight="1">
@@ -45644,13 +46038,13 @@
         <v>2022</v>
       </c>
       <c r="N344" s="46" t="s">
-        <v>16</v>
+        <v>3158</v>
       </c>
       <c r="O344" s="47" t="s">
-        <v>3158</v>
+        <v>16</v>
       </c>
       <c r="P344" s="62" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="17" customHeight="1">
@@ -45695,13 +46089,13 @@
         <v>2024</v>
       </c>
       <c r="N345" s="46" t="s">
-        <v>16</v>
+        <v>2025</v>
       </c>
       <c r="O345" s="47" t="s">
-        <v>2025</v>
+        <v>16</v>
       </c>
       <c r="P345" s="62" t="s">
-        <v>3706</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="17" customHeight="1">
@@ -45746,13 +46140,13 @@
         <v>2027</v>
       </c>
       <c r="N346" s="46" t="s">
-        <v>16</v>
+        <v>2028</v>
       </c>
       <c r="O346" s="47" t="s">
-        <v>2028</v>
+        <v>16</v>
       </c>
       <c r="P346" s="62" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="17" customHeight="1">
@@ -45848,10 +46242,10 @@
         <v>2032</v>
       </c>
       <c r="N348" s="46" t="s">
-        <v>16</v>
+        <v>3159</v>
       </c>
       <c r="O348" s="47" t="s">
-        <v>3159</v>
+        <v>16</v>
       </c>
       <c r="P348" s="62" t="s">
         <v>3310</v>
@@ -45905,7 +46299,7 @@
         <v>2036</v>
       </c>
       <c r="P349" s="62" t="s">
-        <v>3707</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="350" spans="1:16" ht="17" customHeight="1">
@@ -45950,13 +46344,13 @@
         <v>2038</v>
       </c>
       <c r="N350" s="46" t="s">
-        <v>16</v>
+        <v>2039</v>
       </c>
       <c r="O350" s="47" t="s">
-        <v>2039</v>
+        <v>16</v>
       </c>
       <c r="P350" s="62" t="s">
-        <v>3708</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="351" spans="1:16" ht="17" customHeight="1">
@@ -46001,13 +46395,13 @@
         <v>2041</v>
       </c>
       <c r="N351" s="46" t="s">
-        <v>16</v>
+        <v>2042</v>
       </c>
       <c r="O351" s="47" t="s">
-        <v>2042</v>
+        <v>16</v>
       </c>
       <c r="P351" s="62" t="s">
-        <v>3709</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="17" customHeight="1">
@@ -46052,13 +46446,13 @@
         <v>2044</v>
       </c>
       <c r="N352" s="46" t="s">
-        <v>16</v>
+        <v>2045</v>
       </c>
       <c r="O352" s="47" t="s">
-        <v>2045</v>
+        <v>16</v>
       </c>
       <c r="P352" s="62" t="s">
-        <v>3710</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="17" customHeight="1">
@@ -46160,7 +46554,7 @@
         <v>16</v>
       </c>
       <c r="P354" s="62" t="s">
-        <v>3711</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="17" customHeight="1">
@@ -46205,13 +46599,13 @@
         <v>2051</v>
       </c>
       <c r="N355" s="46" t="s">
-        <v>16</v>
+        <v>2052</v>
       </c>
       <c r="O355" s="47" t="s">
-        <v>2052</v>
+        <v>16</v>
       </c>
       <c r="P355" s="62" t="s">
-        <v>3712</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="17" customHeight="1">
@@ -46256,10 +46650,10 @@
         <v>2054</v>
       </c>
       <c r="N356" s="46" t="s">
-        <v>16</v>
+        <v>2055</v>
       </c>
       <c r="O356" s="47" t="s">
-        <v>2055</v>
+        <v>16</v>
       </c>
       <c r="P356" s="62" t="s">
         <v>3312</v>
@@ -46313,7 +46707,7 @@
         <v>16</v>
       </c>
       <c r="P357" s="62" t="s">
-        <v>3713</v>
+        <v>3711</v>
       </c>
     </row>
     <row r="358" spans="1:16" ht="17" customHeight="1">
@@ -46358,13 +46752,13 @@
         <v>2059</v>
       </c>
       <c r="N358" s="46" t="s">
-        <v>16</v>
+        <v>2060</v>
       </c>
       <c r="O358" s="47" t="s">
-        <v>2060</v>
+        <v>16</v>
       </c>
       <c r="P358" s="62" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="359" spans="1:16" ht="17" customHeight="1">
@@ -46409,13 +46803,13 @@
         <v>2062</v>
       </c>
       <c r="N359" s="46" t="s">
-        <v>16</v>
+        <v>2063</v>
       </c>
       <c r="O359" s="47" t="s">
-        <v>2063</v>
+        <v>16</v>
       </c>
       <c r="P359" s="62" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="17" customHeight="1">
@@ -46460,13 +46854,13 @@
         <v>2065</v>
       </c>
       <c r="N360" s="46" t="s">
-        <v>16</v>
+        <v>2066</v>
       </c>
       <c r="O360" s="47" t="s">
-        <v>2066</v>
+        <v>16</v>
       </c>
       <c r="P360" s="62" t="s">
-        <v>3716</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="17" customHeight="1">
@@ -46511,13 +46905,13 @@
         <v>2068</v>
       </c>
       <c r="N361" s="46" t="s">
-        <v>16</v>
+        <v>2069</v>
       </c>
       <c r="O361" s="47" t="s">
-        <v>2069</v>
+        <v>16</v>
       </c>
       <c r="P361" s="62" t="s">
-        <v>3717</v>
+        <v>3715</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="17" customHeight="1">
@@ -46562,13 +46956,13 @@
         <v>2071</v>
       </c>
       <c r="N362" s="46" t="s">
-        <v>16</v>
+        <v>2072</v>
       </c>
       <c r="O362" s="47" t="s">
-        <v>2072</v>
+        <v>16</v>
       </c>
       <c r="P362" s="62" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="17" customHeight="1">
@@ -46613,13 +47007,13 @@
         <v>2074</v>
       </c>
       <c r="N363" s="46" t="s">
-        <v>16</v>
+        <v>2075</v>
       </c>
       <c r="O363" s="47" t="s">
-        <v>2075</v>
+        <v>16</v>
       </c>
       <c r="P363" s="62" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="17" customHeight="1">
@@ -46664,13 +47058,13 @@
         <v>2077</v>
       </c>
       <c r="N364" s="46" t="s">
-        <v>16</v>
+        <v>2078</v>
       </c>
       <c r="O364" s="47" t="s">
-        <v>2078</v>
+        <v>16</v>
       </c>
       <c r="P364" s="62" t="s">
-        <v>3720</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="365" spans="1:16" ht="17" customHeight="1">
@@ -46715,13 +47109,13 @@
         <v>2080</v>
       </c>
       <c r="N365" s="46" t="s">
-        <v>16</v>
+        <v>2081</v>
       </c>
       <c r="O365" s="47" t="s">
-        <v>2081</v>
+        <v>16</v>
       </c>
       <c r="P365" s="62" t="s">
-        <v>3721</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="366" spans="1:16" ht="17" customHeight="1">
@@ -46766,13 +47160,13 @@
         <v>2083</v>
       </c>
       <c r="N366" s="46" t="s">
-        <v>16</v>
+        <v>2084</v>
       </c>
       <c r="O366" s="47" t="s">
-        <v>2084</v>
+        <v>16</v>
       </c>
       <c r="P366" s="62" t="s">
-        <v>3722</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="367" spans="1:16" ht="17" customHeight="1">
@@ -46817,13 +47211,13 @@
         <v>2086</v>
       </c>
       <c r="N367" s="46" t="s">
-        <v>16</v>
+        <v>3204</v>
       </c>
       <c r="O367" s="47" t="s">
-        <v>3204</v>
+        <v>16</v>
       </c>
       <c r="P367" s="62" t="s">
-        <v>3723</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="368" spans="1:16" ht="17" customHeight="1">
@@ -46868,13 +47262,13 @@
         <v>2088</v>
       </c>
       <c r="N368" s="46" t="s">
-        <v>16</v>
+        <v>2089</v>
       </c>
       <c r="O368" s="47" t="s">
-        <v>2089</v>
+        <v>16</v>
       </c>
       <c r="P368" s="62" t="s">
-        <v>3724</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="369" spans="1:16" ht="17" customHeight="1">
@@ -46919,13 +47313,13 @@
         <v>2091</v>
       </c>
       <c r="N369" s="46" t="s">
-        <v>16</v>
+        <v>3160</v>
       </c>
       <c r="O369" s="47" t="s">
-        <v>3160</v>
+        <v>16</v>
       </c>
       <c r="P369" s="62" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="17" customHeight="1">
@@ -46970,13 +47364,13 @@
         <v>2093</v>
       </c>
       <c r="N370" s="46" t="s">
-        <v>16</v>
+        <v>2094</v>
       </c>
       <c r="O370" s="47" t="s">
-        <v>2094</v>
+        <v>16</v>
       </c>
       <c r="P370" s="62" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="371" spans="1:16" ht="17" customHeight="1">
@@ -47021,13 +47415,13 @@
         <v>2096</v>
       </c>
       <c r="N371" s="46" t="s">
-        <v>16</v>
+        <v>2097</v>
       </c>
       <c r="O371" s="47" t="s">
-        <v>2097</v>
+        <v>16</v>
       </c>
       <c r="P371" s="62" t="s">
-        <v>3725</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="372" spans="1:16" ht="17" customHeight="1">
@@ -47072,10 +47466,10 @@
         <v>2099</v>
       </c>
       <c r="N372" s="46" t="s">
-        <v>16</v>
+        <v>2100</v>
       </c>
       <c r="O372" s="47" t="s">
-        <v>2100</v>
+        <v>16</v>
       </c>
       <c r="P372" s="62" t="s">
         <v>3313</v>
@@ -47129,7 +47523,7 @@
         <v>16</v>
       </c>
       <c r="P373" s="62" t="s">
-        <v>3726</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="374" spans="1:16" ht="17" customHeight="1">
@@ -47174,13 +47568,13 @@
         <v>2104</v>
       </c>
       <c r="N374" s="46" t="s">
-        <v>16</v>
+        <v>2105</v>
       </c>
       <c r="O374" s="47" t="s">
-        <v>2105</v>
+        <v>16</v>
       </c>
       <c r="P374" s="62" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="375" spans="1:16" ht="17" customHeight="1">
@@ -47231,7 +47625,7 @@
         <v>16</v>
       </c>
       <c r="P375" s="62" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="17" customHeight="1">
@@ -47276,13 +47670,13 @@
         <v>2109</v>
       </c>
       <c r="N376" s="46" t="s">
-        <v>16</v>
+        <v>3161</v>
       </c>
       <c r="O376" s="47" t="s">
-        <v>3161</v>
+        <v>16</v>
       </c>
       <c r="P376" s="62" t="s">
-        <v>3729</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="377" spans="1:16" ht="17" customHeight="1">
@@ -47327,13 +47721,13 @@
         <v>2111</v>
       </c>
       <c r="N377" s="46" t="s">
-        <v>16</v>
+        <v>2112</v>
       </c>
       <c r="O377" s="47" t="s">
-        <v>2112</v>
+        <v>16</v>
       </c>
       <c r="P377" s="62" t="s">
-        <v>3730</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="17" customHeight="1">
@@ -47429,13 +47823,13 @@
         <v>2116</v>
       </c>
       <c r="N379" s="46" t="s">
-        <v>16</v>
+        <v>2117</v>
       </c>
       <c r="O379" s="47" t="s">
-        <v>2117</v>
+        <v>16</v>
       </c>
       <c r="P379" s="62" t="s">
-        <v>3731</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="380" spans="1:16" ht="17" customHeight="1">
@@ -47480,13 +47874,13 @@
         <v>2119</v>
       </c>
       <c r="N380" s="46" t="s">
-        <v>16</v>
+        <v>2120</v>
       </c>
       <c r="O380" s="47" t="s">
-        <v>2120</v>
+        <v>16</v>
       </c>
       <c r="P380" s="62" t="s">
-        <v>3732</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="381" spans="1:16" ht="17" customHeight="1">
@@ -47537,7 +47931,7 @@
         <v>16</v>
       </c>
       <c r="P381" s="62" t="s">
-        <v>3733</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="382" spans="1:16" ht="17" customHeight="1">
@@ -47582,13 +47976,13 @@
         <v>2124</v>
       </c>
       <c r="N382" s="46" t="s">
-        <v>16</v>
+        <v>2125</v>
       </c>
       <c r="O382" s="47" t="s">
-        <v>2125</v>
+        <v>16</v>
       </c>
       <c r="P382" s="62" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="17" customHeight="1">
@@ -47639,7 +48033,7 @@
         <v>16</v>
       </c>
       <c r="P383" s="62" t="s">
-        <v>3735</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="17" customHeight="1">
@@ -47684,13 +48078,13 @@
         <v>2129</v>
       </c>
       <c r="N384" s="46" t="s">
-        <v>16</v>
+        <v>2130</v>
       </c>
       <c r="O384" s="47" t="s">
-        <v>2130</v>
+        <v>16</v>
       </c>
       <c r="P384" s="62" t="s">
-        <v>3736</v>
+        <v>3734</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="17" customHeight="1">
@@ -47735,13 +48129,13 @@
         <v>2132</v>
       </c>
       <c r="N385" s="46" t="s">
-        <v>16</v>
+        <v>2133</v>
       </c>
       <c r="O385" s="47" t="s">
-        <v>2133</v>
+        <v>16</v>
       </c>
       <c r="P385" s="62" t="s">
-        <v>3737</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="386" spans="1:16" ht="17" customHeight="1">
@@ -47792,7 +48186,7 @@
         <v>16</v>
       </c>
       <c r="P386" s="62" t="s">
-        <v>3738</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="387" spans="1:16" ht="17" customHeight="1">
@@ -47843,7 +48237,7 @@
         <v>16</v>
       </c>
       <c r="P387" s="62" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="388" spans="1:16" ht="17" customHeight="1">
@@ -47888,13 +48282,13 @@
         <v>2139</v>
       </c>
       <c r="N388" s="46" t="s">
-        <v>16</v>
+        <v>3205</v>
       </c>
       <c r="O388" s="47" t="s">
-        <v>3205</v>
+        <v>16</v>
       </c>
       <c r="P388" s="62" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="17" customHeight="1">
@@ -47939,13 +48333,13 @@
         <v>2141</v>
       </c>
       <c r="N389" s="46" t="s">
-        <v>16</v>
+        <v>2142</v>
       </c>
       <c r="O389" s="47" t="s">
-        <v>2142</v>
+        <v>16</v>
       </c>
       <c r="P389" s="62" t="s">
-        <v>3739</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="17" customHeight="1">
@@ -47996,7 +48390,7 @@
         <v>2146</v>
       </c>
       <c r="P390" s="62" t="s">
-        <v>3740</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="391" spans="1:16" ht="17" customHeight="1">
@@ -48047,7 +48441,7 @@
         <v>3206</v>
       </c>
       <c r="P391" s="62" t="s">
-        <v>3741</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="17" customHeight="1">
@@ -48098,7 +48492,7 @@
         <v>16</v>
       </c>
       <c r="P392" s="62" t="s">
-        <v>3742</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="17" customHeight="1">
@@ -48149,7 +48543,7 @@
         <v>2154</v>
       </c>
       <c r="P393" s="62" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="394" spans="1:16" ht="17" customHeight="1">
@@ -48194,13 +48588,13 @@
         <v>2156</v>
       </c>
       <c r="N394" s="46" t="s">
-        <v>16</v>
+        <v>2157</v>
       </c>
       <c r="O394" s="47" t="s">
-        <v>2157</v>
+        <v>16</v>
       </c>
       <c r="P394" s="62" t="s">
-        <v>3744</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="395" spans="1:16" ht="17" customHeight="1">
@@ -48245,13 +48639,13 @@
         <v>2159</v>
       </c>
       <c r="N395" s="46" t="s">
-        <v>16</v>
+        <v>2160</v>
       </c>
       <c r="O395" s="47" t="s">
-        <v>2160</v>
+        <v>16</v>
       </c>
       <c r="P395" s="62" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="396" spans="1:16" ht="17" customHeight="1">
@@ -48296,13 +48690,13 @@
         <v>2162</v>
       </c>
       <c r="N396" s="46" t="s">
-        <v>16</v>
+        <v>2163</v>
       </c>
       <c r="O396" s="47" t="s">
-        <v>2163</v>
+        <v>16</v>
       </c>
       <c r="P396" s="62" t="s">
-        <v>3745</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="17" customHeight="1">
@@ -48347,13 +48741,13 @@
         <v>2165</v>
       </c>
       <c r="N397" s="46" t="s">
-        <v>16</v>
+        <v>2166</v>
       </c>
       <c r="O397" s="47" t="s">
-        <v>2166</v>
+        <v>16</v>
       </c>
       <c r="P397" s="62" t="s">
-        <v>3746</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="398" spans="1:16" ht="17" customHeight="1">
@@ -48398,13 +48792,13 @@
         <v>2168</v>
       </c>
       <c r="N398" s="46" t="s">
-        <v>16</v>
+        <v>2169</v>
       </c>
       <c r="O398" s="47" t="s">
-        <v>2169</v>
+        <v>16</v>
       </c>
       <c r="P398" s="62" t="s">
-        <v>3747</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="399" spans="1:16" ht="17" customHeight="1">
@@ -48449,13 +48843,13 @@
         <v>2171</v>
       </c>
       <c r="N399" s="46" t="s">
-        <v>16</v>
+        <v>2172</v>
       </c>
       <c r="O399" s="47" t="s">
-        <v>2172</v>
+        <v>16</v>
       </c>
       <c r="P399" s="62" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="17" customHeight="1">
@@ -48500,10 +48894,10 @@
         <v>2174</v>
       </c>
       <c r="N400" s="46" t="s">
-        <v>16</v>
+        <v>2175</v>
       </c>
       <c r="O400" s="47" t="s">
-        <v>2175</v>
+        <v>16</v>
       </c>
       <c r="P400" s="62" t="s">
         <v>3315</v>
@@ -48602,13 +48996,13 @@
         <v>2181</v>
       </c>
       <c r="N402" s="46" t="s">
-        <v>16</v>
+        <v>2182</v>
       </c>
       <c r="O402" s="47" t="s">
-        <v>2182</v>
+        <v>16</v>
       </c>
       <c r="P402" s="62" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="17" customHeight="1">
@@ -48653,13 +49047,13 @@
         <v>2184</v>
       </c>
       <c r="N403" s="46" t="s">
-        <v>16</v>
+        <v>2185</v>
       </c>
       <c r="O403" s="47" t="s">
-        <v>2185</v>
+        <v>16</v>
       </c>
       <c r="P403" s="62" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="404" spans="1:16" ht="17" customHeight="1">
@@ -48704,13 +49098,13 @@
         <v>2187</v>
       </c>
       <c r="N404" s="46" t="s">
-        <v>16</v>
+        <v>2188</v>
       </c>
       <c r="O404" s="47" t="s">
-        <v>2188</v>
+        <v>16</v>
       </c>
       <c r="P404" s="62" t="s">
-        <v>3751</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="405" spans="1:16" ht="17" customHeight="1">
@@ -48755,10 +49149,10 @@
         <v>2190</v>
       </c>
       <c r="N405" s="46" t="s">
-        <v>16</v>
+        <v>2191</v>
       </c>
       <c r="O405" s="47" t="s">
-        <v>2191</v>
+        <v>16</v>
       </c>
       <c r="P405" s="62" t="s">
         <v>3317</v>
@@ -48806,13 +49200,13 @@
         <v>2193</v>
       </c>
       <c r="N406" s="46" t="s">
-        <v>16</v>
+        <v>2194</v>
       </c>
       <c r="O406" s="47" t="s">
-        <v>2194</v>
+        <v>16</v>
       </c>
       <c r="P406" s="62" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="17" customHeight="1">
@@ -48857,10 +49251,10 @@
         <v>2196</v>
       </c>
       <c r="N407" s="46" t="s">
-        <v>16</v>
+        <v>2197</v>
       </c>
       <c r="O407" s="47" t="s">
-        <v>2197</v>
+        <v>16</v>
       </c>
       <c r="P407" s="62" t="s">
         <v>3318</v>
@@ -48908,13 +49302,13 @@
         <v>2199</v>
       </c>
       <c r="N408" s="46" t="s">
-        <v>16</v>
+        <v>2200</v>
       </c>
       <c r="O408" s="47" t="s">
-        <v>2200</v>
+        <v>16</v>
       </c>
       <c r="P408" s="62" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="409" spans="1:16" ht="17" customHeight="1">
@@ -48959,13 +49353,13 @@
         <v>2202</v>
       </c>
       <c r="N409" s="46" t="s">
-        <v>16</v>
+        <v>2203</v>
       </c>
       <c r="O409" s="47" t="s">
-        <v>2203</v>
+        <v>16</v>
       </c>
       <c r="P409" s="62" t="s">
-        <v>3754</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="410" spans="1:16" ht="17" customHeight="1">
@@ -49010,13 +49404,13 @@
         <v>2205</v>
       </c>
       <c r="N410" s="46" t="s">
-        <v>16</v>
+        <v>2206</v>
       </c>
       <c r="O410" s="47" t="s">
-        <v>2206</v>
+        <v>16</v>
       </c>
       <c r="P410" s="62" t="s">
-        <v>3755</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="411" spans="1:16" ht="17" customHeight="1">
@@ -49112,13 +49506,13 @@
         <v>2212</v>
       </c>
       <c r="N412" s="46" t="s">
-        <v>16</v>
+        <v>2213</v>
       </c>
       <c r="O412" s="47" t="s">
-        <v>2213</v>
+        <v>16</v>
       </c>
       <c r="P412" s="62" t="s">
-        <v>3756</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="413" spans="1:16" ht="17" customHeight="1">
@@ -49163,13 +49557,13 @@
         <v>2215</v>
       </c>
       <c r="N413" s="46" t="s">
-        <v>16</v>
+        <v>2216</v>
       </c>
       <c r="O413" s="47" t="s">
-        <v>2216</v>
+        <v>16</v>
       </c>
       <c r="P413" s="62" t="s">
-        <v>3757</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="414" spans="1:16" ht="17" customHeight="1">
@@ -49265,13 +49659,13 @@
         <v>2222</v>
       </c>
       <c r="N415" s="46" t="s">
-        <v>16</v>
+        <v>2223</v>
       </c>
       <c r="O415" s="47" t="s">
-        <v>2223</v>
+        <v>16</v>
       </c>
       <c r="P415" s="62" t="s">
-        <v>3758</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="416" spans="1:16" ht="17" customHeight="1">
@@ -49316,13 +49710,13 @@
         <v>2225</v>
       </c>
       <c r="N416" s="46" t="s">
-        <v>16</v>
+        <v>3207</v>
       </c>
       <c r="O416" s="47" t="s">
-        <v>3207</v>
+        <v>16</v>
       </c>
       <c r="P416" s="62" t="s">
-        <v>3759</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="417" spans="1:16" ht="17" customHeight="1">
@@ -49367,10 +49761,10 @@
         <v>2227</v>
       </c>
       <c r="N417" s="46" t="s">
-        <v>16</v>
+        <v>2228</v>
       </c>
       <c r="O417" s="47" t="s">
-        <v>2228</v>
+        <v>16</v>
       </c>
       <c r="P417" s="62" t="s">
         <v>3321</v>
@@ -49418,13 +49812,13 @@
         <v>2230</v>
       </c>
       <c r="N418" s="46" t="s">
-        <v>16</v>
+        <v>2231</v>
       </c>
       <c r="O418" s="47" t="s">
-        <v>2231</v>
+        <v>16</v>
       </c>
       <c r="P418" s="62" t="s">
-        <v>3760</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="419" spans="1:16" ht="17" customHeight="1">
@@ -49520,13 +49914,13 @@
         <v>2235</v>
       </c>
       <c r="N420" s="46" t="s">
-        <v>16</v>
+        <v>3209</v>
       </c>
       <c r="O420" s="47" t="s">
-        <v>3209</v>
+        <v>16</v>
       </c>
       <c r="P420" s="62" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="421" spans="1:16" ht="17" customHeight="1">
@@ -49622,10 +50016,10 @@
         <v>2239</v>
       </c>
       <c r="N422" s="46" t="s">
-        <v>16</v>
+        <v>2240</v>
       </c>
       <c r="O422" s="47" t="s">
-        <v>2240</v>
+        <v>16</v>
       </c>
       <c r="P422" s="62" t="s">
         <v>3324</v>
@@ -49673,13 +50067,13 @@
         <v>2242</v>
       </c>
       <c r="N423" s="46" t="s">
-        <v>16</v>
+        <v>3210</v>
       </c>
       <c r="O423" s="47" t="s">
-        <v>3210</v>
+        <v>16</v>
       </c>
       <c r="P423" s="62" t="s">
-        <v>3761</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="424" spans="1:16" ht="17" customHeight="1">
@@ -49781,7 +50175,7 @@
         <v>16</v>
       </c>
       <c r="P425" s="62" t="s">
-        <v>3762</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="426" spans="1:16" ht="17" customHeight="1">
@@ -49877,13 +50271,13 @@
         <v>2252</v>
       </c>
       <c r="N427" s="46" t="s">
-        <v>16</v>
+        <v>2253</v>
       </c>
       <c r="O427" s="47" t="s">
-        <v>2253</v>
+        <v>16</v>
       </c>
       <c r="P427" s="62" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="428" spans="1:16" ht="17" customHeight="1">
@@ -49928,10 +50322,10 @@
         <v>2255</v>
       </c>
       <c r="N428" s="46" t="s">
-        <v>16</v>
+        <v>3212</v>
       </c>
       <c r="O428" s="47" t="s">
-        <v>3212</v>
+        <v>16</v>
       </c>
       <c r="P428" s="62" t="s">
         <v>3327</v>
@@ -50030,10 +50424,10 @@
         <v>2259</v>
       </c>
       <c r="N430" s="46" t="s">
-        <v>16</v>
+        <v>2260</v>
       </c>
       <c r="O430" s="47" t="s">
-        <v>2260</v>
+        <v>16</v>
       </c>
       <c r="P430" s="62" t="s">
         <v>3329</v>
@@ -50081,13 +50475,13 @@
         <v>2262</v>
       </c>
       <c r="N431" s="46" t="s">
-        <v>16</v>
+        <v>2263</v>
       </c>
       <c r="O431" s="47" t="s">
-        <v>2263</v>
+        <v>16</v>
       </c>
       <c r="P431" s="62" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="432" spans="1:16" ht="17" customHeight="1">
@@ -50132,13 +50526,13 @@
         <v>2265</v>
       </c>
       <c r="N432" s="46" t="s">
-        <v>16</v>
+        <v>3213</v>
       </c>
       <c r="O432" s="47" t="s">
-        <v>3213</v>
+        <v>16</v>
       </c>
       <c r="P432" s="62" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="17" customHeight="1">
@@ -50183,13 +50577,13 @@
         <v>2267</v>
       </c>
       <c r="N433" s="46" t="s">
-        <v>16</v>
+        <v>2268</v>
       </c>
       <c r="O433" s="47" t="s">
-        <v>2268</v>
+        <v>16</v>
       </c>
       <c r="P433" s="62" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="434" spans="1:16" ht="17" customHeight="1">
@@ -50240,7 +50634,7 @@
         <v>16</v>
       </c>
       <c r="P434" s="62" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="435" spans="1:16" ht="17" customHeight="1">
@@ -50285,13 +50679,13 @@
         <v>2272</v>
       </c>
       <c r="N435" s="46" t="s">
-        <v>16</v>
+        <v>2273</v>
       </c>
       <c r="O435" s="47" t="s">
-        <v>2273</v>
+        <v>16</v>
       </c>
       <c r="P435" s="62" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="17" customHeight="1">
@@ -50342,7 +50736,7 @@
         <v>16</v>
       </c>
       <c r="P436" s="62" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="17" customHeight="1">
@@ -50387,10 +50781,10 @@
         <v>2277</v>
       </c>
       <c r="N437" s="46" t="s">
-        <v>16</v>
+        <v>2278</v>
       </c>
       <c r="O437" s="47" t="s">
-        <v>2278</v>
+        <v>16</v>
       </c>
       <c r="P437" s="62" t="s">
         <v>3330</v>
@@ -50438,10 +50832,10 @@
         <v>2280</v>
       </c>
       <c r="N438" s="46" t="s">
-        <v>16</v>
+        <v>2281</v>
       </c>
       <c r="O438" s="47" t="s">
-        <v>2281</v>
+        <v>16</v>
       </c>
       <c r="P438" s="62" t="s">
         <v>3331</v>
@@ -50489,10 +50883,10 @@
         <v>2283</v>
       </c>
       <c r="N439" s="46" t="s">
-        <v>16</v>
+        <v>2284</v>
       </c>
       <c r="O439" s="47" t="s">
-        <v>2284</v>
+        <v>16</v>
       </c>
       <c r="P439" s="62" t="s">
         <v>3332</v>
@@ -50540,10 +50934,10 @@
         <v>2286</v>
       </c>
       <c r="N440" s="46" t="s">
-        <v>16</v>
+        <v>2287</v>
       </c>
       <c r="O440" s="47" t="s">
-        <v>2287</v>
+        <v>16</v>
       </c>
       <c r="P440" s="62" t="s">
         <v>3333</v>
@@ -50591,13 +50985,13 @@
         <v>2289</v>
       </c>
       <c r="N441" s="46" t="s">
-        <v>16</v>
+        <v>3214</v>
       </c>
       <c r="O441" s="47" t="s">
-        <v>3214</v>
+        <v>16</v>
       </c>
       <c r="P441" s="62" t="s">
-        <v>3770</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="442" spans="1:16" ht="17" customHeight="1">
@@ -50642,10 +51036,10 @@
         <v>2291</v>
       </c>
       <c r="N442" s="46" t="s">
-        <v>16</v>
+        <v>2292</v>
       </c>
       <c r="O442" s="47" t="s">
-        <v>2292</v>
+        <v>16</v>
       </c>
       <c r="P442" s="62" t="s">
         <v>3334</v>
@@ -50693,10 +51087,10 @@
         <v>2294</v>
       </c>
       <c r="N443" s="46" t="s">
-        <v>16</v>
+        <v>2295</v>
       </c>
       <c r="O443" s="47" t="s">
-        <v>2295</v>
+        <v>16</v>
       </c>
       <c r="P443" s="62" t="s">
         <v>3335</v>
@@ -50744,13 +51138,13 @@
         <v>2297</v>
       </c>
       <c r="N444" s="46" t="s">
-        <v>16</v>
+        <v>3215</v>
       </c>
       <c r="O444" s="47" t="s">
-        <v>3215</v>
+        <v>16</v>
       </c>
       <c r="P444" s="62" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
     </row>
     <row r="445" spans="1:16" ht="17" customHeight="1">
@@ -50795,13 +51189,13 @@
         <v>2299</v>
       </c>
       <c r="N445" s="46" t="s">
-        <v>16</v>
+        <v>2300</v>
       </c>
       <c r="O445" s="47" t="s">
-        <v>2300</v>
+        <v>16</v>
       </c>
       <c r="P445" s="62" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="446" spans="1:16" ht="17" customHeight="1">
@@ -50846,13 +51240,13 @@
         <v>2302</v>
       </c>
       <c r="N446" s="46" t="s">
-        <v>16</v>
+        <v>2303</v>
       </c>
       <c r="O446" s="47" t="s">
-        <v>2303</v>
+        <v>16</v>
       </c>
       <c r="P446" s="62" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="447" spans="1:16" ht="17" customHeight="1">
@@ -50897,13 +51291,13 @@
         <v>2305</v>
       </c>
       <c r="N447" s="46" t="s">
-        <v>16</v>
+        <v>2306</v>
       </c>
       <c r="O447" s="47" t="s">
-        <v>2306</v>
+        <v>16</v>
       </c>
       <c r="P447" s="62" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="448" spans="1:16" ht="17" customHeight="1">
@@ -50948,10 +51342,10 @@
         <v>2308</v>
       </c>
       <c r="N448" s="46" t="s">
-        <v>16</v>
+        <v>2309</v>
       </c>
       <c r="O448" s="47" t="s">
-        <v>2309</v>
+        <v>16</v>
       </c>
       <c r="P448" s="62" t="s">
         <v>3336</v>
@@ -50999,13 +51393,13 @@
         <v>2311</v>
       </c>
       <c r="N449" s="46" t="s">
-        <v>16</v>
+        <v>3216</v>
       </c>
       <c r="O449" s="47" t="s">
-        <v>3216</v>
+        <v>16</v>
       </c>
       <c r="P449" s="62" t="s">
-        <v>3772</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="450" spans="1:16" ht="17" customHeight="1">
@@ -51050,13 +51444,13 @@
         <v>2313</v>
       </c>
       <c r="N450" s="46" t="s">
-        <v>16</v>
+        <v>2314</v>
       </c>
       <c r="O450" s="47" t="s">
-        <v>2314</v>
+        <v>16</v>
       </c>
       <c r="P450" s="62" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="451" spans="1:16" ht="17" customHeight="1">
@@ -51101,10 +51495,10 @@
         <v>2316</v>
       </c>
       <c r="N451" s="46" t="s">
-        <v>16</v>
+        <v>2317</v>
       </c>
       <c r="O451" s="47" t="s">
-        <v>2317</v>
+        <v>16</v>
       </c>
       <c r="P451" s="62" t="s">
         <v>3337</v>
@@ -51152,13 +51546,13 @@
         <v>2319</v>
       </c>
       <c r="N452" s="46" t="s">
-        <v>16</v>
+        <v>3217</v>
       </c>
       <c r="O452" s="47" t="s">
-        <v>3217</v>
+        <v>16</v>
       </c>
       <c r="P452" s="62" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="453" spans="1:16" ht="17" customHeight="1">
@@ -51203,13 +51597,13 @@
         <v>2321</v>
       </c>
       <c r="N453" s="46" t="s">
-        <v>16</v>
+        <v>3218</v>
       </c>
       <c r="O453" s="47" t="s">
-        <v>3218</v>
+        <v>16</v>
       </c>
       <c r="P453" s="62" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="454" spans="1:16" ht="17" customHeight="1">
@@ -51254,10 +51648,10 @@
         <v>2323</v>
       </c>
       <c r="N454" s="46" t="s">
-        <v>16</v>
+        <v>2324</v>
       </c>
       <c r="O454" s="47" t="s">
-        <v>2324</v>
+        <v>16</v>
       </c>
       <c r="P454" s="62" t="s">
         <v>3338</v>
@@ -51305,13 +51699,13 @@
         <v>2326</v>
       </c>
       <c r="N455" s="46" t="s">
-        <v>16</v>
+        <v>3219</v>
       </c>
       <c r="O455" s="47" t="s">
-        <v>3219</v>
+        <v>16</v>
       </c>
       <c r="P455" s="62" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="456" spans="1:16" ht="17" customHeight="1">
@@ -51356,13 +51750,13 @@
         <v>2328</v>
       </c>
       <c r="N456" s="46" t="s">
-        <v>16</v>
+        <v>3220</v>
       </c>
       <c r="O456" s="47" t="s">
-        <v>3220</v>
+        <v>16</v>
       </c>
       <c r="P456" s="62" t="s">
-        <v>3774</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="457" spans="1:16" ht="17" customHeight="1">
@@ -51407,10 +51801,10 @@
         <v>2330</v>
       </c>
       <c r="N457" s="46" t="s">
-        <v>16</v>
+        <v>2331</v>
       </c>
       <c r="O457" s="47" t="s">
-        <v>2331</v>
+        <v>16</v>
       </c>
       <c r="P457" s="62" t="s">
         <v>3339</v>
@@ -51458,13 +51852,13 @@
         <v>2333</v>
       </c>
       <c r="N458" s="46" t="s">
-        <v>16</v>
+        <v>2334</v>
       </c>
       <c r="O458" s="47" t="s">
-        <v>2334</v>
+        <v>16</v>
       </c>
       <c r="P458" s="62" t="s">
-        <v>3775</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="459" spans="1:16" ht="17" customHeight="1">
@@ -51509,10 +51903,10 @@
         <v>2336</v>
       </c>
       <c r="N459" s="46" t="s">
-        <v>16</v>
+        <v>2337</v>
       </c>
       <c r="O459" s="47" t="s">
-        <v>2337</v>
+        <v>16</v>
       </c>
       <c r="P459" s="62" t="s">
         <v>3340</v>
@@ -51560,10 +51954,10 @@
         <v>2339</v>
       </c>
       <c r="N460" s="46" t="s">
-        <v>16</v>
+        <v>2340</v>
       </c>
       <c r="O460" s="47" t="s">
-        <v>2340</v>
+        <v>16</v>
       </c>
       <c r="P460" s="62" t="s">
         <v>3341</v>
@@ -51617,7 +52011,7 @@
         <v>16</v>
       </c>
       <c r="P461" s="62" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="462" spans="1:16" ht="17" customHeight="1">
@@ -51662,10 +52056,10 @@
         <v>2344</v>
       </c>
       <c r="N462" s="46" t="s">
-        <v>16</v>
+        <v>2345</v>
       </c>
       <c r="O462" s="47" t="s">
-        <v>2345</v>
+        <v>16</v>
       </c>
       <c r="P462" s="62" t="s">
         <v>3342</v>
@@ -51713,13 +52107,13 @@
         <v>2347</v>
       </c>
       <c r="N463" s="46" t="s">
-        <v>16</v>
+        <v>3221</v>
       </c>
       <c r="O463" s="47" t="s">
-        <v>3221</v>
+        <v>16</v>
       </c>
       <c r="P463" s="62" t="s">
-        <v>3776</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="464" spans="1:16" ht="17" customHeight="1">
@@ -51770,7 +52164,7 @@
         <v>3222</v>
       </c>
       <c r="P464" s="62" t="s">
-        <v>3777</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="465" spans="1:16" ht="17" customHeight="1">
@@ -51815,10 +52209,10 @@
         <v>2351</v>
       </c>
       <c r="N465" s="46" t="s">
-        <v>16</v>
+        <v>2352</v>
       </c>
       <c r="O465" s="47" t="s">
-        <v>2352</v>
+        <v>16</v>
       </c>
       <c r="P465" s="62" t="s">
         <v>3343</v>
@@ -51866,10 +52260,10 @@
         <v>2354</v>
       </c>
       <c r="N466" s="46" t="s">
-        <v>16</v>
+        <v>2355</v>
       </c>
       <c r="O466" s="47" t="s">
-        <v>2355</v>
+        <v>16</v>
       </c>
       <c r="P466" s="62" t="s">
         <v>3344</v>
@@ -51917,13 +52311,13 @@
         <v>2357</v>
       </c>
       <c r="N467" s="46" t="s">
-        <v>16</v>
+        <v>2358</v>
       </c>
       <c r="O467" s="47" t="s">
-        <v>2358</v>
+        <v>16</v>
       </c>
       <c r="P467" s="62" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="468" spans="1:16" ht="17" customHeight="1">
@@ -51968,10 +52362,10 @@
         <v>2360</v>
       </c>
       <c r="N468" s="46" t="s">
-        <v>16</v>
+        <v>3223</v>
       </c>
       <c r="O468" s="47" t="s">
-        <v>3223</v>
+        <v>16</v>
       </c>
       <c r="P468" s="62" t="s">
         <v>3345</v>
@@ -52025,7 +52419,7 @@
         <v>2364</v>
       </c>
       <c r="P469" s="62" t="s">
-        <v>3778</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="470" spans="1:16" ht="17" customHeight="1">
@@ -52070,13 +52464,13 @@
         <v>2366</v>
       </c>
       <c r="N470" s="46" t="s">
-        <v>16</v>
+        <v>2367</v>
       </c>
       <c r="O470" s="47" t="s">
-        <v>2367</v>
+        <v>16</v>
       </c>
       <c r="P470" s="62" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="471" spans="1:16" ht="17" customHeight="1">
@@ -52121,10 +52515,10 @@
         <v>2369</v>
       </c>
       <c r="N471" s="46" t="s">
-        <v>16</v>
+        <v>2370</v>
       </c>
       <c r="O471" s="47" t="s">
-        <v>2370</v>
+        <v>16</v>
       </c>
       <c r="P471" s="62" t="s">
         <v>3346</v>
@@ -52172,13 +52566,13 @@
         <v>2372</v>
       </c>
       <c r="N472" s="46" t="s">
-        <v>16</v>
+        <v>2373</v>
       </c>
       <c r="O472" s="47" t="s">
-        <v>2373</v>
+        <v>16</v>
       </c>
       <c r="P472" s="62" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="473" spans="1:16" ht="17" customHeight="1">
@@ -52229,7 +52623,7 @@
         <v>2377</v>
       </c>
       <c r="P473" s="62" t="s">
-        <v>3781</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="474" spans="1:16" ht="17" customHeight="1">
@@ -52280,7 +52674,7 @@
         <v>16</v>
       </c>
       <c r="P474" s="62" t="s">
-        <v>3782</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="475" spans="1:16" ht="17" customHeight="1">
@@ -52325,13 +52719,13 @@
         <v>2381</v>
       </c>
       <c r="N475" s="46" t="s">
-        <v>16</v>
+        <v>2382</v>
       </c>
       <c r="O475" s="47" t="s">
-        <v>2382</v>
+        <v>16</v>
       </c>
       <c r="P475" s="62" t="s">
-        <v>3783</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="476" spans="1:16" ht="17" customHeight="1">
@@ -52376,10 +52770,10 @@
         <v>2384</v>
       </c>
       <c r="N476" s="46" t="s">
-        <v>16</v>
+        <v>2385</v>
       </c>
       <c r="O476" s="47" t="s">
-        <v>2385</v>
+        <v>16</v>
       </c>
       <c r="P476" s="62" t="s">
         <v>3347</v>
@@ -52427,13 +52821,13 @@
         <v>2387</v>
       </c>
       <c r="N477" s="46" t="s">
-        <v>16</v>
+        <v>2388</v>
       </c>
       <c r="O477" s="47" t="s">
-        <v>2388</v>
+        <v>16</v>
       </c>
       <c r="P477" s="62" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="478" spans="1:16" ht="17" customHeight="1">
@@ -52478,13 +52872,13 @@
         <v>2390</v>
       </c>
       <c r="N478" s="46" t="s">
-        <v>16</v>
+        <v>2391</v>
       </c>
       <c r="O478" s="47" t="s">
-        <v>2391</v>
+        <v>16</v>
       </c>
       <c r="P478" s="62" t="s">
-        <v>3784</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="479" spans="1:16" ht="17" customHeight="1">
@@ -52529,10 +52923,10 @@
         <v>2393</v>
       </c>
       <c r="N479" s="46" t="s">
-        <v>16</v>
+        <v>2394</v>
       </c>
       <c r="O479" s="47" t="s">
-        <v>2394</v>
+        <v>16</v>
       </c>
       <c r="P479" s="62" t="s">
         <v>3348</v>
@@ -52580,13 +52974,13 @@
         <v>2396</v>
       </c>
       <c r="N480" s="46" t="s">
-        <v>16</v>
+        <v>2397</v>
       </c>
       <c r="O480" s="47" t="s">
-        <v>2397</v>
+        <v>16</v>
       </c>
       <c r="P480" s="62" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="481" spans="1:16" ht="17" customHeight="1">
@@ -52631,13 +53025,13 @@
         <v>2399</v>
       </c>
       <c r="N481" s="46" t="s">
-        <v>16</v>
+        <v>2400</v>
       </c>
       <c r="O481" s="47" t="s">
-        <v>2400</v>
+        <v>16</v>
       </c>
       <c r="P481" s="62" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="482" spans="1:16" ht="17" customHeight="1">
@@ -52688,7 +53082,7 @@
         <v>16</v>
       </c>
       <c r="P482" s="62" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="483" spans="1:16" ht="17" customHeight="1">
@@ -52733,10 +53127,10 @@
         <v>2404</v>
       </c>
       <c r="N483" s="46" t="s">
-        <v>16</v>
+        <v>2405</v>
       </c>
       <c r="O483" s="47" t="s">
-        <v>2405</v>
+        <v>16</v>
       </c>
       <c r="P483" s="62" t="s">
         <v>3349</v>
@@ -52784,13 +53178,13 @@
         <v>2407</v>
       </c>
       <c r="N484" s="46" t="s">
-        <v>16</v>
+        <v>2408</v>
       </c>
       <c r="O484" s="47" t="s">
-        <v>2408</v>
+        <v>16</v>
       </c>
       <c r="P484" s="62" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="485" spans="1:16" ht="17" customHeight="1">
@@ -52841,7 +53235,7 @@
         <v>16</v>
       </c>
       <c r="P485" s="62" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="486" spans="1:16" ht="17" customHeight="1">
@@ -52886,13 +53280,13 @@
         <v>2412</v>
       </c>
       <c r="N486" s="46" t="s">
-        <v>16</v>
+        <v>2413</v>
       </c>
       <c r="O486" s="47" t="s">
-        <v>2413</v>
+        <v>16</v>
       </c>
       <c r="P486" s="62" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="487" spans="1:16" ht="17" customHeight="1">
@@ -52937,10 +53331,10 @@
         <v>2415</v>
       </c>
       <c r="N487" s="46" t="s">
-        <v>16</v>
+        <v>2416</v>
       </c>
       <c r="O487" s="47" t="s">
-        <v>2416</v>
+        <v>16</v>
       </c>
       <c r="P487" s="62" t="s">
         <v>3350</v>
@@ -52988,10 +53382,10 @@
         <v>2418</v>
       </c>
       <c r="N488" s="46" t="s">
-        <v>16</v>
+        <v>2419</v>
       </c>
       <c r="O488" s="47" t="s">
-        <v>2419</v>
+        <v>16</v>
       </c>
       <c r="P488" s="62" t="s">
         <v>3351</v>
@@ -53039,10 +53433,10 @@
         <v>2421</v>
       </c>
       <c r="N489" s="46" t="s">
-        <v>16</v>
+        <v>2422</v>
       </c>
       <c r="O489" s="47" t="s">
-        <v>2422</v>
+        <v>16</v>
       </c>
       <c r="P489" s="62" t="s">
         <v>3352</v>
@@ -53090,10 +53484,10 @@
         <v>2424</v>
       </c>
       <c r="N490" s="46" t="s">
-        <v>16</v>
+        <v>2425</v>
       </c>
       <c r="O490" s="47" t="s">
-        <v>2425</v>
+        <v>16</v>
       </c>
       <c r="P490" s="62" t="s">
         <v>3353</v>
@@ -53141,13 +53535,13 @@
         <v>2427</v>
       </c>
       <c r="N491" s="46" t="s">
-        <v>16</v>
+        <v>3224</v>
       </c>
       <c r="O491" s="47" t="s">
-        <v>3224</v>
+        <v>16</v>
       </c>
       <c r="P491" s="62" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="492" spans="1:16" ht="17" customHeight="1">
@@ -53198,7 +53592,7 @@
         <v>16</v>
       </c>
       <c r="P492" s="62" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="493" spans="1:16" ht="17" customHeight="1">
@@ -53243,13 +53637,13 @@
         <v>2431</v>
       </c>
       <c r="N493" s="46" t="s">
-        <v>16</v>
+        <v>2432</v>
       </c>
       <c r="O493" s="47" t="s">
-        <v>2432</v>
+        <v>16</v>
       </c>
       <c r="P493" s="62" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="494" spans="1:16" ht="17" customHeight="1">
@@ -53294,10 +53688,10 @@
         <v>2434</v>
       </c>
       <c r="N494" s="46" t="s">
-        <v>16</v>
+        <v>2435</v>
       </c>
       <c r="O494" s="47" t="s">
-        <v>2435</v>
+        <v>16</v>
       </c>
       <c r="P494" s="62" t="s">
         <v>3354</v>
@@ -53345,10 +53739,10 @@
         <v>2437</v>
       </c>
       <c r="N495" s="46" t="s">
-        <v>16</v>
+        <v>2438</v>
       </c>
       <c r="O495" s="47" t="s">
-        <v>2438</v>
+        <v>16</v>
       </c>
       <c r="P495" s="62" t="s">
         <v>3355</v>
@@ -53396,13 +53790,13 @@
         <v>2440</v>
       </c>
       <c r="N496" s="65" t="s">
-        <v>16</v>
+        <v>2441</v>
       </c>
       <c r="O496" s="66" t="s">
-        <v>2441</v>
+        <v>16</v>
       </c>
       <c r="P496" s="67" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="497" spans="1:16" ht="17" customHeight="1">
@@ -53447,13 +53841,13 @@
         <v>2443</v>
       </c>
       <c r="N497" s="65" t="s">
-        <v>16</v>
+        <v>2444</v>
       </c>
       <c r="O497" s="66" t="s">
-        <v>2444</v>
+        <v>16</v>
       </c>
       <c r="P497" s="67" t="s">
-        <v>3947</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="498" spans="1:16" ht="17" customHeight="1">
@@ -53498,13 +53892,13 @@
         <v>2446</v>
       </c>
       <c r="N498" s="65" t="s">
-        <v>16</v>
+        <v>2447</v>
       </c>
       <c r="O498" s="66" t="s">
-        <v>2447</v>
+        <v>16</v>
       </c>
       <c r="P498" s="67" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="499" spans="1:16" ht="17" customHeight="1">
@@ -53555,7 +53949,7 @@
         <v>16</v>
       </c>
       <c r="P499" s="62" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="500" spans="1:16" ht="17" customHeight="1">
@@ -53600,10 +53994,10 @@
         <v>2451</v>
       </c>
       <c r="N500" s="46" t="s">
-        <v>16</v>
+        <v>2452</v>
       </c>
       <c r="O500" s="47" t="s">
-        <v>2452</v>
+        <v>16</v>
       </c>
       <c r="P500" s="62" t="s">
         <v>3356</v>
@@ -53651,13 +54045,13 @@
         <v>2454</v>
       </c>
       <c r="N501" s="46" t="s">
-        <v>16</v>
+        <v>2455</v>
       </c>
       <c r="O501" s="47" t="s">
-        <v>2455</v>
+        <v>16</v>
       </c>
       <c r="P501" s="62" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="502" spans="1:16" ht="17" customHeight="1">
@@ -53702,10 +54096,10 @@
         <v>2457</v>
       </c>
       <c r="N502" s="46" t="s">
-        <v>16</v>
+        <v>2458</v>
       </c>
       <c r="O502" s="47" t="s">
-        <v>2458</v>
+        <v>16</v>
       </c>
       <c r="P502" s="62" t="s">
         <v>3357</v>
@@ -53753,13 +54147,13 @@
         <v>2460</v>
       </c>
       <c r="N503" s="46" t="s">
-        <v>16</v>
+        <v>2461</v>
       </c>
       <c r="O503" s="47" t="s">
-        <v>2461</v>
+        <v>16</v>
       </c>
       <c r="P503" s="62" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="504" spans="1:16" ht="17" customHeight="1">
@@ -53804,10 +54198,10 @@
         <v>2463</v>
       </c>
       <c r="N504" s="46" t="s">
-        <v>16</v>
+        <v>2464</v>
       </c>
       <c r="O504" s="47" t="s">
-        <v>2464</v>
+        <v>16</v>
       </c>
       <c r="P504" s="62" t="s">
         <v>3358</v>
@@ -53855,10 +54249,10 @@
         <v>2466</v>
       </c>
       <c r="N505" s="46" t="s">
-        <v>16</v>
+        <v>2467</v>
       </c>
       <c r="O505" s="47" t="s">
-        <v>2467</v>
+        <v>16</v>
       </c>
       <c r="P505" s="62" t="s">
         <v>3359</v>
@@ -53906,10 +54300,10 @@
         <v>2469</v>
       </c>
       <c r="N506" s="46" t="s">
-        <v>16</v>
+        <v>2470</v>
       </c>
       <c r="O506" s="47" t="s">
-        <v>2470</v>
+        <v>16</v>
       </c>
       <c r="P506" s="62" t="s">
         <v>3360</v>
@@ -53957,10 +54351,10 @@
         <v>2472</v>
       </c>
       <c r="N507" s="46" t="s">
-        <v>16</v>
+        <v>2473</v>
       </c>
       <c r="O507" s="47" t="s">
-        <v>2473</v>
+        <v>16</v>
       </c>
       <c r="P507" s="62" t="s">
         <v>3361</v>
@@ -54008,13 +54402,13 @@
         <v>2475</v>
       </c>
       <c r="N508" s="46" t="s">
-        <v>16</v>
+        <v>2476</v>
       </c>
       <c r="O508" s="47" t="s">
-        <v>2476</v>
+        <v>16</v>
       </c>
       <c r="P508" s="62" t="s">
-        <v>3789</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="509" spans="1:16" ht="17" customHeight="1">
@@ -54059,10 +54453,10 @@
         <v>2478</v>
       </c>
       <c r="N509" s="46" t="s">
-        <v>16</v>
+        <v>2479</v>
       </c>
       <c r="O509" s="47" t="s">
-        <v>2479</v>
+        <v>16</v>
       </c>
       <c r="P509" s="62" t="s">
         <v>3362</v>
@@ -54161,13 +54555,13 @@
         <v>2483</v>
       </c>
       <c r="N511" s="46" t="s">
-        <v>16</v>
+        <v>2484</v>
       </c>
       <c r="O511" s="47" t="s">
-        <v>2484</v>
+        <v>16</v>
       </c>
       <c r="P511" s="62" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="512" spans="1:16" ht="17" customHeight="1">
@@ -54218,7 +54612,7 @@
         <v>2488</v>
       </c>
       <c r="P512" s="62" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="513" spans="1:16" ht="17" customHeight="1">
@@ -54263,13 +54657,13 @@
         <v>2490</v>
       </c>
       <c r="N513" s="46" t="s">
-        <v>16</v>
+        <v>2491</v>
       </c>
       <c r="O513" s="47" t="s">
-        <v>2491</v>
+        <v>16</v>
       </c>
       <c r="P513" s="62" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="514" spans="1:16" ht="17" customHeight="1">
@@ -54314,10 +54708,10 @@
         <v>2493</v>
       </c>
       <c r="N514" s="46" t="s">
-        <v>16</v>
+        <v>2494</v>
       </c>
       <c r="O514" s="47" t="s">
-        <v>2494</v>
+        <v>16</v>
       </c>
       <c r="P514" s="62" t="s">
         <v>3364</v>
@@ -54365,10 +54759,10 @@
         <v>2496</v>
       </c>
       <c r="N515" s="46" t="s">
-        <v>16</v>
+        <v>2497</v>
       </c>
       <c r="O515" s="47" t="s">
-        <v>2497</v>
+        <v>16</v>
       </c>
       <c r="P515" s="62" t="s">
         <v>3365</v>
@@ -54416,13 +54810,13 @@
         <v>2499</v>
       </c>
       <c r="N516" s="46" t="s">
-        <v>16</v>
+        <v>2500</v>
       </c>
       <c r="O516" s="47" t="s">
-        <v>2500</v>
+        <v>16</v>
       </c>
       <c r="P516" s="62" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="517" spans="1:16" ht="17" customHeight="1">
@@ -54467,13 +54861,13 @@
         <v>2502</v>
       </c>
       <c r="N517" s="46" t="s">
-        <v>16</v>
+        <v>2503</v>
       </c>
       <c r="O517" s="47" t="s">
-        <v>2503</v>
+        <v>16</v>
       </c>
       <c r="P517" s="62" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="518" spans="1:16" ht="17" customHeight="1">
@@ -54518,13 +54912,13 @@
         <v>2505</v>
       </c>
       <c r="N518" s="46" t="s">
-        <v>16</v>
+        <v>2506</v>
       </c>
       <c r="O518" s="47" t="s">
-        <v>2506</v>
+        <v>16</v>
       </c>
       <c r="P518" s="62" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="519" spans="1:16" ht="17" customHeight="1">
@@ -54569,13 +54963,13 @@
         <v>2508</v>
       </c>
       <c r="N519" s="46" t="s">
-        <v>16</v>
+        <v>2509</v>
       </c>
       <c r="O519" s="47" t="s">
-        <v>2509</v>
+        <v>16</v>
       </c>
       <c r="P519" s="62" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="520" spans="1:16" ht="17" customHeight="1">
@@ -54620,10 +55014,10 @@
         <v>2511</v>
       </c>
       <c r="N520" s="46" t="s">
-        <v>16</v>
+        <v>2512</v>
       </c>
       <c r="O520" s="47" t="s">
-        <v>2512</v>
+        <v>16</v>
       </c>
       <c r="P520" s="62" t="s">
         <v>3366</v>
@@ -54671,13 +55065,13 @@
         <v>2514</v>
       </c>
       <c r="N521" s="46" t="s">
-        <v>16</v>
+        <v>2515</v>
       </c>
       <c r="O521" s="47" t="s">
-        <v>2515</v>
+        <v>16</v>
       </c>
       <c r="P521" s="62" t="s">
-        <v>3956</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="522" spans="1:16" ht="17" customHeight="1">
@@ -54722,13 +55116,13 @@
         <v>2517</v>
       </c>
       <c r="N522" s="46" t="s">
-        <v>16</v>
+        <v>2518</v>
       </c>
       <c r="O522" s="47" t="s">
-        <v>2518</v>
+        <v>16</v>
       </c>
       <c r="P522" s="62" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="523" spans="1:16" ht="17" customHeight="1">
@@ -54773,13 +55167,13 @@
         <v>2520</v>
       </c>
       <c r="N523" s="46" t="s">
-        <v>16</v>
+        <v>2521</v>
       </c>
       <c r="O523" s="47" t="s">
-        <v>2521</v>
+        <v>16</v>
       </c>
       <c r="P523" s="62" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="524" spans="1:16" ht="17" customHeight="1">
@@ -54824,13 +55218,13 @@
         <v>2523</v>
       </c>
       <c r="N524" s="46" t="s">
-        <v>16</v>
+        <v>2524</v>
       </c>
       <c r="O524" s="47" t="s">
-        <v>2524</v>
+        <v>16</v>
       </c>
       <c r="P524" s="62" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="525" spans="1:16" ht="17" customHeight="1">
@@ -54875,10 +55269,10 @@
         <v>2526</v>
       </c>
       <c r="N525" s="46" t="s">
-        <v>16</v>
+        <v>2527</v>
       </c>
       <c r="O525" s="47" t="s">
-        <v>2527</v>
+        <v>16</v>
       </c>
       <c r="P525" s="62" t="s">
         <v>3367</v>
@@ -54926,13 +55320,13 @@
         <v>2529</v>
       </c>
       <c r="N526" s="46" t="s">
-        <v>16</v>
+        <v>2530</v>
       </c>
       <c r="O526" s="47" t="s">
-        <v>2530</v>
+        <v>16</v>
       </c>
       <c r="P526" s="62" t="s">
-        <v>3799</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="527" spans="1:16" ht="17" customHeight="1">
@@ -54977,13 +55371,13 @@
         <v>2532</v>
       </c>
       <c r="N527" s="46" t="s">
-        <v>16</v>
+        <v>2533</v>
       </c>
       <c r="O527" s="47" t="s">
-        <v>2533</v>
+        <v>16</v>
       </c>
       <c r="P527" s="62" t="s">
-        <v>3800</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="528" spans="1:16" ht="17" customHeight="1">
@@ -55028,13 +55422,13 @@
         <v>2535</v>
       </c>
       <c r="N528" s="46" t="s">
-        <v>16</v>
+        <v>2536</v>
       </c>
       <c r="O528" s="47" t="s">
-        <v>2536</v>
+        <v>16</v>
       </c>
       <c r="P528" s="62" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="529" spans="1:16" ht="17" customHeight="1">
@@ -55085,7 +55479,7 @@
         <v>16</v>
       </c>
       <c r="P529" s="62" t="s">
-        <v>3801</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="530" spans="1:16" ht="17" customHeight="1">
@@ -55130,13 +55524,13 @@
         <v>2540</v>
       </c>
       <c r="N530" s="46" t="s">
-        <v>16</v>
+        <v>2541</v>
       </c>
       <c r="O530" s="47" t="s">
-        <v>2541</v>
+        <v>16</v>
       </c>
       <c r="P530" s="62" t="s">
-        <v>3802</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="531" spans="1:16" ht="17" customHeight="1">
@@ -55232,13 +55626,13 @@
         <v>2545</v>
       </c>
       <c r="N532" s="46" t="s">
-        <v>16</v>
+        <v>2546</v>
       </c>
       <c r="O532" s="47" t="s">
-        <v>2546</v>
+        <v>16</v>
       </c>
       <c r="P532" s="62" t="s">
-        <v>3803</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="533" spans="1:16" ht="17" customHeight="1">
@@ -55283,13 +55677,13 @@
         <v>2548</v>
       </c>
       <c r="N533" s="46" t="s">
-        <v>16</v>
+        <v>2549</v>
       </c>
       <c r="O533" s="47" t="s">
-        <v>2549</v>
+        <v>16</v>
       </c>
       <c r="P533" s="62" t="s">
-        <v>3804</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="534" spans="1:16" ht="17" customHeight="1">
@@ -55334,10 +55728,10 @@
         <v>2551</v>
       </c>
       <c r="N534" s="46" t="s">
-        <v>16</v>
+        <v>2552</v>
       </c>
       <c r="O534" s="47" t="s">
-        <v>2552</v>
+        <v>16</v>
       </c>
       <c r="P534" s="62" t="s">
         <v>3369</v>
@@ -55385,13 +55779,13 @@
         <v>2554</v>
       </c>
       <c r="N535" s="46" t="s">
-        <v>16</v>
+        <v>2555</v>
       </c>
       <c r="O535" s="47" t="s">
-        <v>2555</v>
+        <v>16</v>
       </c>
       <c r="P535" s="62" t="s">
-        <v>3805</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="536" spans="1:16" ht="17" customHeight="1">
@@ -55436,13 +55830,13 @@
         <v>2557</v>
       </c>
       <c r="N536" s="46" t="s">
-        <v>16</v>
+        <v>2558</v>
       </c>
       <c r="O536" s="47" t="s">
-        <v>2558</v>
+        <v>16</v>
       </c>
       <c r="P536" s="62" t="s">
-        <v>3806</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="537" spans="1:16" ht="17" customHeight="1">
@@ -55487,13 +55881,13 @@
         <v>2560</v>
       </c>
       <c r="N537" s="46" t="s">
-        <v>16</v>
+        <v>2561</v>
       </c>
       <c r="O537" s="47" t="s">
-        <v>2561</v>
+        <v>16</v>
       </c>
       <c r="P537" s="62" t="s">
-        <v>3807</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="538" spans="1:16" ht="17" customHeight="1">
@@ -55538,13 +55932,13 @@
         <v>2563</v>
       </c>
       <c r="N538" s="46" t="s">
-        <v>16</v>
+        <v>2564</v>
       </c>
       <c r="O538" s="47" t="s">
-        <v>2564</v>
+        <v>16</v>
       </c>
       <c r="P538" s="62" t="s">
-        <v>3808</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="539" spans="1:16" ht="17" customHeight="1">
@@ -55589,13 +55983,13 @@
         <v>2566</v>
       </c>
       <c r="N539" s="46" t="s">
-        <v>16</v>
+        <v>2567</v>
       </c>
       <c r="O539" s="47" t="s">
-        <v>2567</v>
+        <v>16</v>
       </c>
       <c r="P539" s="62" t="s">
-        <v>3809</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="540" spans="1:16" ht="17" customHeight="1">
@@ -55640,13 +56034,13 @@
         <v>2569</v>
       </c>
       <c r="N540" s="46" t="s">
-        <v>16</v>
+        <v>2570</v>
       </c>
       <c r="O540" s="47" t="s">
-        <v>2570</v>
+        <v>16</v>
       </c>
       <c r="P540" s="62" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="541" spans="1:16" ht="17" customHeight="1">
@@ -55691,13 +56085,13 @@
         <v>2572</v>
       </c>
       <c r="N541" s="46" t="s">
-        <v>16</v>
+        <v>2573</v>
       </c>
       <c r="O541" s="47" t="s">
-        <v>2573</v>
+        <v>16</v>
       </c>
       <c r="P541" s="62" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="542" spans="1:16" ht="17" customHeight="1">
@@ -55742,13 +56136,13 @@
         <v>2575</v>
       </c>
       <c r="N542" s="46" t="s">
-        <v>16</v>
+        <v>2576</v>
       </c>
       <c r="O542" s="47" t="s">
-        <v>2576</v>
+        <v>16</v>
       </c>
       <c r="P542" s="62" t="s">
-        <v>3812</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="543" spans="1:16" ht="17" customHeight="1">
@@ -55793,10 +56187,10 @@
         <v>2578</v>
       </c>
       <c r="N543" s="46" t="s">
-        <v>16</v>
+        <v>2579</v>
       </c>
       <c r="O543" s="47" t="s">
-        <v>2579</v>
+        <v>16</v>
       </c>
       <c r="P543" s="62" t="s">
         <v>3370</v>
@@ -55844,13 +56238,13 @@
         <v>2581</v>
       </c>
       <c r="N544" s="46" t="s">
-        <v>16</v>
+        <v>2582</v>
       </c>
       <c r="O544" s="47" t="s">
-        <v>2582</v>
+        <v>16</v>
       </c>
       <c r="P544" s="62" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="545" spans="1:16" ht="17" customHeight="1">
@@ -55895,13 +56289,13 @@
         <v>2584</v>
       </c>
       <c r="N545" s="46" t="s">
-        <v>16</v>
+        <v>2585</v>
       </c>
       <c r="O545" s="47" t="s">
-        <v>2585</v>
+        <v>16</v>
       </c>
       <c r="P545" s="62" t="s">
-        <v>3814</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="546" spans="1:16" ht="17" customHeight="1">
@@ -55946,13 +56340,13 @@
         <v>2587</v>
       </c>
       <c r="N546" s="46" t="s">
-        <v>16</v>
+        <v>2588</v>
       </c>
       <c r="O546" s="47" t="s">
-        <v>2588</v>
+        <v>16</v>
       </c>
       <c r="P546" s="62" t="s">
-        <v>3815</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="547" spans="1:16" ht="17" customHeight="1">
@@ -55997,13 +56391,13 @@
         <v>2590</v>
       </c>
       <c r="N547" s="46" t="s">
-        <v>16</v>
+        <v>2591</v>
       </c>
       <c r="O547" s="47" t="s">
-        <v>2591</v>
+        <v>16</v>
       </c>
       <c r="P547" s="62" t="s">
-        <v>3816</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="548" spans="1:16" ht="17" customHeight="1">
@@ -56048,13 +56442,13 @@
         <v>2593</v>
       </c>
       <c r="N548" s="46" t="s">
-        <v>16</v>
+        <v>2594</v>
       </c>
       <c r="O548" s="47" t="s">
-        <v>2594</v>
+        <v>16</v>
       </c>
       <c r="P548" s="62" t="s">
-        <v>3817</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="549" spans="1:16" ht="17" customHeight="1">
@@ -56099,13 +56493,13 @@
         <v>2596</v>
       </c>
       <c r="N549" s="46" t="s">
-        <v>16</v>
+        <v>2597</v>
       </c>
       <c r="O549" s="47" t="s">
-        <v>2597</v>
+        <v>16</v>
       </c>
       <c r="P549" s="62" t="s">
-        <v>3818</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="550" spans="1:16" ht="17" customHeight="1">
@@ -56150,13 +56544,13 @@
         <v>2599</v>
       </c>
       <c r="N550" s="46" t="s">
-        <v>16</v>
+        <v>2600</v>
       </c>
       <c r="O550" s="47" t="s">
-        <v>2600</v>
+        <v>16</v>
       </c>
       <c r="P550" s="62" t="s">
-        <v>3819</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="551" spans="1:16" ht="17" customHeight="1">
@@ -56201,13 +56595,13 @@
         <v>2602</v>
       </c>
       <c r="N551" s="46" t="s">
-        <v>16</v>
+        <v>2603</v>
       </c>
       <c r="O551" s="47" t="s">
-        <v>2603</v>
+        <v>16</v>
       </c>
       <c r="P551" s="62" t="s">
-        <v>3820</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="552" spans="1:16" ht="17" customHeight="1">
@@ -56252,13 +56646,13 @@
         <v>2605</v>
       </c>
       <c r="N552" s="46" t="s">
-        <v>16</v>
+        <v>2606</v>
       </c>
       <c r="O552" s="47" t="s">
-        <v>2606</v>
+        <v>16</v>
       </c>
       <c r="P552" s="62" t="s">
-        <v>3821</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="553" spans="1:16" ht="17" customHeight="1">
@@ -56303,13 +56697,13 @@
         <v>2608</v>
       </c>
       <c r="N553" s="46" t="s">
-        <v>16</v>
+        <v>2609</v>
       </c>
       <c r="O553" s="47" t="s">
-        <v>2609</v>
+        <v>16</v>
       </c>
       <c r="P553" s="62" t="s">
-        <v>3822</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="554" spans="1:16" ht="17" customHeight="1">
@@ -56354,13 +56748,13 @@
         <v>2611</v>
       </c>
       <c r="N554" s="46" t="s">
-        <v>16</v>
+        <v>2612</v>
       </c>
       <c r="O554" s="47" t="s">
-        <v>2612</v>
+        <v>16</v>
       </c>
       <c r="P554" s="62" t="s">
-        <v>3823</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="555" spans="1:16" ht="17" customHeight="1">
@@ -56405,13 +56799,13 @@
         <v>2614</v>
       </c>
       <c r="N555" s="46" t="s">
-        <v>16</v>
+        <v>3225</v>
       </c>
       <c r="O555" s="47" t="s">
-        <v>3225</v>
+        <v>16</v>
       </c>
       <c r="P555" s="62" t="s">
-        <v>3824</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="556" spans="1:16" ht="17" customHeight="1">
@@ -56456,13 +56850,13 @@
         <v>2616</v>
       </c>
       <c r="N556" s="46" t="s">
-        <v>16</v>
+        <v>2617</v>
       </c>
       <c r="O556" s="47" t="s">
-        <v>2617</v>
+        <v>16</v>
       </c>
       <c r="P556" s="62" t="s">
-        <v>3825</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="557" spans="1:16" ht="17" customHeight="1">
@@ -56513,7 +56907,7 @@
         <v>16</v>
       </c>
       <c r="P557" s="62" t="s">
-        <v>3826</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="558" spans="1:16" ht="17" customHeight="1">
@@ -56558,13 +56952,13 @@
         <v>2621</v>
       </c>
       <c r="N558" s="46" t="s">
-        <v>16</v>
+        <v>2622</v>
       </c>
       <c r="O558" s="47" t="s">
-        <v>2622</v>
+        <v>16</v>
       </c>
       <c r="P558" s="62" t="s">
-        <v>3827</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="559" spans="1:16" ht="17" customHeight="1">
@@ -56615,7 +57009,7 @@
         <v>16</v>
       </c>
       <c r="P559" s="62" t="s">
-        <v>3828</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="560" spans="1:16" ht="17" customHeight="1">
@@ -56666,7 +57060,7 @@
         <v>16</v>
       </c>
       <c r="P560" s="62" t="s">
-        <v>3829</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="561" spans="1:16" ht="17" customHeight="1">
@@ -56711,13 +57105,13 @@
         <v>2628</v>
       </c>
       <c r="N561" s="46" t="s">
-        <v>16</v>
+        <v>2629</v>
       </c>
       <c r="O561" s="47" t="s">
-        <v>2629</v>
+        <v>16</v>
       </c>
       <c r="P561" s="62" t="s">
-        <v>3830</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="562" spans="1:16" ht="17" customHeight="1">
@@ -56762,13 +57156,13 @@
         <v>2631</v>
       </c>
       <c r="N562" s="46" t="s">
-        <v>16</v>
+        <v>2632</v>
       </c>
       <c r="O562" s="47" t="s">
-        <v>2632</v>
+        <v>16</v>
       </c>
       <c r="P562" s="62" t="s">
-        <v>3831</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="563" spans="1:16" ht="17" customHeight="1">
@@ -56813,13 +57207,13 @@
         <v>2634</v>
       </c>
       <c r="N563" s="46" t="s">
-        <v>16</v>
+        <v>2635</v>
       </c>
       <c r="O563" s="47" t="s">
-        <v>2635</v>
+        <v>16</v>
       </c>
       <c r="P563" s="62" t="s">
-        <v>3832</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="564" spans="1:16" ht="17" customHeight="1">
@@ -56864,13 +57258,13 @@
         <v>2637</v>
       </c>
       <c r="N564" s="46" t="s">
-        <v>16</v>
+        <v>3226</v>
       </c>
       <c r="O564" s="47" t="s">
-        <v>3226</v>
+        <v>16</v>
       </c>
       <c r="P564" s="62" t="s">
-        <v>3833</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="565" spans="1:16" ht="17" customHeight="1">
@@ -56915,13 +57309,13 @@
         <v>2639</v>
       </c>
       <c r="N565" s="46" t="s">
-        <v>16</v>
+        <v>2640</v>
       </c>
       <c r="O565" s="47" t="s">
-        <v>2640</v>
+        <v>16</v>
       </c>
       <c r="P565" s="62" t="s">
-        <v>3834</v>
+        <v>3832</v>
       </c>
     </row>
     <row r="566" spans="1:16" ht="17" customHeight="1">
@@ -56966,13 +57360,13 @@
         <v>2642</v>
       </c>
       <c r="N566" s="46" t="s">
-        <v>16</v>
+        <v>2643</v>
       </c>
       <c r="O566" s="47" t="s">
-        <v>2643</v>
+        <v>16</v>
       </c>
       <c r="P566" s="62" t="s">
-        <v>3835</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="567" spans="1:16" ht="17" customHeight="1">
@@ -57017,13 +57411,13 @@
         <v>2645</v>
       </c>
       <c r="N567" s="46" t="s">
-        <v>16</v>
+        <v>2646</v>
       </c>
       <c r="O567" s="47" t="s">
-        <v>2646</v>
+        <v>16</v>
       </c>
       <c r="P567" s="62" t="s">
-        <v>3836</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="568" spans="1:16" ht="17" customHeight="1">
@@ -57068,13 +57462,13 @@
         <v>2648</v>
       </c>
       <c r="N568" s="46" t="s">
-        <v>16</v>
+        <v>3227</v>
       </c>
       <c r="O568" s="47" t="s">
-        <v>3227</v>
+        <v>16</v>
       </c>
       <c r="P568" s="62" t="s">
-        <v>3837</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="569" spans="1:16" ht="17" customHeight="1">
@@ -57119,13 +57513,13 @@
         <v>2650</v>
       </c>
       <c r="N569" s="46" t="s">
-        <v>16</v>
+        <v>3228</v>
       </c>
       <c r="O569" s="47" t="s">
-        <v>3228</v>
+        <v>16</v>
       </c>
       <c r="P569" s="62" t="s">
-        <v>3838</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="570" spans="1:16" ht="17" customHeight="1">
@@ -57170,13 +57564,13 @@
         <v>2652</v>
       </c>
       <c r="N570" s="46" t="s">
-        <v>16</v>
+        <v>2653</v>
       </c>
       <c r="O570" s="47" t="s">
-        <v>2653</v>
+        <v>16</v>
       </c>
       <c r="P570" s="62" t="s">
-        <v>3839</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="571" spans="1:16" ht="17" customHeight="1">
@@ -57227,7 +57621,7 @@
         <v>16</v>
       </c>
       <c r="P571" s="62" t="s">
-        <v>3840</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="572" spans="1:16" ht="17" customHeight="1">
@@ -57272,13 +57666,13 @@
         <v>2657</v>
       </c>
       <c r="N572" s="46" t="s">
-        <v>16</v>
+        <v>2658</v>
       </c>
       <c r="O572" s="47" t="s">
-        <v>2658</v>
+        <v>16</v>
       </c>
       <c r="P572" s="62" t="s">
-        <v>3841</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="573" spans="1:16" ht="17" customHeight="1">
@@ -57329,7 +57723,7 @@
         <v>16</v>
       </c>
       <c r="P573" s="62" t="s">
-        <v>3842</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="574" spans="1:16" ht="17" customHeight="1">
@@ -57374,13 +57768,13 @@
         <v>2662</v>
       </c>
       <c r="N574" s="46" t="s">
-        <v>16</v>
+        <v>3229</v>
       </c>
       <c r="O574" s="47" t="s">
-        <v>3229</v>
+        <v>16</v>
       </c>
       <c r="P574" s="62" t="s">
-        <v>3843</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="575" spans="1:16" ht="17" customHeight="1">
@@ -57425,13 +57819,13 @@
         <v>2664</v>
       </c>
       <c r="N575" s="46" t="s">
-        <v>16</v>
+        <v>3230</v>
       </c>
       <c r="O575" s="47" t="s">
-        <v>3230</v>
+        <v>16</v>
       </c>
       <c r="P575" s="62" t="s">
-        <v>3844</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="576" spans="1:16" ht="17" customHeight="1">
@@ -57476,13 +57870,13 @@
         <v>2666</v>
       </c>
       <c r="N576" s="46" t="s">
-        <v>16</v>
+        <v>2667</v>
       </c>
       <c r="O576" s="47" t="s">
-        <v>2667</v>
+        <v>16</v>
       </c>
       <c r="P576" s="62" t="s">
-        <v>3845</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="577" spans="1:16" ht="17" customHeight="1">
@@ -57533,7 +57927,7 @@
         <v>16</v>
       </c>
       <c r="P577" s="62" t="s">
-        <v>3846</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="578" spans="1:16" ht="17" customHeight="1">
@@ -57584,7 +57978,7 @@
         <v>16</v>
       </c>
       <c r="P578" s="62" t="s">
-        <v>3847</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="579" spans="1:16" ht="17" customHeight="1">
@@ -57635,7 +58029,7 @@
         <v>2676</v>
       </c>
       <c r="P579" s="62" t="s">
-        <v>3848</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="580" spans="1:16" ht="17" customHeight="1">
@@ -57680,13 +58074,13 @@
         <v>2675</v>
       </c>
       <c r="N580" s="46" t="s">
-        <v>16</v>
+        <v>2676</v>
       </c>
       <c r="O580" s="47" t="s">
-        <v>2676</v>
+        <v>16</v>
       </c>
       <c r="P580" s="62" t="s">
-        <v>3849</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="581" spans="1:16" ht="17" customHeight="1">
@@ -57737,7 +58131,7 @@
         <v>16</v>
       </c>
       <c r="P581" s="62" t="s">
-        <v>3850</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="582" spans="1:16" ht="17" customHeight="1">
@@ -57782,13 +58176,13 @@
         <v>2680</v>
       </c>
       <c r="N582" s="46" t="s">
-        <v>16</v>
+        <v>2681</v>
       </c>
       <c r="O582" s="47" t="s">
-        <v>2681</v>
+        <v>16</v>
       </c>
       <c r="P582" s="62" t="s">
-        <v>3851</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="583" spans="1:16" ht="17" customHeight="1">
@@ -57839,7 +58233,7 @@
         <v>16</v>
       </c>
       <c r="P583" s="62" t="s">
-        <v>3852</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="584" spans="1:16" ht="17" customHeight="1">
@@ -57884,13 +58278,13 @@
         <v>2685</v>
       </c>
       <c r="N584" s="46" t="s">
-        <v>16</v>
+        <v>2686</v>
       </c>
       <c r="O584" s="47" t="s">
-        <v>2686</v>
+        <v>16</v>
       </c>
       <c r="P584" s="62" t="s">
-        <v>3853</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="585" spans="1:16" ht="17" customHeight="1">
@@ -57941,7 +58335,7 @@
         <v>16</v>
       </c>
       <c r="P585" s="62" t="s">
-        <v>3854</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="586" spans="1:16" ht="17" customHeight="1">
@@ -58043,7 +58437,7 @@
         <v>16</v>
       </c>
       <c r="P587" s="62" t="s">
-        <v>3855</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="588" spans="1:16" ht="17" customHeight="1">
@@ -58139,13 +58533,13 @@
         <v>2696</v>
       </c>
       <c r="N589" s="46" t="s">
-        <v>16</v>
+        <v>2697</v>
       </c>
       <c r="O589" s="47" t="s">
-        <v>2697</v>
+        <v>16</v>
       </c>
       <c r="P589" s="62" t="s">
-        <v>3856</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="590" spans="1:16" ht="17" customHeight="1">
@@ -58190,13 +58584,13 @@
         <v>2699</v>
       </c>
       <c r="N590" s="46" t="s">
-        <v>16</v>
+        <v>2700</v>
       </c>
       <c r="O590" s="47" t="s">
-        <v>2700</v>
+        <v>16</v>
       </c>
       <c r="P590" s="62" t="s">
-        <v>3857</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="591" spans="1:16" ht="17" customHeight="1">
@@ -58241,13 +58635,13 @@
         <v>2702</v>
       </c>
       <c r="N591" s="46" t="s">
-        <v>16</v>
+        <v>2703</v>
       </c>
       <c r="O591" s="47" t="s">
-        <v>2703</v>
+        <v>16</v>
       </c>
       <c r="P591" s="62" t="s">
-        <v>3858</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="592" spans="1:16" ht="17" customHeight="1">
@@ -58292,13 +58686,13 @@
         <v>2705</v>
       </c>
       <c r="N592" s="46" t="s">
-        <v>16</v>
+        <v>3231</v>
       </c>
       <c r="O592" s="47" t="s">
-        <v>3231</v>
+        <v>16</v>
       </c>
       <c r="P592" s="62" t="s">
-        <v>3859</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="593" spans="1:16" ht="17" customHeight="1">
@@ -58349,7 +58743,7 @@
         <v>16</v>
       </c>
       <c r="P593" s="62" t="s">
-        <v>3860</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="594" spans="1:16" ht="17" customHeight="1">
@@ -58394,13 +58788,13 @@
         <v>2709</v>
       </c>
       <c r="N594" s="46" t="s">
-        <v>16</v>
+        <v>2710</v>
       </c>
       <c r="O594" s="47" t="s">
-        <v>2710</v>
+        <v>16</v>
       </c>
       <c r="P594" s="62" t="s">
-        <v>3861</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="595" spans="1:16" ht="17" customHeight="1">
@@ -58451,7 +58845,7 @@
         <v>16</v>
       </c>
       <c r="P595" s="62" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="596" spans="1:16" ht="17" customHeight="1">
@@ -58502,7 +58896,7 @@
         <v>16</v>
       </c>
       <c r="P596" s="62" t="s">
-        <v>3862</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="597" spans="1:16" ht="17" customHeight="1">
@@ -58553,7 +58947,7 @@
         <v>16</v>
       </c>
       <c r="P597" s="62" t="s">
-        <v>3863</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="598" spans="1:16" ht="17" customHeight="1">
@@ -58706,7 +59100,7 @@
         <v>16</v>
       </c>
       <c r="P600" s="62" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="601" spans="1:16" ht="17" customHeight="1">
@@ -58808,7 +59202,7 @@
         <v>16</v>
       </c>
       <c r="P602" s="62" t="s">
-        <v>3864</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="603" spans="1:16" ht="17" customHeight="1">
@@ -58859,7 +59253,7 @@
         <v>16</v>
       </c>
       <c r="P603" s="62" t="s">
-        <v>3865</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="604" spans="1:16" ht="17" customHeight="1">
@@ -58910,7 +59304,7 @@
         <v>16</v>
       </c>
       <c r="P604" s="62" t="s">
-        <v>3866</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="605" spans="1:16" ht="17" customHeight="1">
@@ -59012,7 +59406,7 @@
         <v>16</v>
       </c>
       <c r="P606" s="62" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="607" spans="1:16" ht="17" customHeight="1">
@@ -59114,7 +59508,7 @@
         <v>16</v>
       </c>
       <c r="P608" s="62" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="609" spans="1:16" ht="17" customHeight="1">
@@ -59165,7 +59559,7 @@
         <v>16</v>
       </c>
       <c r="P609" s="62" t="s">
-        <v>3957</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="610" spans="1:16" ht="17" customHeight="1">
@@ -59216,7 +59610,7 @@
         <v>16</v>
       </c>
       <c r="P610" s="62" t="s">
-        <v>3867</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="611" spans="1:16" ht="17" customHeight="1">
@@ -59267,7 +59661,7 @@
         <v>16</v>
       </c>
       <c r="P611" s="62" t="s">
-        <v>3868</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="612" spans="1:16" ht="17" customHeight="1">
@@ -59318,7 +59712,7 @@
         <v>16</v>
       </c>
       <c r="P612" s="62" t="s">
-        <v>3869</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="613" spans="1:16" ht="17" customHeight="1">
@@ -59369,7 +59763,7 @@
         <v>16</v>
       </c>
       <c r="P613" s="62" t="s">
-        <v>3870</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="614" spans="1:16" ht="17" customHeight="1">
@@ -59420,7 +59814,7 @@
         <v>16</v>
       </c>
       <c r="P614" s="62" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="615" spans="1:16" ht="17" customHeight="1">
@@ -59471,7 +59865,7 @@
         <v>16</v>
       </c>
       <c r="P615" s="62" t="s">
-        <v>3958</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="616" spans="1:16" ht="17" customHeight="1">
@@ -59522,7 +59916,7 @@
         <v>16</v>
       </c>
       <c r="P616" s="62" t="s">
-        <v>3871</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="617" spans="1:16" ht="17" customHeight="1">
@@ -59573,7 +59967,7 @@
         <v>16</v>
       </c>
       <c r="P617" s="62" t="s">
-        <v>3872</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="618" spans="1:16" ht="17" customHeight="1">
@@ -59675,7 +60069,7 @@
         <v>16</v>
       </c>
       <c r="P619" s="62" t="s">
-        <v>3873</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="620" spans="1:16" ht="17" customHeight="1">
@@ -59726,7 +60120,7 @@
         <v>16</v>
       </c>
       <c r="P620" s="62" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="621" spans="1:16" ht="17" customHeight="1">
@@ -59828,7 +60222,7 @@
         <v>16</v>
       </c>
       <c r="P622" s="62" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="623" spans="1:16" ht="17" customHeight="1">
@@ -59879,7 +60273,7 @@
         <v>16</v>
       </c>
       <c r="P623" s="62" t="s">
-        <v>3874</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="624" spans="1:16" ht="17" customHeight="1">
@@ -59930,7 +60324,7 @@
         <v>16</v>
       </c>
       <c r="P624" s="62" t="s">
-        <v>3875</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="625" spans="1:16" ht="17" customHeight="1">
@@ -59981,7 +60375,7 @@
         <v>16</v>
       </c>
       <c r="P625" s="62" t="s">
-        <v>3876</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="626" spans="1:16" ht="17" customHeight="1">
@@ -60032,7 +60426,7 @@
         <v>16</v>
       </c>
       <c r="P626" s="62" t="s">
-        <v>3877</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="627" spans="1:16" ht="17" customHeight="1">
@@ -60083,7 +60477,7 @@
         <v>16</v>
       </c>
       <c r="P627" s="62" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="628" spans="1:16" ht="17" customHeight="1">
@@ -60134,7 +60528,7 @@
         <v>16</v>
       </c>
       <c r="P628" s="62" t="s">
-        <v>3878</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="629" spans="1:16" ht="17" customHeight="1">
@@ -60185,7 +60579,7 @@
         <v>16</v>
       </c>
       <c r="P629" s="62" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="630" spans="1:16" ht="17" customHeight="1">
@@ -60236,7 +60630,7 @@
         <v>16</v>
       </c>
       <c r="P630" s="62" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="631" spans="1:16" ht="17" customHeight="1">
@@ -60338,7 +60732,7 @@
         <v>16</v>
       </c>
       <c r="P632" s="62" t="s">
-        <v>3879</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="633" spans="1:16" ht="17" customHeight="1">
@@ -60389,7 +60783,7 @@
         <v>16</v>
       </c>
       <c r="P633" s="62" t="s">
-        <v>3880</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="634" spans="1:16" ht="17" customHeight="1">
@@ -60440,7 +60834,7 @@
         <v>16</v>
       </c>
       <c r="P634" s="62" t="s">
-        <v>3881</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="635" spans="1:16" ht="17" customHeight="1">
@@ -60491,7 +60885,7 @@
         <v>16</v>
       </c>
       <c r="P635" s="62" t="s">
-        <v>3882</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="636" spans="1:16" ht="17" customHeight="1">
@@ -60542,7 +60936,7 @@
         <v>16</v>
       </c>
       <c r="P636" s="62" t="s">
-        <v>3883</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="637" spans="1:16" ht="17" customHeight="1">
@@ -60644,7 +61038,7 @@
         <v>16</v>
       </c>
       <c r="P638" s="62" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="639" spans="1:16" ht="17" customHeight="1">
@@ -60695,7 +61089,7 @@
         <v>16</v>
       </c>
       <c r="P639" s="62" t="s">
-        <v>3885</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="640" spans="1:16" ht="17" customHeight="1">
@@ -60746,7 +61140,7 @@
         <v>16</v>
       </c>
       <c r="P640" s="62" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="641" spans="1:16" ht="17" customHeight="1">
@@ -60791,13 +61185,13 @@
         <v>2804</v>
       </c>
       <c r="N641" s="46" t="s">
-        <v>16</v>
+        <v>3232</v>
       </c>
       <c r="O641" s="47" t="s">
-        <v>3232</v>
+        <v>16</v>
       </c>
       <c r="P641" s="62" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="642" spans="1:16" ht="17" customHeight="1">
@@ -60842,13 +61236,13 @@
         <v>2806</v>
       </c>
       <c r="N642" s="46" t="s">
-        <v>16</v>
+        <v>3233</v>
       </c>
       <c r="O642" s="47" t="s">
-        <v>3233</v>
+        <v>16</v>
       </c>
       <c r="P642" s="62" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="643" spans="1:16" ht="17" customHeight="1">
@@ -60893,10 +61287,10 @@
         <v>2808</v>
       </c>
       <c r="N643" s="46" t="s">
-        <v>16</v>
+        <v>3234</v>
       </c>
       <c r="O643" s="47" t="s">
-        <v>3234</v>
+        <v>16</v>
       </c>
       <c r="P643" s="62" t="s">
         <v>3381</v>
@@ -60950,7 +61344,7 @@
         <v>16</v>
       </c>
       <c r="P644" s="62" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="645" spans="1:16" ht="17" customHeight="1">
@@ -60995,13 +61389,13 @@
         <v>2812</v>
       </c>
       <c r="N645" s="46" t="s">
-        <v>16</v>
+        <v>2813</v>
       </c>
       <c r="O645" s="47" t="s">
-        <v>2813</v>
+        <v>16</v>
       </c>
       <c r="P645" s="62" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="646" spans="1:16" ht="17" customHeight="1">
@@ -61052,7 +61446,7 @@
         <v>16</v>
       </c>
       <c r="P646" s="62" t="s">
-        <v>3891</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="647" spans="1:16" ht="17" customHeight="1">
@@ -61103,7 +61497,7 @@
         <v>16</v>
       </c>
       <c r="P647" s="62" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="648" spans="1:16" ht="17" customHeight="1">
@@ -61148,13 +61542,13 @@
         <v>2819</v>
       </c>
       <c r="N648" s="46" t="s">
-        <v>16</v>
+        <v>2820</v>
       </c>
       <c r="O648" s="47" t="s">
-        <v>2820</v>
+        <v>16</v>
       </c>
       <c r="P648" s="62" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="649" spans="1:16" ht="17" customHeight="1">
@@ -61199,13 +61593,13 @@
         <v>2822</v>
       </c>
       <c r="N649" s="46" t="s">
-        <v>16</v>
+        <v>2823</v>
       </c>
       <c r="O649" s="47" t="s">
-        <v>2823</v>
+        <v>16</v>
       </c>
       <c r="P649" s="62" t="s">
-        <v>3894</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="650" spans="1:16" ht="17" customHeight="1">
@@ -61250,13 +61644,13 @@
         <v>2825</v>
       </c>
       <c r="N650" s="46" t="s">
-        <v>16</v>
+        <v>3235</v>
       </c>
       <c r="O650" s="47" t="s">
-        <v>3235</v>
+        <v>16</v>
       </c>
       <c r="P650" s="62" t="s">
-        <v>3895</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="651" spans="1:16" ht="17" customHeight="1">
@@ -61307,7 +61701,7 @@
         <v>16</v>
       </c>
       <c r="P651" s="62" t="s">
-        <v>3896</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="652" spans="1:16" ht="17" customHeight="1">
@@ -61352,13 +61746,13 @@
         <v>2829</v>
       </c>
       <c r="N652" s="46" t="s">
-        <v>16</v>
+        <v>2830</v>
       </c>
       <c r="O652" s="47" t="s">
-        <v>2830</v>
+        <v>16</v>
       </c>
       <c r="P652" s="62" t="s">
-        <v>3897</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="653" spans="1:16" ht="17" customHeight="1">
@@ -61403,13 +61797,13 @@
         <v>2832</v>
       </c>
       <c r="N653" s="46" t="s">
-        <v>16</v>
+        <v>2833</v>
       </c>
       <c r="O653" s="47" t="s">
-        <v>2833</v>
+        <v>16</v>
       </c>
       <c r="P653" s="62" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="654" spans="1:16" ht="17" customHeight="1">
@@ -61460,7 +61854,7 @@
         <v>16</v>
       </c>
       <c r="P654" s="62" t="s">
-        <v>3899</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="655" spans="1:16" ht="17" customHeight="1">
@@ -61505,13 +61899,13 @@
         <v>2837</v>
       </c>
       <c r="N655" s="46" t="s">
-        <v>16</v>
+        <v>2838</v>
       </c>
       <c r="O655" s="47" t="s">
-        <v>2838</v>
+        <v>16</v>
       </c>
       <c r="P655" s="62" t="s">
-        <v>3900</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="656" spans="1:16" ht="17" customHeight="1">
@@ -61556,13 +61950,13 @@
         <v>2840</v>
       </c>
       <c r="N656" s="46" t="s">
-        <v>16</v>
+        <v>2841</v>
       </c>
       <c r="O656" s="47" t="s">
-        <v>2841</v>
+        <v>16</v>
       </c>
       <c r="P656" s="62" t="s">
-        <v>3901</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="657" spans="1:16" ht="17" customHeight="1">
@@ -61607,13 +62001,13 @@
         <v>2843</v>
       </c>
       <c r="N657" s="46" t="s">
-        <v>16</v>
+        <v>2844</v>
       </c>
       <c r="O657" s="47" t="s">
-        <v>2844</v>
+        <v>16</v>
       </c>
       <c r="P657" s="62" t="s">
-        <v>3902</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="658" spans="1:16" ht="17" customHeight="1">
@@ -61658,13 +62052,13 @@
         <v>2846</v>
       </c>
       <c r="N658" s="46" t="s">
-        <v>16</v>
+        <v>2847</v>
       </c>
       <c r="O658" s="47" t="s">
-        <v>2847</v>
+        <v>16</v>
       </c>
       <c r="P658" s="62" t="s">
-        <v>3903</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="659" spans="1:16" ht="17" customHeight="1">
@@ -61715,7 +62109,7 @@
         <v>2851</v>
       </c>
       <c r="P659" s="62" t="s">
-        <v>3904</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="660" spans="1:16" ht="17" customHeight="1">
@@ -61760,13 +62154,13 @@
         <v>2853</v>
       </c>
       <c r="N660" s="46" t="s">
-        <v>16</v>
+        <v>2854</v>
       </c>
       <c r="O660" s="47" t="s">
-        <v>2854</v>
+        <v>16</v>
       </c>
       <c r="P660" s="62" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="661" spans="1:16" ht="17" customHeight="1">
@@ -61817,7 +62211,7 @@
         <v>16</v>
       </c>
       <c r="P661" s="62" t="s">
-        <v>3905</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="662" spans="1:16" ht="17" customHeight="1">
@@ -61862,13 +62256,13 @@
         <v>2858</v>
       </c>
       <c r="N662" s="46" t="s">
-        <v>16</v>
+        <v>2859</v>
       </c>
       <c r="O662" s="47" t="s">
-        <v>2859</v>
+        <v>16</v>
       </c>
       <c r="P662" s="62" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="663" spans="1:16" ht="17" customHeight="1">
@@ -61919,7 +62313,7 @@
         <v>16</v>
       </c>
       <c r="P663" s="62" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="664" spans="1:16" ht="17" customHeight="1">
@@ -61964,13 +62358,13 @@
         <v>2863</v>
       </c>
       <c r="N664" s="46" t="s">
-        <v>16</v>
+        <v>2864</v>
       </c>
       <c r="O664" s="47" t="s">
-        <v>2864</v>
+        <v>16</v>
       </c>
       <c r="P664" s="62" t="s">
-        <v>3908</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="665" spans="1:16" ht="17" customHeight="1">
@@ -62021,7 +62415,7 @@
         <v>16</v>
       </c>
       <c r="P665" s="62" t="s">
-        <v>3909</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="666" spans="1:16" ht="17" customHeight="1">
@@ -62072,7 +62466,7 @@
         <v>16</v>
       </c>
       <c r="P666" s="62" t="s">
-        <v>3910</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="667" spans="1:16" ht="17" customHeight="1">
@@ -62117,13 +62511,13 @@
         <v>2870</v>
       </c>
       <c r="N667" s="46" t="s">
-        <v>16</v>
+        <v>2871</v>
       </c>
       <c r="O667" s="47" t="s">
-        <v>2871</v>
+        <v>16</v>
       </c>
       <c r="P667" s="62" t="s">
-        <v>3911</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="668" spans="1:16" ht="17" customHeight="1">
@@ -62174,7 +62568,7 @@
         <v>16</v>
       </c>
       <c r="P668" s="62" t="s">
-        <v>3912</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="669" spans="1:16" ht="17" customHeight="1">
@@ -62219,13 +62613,13 @@
         <v>2875</v>
       </c>
       <c r="N669" s="46" t="s">
-        <v>16</v>
+        <v>2876</v>
       </c>
       <c r="O669" s="47" t="s">
-        <v>2876</v>
+        <v>16</v>
       </c>
       <c r="P669" s="62" t="s">
-        <v>3913</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="670" spans="1:16" ht="17" customHeight="1">
@@ -62327,7 +62721,7 @@
         <v>2882</v>
       </c>
       <c r="P671" s="62" t="s">
-        <v>3914</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="672" spans="1:16" ht="17" customHeight="1">
@@ -62372,10 +62766,10 @@
         <v>2884</v>
       </c>
       <c r="N672" s="46" t="s">
-        <v>16</v>
+        <v>2885</v>
       </c>
       <c r="O672" s="47" t="s">
-        <v>2885</v>
+        <v>16</v>
       </c>
       <c r="P672" s="62" t="s">
         <v>3383</v>
@@ -62429,7 +62823,7 @@
         <v>16</v>
       </c>
       <c r="P673" s="62" t="s">
-        <v>3915</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="674" spans="1:16" ht="17" customHeight="1">
@@ -62474,13 +62868,13 @@
         <v>2889</v>
       </c>
       <c r="N674" s="46" t="s">
-        <v>16</v>
+        <v>2890</v>
       </c>
       <c r="O674" s="47" t="s">
-        <v>2890</v>
+        <v>16</v>
       </c>
       <c r="P674" s="62" t="s">
-        <v>3916</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="675" spans="1:16" ht="17" customHeight="1">
@@ -62525,13 +62919,13 @@
         <v>2892</v>
       </c>
       <c r="N675" s="46" t="s">
-        <v>16</v>
+        <v>2893</v>
       </c>
       <c r="O675" s="47" t="s">
-        <v>2893</v>
+        <v>16</v>
       </c>
       <c r="P675" s="62" t="s">
-        <v>3917</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="676" spans="1:16" ht="17" customHeight="1">
@@ -62582,7 +62976,7 @@
         <v>16</v>
       </c>
       <c r="P676" s="62" t="s">
-        <v>3918</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="677" spans="1:16" ht="17" customHeight="1">
@@ -62633,7 +63027,7 @@
         <v>16</v>
       </c>
       <c r="P677" s="62" t="s">
-        <v>3919</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="678" spans="1:16" ht="17" customHeight="1">
@@ -62684,7 +63078,7 @@
         <v>16</v>
       </c>
       <c r="P678" s="62" t="s">
-        <v>3920</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="679" spans="1:16" ht="17" customHeight="1">
@@ -62729,13 +63123,13 @@
         <v>2901</v>
       </c>
       <c r="N679" s="46" t="s">
-        <v>16</v>
+        <v>2973</v>
       </c>
       <c r="O679" s="47" t="s">
-        <v>2973</v>
+        <v>16</v>
       </c>
       <c r="P679" s="62" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="680" spans="1:16" ht="17" customHeight="1">
@@ -62786,7 +63180,7 @@
         <v>16</v>
       </c>
       <c r="P680" s="62" t="s">
-        <v>3921</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="681" spans="1:16" ht="17" customHeight="1">
@@ -62831,13 +63225,13 @@
         <v>2905</v>
       </c>
       <c r="N681" s="46" t="s">
-        <v>16</v>
+        <v>2906</v>
       </c>
       <c r="O681" s="47" t="s">
-        <v>2906</v>
+        <v>16</v>
       </c>
       <c r="P681" s="62" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="682" spans="1:16" ht="17" customHeight="1">
@@ -62882,13 +63276,13 @@
         <v>2908</v>
       </c>
       <c r="N682" s="46" t="s">
-        <v>16</v>
+        <v>2909</v>
       </c>
       <c r="O682" s="47" t="s">
-        <v>2909</v>
+        <v>16</v>
       </c>
       <c r="P682" s="62" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="683" spans="1:16" ht="17" customHeight="1">
@@ -62933,13 +63327,13 @@
         <v>2911</v>
       </c>
       <c r="N683" s="46" t="s">
-        <v>16</v>
+        <v>2912</v>
       </c>
       <c r="O683" s="47" t="s">
-        <v>2912</v>
+        <v>16</v>
       </c>
       <c r="P683" s="62" t="s">
-        <v>3924</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="684" spans="1:16" ht="17" customHeight="1">
@@ -62984,13 +63378,13 @@
         <v>2914</v>
       </c>
       <c r="N684" s="46" t="s">
-        <v>16</v>
+        <v>2915</v>
       </c>
       <c r="O684" s="47" t="s">
-        <v>2915</v>
+        <v>16</v>
       </c>
       <c r="P684" s="62" t="s">
-        <v>3925</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="685" spans="1:16" ht="17" customHeight="1">
@@ -63035,13 +63429,13 @@
         <v>2917</v>
       </c>
       <c r="N685" s="46" t="s">
-        <v>16</v>
+        <v>2972</v>
       </c>
       <c r="O685" s="47" t="s">
-        <v>2972</v>
+        <v>16</v>
       </c>
       <c r="P685" s="62" t="s">
-        <v>3926</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="686" spans="1:16" ht="17" customHeight="1">
@@ -63143,7 +63537,7 @@
         <v>16</v>
       </c>
       <c r="P687" s="62" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="688" spans="1:16" ht="17" customHeight="1">
@@ -63188,10 +63582,10 @@
         <v>2923</v>
       </c>
       <c r="N688" s="46" t="s">
-        <v>16</v>
+        <v>2924</v>
       </c>
       <c r="O688" s="47" t="s">
-        <v>2924</v>
+        <v>16</v>
       </c>
       <c r="P688" s="62" t="s">
         <v>3385</v>
@@ -63239,13 +63633,13 @@
         <v>2926</v>
       </c>
       <c r="N689" s="46" t="s">
-        <v>16</v>
+        <v>2927</v>
       </c>
       <c r="O689" s="47" t="s">
-        <v>2927</v>
+        <v>16</v>
       </c>
       <c r="P689" s="62" t="s">
-        <v>3928</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="690" spans="1:16" ht="17" customHeight="1">
@@ -63290,13 +63684,13 @@
         <v>2929</v>
       </c>
       <c r="N690" s="46" t="s">
-        <v>16</v>
+        <v>2930</v>
       </c>
       <c r="O690" s="47" t="s">
-        <v>2930</v>
+        <v>16</v>
       </c>
       <c r="P690" s="62" t="s">
-        <v>3929</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="691" spans="1:16" ht="17" customHeight="1">
@@ -63347,7 +63741,7 @@
         <v>16</v>
       </c>
       <c r="P691" s="62" t="s">
-        <v>3930</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="692" spans="1:16" ht="17" customHeight="1">
@@ -63392,13 +63786,13 @@
         <v>2934</v>
       </c>
       <c r="N692" s="46" t="s">
-        <v>16</v>
+        <v>2971</v>
       </c>
       <c r="O692" s="47" t="s">
-        <v>2971</v>
+        <v>16</v>
       </c>
       <c r="P692" s="62" t="s">
-        <v>3931</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="693" spans="1:16" ht="17" customHeight="1">
@@ -63443,13 +63837,13 @@
         <v>2936</v>
       </c>
       <c r="N693" s="46" t="s">
-        <v>16</v>
+        <v>3236</v>
       </c>
       <c r="O693" s="47" t="s">
-        <v>3236</v>
+        <v>16</v>
       </c>
       <c r="P693" s="62" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="694" spans="1:16" ht="17" customHeight="1">
@@ -63500,7 +63894,7 @@
         <v>16</v>
       </c>
       <c r="P694" s="62" t="s">
-        <v>3933</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="695" spans="1:16" ht="17" customHeight="1">
@@ -63545,13 +63939,13 @@
         <v>2940</v>
       </c>
       <c r="N695" s="46" t="s">
-        <v>16</v>
+        <v>2970</v>
       </c>
       <c r="O695" s="47" t="s">
-        <v>2970</v>
+        <v>16</v>
       </c>
       <c r="P695" s="62" t="s">
-        <v>3934</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="696" spans="1:16" ht="17" customHeight="1">
@@ -63596,13 +63990,13 @@
         <v>2942</v>
       </c>
       <c r="N696" s="46" t="s">
-        <v>16</v>
+        <v>3237</v>
       </c>
       <c r="O696" s="47" t="s">
-        <v>3237</v>
+        <v>16</v>
       </c>
       <c r="P696" s="62" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="697" spans="1:16" ht="17" customHeight="1">
@@ -63647,13 +64041,13 @@
         <v>2944</v>
       </c>
       <c r="N697" s="46" t="s">
-        <v>16</v>
+        <v>3238</v>
       </c>
       <c r="O697" s="47" t="s">
-        <v>3238</v>
+        <v>16</v>
       </c>
       <c r="P697" s="62" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="698" spans="1:16" ht="17" customHeight="1">
@@ -63698,13 +64092,13 @@
         <v>2946</v>
       </c>
       <c r="N698" s="46" t="s">
-        <v>16</v>
+        <v>3239</v>
       </c>
       <c r="O698" s="47" t="s">
-        <v>3239</v>
+        <v>16</v>
       </c>
       <c r="P698" s="62" t="s">
-        <v>3937</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="699" spans="1:16" ht="17" customHeight="1">
@@ -63755,7 +64149,7 @@
         <v>16</v>
       </c>
       <c r="P699" s="62" t="s">
-        <v>3938</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="700" spans="1:16" ht="17" customHeight="1">
@@ -63806,7 +64200,7 @@
         <v>16</v>
       </c>
       <c r="P700" s="62" t="s">
-        <v>3939</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="701" spans="1:16" ht="17" customHeight="1">
@@ -63857,7 +64251,7 @@
         <v>16</v>
       </c>
       <c r="P701" s="62" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="702" spans="1:16" ht="17" customHeight="1">
@@ -63902,13 +64296,13 @@
         <v>2954</v>
       </c>
       <c r="N702" s="46" t="s">
-        <v>16</v>
+        <v>2955</v>
       </c>
       <c r="O702" s="47" t="s">
-        <v>2955</v>
+        <v>16</v>
       </c>
       <c r="P702" s="62" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="703" spans="1:16" ht="17" customHeight="1">
@@ -63953,13 +64347,13 @@
         <v>2957</v>
       </c>
       <c r="N703" s="48" t="s">
-        <v>16</v>
+        <v>3240</v>
       </c>
       <c r="O703" s="49" t="s">
-        <v>3240</v>
+        <v>16</v>
       </c>
       <c r="P703" s="62" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="704" spans="1:16" ht="17" customHeight="1">
@@ -64004,13 +64398,13 @@
         <v>2960</v>
       </c>
       <c r="N704" s="48" t="s">
-        <v>16</v>
+        <v>2961</v>
       </c>
       <c r="O704" s="47" t="s">
-        <v>2961</v>
+        <v>16</v>
       </c>
       <c r="P704" s="62" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="705" spans="1:16" ht="17" customHeight="1">
@@ -64055,13 +64449,13 @@
         <v>3248</v>
       </c>
       <c r="N705" s="46" t="s">
-        <v>16</v>
+        <v>3252</v>
       </c>
       <c r="O705" s="47" t="s">
-        <v>3252</v>
+        <v>16</v>
       </c>
       <c r="P705" s="62" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="706" spans="1:16" ht="17" customHeight="1">
@@ -64106,13 +64500,13 @@
         <v>3249</v>
       </c>
       <c r="N706" s="48" t="s">
-        <v>16</v>
+        <v>3253</v>
       </c>
       <c r="O706" s="49" t="s">
-        <v>3253</v>
+        <v>16</v>
       </c>
       <c r="P706" s="62" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
   </sheetData>
@@ -64121,7 +64515,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="O149" r:id="rId1" xr:uid="{497D5693-3A17-EF4B-A730-4BC33B488035}"/>
+    <hyperlink ref="O149" r:id="rId1" display="https://m.dcinside.com/board/theaterM/2844215" xr:uid="{497D5693-3A17-EF4B-A730-4BC33B488035}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AB989A-A211-E14A-A1B4-79AA2AB664EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A6D7F5-3E2D-8249-B07F-580CE8AB3224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -547,29 +547,832 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>아더: ㅅㅂ
-귀네비어: 이지수
-랜슬롯: 니엘
-모르간: 리사
-멜레아강: 김찬호
-멀린: 지혜근
-케이: 김지욱
-레이아: 정다영
-늑대: 이기흥
-사슴: 이영호
-가웨인: 이종찬
-앙상블: 
-주홍균 최민준 이재범 권기중 
-노해영 오홍학 임동섭 이승현 
-김정민 이보슬 남궁민희 황보주성 
-고샛별 우미나 홍윤영 김재희 임상희
-스윙: 
-전성혜 하웅환 이윤환</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아더</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ㅅㅂ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>귀네비어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이지수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>랜슬롯</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>니엘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>모르간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>리사</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>멜레아강</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김찬호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>멀린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지혜근</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레이아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정다영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>늑대</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이기흥</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>사슴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이영호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>가웨인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이종찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앙상블</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주홍균</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최민준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재범</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>권기중</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>노해영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>오홍학</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임동섭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이승현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김정민</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이보슬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>남궁민희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황보주성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>고샛별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>우미나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍윤영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김재희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임상희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스윙</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전성혜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>하웅환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이윤환</t>
         </r>
       </text>
     </comment>
@@ -5809,14 +6612,103 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>허초희: 정인지
-이달: 양승리
-허균: 최석진</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>허초희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정인지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이달</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>양승리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>허균</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최석진</t>
         </r>
       </text>
     </comment>
@@ -26670,9 +27562,6 @@
     <t>https://drive.google.com/file/d/1nPblUNlw3sbwpt8jMVoxo2IEsYk6XUV2/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1Hbq6yoAsx_00SbCUfF6CA-LjmXd55C16/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1ClAm8oqsLt0Uxx7SHwPKh9lZGiCgMNZ0/view?usp=drive_link</t>
   </si>
   <si>
@@ -27973,6 +28862,9 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1in-jpBTObeoed3dtukd0U15ANqafxHqT/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/171M7wm4y4W9JbfS__QtxCXrfrjxgHh_Q/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -28213,7 +29105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -28420,9 +29312,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -29681,7 +30570,7 @@
       <c r="O3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="70" t="s">
+      <c r="P3" s="62" t="s">
         <v>3257</v>
       </c>
       <c r="R3" s="62"/>
@@ -43402,7 +44291,7 @@
         <v>16</v>
       </c>
       <c r="P272" s="62" t="s">
-        <v>3527</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="17" customHeight="1">
@@ -43453,7 +44342,7 @@
         <v>16</v>
       </c>
       <c r="P273" s="62" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="274" spans="1:16" ht="17" customHeight="1">
@@ -43504,7 +44393,7 @@
         <v>16</v>
       </c>
       <c r="P274" s="62" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="275" spans="1:16" ht="17" customHeight="1">
@@ -43555,7 +44444,7 @@
         <v>16</v>
       </c>
       <c r="P275" s="62" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="17" customHeight="1">
@@ -43606,7 +44495,7 @@
         <v>16</v>
       </c>
       <c r="P276" s="62" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="277" spans="1:16" ht="17" customHeight="1">
@@ -43657,7 +44546,7 @@
         <v>16</v>
       </c>
       <c r="P277" s="62" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="278" spans="1:16" ht="17" customHeight="1">
@@ -43708,7 +44597,7 @@
         <v>16</v>
       </c>
       <c r="P278" s="62" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="279" spans="1:16" ht="17" customHeight="1">
@@ -43759,7 +44648,7 @@
         <v>16</v>
       </c>
       <c r="P279" s="62" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="17" customHeight="1">
@@ -43810,7 +44699,7 @@
         <v>16</v>
       </c>
       <c r="P280" s="62" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="17" customHeight="1">
@@ -43861,7 +44750,7 @@
         <v>16</v>
       </c>
       <c r="P281" s="62" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="17" customHeight="1">
@@ -43912,7 +44801,7 @@
         <v>1855</v>
       </c>
       <c r="P282" s="62" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="283" spans="1:16" ht="17" customHeight="1">
@@ -43963,7 +44852,7 @@
         <v>3145</v>
       </c>
       <c r="P283" s="62" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="284" spans="1:16" ht="17" customHeight="1">
@@ -44014,7 +44903,7 @@
         <v>16</v>
       </c>
       <c r="P284" s="62" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="17" customHeight="1">
@@ -44065,7 +44954,7 @@
         <v>1865</v>
       </c>
       <c r="P285" s="62" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="17" customHeight="1">
@@ -44116,7 +45005,7 @@
         <v>1869</v>
       </c>
       <c r="P286" s="62" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="287" spans="1:16" ht="17" customHeight="1">
@@ -44167,7 +45056,7 @@
         <v>16</v>
       </c>
       <c r="P287" s="62" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="288" spans="1:16" ht="17" customHeight="1">
@@ -44218,7 +45107,7 @@
         <v>16</v>
       </c>
       <c r="P288" s="62" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="289" spans="1:16" ht="17" customHeight="1">
@@ -44269,7 +45158,7 @@
         <v>16</v>
       </c>
       <c r="P289" s="62" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="290" spans="1:16" ht="17" customHeight="1">
@@ -44320,7 +45209,7 @@
         <v>1881</v>
       </c>
       <c r="P290" s="62" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="291" spans="1:16" ht="17" customHeight="1">
@@ -44371,7 +45260,7 @@
         <v>16</v>
       </c>
       <c r="P291" s="62" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="17" customHeight="1">
@@ -44422,7 +45311,7 @@
         <v>16</v>
       </c>
       <c r="P292" s="62" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="293" spans="1:16" ht="17" customHeight="1">
@@ -44473,7 +45362,7 @@
         <v>1890</v>
       </c>
       <c r="P293" s="62" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="294" spans="1:16" ht="17" customHeight="1">
@@ -44524,7 +45413,7 @@
         <v>16</v>
       </c>
       <c r="P294" s="62" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="295" spans="1:16" ht="17" customHeight="1">
@@ -44575,7 +45464,7 @@
         <v>16</v>
       </c>
       <c r="P295" s="62" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="296" spans="1:16" ht="17" customHeight="1">
@@ -44626,7 +45515,7 @@
         <v>16</v>
       </c>
       <c r="P296" s="62" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="297" spans="1:16" ht="17" customHeight="1">
@@ -44677,7 +45566,7 @@
         <v>16</v>
       </c>
       <c r="P297" s="62" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="298" spans="1:16" ht="17" customHeight="1">
@@ -44728,7 +45617,7 @@
         <v>16</v>
       </c>
       <c r="P298" s="62" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="17" customHeight="1">
@@ -44779,7 +45668,7 @@
         <v>3149</v>
       </c>
       <c r="P299" s="62" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="300" spans="1:16" ht="17" customHeight="1">
@@ -44830,7 +45719,7 @@
         <v>16</v>
       </c>
       <c r="P300" s="62" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="301" spans="1:16" ht="17" customHeight="1">
@@ -44881,7 +45770,7 @@
         <v>16</v>
       </c>
       <c r="P301" s="62" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="302" spans="1:16" ht="17" customHeight="1">
@@ -44932,7 +45821,7 @@
         <v>16</v>
       </c>
       <c r="P302" s="62" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="303" spans="1:16" ht="17" customHeight="1">
@@ -44983,7 +45872,7 @@
         <v>16</v>
       </c>
       <c r="P303" s="62" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="17" customHeight="1">
@@ -45034,7 +45923,7 @@
         <v>16</v>
       </c>
       <c r="P304" s="62" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="305" spans="1:16" ht="17" customHeight="1">
@@ -45085,7 +45974,7 @@
         <v>16</v>
       </c>
       <c r="P305" s="62" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="17" customHeight="1">
@@ -45136,7 +46025,7 @@
         <v>16</v>
       </c>
       <c r="P306" s="62" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="307" spans="1:16" ht="17" customHeight="1">
@@ -45187,7 +46076,7 @@
         <v>16</v>
       </c>
       <c r="P307" s="62" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="17" customHeight="1">
@@ -45238,7 +46127,7 @@
         <v>16</v>
       </c>
       <c r="P308" s="62" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="17" customHeight="1">
@@ -45289,7 +46178,7 @@
         <v>16</v>
       </c>
       <c r="P309" s="62" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="17" customHeight="1">
@@ -45340,7 +46229,7 @@
         <v>16</v>
       </c>
       <c r="P310" s="62" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="311" spans="1:16" ht="17" customHeight="1">
@@ -45391,7 +46280,7 @@
         <v>16</v>
       </c>
       <c r="P311" s="62" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="312" spans="1:16" ht="17" customHeight="1">
@@ -45442,7 +46331,7 @@
         <v>16</v>
       </c>
       <c r="P312" s="62" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="313" spans="1:16" ht="17" customHeight="1">
@@ -45493,7 +46382,7 @@
         <v>16</v>
       </c>
       <c r="P313" s="62" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="314" spans="1:16" ht="17" customHeight="1">
@@ -45544,7 +46433,7 @@
         <v>16</v>
       </c>
       <c r="P314" s="62" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="315" spans="1:16" ht="17" customHeight="1">
@@ -45595,7 +46484,7 @@
         <v>16</v>
       </c>
       <c r="P315" s="62" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="316" spans="1:16" ht="17" customHeight="1">
@@ -45646,7 +46535,7 @@
         <v>16</v>
       </c>
       <c r="P316" s="62" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="317" spans="1:16" ht="17" customHeight="1">
@@ -45697,7 +46586,7 @@
         <v>16</v>
       </c>
       <c r="P317" s="62" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="318" spans="1:16" ht="17" customHeight="1">
@@ -45748,7 +46637,7 @@
         <v>16</v>
       </c>
       <c r="P318" s="62" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="319" spans="1:16" ht="17" customHeight="1">
@@ -45799,7 +46688,7 @@
         <v>1958</v>
       </c>
       <c r="P319" s="62" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="320" spans="1:16" ht="17" customHeight="1">
@@ -45850,7 +46739,7 @@
         <v>16</v>
       </c>
       <c r="P320" s="62" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="17" customHeight="1">
@@ -45901,7 +46790,7 @@
         <v>16</v>
       </c>
       <c r="P321" s="62" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="322" spans="1:16" ht="17" customHeight="1">
@@ -45952,7 +46841,7 @@
         <v>16</v>
       </c>
       <c r="P322" s="62" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="323" spans="1:16" ht="17" customHeight="1">
@@ -46003,7 +46892,7 @@
         <v>16</v>
       </c>
       <c r="P323" s="62" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="324" spans="1:16" ht="17" customHeight="1">
@@ -46054,7 +46943,7 @@
         <v>16</v>
       </c>
       <c r="P324" s="62" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="17" customHeight="1">
@@ -46105,7 +46994,7 @@
         <v>16</v>
       </c>
       <c r="P325" s="62" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="326" spans="1:16" ht="17" customHeight="1">
@@ -46156,7 +47045,7 @@
         <v>16</v>
       </c>
       <c r="P326" s="62" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="17" customHeight="1">
@@ -46207,7 +47096,7 @@
         <v>1980</v>
       </c>
       <c r="P327" s="62" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="328" spans="1:16" ht="17" customHeight="1">
@@ -46258,7 +47147,7 @@
         <v>16</v>
       </c>
       <c r="P328" s="62" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="17" customHeight="1">
@@ -46309,7 +47198,7 @@
         <v>16</v>
       </c>
       <c r="P329" s="62" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="330" spans="1:16" ht="17" customHeight="1">
@@ -46360,7 +47249,7 @@
         <v>1990</v>
       </c>
       <c r="P330" s="62" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="331" spans="1:16" ht="17" customHeight="1">
@@ -46411,7 +47300,7 @@
         <v>16</v>
       </c>
       <c r="P331" s="62" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="332" spans="1:16" ht="17" customHeight="1">
@@ -46462,7 +47351,7 @@
         <v>16</v>
       </c>
       <c r="P332" s="62" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="333" spans="1:16" ht="17" customHeight="1">
@@ -46513,7 +47402,7 @@
         <v>16</v>
       </c>
       <c r="P333" s="62" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="334" spans="1:16" ht="17" customHeight="1">
@@ -46564,7 +47453,7 @@
         <v>16</v>
       </c>
       <c r="P334" s="62" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="17" customHeight="1">
@@ -46615,7 +47504,7 @@
         <v>16</v>
       </c>
       <c r="P335" s="62" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="17" customHeight="1">
@@ -46666,7 +47555,7 @@
         <v>16</v>
       </c>
       <c r="P336" s="62" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="17" customHeight="1">
@@ -46717,7 +47606,7 @@
         <v>16</v>
       </c>
       <c r="P337" s="62" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="338" spans="1:16" ht="17" customHeight="1">
@@ -46768,7 +47657,7 @@
         <v>16</v>
       </c>
       <c r="P338" s="62" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="339" spans="1:16" ht="17" customHeight="1">
@@ -46819,7 +47708,7 @@
         <v>16</v>
       </c>
       <c r="P339" s="62" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="340" spans="1:16" ht="17" customHeight="1">
@@ -46870,7 +47759,7 @@
         <v>16</v>
       </c>
       <c r="P340" s="62" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="17" customHeight="1">
@@ -46921,7 +47810,7 @@
         <v>16</v>
       </c>
       <c r="P341" s="62" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="17" customHeight="1">
@@ -46972,7 +47861,7 @@
         <v>16</v>
       </c>
       <c r="P342" s="62" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="17" customHeight="1">
@@ -47023,7 +47912,7 @@
         <v>16</v>
       </c>
       <c r="P343" s="62" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="344" spans="1:16" ht="17" customHeight="1">
@@ -47074,7 +47963,7 @@
         <v>16</v>
       </c>
       <c r="P344" s="62" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="17" customHeight="1">
@@ -47125,7 +48014,7 @@
         <v>16</v>
       </c>
       <c r="P345" s="62" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="17" customHeight="1">
@@ -47176,7 +48065,7 @@
         <v>16</v>
       </c>
       <c r="P346" s="62" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="17" customHeight="1">
@@ -47227,7 +48116,7 @@
         <v>16</v>
       </c>
       <c r="P347" s="62" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="17" customHeight="1">
@@ -47278,7 +48167,7 @@
         <v>16</v>
       </c>
       <c r="P348" s="62" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="349" spans="1:16" ht="17" customHeight="1">
@@ -47329,7 +48218,7 @@
         <v>2036</v>
       </c>
       <c r="P349" s="62" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="350" spans="1:16" ht="17" customHeight="1">
@@ -47380,7 +48269,7 @@
         <v>16</v>
       </c>
       <c r="P350" s="62" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="351" spans="1:16" ht="17" customHeight="1">
@@ -47431,7 +48320,7 @@
         <v>16</v>
       </c>
       <c r="P351" s="62" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="17" customHeight="1">
@@ -47482,7 +48371,7 @@
         <v>16</v>
       </c>
       <c r="P352" s="62" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="17" customHeight="1">
@@ -47533,7 +48422,7 @@
         <v>16</v>
       </c>
       <c r="P353" s="62" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="354" spans="1:16" ht="17" customHeight="1">
@@ -47584,7 +48473,7 @@
         <v>16</v>
       </c>
       <c r="P354" s="62" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="17" customHeight="1">
@@ -47635,7 +48524,7 @@
         <v>16</v>
       </c>
       <c r="P355" s="62" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="17" customHeight="1">
@@ -47686,7 +48575,7 @@
         <v>16</v>
       </c>
       <c r="P356" s="62" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="17" customHeight="1">
@@ -47737,7 +48626,7 @@
         <v>16</v>
       </c>
       <c r="P357" s="62" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="358" spans="1:16" ht="17" customHeight="1">
@@ -47788,7 +48677,7 @@
         <v>16</v>
       </c>
       <c r="P358" s="62" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="359" spans="1:16" ht="17" customHeight="1">
@@ -47839,7 +48728,7 @@
         <v>16</v>
       </c>
       <c r="P359" s="62" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="17" customHeight="1">
@@ -47890,7 +48779,7 @@
         <v>16</v>
       </c>
       <c r="P360" s="62" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="17" customHeight="1">
@@ -47941,7 +48830,7 @@
         <v>16</v>
       </c>
       <c r="P361" s="62" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="17" customHeight="1">
@@ -47992,7 +48881,7 @@
         <v>16</v>
       </c>
       <c r="P362" s="62" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="17" customHeight="1">
@@ -48043,7 +48932,7 @@
         <v>16</v>
       </c>
       <c r="P363" s="62" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="17" customHeight="1">
@@ -48094,7 +48983,7 @@
         <v>16</v>
       </c>
       <c r="P364" s="62" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="365" spans="1:16" ht="17" customHeight="1">
@@ -48145,7 +49034,7 @@
         <v>16</v>
       </c>
       <c r="P365" s="62" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="366" spans="1:16" ht="17" customHeight="1">
@@ -48196,7 +49085,7 @@
         <v>16</v>
       </c>
       <c r="P366" s="62" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="367" spans="1:16" ht="17" customHeight="1">
@@ -48247,7 +49136,7 @@
         <v>16</v>
       </c>
       <c r="P367" s="62" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="368" spans="1:16" ht="17" customHeight="1">
@@ -48298,7 +49187,7 @@
         <v>16</v>
       </c>
       <c r="P368" s="62" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="369" spans="1:16" ht="17" customHeight="1">
@@ -48349,7 +49238,7 @@
         <v>16</v>
       </c>
       <c r="P369" s="62" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="17" customHeight="1">
@@ -48400,7 +49289,7 @@
         <v>16</v>
       </c>
       <c r="P370" s="62" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="371" spans="1:16" ht="17" customHeight="1">
@@ -48451,7 +49340,7 @@
         <v>16</v>
       </c>
       <c r="P371" s="62" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="372" spans="1:16" ht="17" customHeight="1">
@@ -48502,7 +49391,7 @@
         <v>16</v>
       </c>
       <c r="P372" s="62" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="17" customHeight="1">
@@ -48553,7 +49442,7 @@
         <v>16</v>
       </c>
       <c r="P373" s="62" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="374" spans="1:16" ht="17" customHeight="1">
@@ -48604,7 +49493,7 @@
         <v>16</v>
       </c>
       <c r="P374" s="62" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="375" spans="1:16" ht="17" customHeight="1">
@@ -48655,7 +49544,7 @@
         <v>16</v>
       </c>
       <c r="P375" s="62" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="17" customHeight="1">
@@ -48706,7 +49595,7 @@
         <v>16</v>
       </c>
       <c r="P376" s="62" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="377" spans="1:16" ht="17" customHeight="1">
@@ -48757,7 +49646,7 @@
         <v>16</v>
       </c>
       <c r="P377" s="62" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="17" customHeight="1">
@@ -48808,7 +49697,7 @@
         <v>3162</v>
       </c>
       <c r="P378" s="62" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="379" spans="1:16" ht="17" customHeight="1">
@@ -48859,7 +49748,7 @@
         <v>16</v>
       </c>
       <c r="P379" s="62" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="380" spans="1:16" ht="17" customHeight="1">
@@ -48910,7 +49799,7 @@
         <v>16</v>
       </c>
       <c r="P380" s="62" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="381" spans="1:16" ht="17" customHeight="1">
@@ -48961,7 +49850,7 @@
         <v>16</v>
       </c>
       <c r="P381" s="62" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="382" spans="1:16" ht="17" customHeight="1">
@@ -49012,7 +49901,7 @@
         <v>16</v>
       </c>
       <c r="P382" s="62" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="17" customHeight="1">
@@ -49063,7 +49952,7 @@
         <v>16</v>
       </c>
       <c r="P383" s="62" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="17" customHeight="1">
@@ -49114,7 +50003,7 @@
         <v>16</v>
       </c>
       <c r="P384" s="62" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="17" customHeight="1">
@@ -49165,7 +50054,7 @@
         <v>16</v>
       </c>
       <c r="P385" s="62" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="386" spans="1:16" ht="17" customHeight="1">
@@ -49216,7 +50105,7 @@
         <v>16</v>
       </c>
       <c r="P386" s="62" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="387" spans="1:16" ht="17" customHeight="1">
@@ -49267,7 +50156,7 @@
         <v>16</v>
       </c>
       <c r="P387" s="62" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="388" spans="1:16" ht="17" customHeight="1">
@@ -49318,7 +50207,7 @@
         <v>16</v>
       </c>
       <c r="P388" s="62" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="17" customHeight="1">
@@ -49369,7 +50258,7 @@
         <v>16</v>
       </c>
       <c r="P389" s="62" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="17" customHeight="1">
@@ -49420,7 +50309,7 @@
         <v>2146</v>
       </c>
       <c r="P390" s="62" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="391" spans="1:16" ht="17" customHeight="1">
@@ -49471,7 +50360,7 @@
         <v>3206</v>
       </c>
       <c r="P391" s="62" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="17" customHeight="1">
@@ -49522,7 +50411,7 @@
         <v>16</v>
       </c>
       <c r="P392" s="62" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="17" customHeight="1">
@@ -49573,7 +50462,7 @@
         <v>2154</v>
       </c>
       <c r="P393" s="62" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="394" spans="1:16" ht="17" customHeight="1">
@@ -49624,7 +50513,7 @@
         <v>16</v>
       </c>
       <c r="P394" s="62" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="395" spans="1:16" ht="17" customHeight="1">
@@ -49675,7 +50564,7 @@
         <v>16</v>
       </c>
       <c r="P395" s="62" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="396" spans="1:16" ht="17" customHeight="1">
@@ -49726,7 +50615,7 @@
         <v>16</v>
       </c>
       <c r="P396" s="62" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="17" customHeight="1">
@@ -49777,7 +50666,7 @@
         <v>16</v>
       </c>
       <c r="P397" s="62" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="398" spans="1:16" ht="17" customHeight="1">
@@ -49828,7 +50717,7 @@
         <v>16</v>
       </c>
       <c r="P398" s="62" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="399" spans="1:16" ht="17" customHeight="1">
@@ -49879,7 +50768,7 @@
         <v>16</v>
       </c>
       <c r="P399" s="62" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="17" customHeight="1">
@@ -49930,7 +50819,7 @@
         <v>16</v>
       </c>
       <c r="P400" s="62" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="17" customHeight="1">
@@ -49981,7 +50870,7 @@
         <v>2179</v>
       </c>
       <c r="P401" s="62" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="17" customHeight="1">
@@ -50032,7 +50921,7 @@
         <v>16</v>
       </c>
       <c r="P402" s="62" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="17" customHeight="1">
@@ -50083,7 +50972,7 @@
         <v>16</v>
       </c>
       <c r="P403" s="62" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="404" spans="1:16" ht="17" customHeight="1">
@@ -50134,7 +51023,7 @@
         <v>16</v>
       </c>
       <c r="P404" s="62" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="405" spans="1:16" ht="17" customHeight="1">
@@ -50185,7 +51074,7 @@
         <v>16</v>
       </c>
       <c r="P405" s="62" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="17" customHeight="1">
@@ -50236,7 +51125,7 @@
         <v>16</v>
       </c>
       <c r="P406" s="62" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="17" customHeight="1">
@@ -50287,7 +51176,7 @@
         <v>16</v>
       </c>
       <c r="P407" s="62" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="17" customHeight="1">
@@ -50338,7 +51227,7 @@
         <v>16</v>
       </c>
       <c r="P408" s="62" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="409" spans="1:16" ht="17" customHeight="1">
@@ -50389,7 +51278,7 @@
         <v>16</v>
       </c>
       <c r="P409" s="62" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="410" spans="1:16" ht="17" customHeight="1">
@@ -50440,7 +51329,7 @@
         <v>16</v>
       </c>
       <c r="P410" s="62" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="411" spans="1:16" ht="17" customHeight="1">
@@ -50491,7 +51380,7 @@
         <v>2210</v>
       </c>
       <c r="P411" s="62" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="412" spans="1:16" ht="17" customHeight="1">
@@ -50542,7 +51431,7 @@
         <v>16</v>
       </c>
       <c r="P412" s="62" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="413" spans="1:16" ht="17" customHeight="1">
@@ -50593,7 +51482,7 @@
         <v>16</v>
       </c>
       <c r="P413" s="62" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="414" spans="1:16" ht="17" customHeight="1">
@@ -50644,7 +51533,7 @@
         <v>2220</v>
       </c>
       <c r="P414" s="62" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="17" customHeight="1">
@@ -50695,7 +51584,7 @@
         <v>16</v>
       </c>
       <c r="P415" s="62" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="416" spans="1:16" ht="17" customHeight="1">
@@ -50746,7 +51635,7 @@
         <v>16</v>
       </c>
       <c r="P416" s="62" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="417" spans="1:16" ht="17" customHeight="1">
@@ -50797,7 +51686,7 @@
         <v>16</v>
       </c>
       <c r="P417" s="62" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="418" spans="1:16" ht="17" customHeight="1">
@@ -50848,7 +51737,7 @@
         <v>16</v>
       </c>
       <c r="P418" s="62" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="419" spans="1:16" ht="17" customHeight="1">
@@ -50899,7 +51788,7 @@
         <v>3208</v>
       </c>
       <c r="P419" s="62" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="420" spans="1:16" ht="17" customHeight="1">
@@ -50950,7 +51839,7 @@
         <v>16</v>
       </c>
       <c r="P420" s="62" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="421" spans="1:16" ht="17" customHeight="1">
@@ -51001,7 +51890,7 @@
         <v>16</v>
       </c>
       <c r="P421" s="62" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="17" customHeight="1">
@@ -51052,7 +51941,7 @@
         <v>16</v>
       </c>
       <c r="P422" s="62" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="423" spans="1:16" ht="17" customHeight="1">
@@ -51103,7 +51992,7 @@
         <v>16</v>
       </c>
       <c r="P423" s="62" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="424" spans="1:16" ht="17" customHeight="1">
@@ -51154,7 +52043,7 @@
         <v>3211</v>
       </c>
       <c r="P424" s="62" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="425" spans="1:16" ht="17" customHeight="1">
@@ -51205,7 +52094,7 @@
         <v>16</v>
       </c>
       <c r="P425" s="62" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
     </row>
     <row r="426" spans="1:16" ht="17" customHeight="1">
@@ -51256,7 +52145,7 @@
         <v>2250</v>
       </c>
       <c r="P426" s="62" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="427" spans="1:16" ht="17" customHeight="1">
@@ -51307,7 +52196,7 @@
         <v>16</v>
       </c>
       <c r="P427" s="62" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="428" spans="1:16" ht="17" customHeight="1">
@@ -51358,7 +52247,7 @@
         <v>16</v>
       </c>
       <c r="P428" s="62" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="429" spans="1:16" ht="17" customHeight="1">
@@ -51409,7 +52298,7 @@
         <v>16</v>
       </c>
       <c r="P429" s="62" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="430" spans="1:16" ht="17" customHeight="1">
@@ -51460,7 +52349,7 @@
         <v>16</v>
       </c>
       <c r="P430" s="62" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="431" spans="1:16" ht="17" customHeight="1">
@@ -51511,7 +52400,7 @@
         <v>16</v>
       </c>
       <c r="P431" s="62" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="432" spans="1:16" ht="17" customHeight="1">
@@ -51562,7 +52451,7 @@
         <v>16</v>
       </c>
       <c r="P432" s="62" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="17" customHeight="1">
@@ -51613,7 +52502,7 @@
         <v>16</v>
       </c>
       <c r="P433" s="62" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="434" spans="1:16" ht="17" customHeight="1">
@@ -51664,7 +52553,7 @@
         <v>16</v>
       </c>
       <c r="P434" s="62" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="435" spans="1:16" ht="17" customHeight="1">
@@ -51715,7 +52604,7 @@
         <v>16</v>
       </c>
       <c r="P435" s="62" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="17" customHeight="1">
@@ -51766,7 +52655,7 @@
         <v>16</v>
       </c>
       <c r="P436" s="62" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="17" customHeight="1">
@@ -51817,7 +52706,7 @@
         <v>16</v>
       </c>
       <c r="P437" s="62" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="438" spans="1:16" ht="17" customHeight="1">
@@ -51868,7 +52757,7 @@
         <v>16</v>
       </c>
       <c r="P438" s="62" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="17" customHeight="1">
@@ -51919,7 +52808,7 @@
         <v>16</v>
       </c>
       <c r="P439" s="62" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="440" spans="1:16" ht="17" customHeight="1">
@@ -51970,7 +52859,7 @@
         <v>16</v>
       </c>
       <c r="P440" s="62" t="s">
-        <v>3694</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="441" spans="1:16" ht="17" customHeight="1">
@@ -52021,7 +52910,7 @@
         <v>16</v>
       </c>
       <c r="P441" s="62" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="442" spans="1:16" ht="17" customHeight="1">
@@ -52072,7 +52961,7 @@
         <v>16</v>
       </c>
       <c r="P442" s="62" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="443" spans="1:16" ht="17" customHeight="1">
@@ -52123,7 +53012,7 @@
         <v>16</v>
       </c>
       <c r="P443" s="62" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="17" customHeight="1">
@@ -52174,7 +53063,7 @@
         <v>16</v>
       </c>
       <c r="P444" s="62" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="445" spans="1:16" ht="17" customHeight="1">
@@ -52225,7 +53114,7 @@
         <v>16</v>
       </c>
       <c r="P445" s="62" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="446" spans="1:16" ht="17" customHeight="1">
@@ -52276,7 +53165,7 @@
         <v>16</v>
       </c>
       <c r="P446" s="62" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="447" spans="1:16" ht="17" customHeight="1">
@@ -52327,7 +53216,7 @@
         <v>16</v>
       </c>
       <c r="P447" s="62" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="448" spans="1:16" ht="17" customHeight="1">
@@ -52378,7 +53267,7 @@
         <v>16</v>
       </c>
       <c r="P448" s="62" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="449" spans="1:16" ht="17" customHeight="1">
@@ -52429,7 +53318,7 @@
         <v>16</v>
       </c>
       <c r="P449" s="62" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
     </row>
     <row r="450" spans="1:16" ht="17" customHeight="1">
@@ -52480,7 +53369,7 @@
         <v>16</v>
       </c>
       <c r="P450" s="62" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="451" spans="1:16" ht="17" customHeight="1">
@@ -52531,7 +53420,7 @@
         <v>16</v>
       </c>
       <c r="P451" s="62" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="452" spans="1:16" ht="17" customHeight="1">
@@ -52582,7 +53471,7 @@
         <v>16</v>
       </c>
       <c r="P452" s="62" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="453" spans="1:16" ht="17" customHeight="1">
@@ -52633,7 +53522,7 @@
         <v>16</v>
       </c>
       <c r="P453" s="62" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="454" spans="1:16" ht="17" customHeight="1">
@@ -52684,7 +53573,7 @@
         <v>16</v>
       </c>
       <c r="P454" s="62" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="455" spans="1:16" ht="17" customHeight="1">
@@ -52735,7 +53624,7 @@
         <v>16</v>
       </c>
       <c r="P455" s="62" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="456" spans="1:16" ht="17" customHeight="1">
@@ -52786,7 +53675,7 @@
         <v>16</v>
       </c>
       <c r="P456" s="62" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="457" spans="1:16" ht="17" customHeight="1">
@@ -52837,7 +53726,7 @@
         <v>16</v>
       </c>
       <c r="P457" s="62" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="458" spans="1:16" ht="17" customHeight="1">
@@ -52888,7 +53777,7 @@
         <v>16</v>
       </c>
       <c r="P458" s="62" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
     </row>
     <row r="459" spans="1:16" ht="17" customHeight="1">
@@ -52939,7 +53828,7 @@
         <v>16</v>
       </c>
       <c r="P459" s="62" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="460" spans="1:16" ht="17" customHeight="1">
@@ -52990,7 +53879,7 @@
         <v>16</v>
       </c>
       <c r="P460" s="62" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="461" spans="1:16" ht="17" customHeight="1">
@@ -53041,7 +53930,7 @@
         <v>16</v>
       </c>
       <c r="P461" s="62" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="462" spans="1:16" ht="17" customHeight="1">
@@ -53092,7 +53981,7 @@
         <v>16</v>
       </c>
       <c r="P462" s="62" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
     </row>
     <row r="463" spans="1:16" ht="17" customHeight="1">
@@ -53143,7 +54032,7 @@
         <v>16</v>
       </c>
       <c r="P463" s="62" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="464" spans="1:16" ht="17" customHeight="1">
@@ -53194,7 +54083,7 @@
         <v>3222</v>
       </c>
       <c r="P464" s="62" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="465" spans="1:16" ht="17" customHeight="1">
@@ -53245,7 +54134,7 @@
         <v>16</v>
       </c>
       <c r="P465" s="62" t="s">
-        <v>3719</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="466" spans="1:16" ht="17" customHeight="1">
@@ -53296,7 +54185,7 @@
         <v>16</v>
       </c>
       <c r="P466" s="62" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="467" spans="1:16" ht="17" customHeight="1">
@@ -53347,7 +54236,7 @@
         <v>16</v>
       </c>
       <c r="P467" s="62" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="468" spans="1:16" ht="17" customHeight="1">
@@ -53398,7 +54287,7 @@
         <v>16</v>
       </c>
       <c r="P468" s="62" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="469" spans="1:16" ht="17" customHeight="1">
@@ -53449,7 +54338,7 @@
         <v>2364</v>
       </c>
       <c r="P469" s="62" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="470" spans="1:16" ht="17" customHeight="1">
@@ -53500,7 +54389,7 @@
         <v>16</v>
       </c>
       <c r="P470" s="62" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="471" spans="1:16" ht="17" customHeight="1">
@@ -53551,7 +54440,7 @@
         <v>16</v>
       </c>
       <c r="P471" s="62" t="s">
-        <v>3725</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="472" spans="1:16" ht="17" customHeight="1">
@@ -53602,7 +54491,7 @@
         <v>16</v>
       </c>
       <c r="P472" s="62" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="473" spans="1:16" ht="17" customHeight="1">
@@ -53653,7 +54542,7 @@
         <v>2377</v>
       </c>
       <c r="P473" s="62" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="474" spans="1:16" ht="17" customHeight="1">
@@ -53704,7 +54593,7 @@
         <v>16</v>
       </c>
       <c r="P474" s="62" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="475" spans="1:16" ht="17" customHeight="1">
@@ -53755,7 +54644,7 @@
         <v>16</v>
       </c>
       <c r="P475" s="62" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="476" spans="1:16" ht="17" customHeight="1">
@@ -53806,7 +54695,7 @@
         <v>16</v>
       </c>
       <c r="P476" s="62" t="s">
-        <v>3730</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="477" spans="1:16" ht="17" customHeight="1">
@@ -53857,7 +54746,7 @@
         <v>16</v>
       </c>
       <c r="P477" s="62" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="478" spans="1:16" ht="17" customHeight="1">
@@ -53908,7 +54797,7 @@
         <v>16</v>
       </c>
       <c r="P478" s="62" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="479" spans="1:16" ht="17" customHeight="1">
@@ -53959,7 +54848,7 @@
         <v>16</v>
       </c>
       <c r="P479" s="62" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="480" spans="1:16" ht="17" customHeight="1">
@@ -54010,7 +54899,7 @@
         <v>16</v>
       </c>
       <c r="P480" s="62" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="481" spans="1:16" ht="17" customHeight="1">
@@ -54061,7 +54950,7 @@
         <v>16</v>
       </c>
       <c r="P481" s="62" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
     </row>
     <row r="482" spans="1:16" ht="17" customHeight="1">
@@ -54112,7 +55001,7 @@
         <v>16</v>
       </c>
       <c r="P482" s="62" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="483" spans="1:16" ht="17" customHeight="1">
@@ -54163,7 +55052,7 @@
         <v>16</v>
       </c>
       <c r="P483" s="62" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="484" spans="1:16" ht="17" customHeight="1">
@@ -54214,7 +55103,7 @@
         <v>16</v>
       </c>
       <c r="P484" s="62" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="485" spans="1:16" ht="17" customHeight="1">
@@ -54265,7 +55154,7 @@
         <v>16</v>
       </c>
       <c r="P485" s="62" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="486" spans="1:16" ht="17" customHeight="1">
@@ -54316,7 +55205,7 @@
         <v>16</v>
       </c>
       <c r="P486" s="62" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="487" spans="1:16" ht="17" customHeight="1">
@@ -54367,7 +55256,7 @@
         <v>16</v>
       </c>
       <c r="P487" s="62" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="488" spans="1:16" ht="17" customHeight="1">
@@ -54418,7 +55307,7 @@
         <v>16</v>
       </c>
       <c r="P488" s="62" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="489" spans="1:16" ht="17" customHeight="1">
@@ -54469,7 +55358,7 @@
         <v>16</v>
       </c>
       <c r="P489" s="62" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="490" spans="1:16" ht="17" customHeight="1">
@@ -54520,7 +55409,7 @@
         <v>16</v>
       </c>
       <c r="P490" s="62" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="491" spans="1:16" ht="17" customHeight="1">
@@ -54571,7 +55460,7 @@
         <v>16</v>
       </c>
       <c r="P491" s="62" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="492" spans="1:16" ht="17" customHeight="1">
@@ -54622,7 +55511,7 @@
         <v>16</v>
       </c>
       <c r="P492" s="62" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="493" spans="1:16" ht="17" customHeight="1">
@@ -54673,7 +55562,7 @@
         <v>16</v>
       </c>
       <c r="P493" s="62" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="494" spans="1:16" ht="17" customHeight="1">
@@ -54724,7 +55613,7 @@
         <v>16</v>
       </c>
       <c r="P494" s="62" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="495" spans="1:16" ht="17" customHeight="1">
@@ -54775,7 +55664,7 @@
         <v>16</v>
       </c>
       <c r="P495" s="62" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="496" spans="1:16" ht="17" customHeight="1">
@@ -54826,7 +55715,7 @@
         <v>16</v>
       </c>
       <c r="P496" s="67" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="497" spans="1:16" ht="17" customHeight="1">
@@ -54877,7 +55766,7 @@
         <v>16</v>
       </c>
       <c r="P497" s="67" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="498" spans="1:16" ht="17" customHeight="1">
@@ -54928,7 +55817,7 @@
         <v>16</v>
       </c>
       <c r="P498" s="67" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="499" spans="1:16" ht="17" customHeight="1">
@@ -54979,7 +55868,7 @@
         <v>16</v>
       </c>
       <c r="P499" s="62" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="500" spans="1:16" ht="17" customHeight="1">
@@ -55030,7 +55919,7 @@
         <v>16</v>
       </c>
       <c r="P500" s="62" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="501" spans="1:16" ht="17" customHeight="1">
@@ -55081,7 +55970,7 @@
         <v>16</v>
       </c>
       <c r="P501" s="62" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="502" spans="1:16" ht="17" customHeight="1">
@@ -55132,7 +56021,7 @@
         <v>16</v>
       </c>
       <c r="P502" s="62" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="503" spans="1:16" ht="17" customHeight="1">
@@ -55183,7 +56072,7 @@
         <v>16</v>
       </c>
       <c r="P503" s="62" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="504" spans="1:16" ht="17" customHeight="1">
@@ -55234,7 +56123,7 @@
         <v>16</v>
       </c>
       <c r="P504" s="62" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="505" spans="1:16" ht="17" customHeight="1">
@@ -55285,7 +56174,7 @@
         <v>16</v>
       </c>
       <c r="P505" s="62" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="506" spans="1:16" ht="17" customHeight="1">
@@ -55336,7 +56225,7 @@
         <v>16</v>
       </c>
       <c r="P506" s="62" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="507" spans="1:16" ht="17" customHeight="1">
@@ -55387,7 +56276,7 @@
         <v>16</v>
       </c>
       <c r="P507" s="62" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="508" spans="1:16" ht="17" customHeight="1">
@@ -55438,7 +56327,7 @@
         <v>16</v>
       </c>
       <c r="P508" s="62" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="509" spans="1:16" ht="17" customHeight="1">
@@ -55489,7 +56378,7 @@
         <v>16</v>
       </c>
       <c r="P509" s="62" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="510" spans="1:16" ht="17" customHeight="1">
@@ -55540,7 +56429,7 @@
         <v>16</v>
       </c>
       <c r="P510" s="62" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="511" spans="1:16" ht="17" customHeight="1">
@@ -55591,7 +56480,7 @@
         <v>16</v>
       </c>
       <c r="P511" s="62" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="512" spans="1:16" ht="17" customHeight="1">
@@ -55642,7 +56531,7 @@
         <v>2488</v>
       </c>
       <c r="P512" s="62" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="513" spans="1:16" ht="17" customHeight="1">
@@ -55693,7 +56582,7 @@
         <v>16</v>
       </c>
       <c r="P513" s="62" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="514" spans="1:16" ht="17" customHeight="1">
@@ -55744,7 +56633,7 @@
         <v>16</v>
       </c>
       <c r="P514" s="62" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="515" spans="1:16" ht="17" customHeight="1">
@@ -55795,7 +56684,7 @@
         <v>16</v>
       </c>
       <c r="P515" s="62" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="516" spans="1:16" ht="17" customHeight="1">
@@ -55846,7 +56735,7 @@
         <v>16</v>
       </c>
       <c r="P516" s="62" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
     </row>
     <row r="517" spans="1:16" ht="17" customHeight="1">
@@ -55897,7 +56786,7 @@
         <v>16</v>
       </c>
       <c r="P517" s="62" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="518" spans="1:16" ht="17" customHeight="1">
@@ -55948,7 +56837,7 @@
         <v>16</v>
       </c>
       <c r="P518" s="62" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="519" spans="1:16" ht="17" customHeight="1">
@@ -55999,7 +56888,7 @@
         <v>16</v>
       </c>
       <c r="P519" s="62" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="520" spans="1:16" ht="17" customHeight="1">
@@ -56050,7 +56939,7 @@
         <v>16</v>
       </c>
       <c r="P520" s="62" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="521" spans="1:16" ht="17" customHeight="1">
@@ -56101,7 +56990,7 @@
         <v>16</v>
       </c>
       <c r="P521" s="62" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="522" spans="1:16" ht="17" customHeight="1">
@@ -56152,7 +57041,7 @@
         <v>16</v>
       </c>
       <c r="P522" s="62" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="523" spans="1:16" ht="17" customHeight="1">
@@ -56203,7 +57092,7 @@
         <v>16</v>
       </c>
       <c r="P523" s="62" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="524" spans="1:16" ht="17" customHeight="1">
@@ -56254,7 +57143,7 @@
         <v>16</v>
       </c>
       <c r="P524" s="62" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="525" spans="1:16" ht="17" customHeight="1">
@@ -56305,7 +57194,7 @@
         <v>16</v>
       </c>
       <c r="P525" s="62" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="526" spans="1:16" ht="17" customHeight="1">
@@ -56356,7 +57245,7 @@
         <v>16</v>
       </c>
       <c r="P526" s="62" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="527" spans="1:16" ht="17" customHeight="1">
@@ -56407,7 +57296,7 @@
         <v>16</v>
       </c>
       <c r="P527" s="62" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="528" spans="1:16" ht="17" customHeight="1">
@@ -56458,7 +57347,7 @@
         <v>16</v>
       </c>
       <c r="P528" s="62" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="529" spans="1:16" ht="17" customHeight="1">
@@ -56509,7 +57398,7 @@
         <v>16</v>
       </c>
       <c r="P529" s="62" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="530" spans="1:16" ht="17" customHeight="1">
@@ -56560,7 +57449,7 @@
         <v>16</v>
       </c>
       <c r="P530" s="62" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="531" spans="1:16" ht="17" customHeight="1">
@@ -56611,7 +57500,7 @@
         <v>16</v>
       </c>
       <c r="P531" s="62" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="532" spans="1:16" ht="17" customHeight="1">
@@ -56662,7 +57551,7 @@
         <v>16</v>
       </c>
       <c r="P532" s="62" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="533" spans="1:16" ht="17" customHeight="1">
@@ -56713,7 +57602,7 @@
         <v>16</v>
       </c>
       <c r="P533" s="62" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="534" spans="1:16" ht="17" customHeight="1">
@@ -56764,7 +57653,7 @@
         <v>16</v>
       </c>
       <c r="P534" s="62" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="535" spans="1:16" ht="17" customHeight="1">
@@ -56815,7 +57704,7 @@
         <v>16</v>
       </c>
       <c r="P535" s="62" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="536" spans="1:16" ht="17" customHeight="1">
@@ -56866,7 +57755,7 @@
         <v>16</v>
       </c>
       <c r="P536" s="62" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="537" spans="1:16" ht="17" customHeight="1">
@@ -56917,7 +57806,7 @@
         <v>16</v>
       </c>
       <c r="P537" s="62" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="538" spans="1:16" ht="17" customHeight="1">
@@ -56968,7 +57857,7 @@
         <v>16</v>
       </c>
       <c r="P538" s="62" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="539" spans="1:16" ht="17" customHeight="1">
@@ -57019,7 +57908,7 @@
         <v>16</v>
       </c>
       <c r="P539" s="62" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="540" spans="1:16" ht="17" customHeight="1">
@@ -57070,7 +57959,7 @@
         <v>16</v>
       </c>
       <c r="P540" s="62" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="541" spans="1:16" ht="17" customHeight="1">
@@ -57121,7 +58010,7 @@
         <v>16</v>
       </c>
       <c r="P541" s="62" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="542" spans="1:16" ht="17" customHeight="1">
@@ -57172,7 +58061,7 @@
         <v>16</v>
       </c>
       <c r="P542" s="62" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="543" spans="1:16" ht="17" customHeight="1">
@@ -57223,7 +58112,7 @@
         <v>16</v>
       </c>
       <c r="P543" s="62" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="544" spans="1:16" ht="17" customHeight="1">
@@ -57274,7 +58163,7 @@
         <v>16</v>
       </c>
       <c r="P544" s="62" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="545" spans="1:16" ht="17" customHeight="1">
@@ -57325,7 +58214,7 @@
         <v>16</v>
       </c>
       <c r="P545" s="62" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="546" spans="1:16" ht="17" customHeight="1">
@@ -57376,7 +58265,7 @@
         <v>16</v>
       </c>
       <c r="P546" s="62" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="547" spans="1:16" ht="17" customHeight="1">
@@ -57427,7 +58316,7 @@
         <v>16</v>
       </c>
       <c r="P547" s="62" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="548" spans="1:16" ht="17" customHeight="1">
@@ -57478,7 +58367,7 @@
         <v>16</v>
       </c>
       <c r="P548" s="62" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="549" spans="1:16" ht="17" customHeight="1">
@@ -57529,7 +58418,7 @@
         <v>16</v>
       </c>
       <c r="P549" s="62" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="550" spans="1:16" ht="17" customHeight="1">
@@ -57580,7 +58469,7 @@
         <v>16</v>
       </c>
       <c r="P550" s="62" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="551" spans="1:16" ht="17" customHeight="1">
@@ -57631,7 +58520,7 @@
         <v>16</v>
       </c>
       <c r="P551" s="62" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="552" spans="1:16" ht="17" customHeight="1">
@@ -57682,7 +58571,7 @@
         <v>16</v>
       </c>
       <c r="P552" s="62" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="553" spans="1:16" ht="17" customHeight="1">
@@ -57733,7 +58622,7 @@
         <v>16</v>
       </c>
       <c r="P553" s="62" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="554" spans="1:16" ht="17" customHeight="1">
@@ -57784,7 +58673,7 @@
         <v>16</v>
       </c>
       <c r="P554" s="62" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="555" spans="1:16" ht="17" customHeight="1">
@@ -57835,7 +58724,7 @@
         <v>16</v>
       </c>
       <c r="P555" s="62" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="556" spans="1:16" ht="17" customHeight="1">
@@ -57886,7 +58775,7 @@
         <v>16</v>
       </c>
       <c r="P556" s="62" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="557" spans="1:16" ht="17" customHeight="1">
@@ -57937,7 +58826,7 @@
         <v>16</v>
       </c>
       <c r="P557" s="62" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="558" spans="1:16" ht="17" customHeight="1">
@@ -57988,7 +58877,7 @@
         <v>16</v>
       </c>
       <c r="P558" s="62" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="559" spans="1:16" ht="17" customHeight="1">
@@ -58039,7 +58928,7 @@
         <v>16</v>
       </c>
       <c r="P559" s="62" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="560" spans="1:16" ht="17" customHeight="1">
@@ -58090,7 +58979,7 @@
         <v>16</v>
       </c>
       <c r="P560" s="62" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="561" spans="1:16" ht="17" customHeight="1">
@@ -58141,7 +59030,7 @@
         <v>16</v>
       </c>
       <c r="P561" s="62" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="562" spans="1:16" ht="17" customHeight="1">
@@ -58192,7 +59081,7 @@
         <v>16</v>
       </c>
       <c r="P562" s="62" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="563" spans="1:16" ht="17" customHeight="1">
@@ -58243,7 +59132,7 @@
         <v>16</v>
       </c>
       <c r="P563" s="62" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="564" spans="1:16" ht="17" customHeight="1">
@@ -58294,7 +59183,7 @@
         <v>16</v>
       </c>
       <c r="P564" s="62" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="565" spans="1:16" ht="17" customHeight="1">
@@ -58345,7 +59234,7 @@
         <v>16</v>
       </c>
       <c r="P565" s="62" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="566" spans="1:16" ht="17" customHeight="1">
@@ -58396,7 +59285,7 @@
         <v>16</v>
       </c>
       <c r="P566" s="62" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="567" spans="1:16" ht="17" customHeight="1">
@@ -58447,7 +59336,7 @@
         <v>16</v>
       </c>
       <c r="P567" s="62" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="568" spans="1:16" ht="17" customHeight="1">
@@ -58498,7 +59387,7 @@
         <v>16</v>
       </c>
       <c r="P568" s="62" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="569" spans="1:16" ht="17" customHeight="1">
@@ -58549,7 +59438,7 @@
         <v>16</v>
       </c>
       <c r="P569" s="62" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="570" spans="1:16" ht="17" customHeight="1">
@@ -58600,7 +59489,7 @@
         <v>16</v>
       </c>
       <c r="P570" s="62" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="571" spans="1:16" ht="17" customHeight="1">
@@ -58651,7 +59540,7 @@
         <v>16</v>
       </c>
       <c r="P571" s="62" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="572" spans="1:16" ht="17" customHeight="1">
@@ -58702,7 +59591,7 @@
         <v>16</v>
       </c>
       <c r="P572" s="62" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="573" spans="1:16" ht="17" customHeight="1">
@@ -58753,7 +59642,7 @@
         <v>16</v>
       </c>
       <c r="P573" s="62" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="574" spans="1:16" ht="17" customHeight="1">
@@ -58804,7 +59693,7 @@
         <v>16</v>
       </c>
       <c r="P574" s="62" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="575" spans="1:16" ht="17" customHeight="1">
@@ -58855,7 +59744,7 @@
         <v>16</v>
       </c>
       <c r="P575" s="62" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="576" spans="1:16" ht="17" customHeight="1">
@@ -58906,7 +59795,7 @@
         <v>16</v>
       </c>
       <c r="P576" s="62" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="577" spans="1:16" ht="17" customHeight="1">
@@ -58957,7 +59846,7 @@
         <v>16</v>
       </c>
       <c r="P577" s="62" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="578" spans="1:16" ht="17" customHeight="1">
@@ -59008,7 +59897,7 @@
         <v>16</v>
       </c>
       <c r="P578" s="62" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="579" spans="1:16" ht="17" customHeight="1">
@@ -59059,7 +59948,7 @@
         <v>2676</v>
       </c>
       <c r="P579" s="62" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
     </row>
     <row r="580" spans="1:16" ht="17" customHeight="1">
@@ -59110,7 +59999,7 @@
         <v>16</v>
       </c>
       <c r="P580" s="62" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="581" spans="1:16" ht="17" customHeight="1">
@@ -59161,7 +60050,7 @@
         <v>16</v>
       </c>
       <c r="P581" s="62" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="582" spans="1:16" ht="17" customHeight="1">
@@ -59212,7 +60101,7 @@
         <v>16</v>
       </c>
       <c r="P582" s="62" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="583" spans="1:16" ht="17" customHeight="1">
@@ -59263,7 +60152,7 @@
         <v>16</v>
       </c>
       <c r="P583" s="62" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="584" spans="1:16" ht="17" customHeight="1">
@@ -59314,7 +60203,7 @@
         <v>16</v>
       </c>
       <c r="P584" s="62" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="585" spans="1:16" ht="17" customHeight="1">
@@ -59365,7 +60254,7 @@
         <v>16</v>
       </c>
       <c r="P585" s="62" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="586" spans="1:16" ht="17" customHeight="1">
@@ -59416,7 +60305,7 @@
         <v>16</v>
       </c>
       <c r="P586" s="62" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="587" spans="1:16" ht="17" customHeight="1">
@@ -59467,7 +60356,7 @@
         <v>16</v>
       </c>
       <c r="P587" s="62" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="588" spans="1:16" ht="17" customHeight="1">
@@ -59518,7 +60407,7 @@
         <v>16</v>
       </c>
       <c r="P588" s="62" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="589" spans="1:16" ht="17" customHeight="1">
@@ -59569,7 +60458,7 @@
         <v>16</v>
       </c>
       <c r="P589" s="62" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="590" spans="1:16" ht="17" customHeight="1">
@@ -59620,7 +60509,7 @@
         <v>16</v>
       </c>
       <c r="P590" s="62" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="591" spans="1:16" ht="17" customHeight="1">
@@ -59671,7 +60560,7 @@
         <v>16</v>
       </c>
       <c r="P591" s="62" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="592" spans="1:16" ht="17" customHeight="1">
@@ -59722,7 +60611,7 @@
         <v>16</v>
       </c>
       <c r="P592" s="62" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="593" spans="1:16" ht="17" customHeight="1">
@@ -59773,7 +60662,7 @@
         <v>16</v>
       </c>
       <c r="P593" s="62" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="594" spans="1:16" ht="17" customHeight="1">
@@ -59824,7 +60713,7 @@
         <v>16</v>
       </c>
       <c r="P594" s="62" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="595" spans="1:16" ht="17" customHeight="1">
@@ -59875,7 +60764,7 @@
         <v>16</v>
       </c>
       <c r="P595" s="62" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="596" spans="1:16" ht="17" customHeight="1">
@@ -59926,7 +60815,7 @@
         <v>16</v>
       </c>
       <c r="P596" s="62" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="597" spans="1:16" ht="17" customHeight="1">
@@ -59977,7 +60866,7 @@
         <v>16</v>
       </c>
       <c r="P597" s="62" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="598" spans="1:16" ht="17" customHeight="1">
@@ -60028,7 +60917,7 @@
         <v>16</v>
       </c>
       <c r="P598" s="62" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="599" spans="1:16" ht="17" customHeight="1">
@@ -60079,7 +60968,7 @@
         <v>16</v>
       </c>
       <c r="P599" s="62" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="600" spans="1:16" ht="17" customHeight="1">
@@ -60130,7 +61019,7 @@
         <v>16</v>
       </c>
       <c r="P600" s="62" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="601" spans="1:16" ht="17" customHeight="1">
@@ -60181,7 +61070,7 @@
         <v>16</v>
       </c>
       <c r="P601" s="62" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="602" spans="1:16" ht="17" customHeight="1">
@@ -60232,7 +61121,7 @@
         <v>16</v>
       </c>
       <c r="P602" s="62" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="603" spans="1:16" ht="17" customHeight="1">
@@ -60283,7 +61172,7 @@
         <v>16</v>
       </c>
       <c r="P603" s="62" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="604" spans="1:16" ht="17" customHeight="1">
@@ -60334,7 +61223,7 @@
         <v>16</v>
       </c>
       <c r="P604" s="62" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="605" spans="1:16" ht="17" customHeight="1">
@@ -60385,7 +61274,7 @@
         <v>16</v>
       </c>
       <c r="P605" s="62" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="606" spans="1:16" ht="17" customHeight="1">
@@ -60436,7 +61325,7 @@
         <v>16</v>
       </c>
       <c r="P606" s="62" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="607" spans="1:16" ht="17" customHeight="1">
@@ -60487,7 +61376,7 @@
         <v>16</v>
       </c>
       <c r="P607" s="62" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="608" spans="1:16" ht="17" customHeight="1">
@@ -60538,7 +61427,7 @@
         <v>16</v>
       </c>
       <c r="P608" s="62" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="609" spans="1:16" ht="17" customHeight="1">
@@ -60589,7 +61478,7 @@
         <v>16</v>
       </c>
       <c r="P609" s="62" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="610" spans="1:16" ht="17" customHeight="1">
@@ -60640,7 +61529,7 @@
         <v>16</v>
       </c>
       <c r="P610" s="62" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="611" spans="1:16" ht="17" customHeight="1">
@@ -60691,7 +61580,7 @@
         <v>16</v>
       </c>
       <c r="P611" s="62" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="612" spans="1:16" ht="17" customHeight="1">
@@ -60742,7 +61631,7 @@
         <v>16</v>
       </c>
       <c r="P612" s="62" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="613" spans="1:16" ht="17" customHeight="1">
@@ -60793,7 +61682,7 @@
         <v>16</v>
       </c>
       <c r="P613" s="62" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="614" spans="1:16" ht="17" customHeight="1">
@@ -60844,7 +61733,7 @@
         <v>16</v>
       </c>
       <c r="P614" s="62" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="615" spans="1:16" ht="17" customHeight="1">
@@ -60895,7 +61784,7 @@
         <v>16</v>
       </c>
       <c r="P615" s="62" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="616" spans="1:16" ht="17" customHeight="1">
@@ -60946,7 +61835,7 @@
         <v>16</v>
       </c>
       <c r="P616" s="62" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="617" spans="1:16" ht="17" customHeight="1">
@@ -60997,7 +61886,7 @@
         <v>16</v>
       </c>
       <c r="P617" s="62" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="618" spans="1:16" ht="17" customHeight="1">
@@ -61048,7 +61937,7 @@
         <v>16</v>
       </c>
       <c r="P618" s="62" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="619" spans="1:16" ht="17" customHeight="1">
@@ -61099,7 +61988,7 @@
         <v>16</v>
       </c>
       <c r="P619" s="62" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="620" spans="1:16" ht="17" customHeight="1">
@@ -61150,7 +62039,7 @@
         <v>16</v>
       </c>
       <c r="P620" s="62" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="621" spans="1:16" ht="17" customHeight="1">
@@ -61201,7 +62090,7 @@
         <v>16</v>
       </c>
       <c r="P621" s="62" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="622" spans="1:16" ht="17" customHeight="1">
@@ -61252,7 +62141,7 @@
         <v>16</v>
       </c>
       <c r="P622" s="62" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="623" spans="1:16" ht="17" customHeight="1">
@@ -61303,7 +62192,7 @@
         <v>16</v>
       </c>
       <c r="P623" s="62" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="624" spans="1:16" ht="17" customHeight="1">
@@ -61354,7 +62243,7 @@
         <v>16</v>
       </c>
       <c r="P624" s="62" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="625" spans="1:16" ht="17" customHeight="1">
@@ -61405,7 +62294,7 @@
         <v>16</v>
       </c>
       <c r="P625" s="62" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="626" spans="1:16" ht="17" customHeight="1">
@@ -61456,7 +62345,7 @@
         <v>16</v>
       </c>
       <c r="P626" s="62" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="627" spans="1:16" ht="17" customHeight="1">
@@ -61507,7 +62396,7 @@
         <v>16</v>
       </c>
       <c r="P627" s="62" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="628" spans="1:16" ht="17" customHeight="1">
@@ -61558,7 +62447,7 @@
         <v>16</v>
       </c>
       <c r="P628" s="62" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="629" spans="1:16" ht="17" customHeight="1">
@@ -61609,7 +62498,7 @@
         <v>16</v>
       </c>
       <c r="P629" s="62" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="630" spans="1:16" ht="17" customHeight="1">
@@ -61660,7 +62549,7 @@
         <v>16</v>
       </c>
       <c r="P630" s="62" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="631" spans="1:16" ht="17" customHeight="1">
@@ -61711,7 +62600,7 @@
         <v>16</v>
       </c>
       <c r="P631" s="62" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="632" spans="1:16" ht="17" customHeight="1">
@@ -61762,7 +62651,7 @@
         <v>16</v>
       </c>
       <c r="P632" s="62" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="633" spans="1:16" ht="17" customHeight="1">
@@ -61813,7 +62702,7 @@
         <v>16</v>
       </c>
       <c r="P633" s="62" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="634" spans="1:16" ht="17" customHeight="1">
@@ -61864,7 +62753,7 @@
         <v>16</v>
       </c>
       <c r="P634" s="62" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="635" spans="1:16" ht="17" customHeight="1">
@@ -61915,7 +62804,7 @@
         <v>16</v>
       </c>
       <c r="P635" s="62" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="636" spans="1:16" ht="17" customHeight="1">
@@ -61966,7 +62855,7 @@
         <v>16</v>
       </c>
       <c r="P636" s="62" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="637" spans="1:16" ht="17" customHeight="1">
@@ -62017,7 +62906,7 @@
         <v>16</v>
       </c>
       <c r="P637" s="62" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="638" spans="1:16" ht="17" customHeight="1">
@@ -62068,7 +62957,7 @@
         <v>16</v>
       </c>
       <c r="P638" s="62" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="639" spans="1:16" ht="17" customHeight="1">
@@ -62083,7 +62972,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D639" s="22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E639" s="22" t="s">
         <v>28</v>
@@ -62119,7 +63008,7 @@
         <v>16</v>
       </c>
       <c r="P639" s="62" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="640" spans="1:16" ht="17" customHeight="1">
@@ -62170,7 +63059,7 @@
         <v>16</v>
       </c>
       <c r="P640" s="62" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="641" spans="1:16" ht="17" customHeight="1">
@@ -62221,7 +63110,7 @@
         <v>16</v>
       </c>
       <c r="P641" s="62" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="642" spans="1:16" ht="17" customHeight="1">
@@ -62272,7 +63161,7 @@
         <v>16</v>
       </c>
       <c r="P642" s="62" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="643" spans="1:16" ht="17" customHeight="1">
@@ -62323,7 +63212,7 @@
         <v>16</v>
       </c>
       <c r="P643" s="62" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="644" spans="1:16" ht="17" customHeight="1">
@@ -62374,7 +63263,7 @@
         <v>16</v>
       </c>
       <c r="P644" s="62" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="645" spans="1:16" ht="17" customHeight="1">
@@ -62425,7 +63314,7 @@
         <v>16</v>
       </c>
       <c r="P645" s="62" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="646" spans="1:16" ht="17" customHeight="1">
@@ -62476,7 +63365,7 @@
         <v>16</v>
       </c>
       <c r="P646" s="62" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="647" spans="1:16" ht="17" customHeight="1">
@@ -62527,7 +63416,7 @@
         <v>16</v>
       </c>
       <c r="P647" s="62" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="648" spans="1:16" ht="17" customHeight="1">
@@ -62578,7 +63467,7 @@
         <v>16</v>
       </c>
       <c r="P648" s="62" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="649" spans="1:16" ht="17" customHeight="1">
@@ -62629,7 +63518,7 @@
         <v>16</v>
       </c>
       <c r="P649" s="62" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="650" spans="1:16" ht="17" customHeight="1">
@@ -62680,7 +63569,7 @@
         <v>16</v>
       </c>
       <c r="P650" s="62" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="651" spans="1:16" ht="17" customHeight="1">
@@ -62731,7 +63620,7 @@
         <v>16</v>
       </c>
       <c r="P651" s="62" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="652" spans="1:16" ht="17" customHeight="1">
@@ -62782,7 +63671,7 @@
         <v>16</v>
       </c>
       <c r="P652" s="62" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="653" spans="1:16" ht="17" customHeight="1">
@@ -62833,7 +63722,7 @@
         <v>16</v>
       </c>
       <c r="P653" s="62" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="654" spans="1:16" ht="17" customHeight="1">
@@ -62884,7 +63773,7 @@
         <v>16</v>
       </c>
       <c r="P654" s="62" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="655" spans="1:16" ht="17" customHeight="1">
@@ -62935,7 +63824,7 @@
         <v>16</v>
       </c>
       <c r="P655" s="62" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="656" spans="1:16" ht="17" customHeight="1">
@@ -62986,7 +63875,7 @@
         <v>16</v>
       </c>
       <c r="P656" s="62" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="657" spans="1:16" ht="17" customHeight="1">
@@ -63037,7 +63926,7 @@
         <v>16</v>
       </c>
       <c r="P657" s="62" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="658" spans="1:16" ht="17" customHeight="1">
@@ -63088,7 +63977,7 @@
         <v>16</v>
       </c>
       <c r="P658" s="62" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="659" spans="1:16" ht="17" customHeight="1">
@@ -63139,7 +64028,7 @@
         <v>2851</v>
       </c>
       <c r="P659" s="62" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="660" spans="1:16" ht="17" customHeight="1">
@@ -63190,7 +64079,7 @@
         <v>16</v>
       </c>
       <c r="P660" s="62" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="661" spans="1:16" ht="17" customHeight="1">
@@ -63241,7 +64130,7 @@
         <v>16</v>
       </c>
       <c r="P661" s="62" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="662" spans="1:16" ht="17" customHeight="1">
@@ -63292,7 +64181,7 @@
         <v>16</v>
       </c>
       <c r="P662" s="62" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="663" spans="1:16" ht="17" customHeight="1">
@@ -63343,7 +64232,7 @@
         <v>16</v>
       </c>
       <c r="P663" s="62" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="664" spans="1:16" ht="17" customHeight="1">
@@ -63394,7 +64283,7 @@
         <v>16</v>
       </c>
       <c r="P664" s="62" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="665" spans="1:16" ht="17" customHeight="1">
@@ -63445,7 +64334,7 @@
         <v>16</v>
       </c>
       <c r="P665" s="62" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="666" spans="1:16" ht="17" customHeight="1">
@@ -63496,7 +64385,7 @@
         <v>16</v>
       </c>
       <c r="P666" s="62" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="667" spans="1:16" ht="17" customHeight="1">
@@ -63547,7 +64436,7 @@
         <v>16</v>
       </c>
       <c r="P667" s="62" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="668" spans="1:16" ht="17" customHeight="1">
@@ -63598,7 +64487,7 @@
         <v>16</v>
       </c>
       <c r="P668" s="62" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="669" spans="1:16" ht="17" customHeight="1">
@@ -63649,7 +64538,7 @@
         <v>16</v>
       </c>
       <c r="P669" s="62" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="670" spans="1:16" ht="17" customHeight="1">
@@ -63700,7 +64589,7 @@
         <v>16</v>
       </c>
       <c r="P670" s="62" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="671" spans="1:16" ht="17" customHeight="1">
@@ -63751,7 +64640,7 @@
         <v>2882</v>
       </c>
       <c r="P671" s="62" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="672" spans="1:16" ht="17" customHeight="1">
@@ -63802,7 +64691,7 @@
         <v>16</v>
       </c>
       <c r="P672" s="62" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="673" spans="1:16" ht="17" customHeight="1">
@@ -63853,7 +64742,7 @@
         <v>16</v>
       </c>
       <c r="P673" s="62" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="674" spans="1:16" ht="17" customHeight="1">
@@ -63904,7 +64793,7 @@
         <v>16</v>
       </c>
       <c r="P674" s="62" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="675" spans="1:16" ht="17" customHeight="1">
@@ -63955,7 +64844,7 @@
         <v>16</v>
       </c>
       <c r="P675" s="62" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="676" spans="1:16" ht="17" customHeight="1">
@@ -64006,7 +64895,7 @@
         <v>16</v>
       </c>
       <c r="P676" s="62" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="677" spans="1:16" ht="17" customHeight="1">
@@ -64057,7 +64946,7 @@
         <v>16</v>
       </c>
       <c r="P677" s="62" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="678" spans="1:16" ht="17" customHeight="1">
@@ -64108,7 +64997,7 @@
         <v>16</v>
       </c>
       <c r="P678" s="62" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="679" spans="1:16" ht="17" customHeight="1">
@@ -64159,7 +65048,7 @@
         <v>16</v>
       </c>
       <c r="P679" s="62" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="680" spans="1:16" ht="17" customHeight="1">
@@ -64210,7 +65099,7 @@
         <v>16</v>
       </c>
       <c r="P680" s="62" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="681" spans="1:16" ht="17" customHeight="1">
@@ -64261,7 +65150,7 @@
         <v>16</v>
       </c>
       <c r="P681" s="62" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="682" spans="1:16" ht="17" customHeight="1">
@@ -64312,7 +65201,7 @@
         <v>16</v>
       </c>
       <c r="P682" s="62" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="683" spans="1:16" ht="17" customHeight="1">
@@ -64363,7 +65252,7 @@
         <v>16</v>
       </c>
       <c r="P683" s="62" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="684" spans="1:16" ht="17" customHeight="1">
@@ -64414,7 +65303,7 @@
         <v>16</v>
       </c>
       <c r="P684" s="62" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="685" spans="1:16" ht="17" customHeight="1">
@@ -64465,7 +65354,7 @@
         <v>16</v>
       </c>
       <c r="P685" s="62" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="686" spans="1:16" ht="17" customHeight="1">
@@ -64516,7 +65405,7 @@
         <v>16</v>
       </c>
       <c r="P686" s="62" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="687" spans="1:16" ht="17" customHeight="1">
@@ -64567,7 +65456,7 @@
         <v>16</v>
       </c>
       <c r="P687" s="62" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="688" spans="1:16" ht="17" customHeight="1">
@@ -64618,7 +65507,7 @@
         <v>16</v>
       </c>
       <c r="P688" s="62" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="689" spans="1:16" ht="17" customHeight="1">
@@ -64669,7 +65558,7 @@
         <v>16</v>
       </c>
       <c r="P689" s="62" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="690" spans="1:16" ht="17" customHeight="1">
@@ -64720,7 +65609,7 @@
         <v>16</v>
       </c>
       <c r="P690" s="62" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="691" spans="1:16" ht="17" customHeight="1">
@@ -64771,7 +65660,7 @@
         <v>16</v>
       </c>
       <c r="P691" s="62" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="692" spans="1:16" ht="17" customHeight="1">
@@ -64822,7 +65711,7 @@
         <v>16</v>
       </c>
       <c r="P692" s="62" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="693" spans="1:16" ht="17" customHeight="1">
@@ -64873,7 +65762,7 @@
         <v>16</v>
       </c>
       <c r="P693" s="62" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="694" spans="1:16" ht="17" customHeight="1">
@@ -64924,7 +65813,7 @@
         <v>16</v>
       </c>
       <c r="P694" s="62" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="695" spans="1:16" ht="17" customHeight="1">
@@ -64975,7 +65864,7 @@
         <v>16</v>
       </c>
       <c r="P695" s="62" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="696" spans="1:16" ht="17" customHeight="1">
@@ -65026,7 +65915,7 @@
         <v>16</v>
       </c>
       <c r="P696" s="62" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="697" spans="1:16" ht="17" customHeight="1">
@@ -65077,7 +65966,7 @@
         <v>16</v>
       </c>
       <c r="P697" s="62" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="698" spans="1:16" ht="17" customHeight="1">
@@ -65128,7 +66017,7 @@
         <v>16</v>
       </c>
       <c r="P698" s="62" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="699" spans="1:16" ht="17" customHeight="1">
@@ -65179,7 +66068,7 @@
         <v>16</v>
       </c>
       <c r="P699" s="62" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="700" spans="1:16" ht="17" customHeight="1">
@@ -65230,7 +66119,7 @@
         <v>16</v>
       </c>
       <c r="P700" s="62" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="701" spans="1:16" ht="17" customHeight="1">
@@ -65281,7 +66170,7 @@
         <v>16</v>
       </c>
       <c r="P701" s="62" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="702" spans="1:16" ht="17" customHeight="1">
@@ -65332,7 +66221,7 @@
         <v>16</v>
       </c>
       <c r="P702" s="62" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="703" spans="1:16" ht="17" customHeight="1">
@@ -65383,7 +66272,7 @@
         <v>16</v>
       </c>
       <c r="P703" s="62" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="704" spans="1:16" ht="17" customHeight="1">
@@ -65434,7 +66323,7 @@
         <v>16</v>
       </c>
       <c r="P704" s="62" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="705" spans="1:16" ht="17" customHeight="1">
@@ -65485,7 +66374,7 @@
         <v>16</v>
       </c>
       <c r="P705" s="62" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="706" spans="1:16" ht="17" customHeight="1">
@@ -65536,7 +66425,7 @@
         <v>16</v>
       </c>
       <c r="P706" s="62" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27943853-867F-1545-89B5-8123BDA4A322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8239FF8-E36E-0D49-8EAC-EB2BCD1C3E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,10 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>System</author>
+    <author>Jie-Soo Lee</author>
   </authors>
   <commentList>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{A305B96A-5BAD-FD4A-A464-6E6B10814B64}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{F241879F-2CEA-D541-B33D-4CE3AA78DF2D}">
       <text>
         <r>
           <rPr>
@@ -78,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{AFF62DFF-848C-1148-8D07-A1C62C376FFD}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{D6B0BAA5-F3A5-5542-9D22-3BD36F2CD692}">
       <text>
         <r>
           <rPr>
@@ -106,37 +107,868 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{B37586D5-17C0-DB40-A5A7-17F15B09BA1F}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>지킬&amp;하이드: 홍광호
-루시: 윤공주
-엠마: 이정화
-댄버스 경: 김봉환
-어터슨: 김도형
-새비지/풀: 강상범
-비컨스필드/기네비어: 홍금단
-글로솝: 이창완
-주교: 이상훈
-스트라이드/스파이더: 이용진
-프룹스: 김이삭
-앙상블: 
-이재현 신재희 장은희 맹원태 
-이호진 김도현 김준희 남궁혜윤 
-허윤혜 김도하(김지훈) 이다경 정귀희
-스윙: 
-유환 권오현 윤나영</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{A5A86032-861B-184B-932B-E907666EEBBC}">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{F5F43810-9820-E142-B8E4-A4D18A1D3135}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지킬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>&amp;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>하이드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍광호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>윤공주</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>엠마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이정화</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>댄버스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>경</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김봉환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>어터슨</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김도형</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>새비지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>풀</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강상범</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>비컨스필드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>기네비어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍금단</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>글로솝</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이창완</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주교</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이상훈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스트라이드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스파이더</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이용진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>프룹스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김이삭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앙상블</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신재희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장은희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>맹원태</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이호진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김도현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>남궁혜윤</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>허윤혜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김도하</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지훈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이다경</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정귀희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스윙</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>유환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>권오현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>윤나영</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{679A1A29-C802-FC45-B663-CB1B4E773B32}">
       <text>
         <r>
           <rPr>
@@ -170,7 +1002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{51D025EE-7153-634B-86C0-5B123FA2524C}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{D6046E75-224C-D74E-8CA1-AA7830C8CBCB}">
       <text>
         <r>
           <rPr>
@@ -204,7 +1036,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{DEE9D90C-885B-3543-B180-B9737F4B292A}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{6429579C-6F02-FA4A-A904-83305B30EE23}">
       <text>
         <r>
           <rPr>
@@ -234,7 +1066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{4B143062-8CC3-454F-BF71-406D882A418C}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{F88A2CFD-7027-714A-9B9A-0D79174FC116}">
       <text>
         <r>
           <rPr>
@@ -264,841 +1096,38 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{190096CC-4C14-3246-B799-FF696CE01B99}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>아더</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ㅅㅂ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>귀네비어</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임정희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>랜슬롯</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>니엘</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>모르간</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>박혜나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>멜레아강</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이충주</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>멀린</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>지혜근</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>케이</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김지욱</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>레이아</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정다영</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>늑대</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이기흥</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>사슴</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이영호</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>가웨인</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이종찬</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>앙상블</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>주홍균</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최민준</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이재범</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>권기중</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>노해영</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>오홍학</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임동섭</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이승현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김정민</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이보슬</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>남궁민희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>황보주성</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>고샛별</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>우미나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>홍윤영</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김재희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임상희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스윙</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>전성혜</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>하웅환</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이윤환</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{3689D9F5-01B7-F642-BE6D-2D40B2E2DEB8}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{F112996B-AD6E-E047-AFCC-16B052C25307}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>아더: ㅅㅂ
+귀네비어: 임정희
+랜슬롯: 니엘
+모르간: 박혜나
+멜레아강: 이충주
+멀린: 지혜근
+케이: 김지욱
+레이아: 정다영
+늑대: 이기흥
+사슴: 이영호
+가웨인: 이종찬
+앙상블: 
+주홍균 최민준 이재범 권기중 
+노해영 오홍학 임동섭 이승현 
+김정민 이보슬 남궁민희 황보주성 
+고샛별 우미나 홍윤영 김재희 임상희
+스윙: 
+전성혜 하웅환 이윤환</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{60946D83-AF99-BC47-89A3-B815C936DFD9}">
       <text>
         <r>
           <rPr>
@@ -1129,7 +1158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{ACE3468F-7DF9-2140-A447-AF9BDC069CF8}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{1DB826E8-1C96-BC40-91BD-03E3962B1D96}">
       <text>
         <r>
           <rPr>
@@ -1160,7 +1189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{6B45B68D-E539-4B47-95A1-5F3EA99C7EEB}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{1CF0D8AB-C22A-8A4F-869E-C0467FC18C49}">
       <text>
         <r>
           <rPr>
@@ -1191,7 +1220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{AB1ECB8F-9BC8-C44E-BA01-A1445584156A}">
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{710890DC-AE3A-5F42-9D51-1EF9F68BC27B}">
       <text>
         <r>
           <rPr>
@@ -1221,7 +1250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{94652BBD-3362-E344-A803-7E3E9BB94D0F}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{AF863A0E-963C-1446-A964-750A165575B0}">
       <text>
         <r>
           <rPr>
@@ -1252,7 +1281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{592CE06A-CF28-A940-9947-B77B5B2C5441}">
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{6A2BC204-B745-8040-B088-9DA110ECC7EE}">
       <text>
         <r>
           <rPr>
@@ -1283,7 +1312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{2F6DD730-FEC8-9442-9C23-B3FE4D47E5FE}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{85305F9D-5786-EB45-A40C-CA8C31CEB6F2}">
       <text>
         <r>
           <rPr>
@@ -1314,7 +1343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{1CC9383B-ACA9-F349-9FAF-DF80F4701794}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{43EB95C4-DD81-974C-97EE-22C9B88293D7}">
       <text>
         <r>
           <rPr>
@@ -1345,7 +1374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{307C02B6-8F67-7748-B304-F6EEB479790A}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{2FFF2CB9-CC10-6C4C-B38A-B4E9420984A9}">
       <text>
         <r>
           <rPr>
@@ -1376,7 +1405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{F9DA2FDC-75DE-A24C-9400-CC6356D11FA8}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{853386D7-D3C4-234B-B1F5-510E90F8C740}">
       <text>
         <r>
           <rPr>
@@ -1407,43 +1436,43 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{740DA13A-08AD-5A4E-9A79-9F271A95A134}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>바슬라프 포미치 니진스키: 김찬호
-세르게이 파블로비치 디아길레프: 김종구
-이고르 표도로비치 스트라빈스키: 신재범
-로몰라 드 풀츠키 로몰라: 임소라
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00A46DBB-9AAF-364C-B1B3-165575704896}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>니진스키: 김찬호
+디아길레프: 김종구
+스트라빈스키: 신재범
+로몰라: 임소라
 한스 / 분신: 박수현</t>
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{F707494E-761C-3D4E-9E63-0BE559DD52DE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>바슬라프 포미치 니진스키: 김찬호
-세르게이 파블로비치 디아길레프: 김종구
-이고르 표도로비치 스트라빈스키: 임준혁
-로몰라 드 풀츠키 로몰라: 최미소
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{024AFD6A-FE69-E940-91B2-DA9F8A3D4B74}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>니진스키: 김찬호
+디아길레프: 김종구
+스트라빈스키: 임준혁
+로몰라: 최미소
 한스 / 분신: 백두산</t>
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{B411F056-5AD9-E348-86FA-06DEA8293941}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{E5E2013F-AF04-8B4B-A0C8-EC717BF36DE9}">
       <text>
         <r>
           <rPr>
@@ -1460,7 +1489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{C424C6E7-8617-D04C-A6A8-FDF5BF3F854A}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{D5CC1712-3806-9A4D-A480-B544E6CAC04D}">
       <text>
         <r>
           <rPr>
@@ -1477,7 +1506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{B82F62FC-360F-7543-8A36-9C33062721C2}">
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{C0EDC518-5CE9-7B4E-B6EE-6FFCB89AA9BF}">
       <text>
         <r>
           <rPr>
@@ -1493,7 +1522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{00B1B8B1-9CC2-7C49-97E9-58FB873560DD}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{AE21ABC5-2E5B-4442-8F6A-93AD8F9D5F06}">
       <text>
         <r>
           <rPr>
@@ -1517,25 +1546,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{6DD3AE58-60C2-1444-91CD-B768B3D68B36}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>바슬라프 포미치 니진스키: 김찬호
-세르게이 파블로비치 디아길레프: 조성윤
-이고르 표도로비치 스트라빈스키: 홍승안
-로몰라 드 풀츠키 로몰라: 임소라
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{EF58C723-FBE9-4549-9416-39FABE1C5D70}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>니진스키: 김찬호
+디아길레프: 조성윤
+스트라빈스키: 홍승안
+로몰라: 임소라
 한스 / 분신: 백두산</t>
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{96AE8598-0879-234E-B7C1-A279439C914F}">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{AA638651-B2F4-AF4C-B9A1-3A39BEBBC402}">
       <text>
         <r>
           <rPr>
@@ -1551,7 +1580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{EB3AEEB4-FD71-A840-AF75-EEDA3AC63A8E}">
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{01AE70F3-1186-0E44-B34F-4E6ED05A6F9A}">
       <text>
         <r>
           <rPr>
@@ -1580,7 +1609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{09106A55-6CB8-934E-B664-F6FD78570A8E}">
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{09D09F2D-14DF-414B-B69F-4B66CED0B6B6}">
       <text>
         <r>
           <rPr>
@@ -1596,7 +1625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{2D98C22E-4DDA-BD44-9FE3-B9EF71355B01}">
+    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{7E82B788-B12D-784F-AF25-B3D53056A86A}">
       <text>
         <r>
           <rPr>
@@ -1625,7 +1654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{F6863A2C-425B-7F4A-80DC-A82FFE63EF1E}">
+    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{9A3A6D99-A9FC-FE49-BE46-FB2E21986E08}">
       <text>
         <r>
           <rPr>
@@ -1654,7 +1683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{B476C9C4-9FB0-BF48-99DB-F152720B147D}">
+    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{EA55C0F2-6DF0-7740-9282-23869585F59A}">
       <text>
         <r>
           <rPr>
@@ -1678,7 +1707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{FEFA749B-D5C7-7747-81C6-DD2DDE9E3E5D}">
+    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{B5AAF0D3-6DCF-5B44-8A61-84E3B4DB1791}">
       <text>
         <r>
           <rPr>
@@ -1694,7 +1723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{F0E3F962-BA8A-9844-8E06-6B41F6F94DF7}">
+    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{E6FCB3C2-E368-5D4F-92BA-5568A9541F5F}">
       <text>
         <r>
           <rPr>
@@ -1723,7 +1752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{294124CF-DE42-E54D-A3DB-3961E2F3C18C}">
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{84F657B9-E031-B14F-BC7E-1B1808ADA6FD}">
       <text>
         <r>
           <rPr>
@@ -1740,7 +1769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{E6F8BE74-B08B-8345-9EBC-CD990CD32783}">
+    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{3B2F671C-EE0B-3D4F-8E0A-FF37747060A8}">
       <text>
         <r>
           <rPr>
@@ -1769,7 +1798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{8D1DBAF3-C589-2E4E-B8CE-67E0F15231E3}">
+    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{8EEBF8DC-832D-9C4D-B0AC-BC1D9D737C63}">
       <text>
         <r>
           <rPr>
@@ -1785,7 +1814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{C46CA7C9-A9B1-A743-8AB6-4EAC547B6814}">
+    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{CB503437-8718-284E-A7CA-E993DE56E5D0}">
       <text>
         <r>
           <rPr>
@@ -1811,7 +1840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{8D0594B8-65C6-A346-A290-693421A2EAC3}">
+    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{8335AF87-4D18-B141-A1AD-664AE765BFFF}">
       <text>
         <r>
           <rPr>
@@ -1827,7 +1856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I40" authorId="0" shapeId="0" xr:uid="{7E92B77C-F016-3745-8D14-A632EBA2E7ED}">
+    <comment ref="I40" authorId="0" shapeId="0" xr:uid="{774D8452-C118-1445-9C9B-F228D7B1398E}">
       <text>
         <r>
           <rPr>
@@ -1843,7 +1872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{E1F41FBA-D982-C64C-A2B5-076FC0D811A3}">
+    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{87DB4414-D027-EB43-8FBE-E70E2F24A248}">
       <text>
         <r>
           <rPr>
@@ -1860,7 +1889,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{7A05997A-20B2-924B-8167-9E5EDC025B1B}">
+    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{11906F85-85CD-CA49-A089-72A9A3112843}">
       <text>
         <r>
           <rPr>
@@ -1876,7 +1905,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{0D69BDA4-846F-D94F-82D0-9C51E76A6005}">
+    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{53642EC4-D884-0042-8D62-508558A1C790}">
       <text>
         <r>
           <rPr>
@@ -1892,7 +1921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I44" authorId="0" shapeId="0" xr:uid="{42B46701-D4C2-EC41-96BA-3EAA70C532C1}">
+    <comment ref="I44" authorId="0" shapeId="0" xr:uid="{E82C5067-42EB-CC41-9C60-93CA9C28B3E4}">
       <text>
         <r>
           <rPr>
@@ -1908,7 +1937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I45" authorId="0" shapeId="0" xr:uid="{F16B4AFC-5A6D-A34E-B2AE-E0DC4A4A0744}">
+    <comment ref="I45" authorId="0" shapeId="0" xr:uid="{FCBA8920-BAF3-6A45-8E79-C9A30C55E3A1}">
       <text>
         <r>
           <rPr>
@@ -1935,7 +1964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I46" authorId="0" shapeId="0" xr:uid="{A39D0787-5131-4D48-AC39-158E18666A48}">
+    <comment ref="I46" authorId="0" shapeId="0" xr:uid="{A5A089FF-D727-1E49-BCEA-5DE8896FF100}">
       <text>
         <r>
           <rPr>
@@ -1964,7 +1993,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{33881AE9-1AE5-604D-891E-654A6C66F8BC}">
+    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{BE53CE3D-119E-BD43-BB60-83FA223445A1}">
       <text>
         <r>
           <rPr>
@@ -1980,7 +2009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{DF12D914-774D-B24F-8A42-895351A0964F}">
+    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{AB039D0E-E07A-934F-A338-763E5898DF5B}">
       <text>
         <r>
           <rPr>
@@ -1996,7 +2025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{DF077E3F-F551-EA40-BE53-D6F173250849}">
+    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{FE013450-1C47-0843-8B66-92C2C14E5FFB}">
       <text>
         <r>
           <rPr>
@@ -2011,7 +2040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{8C41CBD8-A0BB-CD45-8FC4-A1E042F3B711}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{2063074F-0B3B-FC44-AFC9-59EED48C8F96}">
       <text>
         <r>
           <rPr>
@@ -2038,7 +2067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{DC22C661-3FD9-7A49-8943-727870BB6472}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{55954392-5C0D-2248-B496-D8C1F6C9F93C}">
       <text>
         <r>
           <rPr>
@@ -2054,7 +2083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{E3F9884E-3ECC-9547-87BC-6C64CEAC0E0C}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{43D76953-9312-8E4B-AA55-EBB5C24E09AA}">
       <text>
         <r>
           <rPr>
@@ -2070,7 +2099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{4D4F051A-0193-2748-9EDE-57328779B2F9}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{A49B2986-229F-EC40-95AD-F040EE5D9201}">
       <text>
         <r>
           <rPr>
@@ -2094,7 +2123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I54" authorId="0" shapeId="0" xr:uid="{E48FABCA-4CDC-6E48-A133-725E52237DAB}">
+    <comment ref="I54" authorId="0" shapeId="0" xr:uid="{7C5A286C-3D82-0B41-9C86-1FF54881CEF4}">
       <text>
         <r>
           <rPr>
@@ -2110,7 +2139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I55" authorId="0" shapeId="0" xr:uid="{D67E2F79-0670-0849-BFA2-3FFE2A717B5A}">
+    <comment ref="I55" authorId="0" shapeId="0" xr:uid="{161EFF59-16A6-F646-9564-34134EE1CAB4}">
       <text>
         <r>
           <rPr>
@@ -2126,7 +2155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{91EE8C7C-2D50-5545-BDD2-F5EBA87BA46E}">
+    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{87735BA0-D752-054D-B52D-16A1B360EE6C}">
       <text>
         <r>
           <rPr>
@@ -2151,7 +2180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I57" authorId="0" shapeId="0" xr:uid="{32C3A827-BEB8-D443-8E3C-A56A37386C05}">
+    <comment ref="I57" authorId="0" shapeId="0" xr:uid="{A01490E5-1413-EF45-8BB3-D7F6F745671D}">
       <text>
         <r>
           <rPr>
@@ -2176,7 +2205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{0E2391C7-35E4-2544-81AB-6A570858F8C3}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{1A4BAEA6-C93C-F64C-8EBC-FAD2D15D0296}">
       <text>
         <r>
           <rPr>
@@ -2196,7 +2225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{3A4B7751-99E9-594C-AB9A-6F956FF6AADB}">
+    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{CD93AECA-6586-C241-AC7D-6328006480E3}">
       <text>
         <r>
           <rPr>
@@ -2211,7 +2240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I60" authorId="0" shapeId="0" xr:uid="{72F27867-EE84-1148-9EC1-CC62C55EC762}">
+    <comment ref="I60" authorId="0" shapeId="0" xr:uid="{DD38654A-DE46-DF43-9858-A9EAFA8541F6}">
       <text>
         <r>
           <rPr>
@@ -2231,7 +2260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I61" authorId="0" shapeId="0" xr:uid="{5D0D319E-DF71-034E-B968-F3C32ECC3B33}">
+    <comment ref="I61" authorId="0" shapeId="0" xr:uid="{D3D8BC99-1A40-094B-8B1C-D6D743E13974}">
       <text>
         <r>
           <rPr>
@@ -2247,7 +2276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I62" authorId="0" shapeId="0" xr:uid="{3096B6DB-0D9A-3144-93AA-81A0880DBEEC}">
+    <comment ref="I62" authorId="0" shapeId="0" xr:uid="{944D6A2E-F73C-BE42-ABB5-DDE9449D1AB9}">
       <text>
         <r>
           <rPr>
@@ -2263,7 +2292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I63" authorId="0" shapeId="0" xr:uid="{9AA30CD2-3E2E-1346-BC48-C01888A52138}">
+    <comment ref="I63" authorId="0" shapeId="0" xr:uid="{26462BC6-F9E7-BC40-9FE1-E1A1BCBECAC7}">
       <text>
         <r>
           <rPr>
@@ -2278,7 +2307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I64" authorId="0" shapeId="0" xr:uid="{A8C86BEF-9346-2A4F-92B9-B8CDBF2DDA11}">
+    <comment ref="I64" authorId="0" shapeId="0" xr:uid="{D67D3806-C7B0-254B-B6A4-2D5F6FCE6D23}">
       <text>
         <r>
           <rPr>
@@ -2294,7 +2323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I65" authorId="0" shapeId="0" xr:uid="{2D57D80B-C5E8-3B47-9B51-AD8CFDC32FBA}">
+    <comment ref="I65" authorId="0" shapeId="0" xr:uid="{9126337A-6691-A64B-919A-A0283A86178F}">
       <text>
         <r>
           <rPr>
@@ -2323,7 +2352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I66" authorId="0" shapeId="0" xr:uid="{25756CBC-41B1-8C4D-997A-79CB210D96FD}">
+    <comment ref="I66" authorId="0" shapeId="0" xr:uid="{07780261-FBDA-464E-B735-7E2FEE0817B5}">
       <text>
         <r>
           <rPr>
@@ -2338,7 +2367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{88B76ADD-ADF3-E043-B15D-0D1964787545}">
+    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{039BC6E1-A0BC-4944-A20E-38ED08882DD7}">
       <text>
         <r>
           <rPr>
@@ -2358,7 +2387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{4C3F800C-B6B4-4641-B2BC-F94A7DA54344}">
+    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{01921435-8C22-7149-A61B-0F1307F51CA9}">
       <text>
         <r>
           <rPr>
@@ -2378,7 +2407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{743D6D63-CEBE-174E-8FA9-EE4BCC068D9E}">
+    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{D00419A2-8BE6-D948-BC05-BEF88A283BAC}">
       <text>
         <r>
           <rPr>
@@ -2398,7 +2427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I70" authorId="0" shapeId="0" xr:uid="{FB476FF9-703C-0748-AF91-57583A6FF956}">
+    <comment ref="I70" authorId="0" shapeId="0" xr:uid="{8C525EA1-FA2B-1A4E-BCB8-7E328A25C5D8}">
       <text>
         <r>
           <rPr>
@@ -2421,7 +2450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I71" authorId="0" shapeId="0" xr:uid="{0148CDF5-0D30-894D-B71D-B590ACDD5453}">
+    <comment ref="I71" authorId="0" shapeId="0" xr:uid="{30342D18-073C-8D47-81B1-8E6E13DD94D9}">
       <text>
         <r>
           <rPr>
@@ -2437,7 +2466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{AB89E7E0-A385-FA4F-99B5-D689BA79290D}">
+    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{CFE4033D-0A0D-3241-993C-87C30EFC93AA}">
       <text>
         <r>
           <rPr>
@@ -2466,7 +2495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I73" authorId="0" shapeId="0" xr:uid="{53857329-A141-CA4C-8D4A-41DF78E2ECEA}">
+    <comment ref="I73" authorId="0" shapeId="0" xr:uid="{44EFD821-70C7-1340-89E3-A1F0B109531C}">
       <text>
         <r>
           <rPr>
@@ -2481,7 +2510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I74" authorId="0" shapeId="0" xr:uid="{F8B52236-A07C-E241-8F86-73C372B8E174}">
+    <comment ref="I74" authorId="0" shapeId="0" xr:uid="{9724BD29-B5A8-474B-A926-FB6BDE267669}">
       <text>
         <r>
           <rPr>
@@ -2501,7 +2530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I75" authorId="0" shapeId="0" xr:uid="{3C60B74B-F066-0543-ABA8-434F6E2FE669}">
+    <comment ref="I75" authorId="0" shapeId="0" xr:uid="{29C5BAF2-3C06-A24D-9041-4010363EF2AC}">
       <text>
         <r>
           <rPr>
@@ -2521,7 +2550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I76" authorId="0" shapeId="0" xr:uid="{ABCBE740-7F7A-0746-94D4-7BD11D17F024}">
+    <comment ref="I76" authorId="0" shapeId="0" xr:uid="{4354588A-AFB6-CB48-B13A-E9D51EF78BC8}">
       <text>
         <r>
           <rPr>
@@ -2541,7 +2570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I77" authorId="0" shapeId="0" xr:uid="{C34766EE-2E42-334D-8401-67B5D2135B85}">
+    <comment ref="I77" authorId="0" shapeId="0" xr:uid="{8812F474-87A8-E448-82F8-367B63670671}">
       <text>
         <r>
           <rPr>
@@ -2561,7 +2590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I78" authorId="0" shapeId="0" xr:uid="{54818FE8-14BC-6448-9E88-F330900648D0}">
+    <comment ref="I78" authorId="0" shapeId="0" xr:uid="{4F339964-9B17-9149-94BC-04693862EF9D}">
       <text>
         <r>
           <rPr>
@@ -2577,7 +2606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I79" authorId="0" shapeId="0" xr:uid="{49013FEA-18E7-2342-8B61-BEA7722CA5B0}">
+    <comment ref="I79" authorId="0" shapeId="0" xr:uid="{920E6B95-D187-734C-8FC9-22EB071BF11F}">
       <text>
         <r>
           <rPr>
@@ -2592,7 +2621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I80" authorId="0" shapeId="0" xr:uid="{D9F3A01F-865E-D544-8F24-AC9D1AFBF522}">
+    <comment ref="I80" authorId="0" shapeId="0" xr:uid="{E2373000-4E3F-FF49-97C4-A9A467EC6273}">
       <text>
         <r>
           <rPr>
@@ -2612,7 +2641,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I81" authorId="0" shapeId="0" xr:uid="{014C3750-BDA1-9F4E-95ED-337406F20F7C}">
+    <comment ref="I81" authorId="0" shapeId="0" xr:uid="{E0773EF7-7484-E940-BB33-07971FFA3CA6}">
       <text>
         <r>
           <rPr>
@@ -2632,7 +2661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I82" authorId="0" shapeId="0" xr:uid="{7C1C52A6-4A0F-E643-AE54-860253F57179}">
+    <comment ref="I82" authorId="0" shapeId="0" xr:uid="{62C6FB66-597B-6647-AED9-4064CC7E985D}">
       <text>
         <r>
           <rPr>
@@ -2659,7 +2688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I83" authorId="0" shapeId="0" xr:uid="{08251DB8-2EA0-4F4D-A307-255ECF18690A}">
+    <comment ref="I83" authorId="0" shapeId="0" xr:uid="{EA80ABF8-9776-9B49-99BF-F629B0D8558E}">
       <text>
         <r>
           <rPr>
@@ -2677,7 +2706,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I84" authorId="0" shapeId="0" xr:uid="{A6EEEA65-57C0-5E48-9ECB-196315704756}">
+    <comment ref="I84" authorId="0" shapeId="0" xr:uid="{06D7A474-F9E2-BB44-8317-9C7D96F15756}">
       <text>
         <r>
           <rPr>
@@ -2706,7 +2735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{6E1EE72A-5CD3-744A-9D31-C21D5C628058}">
+    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{E93CFABC-FBAD-2140-823E-C77AEA71D8A1}">
       <text>
         <r>
           <rPr>
@@ -2726,7 +2755,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{13CB8369-DF97-D64B-864C-C319D1A0659E}">
+    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{564FE5E7-91A7-F743-A512-57A67B2E2DDE}">
       <text>
         <r>
           <rPr>
@@ -2741,7 +2770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{B0AF9D16-D6E4-314F-845E-AF37185DF325}">
+    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{166CE5E6-E44C-7844-8B1D-E99B8EF96C8F}">
       <text>
         <r>
           <rPr>
@@ -2757,7 +2786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{A30A5B88-EE6F-EE4B-878E-8AD80F3466A0}">
+    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{C5F81559-1732-5342-BBD2-75E4D083B7F6}">
       <text>
         <r>
           <rPr>
@@ -2775,7 +2804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{2013E0CD-22F1-0E45-8E91-545BB267E136}">
+    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{200158D0-CEA4-394B-8EBD-AADEB4F27900}">
       <text>
         <r>
           <rPr>
@@ -2794,7 +2823,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{EB6EC252-7379-9049-957F-3F18F71D4ACF}">
+    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{5112E077-D346-4940-82E4-340DC91C9A3F}">
       <text>
         <r>
           <rPr>
@@ -2814,7 +2843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I91" authorId="0" shapeId="0" xr:uid="{E73D8AB8-8E7F-3544-8638-0409439E61ED}">
+    <comment ref="I91" authorId="0" shapeId="0" xr:uid="{122943B9-1A1D-ED4E-BD41-2CF019C6F691}">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I92" authorId="0" shapeId="0" xr:uid="{FEE94D14-3018-C14E-B8F0-7BDCE13206BC}">
+    <comment ref="I92" authorId="0" shapeId="0" xr:uid="{122FDA04-1CEC-FF4D-AC99-F398E6D42EA5}">
       <text>
         <r>
           <rPr>
@@ -2857,7 +2886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I93" authorId="0" shapeId="0" xr:uid="{6F4573EB-831F-4947-ADB2-511D95DBD32A}">
+    <comment ref="I93" authorId="0" shapeId="0" xr:uid="{DA3CB83E-2E83-8949-B8D7-55767B019D22}">
       <text>
         <r>
           <rPr>
@@ -2872,7 +2901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I94" authorId="0" shapeId="0" xr:uid="{4083A69F-3060-5141-80A5-1C976D0B0AE3}">
+    <comment ref="I94" authorId="0" shapeId="0" xr:uid="{DFF5DBC4-E077-F143-9B4E-8DFE2DA606D2}">
       <text>
         <r>
           <rPr>
@@ -2888,7 +2917,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I95" authorId="0" shapeId="0" xr:uid="{ADF94C28-FFC2-8B49-B76B-C582769CEFE8}">
+    <comment ref="I95" authorId="0" shapeId="0" xr:uid="{AE7A2981-690A-DF49-B8DE-1ABA509EE4E3}">
       <text>
         <r>
           <rPr>
@@ -2917,7 +2946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I96" authorId="0" shapeId="0" xr:uid="{D76781AA-E91B-B14E-9760-962A8F17EC65}">
+    <comment ref="I96" authorId="0" shapeId="0" xr:uid="{71D9C317-3673-EF4F-AE4E-0AA254962EC1}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I97" authorId="0" shapeId="0" xr:uid="{98D03843-4255-B54E-BE9C-345EF77F33B3}">
+    <comment ref="I97" authorId="0" shapeId="0" xr:uid="{5B514A54-6A80-3E48-A6ED-8F46B5C78EC3}">
       <text>
         <r>
           <rPr>
@@ -2956,7 +2985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I98" authorId="0" shapeId="0" xr:uid="{96231356-C2F8-AD43-9BAC-5EED8EE164B5}">
+    <comment ref="I98" authorId="0" shapeId="0" xr:uid="{EBD49A71-F84F-2643-A409-3A0420049B2F}">
       <text>
         <r>
           <rPr>
@@ -2976,7 +3005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{DD5A9A5A-DD1C-D84D-9E1A-50C510FE5C9B}">
+    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{35D6A9EB-692D-9F41-9129-72A2A1701AD6}">
       <text>
         <r>
           <rPr>
@@ -2996,7 +3025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{24266AF0-0509-1642-BB23-66393E9D1B89}">
+    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{6DDD74D2-65C9-AF49-87D1-BE7DAB1B43BB}">
       <text>
         <r>
           <rPr>
@@ -3011,7 +3040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{CF5A1FBB-DCA7-9E4D-BC1A-5C4ACCE93C8C}">
+    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{16441AEF-89CA-FE4B-80F8-DF79C04D7529}">
       <text>
         <r>
           <rPr>
@@ -3040,7 +3069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I102" authorId="0" shapeId="0" xr:uid="{6F6F679E-BBF7-AE4C-A3B9-3FD47E6E547F}">
+    <comment ref="I102" authorId="0" shapeId="0" xr:uid="{BACE25D9-344F-B948-844C-61FCB6981AF3}">
       <text>
         <r>
           <rPr>
@@ -3058,7 +3087,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I103" authorId="0" shapeId="0" xr:uid="{A27766BA-CD70-904E-A58C-1E19ABC8F814}">
+    <comment ref="I103" authorId="0" shapeId="0" xr:uid="{7B0CD44B-E2E3-FB40-8172-677E09817684}">
       <text>
         <r>
           <rPr>
@@ -3078,7 +3107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I104" authorId="0" shapeId="0" xr:uid="{06FC5FEC-F740-4B44-9F15-3111B0F69806}">
+    <comment ref="I104" authorId="0" shapeId="0" xr:uid="{B1B720FA-F825-B746-8CCF-11E96A2986BF}">
       <text>
         <r>
           <rPr>
@@ -3096,7 +3125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I105" authorId="0" shapeId="0" xr:uid="{A8DE99F8-0C0D-EB43-8399-AEEE80BA3755}">
+    <comment ref="I105" authorId="0" shapeId="0" xr:uid="{AB2B49FE-DF11-6146-B512-2C440EB42875}">
       <text>
         <r>
           <rPr>
@@ -3114,7 +3143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I106" authorId="0" shapeId="0" xr:uid="{D9203566-B30E-5D40-AF66-B4008A084CC2}">
+    <comment ref="I106" authorId="0" shapeId="0" xr:uid="{D78B0419-7DC6-9847-AB46-AE5769696648}">
       <text>
         <r>
           <rPr>
@@ -3134,7 +3163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I107" authorId="0" shapeId="0" xr:uid="{3322912F-3898-6A48-BDED-5CFD115E9616}">
+    <comment ref="I107" authorId="0" shapeId="0" xr:uid="{890420D5-FA9F-2F43-B1F9-C59CF3530119}">
       <text>
         <r>
           <rPr>
@@ -3149,7 +3178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I108" authorId="0" shapeId="0" xr:uid="{757D76AE-DF1B-9649-95F3-56A2A9DF9E90}">
+    <comment ref="I108" authorId="0" shapeId="0" xr:uid="{2B236E1F-7A48-F240-9F8B-88B745F694A4}">
       <text>
         <r>
           <rPr>
@@ -3172,7 +3201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I109" authorId="0" shapeId="0" xr:uid="{6F874931-1779-B944-B5FF-A70362756888}">
+    <comment ref="I109" authorId="0" shapeId="0" xr:uid="{8880574D-A041-1746-9020-F217E9789F66}">
       <text>
         <r>
           <rPr>
@@ -3187,7 +3216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I110" authorId="0" shapeId="0" xr:uid="{1073BC31-EDA9-1C48-BE97-E0A84F85FB69}">
+    <comment ref="I110" authorId="0" shapeId="0" xr:uid="{DA24B8AB-BA36-6647-B21F-CDBFEAA88371}">
       <text>
         <r>
           <rPr>
@@ -3202,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I111" authorId="0" shapeId="0" xr:uid="{F59F3232-0B6C-024E-87D7-6975544267A8}">
+    <comment ref="I111" authorId="0" shapeId="0" xr:uid="{9A0725F9-3D96-B44E-93AE-29449FF0DD0D}">
       <text>
         <r>
           <rPr>
@@ -3217,7 +3246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I112" authorId="0" shapeId="0" xr:uid="{C65083F7-4C88-B24A-8620-AC853859FE18}">
+    <comment ref="I112" authorId="0" shapeId="0" xr:uid="{99506EC8-21D8-444B-A574-BF299E41C528}">
       <text>
         <r>
           <rPr>
@@ -3238,7 +3267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I113" authorId="0" shapeId="0" xr:uid="{66B48C17-EF5F-A44B-A7EA-F3506A60D354}">
+    <comment ref="I113" authorId="0" shapeId="0" xr:uid="{8F315B8A-0FED-FA4B-86FA-DACFCF07704A}">
       <text>
         <r>
           <rPr>
@@ -3255,7 +3284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I114" authorId="0" shapeId="0" xr:uid="{853D651C-46E2-934B-A2FF-FE551D4C2917}">
+    <comment ref="I114" authorId="0" shapeId="0" xr:uid="{8C3F68B2-F6A7-9A47-80F2-7382D073DF8C}">
       <text>
         <r>
           <rPr>
@@ -3270,7 +3299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I115" authorId="0" shapeId="0" xr:uid="{EF7E0B4B-E249-4044-A786-63C0D8AC1563}">
+    <comment ref="I115" authorId="0" shapeId="0" xr:uid="{D2688350-D62A-AB44-86A1-6C0B3055FDF6}">
       <text>
         <r>
           <rPr>
@@ -3289,7 +3318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I116" authorId="0" shapeId="0" xr:uid="{ACE61D65-2351-1B4F-97C9-860EE94B3ADC}">
+    <comment ref="I116" authorId="0" shapeId="0" xr:uid="{41C16B57-3B7B-1B4C-B622-A88B1BE2C6CD}">
       <text>
         <r>
           <rPr>
@@ -3306,7 +3335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I117" authorId="0" shapeId="0" xr:uid="{BF5F6DCA-C981-7048-A857-9B5622D587DF}">
+    <comment ref="I117" authorId="0" shapeId="0" xr:uid="{F2A33C47-C2D3-B340-B3E0-98750A60E1E1}">
       <text>
         <r>
           <rPr>
@@ -3332,7 +3361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I118" authorId="0" shapeId="0" xr:uid="{A8606B28-50ED-7C42-AB0C-1100CCA36C38}">
+    <comment ref="I118" authorId="0" shapeId="0" xr:uid="{7A4E0879-9493-8744-94DF-6A6A51931CDD}">
       <text>
         <r>
           <rPr>
@@ -3349,7 +3378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I119" authorId="0" shapeId="0" xr:uid="{1871195F-9F66-C44B-B613-43632976D293}">
+    <comment ref="I119" authorId="0" shapeId="0" xr:uid="{88BF1485-D8A7-994B-AE44-4833DDCABC45}">
       <text>
         <r>
           <rPr>
@@ -3377,7 +3406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I120" authorId="0" shapeId="0" xr:uid="{313CB1A8-DDDE-3F49-A877-A8C3BF47CCE3}">
+    <comment ref="I120" authorId="0" shapeId="0" xr:uid="{04F445C0-B843-324F-AF08-8F1D70C3758C}">
       <text>
         <r>
           <rPr>
@@ -3393,7 +3422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I121" authorId="0" shapeId="0" xr:uid="{53A39454-8890-0E4D-BF89-34A57627834D}">
+    <comment ref="I121" authorId="0" shapeId="0" xr:uid="{C8DFFB88-0C57-DD4B-ABC4-7728AE0AD202}">
       <text>
         <r>
           <rPr>
@@ -3410,7 +3439,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I122" authorId="0" shapeId="0" xr:uid="{95AC0C98-2110-CC4F-988C-0361202C7F85}">
+    <comment ref="I122" authorId="0" shapeId="0" xr:uid="{C44A74CF-772B-E041-BFE3-0CEECFB0F3B7}">
       <text>
         <r>
           <rPr>
@@ -3426,7 +3455,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I123" authorId="0" shapeId="0" xr:uid="{B5020AB6-B562-2F4D-9428-81439968B216}">
+    <comment ref="I123" authorId="0" shapeId="0" xr:uid="{ADF05674-6ECF-404D-944B-C71486F896AB}">
       <text>
         <r>
           <rPr>
@@ -3443,7 +3472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I124" authorId="0" shapeId="0" xr:uid="{7F80F071-C377-504E-9190-053835116C73}">
+    <comment ref="I124" authorId="0" shapeId="0" xr:uid="{A9D81B34-12C0-BD4E-A670-53C2245D12BB}">
       <text>
         <r>
           <rPr>
@@ -3475,7 +3504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I125" authorId="0" shapeId="0" xr:uid="{C9C3E044-DF34-7B4D-BE5E-6103DA72DD79}">
+    <comment ref="I125" authorId="0" shapeId="0" xr:uid="{7FB9270C-46CF-AD46-965A-E4F0D97C0C6F}">
       <text>
         <r>
           <rPr>
@@ -3494,7 +3523,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I126" authorId="0" shapeId="0" xr:uid="{2815B612-4299-9444-B2D4-6F364C4FEA97}">
+    <comment ref="I126" authorId="0" shapeId="0" xr:uid="{D0F85AA8-0416-1C40-95F9-088E9E3FFBE9}">
       <text>
         <r>
           <rPr>
@@ -3512,7 +3541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I127" authorId="0" shapeId="0" xr:uid="{467146BF-1776-544F-B479-C3E9775E45E1}">
+    <comment ref="I127" authorId="0" shapeId="0" xr:uid="{EDEDB30C-55AE-AF46-9EB8-795F9ED00126}">
       <text>
         <r>
           <rPr>
@@ -3527,7 +3556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I128" authorId="0" shapeId="0" xr:uid="{6BCE99C0-903C-9A41-90AA-6921E0DA5401}">
+    <comment ref="I128" authorId="0" shapeId="0" xr:uid="{6248E1C1-BE06-2046-89FA-467CE61C5117}">
       <text>
         <r>
           <rPr>
@@ -3544,7 +3573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I129" authorId="0" shapeId="0" xr:uid="{3D8705F1-0F27-7544-8B37-4001A2ADCCD8}">
+    <comment ref="I129" authorId="0" shapeId="0" xr:uid="{14FA2F63-40BD-5D4E-8757-72C05E82C6B8}">
       <text>
         <r>
           <rPr>
@@ -3561,7 +3590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I130" authorId="0" shapeId="0" xr:uid="{88563FBF-7171-AA4B-8D9E-5B0B36CA93B7}">
+    <comment ref="I130" authorId="0" shapeId="0" xr:uid="{C9E08B14-CB59-3247-B9F3-7B107408C140}">
       <text>
         <r>
           <rPr>
@@ -3576,7 +3605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I131" authorId="0" shapeId="0" xr:uid="{83311D81-D85C-BC43-AF66-9B6A0B7B5911}">
+    <comment ref="I131" authorId="0" shapeId="0" xr:uid="{CC0F1275-534F-BA4C-810A-BB3711BAF564}">
       <text>
         <r>
           <rPr>
@@ -3595,7 +3624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I132" authorId="0" shapeId="0" xr:uid="{D8937F10-11FE-CE45-A4B8-C20356BF4D0E}">
+    <comment ref="I132" authorId="0" shapeId="0" xr:uid="{91DF5060-C04C-F348-B5CD-043E8053F35C}">
       <text>
         <r>
           <rPr>
@@ -3614,7 +3643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I133" authorId="0" shapeId="0" xr:uid="{26C1B0FC-D098-3749-8A87-F4EB87DA7F97}">
+    <comment ref="I133" authorId="0" shapeId="0" xr:uid="{B83E1DE9-348E-904C-BB00-72CA6CE8CC91}">
       <text>
         <r>
           <rPr>
@@ -3631,7 +3660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I134" authorId="0" shapeId="0" xr:uid="{ACC4DE68-268B-344C-B6B9-078B2A49EAD2}">
+    <comment ref="I134" authorId="0" shapeId="0" xr:uid="{B0939CFC-6F65-E545-AF70-132339CE42BA}">
       <text>
         <r>
           <rPr>
@@ -3646,7 +3675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I135" authorId="0" shapeId="0" xr:uid="{E75C2037-8D65-D241-BE39-C40F1A02C9AB}">
+    <comment ref="I135" authorId="0" shapeId="0" xr:uid="{25AEF7A7-638D-F047-B743-81E21A087D2B}">
       <text>
         <r>
           <rPr>
@@ -3662,7 +3691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I136" authorId="0" shapeId="0" xr:uid="{D1E62BD3-EA24-E948-8E58-FD1E31CE0E0C}">
+    <comment ref="I136" authorId="0" shapeId="0" xr:uid="{ABEF14D4-06B9-0E40-ABA2-5EF0C586E411}">
       <text>
         <r>
           <rPr>
@@ -3679,7 +3708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I137" authorId="0" shapeId="0" xr:uid="{04D52844-D66D-BD4B-BBCA-8E85F2F269C1}">
+    <comment ref="I137" authorId="0" shapeId="0" xr:uid="{B53809DE-3A38-5140-9C9A-7832D470A749}">
       <text>
         <r>
           <rPr>
@@ -3707,7 +3736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I138" authorId="0" shapeId="0" xr:uid="{66A15169-9AD8-9E4D-B371-BBA1215D7D3F}">
+    <comment ref="I138" authorId="0" shapeId="0" xr:uid="{034311FC-AA7E-3946-AC4B-C90C5757FDC1}">
       <text>
         <r>
           <rPr>
@@ -3724,7 +3753,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I139" authorId="0" shapeId="0" xr:uid="{CB608B36-82E6-D64C-8F93-DFB3A4C5EF52}">
+    <comment ref="I139" authorId="0" shapeId="0" xr:uid="{1CBF530E-2F10-7E48-AE26-A2590302F6AF}">
       <text>
         <r>
           <rPr>
@@ -3740,7 +3769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I140" authorId="0" shapeId="0" xr:uid="{A1A2228C-0906-154B-888B-901BEFC2F6FC}">
+    <comment ref="I140" authorId="0" shapeId="0" xr:uid="{A310F016-98A4-634B-BEC3-FCC11F946B41}">
       <text>
         <r>
           <rPr>
@@ -3756,7 +3785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I141" authorId="0" shapeId="0" xr:uid="{6EDCD3FD-7D2D-994E-AC36-468F3C22D8FC}">
+    <comment ref="I141" authorId="0" shapeId="0" xr:uid="{191ED7C9-87D9-3946-8436-4EF6B5AAF606}">
       <text>
         <r>
           <rPr>
@@ -3774,7 +3803,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I142" authorId="0" shapeId="0" xr:uid="{4D04D217-8BCD-0D49-90E7-BB1F78A2535E}">
+    <comment ref="I142" authorId="0" shapeId="0" xr:uid="{788CBBD8-7241-DB48-AC2E-2A926805C572}">
       <text>
         <r>
           <rPr>
@@ -3792,7 +3821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I143" authorId="0" shapeId="0" xr:uid="{2179CCB1-AEDF-9F42-ABC7-2968DE1ACB4E}">
+    <comment ref="I143" authorId="0" shapeId="0" xr:uid="{EB9FCDDA-077E-5742-BBAE-108E757BF446}">
       <text>
         <r>
           <rPr>
@@ -3808,7 +3837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I144" authorId="0" shapeId="0" xr:uid="{228F427D-3AEB-6F4D-955F-2B6D073B09AB}">
+    <comment ref="I144" authorId="0" shapeId="0" xr:uid="{B8F5D2C2-8A5D-854A-A1FF-A63B579B25CA}">
       <text>
         <r>
           <rPr>
@@ -3825,7 +3854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I145" authorId="0" shapeId="0" xr:uid="{79A0755F-A5F6-AF46-949A-5887C3873303}">
+    <comment ref="I145" authorId="0" shapeId="0" xr:uid="{79724995-0C87-D048-AC3A-AFE88864430B}">
       <text>
         <r>
           <rPr>
@@ -3841,7 +3870,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I146" authorId="0" shapeId="0" xr:uid="{E537C6D2-CDBD-0F49-977A-FAE2482D6D76}">
+    <comment ref="I146" authorId="0" shapeId="0" xr:uid="{A981FF28-0EA2-F643-BF65-3DB4AC2CEF80}">
       <text>
         <r>
           <rPr>
@@ -3858,7 +3887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I147" authorId="0" shapeId="0" xr:uid="{88D66291-4C18-D94E-81EA-A0C5CBB9BECA}">
+    <comment ref="I147" authorId="0" shapeId="0" xr:uid="{2C834151-9AB7-0344-82CA-5DC271EFC789}">
       <text>
         <r>
           <rPr>
@@ -3878,7 +3907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I148" authorId="0" shapeId="0" xr:uid="{D693833A-2CC5-E34F-BF92-BBF822F29AEA}">
+    <comment ref="I148" authorId="0" shapeId="0" xr:uid="{BAA73ECE-EA32-9C4D-B9B8-D34D541614DE}">
       <text>
         <r>
           <rPr>
@@ -3913,7 +3942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I149" authorId="0" shapeId="0" xr:uid="{AECC01C4-C2B3-1043-9914-83A09880C408}">
+    <comment ref="I149" authorId="0" shapeId="0" xr:uid="{6DCB4D26-3FF3-9147-B19B-53BDB03C03FE}">
       <text>
         <r>
           <rPr>
@@ -3929,7 +3958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I150" authorId="0" shapeId="0" xr:uid="{4D5DE6D5-2CAE-8746-88D6-30C154059281}">
+    <comment ref="I150" authorId="0" shapeId="0" xr:uid="{36DA116B-F6C6-2A48-87F4-FC625A5111DE}">
       <text>
         <r>
           <rPr>
@@ -3951,7 +3980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I151" authorId="0" shapeId="0" xr:uid="{4CEA6473-E753-6E45-9BDF-322751B615B4}">
+    <comment ref="I151" authorId="0" shapeId="0" xr:uid="{B7BAC43B-750B-8243-8296-4A286D2B159A}">
       <text>
         <r>
           <rPr>
@@ -3975,7 +4004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I152" authorId="0" shapeId="0" xr:uid="{34AEBDC8-337D-4F41-9470-BCC62A610C73}">
+    <comment ref="I152" authorId="0" shapeId="0" xr:uid="{E6D38539-35E5-8D48-BF75-D9C81C980904}">
       <text>
         <r>
           <rPr>
@@ -3993,7 +4022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I153" authorId="0" shapeId="0" xr:uid="{360DE7BD-8B41-A547-BFBB-E7485E70F48D}">
+    <comment ref="I153" authorId="0" shapeId="0" xr:uid="{0231BC5A-BF67-2744-A124-B0E08EEA99BB}">
       <text>
         <r>
           <rPr>
@@ -4009,7 +4038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I154" authorId="0" shapeId="0" xr:uid="{CA4A7ECD-6648-3441-95B4-6B0120B39B40}">
+    <comment ref="I154" authorId="0" shapeId="0" xr:uid="{B8AD17CA-D92F-B34D-B2C7-C21703B01921}">
       <text>
         <r>
           <rPr>
@@ -4033,7 +4062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I155" authorId="0" shapeId="0" xr:uid="{AC6CBB87-2678-014F-9FA6-2BD9C780ABCA}">
+    <comment ref="I155" authorId="0" shapeId="0" xr:uid="{D5C1827E-7935-1440-8DC8-7291810AA447}">
       <text>
         <r>
           <rPr>
@@ -4052,7 +4081,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I156" authorId="0" shapeId="0" xr:uid="{06D47D48-34F7-A147-8DBD-833352E1D312}">
+    <comment ref="I156" authorId="0" shapeId="0" xr:uid="{5BA36180-8DDA-9743-8459-F808DA6FC7E6}">
       <text>
         <r>
           <rPr>
@@ -4072,7 +4101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I157" authorId="0" shapeId="0" xr:uid="{1C2AD5DB-CE62-D84B-B70F-50563E7B854E}">
+    <comment ref="I157" authorId="0" shapeId="0" xr:uid="{8C01E368-07BF-C548-81F9-8A10568F4F9D}">
       <text>
         <r>
           <rPr>
@@ -4092,7 +4121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I158" authorId="0" shapeId="0" xr:uid="{5C153B94-A763-4D47-B38F-CB791B082412}">
+    <comment ref="I158" authorId="0" shapeId="0" xr:uid="{F56F6525-87F5-464A-947F-E3EADCE792B7}">
       <text>
         <r>
           <rPr>
@@ -4112,7 +4141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I159" authorId="0" shapeId="0" xr:uid="{F270C797-1C05-AF4B-93E3-FA644BD01DA3}">
+    <comment ref="I159" authorId="0" shapeId="0" xr:uid="{60F748A4-28DB-BC4E-B9E9-A28D792E439A}">
       <text>
         <r>
           <rPr>
@@ -4128,7 +4157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I160" authorId="0" shapeId="0" xr:uid="{EB86480F-2DCC-3645-93A6-DD76FF84918D}">
+    <comment ref="I160" authorId="0" shapeId="0" xr:uid="{F7BC204E-145F-1F44-989E-718FEE9ED871}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I161" authorId="0" shapeId="0" xr:uid="{A38E1ECA-756D-4F42-B6A0-CDA1ABB0E8D5}">
+    <comment ref="I161" authorId="0" shapeId="0" xr:uid="{534E5985-221E-C749-B873-DDD574BEDC96}">
       <text>
         <r>
           <rPr>
@@ -4176,7 +4205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I162" authorId="0" shapeId="0" xr:uid="{80E84D35-0303-A54C-BEBB-F8DB10C74983}">
+    <comment ref="I162" authorId="0" shapeId="0" xr:uid="{6960C695-3011-BF43-89DE-2586ED228399}">
       <text>
         <r>
           <rPr>
@@ -4200,7 +4229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I163" authorId="0" shapeId="0" xr:uid="{E539571F-C63C-6F48-A932-EB590F06B118}">
+    <comment ref="I163" authorId="0" shapeId="0" xr:uid="{E063ACA4-1EC2-0A4C-BB82-3A0253F4C45A}">
       <text>
         <r>
           <rPr>
@@ -4218,7 +4247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I164" authorId="0" shapeId="0" xr:uid="{6F274F2F-BFD1-1E43-80B8-A549690FAADE}">
+    <comment ref="I164" authorId="0" shapeId="0" xr:uid="{517F47E7-7C21-8848-8360-375AC2999E46}">
       <text>
         <r>
           <rPr>
@@ -4240,7 +4269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I165" authorId="0" shapeId="0" xr:uid="{9438DD71-039A-EB4D-8BD3-F98EDD8A5614}">
+    <comment ref="I165" authorId="0" shapeId="0" xr:uid="{6594536E-D697-0C4D-B138-230873098102}">
       <text>
         <r>
           <rPr>
@@ -4258,7 +4287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I166" authorId="0" shapeId="0" xr:uid="{726179B1-E440-9A44-A88C-8CAF48A11CD8}">
+    <comment ref="I166" authorId="0" shapeId="0" xr:uid="{4A527715-4F86-8140-9D08-4EE23774D1FE}">
       <text>
         <r>
           <rPr>
@@ -4274,7 +4303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I167" authorId="0" shapeId="0" xr:uid="{BF18A198-1D0B-0042-906B-BF35652A5628}">
+    <comment ref="I167" authorId="0" shapeId="0" xr:uid="{258FA360-8073-454D-850B-F8F6DC30B26B}">
       <text>
         <r>
           <rPr>
@@ -4301,7 +4330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I168" authorId="0" shapeId="0" xr:uid="{4512FCEF-F665-E143-BC8B-94B4922EDA3E}">
+    <comment ref="I168" authorId="0" shapeId="0" xr:uid="{F3D3AA81-6D87-CD49-9892-441342AE8BCC}">
       <text>
         <r>
           <rPr>
@@ -4322,7 +4351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I169" authorId="0" shapeId="0" xr:uid="{B9627055-75CD-6340-82BB-79F76C677B56}">
+    <comment ref="I169" authorId="0" shapeId="0" xr:uid="{EF5BCBD2-40A2-5042-BBB1-16FDED9811ED}">
       <text>
         <r>
           <rPr>
@@ -4346,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I170" authorId="0" shapeId="0" xr:uid="{529A6BFE-FE03-0C4C-BC83-F72D5E565DA9}">
+    <comment ref="I170" authorId="0" shapeId="0" xr:uid="{6FBE1B88-EF7D-A74D-A731-84D93CAB42E4}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I171" authorId="0" shapeId="0" xr:uid="{4FE36BBF-427F-3B4F-BD71-5E2966C1FD1E}">
+    <comment ref="I171" authorId="0" shapeId="0" xr:uid="{85FCAFDA-848F-7B4C-8F6E-610D10B36B72}">
       <text>
         <r>
           <rPr>
@@ -4381,7 +4410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I172" authorId="0" shapeId="0" xr:uid="{16CBBCAB-BA87-A14F-8CBA-D41EEBEA1FB5}">
+    <comment ref="I172" authorId="0" shapeId="0" xr:uid="{44605528-B46F-024F-8081-F2F26D042E6A}">
       <text>
         <r>
           <rPr>
@@ -4396,7 +4425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I173" authorId="0" shapeId="0" xr:uid="{F0F25FD5-9BA8-8E4D-A197-0BBBE5D531BA}">
+    <comment ref="I173" authorId="0" shapeId="0" xr:uid="{5CC02FDD-CD2F-2C48-B2F1-72618F981B1D}">
       <text>
         <r>
           <rPr>
@@ -4412,7 +4441,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I174" authorId="0" shapeId="0" xr:uid="{47612BDA-F59F-B248-8F5A-D85E038FE0B2}">
+    <comment ref="I174" authorId="0" shapeId="0" xr:uid="{85639E0E-DBBD-FE40-ADE5-62581A6F384C}">
       <text>
         <r>
           <rPr>
@@ -4431,7 +4460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I175" authorId="0" shapeId="0" xr:uid="{34E9DD36-A1BA-0945-BF1F-84137D970295}">
+    <comment ref="I175" authorId="0" shapeId="0" xr:uid="{E20B1C67-B11C-7A45-9F21-C4805EEB7092}">
       <text>
         <r>
           <rPr>
@@ -4455,7 +4484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I176" authorId="0" shapeId="0" xr:uid="{B4682C2C-4E8E-A04A-8119-945D9DC54ED8}">
+    <comment ref="I176" authorId="0" shapeId="0" xr:uid="{4CC3F33B-57F8-9E46-B0C6-2906C55617BB}">
       <text>
         <r>
           <rPr>
@@ -4473,7 +4502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I177" authorId="0" shapeId="0" xr:uid="{2A82A5EA-0F78-7C4C-ABAC-89C2874585EA}">
+    <comment ref="I177" authorId="0" shapeId="0" xr:uid="{D548183E-F4A1-8A41-95BF-FA1C1664B427}">
       <text>
         <r>
           <rPr>
@@ -4491,7 +4520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I178" authorId="0" shapeId="0" xr:uid="{1C137002-DDA6-8342-AB08-122C1276F953}">
+    <comment ref="I178" authorId="0" shapeId="0" xr:uid="{FBE2FE42-840B-7842-A686-4B9DDC71DA29}">
       <text>
         <r>
           <rPr>
@@ -4508,7 +4537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I179" authorId="0" shapeId="0" xr:uid="{7989BEE1-8682-0A4F-B59F-C1492E53089F}">
+    <comment ref="I179" authorId="0" shapeId="0" xr:uid="{E341A0B0-68E8-7545-8088-0D17265E74E9}">
       <text>
         <r>
           <rPr>
@@ -4527,7 +4556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I180" authorId="0" shapeId="0" xr:uid="{CCF031D3-D086-BF4D-AD14-96DD6CD52E12}">
+    <comment ref="I180" authorId="0" shapeId="0" xr:uid="{19933615-2C42-4E4C-8195-E5C5E5F87649}">
       <text>
         <r>
           <rPr>
@@ -4551,7 +4580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I181" authorId="0" shapeId="0" xr:uid="{DF46C770-AC9B-DF44-BFBB-5214FF7E88BD}">
+    <comment ref="I181" authorId="0" shapeId="0" xr:uid="{C842AF1F-A155-AE45-9A8A-AED1728E15A6}">
       <text>
         <r>
           <rPr>
@@ -4586,7 +4615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I182" authorId="0" shapeId="0" xr:uid="{4B7AF0AD-6CCA-0641-AFB4-F85653C11094}">
+    <comment ref="I182" authorId="0" shapeId="0" xr:uid="{38929870-C132-C045-97DB-DAACD2B67E8F}">
       <text>
         <r>
           <rPr>
@@ -4601,7 +4630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I183" authorId="0" shapeId="0" xr:uid="{C417CBE8-9263-E442-A7D3-AABE5433A909}">
+    <comment ref="I183" authorId="0" shapeId="0" xr:uid="{A8D12412-7F02-3F41-AFFA-FEA4633A2BC0}">
       <text>
         <r>
           <rPr>
@@ -4616,7 +4645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I184" authorId="0" shapeId="0" xr:uid="{F89016A6-E6F1-CA45-AF0C-B5B726BF0C51}">
+    <comment ref="I184" authorId="0" shapeId="0" xr:uid="{6B90F7D3-2E6F-3A4C-8F71-6D0CADDA8E17}">
       <text>
         <r>
           <rPr>
@@ -4631,7 +4660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I185" authorId="0" shapeId="0" xr:uid="{D93FC280-66C2-F449-A758-61D1CECE95DD}">
+    <comment ref="I185" authorId="0" shapeId="0" xr:uid="{B435F3D8-F8DC-6245-92D1-219AF8F60861}">
       <text>
         <r>
           <rPr>
@@ -4646,7 +4675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I186" authorId="0" shapeId="0" xr:uid="{1764AE3F-5206-0842-A361-4B3FF35F1AAB}">
+    <comment ref="I186" authorId="0" shapeId="0" xr:uid="{863ED2C9-7F3E-064A-821E-24F65156540C}">
       <text>
         <r>
           <rPr>
@@ -4666,7 +4695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I187" authorId="0" shapeId="0" xr:uid="{1EE48B47-17E8-294B-B21D-BCF355A6CBD6}">
+    <comment ref="I187" authorId="0" shapeId="0" xr:uid="{77CE9ADC-27FF-1B49-91B5-0D675F153267}">
       <text>
         <r>
           <rPr>
@@ -4686,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I188" authorId="0" shapeId="0" xr:uid="{FB2D321D-34D2-F140-989D-12E63BDE844D}">
+    <comment ref="I188" authorId="0" shapeId="0" xr:uid="{A722F798-3DB5-E942-9807-DE50CE0298C0}">
       <text>
         <r>
           <rPr>
@@ -4719,7 +4748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I189" authorId="0" shapeId="0" xr:uid="{E1D9F635-103B-F64D-9F95-5A9AFA87B6F2}">
+    <comment ref="I189" authorId="0" shapeId="0" xr:uid="{5D40908C-BC6C-4046-8F81-779BF1FDD3DF}">
       <text>
         <r>
           <rPr>
@@ -4735,7 +4764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I190" authorId="0" shapeId="0" xr:uid="{81ECF36F-20BD-FD4A-BAA0-540C4A051179}">
+    <comment ref="I190" authorId="0" shapeId="0" xr:uid="{857F76EE-0D48-E945-9EE5-828FFC4A56AE}">
       <text>
         <r>
           <rPr>
@@ -4750,7 +4779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I191" authorId="0" shapeId="0" xr:uid="{7F9C70B7-F463-1B41-A68C-8B715130F98B}">
+    <comment ref="I191" authorId="0" shapeId="0" xr:uid="{62BBD6C4-B450-AD41-A81F-7440F994DB6A}">
       <text>
         <r>
           <rPr>
@@ -4765,7 +4794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I192" authorId="0" shapeId="0" xr:uid="{AC1F67DA-370B-714E-9B6D-E9100F6F7D52}">
+    <comment ref="I192" authorId="0" shapeId="0" xr:uid="{79900091-25D9-ED4F-9E79-B61BE967281F}">
       <text>
         <r>
           <rPr>
@@ -4780,7 +4809,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I193" authorId="0" shapeId="0" xr:uid="{4C808D25-A8AA-5343-94B1-ABEC62C8E886}">
+    <comment ref="I193" authorId="0" shapeId="0" xr:uid="{A6255798-48FC-5148-A086-D307434D6C9E}">
       <text>
         <r>
           <rPr>
@@ -4796,7 +4825,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I194" authorId="0" shapeId="0" xr:uid="{157DF163-B46D-CB43-A948-8C2330E44971}">
+    <comment ref="I194" authorId="0" shapeId="0" xr:uid="{F1B66C5C-34E0-0546-ADE8-EC9FE8FEF077}">
       <text>
         <r>
           <rPr>
@@ -4811,7 +4840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I195" authorId="0" shapeId="0" xr:uid="{9F11EA26-79CA-B54A-A618-6E608E507C9B}">
+    <comment ref="I195" authorId="0" shapeId="0" xr:uid="{92F8AF71-4319-4D44-AF96-35C205958D37}">
       <text>
         <r>
           <rPr>
@@ -4827,7 +4856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I196" authorId="0" shapeId="0" xr:uid="{CE0EDE74-EBBA-B74A-B457-72D7DF403AA0}">
+    <comment ref="I196" authorId="0" shapeId="0" xr:uid="{95844CAF-C71B-B74E-A789-22B3457C9012}">
       <text>
         <r>
           <rPr>
@@ -4848,7 +4877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I197" authorId="0" shapeId="0" xr:uid="{DD172339-11A2-F54C-B790-F4A655902D45}">
+    <comment ref="I197" authorId="0" shapeId="0" xr:uid="{59C73CB7-58C9-2F4E-A094-954843BF73F7}">
       <text>
         <r>
           <rPr>
@@ -4866,7 +4895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I198" authorId="0" shapeId="0" xr:uid="{64D8B693-4881-FD44-9DFD-9C8B5B42046C}">
+    <comment ref="I198" authorId="0" shapeId="0" xr:uid="{AB8B2C39-6A1F-644F-8626-E8733F67E8D6}">
       <text>
         <r>
           <rPr>
@@ -4884,7 +4913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I199" authorId="0" shapeId="0" xr:uid="{07B9D13F-DFBE-9341-B0BC-0A0AF5017EDD}">
+    <comment ref="I199" authorId="0" shapeId="0" xr:uid="{9C1BB033-C1A6-564B-88C0-21CF3675C9E7}">
       <text>
         <r>
           <rPr>
@@ -4905,7 +4934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I200" authorId="0" shapeId="0" xr:uid="{F8D56C66-C93B-3040-A256-28A354219557}">
+    <comment ref="I200" authorId="0" shapeId="0" xr:uid="{05575B7B-C9DF-4441-A0CC-6CDE0121D6AF}">
       <text>
         <r>
           <rPr>
@@ -4920,7 +4949,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I201" authorId="0" shapeId="0" xr:uid="{C2D04466-2F50-614C-9F70-788109AEFCD3}">
+    <comment ref="I201" authorId="0" shapeId="0" xr:uid="{5A53B5AE-8D4B-E347-AEE8-27825D4F95E4}">
       <text>
         <r>
           <rPr>
@@ -4948,7 +4977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I202" authorId="0" shapeId="0" xr:uid="{D9545CC6-41C6-E84D-A961-21454CD4E8D8}">
+    <comment ref="I202" authorId="0" shapeId="0" xr:uid="{AC6C0EC8-7BDB-DD45-B937-6BE44445D0C5}">
       <text>
         <r>
           <rPr>
@@ -4965,7 +4994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I203" authorId="0" shapeId="0" xr:uid="{BDE218BA-6E63-0A4D-92EC-BB465AA23216}">
+    <comment ref="I203" authorId="0" shapeId="0" xr:uid="{1B99C76D-8E89-1440-870D-2A686D18EE39}">
       <text>
         <r>
           <rPr>
@@ -4985,7 +5014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I204" authorId="0" shapeId="0" xr:uid="{4C16B76D-EF7A-7D46-B809-A5837994D902}">
+    <comment ref="I204" authorId="0" shapeId="0" xr:uid="{ABD9CD8B-088B-6347-BDC2-EA74C866526E}">
       <text>
         <r>
           <rPr>
@@ -5001,7 +5030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I205" authorId="0" shapeId="0" xr:uid="{F1FD8E0B-0748-C740-BE2A-74416E71335D}">
+    <comment ref="I205" authorId="0" shapeId="0" xr:uid="{E2C90B49-F7CF-F54E-B523-5EAB214A1AA6}">
       <text>
         <r>
           <rPr>
@@ -5017,7 +5046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I206" authorId="0" shapeId="0" xr:uid="{13FD1D9D-31DA-2F45-92A3-9C47ED85213C}">
+    <comment ref="I206" authorId="0" shapeId="0" xr:uid="{1F9D63F3-11F7-C748-95F8-F94A5DE8F77C}">
       <text>
         <r>
           <rPr>
@@ -5042,7 +5071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I207" authorId="0" shapeId="0" xr:uid="{5E724471-4F86-724B-9C3F-6468CD13A252}">
+    <comment ref="I207" authorId="0" shapeId="0" xr:uid="{4702335D-6B46-2648-9F0D-85835D180D12}">
       <text>
         <r>
           <rPr>
@@ -5061,7 +5090,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I208" authorId="0" shapeId="0" xr:uid="{7B65723F-C41C-554F-A028-D3ECC5DF1E33}">
+    <comment ref="I208" authorId="0" shapeId="0" xr:uid="{D77C350F-FAC9-4B48-B5DF-40461DFF012E}">
       <text>
         <r>
           <rPr>
@@ -5080,7 +5109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I209" authorId="0" shapeId="0" xr:uid="{11E19C98-AA17-884C-9BFC-1040D94BD99B}">
+    <comment ref="I209" authorId="0" shapeId="0" xr:uid="{E181A851-067A-8A49-85B8-1B6ACC021E95}">
       <text>
         <r>
           <rPr>
@@ -5097,7 +5126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I210" authorId="0" shapeId="0" xr:uid="{FCFC2D89-C331-F349-8CB3-85F8E69DB695}">
+    <comment ref="I210" authorId="0" shapeId="0" xr:uid="{B922EAAD-9A01-5249-B885-910EE5B22B4A}">
       <text>
         <r>
           <rPr>
@@ -5117,7 +5146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I211" authorId="0" shapeId="0" xr:uid="{B4C865B8-7ED3-7B49-8389-1E477FCDADCE}">
+    <comment ref="I211" authorId="0" shapeId="0" xr:uid="{5A178D29-DF9F-0C46-B4D8-D0F510BEBCD6}">
       <text>
         <r>
           <rPr>
@@ -5139,7 +5168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I212" authorId="0" shapeId="0" xr:uid="{F2ABBB3F-558A-E54A-8A2B-BB1C486540BF}">
+    <comment ref="I212" authorId="0" shapeId="0" xr:uid="{499D6B92-5AAB-B549-B8F8-6341C820B0BF}">
       <text>
         <r>
           <rPr>
@@ -5155,7 +5184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I213" authorId="0" shapeId="0" xr:uid="{14FA7F5C-50E6-5F47-B674-640C6B3AE415}">
+    <comment ref="I213" authorId="0" shapeId="0" xr:uid="{8D269498-4C2D-764D-AB24-EA8C372DBD91}">
       <text>
         <r>
           <rPr>
@@ -5171,7 +5200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I214" authorId="0" shapeId="0" xr:uid="{82828576-6F9B-0949-98D0-EF2E0CE8DBDB}">
+    <comment ref="I214" authorId="0" shapeId="0" xr:uid="{D5B65371-578D-0340-9874-23DB06FFBD15}">
       <text>
         <r>
           <rPr>
@@ -5193,7 +5222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I215" authorId="0" shapeId="0" xr:uid="{8D3BD777-C94A-BD40-92CE-FCDF65390E7F}">
+    <comment ref="I215" authorId="0" shapeId="0" xr:uid="{DCEFEA34-B503-C141-BC2B-30777EC7D943}">
       <text>
         <r>
           <rPr>
@@ -5213,7 +5242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I216" authorId="0" shapeId="0" xr:uid="{868E5807-7074-074B-83DC-A30E3BA68CC5}">
+    <comment ref="I216" authorId="0" shapeId="0" xr:uid="{BF9EC3C5-2120-B549-944E-E8F2904123BE}">
       <text>
         <r>
           <rPr>
@@ -5229,7 +5258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I217" authorId="0" shapeId="0" xr:uid="{35B07B67-1B4A-C54B-9F49-319C8AEC070B}">
+    <comment ref="I217" authorId="0" shapeId="0" xr:uid="{B1E79E58-BAC0-4543-8C4D-5A87FB0946ED}">
       <text>
         <r>
           <rPr>
@@ -5246,7 +5275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I218" authorId="0" shapeId="0" xr:uid="{E23D8F7D-A6D5-C347-BF31-EAE048CD21C4}">
+    <comment ref="I218" authorId="0" shapeId="0" xr:uid="{3D126290-0DCF-8543-8A00-FEF0717BF526}">
       <text>
         <r>
           <rPr>
@@ -5266,7 +5295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I219" authorId="0" shapeId="0" xr:uid="{DDD39E15-3DD5-204D-AC4C-1CF197BC7299}">
+    <comment ref="I219" authorId="0" shapeId="0" xr:uid="{1276DB85-34C9-CF43-8030-B1D7A42D458E}">
       <text>
         <r>
           <rPr>
@@ -5281,7 +5310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I220" authorId="0" shapeId="0" xr:uid="{2863962C-0FCF-C143-8ED1-2C8D58719EF2}">
+    <comment ref="I220" authorId="0" shapeId="0" xr:uid="{DA2E4A88-2CA4-2149-A45C-09A4156D31C0}">
       <text>
         <r>
           <rPr>
@@ -5303,7 +5332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I221" authorId="0" shapeId="0" xr:uid="{B096EC70-2959-6C49-AEC5-4C09F3D68952}">
+    <comment ref="I221" authorId="0" shapeId="0" xr:uid="{CDADD7A0-9B42-EF42-89D7-F4A82B781071}">
       <text>
         <r>
           <rPr>
@@ -5325,7 +5354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I222" authorId="0" shapeId="0" xr:uid="{3CACD4C9-F556-6246-9416-0FCCD20FD21C}">
+    <comment ref="I222" authorId="0" shapeId="0" xr:uid="{6AE17AF7-79E2-7A4A-AB2F-BED9028531C0}">
       <text>
         <r>
           <rPr>
@@ -5358,7 +5387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I223" authorId="0" shapeId="0" xr:uid="{27CD1852-93F5-ED42-BDDD-06C5D6B34A18}">
+    <comment ref="I223" authorId="0" shapeId="0" xr:uid="{7BB493D1-1C28-B243-B4FC-143CED981E30}">
       <text>
         <r>
           <rPr>
@@ -5388,7 +5417,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I224" authorId="0" shapeId="0" xr:uid="{9C70B63E-8CBC-B74E-8458-4CBE07BB943E}">
+    <comment ref="I224" authorId="0" shapeId="0" xr:uid="{F603BB0B-8777-0D4F-AAB9-D20CB5D807AE}">
       <text>
         <r>
           <rPr>
@@ -5403,7 +5432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I225" authorId="0" shapeId="0" xr:uid="{62DE37F0-2B00-D148-B6D7-0F5A4B70E2C1}">
+    <comment ref="I225" authorId="0" shapeId="0" xr:uid="{C2D75DBB-155C-0347-B910-8A06BEB4DDFA}">
       <text>
         <r>
           <rPr>
@@ -5422,7 +5451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I226" authorId="0" shapeId="0" xr:uid="{88B51800-1AF2-1C4C-B6A7-17812D98925B}">
+    <comment ref="I226" authorId="0" shapeId="0" xr:uid="{3E781C2F-A3D7-0342-AC54-0590A3035916}">
       <text>
         <r>
           <rPr>
@@ -5440,7 +5469,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I227" authorId="0" shapeId="0" xr:uid="{890895DC-976A-4642-895A-ED4430BE76F6}">
+    <comment ref="I227" authorId="0" shapeId="0" xr:uid="{91BB57EC-35D1-AC40-A3CC-D28997AF1331}">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I228" authorId="0" shapeId="0" xr:uid="{1A3AC05B-4896-164B-B6FE-8B4F17D367B2}">
+    <comment ref="I228" authorId="0" shapeId="0" xr:uid="{875A7EC0-7F2C-AF42-ACAE-CE8DB71F1E9D}">
       <text>
         <r>
           <rPr>
@@ -5481,7 +5510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I229" authorId="0" shapeId="0" xr:uid="{0E13DB01-CE0B-AD40-9B74-62129913BFA8}">
+    <comment ref="I229" authorId="0" shapeId="0" xr:uid="{4E2B6038-334C-5F4A-9E72-32C5F4A34AC2}">
       <text>
         <r>
           <rPr>
@@ -5500,7 +5529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I230" authorId="0" shapeId="0" xr:uid="{A88C568B-6B91-AD49-90AC-72D84D23CDA9}">
+    <comment ref="I230" authorId="0" shapeId="0" xr:uid="{5707B953-345B-904A-A9CE-55E853DB46E7}">
       <text>
         <r>
           <rPr>
@@ -5516,7 +5545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I231" authorId="0" shapeId="0" xr:uid="{D6EE0C6F-0210-904F-848A-093FECA45A31}">
+    <comment ref="I231" authorId="0" shapeId="0" xr:uid="{5489B042-FCED-6A43-A357-3651CDB27940}">
       <text>
         <r>
           <rPr>
@@ -5544,7 +5573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I232" authorId="0" shapeId="0" xr:uid="{4B54044F-9550-6B4D-BDD5-A514F1FA4CC1}">
+    <comment ref="I232" authorId="0" shapeId="0" xr:uid="{BB615D1F-67EB-0B4B-9B4D-BF60A9C77C97}">
       <text>
         <r>
           <rPr>
@@ -5564,7 +5593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I233" authorId="0" shapeId="0" xr:uid="{CD7D05DD-DAE4-9448-A995-7DF718B47BE5}">
+    <comment ref="I233" authorId="0" shapeId="0" xr:uid="{15E01AAB-8D60-E44D-81EA-FD552DD934B5}">
       <text>
         <r>
           <rPr>
@@ -5589,7 +5618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I234" authorId="0" shapeId="0" xr:uid="{B927169F-5CA8-964C-A6F3-65DA51CBB2B5}">
+    <comment ref="I234" authorId="0" shapeId="0" xr:uid="{0AD3A748-DAB6-754C-A26E-8BEDA6F12D6E}">
       <text>
         <r>
           <rPr>
@@ -5605,7 +5634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I235" authorId="0" shapeId="0" xr:uid="{A4C30E61-6B25-AD41-BE13-31CDEE9994B5}">
+    <comment ref="I235" authorId="0" shapeId="0" xr:uid="{1A4B7505-7A7D-2B48-A7E9-1FFB7FD04323}">
       <text>
         <r>
           <rPr>
@@ -5621,7 +5650,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I236" authorId="0" shapeId="0" xr:uid="{9E512871-F652-2445-A5F6-9930D6AFF414}">
+    <comment ref="I236" authorId="0" shapeId="0" xr:uid="{603284CF-0E46-8E44-BA5B-FF864DA732F4}">
       <text>
         <r>
           <rPr>
@@ -5637,7 +5666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I237" authorId="0" shapeId="0" xr:uid="{A7C57EAC-7D65-C24A-8192-03F0AC360BFA}">
+    <comment ref="I237" authorId="0" shapeId="0" xr:uid="{C75D8A67-BC3A-A146-88FE-139E85EF6433}">
       <text>
         <r>
           <rPr>
@@ -5656,7 +5685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I238" authorId="0" shapeId="0" xr:uid="{A0E0D9F0-52F5-534E-B856-6911E5B61BAB}">
+    <comment ref="I238" authorId="0" shapeId="0" xr:uid="{11857B4F-463D-7E49-9249-8C23ABD9216C}">
       <text>
         <r>
           <rPr>
@@ -5671,7 +5700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I239" authorId="0" shapeId="0" xr:uid="{5006CB0F-5C8A-4341-B072-8ED0C45BF38B}">
+    <comment ref="I239" authorId="0" shapeId="0" xr:uid="{B83170C7-6BD3-FB43-ACE0-4B3BDD4D282A}">
       <text>
         <r>
           <rPr>
@@ -5693,7 +5722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I240" authorId="0" shapeId="0" xr:uid="{4908E545-7F95-9641-A748-374B31510C3E}">
+    <comment ref="I240" authorId="0" shapeId="0" xr:uid="{DDE824A3-693A-014A-88B4-1F8E9F418063}">
       <text>
         <r>
           <rPr>
@@ -5709,7 +5738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I241" authorId="0" shapeId="0" xr:uid="{C8187621-52C7-C148-883D-056716C629EC}">
+    <comment ref="I241" authorId="0" shapeId="0" xr:uid="{E71D9C9D-5598-7E44-9B9A-C4C8091B720F}">
       <text>
         <r>
           <rPr>
@@ -5727,7 +5756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I242" authorId="0" shapeId="0" xr:uid="{0C083B2F-4C38-1945-8207-D1597EFC4185}">
+    <comment ref="I242" authorId="0" shapeId="0" xr:uid="{E6B467C3-E1DF-9543-B012-315C190D640F}">
       <text>
         <r>
           <rPr>
@@ -5743,7 +5772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I243" authorId="0" shapeId="0" xr:uid="{03AAD44B-63C8-494B-A864-357BABD88AA2}">
+    <comment ref="I243" authorId="0" shapeId="0" xr:uid="{B987477B-1928-F44C-AE06-C76940CCF418}">
       <text>
         <r>
           <rPr>
@@ -5759,7 +5788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I244" authorId="0" shapeId="0" xr:uid="{1744AA36-A9E4-4645-8DE9-81A2649E997B}">
+    <comment ref="I244" authorId="0" shapeId="0" xr:uid="{9199F696-7DE9-4340-BA5F-0DC5FA076866}">
       <text>
         <r>
           <rPr>
@@ -5775,7 +5804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I245" authorId="0" shapeId="0" xr:uid="{EF7C573D-9BA0-F24F-BD46-CABB3960DD92}">
+    <comment ref="I245" authorId="0" shapeId="0" xr:uid="{3054F03F-C0AD-AC4F-990C-D17A7ADCD911}">
       <text>
         <r>
           <rPr>
@@ -5791,7 +5820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I246" authorId="0" shapeId="0" xr:uid="{A2878FE1-A490-CD45-B9B9-B2D17367BD1B}">
+    <comment ref="I246" authorId="0" shapeId="0" xr:uid="{007DF422-3FFC-7F4B-80D5-F4E2C91D3165}">
       <text>
         <r>
           <rPr>
@@ -5806,7 +5835,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I247" authorId="0" shapeId="0" xr:uid="{4F41DCEF-6793-7441-9698-3354AABEB492}">
+    <comment ref="I247" authorId="0" shapeId="0" xr:uid="{822164AA-6599-9545-B4B1-CCABE57771ED}">
       <text>
         <r>
           <rPr>
@@ -5822,7 +5851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I248" authorId="0" shapeId="0" xr:uid="{BD143744-37E3-F646-AD7A-11ADF182CA2B}">
+    <comment ref="I248" authorId="0" shapeId="0" xr:uid="{30CF8857-A146-464D-A68B-9040FADE2142}">
       <text>
         <r>
           <rPr>
@@ -5837,7 +5866,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I249" authorId="0" shapeId="0" xr:uid="{9FBE941A-F572-9245-820B-6A1AFA243C1B}">
+    <comment ref="I249" authorId="0" shapeId="0" xr:uid="{ED3ECEDE-92E6-7E49-B57C-9EE7CDD16A52}">
       <text>
         <r>
           <rPr>
@@ -5856,7 +5885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I250" authorId="0" shapeId="0" xr:uid="{2879E451-BBDF-D64A-84A8-7290DFAD48DD}">
+    <comment ref="I250" authorId="0" shapeId="0" xr:uid="{7713CDCB-5416-9145-A9C9-662B95936045}">
       <text>
         <r>
           <rPr>
@@ -5872,7 +5901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I251" authorId="0" shapeId="0" xr:uid="{9FD6204E-845A-9B47-A85F-5A9F5D1F7DA4}">
+    <comment ref="I251" authorId="0" shapeId="0" xr:uid="{C1C35909-EAA4-EF45-8EB5-CE6D0EF5998C}">
       <text>
         <r>
           <rPr>
@@ -5891,7 +5920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I252" authorId="0" shapeId="0" xr:uid="{72D7CD34-13DC-D74A-87EE-1EF787D328C4}">
+    <comment ref="I252" authorId="0" shapeId="0" xr:uid="{126D6761-2F34-1549-A842-9AAF14288C74}">
       <text>
         <r>
           <rPr>
@@ -5919,7 +5948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I253" authorId="0" shapeId="0" xr:uid="{1843229A-DB0F-8741-B006-83600821F840}">
+    <comment ref="I253" authorId="0" shapeId="0" xr:uid="{D32E4AA5-91FF-304A-A1B6-A24543032D00}">
       <text>
         <r>
           <rPr>
@@ -5935,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I254" authorId="0" shapeId="0" xr:uid="{5273BEDC-494C-2B46-BC3E-14CB616CA99B}">
+    <comment ref="I254" authorId="0" shapeId="0" xr:uid="{59817223-1821-D943-AE3E-8F2B62A44DD1}">
       <text>
         <r>
           <rPr>
@@ -5962,7 +5991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I255" authorId="0" shapeId="0" xr:uid="{627CB76C-C6A2-254F-B7DC-424ED7DFEF4E}">
+    <comment ref="I255" authorId="0" shapeId="0" xr:uid="{EE82321A-EE04-2F42-ABB3-1C9000961906}">
       <text>
         <r>
           <rPr>
@@ -5978,7 +6007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I256" authorId="0" shapeId="0" xr:uid="{EE676D79-61B5-8149-927C-3312AF3AAA97}">
+    <comment ref="I256" authorId="0" shapeId="0" xr:uid="{BCC2B9AF-B6F0-0B43-9CAE-987654FAC515}">
       <text>
         <r>
           <rPr>
@@ -5993,7 +6022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I257" authorId="0" shapeId="0" xr:uid="{C1D8F2F6-8716-5547-B2A3-50C3AFB898B4}">
+    <comment ref="I257" authorId="0" shapeId="0" xr:uid="{FCB7BD37-3C24-D245-95C7-016434A957FC}">
       <text>
         <r>
           <rPr>
@@ -6009,7 +6038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I258" authorId="0" shapeId="0" xr:uid="{D7F91EA6-2D9A-1C4D-A328-66AE1471E516}">
+    <comment ref="I258" authorId="0" shapeId="0" xr:uid="{D89C5216-DB94-2B46-B0D8-3289B75561BF}">
       <text>
         <r>
           <rPr>
@@ -6028,7 +6057,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I259" authorId="0" shapeId="0" xr:uid="{7FECB5D6-A7BA-1142-B344-84A5E91F2426}">
+    <comment ref="I259" authorId="0" shapeId="0" xr:uid="{D8676727-0E1A-9040-8503-362961BD36BD}">
       <text>
         <r>
           <rPr>
@@ -6043,7 +6072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I260" authorId="0" shapeId="0" xr:uid="{117A0E85-5A64-9649-ABD7-849B4AE6993D}">
+    <comment ref="I260" authorId="0" shapeId="0" xr:uid="{49A0D2CA-4F6A-954E-89C1-91985863659B}">
       <text>
         <r>
           <rPr>
@@ -6059,7 +6088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I261" authorId="0" shapeId="0" xr:uid="{71C4A3FC-C5BB-0344-AA44-E721EC93EF9A}">
+    <comment ref="I261" authorId="0" shapeId="0" xr:uid="{E7694C46-6187-0440-AF15-B4E5AA7DB60A}">
       <text>
         <r>
           <rPr>
@@ -6077,7 +6106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I262" authorId="0" shapeId="0" xr:uid="{6E9708F3-19A1-DB49-B977-4EADE1FD211B}">
+    <comment ref="I262" authorId="0" shapeId="0" xr:uid="{E1CEBF6E-2ACE-4243-A7BC-58DD21D12393}">
       <text>
         <r>
           <rPr>
@@ -6093,7 +6122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I263" authorId="0" shapeId="0" xr:uid="{B2039641-EDBB-7F45-AD00-E4F1E20B2868}">
+    <comment ref="I263" authorId="0" shapeId="0" xr:uid="{CA3FFF3F-94AB-8A40-A471-0757BFA32C17}">
       <text>
         <r>
           <rPr>
@@ -6112,7 +6141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I264" authorId="0" shapeId="0" xr:uid="{FA0C8805-B387-E944-BBD7-A55F12EC5522}">
+    <comment ref="I264" authorId="0" shapeId="0" xr:uid="{34936AB9-DCE0-844D-9D43-6E6161062632}">
       <text>
         <r>
           <rPr>
@@ -6128,7 +6157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I265" authorId="0" shapeId="0" xr:uid="{E75C30D4-C4F7-8D49-88E0-DF84184164CB}">
+    <comment ref="I265" authorId="0" shapeId="0" xr:uid="{0B6170B7-FC81-A94E-9957-1476962534BB}">
       <text>
         <r>
           <rPr>
@@ -6146,7 +6175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I266" authorId="0" shapeId="0" xr:uid="{F3EF54E0-D367-2A4A-80B7-4A8D86541445}">
+    <comment ref="I266" authorId="0" shapeId="0" xr:uid="{CDF88906-7F8C-4A49-8F8A-89F86DA617AF}">
       <text>
         <r>
           <rPr>
@@ -6164,7 +6193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I267" authorId="0" shapeId="0" xr:uid="{AC758D10-95C2-6F46-92FE-1197234E7826}">
+    <comment ref="I267" authorId="0" shapeId="0" xr:uid="{BC6A6B55-3520-344C-8A46-6F53F217F073}">
       <text>
         <r>
           <rPr>
@@ -6182,7 +6211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I268" authorId="0" shapeId="0" xr:uid="{42E8DFE0-F529-9B43-92EB-9D61DF7DEC19}">
+    <comment ref="I268" authorId="0" shapeId="0" xr:uid="{75EEB886-C097-304F-94C4-387671F7BFCF}">
       <text>
         <r>
           <rPr>
@@ -6197,7 +6226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I269" authorId="0" shapeId="0" xr:uid="{D1BDFF14-B183-334C-ADA5-49352981ACC3}">
+    <comment ref="I269" authorId="0" shapeId="0" xr:uid="{C8A3F29D-FB42-AE41-8C50-C2CC0DDF9AC0}">
       <text>
         <r>
           <rPr>
@@ -6216,7 +6245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I270" authorId="0" shapeId="0" xr:uid="{D522FE13-638F-FF4E-BA48-22CE20EF1B2A}">
+    <comment ref="I270" authorId="0" shapeId="0" xr:uid="{FFDAA77A-02A0-C041-B65B-7D22D4F37B6D}">
       <text>
         <r>
           <rPr>
@@ -6232,7 +6261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I271" authorId="0" shapeId="0" xr:uid="{36A8172D-1603-6A45-BCC7-2C2C21203D5F}">
+    <comment ref="I271" authorId="0" shapeId="0" xr:uid="{E96B6831-0F09-AD4C-91E5-C2709024D177}">
       <text>
         <r>
           <rPr>
@@ -6250,7 +6279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I272" authorId="0" shapeId="0" xr:uid="{5BCD2E59-88BE-9747-8D6E-9E59FED6C3FE}">
+    <comment ref="I272" authorId="0" shapeId="0" xr:uid="{D15AAC17-25A8-EE47-8E9C-910C6366CCB3}">
       <text>
         <r>
           <rPr>
@@ -6266,7 +6295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I273" authorId="0" shapeId="0" xr:uid="{7DE37DBC-0538-654E-AE59-39ECDA9E2828}">
+    <comment ref="I273" authorId="0" shapeId="0" xr:uid="{707872CA-14B8-9047-9610-17F8A740BB7C}">
       <text>
         <r>
           <rPr>
@@ -6285,7 +6314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I274" authorId="0" shapeId="0" xr:uid="{61CA4F98-6464-5244-99F7-62285B1B2F3E}">
+    <comment ref="I274" authorId="0" shapeId="0" xr:uid="{CAE70F3A-6AD5-0E43-AB89-1B5CFA40744A}">
       <text>
         <r>
           <rPr>
@@ -6301,7 +6330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I275" authorId="0" shapeId="0" xr:uid="{147B511C-AC23-584D-8C91-4A90FF41B075}">
+    <comment ref="I275" authorId="0" shapeId="0" xr:uid="{B569FD6A-C118-F544-BB8A-5C6242A4AC50}">
       <text>
         <r>
           <rPr>
@@ -6317,7 +6346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I276" authorId="0" shapeId="0" xr:uid="{D84ACB8E-F43F-6747-9F6C-2D3143945DC3}">
+    <comment ref="I276" authorId="0" shapeId="0" xr:uid="{8507B332-DA9A-B240-AA53-E3B0FC4413EB}">
       <text>
         <r>
           <rPr>
@@ -6335,7 +6364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I277" authorId="0" shapeId="0" xr:uid="{50E6B05D-C45E-454C-B06E-081C6587E1A7}">
+    <comment ref="I277" authorId="0" shapeId="0" xr:uid="{D750ADB1-8C16-3D40-B5A6-EC14B044F718}">
       <text>
         <r>
           <rPr>
@@ -6351,7 +6380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I278" authorId="0" shapeId="0" xr:uid="{DCEFA173-6036-924E-AC38-2D5E230305BE}">
+    <comment ref="I278" authorId="0" shapeId="0" xr:uid="{3B7BD0F5-85BC-5847-BA85-8F8A1E8A1701}">
       <text>
         <r>
           <rPr>
@@ -6367,7 +6396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I279" authorId="0" shapeId="0" xr:uid="{759E4757-7D6A-B646-BE82-0DFD1ED76DFF}">
+    <comment ref="I279" authorId="0" shapeId="0" xr:uid="{C4683E4D-EA94-F949-BF46-9BCBA08967B6}">
       <text>
         <r>
           <rPr>
@@ -6383,7 +6412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I280" authorId="0" shapeId="0" xr:uid="{C4A85C75-680E-CF49-A192-87C5F84B8931}">
+    <comment ref="I280" authorId="0" shapeId="0" xr:uid="{4A8D99F1-1D51-5342-91B9-2050AB6F9123}">
       <text>
         <r>
           <rPr>
@@ -6403,7 +6432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I281" authorId="0" shapeId="0" xr:uid="{97E4C37B-8E39-2A43-93C4-FEF6FF09BB56}">
+    <comment ref="I281" authorId="0" shapeId="0" xr:uid="{D9B229F4-1E91-784C-9F62-2475FABC5BFB}">
       <text>
         <r>
           <rPr>
@@ -6421,7 +6450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I282" authorId="0" shapeId="0" xr:uid="{44899366-4304-8640-832F-94AFA0C19F17}">
+    <comment ref="I282" authorId="0" shapeId="0" xr:uid="{BDADAC3E-074C-EC46-8E30-102FE0BC9647}">
       <text>
         <r>
           <rPr>
@@ -6449,7 +6478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I283" authorId="0" shapeId="0" xr:uid="{5C5A2032-6DE1-7B4F-85BA-14D5E8D7E409}">
+    <comment ref="I283" authorId="0" shapeId="0" xr:uid="{294DCC3A-A99C-884D-B42C-859829A2777C}">
       <text>
         <r>
           <rPr>
@@ -6478,7 +6507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I284" authorId="0" shapeId="0" xr:uid="{1573BD22-5E42-2E4D-9618-FC1681F5D83F}">
+    <comment ref="I284" authorId="0" shapeId="0" xr:uid="{B8E3533E-089A-6347-B923-18FF3F0909A1}">
       <text>
         <r>
           <rPr>
@@ -6495,7 +6524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I285" authorId="0" shapeId="0" xr:uid="{3B9F29C2-FF8B-6147-A1E0-A10DD9C9F912}">
+    <comment ref="I285" authorId="0" shapeId="0" xr:uid="{9E912087-25D8-F44D-89F2-3C2FEA356A61}">
       <text>
         <r>
           <rPr>
@@ -6524,7 +6553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I286" authorId="0" shapeId="0" xr:uid="{2F84DDBB-925E-6349-9497-25EAC3A6ABDB}">
+    <comment ref="I286" authorId="0" shapeId="0" xr:uid="{4D457188-CEB8-D24A-A11E-14A86AE74994}">
       <text>
         <r>
           <rPr>
@@ -6553,7 +6582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I287" authorId="0" shapeId="0" xr:uid="{1DDB0E4C-9FB0-AA45-8014-D70C02C10689}">
+    <comment ref="I287" authorId="0" shapeId="0" xr:uid="{9402037A-572F-E74A-B579-C404BC590F34}">
       <text>
         <r>
           <rPr>
@@ -6568,7 +6597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I288" authorId="0" shapeId="0" xr:uid="{E132395E-67A7-B040-8E12-4DA44FF68530}">
+    <comment ref="I288" authorId="0" shapeId="0" xr:uid="{238CCC8F-97A2-7F4A-94D0-0E4E2BE4B363}">
       <text>
         <r>
           <rPr>
@@ -6586,7 +6615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I289" authorId="0" shapeId="0" xr:uid="{114A5DBD-F4B4-B44E-AAAE-97A4F6A43977}">
+    <comment ref="I289" authorId="0" shapeId="0" xr:uid="{31EDD7BF-2A67-044B-A656-1102CB6D25E5}">
       <text>
         <r>
           <rPr>
@@ -6606,7 +6635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I290" authorId="0" shapeId="0" xr:uid="{8E4523BB-CA5D-5640-A101-0A22A125CEE8}">
+    <comment ref="I290" authorId="0" shapeId="0" xr:uid="{4C567587-3CAD-6242-B5C1-190C2AE06422}">
       <text>
         <r>
           <rPr>
@@ -6625,7 +6654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I291" authorId="0" shapeId="0" xr:uid="{170656E8-D684-3A43-AFCB-2398ACE6640F}">
+    <comment ref="I291" authorId="0" shapeId="0" xr:uid="{E6B0B248-B7EC-784D-ACFF-4C6DBBDCD5B0}">
       <text>
         <r>
           <rPr>
@@ -6644,7 +6673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I292" authorId="0" shapeId="0" xr:uid="{903937B9-5E6E-2F40-9A69-EC40AA0A72B1}">
+    <comment ref="I292" authorId="0" shapeId="0" xr:uid="{762CCB2B-CA6C-C34C-82E5-D3AA041DA5BE}">
       <text>
         <r>
           <rPr>
@@ -6664,7 +6693,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I293" authorId="0" shapeId="0" xr:uid="{114C6CB1-A9BE-1941-A315-D3420CBE2D0B}">
+    <comment ref="I293" authorId="0" shapeId="0" xr:uid="{52B78231-59AE-1E46-BD4F-68A49C062E88}">
       <text>
         <r>
           <rPr>
@@ -6693,7 +6722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I294" authorId="0" shapeId="0" xr:uid="{3A701C0A-097A-664F-8EEA-900E6959E275}">
+    <comment ref="I294" authorId="0" shapeId="0" xr:uid="{F254CE40-C2AD-C640-94D8-0BE14BB82384}">
       <text>
         <r>
           <rPr>
@@ -6714,7 +6743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I295" authorId="0" shapeId="0" xr:uid="{399C088A-E371-6D4B-AD5B-F24160A65DAE}">
+    <comment ref="I295" authorId="0" shapeId="0" xr:uid="{4F0B15B8-C7E3-F048-B659-BECDDB14E3E1}">
       <text>
         <r>
           <rPr>
@@ -6729,7 +6758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I296" authorId="0" shapeId="0" xr:uid="{487F180E-FBED-D540-88BC-A6C86846DA6A}">
+    <comment ref="I296" authorId="0" shapeId="0" xr:uid="{A780D1D1-C7F6-F74E-926E-AD16D62B62BE}">
       <text>
         <r>
           <rPr>
@@ -6749,7 +6778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I297" authorId="0" shapeId="0" xr:uid="{4763D7D6-9ACA-F949-8DCD-AEFB4E4A2DB0}">
+    <comment ref="I297" authorId="0" shapeId="0" xr:uid="{D697DC4B-626F-CB42-A30E-041534EC809D}">
       <text>
         <r>
           <rPr>
@@ -6768,7 +6797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I298" authorId="0" shapeId="0" xr:uid="{1CFE209D-1393-3F4B-99FE-A74D084609CE}">
+    <comment ref="I298" authorId="0" shapeId="0" xr:uid="{10D181C3-4A74-D24C-A0E7-24A9A34306F8}">
       <text>
         <r>
           <rPr>
@@ -6788,7 +6817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I299" authorId="0" shapeId="0" xr:uid="{128C9B30-5E7D-C24F-8F85-A7902BDCEABE}">
+    <comment ref="I299" authorId="0" shapeId="0" xr:uid="{FAED49EB-8719-2148-A4D9-EBF20B313E37}">
       <text>
         <r>
           <rPr>
@@ -6812,7 +6841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I300" authorId="0" shapeId="0" xr:uid="{61A31255-C086-4E45-8CC0-19B754CA933E}">
+    <comment ref="I300" authorId="0" shapeId="0" xr:uid="{B705384C-D315-0F47-9752-67EFA1A3AF80}">
       <text>
         <r>
           <rPr>
@@ -6827,7 +6856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I301" authorId="0" shapeId="0" xr:uid="{E130676C-BE05-0849-ACBB-4BA36C8ECB8F}">
+    <comment ref="I301" authorId="0" shapeId="0" xr:uid="{D97BC0BE-7580-104B-A9D4-A9826F1DED78}">
       <text>
         <r>
           <rPr>
@@ -6843,7 +6872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I302" authorId="0" shapeId="0" xr:uid="{96D77AAB-4EE3-EC42-969E-AE4B6E7A50B0}">
+    <comment ref="I302" authorId="0" shapeId="0" xr:uid="{0C46EDFA-74A0-154B-B480-105827AA2403}">
       <text>
         <r>
           <rPr>
@@ -6859,7 +6888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I303" authorId="0" shapeId="0" xr:uid="{A311B80F-B153-8549-AAC6-17D24762AD40}">
+    <comment ref="I303" authorId="0" shapeId="0" xr:uid="{F071D1CC-CC1B-954C-A757-01801760B922}">
       <text>
         <r>
           <rPr>
@@ -6877,7 +6906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I304" authorId="0" shapeId="0" xr:uid="{FCFFBDA3-2A58-BB40-9757-E4822984567A}">
+    <comment ref="I304" authorId="0" shapeId="0" xr:uid="{069718CC-FD0F-A541-9885-A39CED86812D}">
       <text>
         <r>
           <rPr>
@@ -6894,7 +6923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I305" authorId="0" shapeId="0" xr:uid="{B2DD4BAE-0531-C443-B326-B2BA6E0B6330}">
+    <comment ref="I305" authorId="0" shapeId="0" xr:uid="{FADF5F13-6D5D-DC43-92DE-1D94F40A71F9}">
       <text>
         <r>
           <rPr>
@@ -6910,7 +6939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I306" authorId="0" shapeId="0" xr:uid="{2E7A148C-5A34-8843-9922-46C13293C789}">
+    <comment ref="I306" authorId="0" shapeId="0" xr:uid="{EA164EF4-69CA-014F-9D29-9F470C2FAC62}">
       <text>
         <r>
           <rPr>
@@ -6926,7 +6955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I307" authorId="0" shapeId="0" xr:uid="{B175EE86-09A7-1049-A3F8-1C48A0063BB1}">
+    <comment ref="I307" authorId="0" shapeId="0" xr:uid="{F1CC2CC7-D833-144E-80CE-11D3C509F1D2}">
       <text>
         <r>
           <rPr>
@@ -6948,7 +6977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I308" authorId="0" shapeId="0" xr:uid="{1F2FF6AB-0A4A-A74B-9D99-6A64809691F4}">
+    <comment ref="I308" authorId="0" shapeId="0" xr:uid="{BA88B69D-A5F7-1D43-B843-A8D63C774A89}">
       <text>
         <r>
           <rPr>
@@ -6964,7 +6993,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I309" authorId="0" shapeId="0" xr:uid="{F28498FF-A3F1-8949-849B-6EA04437E3B0}">
+    <comment ref="I309" authorId="0" shapeId="0" xr:uid="{B1051356-77CE-C040-98E7-3A139BDB21F1}">
       <text>
         <r>
           <rPr>
@@ -6980,7 +7009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I310" authorId="0" shapeId="0" xr:uid="{EF246102-42DE-4E45-B2FC-EE026DFF7712}">
+    <comment ref="I310" authorId="0" shapeId="0" xr:uid="{91BC1D89-B2BE-6F4C-B8FF-910AFE19F2A4}">
       <text>
         <r>
           <rPr>
@@ -7000,7 +7029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I311" authorId="0" shapeId="0" xr:uid="{87510263-2EFD-C14A-8F70-8B4706A715CD}">
+    <comment ref="I311" authorId="0" shapeId="0" xr:uid="{441CAC05-AC5A-214D-9860-94C91B52BAC3}">
       <text>
         <r>
           <rPr>
@@ -7024,7 +7053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I312" authorId="0" shapeId="0" xr:uid="{739F5283-B0F6-6848-8E7E-E38B1B00C71A}">
+    <comment ref="I312" authorId="0" shapeId="0" xr:uid="{4A9C8FB5-4DCE-544C-81A5-2E9B4820EA93}">
       <text>
         <r>
           <rPr>
@@ -7046,7 +7075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I313" authorId="0" shapeId="0" xr:uid="{9CC07160-E800-3E44-A2A7-63A8CA6AAB8E}">
+    <comment ref="I313" authorId="0" shapeId="0" xr:uid="{8D3C3500-80BB-E44B-A4E4-21D9C59A7294}">
       <text>
         <r>
           <rPr>
@@ -7068,7 +7097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I314" authorId="0" shapeId="0" xr:uid="{1F881B31-EEAE-B143-BC53-3A552E2EA4AA}">
+    <comment ref="I314" authorId="0" shapeId="0" xr:uid="{A7BE04AD-0E36-C04B-A488-F85498DB7E55}">
       <text>
         <r>
           <rPr>
@@ -7096,7 +7125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I315" authorId="0" shapeId="0" xr:uid="{EBCED108-9325-D341-9B50-E39C15A316AD}">
+    <comment ref="I315" authorId="0" shapeId="0" xr:uid="{B6269AF0-2B3A-0847-AC6E-7C87A6B3C8C6}">
       <text>
         <r>
           <rPr>
@@ -7115,7 +7144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I316" authorId="0" shapeId="0" xr:uid="{7AB446CA-E99E-6143-BCB0-0017D58306A7}">
+    <comment ref="I316" authorId="0" shapeId="0" xr:uid="{4CB33A19-ADFE-B949-9651-E80760F86AB8}">
       <text>
         <r>
           <rPr>
@@ -7135,7 +7164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I317" authorId="0" shapeId="0" xr:uid="{AAA23A79-6BD8-7A4F-AF50-C7E9656F5FBF}">
+    <comment ref="I317" authorId="0" shapeId="0" xr:uid="{4E438ED6-45CD-8F46-B5D6-3707901372FE}">
       <text>
         <r>
           <rPr>
@@ -7153,7 +7182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I318" authorId="0" shapeId="0" xr:uid="{8835C0DB-90BD-C64D-BBB9-82352999D1E5}">
+    <comment ref="I318" authorId="0" shapeId="0" xr:uid="{CE54E930-FB04-C341-9C51-151D6A2F18D3}">
       <text>
         <r>
           <rPr>
@@ -7168,7 +7197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I319" authorId="0" shapeId="0" xr:uid="{CA038CEB-590A-7140-9962-51B6293154FE}">
+    <comment ref="I319" authorId="0" shapeId="0" xr:uid="{73B85D92-3E8A-3841-AC7A-E2D2C7F02541}">
       <text>
         <r>
           <rPr>
@@ -7192,7 +7221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I320" authorId="0" shapeId="0" xr:uid="{5B6D4963-151B-E444-A652-BF7F2B52B07B}">
+    <comment ref="I320" authorId="0" shapeId="0" xr:uid="{6A08117A-D460-4E43-8DF0-8A59470FBC44}">
       <text>
         <r>
           <rPr>
@@ -7211,7 +7240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I321" authorId="0" shapeId="0" xr:uid="{45A9D267-9020-DB46-8AF9-7AAB97C5C14F}">
+    <comment ref="I321" authorId="0" shapeId="0" xr:uid="{54B0DA6D-4A9E-A84D-8266-A7794C57301C}">
       <text>
         <r>
           <rPr>
@@ -7227,7 +7256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I322" authorId="0" shapeId="0" xr:uid="{C3949E62-7C36-F542-B137-E0AAE84EA535}">
+    <comment ref="I322" authorId="0" shapeId="0" xr:uid="{739FF6F8-AE7A-934D-981A-4C7349854D7D}">
       <text>
         <r>
           <rPr>
@@ -7245,7 +7274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I323" authorId="0" shapeId="0" xr:uid="{DC9F569C-345A-B948-9C1C-F31FF3B7C7EE}">
+    <comment ref="I323" authorId="0" shapeId="0" xr:uid="{A6E350EA-BCF8-FD40-BB54-B1E93FE5B88A}">
       <text>
         <r>
           <rPr>
@@ -7260,7 +7289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I324" authorId="0" shapeId="0" xr:uid="{FF606074-8148-E54E-B521-38BA97DF0FC8}">
+    <comment ref="I324" authorId="0" shapeId="0" xr:uid="{BDAC4BE4-B82F-034F-B4AB-29060C34DF22}">
       <text>
         <r>
           <rPr>
@@ -7279,7 +7308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I325" authorId="0" shapeId="0" xr:uid="{AD1E0ED2-B5DF-B34B-9662-CA533F02CE38}">
+    <comment ref="I325" authorId="0" shapeId="0" xr:uid="{EB54B8DF-2CEE-D240-9F27-97207B743166}">
       <text>
         <r>
           <rPr>
@@ -7308,7 +7337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I326" authorId="0" shapeId="0" xr:uid="{17896D89-6612-9542-B405-8391EDCF80A7}">
+    <comment ref="I326" authorId="0" shapeId="0" xr:uid="{F09BA5BA-1852-4C4C-9896-253100D27EF9}">
       <text>
         <r>
           <rPr>
@@ -7326,7 +7355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I327" authorId="0" shapeId="0" xr:uid="{DCECD15F-293E-744E-9E5C-BBD1AFCA0CD5}">
+    <comment ref="I327" authorId="0" shapeId="0" xr:uid="{213ED458-3BF5-5444-BDDD-5273D5422B7D}">
       <text>
         <r>
           <rPr>
@@ -7355,7 +7384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I328" authorId="0" shapeId="0" xr:uid="{B4908097-83EF-1F41-BC96-C47FACDAC67B}">
+    <comment ref="I328" authorId="0" shapeId="0" xr:uid="{3DEAFA99-95F0-0047-B23F-1D7A6361C21F}">
       <text>
         <r>
           <rPr>
@@ -7371,7 +7400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I329" authorId="0" shapeId="0" xr:uid="{DBB14B07-5D52-7E42-866C-7B27A91DC7AA}">
+    <comment ref="I329" authorId="0" shapeId="0" xr:uid="{584B6D46-22E4-004E-8B66-091E1CF8C6D7}">
       <text>
         <r>
           <rPr>
@@ -7387,7 +7416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I330" authorId="0" shapeId="0" xr:uid="{666758DE-2819-9947-ADDF-73E764071AC3}">
+    <comment ref="I330" authorId="0" shapeId="0" xr:uid="{7EA63503-0D69-EE40-88A4-AE4412BF6255}">
       <text>
         <r>
           <rPr>
@@ -7416,7 +7445,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I331" authorId="0" shapeId="0" xr:uid="{D44F1D8A-0DAB-4043-928B-A927EB847B8D}">
+    <comment ref="I331" authorId="0" shapeId="0" xr:uid="{C45B3B4A-AB5F-194C-9345-6F463683AFC1}">
       <text>
         <r>
           <rPr>
@@ -7441,7 +7470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I332" authorId="0" shapeId="0" xr:uid="{311763D8-A9D9-5E45-BEF9-A833B6B408E2}">
+    <comment ref="I332" authorId="0" shapeId="0" xr:uid="{ECB7B9A8-A606-AA47-8E1D-190BD6E43593}">
       <text>
         <r>
           <rPr>
@@ -7460,7 +7489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I333" authorId="0" shapeId="0" xr:uid="{AA297D14-C923-4E4D-AD87-4BD997113B90}">
+    <comment ref="I333" authorId="0" shapeId="0" xr:uid="{5CFF66C0-CBE0-4642-9D25-3BA053BCC668}">
       <text>
         <r>
           <rPr>
@@ -7484,7 +7513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I334" authorId="0" shapeId="0" xr:uid="{675B6CAD-70C2-7643-95F9-708F83E171E4}">
+    <comment ref="I334" authorId="0" shapeId="0" xr:uid="{8E1F3995-23C3-9347-8DC5-552B8FC25FCB}">
       <text>
         <r>
           <rPr>
@@ -7503,7 +7532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I335" authorId="0" shapeId="0" xr:uid="{38F8DA7B-DEF6-C349-BA4C-98CB8764941A}">
+    <comment ref="I335" authorId="0" shapeId="0" xr:uid="{77392464-6CC4-F442-B416-E1243B789C97}">
       <text>
         <r>
           <rPr>
@@ -7522,7 +7551,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I336" authorId="0" shapeId="0" xr:uid="{8DF9F0C0-E79F-0844-B3EB-B7CB36853085}">
+    <comment ref="I336" authorId="0" shapeId="0" xr:uid="{E116FD34-2D62-2443-9C1D-5CD173CB761B}">
       <text>
         <r>
           <rPr>
@@ -7541,7 +7570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I337" authorId="0" shapeId="0" xr:uid="{50C49E25-36AC-8B44-A58F-0586F43F0B6C}">
+    <comment ref="I337" authorId="0" shapeId="0" xr:uid="{84CBB1BD-DEA3-7A44-A697-ACB51ABAC997}">
       <text>
         <r>
           <rPr>
@@ -7569,7 +7598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I338" authorId="0" shapeId="0" xr:uid="{41353585-2526-CA4C-9D05-690DDE8CD8B9}">
+    <comment ref="I338" authorId="0" shapeId="0" xr:uid="{7DCB2D7D-AC6D-004B-8BEA-6B6F7EBB7E6D}">
       <text>
         <r>
           <rPr>
@@ -7588,7 +7617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I339" authorId="0" shapeId="0" xr:uid="{59B08D91-9C25-D148-8BF9-0D6EF04CB4E6}">
+    <comment ref="I339" authorId="0" shapeId="0" xr:uid="{EFCFE2E8-0426-D540-B5EA-C39A04B62C7B}">
       <text>
         <r>
           <rPr>
@@ -7618,7 +7647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I340" authorId="0" shapeId="0" xr:uid="{A322A017-D87F-3940-98EE-543F021B3AD4}">
+    <comment ref="I340" authorId="0" shapeId="0" xr:uid="{6EFCD771-F87E-854E-B0BF-30B836D6E1B3}">
       <text>
         <r>
           <rPr>
@@ -7637,7 +7666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I341" authorId="0" shapeId="0" xr:uid="{C5B67FC4-88FB-D541-B864-DDD3A6C10D90}">
+    <comment ref="I341" authorId="0" shapeId="0" xr:uid="{2164C086-E1D6-5B48-984C-8C40C58D5692}">
       <text>
         <r>
           <rPr>
@@ -7653,7 +7682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I342" authorId="0" shapeId="0" xr:uid="{D9B4A591-0F88-CE42-9BD1-2C165BC882BB}">
+    <comment ref="I342" authorId="0" shapeId="0" xr:uid="{197FC39B-C9F8-094F-9ECB-73894C8F25BD}">
       <text>
         <r>
           <rPr>
@@ -7672,7 +7701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I343" authorId="0" shapeId="0" xr:uid="{2F4072FD-0916-C848-9B10-6CF7137CFB72}">
+    <comment ref="I343" authorId="0" shapeId="0" xr:uid="{BC91C05A-A910-B04C-9FBD-5AEACE9B9B1A}">
       <text>
         <r>
           <rPr>
@@ -7701,7 +7730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I344" authorId="0" shapeId="0" xr:uid="{3E3E8E80-70A7-FF45-8434-73CB98FD9F4B}">
+    <comment ref="I344" authorId="0" shapeId="0" xr:uid="{C334D55C-5000-4E45-8076-93F63CF63DDA}">
       <text>
         <r>
           <rPr>
@@ -7720,7 +7749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I345" authorId="0" shapeId="0" xr:uid="{5BCB777D-D1FF-DA4D-80CA-96994D31D5DD}">
+    <comment ref="I345" authorId="0" shapeId="0" xr:uid="{08099C3F-D499-A04B-B6D4-D353CD8BC820}">
       <text>
         <r>
           <rPr>
@@ -7736,7 +7765,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I346" authorId="0" shapeId="0" xr:uid="{154BC165-FC67-FC40-88E3-A2E5FEC9CEFB}">
+    <comment ref="I346" authorId="0" shapeId="0" xr:uid="{474EF982-D1AB-2C4F-875D-70EEA34CCD15}">
       <text>
         <r>
           <rPr>
@@ -7755,7 +7784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I347" authorId="0" shapeId="0" xr:uid="{C621C3B4-55AB-144D-892F-BAE0866625B5}">
+    <comment ref="I347" authorId="0" shapeId="0" xr:uid="{20AD4FC5-BE41-1545-9C3D-FBED6F73995D}">
       <text>
         <r>
           <rPr>
@@ -7784,7 +7813,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I348" authorId="0" shapeId="0" xr:uid="{315CE74B-393B-4B41-A1E8-95967E279702}">
+    <comment ref="I348" authorId="0" shapeId="0" xr:uid="{17AD7F34-6BC3-3C45-87B3-BCB8DCEB22DD}">
       <text>
         <r>
           <rPr>
@@ -7800,7 +7829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I349" authorId="0" shapeId="0" xr:uid="{D1501190-063E-DD4A-B865-0E621C24D767}">
+    <comment ref="I349" authorId="0" shapeId="0" xr:uid="{21159CCD-31B3-274A-8C53-E0F405FCDF24}">
       <text>
         <r>
           <rPr>
@@ -7815,7 +7844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I350" authorId="0" shapeId="0" xr:uid="{7931F113-241C-FC4F-8753-E2F79206BB8F}">
+    <comment ref="I350" authorId="0" shapeId="0" xr:uid="{D4285962-A75B-4B4D-9687-11FEE56624BD}">
       <text>
         <r>
           <rPr>
@@ -7827,14 +7856,14 @@
           </rPr>
           <t>X-White: 조환지
 X-Black: 박규원
-John Faust: 이석준
-Gretchen: 김수연
-Guardian: 
+존 파우스트: 이석준
+그레첸: 김수연
+가디언: 
 유민영 서채이 신윤재 조민호 이설아</t>
         </r>
       </text>
     </comment>
-    <comment ref="I351" authorId="0" shapeId="0" xr:uid="{5C5B055A-FADB-E147-9C10-714BB1415521}">
+    <comment ref="I351" authorId="0" shapeId="0" xr:uid="{9E1A647E-6653-0F47-81F6-63E6C352115B}">
       <text>
         <r>
           <rPr>
@@ -7853,7 +7882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I352" authorId="0" shapeId="0" xr:uid="{D4C7AF41-DD8E-2049-B6F3-94906B0382BA}">
+    <comment ref="I352" authorId="0" shapeId="0" xr:uid="{C170AE85-5F1E-B441-BCDA-EF047C703FDB}">
       <text>
         <r>
           <rPr>
@@ -7874,7 +7903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I353" authorId="0" shapeId="0" xr:uid="{5CC500D8-9827-4547-916B-950FE59A3E7A}">
+    <comment ref="I353" authorId="0" shapeId="0" xr:uid="{38E50066-D7C3-DE49-8673-E942DC0B5375}">
       <text>
         <r>
           <rPr>
@@ -7889,7 +7918,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I354" authorId="0" shapeId="0" xr:uid="{F404671A-3F84-9B4D-81D7-4CF124DCBC67}">
+    <comment ref="I354" authorId="0" shapeId="0" xr:uid="{44FBB1D0-5C00-DD49-B3D7-FC71AFE20D2A}">
       <text>
         <r>
           <rPr>
@@ -7905,7 +7934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I355" authorId="0" shapeId="0" xr:uid="{CB0E6140-594E-EB47-BB42-751F720D27A8}">
+    <comment ref="I355" authorId="0" shapeId="0" xr:uid="{35CF5966-AD1D-F243-8E0B-1F3EAA5FE982}">
       <text>
         <r>
           <rPr>
@@ -7922,23 +7951,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="I356" authorId="0" shapeId="0" xr:uid="{94328512-EEEA-2E43-9528-34D6D86777F1}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Simon: 이준우
-Kosmo: 김민범
-Michael: 이진혁</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I357" authorId="0" shapeId="0" xr:uid="{67115E88-E831-644C-9155-BAB24F052E08}">
+    <comment ref="I356" authorId="0" shapeId="0" xr:uid="{351C2317-709B-974E-ABB2-4646A462C9E2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>사이먼 세즈: 이준우
+코스모: 김민범
+마이클: 이진혁</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I357" authorId="0" shapeId="0" xr:uid="{711756CB-8C15-014F-A6E6-1AF592577E18}">
       <text>
         <r>
           <rPr>
@@ -7957,7 +7986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I358" authorId="0" shapeId="0" xr:uid="{0A1EBE31-107D-D145-AFE3-8E37CD18A63D}">
+    <comment ref="I358" authorId="0" shapeId="0" xr:uid="{286EC909-860D-2140-808B-104A30F3C545}">
       <text>
         <r>
           <rPr>
@@ -7974,7 +8003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I359" authorId="0" shapeId="0" xr:uid="{00E6A5C4-F0A2-2A4B-8224-E97C0E720AEA}">
+    <comment ref="I359" authorId="0" shapeId="0" xr:uid="{AFF87048-BC64-E240-A258-B8D8422D7C30}">
       <text>
         <r>
           <rPr>
@@ -7993,7 +8022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I360" authorId="0" shapeId="0" xr:uid="{01C70DC0-CB3E-BF45-A98E-5B9B50100BBB}">
+    <comment ref="I360" authorId="0" shapeId="0" xr:uid="{00863649-15A3-6C4F-9139-768123618A2B}">
       <text>
         <r>
           <rPr>
@@ -8010,7 +8039,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I361" authorId="0" shapeId="0" xr:uid="{8FA7C05E-3F90-D743-98F6-D4999749D146}">
+    <comment ref="I361" authorId="0" shapeId="0" xr:uid="{D4687ADE-EA77-7344-A21F-AAC0AF3C8E1D}">
       <text>
         <r>
           <rPr>
@@ -8027,7 +8056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I362" authorId="0" shapeId="0" xr:uid="{9F507DEB-7B0C-8944-AB99-256EA4342E63}">
+    <comment ref="I362" authorId="0" shapeId="0" xr:uid="{22688EFB-FF20-414B-B8FB-D32527EDECC7}">
       <text>
         <r>
           <rPr>
@@ -8044,7 +8073,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I363" authorId="0" shapeId="0" xr:uid="{01DA5FCB-53E4-FB43-847F-981864004A29}">
+    <comment ref="I363" authorId="0" shapeId="0" xr:uid="{E331C90D-AEDB-BA4B-9D6F-AEDADC5608D6}">
       <text>
         <r>
           <rPr>
@@ -8069,7 +8098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I364" authorId="0" shapeId="0" xr:uid="{1C7D8FF6-5557-6343-B4AA-1D5588E10679}">
+    <comment ref="I364" authorId="0" shapeId="0" xr:uid="{E4B377F1-CD05-334C-A37A-0D7D2D36F0EE}">
       <text>
         <r>
           <rPr>
@@ -8086,7 +8115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I365" authorId="0" shapeId="0" xr:uid="{C7B86A90-8E1F-444A-8ECD-45804D6E3AFE}">
+    <comment ref="I365" authorId="0" shapeId="0" xr:uid="{F18CF403-FF77-3B41-B904-C51EE13B6106}">
       <text>
         <r>
           <rPr>
@@ -8103,7 +8132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I366" authorId="0" shapeId="0" xr:uid="{F94B983E-70FB-7147-A841-CB5BF0A9F452}">
+    <comment ref="I366" authorId="0" shapeId="0" xr:uid="{CE253AD8-4F90-7648-B1DD-A6AD388B1BFD}">
       <text>
         <r>
           <rPr>
@@ -8120,7 +8149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I367" authorId="0" shapeId="0" xr:uid="{868F3697-6095-FD4B-B6A7-C1E9A5D60E3A}">
+    <comment ref="I367" authorId="0" shapeId="0" xr:uid="{3B45BF28-EE17-4C43-81C0-FE9925EAEAAA}">
       <text>
         <r>
           <rPr>
@@ -8137,7 +8166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I368" authorId="0" shapeId="0" xr:uid="{A1E2671F-5C24-5247-BE1A-4A1F9DC02A93}">
+    <comment ref="I368" authorId="0" shapeId="0" xr:uid="{4A3E0464-A9E7-D143-8C99-C45C73C4EE61}">
       <text>
         <r>
           <rPr>
@@ -8154,7 +8183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I369" authorId="0" shapeId="0" xr:uid="{34716257-7C9F-394E-BC72-BE6E385BE6CF}">
+    <comment ref="I369" authorId="0" shapeId="0" xr:uid="{F809BA46-2C30-EC49-989C-C21E2982A2D8}">
       <text>
         <r>
           <rPr>
@@ -8172,7 +8201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I370" authorId="0" shapeId="0" xr:uid="{8D39C2E8-9518-8E47-BDB4-80514CB380A8}">
+    <comment ref="I370" authorId="0" shapeId="0" xr:uid="{693A4184-A1D9-C643-8CDB-C8044246DD75}">
       <text>
         <r>
           <rPr>
@@ -8189,7 +8218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I371" authorId="0" shapeId="0" xr:uid="{CA3B13AE-BFDA-C94A-BA30-0092465AB402}">
+    <comment ref="I371" authorId="0" shapeId="0" xr:uid="{0B0D3E26-DF98-9148-9AEA-C2F597B2B1FB}">
       <text>
         <r>
           <rPr>
@@ -8207,7 +8236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I372" authorId="0" shapeId="0" xr:uid="{2CD78085-FCE5-2E4A-88C9-965B240EA12D}">
+    <comment ref="I372" authorId="0" shapeId="0" xr:uid="{823467D8-FE6D-4940-9D58-D35D86285E4F}">
       <text>
         <r>
           <rPr>
@@ -8231,7 +8260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I373" authorId="0" shapeId="0" xr:uid="{17612CD6-E860-5B4F-8786-CD463347C076}">
+    <comment ref="I373" authorId="0" shapeId="0" xr:uid="{6D5D2DE4-AC2F-7749-B9BE-D520CE2C5162}">
       <text>
         <r>
           <rPr>
@@ -8250,7 +8279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I374" authorId="0" shapeId="0" xr:uid="{240E4169-C03D-DC47-9817-DDE74FFD1980}">
+    <comment ref="I374" authorId="0" shapeId="0" xr:uid="{34F70CEE-83EA-BC49-B175-D38D8F46ACC5}">
       <text>
         <r>
           <rPr>
@@ -8268,7 +8297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I375" authorId="0" shapeId="0" xr:uid="{3AAE050E-2892-FD41-9A6C-DD0B5B2A0130}">
+    <comment ref="I375" authorId="0" shapeId="0" xr:uid="{AD70CB1C-7F54-6146-86FB-B64FAA1A8016}">
       <text>
         <r>
           <rPr>
@@ -8285,7 +8314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I376" authorId="0" shapeId="0" xr:uid="{D008E113-F46D-4A4F-A556-C0C860FE5F1A}">
+    <comment ref="I376" authorId="0" shapeId="0" xr:uid="{39EB5C82-C3CE-084A-B500-0FBC0E0F5E17}">
       <text>
         <r>
           <rPr>
@@ -8302,7 +8331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I377" authorId="0" shapeId="0" xr:uid="{75B64AB7-1765-9C46-BBA7-37B669C27286}">
+    <comment ref="I377" authorId="0" shapeId="0" xr:uid="{1EA8BD7B-06AD-A747-833E-48E1F44123B2}">
       <text>
         <r>
           <rPr>
@@ -8319,7 +8348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I378" authorId="0" shapeId="0" xr:uid="{B714113A-C15D-BA40-9E34-6D641830DCAF}">
+    <comment ref="I378" authorId="0" shapeId="0" xr:uid="{8E1DF46E-E227-704A-B138-5AF9BA40A72C}">
       <text>
         <r>
           <rPr>
@@ -8339,7 +8368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I379" authorId="0" shapeId="0" xr:uid="{75E2A73F-0775-704A-9308-DFC15995D79A}">
+    <comment ref="I379" authorId="0" shapeId="0" xr:uid="{00D556C1-5C2D-6441-ACB2-D5AFD26C5A46}">
       <text>
         <r>
           <rPr>
@@ -8356,7 +8385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I380" authorId="0" shapeId="0" xr:uid="{78E0CAAA-70CE-B648-BC3C-D6ED0717AA48}">
+    <comment ref="I380" authorId="0" shapeId="0" xr:uid="{92A93FE3-71DC-F34B-B9AF-A5D94F674D1A}">
       <text>
         <r>
           <rPr>
@@ -8373,7 +8402,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I381" authorId="0" shapeId="0" xr:uid="{D264F37E-5E1C-254E-9358-D830EF9291AF}">
+    <comment ref="I381" authorId="0" shapeId="0" xr:uid="{8F7FE5A2-D66E-2348-B56B-8F1503CA1707}">
       <text>
         <r>
           <rPr>
@@ -8390,7 +8419,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I382" authorId="0" shapeId="0" xr:uid="{A41980B9-6FBC-D944-BB10-79DF812CBD56}">
+    <comment ref="I382" authorId="0" shapeId="0" xr:uid="{88945F33-1D56-8C43-B414-95B3AB18CD34}">
       <text>
         <r>
           <rPr>
@@ -8407,7 +8436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I383" authorId="0" shapeId="0" xr:uid="{B58D9B4B-5324-7741-9A2B-90C0A3B5FD66}">
+    <comment ref="I383" authorId="0" shapeId="0" xr:uid="{A44890B6-5C05-0F40-A11B-4CACF83A637F}">
       <text>
         <r>
           <rPr>
@@ -8424,7 +8453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I384" authorId="0" shapeId="0" xr:uid="{6C4AC77B-C027-A04C-9B9E-189F45247B0D}">
+    <comment ref="I384" authorId="0" shapeId="0" xr:uid="{3B8DB17D-864B-CB41-8A77-3E07F86EAD3F}">
       <text>
         <r>
           <rPr>
@@ -8441,7 +8470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I385" authorId="0" shapeId="0" xr:uid="{6CAEBEA5-22B7-8A41-AFF4-65C16858C886}">
+    <comment ref="I385" authorId="0" shapeId="0" xr:uid="{48103161-84B6-824E-BF4C-B56A600FEA0D}">
       <text>
         <r>
           <rPr>
@@ -8474,7 +8503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I386" authorId="0" shapeId="0" xr:uid="{6CD6BA6B-4727-B045-B931-99561D8B088E}">
+    <comment ref="I386" authorId="0" shapeId="0" xr:uid="{D410E63B-42C8-3841-98C5-6FC191B330EA}">
       <text>
         <r>
           <rPr>
@@ -8489,7 +8518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I387" authorId="0" shapeId="0" xr:uid="{67A83EB0-4A65-114D-AF10-DBCC7B735BD3}">
+    <comment ref="I387" authorId="0" shapeId="0" xr:uid="{A6DE13DA-BD9A-7244-9DAF-4DEFC3597D75}">
       <text>
         <r>
           <rPr>
@@ -8509,7 +8538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I388" authorId="0" shapeId="0" xr:uid="{D00792BA-6883-AA4C-8662-3F2DF4A4EC65}">
+    <comment ref="I388" authorId="0" shapeId="0" xr:uid="{A1B86E64-CCFC-9A4C-8384-1D5FF3275ED9}">
       <text>
         <r>
           <rPr>
@@ -8529,7 +8558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I389" authorId="0" shapeId="0" xr:uid="{9B2D8F25-F30B-CE4B-8D7D-92995F0EC11A}">
+    <comment ref="I389" authorId="0" shapeId="0" xr:uid="{A63A6C56-D6BD-1443-B0EC-AB5BF0D7CE7E}">
       <text>
         <r>
           <rPr>
@@ -8547,7 +8576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I390" authorId="0" shapeId="0" xr:uid="{BDF530CB-7935-384A-9DA5-64FDBA308FDF}">
+    <comment ref="I390" authorId="0" shapeId="0" xr:uid="{E43C493E-90D6-B849-8889-75D4FFBD57A7}">
       <text>
         <r>
           <rPr>
@@ -8565,7 +8594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I391" authorId="0" shapeId="0" xr:uid="{923C6E67-C40A-5C48-BCAE-1C0607C7C125}">
+    <comment ref="I391" authorId="0" shapeId="0" xr:uid="{02530C73-BF06-5B48-8B68-84F62196A226}">
       <text>
         <r>
           <rPr>
@@ -8582,7 +8611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I392" authorId="0" shapeId="0" xr:uid="{64EE4A8C-F74D-534A-AB9E-DE8B6D73073E}">
+    <comment ref="I392" authorId="0" shapeId="0" xr:uid="{783E52D0-7512-B041-9E37-9E1703D3F72E}">
       <text>
         <r>
           <rPr>
@@ -8599,7 +8628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I393" authorId="0" shapeId="0" xr:uid="{93F888DF-77E3-CB46-A72A-E444A73CB309}">
+    <comment ref="I393" authorId="0" shapeId="0" xr:uid="{CD0DEE07-F092-F44C-8D09-307F44935E31}">
       <text>
         <r>
           <rPr>
@@ -8628,7 +8657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I394" authorId="0" shapeId="0" xr:uid="{468AC866-A314-8347-810E-5930DC61D614}">
+    <comment ref="I394" authorId="0" shapeId="0" xr:uid="{D2DA3317-993B-1842-8EFC-7137BB317956}">
       <text>
         <r>
           <rPr>
@@ -8650,7 +8679,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I395" authorId="0" shapeId="0" xr:uid="{34C49544-F39C-CE45-B310-87A64B4F4670}">
+    <comment ref="I395" authorId="0" shapeId="0" xr:uid="{B3C37DCE-7A03-474E-B9C2-9CB19F23E00B}">
       <text>
         <r>
           <rPr>
@@ -8666,7 +8695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I396" authorId="0" shapeId="0" xr:uid="{1F2CAECF-CF77-E444-B8B9-DF6F516B8043}">
+    <comment ref="I396" authorId="0" shapeId="0" xr:uid="{ADA554D5-B62A-0A4E-AE52-4CC75477AB60}">
       <text>
         <r>
           <rPr>
@@ -8685,7 +8714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I397" authorId="0" shapeId="0" xr:uid="{EF8CE946-FCDF-5F4E-AA89-98D615EC9DF8}">
+    <comment ref="I397" authorId="0" shapeId="0" xr:uid="{04BC9BCB-E43D-4A48-9178-82EC5BB8BD0C}">
       <text>
         <r>
           <rPr>
@@ -8707,7 +8736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I398" authorId="0" shapeId="0" xr:uid="{110752FC-9EE7-EC41-BC90-53068AD0908A}">
+    <comment ref="I398" authorId="0" shapeId="0" xr:uid="{55DA0408-64AD-5746-BFA1-59A6978BB330}">
       <text>
         <r>
           <rPr>
@@ -8725,7 +8754,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I399" authorId="0" shapeId="0" xr:uid="{FCDD5607-056A-594D-874A-82723FFC684F}">
+    <comment ref="I399" authorId="0" shapeId="0" xr:uid="{F274200A-E41C-D740-88B2-FFCDF40E4C79}">
       <text>
         <r>
           <rPr>
@@ -8743,7 +8772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I400" authorId="0" shapeId="0" xr:uid="{6CF2958B-4314-654E-B6E6-3241DABBD999}">
+    <comment ref="I400" authorId="0" shapeId="0" xr:uid="{548F211D-1ED9-234B-B7BF-CF72B1A89019}">
       <text>
         <r>
           <rPr>
@@ -8759,7 +8788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I401" authorId="0" shapeId="0" xr:uid="{BE1DA944-E8AA-DB46-A151-FB0EA649C8C8}">
+    <comment ref="I401" authorId="0" shapeId="0" xr:uid="{184DBF28-2590-1041-8FD6-2000F2E10EA7}">
       <text>
         <r>
           <rPr>
@@ -8782,7 +8811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I402" authorId="0" shapeId="0" xr:uid="{CA2FF937-97CD-4042-8646-66FA6D649434}">
+    <comment ref="I402" authorId="0" shapeId="0" xr:uid="{E53AAC39-278E-1C46-87B7-3F720905B5C1}">
       <text>
         <r>
           <rPr>
@@ -8800,7 +8829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I403" authorId="0" shapeId="0" xr:uid="{97E5FAE1-3FEB-5243-B266-3C75599F2859}">
+    <comment ref="I403" authorId="0" shapeId="0" xr:uid="{821E5E81-E1A5-1848-A8CC-600D0F43F4BE}">
       <text>
         <r>
           <rPr>
@@ -8818,7 +8847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I404" authorId="0" shapeId="0" xr:uid="{2A265ADD-998D-E845-9A9D-A6D6110DC656}">
+    <comment ref="I404" authorId="0" shapeId="0" xr:uid="{CF74A982-9BDF-6849-BE44-BDA8563D56D8}">
       <text>
         <r>
           <rPr>
@@ -8836,7 +8865,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I405" authorId="0" shapeId="0" xr:uid="{B3A0F954-D9C3-8A47-BA4A-255652AD1102}">
+    <comment ref="I405" authorId="0" shapeId="0" xr:uid="{7AAB8EBB-2E3E-9F43-96E4-766800A20784}">
       <text>
         <r>
           <rPr>
@@ -8859,7 +8888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I406" authorId="0" shapeId="0" xr:uid="{D73EB30B-A269-0849-BBA9-621A282031CC}">
+    <comment ref="I406" authorId="0" shapeId="0" xr:uid="{B999BECC-8833-044B-8EDF-D3EEEE152306}">
       <text>
         <r>
           <rPr>
@@ -8877,7 +8906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I407" authorId="0" shapeId="0" xr:uid="{944FE55C-1E24-E648-96EA-DE20898142EE}">
+    <comment ref="I407" authorId="0" shapeId="0" xr:uid="{4ED74A6E-D383-614A-B4AE-D395DE4CD32D}">
       <text>
         <r>
           <rPr>
@@ -8900,7 +8929,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I408" authorId="0" shapeId="0" xr:uid="{7EF6C8EC-5745-4144-A126-AE71D9270C08}">
+    <comment ref="I408" authorId="0" shapeId="0" xr:uid="{183E45FF-C801-AE4E-98DA-57E762B21F38}">
       <text>
         <r>
           <rPr>
@@ -8918,7 +8947,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I409" authorId="0" shapeId="0" xr:uid="{3BA64FE4-F0D4-0840-801F-DFBE6FFB2E04}">
+    <comment ref="I409" authorId="0" shapeId="0" xr:uid="{B1213E9D-9E81-9441-AE17-64A73AD915EB}">
       <text>
         <r>
           <rPr>
@@ -8936,7 +8965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I410" authorId="0" shapeId="0" xr:uid="{57461216-791C-9747-AD65-A008BD288AB2}">
+    <comment ref="I410" authorId="0" shapeId="0" xr:uid="{0AC6BD87-351E-0847-A16C-937DCC59786D}">
       <text>
         <r>
           <rPr>
@@ -8955,7 +8984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I411" authorId="0" shapeId="0" xr:uid="{6CD6B6EC-621C-EC46-A8F4-E9C1EDB04EC9}">
+    <comment ref="I411" authorId="0" shapeId="0" xr:uid="{6AF283DA-F4E0-D744-830A-81540973DC30}">
       <text>
         <r>
           <rPr>
@@ -8978,7 +9007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I412" authorId="0" shapeId="0" xr:uid="{BA808BA9-B9B7-084D-8683-A9141A92EF4D}">
+    <comment ref="I412" authorId="0" shapeId="0" xr:uid="{DABDB5CF-7439-DD46-A8DF-43146B8D3747}">
       <text>
         <r>
           <rPr>
@@ -8996,7 +9025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I413" authorId="0" shapeId="0" xr:uid="{E9817469-1A8E-4348-B53D-1361E10A0F97}">
+    <comment ref="I413" authorId="0" shapeId="0" xr:uid="{27ABB536-F02E-5D46-8C71-75B7BDACB7A3}">
       <text>
         <r>
           <rPr>
@@ -9012,7 +9041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I414" authorId="0" shapeId="0" xr:uid="{5B26BA85-DB5C-724C-91D4-C14A78D02460}">
+    <comment ref="I414" authorId="0" shapeId="0" xr:uid="{ECB50423-A9EB-9541-9AC5-2BB6567B2A39}">
       <text>
         <r>
           <rPr>
@@ -9035,7 +9064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I415" authorId="0" shapeId="0" xr:uid="{A7181874-727D-D84B-8BDE-1EB25C6F11DC}">
+    <comment ref="I415" authorId="0" shapeId="0" xr:uid="{70DD5B8C-CB33-2745-8D71-35D9B0780301}">
       <text>
         <r>
           <rPr>
@@ -9053,7 +9082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I416" authorId="0" shapeId="0" xr:uid="{D9C60D0F-B7D6-574A-93F3-8E32DE0EAF19}">
+    <comment ref="I416" authorId="0" shapeId="0" xr:uid="{55C926C7-170D-7548-975A-7921AAD9CC4D}">
       <text>
         <r>
           <rPr>
@@ -9068,7 +9097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I417" authorId="0" shapeId="0" xr:uid="{E254B407-FFB4-4144-9827-6D30C40376E1}">
+    <comment ref="I417" authorId="0" shapeId="0" xr:uid="{4AC3D76E-471F-B141-9E62-F1F8316413E7}">
       <text>
         <r>
           <rPr>
@@ -9091,7 +9120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I418" authorId="0" shapeId="0" xr:uid="{55BF9BFC-0ADA-1A4F-B748-AB4C2586D8A4}">
+    <comment ref="I418" authorId="0" shapeId="0" xr:uid="{E93E9C93-580F-1C49-90CF-D1B6F8FBD915}">
       <text>
         <r>
           <rPr>
@@ -9110,7 +9139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I419" authorId="0" shapeId="0" xr:uid="{234A208F-AFE8-4742-BCA2-59BB3984A9F6}">
+    <comment ref="I419" authorId="0" shapeId="0" xr:uid="{BA4D9641-8E8D-7F45-8229-CB774F597F05}">
       <text>
         <r>
           <rPr>
@@ -9133,7 +9162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I420" authorId="0" shapeId="0" xr:uid="{8DEAF340-FEF1-8049-804F-6A2C247F83D3}">
+    <comment ref="I420" authorId="0" shapeId="0" xr:uid="{AD93E3FC-E14F-894F-BE1C-1A27C1B443C1}">
       <text>
         <r>
           <rPr>
@@ -9151,7 +9180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I421" authorId="0" shapeId="0" xr:uid="{B8905381-4DB2-A045-A25E-EDA65FFB46FD}">
+    <comment ref="I421" authorId="0" shapeId="0" xr:uid="{3FC9997E-5E36-C747-9126-C6F4B15D7CB4}">
       <text>
         <r>
           <rPr>
@@ -9174,7 +9203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I422" authorId="0" shapeId="0" xr:uid="{B54A2FA3-FB11-B848-AC29-0B2253C24685}">
+    <comment ref="I422" authorId="0" shapeId="0" xr:uid="{499829D3-52BF-9348-9795-9B1B0873939A}">
       <text>
         <r>
           <rPr>
@@ -9197,7 +9226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I423" authorId="0" shapeId="0" xr:uid="{B1F64A5D-BE2F-A844-BAC5-E0C61330E8B6}">
+    <comment ref="I423" authorId="0" shapeId="0" xr:uid="{7169E8F3-99FD-D545-B68C-2BA6732196EE}">
       <text>
         <r>
           <rPr>
@@ -9220,7 +9249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I424" authorId="0" shapeId="0" xr:uid="{EAB5A49A-8DA3-F54C-8993-9013A5E38D9A}">
+    <comment ref="I424" authorId="0" shapeId="0" xr:uid="{69DE4FF4-C55D-1346-8AD7-456C5F6B4870}">
       <text>
         <r>
           <rPr>
@@ -9243,7 +9272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I425" authorId="0" shapeId="0" xr:uid="{7E957CFC-D020-604F-8760-054BDFDBAC73}">
+    <comment ref="I425" authorId="0" shapeId="0" xr:uid="{F8F088CD-6E59-1247-9D71-6EABFC86CC44}">
       <text>
         <r>
           <rPr>
@@ -9261,7 +9290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I426" authorId="0" shapeId="0" xr:uid="{29CF7129-E504-C64E-A1AD-88A0005ED557}">
+    <comment ref="I426" authorId="0" shapeId="0" xr:uid="{F0EFB85C-883D-A94D-A45C-846CB04952BB}">
       <text>
         <r>
           <rPr>
@@ -9284,7 +9313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I427" authorId="0" shapeId="0" xr:uid="{7214E3AF-E1B3-4C4C-8CC5-D8ECC1E51965}">
+    <comment ref="I427" authorId="0" shapeId="0" xr:uid="{BD8BBC17-B1C3-BF43-B774-0692322C7AD6}">
       <text>
         <r>
           <rPr>
@@ -9307,7 +9336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I428" authorId="0" shapeId="0" xr:uid="{751F486A-F503-154E-8689-0FDC30EE3CF7}">
+    <comment ref="I428" authorId="0" shapeId="0" xr:uid="{C3C9CE05-FE4E-C241-A095-30B3F8C396A9}">
       <text>
         <r>
           <rPr>
@@ -9330,7 +9359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I429" authorId="0" shapeId="0" xr:uid="{596C506B-7573-0E43-8BCE-1E2CB0AA0CF0}">
+    <comment ref="I429" authorId="0" shapeId="0" xr:uid="{8BBF7758-9781-E547-9FC7-74E657A145C6}">
       <text>
         <r>
           <rPr>
@@ -9353,7 +9382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I430" authorId="0" shapeId="0" xr:uid="{9B52CEBE-E1C7-4E4D-8FD0-006B9C12E83B}">
+    <comment ref="I430" authorId="0" shapeId="0" xr:uid="{896DFC0D-AF9C-DA4E-8646-6D7F3E2FB600}">
       <text>
         <r>
           <rPr>
@@ -9376,7 +9405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I431" authorId="0" shapeId="0" xr:uid="{2449A094-B748-6F4C-B066-8B0D77F16996}">
+    <comment ref="I431" authorId="0" shapeId="0" xr:uid="{AA3F9C77-C772-444F-A7ED-8AA97673AA9A}">
       <text>
         <r>
           <rPr>
@@ -9399,7 +9428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I432" authorId="0" shapeId="0" xr:uid="{A78E48F0-18AB-F047-B7FD-A8C8E9E207E9}">
+    <comment ref="I432" authorId="0" shapeId="0" xr:uid="{D409EB21-B3F1-EF49-9856-5ABDB8404E78}">
       <text>
         <r>
           <rPr>
@@ -9414,7 +9443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I433" authorId="0" shapeId="0" xr:uid="{75C90A15-8AFA-F64A-823D-7BC9E3ABD1BD}">
+    <comment ref="I433" authorId="0" shapeId="0" xr:uid="{CC2F6A80-9444-CE49-9F59-2BA7A77F191E}">
       <text>
         <r>
           <rPr>
@@ -9444,7 +9473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I434" authorId="0" shapeId="0" xr:uid="{46431E84-03F9-8F4F-8AE8-D5C87823DEB4}">
+    <comment ref="I434" authorId="0" shapeId="0" xr:uid="{63A96FE4-80C7-5E42-99BC-BF8CAB44CFAB}">
       <text>
         <r>
           <rPr>
@@ -9473,7 +9502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I435" authorId="0" shapeId="0" xr:uid="{F856EF10-6667-3544-95D8-4238EB04AF68}">
+    <comment ref="I435" authorId="0" shapeId="0" xr:uid="{660FD3BE-055A-DC4F-8A70-C8E0373F1939}">
       <text>
         <r>
           <rPr>
@@ -9489,7 +9518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I436" authorId="0" shapeId="0" xr:uid="{15FE0CD5-8DF1-E244-B4EC-7702ADD73120}">
+    <comment ref="I436" authorId="0" shapeId="0" xr:uid="{B51CF53C-4E5E-D641-8967-C18A1BEEE077}">
       <text>
         <r>
           <rPr>
@@ -9508,7 +9537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I437" authorId="0" shapeId="0" xr:uid="{8D2D0C40-1080-4047-9EB6-AC85531D01C0}">
+    <comment ref="I437" authorId="0" shapeId="0" xr:uid="{2C931645-E2CE-CA48-A4E9-DD42AC61A1AB}">
       <text>
         <r>
           <rPr>
@@ -9528,7 +9557,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I438" authorId="0" shapeId="0" xr:uid="{AFD1ADF3-2A80-2342-9285-FD9AF481FC29}">
+    <comment ref="I438" authorId="0" shapeId="0" xr:uid="{0496E561-D77C-5149-819F-D65E3C2A597E}">
       <text>
         <r>
           <rPr>
@@ -9548,7 +9577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I439" authorId="0" shapeId="0" xr:uid="{DAEA9B02-3480-0449-A37B-3FDBE6711AF7}">
+    <comment ref="I439" authorId="0" shapeId="0" xr:uid="{495DD6C2-398B-AC44-8E24-BECF7C8D7F1A}">
       <text>
         <r>
           <rPr>
@@ -9564,7 +9593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I440" authorId="0" shapeId="0" xr:uid="{5980A8C4-8BC3-3047-BBC9-4EC47E531167}">
+    <comment ref="I440" authorId="0" shapeId="0" xr:uid="{80E71F84-C777-A44A-AE7E-2260C7F68EB0}">
       <text>
         <r>
           <rPr>
@@ -9584,7 +9613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I441" authorId="0" shapeId="0" xr:uid="{51B1378B-4127-D841-A5E1-2A018ECADC18}">
+    <comment ref="I441" authorId="0" shapeId="0" xr:uid="{28FFB1CF-6EB6-2A43-90F8-FB82DB0A5A82}">
       <text>
         <r>
           <rPr>
@@ -9603,7 +9632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I442" authorId="0" shapeId="0" xr:uid="{84095459-39A0-6F41-A793-F1D5F0A8FB49}">
+    <comment ref="I442" authorId="0" shapeId="0" xr:uid="{4C260DF8-B605-6443-80CD-B7008BFD3E64}">
       <text>
         <r>
           <rPr>
@@ -9623,7 +9652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I443" authorId="0" shapeId="0" xr:uid="{8E4C6A39-99F6-674F-8187-E99D40AC32D9}">
+    <comment ref="I443" authorId="0" shapeId="0" xr:uid="{C1884AD5-6EE1-544A-AC55-FE7B27041660}">
       <text>
         <r>
           <rPr>
@@ -9643,7 +9672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I444" authorId="0" shapeId="0" xr:uid="{76CD7F46-0E1F-764D-A41E-4046AA5A9BDF}">
+    <comment ref="I444" authorId="0" shapeId="0" xr:uid="{FEDEE016-09BE-6A4A-87D2-073273D7D9CF}">
       <text>
         <r>
           <rPr>
@@ -9662,7 +9691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I445" authorId="0" shapeId="0" xr:uid="{72C931ED-35C0-994C-AE4E-1C61C9CEFFB6}">
+    <comment ref="I445" authorId="0" shapeId="0" xr:uid="{11B4025D-E2A8-DE4B-AEE7-D283C691CBD1}">
       <text>
         <r>
           <rPr>
@@ -9688,7 +9717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I446" authorId="0" shapeId="0" xr:uid="{34840F6D-CB2A-FE46-BCA2-07D7A9A3B551}">
+    <comment ref="I446" authorId="0" shapeId="0" xr:uid="{A40040C8-393A-2C4C-9C73-5D1A45EF5A59}">
       <text>
         <r>
           <rPr>
@@ -9714,7 +9743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I447" authorId="0" shapeId="0" xr:uid="{3D07F873-EE91-4445-A572-BB4849B8F2C0}">
+    <comment ref="I447" authorId="0" shapeId="0" xr:uid="{E53CA82B-46DE-9E41-A4F7-E91B4BCB1503}">
       <text>
         <r>
           <rPr>
@@ -9740,7 +9769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I448" authorId="0" shapeId="0" xr:uid="{B17E1BD1-3D5D-9C43-AC0C-4918354AA765}">
+    <comment ref="I448" authorId="0" shapeId="0" xr:uid="{98F76995-4BE6-584B-9827-CDE83CBDAB66}">
       <text>
         <r>
           <rPr>
@@ -9760,7 +9789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I449" authorId="0" shapeId="0" xr:uid="{D9195894-23DF-9145-B700-A666124BCF76}">
+    <comment ref="I449" authorId="0" shapeId="0" xr:uid="{7B94F910-D83D-D741-B652-07D8030D7F65}">
       <text>
         <r>
           <rPr>
@@ -9783,7 +9812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I450" authorId="0" shapeId="0" xr:uid="{9270BD4D-9111-DB47-A1E3-A791D7338475}">
+    <comment ref="I450" authorId="0" shapeId="0" xr:uid="{E6731921-BB23-3345-9199-E477C90C22F8}">
       <text>
         <r>
           <rPr>
@@ -9809,7 +9838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I451" authorId="0" shapeId="0" xr:uid="{0BB76E01-6CE9-4647-886B-23A7515C9FF1}">
+    <comment ref="I451" authorId="0" shapeId="0" xr:uid="{86912B04-DE90-6D43-A530-A4D22B3396DC}">
       <text>
         <r>
           <rPr>
@@ -9829,7 +9858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I452" authorId="0" shapeId="0" xr:uid="{EFE47B3D-39A9-BC43-A98F-2009ED038E6A}">
+    <comment ref="I452" authorId="0" shapeId="0" xr:uid="{A71A225A-4984-2B44-A293-6E4D2DEDA351}">
       <text>
         <r>
           <rPr>
@@ -9855,7 +9884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I453" authorId="0" shapeId="0" xr:uid="{D18195A3-321F-E142-8B07-B1C3630B4026}">
+    <comment ref="I453" authorId="0" shapeId="0" xr:uid="{841D12E7-0F19-984B-B338-E1DB73C559E0}">
       <text>
         <r>
           <rPr>
@@ -9881,7 +9910,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I454" authorId="0" shapeId="0" xr:uid="{931CC000-92BE-7148-8669-5CD18AE3DEA7}">
+    <comment ref="I454" authorId="0" shapeId="0" xr:uid="{CD5B4EF4-B9B3-BB4E-B053-BA724D394C3A}">
       <text>
         <r>
           <rPr>
@@ -9901,7 +9930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I455" authorId="0" shapeId="0" xr:uid="{89A99E5E-5957-DD48-8A42-C281ADDA2140}">
+    <comment ref="I455" authorId="0" shapeId="0" xr:uid="{9A594232-91BB-4F4B-A49F-49FF95EC17E3}">
       <text>
         <r>
           <rPr>
@@ -9924,7 +9953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I456" authorId="0" shapeId="0" xr:uid="{472B8791-0C0D-8340-B2A7-C7232F48A9C4}">
+    <comment ref="I456" authorId="0" shapeId="0" xr:uid="{023B903E-6841-F648-B101-B0413F4C25FB}">
       <text>
         <r>
           <rPr>
@@ -9947,7 +9976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I457" authorId="0" shapeId="0" xr:uid="{3AB6FAA1-0F3E-EA4F-BBE1-07151797482E}">
+    <comment ref="I457" authorId="0" shapeId="0" xr:uid="{69F6CA35-B508-0B43-B071-DD4DA1FCFB40}">
       <text>
         <r>
           <rPr>
@@ -9967,7 +9996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I458" authorId="0" shapeId="0" xr:uid="{4F397541-6B6F-4848-8730-140E0BB90FAD}">
+    <comment ref="I458" authorId="0" shapeId="0" xr:uid="{E544DB34-CB22-6749-94A6-52129F690CF5}">
       <text>
         <r>
           <rPr>
@@ -9993,7 +10022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I459" authorId="0" shapeId="0" xr:uid="{79AEF1B9-A4A3-5146-9617-48BA82609BA0}">
+    <comment ref="I459" authorId="0" shapeId="0" xr:uid="{8EE463BC-777C-0A47-875E-EEDD77D252A0}">
       <text>
         <r>
           <rPr>
@@ -10013,7 +10042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I460" authorId="0" shapeId="0" xr:uid="{2DFC3A45-1082-A34C-8E27-123A5295B098}">
+    <comment ref="I460" authorId="0" shapeId="0" xr:uid="{6EA77256-B734-5743-B86A-9A6BA09DCE1C}">
       <text>
         <r>
           <rPr>
@@ -10033,7 +10062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I461" authorId="0" shapeId="0" xr:uid="{25063152-3352-014B-B880-CA700805DDA8}">
+    <comment ref="I461" authorId="0" shapeId="0" xr:uid="{77158EA5-2975-9543-81EF-4A29FEB82478}">
       <text>
         <r>
           <rPr>
@@ -10059,7 +10088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I462" authorId="0" shapeId="0" xr:uid="{55CDC0FC-36CA-4643-AA5A-D14B5216D2B2}">
+    <comment ref="I462" authorId="0" shapeId="0" xr:uid="{94B60FF6-320C-4942-B533-A93CE235105E}">
       <text>
         <r>
           <rPr>
@@ -10079,7 +10108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I463" authorId="0" shapeId="0" xr:uid="{D8D2B604-C70C-D74B-9FC9-827AD2D796A7}">
+    <comment ref="I463" authorId="0" shapeId="0" xr:uid="{0A22ADFF-8C8D-1845-ADD8-7D89CF9FB1EC}">
       <text>
         <r>
           <rPr>
@@ -10105,7 +10134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I464" authorId="0" shapeId="0" xr:uid="{FFD01976-7984-5444-9F65-167C1F698236}">
+    <comment ref="I464" authorId="0" shapeId="0" xr:uid="{36C0A501-A125-7E42-8173-E977A5CB804A}">
       <text>
         <r>
           <rPr>
@@ -10131,7 +10160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I465" authorId="0" shapeId="0" xr:uid="{D368F6E0-86C2-9846-B54B-DBAB717D3832}">
+    <comment ref="I465" authorId="0" shapeId="0" xr:uid="{40ECCF90-A5B0-F14A-B192-9E98A6041A0C}">
       <text>
         <r>
           <rPr>
@@ -10151,7 +10180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I466" authorId="0" shapeId="0" xr:uid="{4EF1415F-335F-1743-958E-84D40FDD9716}">
+    <comment ref="I466" authorId="0" shapeId="0" xr:uid="{AD3EBD9C-482C-8242-B7C0-FA9AC5231823}">
       <text>
         <r>
           <rPr>
@@ -10171,7 +10200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I467" authorId="0" shapeId="0" xr:uid="{A7327CB9-36B5-A248-AA25-D1F29AAA666E}">
+    <comment ref="I467" authorId="0" shapeId="0" xr:uid="{98D23B2C-C0AD-A845-9C47-EA4FF915A8B7}">
       <text>
         <r>
           <rPr>
@@ -10197,7 +10226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I468" authorId="0" shapeId="0" xr:uid="{9628A345-6EB7-8543-915B-E0D665FCD3EC}">
+    <comment ref="I468" authorId="0" shapeId="0" xr:uid="{668FD319-3692-F54E-A09D-13BF6CEE999B}">
       <text>
         <r>
           <rPr>
@@ -10217,7 +10246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I469" authorId="0" shapeId="0" xr:uid="{2100EF79-5D38-0942-99A4-09712D3BD1A3}">
+    <comment ref="I469" authorId="0" shapeId="0" xr:uid="{0D3A92F2-91D8-D241-85CA-3B2540EDF91E}">
       <text>
         <r>
           <rPr>
@@ -10243,7 +10272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I470" authorId="0" shapeId="0" xr:uid="{8640544E-9642-9149-AD41-1E02F42357D4}">
+    <comment ref="I470" authorId="0" shapeId="0" xr:uid="{88DF22AA-CB44-6E49-AA22-F663AEDC018F}">
       <text>
         <r>
           <rPr>
@@ -10269,7 +10298,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I471" authorId="0" shapeId="0" xr:uid="{A814E5C8-97DC-5D46-BC8E-4AA46DD8A01B}">
+    <comment ref="I471" authorId="0" shapeId="0" xr:uid="{950838F2-19F3-AD4C-8A89-4203F9E4571D}">
       <text>
         <r>
           <rPr>
@@ -10289,7 +10318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I472" authorId="0" shapeId="0" xr:uid="{EEE88397-9B02-F843-950F-A84C0184A67A}">
+    <comment ref="I472" authorId="0" shapeId="0" xr:uid="{D94AA941-2C64-224A-A549-B354BDEA7471}">
       <text>
         <r>
           <rPr>
@@ -10307,7 +10336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I473" authorId="0" shapeId="0" xr:uid="{151D6B62-14F0-224F-A7EA-52627EC0BD0F}">
+    <comment ref="I473" authorId="0" shapeId="0" xr:uid="{5168916A-4F26-6B43-8848-1D1E7DE0AE13}">
       <text>
         <r>
           <rPr>
@@ -10336,7 +10365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I474" authorId="0" shapeId="0" xr:uid="{B5C7A2A2-1105-D84A-97BF-E11AD0D2EA19}">
+    <comment ref="I474" authorId="0" shapeId="0" xr:uid="{A4FC76E8-1A91-FB49-86D2-25D0883D4386}">
       <text>
         <r>
           <rPr>
@@ -10352,7 +10381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I475" authorId="0" shapeId="0" xr:uid="{577D07EA-C1D6-C840-8917-1EA3B9FC84B0}">
+    <comment ref="I475" authorId="0" shapeId="0" xr:uid="{CE7D1CBD-DD0D-D246-89E3-80F442CC7C66}">
       <text>
         <r>
           <rPr>
@@ -10368,7 +10397,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I476" authorId="0" shapeId="0" xr:uid="{385A3F8A-B203-BF4A-B8AB-4417209BF61E}">
+    <comment ref="I476" authorId="0" shapeId="0" xr:uid="{04636EDF-A157-C942-9129-EE6A0C9A49F1}">
       <text>
         <r>
           <rPr>
@@ -10388,7 +10417,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I477" authorId="0" shapeId="0" xr:uid="{63616988-E9BA-994B-B39F-151D1A9DBD3F}">
+    <comment ref="I477" authorId="0" shapeId="0" xr:uid="{86C7F3A3-21F9-9041-B0AA-034EFC9AE6C6}">
       <text>
         <r>
           <rPr>
@@ -10414,7 +10443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I478" authorId="0" shapeId="0" xr:uid="{D70C1D03-5FF8-0D4F-A731-47F5050DA6DC}">
+    <comment ref="I478" authorId="0" shapeId="0" xr:uid="{84678152-0C60-7849-97F2-DE505AB23902}">
       <text>
         <r>
           <rPr>
@@ -10430,7 +10459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I479" authorId="0" shapeId="0" xr:uid="{9F8B5B07-501F-1245-80A8-3CEC524C4FA4}">
+    <comment ref="I479" authorId="0" shapeId="0" xr:uid="{95A6FF2D-B860-AA4A-9AD5-F270F3EF029D}">
       <text>
         <r>
           <rPr>
@@ -10450,7 +10479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I480" authorId="0" shapeId="0" xr:uid="{A9B13606-61E5-9942-8570-6985AAD077D0}">
+    <comment ref="I480" authorId="0" shapeId="0" xr:uid="{90A9E2B9-7F67-054B-80DD-E4C04429F208}">
       <text>
         <r>
           <rPr>
@@ -10466,7 +10495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I481" authorId="0" shapeId="0" xr:uid="{3EF9BB5E-2ABC-1D46-920A-437D9C821DDE}">
+    <comment ref="I481" authorId="0" shapeId="0" xr:uid="{00E53211-5952-AA4C-A64D-11F772081CC9}">
       <text>
         <r>
           <rPr>
@@ -10492,7 +10521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I482" authorId="0" shapeId="0" xr:uid="{634DA01E-12E3-824D-825A-E80186721F59}">
+    <comment ref="I482" authorId="0" shapeId="0" xr:uid="{F004A8CD-ACE5-5A40-956D-587FEEF8951C}">
       <text>
         <r>
           <rPr>
@@ -10515,7 +10544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I483" authorId="0" shapeId="0" xr:uid="{9C5168D7-B453-9F4B-8581-EB17E31B411E}">
+    <comment ref="I483" authorId="0" shapeId="0" xr:uid="{897AA9EA-11C8-1E42-B9BB-5CC9A6542636}">
       <text>
         <r>
           <rPr>
@@ -10535,7 +10564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I484" authorId="0" shapeId="0" xr:uid="{C308DB79-0FA5-1841-AAEC-C7EE6CB227EA}">
+    <comment ref="I484" authorId="0" shapeId="0" xr:uid="{3857718F-3C8A-174B-BB0D-115B2CCC33C8}">
       <text>
         <r>
           <rPr>
@@ -10551,7 +10580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I485" authorId="0" shapeId="0" xr:uid="{97113C4F-9658-314A-8C96-1D504A2F0ABD}">
+    <comment ref="I485" authorId="0" shapeId="0" xr:uid="{52276DE7-2862-EA48-A20F-00881AD326F4}">
       <text>
         <r>
           <rPr>
@@ -10577,7 +10606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I486" authorId="0" shapeId="0" xr:uid="{DF2C440A-AA7B-C143-9CD9-7B6946E881B1}">
+    <comment ref="I486" authorId="0" shapeId="0" xr:uid="{4C3DB519-C3D0-3242-BF2D-0B6C24756860}">
       <text>
         <r>
           <rPr>
@@ -10593,7 +10622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I487" authorId="0" shapeId="0" xr:uid="{9EB89716-1E13-D345-B9B5-8A3FFA0B83B6}">
+    <comment ref="I487" authorId="0" shapeId="0" xr:uid="{49A93E11-BFE8-0F43-80F9-B347E296864C}">
       <text>
         <r>
           <rPr>
@@ -10613,7 +10642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I488" authorId="0" shapeId="0" xr:uid="{EB7B26AD-E4C5-5546-AAB1-45A05C47F69A}">
+    <comment ref="I488" authorId="0" shapeId="0" xr:uid="{AB16B213-A145-C841-A2C8-FBDE0F3AC833}">
       <text>
         <r>
           <rPr>
@@ -10633,7 +10662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I489" authorId="0" shapeId="0" xr:uid="{87FBAB6D-D2BA-D54E-9005-A9CEF6E777DB}">
+    <comment ref="I489" authorId="0" shapeId="0" xr:uid="{BB2C1A6E-847D-D240-8843-C4C7601B0315}">
       <text>
         <r>
           <rPr>
@@ -10653,7 +10682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I490" authorId="0" shapeId="0" xr:uid="{8B59CFDC-9589-E543-AC09-E62F6C302BDE}">
+    <comment ref="I490" authorId="0" shapeId="0" xr:uid="{268F339C-8D34-BE43-9BFC-B5CE68ED4E46}">
       <text>
         <r>
           <rPr>
@@ -10673,7 +10702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I491" authorId="0" shapeId="0" xr:uid="{0C0F6CBE-32CF-A547-8D7C-329B9BA8C4D0}">
+    <comment ref="I491" authorId="0" shapeId="0" xr:uid="{E5AF521F-492F-1345-99C6-6AABCB07CF5A}">
       <text>
         <r>
           <rPr>
@@ -10699,7 +10728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I492" authorId="0" shapeId="0" xr:uid="{918D1F4B-8D5C-1F4B-9232-F717AA6A1973}">
+    <comment ref="I492" authorId="0" shapeId="0" xr:uid="{96A39834-F35A-DA42-8C44-DA96DB992A5C}">
       <text>
         <r>
           <rPr>
@@ -10722,7 +10751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I493" authorId="0" shapeId="0" xr:uid="{10A925BF-5118-F147-BAB7-E6BE86088A7B}">
+    <comment ref="I493" authorId="0" shapeId="0" xr:uid="{019C5520-6B7F-8A47-B7A1-3D6A8CC38713}">
       <text>
         <r>
           <rPr>
@@ -10748,7 +10777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I494" authorId="0" shapeId="0" xr:uid="{96A52359-2A90-D04C-9ED0-15D63D52A2A9}">
+    <comment ref="I494" authorId="0" shapeId="0" xr:uid="{103DB91A-F442-354D-B5CD-ADCD6B2DD221}">
       <text>
         <r>
           <rPr>
@@ -10768,7 +10797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I495" authorId="0" shapeId="0" xr:uid="{D1DF2B0C-8943-3D4A-8591-2F185413F447}">
+    <comment ref="I495" authorId="0" shapeId="0" xr:uid="{27E32BB8-41BB-A94E-B811-002612BED525}">
       <text>
         <r>
           <rPr>
@@ -10788,7 +10817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I496" authorId="0" shapeId="0" xr:uid="{548CC66F-BBCF-E540-87BE-544C935D2449}">
+    <comment ref="I496" authorId="0" shapeId="0" xr:uid="{B174D313-E312-544A-A195-7BB66C54B7EA}">
       <text>
         <r>
           <rPr>
@@ -10808,7 +10837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I497" authorId="0" shapeId="0" xr:uid="{A262461C-A9F9-6D40-8CE7-C5FACAF02F0E}">
+    <comment ref="I497" authorId="0" shapeId="0" xr:uid="{4EA54391-7B8C-CC49-A265-F726CDD4F5C9}">
       <text>
         <r>
           <rPr>
@@ -10828,7 +10857,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I498" authorId="0" shapeId="0" xr:uid="{231D5B9E-8066-EB44-A72A-2009068DDC29}">
+    <comment ref="I498" authorId="0" shapeId="0" xr:uid="{9FFE8671-D78E-7040-867E-3DE37C998A6B}">
       <text>
         <r>
           <rPr>
@@ -10848,7 +10877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I499" authorId="0" shapeId="0" xr:uid="{616AB275-2F01-114C-B02E-E396EA62B0DD}">
+    <comment ref="I499" authorId="0" shapeId="0" xr:uid="{877093EE-B8E3-3E42-B250-299B76DBBE4C}">
       <text>
         <r>
           <rPr>
@@ -10869,7 +10898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I500" authorId="0" shapeId="0" xr:uid="{7D88F632-66A3-2945-8C12-FFFC24A0581F}">
+    <comment ref="I500" authorId="0" shapeId="0" xr:uid="{B688D7AF-AF03-E14F-A853-86CA681638B1}">
       <text>
         <r>
           <rPr>
@@ -10889,7 +10918,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I501" authorId="0" shapeId="0" xr:uid="{1281637C-3158-6742-830A-60EA4AA44EA6}">
+    <comment ref="I501" authorId="0" shapeId="0" xr:uid="{5AB3F8F7-5765-4744-ADCD-1592A23C3BCC}">
       <text>
         <r>
           <rPr>
@@ -10907,7 +10936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I502" authorId="0" shapeId="0" xr:uid="{1268F298-1785-3C4E-9C8B-128995387A6D}">
+    <comment ref="I502" authorId="0" shapeId="0" xr:uid="{6F891F55-3B81-6149-8160-47AE790CEBEE}">
       <text>
         <r>
           <rPr>
@@ -10927,7 +10956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I503" authorId="0" shapeId="0" xr:uid="{63FB3D82-D753-7946-BE3B-9C9C1B4B073A}">
+    <comment ref="I503" authorId="0" shapeId="0" xr:uid="{29115A4D-7641-1643-8FAA-80534CC2D884}">
       <text>
         <r>
           <rPr>
@@ -10942,7 +10971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I504" authorId="0" shapeId="0" xr:uid="{3B877F22-EE8B-A84E-B750-F053C8FF16AE}">
+    <comment ref="I504" authorId="0" shapeId="0" xr:uid="{BFDBA3C5-3527-094C-A280-59C1E701ED68}">
       <text>
         <r>
           <rPr>
@@ -10962,7 +10991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I505" authorId="0" shapeId="0" xr:uid="{76B95071-4535-854F-89D1-6AE348B09D6A}">
+    <comment ref="I505" authorId="0" shapeId="0" xr:uid="{B3EB2621-99A4-064E-959E-89B148CE0939}">
       <text>
         <r>
           <rPr>
@@ -10982,7 +11011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I506" authorId="0" shapeId="0" xr:uid="{EB35E59D-130D-7F4F-A1DF-D434E863C8D0}">
+    <comment ref="I506" authorId="0" shapeId="0" xr:uid="{A7370203-1FEA-8B4D-9BEF-B394CFFADF8C}">
       <text>
         <r>
           <rPr>
@@ -11002,7 +11031,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I507" authorId="0" shapeId="0" xr:uid="{53408B7E-E2D0-8945-9664-A6A89997AD39}">
+    <comment ref="I507" authorId="0" shapeId="0" xr:uid="{D9D5EED4-0899-6E42-9158-CC89495D4A0C}">
       <text>
         <r>
           <rPr>
@@ -11022,7 +11051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I508" authorId="0" shapeId="0" xr:uid="{BA1045B5-B9F6-244F-95CC-41C61FE2FD1D}">
+    <comment ref="I508" authorId="0" shapeId="0" xr:uid="{8B9BA080-F775-C244-B9D3-ECE7D6D4C112}">
       <text>
         <r>
           <rPr>
@@ -11039,7 +11068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I509" authorId="0" shapeId="0" xr:uid="{1F3D3543-2D97-5844-ADFE-650FD175744F}">
+    <comment ref="I509" authorId="0" shapeId="0" xr:uid="{AFD250B9-B919-0A4C-BB0C-DEEEF4D2A495}">
       <text>
         <r>
           <rPr>
@@ -11059,7 +11088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I510" authorId="0" shapeId="0" xr:uid="{4C001A24-A4B3-8D45-874A-495E18286DB0}">
+    <comment ref="I510" authorId="0" shapeId="0" xr:uid="{41FEEE6F-574F-8D4F-BF53-C8AC1D01D3E5}">
       <text>
         <r>
           <rPr>
@@ -11079,7 +11108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I511" authorId="0" shapeId="0" xr:uid="{2E8ED7CD-D3DF-1845-AA8D-A754557F22D3}">
+    <comment ref="I511" authorId="0" shapeId="0" xr:uid="{E6487B68-C16C-914E-9253-C14EA372EC85}">
       <text>
         <r>
           <rPr>
@@ -11097,7 +11126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I512" authorId="0" shapeId="0" xr:uid="{55DA11C0-7D53-7042-A638-75AEE4AC07CC}">
+    <comment ref="I512" authorId="0" shapeId="0" xr:uid="{1A661793-6F37-894D-A3A3-AF0411E70BCA}">
       <text>
         <r>
           <rPr>
@@ -11120,7 +11149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I513" authorId="0" shapeId="0" xr:uid="{9C73A438-D262-C243-BFDD-59942F66E45F}">
+    <comment ref="I513" authorId="0" shapeId="0" xr:uid="{1113C9C3-E685-734B-9EE7-856359EA7A3F}">
       <text>
         <r>
           <rPr>
@@ -11136,7 +11165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I514" authorId="0" shapeId="0" xr:uid="{6165E274-DE2B-B148-9CD0-7430D25C29A0}">
+    <comment ref="I514" authorId="0" shapeId="0" xr:uid="{134B4A3D-CB7F-A945-AAD3-1AC2EB823966}">
       <text>
         <r>
           <rPr>
@@ -11162,7 +11191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I515" authorId="0" shapeId="0" xr:uid="{4C6A7653-9264-5543-B288-66F95FE30F8E}">
+    <comment ref="I515" authorId="0" shapeId="0" xr:uid="{3C6CD736-C6B6-B545-B3A7-29EBE247D651}">
       <text>
         <r>
           <rPr>
@@ -11188,7 +11217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I516" authorId="0" shapeId="0" xr:uid="{3458FCF1-8FBE-4042-9E81-0287D6979651}">
+    <comment ref="I516" authorId="0" shapeId="0" xr:uid="{14BDA5F3-4ED9-9048-983A-ED560D3747DC}">
       <text>
         <r>
           <rPr>
@@ -11204,7 +11233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I517" authorId="0" shapeId="0" xr:uid="{8CA70006-7C35-8E4F-ADA6-D66BDA274089}">
+    <comment ref="I517" authorId="0" shapeId="0" xr:uid="{2BF818D3-466F-AA4C-8CF0-3B0D31C6452E}">
       <text>
         <r>
           <rPr>
@@ -11220,7 +11249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I518" authorId="0" shapeId="0" xr:uid="{63653425-C2C1-F74B-A582-555DAF88C2A3}">
+    <comment ref="I518" authorId="0" shapeId="0" xr:uid="{681EFC1E-35CD-F542-B63B-6055B4BE29F7}">
       <text>
         <r>
           <rPr>
@@ -11236,24 +11265,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="I519" authorId="0" shapeId="0" xr:uid="{07FC40C6-378E-3441-A7BD-825E3F24867E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Fraser: 윤재호
-Gordon: 김서환
-Paul: 양병열
-Alan: 이형훈</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I520" authorId="0" shapeId="0" xr:uid="{75F5DCF2-C994-F84E-8061-CCE646B578B3}">
+    <comment ref="I519" authorId="0" shapeId="0" xr:uid="{A06D4EDD-3EBD-3949-887B-621A9F98881C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>프레이저: 윤재호
+고든: 김서환
+폴: 양병열
+앨런: 이형훈</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I520" authorId="0" shapeId="0" xr:uid="{9F35AF5D-D792-2945-A937-34937B751668}">
       <text>
         <r>
           <rPr>
@@ -11270,7 +11299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I521" authorId="0" shapeId="0" xr:uid="{211C686B-D318-3D40-B3D0-B14741763CC3}">
+    <comment ref="I521" authorId="0" shapeId="0" xr:uid="{5B196590-D2E6-354C-8F31-5803F743A38B}">
       <text>
         <r>
           <rPr>
@@ -11289,7 +11318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I522" authorId="0" shapeId="0" xr:uid="{118B07DE-825C-4844-A27D-280197B591F3}">
+    <comment ref="I522" authorId="0" shapeId="0" xr:uid="{8C1685AE-E6A8-5041-8A65-CCA6E8380921}">
       <text>
         <r>
           <rPr>
@@ -11309,7 +11338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I523" authorId="0" shapeId="0" xr:uid="{91D34709-E0FD-D746-BEF6-28B6C057527D}">
+    <comment ref="I523" authorId="0" shapeId="0" xr:uid="{75A89B74-16C8-694D-A66E-70B44CCE6ABD}">
       <text>
         <r>
           <rPr>
@@ -11325,7 +11354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I524" authorId="0" shapeId="0" xr:uid="{171F5D8D-69F5-7E40-96F3-C9112BC1D2DE}">
+    <comment ref="I524" authorId="0" shapeId="0" xr:uid="{471876C4-DB14-FB41-A7FC-75F98BD61511}">
       <text>
         <r>
           <rPr>
@@ -11341,7 +11370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I525" authorId="0" shapeId="0" xr:uid="{8C254E05-CE70-634B-8F36-1C7AA4760DBC}">
+    <comment ref="I525" authorId="0" shapeId="0" xr:uid="{F25FC5B2-DB9E-7244-B664-F5AB79C303C3}">
       <text>
         <r>
           <rPr>
@@ -11358,7 +11387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I526" authorId="0" shapeId="0" xr:uid="{5DA10632-9C29-A645-8E1E-6AEDA857129B}">
+    <comment ref="I526" authorId="0" shapeId="0" xr:uid="{82CC9EE3-7842-5844-980F-E66D4D2ED737}">
       <text>
         <r>
           <rPr>
@@ -11374,7 +11403,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I527" authorId="0" shapeId="0" xr:uid="{D6484118-F548-7441-8B52-57E5C53BBA21}">
+    <comment ref="I527" authorId="0" shapeId="0" xr:uid="{371B328A-BD25-0147-8FCE-B3DE5C212A4C}">
       <text>
         <r>
           <rPr>
@@ -11391,7 +11420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I528" authorId="0" shapeId="0" xr:uid="{2BE65293-D37B-9747-94DB-268C25384BEF}">
+    <comment ref="I528" authorId="0" shapeId="0" xr:uid="{619BAF2A-9A32-0B45-8A2B-828F77E1C0E3}">
       <text>
         <r>
           <rPr>
@@ -11411,7 +11440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I529" authorId="0" shapeId="0" xr:uid="{6BDC6724-9BD0-D144-AA52-FE332A00A7BC}">
+    <comment ref="I529" authorId="0" shapeId="0" xr:uid="{68B4890B-332B-2249-A54E-0079937E79A7}">
       <text>
         <r>
           <rPr>
@@ -11427,7 +11456,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I530" authorId="0" shapeId="0" xr:uid="{6AD202D7-9DD5-5949-8D48-F7EF3FD8DA1C}">
+    <comment ref="I530" authorId="0" shapeId="0" xr:uid="{204066FC-D346-7642-AFB8-64036A7F8586}">
       <text>
         <r>
           <rPr>
@@ -11443,7 +11472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I531" authorId="0" shapeId="0" xr:uid="{200C0520-988F-CE42-888B-F6BC9EAF912F}">
+    <comment ref="I531" authorId="0" shapeId="0" xr:uid="{6C9F618A-98E0-6E4C-B150-F445EBDBFCA3}">
       <text>
         <r>
           <rPr>
@@ -11460,7 +11489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I532" authorId="0" shapeId="0" xr:uid="{98F23A36-D8B1-AB4E-ABEF-9ABB6535E9B8}">
+    <comment ref="I532" authorId="0" shapeId="0" xr:uid="{5E7B9178-A075-D14B-9584-45FFDF201B7C}">
       <text>
         <r>
           <rPr>
@@ -11476,7 +11505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I533" authorId="0" shapeId="0" xr:uid="{2E1D0014-D0BC-0F45-BCE8-7B31E6F57BED}">
+    <comment ref="I533" authorId="0" shapeId="0" xr:uid="{A4BA99E3-A412-EB44-B365-534B8CEDE3B2}">
       <text>
         <r>
           <rPr>
@@ -11495,7 +11524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I534" authorId="0" shapeId="0" xr:uid="{D0F877A3-4AC0-BF47-8AE3-0FFB310A8187}">
+    <comment ref="I534" authorId="0" shapeId="0" xr:uid="{D79E0660-D424-784D-B6D6-9506ADFCA956}">
       <text>
         <r>
           <rPr>
@@ -11512,7 +11541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I535" authorId="0" shapeId="0" xr:uid="{B3DE2366-C9A7-5344-82A2-52C1CDC7E8BF}">
+    <comment ref="I535" authorId="0" shapeId="0" xr:uid="{EDD423CE-A8F0-BC46-BA75-E43E8FD4D5A1}">
       <text>
         <r>
           <rPr>
@@ -11528,7 +11557,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I536" authorId="0" shapeId="0" xr:uid="{9E215C08-84E0-9C47-AE27-1D38D1B2475F}">
+    <comment ref="I536" authorId="0" shapeId="0" xr:uid="{E06F720B-CE98-6A48-A056-0BBCB30FDBFB}">
       <text>
         <r>
           <rPr>
@@ -11544,7 +11573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I537" authorId="0" shapeId="0" xr:uid="{F3270690-FFC3-E948-9EB6-5AEEC9A34348}">
+    <comment ref="I537" authorId="0" shapeId="0" xr:uid="{9FE11772-049E-CC4B-A44D-89A5C0000905}">
       <text>
         <r>
           <rPr>
@@ -11560,7 +11589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I538" authorId="0" shapeId="0" xr:uid="{9D45BF5C-0B32-F94D-9023-C4B196989A4A}">
+    <comment ref="I538" authorId="0" shapeId="0" xr:uid="{ECCB8ED9-4B64-7246-AA45-88106ED5E9C1}">
       <text>
         <r>
           <rPr>
@@ -11579,7 +11608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I539" authorId="0" shapeId="0" xr:uid="{FA1484DE-1C2E-B84C-9CF7-442CEA34C985}">
+    <comment ref="I539" authorId="0" shapeId="0" xr:uid="{1F44F5AC-F003-3A4F-9497-291AA6CE7BC5}">
       <text>
         <r>
           <rPr>
@@ -11595,7 +11624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I540" authorId="0" shapeId="0" xr:uid="{A360271F-1F95-374A-989B-0648CD8955F2}">
+    <comment ref="I540" authorId="0" shapeId="0" xr:uid="{10EA17B3-6834-D047-BA20-5F9E29A97794}">
       <text>
         <r>
           <rPr>
@@ -11610,7 +11639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I541" authorId="0" shapeId="0" xr:uid="{9B843E0D-E966-E244-B157-7A0916561709}">
+    <comment ref="I541" authorId="0" shapeId="0" xr:uid="{511EAAB5-4B8C-4A4C-BF8E-748D78C18F69}">
       <text>
         <r>
           <rPr>
@@ -11634,7 +11663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I542" authorId="0" shapeId="0" xr:uid="{CE55E0ED-1223-D143-873F-E06358A461E9}">
+    <comment ref="I542" authorId="0" shapeId="0" xr:uid="{D706887B-DB68-ED4A-8F27-8AC5B61AB95A}">
       <text>
         <r>
           <rPr>
@@ -11650,7 +11679,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I543" authorId="0" shapeId="0" xr:uid="{212707CF-649F-E645-B581-11DBD06A9555}">
+    <comment ref="I543" authorId="0" shapeId="0" xr:uid="{9367EE3A-B443-6343-B287-AE8EBFA83B43}">
       <text>
         <r>
           <rPr>
@@ -11667,7 +11696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I544" authorId="0" shapeId="0" xr:uid="{4BC3246C-A41A-4540-BA42-EC7AC7AA3A47}">
+    <comment ref="I544" authorId="0" shapeId="0" xr:uid="{6BC90581-113D-FB48-8601-53BB12B9C44C}">
       <text>
         <r>
           <rPr>
@@ -11683,7 +11712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I545" authorId="0" shapeId="0" xr:uid="{AC977199-7CFC-6A4A-A047-3ED17F10C099}">
+    <comment ref="I545" authorId="0" shapeId="0" xr:uid="{AA790FF3-5ADF-ED4E-AA34-A9B862A47F19}">
       <text>
         <r>
           <rPr>
@@ -11699,7 +11728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I546" authorId="0" shapeId="0" xr:uid="{19470CC7-87B7-054D-A059-AD04F3CFFA4B}">
+    <comment ref="I546" authorId="0" shapeId="0" xr:uid="{CEFA9CFF-9E31-4740-A09D-C18397AAEE6F}">
       <text>
         <r>
           <rPr>
@@ -11715,7 +11744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I547" authorId="0" shapeId="0" xr:uid="{CAE6EFCB-744C-4F42-BA69-F78DDC7BBC88}">
+    <comment ref="I547" authorId="0" shapeId="0" xr:uid="{487AA2DA-5D88-F84F-BFF5-7858AD45C998}">
       <text>
         <r>
           <rPr>
@@ -11729,7 +11758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I548" authorId="0" shapeId="0" xr:uid="{5CD7323E-0A90-124C-B3CF-F22BC4511D2B}">
+    <comment ref="I548" authorId="0" shapeId="0" xr:uid="{66896341-9868-E94E-8533-D156B8111C3D}">
       <text>
         <r>
           <rPr>
@@ -11745,7 +11774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I549" authorId="0" shapeId="0" xr:uid="{F76FD83D-8820-C64E-B51D-B36CF8EC657F}">
+    <comment ref="I549" authorId="0" shapeId="0" xr:uid="{874D3025-0707-F04B-A98D-8D7912444396}">
       <text>
         <r>
           <rPr>
@@ -11760,7 +11789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I550" authorId="0" shapeId="0" xr:uid="{CBDF412F-4EAC-E948-8D9D-E24F340FB9A9}">
+    <comment ref="I550" authorId="0" shapeId="0" xr:uid="{D439E06D-D2FC-4A44-A179-20D191499BA5}">
       <text>
         <r>
           <rPr>
@@ -11776,7 +11805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I551" authorId="0" shapeId="0" xr:uid="{E5AF64BA-AA8E-DB47-8528-04866ABC48B9}">
+    <comment ref="I551" authorId="0" shapeId="0" xr:uid="{71F279A9-91C4-2D4C-8561-A15083D394B6}">
       <text>
         <r>
           <rPr>
@@ -11792,7 +11821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I552" authorId="0" shapeId="0" xr:uid="{0BCEF236-21EC-2040-BEE1-5FBD54EDC116}">
+    <comment ref="I552" authorId="0" shapeId="0" xr:uid="{D61F443A-155A-AB4F-8373-7E913F97DC2E}">
       <text>
         <r>
           <rPr>
@@ -11821,7 +11850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I553" authorId="0" shapeId="0" xr:uid="{ECE02E08-1B5E-4140-8A56-DF203AE71053}">
+    <comment ref="I553" authorId="0" shapeId="0" xr:uid="{44049E61-5B78-9546-955B-236AA761BE1E}">
       <text>
         <r>
           <rPr>
@@ -11836,22 +11865,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="I554" authorId="0" shapeId="0" xr:uid="{361B7318-EC4A-D948-9D3E-75A128D1400E}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>John William Polidori: 현석준
-George Gordon Byron: 주민진</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I555" authorId="0" shapeId="0" xr:uid="{F4672FEB-D44A-7441-8292-EBD5733DB817}">
+    <comment ref="I554" authorId="0" shapeId="0" xr:uid="{2B5B5424-48B2-6748-B445-B1CA8A78863E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>존 윌리엄 폴리도리: 현석준
+조지 고든 바이런: 주민진</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I555" authorId="0" shapeId="0" xr:uid="{FF4FA113-81E2-0249-9FCD-6A048BEDEE3C}">
       <text>
         <r>
           <rPr>
@@ -11868,7 +11897,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I556" authorId="0" shapeId="0" xr:uid="{A93C1FB2-4912-6B4F-B319-2F9058663DB4}">
+    <comment ref="I556" authorId="0" shapeId="0" xr:uid="{17BE3D0A-82DB-F644-A7F6-8180B191CADF}">
       <text>
         <r>
           <rPr>
@@ -11887,7 +11916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I557" authorId="0" shapeId="0" xr:uid="{D775F583-D425-FF4B-857B-2344FDCC3A2C}">
+    <comment ref="I557" authorId="0" shapeId="0" xr:uid="{0CD404E0-8128-1243-BFB4-A4677B6618CD}">
       <text>
         <r>
           <rPr>
@@ -11906,7 +11935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I558" authorId="0" shapeId="0" xr:uid="{FB411476-622F-ED48-BE7E-3D33A0D50A02}">
+    <comment ref="I558" authorId="0" shapeId="0" xr:uid="{14278096-6C01-B048-8A6B-FEDA80F72206}">
       <text>
         <r>
           <rPr>
@@ -11925,7 +11954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I559" authorId="0" shapeId="0" xr:uid="{113E4BED-84C8-8446-ABE2-57A818E4921C}">
+    <comment ref="I559" authorId="0" shapeId="0" xr:uid="{A0CD808C-24DD-4849-A2B5-D2C221FFC95C}">
       <text>
         <r>
           <rPr>
@@ -11944,7 +11973,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I560" authorId="0" shapeId="0" xr:uid="{5A62D7C7-6033-D044-BE78-291E30BC157E}">
+    <comment ref="I560" authorId="0" shapeId="0" xr:uid="{7898ED51-38B3-0147-BE75-2A99250A59CD}">
       <text>
         <r>
           <rPr>
@@ -11963,22 +11992,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="I561" authorId="0" shapeId="0" xr:uid="{432A1183-692C-9642-BA21-67EBA369E5C4}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>John William Polidori: 현석준
-George Gordon Byron: 손유동</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I562" authorId="0" shapeId="0" xr:uid="{577678B2-62F0-FF48-89AD-4729D58E221F}">
+    <comment ref="I561" authorId="0" shapeId="0" xr:uid="{DD75F448-176E-0742-A012-D5EEFA4BF4DB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>존 윌리엄 폴리도리: 현석준
+조지 고든 바이런: 손유동</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I562" authorId="0" shapeId="0" xr:uid="{61635A94-8B33-A24D-A2B4-2670CF24D4DF}">
       <text>
         <r>
           <rPr>
@@ -11997,7 +12026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I563" authorId="0" shapeId="0" xr:uid="{5B11CE54-E77B-D64F-801B-7C34B9E226FD}">
+    <comment ref="I563" authorId="0" shapeId="0" xr:uid="{58C8CBF1-9C27-0040-B0B6-DE1448D594CF}">
       <text>
         <r>
           <rPr>
@@ -12014,7 +12043,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I564" authorId="0" shapeId="0" xr:uid="{624AF9E4-1EA0-8642-A065-C4C258698792}">
+    <comment ref="I564" authorId="0" shapeId="0" xr:uid="{7446774B-D39C-A841-938B-A43447A55C73}">
       <text>
         <r>
           <rPr>
@@ -12033,7 +12062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I565" authorId="0" shapeId="0" xr:uid="{43234406-ABBD-2143-AA5F-6E85FDB2C297}">
+    <comment ref="I565" authorId="0" shapeId="0" xr:uid="{A9F246B3-773C-684D-86E3-4ABD1EF0540A}">
       <text>
         <r>
           <rPr>
@@ -12052,7 +12081,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I566" authorId="0" shapeId="0" xr:uid="{E188F938-D762-3441-A597-DB2407CB28B0}">
+    <comment ref="I566" authorId="0" shapeId="0" xr:uid="{BA9EDC49-62E4-5244-9BC7-29C35B8D5288}">
       <text>
         <r>
           <rPr>
@@ -12070,7 +12099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I567" authorId="0" shapeId="0" xr:uid="{8F59231D-E8FF-2546-8CC6-7E4834FD3F94}">
+    <comment ref="I567" authorId="0" shapeId="0" xr:uid="{F4402495-6D3A-B74D-8730-680BD54F2C0E}">
       <text>
         <r>
           <rPr>
@@ -12100,7 +12129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I568" authorId="0" shapeId="0" xr:uid="{4F8E7B9B-A21A-3542-9B52-986D38A9FF05}">
+    <comment ref="I568" authorId="0" shapeId="0" xr:uid="{903C28F0-550F-A846-8EB9-41B6CC13A6BF}">
       <text>
         <r>
           <rPr>
@@ -12119,7 +12148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I569" authorId="0" shapeId="0" xr:uid="{732FD05B-1766-744C-8E6B-192E5149C62F}">
+    <comment ref="I569" authorId="0" shapeId="0" xr:uid="{E8ACC8C2-8756-3948-8BDF-2FDC564CF7E3}">
       <text>
         <r>
           <rPr>
@@ -12138,7 +12167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I570" authorId="0" shapeId="0" xr:uid="{BF262B2A-2EB7-B74F-88E8-71FF1D7BBE09}">
+    <comment ref="I570" authorId="0" shapeId="0" xr:uid="{36DAF9EC-0902-9341-AE06-2A64FC757EDD}">
       <text>
         <r>
           <rPr>
@@ -12157,7 +12186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I571" authorId="0" shapeId="0" xr:uid="{8B259698-CCF4-9E45-8883-CDC05A727F3B}">
+    <comment ref="I571" authorId="0" shapeId="0" xr:uid="{C08D1A6D-395A-A64C-9B73-C7E7674DDEDA}">
       <text>
         <r>
           <rPr>
@@ -12187,7 +12216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I572" authorId="0" shapeId="0" xr:uid="{E4ED07A3-D35B-AE4D-903D-073C426D0DD3}">
+    <comment ref="I572" authorId="0" shapeId="0" xr:uid="{CA3E5238-E27D-FB4A-A0F2-281524E027F0}">
       <text>
         <r>
           <rPr>
@@ -12203,7 +12232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I573" authorId="0" shapeId="0" xr:uid="{D169482D-6D0B-484F-B00C-A6F4485DFE91}">
+    <comment ref="I573" authorId="0" shapeId="0" xr:uid="{432B7F45-00B1-DE4B-B539-ADA2CC31DBBB}">
       <text>
         <r>
           <rPr>
@@ -12222,7 +12251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I574" authorId="0" shapeId="0" xr:uid="{4FB6691A-4F41-9C4B-95FA-4432BB464343}">
+    <comment ref="I574" authorId="0" shapeId="0" xr:uid="{B30D1F27-13D9-FB4F-AD0C-0CC7B5439892}">
       <text>
         <r>
           <rPr>
@@ -12252,7 +12281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I575" authorId="0" shapeId="0" xr:uid="{E9E553E3-2FF8-1246-973B-6C8967549710}">
+    <comment ref="I575" authorId="0" shapeId="0" xr:uid="{BE602DC9-BEF2-9347-B8A1-463DBEFD33C3}">
       <text>
         <r>
           <rPr>
@@ -12271,7 +12300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I576" authorId="0" shapeId="0" xr:uid="{40C0ABF7-F0C4-2848-9BC7-436B5EA79C11}">
+    <comment ref="I576" authorId="0" shapeId="0" xr:uid="{88B1B0B9-5485-9A4E-91C8-3C09FBE88F5D}">
       <text>
         <r>
           <rPr>
@@ -12287,7 +12316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I577" authorId="0" shapeId="0" xr:uid="{D502A5A9-3E34-784A-A295-8CCAF52F5780}">
+    <comment ref="I577" authorId="0" shapeId="0" xr:uid="{4A816C83-A057-234B-8E3C-0FD3236404EC}">
       <text>
         <r>
           <rPr>
@@ -12306,7 +12335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I578" authorId="0" shapeId="0" xr:uid="{31B15656-8191-3548-A2E4-D401DD0B3B29}">
+    <comment ref="I578" authorId="0" shapeId="0" xr:uid="{08402326-FA3B-C042-801C-2C41FC142DDE}">
       <text>
         <r>
           <rPr>
@@ -12336,7 +12365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I579" authorId="0" shapeId="0" xr:uid="{A86ED408-1748-924F-B5DA-0635FD7141F9}">
+    <comment ref="I579" authorId="0" shapeId="0" xr:uid="{89D6D04A-C41D-DA44-AC12-4E42C6BE53F7}">
       <text>
         <r>
           <rPr>
@@ -12355,7 +12384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I580" authorId="0" shapeId="0" xr:uid="{B2D86606-9E07-6F4B-8B0A-FEC47D764F95}">
+    <comment ref="I580" authorId="0" shapeId="0" xr:uid="{21C27946-7171-3E4F-8AB0-E7034640B74F}">
       <text>
         <r>
           <rPr>
@@ -12374,7 +12403,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I581" authorId="0" shapeId="0" xr:uid="{D28DE2D2-7A83-6948-B59C-DB4A259E9033}">
+    <comment ref="I581" authorId="0" shapeId="0" xr:uid="{C64F0D92-B5D3-E64D-8D30-16946C3BAA6F}">
       <text>
         <r>
           <rPr>
@@ -12393,7 +12422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I582" authorId="0" shapeId="0" xr:uid="{66817D0A-A69F-1748-BBA3-47C9A5DB1178}">
+    <comment ref="I582" authorId="0" shapeId="0" xr:uid="{2A6AA9A8-A931-A14E-84AC-8CE98E79D812}">
       <text>
         <r>
           <rPr>
@@ -12412,7 +12441,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I583" authorId="0" shapeId="0" xr:uid="{6798A307-DB2A-8949-B550-72BB909574BC}">
+    <comment ref="I583" authorId="0" shapeId="0" xr:uid="{31C31942-F538-984C-A975-62A78585830E}">
       <text>
         <r>
           <rPr>
@@ -12444,7 +12473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I584" authorId="0" shapeId="0" xr:uid="{7557B441-4578-A046-AAB9-8E747A5D55DE}">
+    <comment ref="I584" authorId="0" shapeId="0" xr:uid="{A35F52E6-FDB3-6547-BE60-EBF3BB642C1B}">
       <text>
         <r>
           <rPr>
@@ -12461,7 +12490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I585" authorId="0" shapeId="0" xr:uid="{B9BC503F-CABD-9742-8264-277B0327C6F7}">
+    <comment ref="I585" authorId="0" shapeId="0" xr:uid="{17878D83-07B5-0245-86DE-0E9B5A016066}">
       <text>
         <r>
           <rPr>
@@ -12491,7 +12520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I586" authorId="0" shapeId="0" xr:uid="{E1549801-63B2-424F-82C3-EC94F56DCB34}">
+    <comment ref="I586" authorId="0" shapeId="0" xr:uid="{ED74EE8A-AF60-EC49-BB51-4BEB98BCA7EF}">
       <text>
         <r>
           <rPr>
@@ -12519,7 +12548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I587" authorId="0" shapeId="0" xr:uid="{D6EFE5EE-F835-7346-9D44-4626DFF237B9}">
+    <comment ref="I587" authorId="0" shapeId="0" xr:uid="{66A0F166-FF36-4547-BA60-2BAA003AF1EC}">
       <text>
         <r>
           <rPr>
@@ -12540,7 +12569,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I588" authorId="0" shapeId="0" xr:uid="{C88157F9-4FE7-1243-825F-684FEFCA57C5}">
+    <comment ref="I588" authorId="0" shapeId="0" xr:uid="{16BA1152-D6A1-3441-954F-E62D5F6071CB}">
       <text>
         <r>
           <rPr>
@@ -12568,7 +12597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I589" authorId="0" shapeId="0" xr:uid="{7246133C-C053-0747-84E6-A5AD2DE9CD1A}">
+    <comment ref="I589" authorId="0" shapeId="0" xr:uid="{D66497E2-1F79-3D40-B225-A13AEBA14471}">
       <text>
         <r>
           <rPr>
@@ -12585,7 +12614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I590" authorId="0" shapeId="0" xr:uid="{A1C156D2-B046-834A-97D2-114F450225BE}">
+    <comment ref="I590" authorId="0" shapeId="0" xr:uid="{5886FBF5-C07D-9E4C-A76C-6F1086C724BE}">
       <text>
         <r>
           <rPr>
@@ -12605,7 +12634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I591" authorId="0" shapeId="0" xr:uid="{8246D8F2-EC9B-B740-963E-C167A6FDCDDB}">
+    <comment ref="I591" authorId="0" shapeId="0" xr:uid="{39962BBC-CEBC-C547-9AA2-0C42B35E0854}">
       <text>
         <r>
           <rPr>
@@ -12627,7 +12656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I592" authorId="0" shapeId="0" xr:uid="{B421E78E-E8B2-0347-9992-876F089577FF}">
+    <comment ref="I592" authorId="0" shapeId="0" xr:uid="{09330405-396E-A248-8F3E-D35DA9B202A9}">
       <text>
         <r>
           <rPr>
@@ -12644,7 +12673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I593" authorId="0" shapeId="0" xr:uid="{45D82E8A-6F81-584F-8016-1244E4167128}">
+    <comment ref="I593" authorId="0" shapeId="0" xr:uid="{520F7532-198B-C446-9185-0564D588A84D}">
       <text>
         <r>
           <rPr>
@@ -12660,7 +12689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I594" authorId="0" shapeId="0" xr:uid="{BF28FEFD-2CDC-F844-A61C-2CB61E36425D}">
+    <comment ref="I594" authorId="0" shapeId="0" xr:uid="{5D82BE74-9A8E-AC46-B0C8-C030CD91695D}">
       <text>
         <r>
           <rPr>
@@ -12683,7 +12712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I595" authorId="0" shapeId="0" xr:uid="{51AD775A-43C2-D34B-A5BD-8382C4E1AE96}">
+    <comment ref="I595" authorId="0" shapeId="0" xr:uid="{2981B63A-3DC2-A745-806B-65AF231FEC4A}">
       <text>
         <r>
           <rPr>
@@ -12714,7 +12743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I596" authorId="0" shapeId="0" xr:uid="{A1641957-5883-9545-AFB7-ED7D9CF2141E}">
+    <comment ref="I596" authorId="0" shapeId="0" xr:uid="{C2BF535A-A3AB-6142-87E2-0D947152E7FA}">
       <text>
         <r>
           <rPr>
@@ -12755,7 +12784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I597" authorId="0" shapeId="0" xr:uid="{51F2DD32-158A-B84F-AB96-54369C206921}">
+    <comment ref="I597" authorId="0" shapeId="0" xr:uid="{23FF9160-D15A-B24C-AD75-4FF1D37E62FF}">
       <text>
         <r>
           <rPr>
@@ -12775,7 +12804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I598" authorId="0" shapeId="0" xr:uid="{7014BC35-11ED-C248-A369-83DDCCD3BDA9}">
+    <comment ref="I598" authorId="0" shapeId="0" xr:uid="{686FB4FC-865E-674D-A854-B3279FB8159D}">
       <text>
         <r>
           <rPr>
@@ -12815,7 +12844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I599" authorId="0" shapeId="0" xr:uid="{36AE0EAA-334D-2E46-A53B-1E40DFCA36FC}">
+    <comment ref="I599" authorId="0" shapeId="0" xr:uid="{B547E0DD-5893-DE45-8E1A-CD65D4CB5E09}">
       <text>
         <r>
           <rPr>
@@ -12855,7 +12884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I600" authorId="0" shapeId="0" xr:uid="{89C0CA5B-F7E4-3148-8FB8-837BB4EAF3C6}">
+    <comment ref="I600" authorId="0" shapeId="0" xr:uid="{96C8E188-A2E6-5D4D-81CB-9550B50D982D}">
       <text>
         <r>
           <rPr>
@@ -12882,7 +12911,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I601" authorId="0" shapeId="0" xr:uid="{269BA92A-F605-0944-AD40-44507612F01B}">
+    <comment ref="I601" authorId="0" shapeId="0" xr:uid="{31BD34EB-681F-8A4C-80B2-D9ABA91FF36F}">
       <text>
         <r>
           <rPr>
@@ -12911,7 +12940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I602" authorId="0" shapeId="0" xr:uid="{84E6729C-8E29-254C-9ED4-297131D3B6CA}">
+    <comment ref="I602" authorId="0" shapeId="0" xr:uid="{26DB159F-0452-864D-ACEF-DAEA461794CC}">
       <text>
         <r>
           <rPr>
@@ -12927,7 +12956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I603" authorId="0" shapeId="0" xr:uid="{3DD3FF8E-3E65-9441-9EC7-AB8A58A46761}">
+    <comment ref="I603" authorId="0" shapeId="0" xr:uid="{EFCC04BC-1515-1148-88AE-E23BECF0700D}">
       <text>
         <r>
           <rPr>
@@ -12950,7 +12979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I604" authorId="0" shapeId="0" xr:uid="{DD6818AB-505C-664B-91E4-288F9E38C410}">
+    <comment ref="I604" authorId="0" shapeId="0" xr:uid="{13D2454C-6115-1549-B1B8-AE965ABC651C}">
       <text>
         <r>
           <rPr>
@@ -12975,7 +13004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I605" authorId="0" shapeId="0" xr:uid="{61F2B98B-444B-EB4F-AC0B-1874818FCCBB}">
+    <comment ref="I605" authorId="0" shapeId="0" xr:uid="{F236D4FB-6F06-6C4A-AA44-B5B36F54C2EA}">
       <text>
         <r>
           <rPr>
@@ -13007,7 +13036,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I606" authorId="0" shapeId="0" xr:uid="{13481CC9-19FB-894E-8D90-398C85BDE3EB}">
+    <comment ref="I606" authorId="0" shapeId="0" xr:uid="{DB9CD3AD-7730-5545-9740-1E33A73D0C5B}">
       <text>
         <r>
           <rPr>
@@ -13042,7 +13071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I607" authorId="0" shapeId="0" xr:uid="{4E286A56-679A-A84D-955E-C02E3888D797}">
+    <comment ref="I607" authorId="0" shapeId="0" xr:uid="{277BDC98-6D4C-2D4D-A0E5-B8447A4E0EAB}">
       <text>
         <r>
           <rPr>
@@ -13064,7 +13093,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I608" authorId="0" shapeId="0" xr:uid="{978F746F-B3CF-F046-A7D0-B0BF7F2CA8BE}">
+    <comment ref="I608" authorId="0" shapeId="0" xr:uid="{7B7AA93C-4999-CC47-9033-987AAF33CC2E}">
       <text>
         <r>
           <rPr>
@@ -13094,7 +13123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I609" authorId="0" shapeId="0" xr:uid="{53FC9082-A94D-8D4D-AB9D-704DF43AA657}">
+    <comment ref="I609" authorId="0" shapeId="0" xr:uid="{A8164643-304F-A74E-B045-E4441049F0C7}">
       <text>
         <r>
           <rPr>
@@ -13109,7 +13138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I610" authorId="0" shapeId="0" xr:uid="{DF6D805C-1BD6-E949-92B9-4C882E6EF269}">
+    <comment ref="I610" authorId="0" shapeId="0" xr:uid="{25BB3796-5CF1-5A42-BCD3-0343193957EB}">
       <text>
         <r>
           <rPr>
@@ -13137,7 +13166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I611" authorId="0" shapeId="0" xr:uid="{6131C9FF-77C1-9643-B178-3B23F8AA44AD}">
+    <comment ref="I611" authorId="0" shapeId="0" xr:uid="{1FB1886F-5A6E-1548-AA79-7085D87325BB}">
       <text>
         <r>
           <rPr>
@@ -13158,7 +13187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I612" authorId="0" shapeId="0" xr:uid="{DECC3148-E827-E544-975C-68AC47CF00DA}">
+    <comment ref="I612" authorId="0" shapeId="0" xr:uid="{0E622974-E7CE-B74D-989D-D59C623915A5}">
       <text>
         <r>
           <rPr>
@@ -13199,7 +13228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I613" authorId="0" shapeId="0" xr:uid="{13A19588-2DC0-9444-980F-202D89B8237E}">
+    <comment ref="I613" authorId="0" shapeId="0" xr:uid="{0EC98399-2252-7749-896C-022AE027A958}">
       <text>
         <r>
           <rPr>
@@ -13240,7 +13269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I614" authorId="0" shapeId="0" xr:uid="{B9C1CA9D-1F5F-044B-9E22-398346917A38}">
+    <comment ref="I614" authorId="0" shapeId="0" xr:uid="{983A296A-F14E-6444-B01C-60B2401B8902}">
       <text>
         <r>
           <rPr>
@@ -13272,7 +13301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I615" authorId="0" shapeId="0" xr:uid="{34D3C08F-38E9-EB46-B584-DC198536B622}">
+    <comment ref="I615" authorId="0" shapeId="0" xr:uid="{C6ACAC23-2F43-E141-8049-080EC50F4A42}">
       <text>
         <r>
           <rPr>
@@ -13291,7 +13320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I616" authorId="0" shapeId="0" xr:uid="{44D15BB9-258F-6D44-A812-F40184B9AACC}">
+    <comment ref="I616" authorId="0" shapeId="0" xr:uid="{710334E1-8286-1249-AB8D-A418A8F95CB6}">
       <text>
         <r>
           <rPr>
@@ -13307,7 +13336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I617" authorId="0" shapeId="0" xr:uid="{C7A6667F-D7A2-5E4F-BC1F-2F140691417B}">
+    <comment ref="I617" authorId="0" shapeId="0" xr:uid="{5D7CA182-3EFF-F445-9AF3-F070BCD1313B}">
       <text>
         <r>
           <rPr>
@@ -13326,7 +13355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I618" authorId="0" shapeId="0" xr:uid="{4B369C6D-826C-F440-9F48-851620722727}">
+    <comment ref="I618" authorId="0" shapeId="0" xr:uid="{67AC4783-1123-9049-9DC0-16B11A987838}">
       <text>
         <r>
           <rPr>
@@ -13365,7 +13394,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I619" authorId="0" shapeId="0" xr:uid="{45244FC3-5C90-4742-B5BD-EDCECFC81FBE}">
+    <comment ref="I619" authorId="0" shapeId="0" xr:uid="{3B7EF804-A1CA-D549-A792-1839CEA1C9FC}">
       <text>
         <r>
           <rPr>
@@ -13392,7 +13421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I620" authorId="0" shapeId="0" xr:uid="{ADEFEA2F-D2DF-F04C-92DA-2D9DB2B53798}">
+    <comment ref="I620" authorId="0" shapeId="0" xr:uid="{20D87EF8-F519-5C40-A846-B55691CE5D67}">
       <text>
         <r>
           <rPr>
@@ -13421,7 +13450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I621" authorId="0" shapeId="0" xr:uid="{DB5F3410-DFC9-8F47-AFD2-9434CF832E65}">
+    <comment ref="I621" authorId="0" shapeId="0" xr:uid="{73FE9198-C9CE-FA41-B87F-BF81464AF689}">
       <text>
         <r>
           <rPr>
@@ -13460,7 +13489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I622" authorId="0" shapeId="0" xr:uid="{1415448F-B9BF-A34D-A17D-2BA447D3577A}">
+    <comment ref="I622" authorId="0" shapeId="0" xr:uid="{6F87ED15-D57A-384D-8C9A-7B6430807389}">
       <text>
         <r>
           <rPr>
@@ -13487,7 +13516,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I623" authorId="0" shapeId="0" xr:uid="{A6D383E0-4F25-5A45-B9F2-55C57D236EDD}">
+    <comment ref="I623" authorId="0" shapeId="0" xr:uid="{9452E8EA-E4DD-1F4F-AA82-54B6CAE36EE9}">
       <text>
         <r>
           <rPr>
@@ -13514,7 +13543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I624" authorId="0" shapeId="0" xr:uid="{19F0BCC3-8462-D345-8E24-C94129B13268}">
+    <comment ref="I624" authorId="0" shapeId="0" xr:uid="{C9E906BB-EB08-8C47-8912-6921AC44E132}">
       <text>
         <r>
           <rPr>
@@ -13555,7 +13584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I625" authorId="0" shapeId="0" xr:uid="{B5BB632F-17C9-6348-A5F6-447DEF40F5C2}">
+    <comment ref="I625" authorId="0" shapeId="0" xr:uid="{2EEF9D5F-C3C1-DB4C-A013-8B08BD3D22A3}">
       <text>
         <r>
           <rPr>
@@ -13596,7 +13625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I626" authorId="0" shapeId="0" xr:uid="{0A1BB025-2C22-6C4D-BA28-BFA4084F45A7}">
+    <comment ref="I626" authorId="0" shapeId="0" xr:uid="{EA980E7E-2587-874A-9D41-98EB57C19B7E}">
       <text>
         <r>
           <rPr>
@@ -13619,7 +13648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I627" authorId="0" shapeId="0" xr:uid="{E1B37EC4-C0DF-5F46-9BDD-AD6BE0FB9DF6}">
+    <comment ref="I627" authorId="0" shapeId="0" xr:uid="{FA53D03B-057C-644D-8D75-65AD905B26AA}">
       <text>
         <r>
           <rPr>
@@ -13646,7 +13675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I628" authorId="0" shapeId="0" xr:uid="{99992B86-7FC3-5641-9CF7-167724CC2193}">
+    <comment ref="I628" authorId="0" shapeId="0" xr:uid="{766733FA-82C2-5C43-A5C1-4E2FCBD01870}">
       <text>
         <r>
           <rPr>
@@ -13673,7 +13702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I629" authorId="0" shapeId="0" xr:uid="{4ED8C5CD-4C4D-D74C-9D8A-71DE9E1E79C2}">
+    <comment ref="I629" authorId="0" shapeId="0" xr:uid="{43F2E400-0676-7740-80CE-EC3A4EB2A9D6}">
       <text>
         <r>
           <rPr>
@@ -13706,7 +13735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I630" authorId="0" shapeId="0" xr:uid="{D19E3554-FF85-7443-8AB2-62BF1262FBE3}">
+    <comment ref="I630" authorId="0" shapeId="0" xr:uid="{570F715B-65D9-2140-9754-75523FC8DD6C}">
       <text>
         <r>
           <rPr>
@@ -13725,7 +13754,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I631" authorId="0" shapeId="0" xr:uid="{0F3B0531-E698-964C-9CAF-08BEF5597388}">
+    <comment ref="I631" authorId="0" shapeId="0" xr:uid="{701849ED-D5DC-A748-AE2A-161C9246DC46}">
       <text>
         <r>
           <rPr>
@@ -13761,7 +13790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I632" authorId="0" shapeId="0" xr:uid="{BB13A93C-711B-9B4C-878C-7692652A864A}">
+    <comment ref="I632" authorId="0" shapeId="0" xr:uid="{3C6A48A7-E57D-BB4E-9801-608E81DA930C}">
       <text>
         <r>
           <rPr>
@@ -13802,7 +13831,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I633" authorId="0" shapeId="0" xr:uid="{A8640C62-524D-0444-A45C-FBEB934BE552}">
+    <comment ref="I633" authorId="0" shapeId="0" xr:uid="{E19605E3-77F1-4D43-A068-1A559986740D}">
       <text>
         <r>
           <rPr>
@@ -13834,7 +13863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I634" authorId="0" shapeId="0" xr:uid="{FB38A7CD-962B-334D-9B36-B4AD151C25D7}">
+    <comment ref="I634" authorId="0" shapeId="0" xr:uid="{4211EEC8-3427-F440-B9E5-1E2EAF2B890C}">
       <text>
         <r>
           <rPr>
@@ -13875,7 +13904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I635" authorId="0" shapeId="0" xr:uid="{0A195F30-E9D1-654D-9A46-2A315232EBE9}">
+    <comment ref="I635" authorId="0" shapeId="0" xr:uid="{39721C71-A384-BF45-95FA-9C9EA7B5FAC0}">
       <text>
         <r>
           <rPr>
@@ -13916,7 +13945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I636" authorId="0" shapeId="0" xr:uid="{EDAC8695-82C9-844C-B8B5-491DF99167DF}">
+    <comment ref="I636" authorId="0" shapeId="0" xr:uid="{881F5E36-2D72-2F4B-BC02-AFD522821971}">
       <text>
         <r>
           <rPr>
@@ -13957,7 +13986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I637" authorId="0" shapeId="0" xr:uid="{B25835E8-F920-6B44-9298-1334AFDB6BA5}">
+    <comment ref="I637" authorId="0" shapeId="0" xr:uid="{ED1361EA-7A2C-AB43-9BBA-22178F03141A}">
       <text>
         <r>
           <rPr>
@@ -13989,7 +14018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I638" authorId="0" shapeId="0" xr:uid="{1053980A-07CB-454E-A29A-5575BF875330}">
+    <comment ref="I638" authorId="0" shapeId="0" xr:uid="{E2FFA344-4DBD-D244-8576-F00FBF5D733D}">
       <text>
         <r>
           <rPr>
@@ -14015,7 +14044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I639" authorId="0" shapeId="0" xr:uid="{0A313A35-5F4B-FA4D-A09E-5CF3BB7A3D6E}">
+    <comment ref="I639" authorId="0" shapeId="0" xr:uid="{BC53FD0D-AE0B-FE46-88D9-6D9445C962FB}">
       <text>
         <r>
           <rPr>
@@ -14048,7 +14077,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I640" authorId="0" shapeId="0" xr:uid="{CDCC438E-5E2E-E24D-9913-AF0D7BACCE45}">
+    <comment ref="I640" authorId="0" shapeId="0" xr:uid="{477FA2C5-2156-4641-9E20-721C990DAC70}">
       <text>
         <r>
           <rPr>
@@ -14089,7 +14118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I641" authorId="0" shapeId="0" xr:uid="{A0B5548D-B55F-E244-B718-BDCC87E419DA}">
+    <comment ref="I641" authorId="0" shapeId="0" xr:uid="{20BB0B49-7C95-6247-9C98-929DD2A9A742}">
       <text>
         <r>
           <rPr>
@@ -14106,7 +14135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I642" authorId="0" shapeId="0" xr:uid="{C9C08CDF-20C2-EB48-A57D-3E20285E4EDF}">
+    <comment ref="I642" authorId="0" shapeId="0" xr:uid="{32BA6181-A3BA-7F40-8C5B-6F2B4D0F476D}">
       <text>
         <r>
           <rPr>
@@ -14136,7 +14165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I643" authorId="0" shapeId="0" xr:uid="{4CAAE262-77B8-9B41-9070-A82D60A545F9}">
+    <comment ref="I643" authorId="0" shapeId="0" xr:uid="{BB869905-0224-014E-910C-87CB2F2D6151}">
       <text>
         <r>
           <rPr>
@@ -14152,7 +14181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I644" authorId="0" shapeId="0" xr:uid="{805963B2-37CE-A840-A187-6DC3ADA8742A}">
+    <comment ref="I644" authorId="0" shapeId="0" xr:uid="{7075EA8C-BA93-394B-B79A-C0EADE1115EB}">
       <text>
         <r>
           <rPr>
@@ -14173,7 +14202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I645" authorId="0" shapeId="0" xr:uid="{049F18A5-D072-C748-AE66-DC227FF5C019}">
+    <comment ref="I645" authorId="0" shapeId="0" xr:uid="{0F134B70-353D-FD43-B9C4-4C4DCBD558E0}">
       <text>
         <r>
           <rPr>
@@ -14190,7 +14219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I646" authorId="0" shapeId="0" xr:uid="{927FF306-DEDD-8B4B-9460-0C3E6EE08C8D}">
+    <comment ref="I646" authorId="0" shapeId="0" xr:uid="{A761C2CF-0E0B-1F45-8589-F92DAF02541B}">
       <text>
         <r>
           <rPr>
@@ -14218,7 +14247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I647" authorId="0" shapeId="0" xr:uid="{71B26D0A-2746-A947-A874-B8AE3FBE6F44}">
+    <comment ref="I647" authorId="0" shapeId="0" xr:uid="{BB18D1F4-C8D1-D04B-A634-3ABDB9E86C59}">
       <text>
         <r>
           <rPr>
@@ -14246,7 +14275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I648" authorId="0" shapeId="0" xr:uid="{67CAA1EB-B8A8-E344-8B18-87B5E0C3751E}">
+    <comment ref="I648" authorId="0" shapeId="0" xr:uid="{11D0894E-2A64-644D-A6C3-602B54505CB8}">
       <text>
         <r>
           <rPr>
@@ -14263,7 +14292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I649" authorId="0" shapeId="0" xr:uid="{F7CCABDB-F6D4-B348-81BD-C1D03515AFB5}">
+    <comment ref="I649" authorId="0" shapeId="0" xr:uid="{EBDB1BE5-EEF5-3742-ACE1-12B506DCDD49}">
       <text>
         <r>
           <rPr>
@@ -14278,7 +14307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I650" authorId="0" shapeId="0" xr:uid="{89BBEE84-F6E9-1344-8127-4806D9F68FD5}">
+    <comment ref="I650" authorId="0" shapeId="0" xr:uid="{2EEB9C26-DF52-354A-9765-057EAF5B99A8}">
       <text>
         <r>
           <rPr>
@@ -14298,7 +14327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I651" authorId="0" shapeId="0" xr:uid="{CB5DE6B4-687A-C94D-95CA-FEF4CA184EFE}">
+    <comment ref="I651" authorId="0" shapeId="0" xr:uid="{9D2C7DA8-FCC7-6842-844E-6442B8532E16}">
       <text>
         <r>
           <rPr>
@@ -14320,7 +14349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I652" authorId="0" shapeId="0" xr:uid="{C1FEBF44-E6FF-0A4D-B688-D839B9B39A64}">
+    <comment ref="I652" authorId="0" shapeId="0" xr:uid="{1A93EBC6-B0FD-E44E-8497-FCF131C05327}">
       <text>
         <r>
           <rPr>
@@ -14342,7 +14371,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I653" authorId="0" shapeId="0" xr:uid="{D3AC4A67-4D84-2E49-A1BD-AB85CF836459}">
+    <comment ref="I653" authorId="0" shapeId="0" xr:uid="{FEA1924E-E195-114C-9C68-E627E92BBCA3}">
       <text>
         <r>
           <rPr>
@@ -14358,7 +14387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I654" authorId="0" shapeId="0" xr:uid="{A0D71025-B2E7-D745-BF6B-03F35351262E}">
+    <comment ref="I654" authorId="0" shapeId="0" xr:uid="{D0544D85-A2E8-264F-999A-DBFDCD8B02ED}">
       <text>
         <r>
           <rPr>
@@ -14374,7 +14403,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I655" authorId="0" shapeId="0" xr:uid="{44279DFB-D5FE-1749-BAF0-F8231609132C}">
+    <comment ref="I655" authorId="0" shapeId="0" xr:uid="{237909DC-D1AB-9246-88D0-588C63655658}">
       <text>
         <r>
           <rPr>
@@ -14392,7 +14421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I656" authorId="0" shapeId="0" xr:uid="{ED8768CD-357E-B648-9906-965D28785AD9}">
+    <comment ref="I656" authorId="0" shapeId="0" xr:uid="{82652164-5C8B-F140-B74A-1F98F884EC2E}">
       <text>
         <r>
           <rPr>
@@ -14408,7 +14437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I657" authorId="0" shapeId="0" xr:uid="{EF8F31A7-3137-C345-A2AB-A720077732A9}">
+    <comment ref="I657" authorId="0" shapeId="0" xr:uid="{7ADBA39D-2C37-DD4C-87D5-41D3F4C0BD64}">
       <text>
         <r>
           <rPr>
@@ -14426,7 +14455,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I658" authorId="0" shapeId="0" xr:uid="{0396AD95-C008-1042-A4C8-DFFA8B216711}">
+    <comment ref="I658" authorId="0" shapeId="0" xr:uid="{3A6C0413-E61A-4547-90B3-DAEC9A01B04F}">
       <text>
         <r>
           <rPr>
@@ -14448,7 +14477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I659" authorId="0" shapeId="0" xr:uid="{EDE6F123-125D-4A47-B079-B7D2D599CECA}">
+    <comment ref="I659" authorId="0" shapeId="0" xr:uid="{31F63E9A-539E-064B-8B71-D6D15F1FDD3C}">
       <text>
         <r>
           <rPr>
@@ -14472,7 +14501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I660" authorId="0" shapeId="0" xr:uid="{AF14C7C3-0B2A-7C4C-90C6-43DAFC9942E3}">
+    <comment ref="I660" authorId="0" shapeId="0" xr:uid="{8BA525F3-E790-C541-8383-257364E1A701}">
       <text>
         <r>
           <rPr>
@@ -14490,7 +14519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I661" authorId="0" shapeId="0" xr:uid="{1995D89F-E560-814E-8C70-206F6C0100BC}">
+    <comment ref="I661" authorId="0" shapeId="0" xr:uid="{46474E5B-84AC-C048-9A4B-53DBCEF9FDEB}">
       <text>
         <r>
           <rPr>
@@ -14514,7 +14543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I662" authorId="0" shapeId="0" xr:uid="{8D934E7C-6193-674B-9B13-49602E0BD212}">
+    <comment ref="I662" authorId="0" shapeId="0" xr:uid="{FC1ECBF8-2DD3-F244-A17A-2A7590389396}">
       <text>
         <r>
           <rPr>
@@ -14530,7 +14559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I663" authorId="0" shapeId="0" xr:uid="{3D7F30D1-0DBE-BB4F-8B92-C167F9B59A3C}">
+    <comment ref="I663" authorId="0" shapeId="0" xr:uid="{A4C66D65-A816-B84F-B6C4-D607B3B1BA06}">
       <text>
         <r>
           <rPr>
@@ -14546,7 +14575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I664" authorId="0" shapeId="0" xr:uid="{D18EE9CE-7076-4546-8646-CABD633F5153}">
+    <comment ref="I664" authorId="0" shapeId="0" xr:uid="{CD0D63CF-6382-4B49-A0D9-35A866BF41D5}">
       <text>
         <r>
           <rPr>
@@ -14562,7 +14591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I665" authorId="0" shapeId="0" xr:uid="{08070E31-B217-544F-9DBC-77A1A3454A4A}">
+    <comment ref="I665" authorId="0" shapeId="0" xr:uid="{86BFBFCB-CD3F-CC4F-94C0-AA57FDBFCE85}">
       <text>
         <r>
           <rPr>
@@ -14578,7 +14607,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I666" authorId="0" shapeId="0" xr:uid="{CE81F9EC-B8EE-CC4B-B7A8-BF1ECA85D270}">
+    <comment ref="I666" authorId="0" shapeId="0" xr:uid="{23C6FE18-DE50-D84E-A8A0-F18E0F6A942E}">
       <text>
         <r>
           <rPr>
@@ -14607,7 +14636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I667" authorId="0" shapeId="0" xr:uid="{7EE566BB-B675-224F-B4AE-0090838FC037}">
+    <comment ref="I667" authorId="0" shapeId="0" xr:uid="{3606F3EF-ACA6-D14E-A924-3D1CC257BB77}">
       <text>
         <r>
           <rPr>
@@ -14624,7 +14653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I668" authorId="0" shapeId="0" xr:uid="{C1CB1F04-81F7-E94A-B1E3-29926A92CB25}">
+    <comment ref="I668" authorId="0" shapeId="0" xr:uid="{B6835CE5-55D6-F54E-8E16-C19CC3A171F8}">
       <text>
         <r>
           <rPr>
@@ -14639,7 +14668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I669" authorId="0" shapeId="0" xr:uid="{9506F1CF-FC85-7C4A-9EED-E0AED9493570}">
+    <comment ref="I669" authorId="0" shapeId="0" xr:uid="{7A995559-FC5B-C747-9F08-C92FFE18AE81}">
       <text>
         <r>
           <rPr>
@@ -14654,7 +14683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I670" authorId="0" shapeId="0" xr:uid="{3B485F75-409F-9E44-A05A-407CDEE3BC29}">
+    <comment ref="I670" authorId="0" shapeId="0" xr:uid="{DD8A15B9-749D-AE43-8FF6-4D13CDA32B23}">
       <text>
         <r>
           <rPr>
@@ -14670,7 +14699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I671" authorId="0" shapeId="0" xr:uid="{EDE38C4D-4DFE-9742-9BC2-E49DE8DF193D}">
+    <comment ref="I671" authorId="0" shapeId="0" xr:uid="{99E93C0A-9C38-7B44-A0D9-1BDF6CCD24EF}">
       <text>
         <r>
           <rPr>
@@ -14699,7 +14728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I672" authorId="0" shapeId="0" xr:uid="{81BB9D30-31CE-B844-B482-8831F3B132ED}">
+    <comment ref="I672" authorId="0" shapeId="0" xr:uid="{7BABFBAE-E8B2-D44D-B62E-E5B7CF10748C}">
       <text>
         <r>
           <rPr>
@@ -14728,7 +14757,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I673" authorId="0" shapeId="0" xr:uid="{0ABB16AA-C0B4-F74C-AA80-3D039A800B5E}">
+    <comment ref="I673" authorId="0" shapeId="0" xr:uid="{3B32DAEC-3AA2-B448-9F6B-FBCBDC9E7913}">
       <text>
         <r>
           <rPr>
@@ -14752,7 +14781,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I674" authorId="0" shapeId="0" xr:uid="{C17C1DD7-B2F0-6F4A-8896-EE21E001F380}">
+    <comment ref="I674" authorId="0" shapeId="0" xr:uid="{01CDDD1D-8AD4-7A43-8E08-4F7A3043E822}">
       <text>
         <r>
           <rPr>
@@ -14769,7 +14798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I675" authorId="0" shapeId="0" xr:uid="{4164230B-2822-8543-BC1B-3784FA539781}">
+    <comment ref="I675" authorId="0" shapeId="0" xr:uid="{D2A697AF-96E7-0541-80F4-36B527E9917E}">
       <text>
         <r>
           <rPr>
@@ -14798,7 +14827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I676" authorId="0" shapeId="0" xr:uid="{6A31E0DF-100F-A94C-899F-C499B795A8F8}">
+    <comment ref="I676" authorId="0" shapeId="0" xr:uid="{1BEAE932-5ECD-C44F-A9F9-124AB027B20E}">
       <text>
         <r>
           <rPr>
@@ -14834,7 +14863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I677" authorId="0" shapeId="0" xr:uid="{5D1C2575-AE1B-E44C-B94A-64184294E8FA}">
+    <comment ref="I677" authorId="0" shapeId="0" xr:uid="{3C67899E-3A76-6E4A-B70B-AEE008A0D37F}">
       <text>
         <r>
           <rPr>
@@ -14869,7 +14898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I678" authorId="0" shapeId="0" xr:uid="{0D97C623-E740-C545-8A58-2FF500515D03}">
+    <comment ref="I678" authorId="0" shapeId="0" xr:uid="{FCB50A92-44B2-424B-9DB5-D696B533495A}">
       <text>
         <r>
           <rPr>
@@ -14884,7 +14913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I679" authorId="0" shapeId="0" xr:uid="{8A87145C-AE5D-C64E-87BF-0C3853C02292}">
+    <comment ref="I679" authorId="0" shapeId="0" xr:uid="{DA647732-AEA0-8541-9988-871049975F25}">
       <text>
         <r>
           <rPr>
@@ -14902,7 +14931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I680" authorId="0" shapeId="0" xr:uid="{51F44B54-C1C3-B142-96E9-D992C48317B9}">
+    <comment ref="I680" authorId="0" shapeId="0" xr:uid="{B207843F-C069-0B4E-8C3E-0FCD1801FF40}">
       <text>
         <r>
           <rPr>
@@ -14917,7 +14946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I681" authorId="0" shapeId="0" xr:uid="{E81FD5D4-DC45-944C-BDFD-B51E743D0D7C}">
+    <comment ref="I681" authorId="0" shapeId="0" xr:uid="{0D1C082E-F066-8348-8A65-0E623C14442E}">
       <text>
         <r>
           <rPr>
@@ -14935,7 +14964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I682" authorId="0" shapeId="0" xr:uid="{7B431798-57D6-2642-B9E3-3457326B4387}">
+    <comment ref="I682" authorId="0" shapeId="0" xr:uid="{1CD47A58-0A9C-4D48-B13A-B1186744BA91}">
       <text>
         <r>
           <rPr>
@@ -14952,7 +14981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I683" authorId="0" shapeId="0" xr:uid="{9CF41E23-62B3-0F41-9A09-85B6A2600A75}">
+    <comment ref="I683" authorId="0" shapeId="0" xr:uid="{8447B169-F392-6D44-97BD-74B81AC8E5B5}">
       <text>
         <r>
           <rPr>
@@ -14968,7 +14997,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I684" authorId="0" shapeId="0" xr:uid="{C8EDDDEC-34B7-FB4F-879D-1E8CBFCD8B13}">
+    <comment ref="I684" authorId="0" shapeId="0" xr:uid="{5C03A259-2BAB-E345-A620-163826C85B53}">
       <text>
         <r>
           <rPr>
@@ -14984,7 +15013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I685" authorId="0" shapeId="0" xr:uid="{0A405254-95D9-C747-9EFC-D4C55C2A151F}">
+    <comment ref="I685" authorId="0" shapeId="0" xr:uid="{B69B8EC8-5BF3-D246-B989-CE355D8FF9F3}">
       <text>
         <r>
           <rPr>
@@ -15000,7 +15029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I686" authorId="0" shapeId="0" xr:uid="{7980B67B-B764-0143-9503-C715EF28CE7C}">
+    <comment ref="I686" authorId="0" shapeId="0" xr:uid="{6A47F435-B5CC-934A-B627-7866C5F90E49}">
       <text>
         <r>
           <rPr>
@@ -15020,7 +15049,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I687" authorId="0" shapeId="0" xr:uid="{8876C77B-DFDF-A94D-B50A-835723A38BC7}">
+    <comment ref="I687" authorId="0" shapeId="0" xr:uid="{FD9FAA42-22F3-0244-A57A-85FBEC4C7328}">
       <text>
         <r>
           <rPr>
@@ -15038,7 +15067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I688" authorId="0" shapeId="0" xr:uid="{012BCE5F-E9E3-F144-B26F-8330D9478B2F}">
+    <comment ref="I688" authorId="0" shapeId="0" xr:uid="{D3995A77-1FD9-6B44-838C-E30FED575BB1}">
       <text>
         <r>
           <rPr>
@@ -15055,7 +15084,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I689" authorId="0" shapeId="0" xr:uid="{DD62EC0B-0EF7-4C4D-9FDF-E10807C2F697}">
+    <comment ref="I689" authorId="0" shapeId="0" xr:uid="{1B927980-DE54-5240-A023-DF5C3001E92C}">
       <text>
         <r>
           <rPr>
@@ -15069,7 +15098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I690" authorId="0" shapeId="0" xr:uid="{11A47137-1294-1B45-A803-1AD3247C9D29}">
+    <comment ref="I690" authorId="0" shapeId="0" xr:uid="{6CCFD22A-86B2-1E4F-BBDE-FDE2494F6A2C}">
       <text>
         <r>
           <rPr>
@@ -15087,7 +15116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I691" authorId="0" shapeId="0" xr:uid="{D592889A-9EBE-1A4D-8401-1512DFA05BDC}">
+    <comment ref="I691" authorId="0" shapeId="0" xr:uid="{11ABFCA2-2F31-1F4C-958B-D2EEED6C027A}">
       <text>
         <r>
           <rPr>
@@ -15105,7 +15134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I692" authorId="0" shapeId="0" xr:uid="{0AD775B5-F2CF-F441-9914-FD7645D42040}">
+    <comment ref="I692" authorId="0" shapeId="0" xr:uid="{6DDD2BE0-E23F-B940-BCC0-1AFB87FBEDA7}">
       <text>
         <r>
           <rPr>
@@ -15123,7 +15152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I693" authorId="0" shapeId="0" xr:uid="{A0C3AD79-1D9B-2446-9AA9-5A8C48E1BF12}">
+    <comment ref="I693" authorId="0" shapeId="0" xr:uid="{6E2E78D3-A4D3-FE47-87CE-C4E25B409A91}">
       <text>
         <r>
           <rPr>
@@ -15143,7 +15172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I694" authorId="0" shapeId="0" xr:uid="{8CC63BAF-34D5-514F-97B4-62681DC61527}">
+    <comment ref="I694" authorId="0" shapeId="0" xr:uid="{50B9023D-782E-9B46-AC26-2033432159F0}">
       <text>
         <r>
           <rPr>
@@ -15160,7 +15189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I695" authorId="0" shapeId="0" xr:uid="{F3DBD689-1946-9D40-9629-5D6D460391AB}">
+    <comment ref="I695" authorId="0" shapeId="0" xr:uid="{0604CB0E-B8D8-B74B-8DD7-97296BF8C962}">
       <text>
         <r>
           <rPr>
@@ -15177,7 +15206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I696" authorId="0" shapeId="0" xr:uid="{ED768AF5-FD89-EE43-BAB9-D081967B82A7}">
+    <comment ref="I696" authorId="0" shapeId="0" xr:uid="{71F36FFB-AC31-A04D-A759-31D323CBBCBB}">
       <text>
         <r>
           <rPr>
@@ -15194,45 +15223,431 @@
         </r>
       </text>
     </comment>
-    <comment ref="I697" authorId="0" shapeId="0" xr:uid="{70784545-0E88-6044-8EEF-FA0C3F7AA51D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>엘리자베스 제인 코크런: 주다온
-에라스무스 윌슨: 최민우
-조지 매든: 유성재
-콜드웰&amp;공장부장: 나현진
-도로시&amp;에이프릴: 시민지
-밀라: 임바로미
-루나&amp;소피아: 이준혁(넬)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I698" authorId="0" shapeId="0" xr:uid="{47F94695-D35A-224C-A087-5FE8D51D03F4}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>바슬라프 포미치 니진스키: 신주협
-세르게이 파블로비치 디아길레프: 조성윤
-이고르 표도로비치 스트라빈스키: 김도하(김지훈)
-로몰라 드 풀츠키 로몰라: 이다경
+    <comment ref="I697" authorId="0" shapeId="0" xr:uid="{6C4FCAA3-3AA0-BF42-A1B7-0FA10D9BD21A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>엘리자베스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>제인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>코크런</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주다온</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에라스무스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>윌슨</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최민우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>매든</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>유성재</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>콜드웰</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>&amp;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>공장부장</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>나현진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>도로시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>&amp;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에이프릴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>시민지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>밀라</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임바로미</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>&amp;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>소피아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이준혁</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>넬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I698" authorId="0" shapeId="0" xr:uid="{70DDE62C-5C47-634F-827F-83A24D43D3FF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>니진스키: 신주협
+디아길레프: 조성윤
+스트라빈스키: 김도하(김지훈)
+로몰라: 이다경
 한스 / 분신: 이지명</t>
         </r>
       </text>
     </comment>
-    <comment ref="I699" authorId="0" shapeId="0" xr:uid="{E7D66FE6-9412-2C4E-BF82-36D1285FD963}">
+    <comment ref="I699" authorId="0" shapeId="0" xr:uid="{221D3F93-CACC-AF4C-AEEC-E1CAA5A18790}">
       <text>
         <r>
           <rPr>
@@ -15248,7 +15663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I700" authorId="0" shapeId="0" xr:uid="{97657C22-2F11-4244-947B-63715A331D28}">
+    <comment ref="I700" authorId="0" shapeId="0" xr:uid="{AED1D80C-4B31-A94D-AAF9-7CB77CB87AFD}">
       <text>
         <r>
           <rPr>
@@ -15266,7 +15681,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I701" authorId="0" shapeId="0" xr:uid="{553C47A4-98A2-F640-BBC3-ED7FB6CCF47B}">
+    <comment ref="I701" authorId="0" shapeId="0" xr:uid="{A7C70930-05F8-184E-B364-7C9C7AAA242D}">
       <text>
         <r>
           <rPr>
@@ -15285,7 +15700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I702" authorId="0" shapeId="0" xr:uid="{D0C3964F-C27A-7948-ACB0-4D0A5FD24FFD}">
+    <comment ref="I702" authorId="0" shapeId="0" xr:uid="{F70962D0-CA49-B44C-BF47-AF679AB8AFC8}">
       <text>
         <r>
           <rPr>
@@ -15300,25 +15715,25 @@
         </r>
       </text>
     </comment>
-    <comment ref="I703" authorId="0" shapeId="0" xr:uid="{156BC767-AFA4-FB4C-A9F7-8D34C19BCADE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>바슬라프 포미치 니진스키: 박준휘
-세르게이 파블로비치 디아길레프: 조성윤
-이고르 표도로비치 스트라빈스키: 박선영
-로몰라 드 풀츠키 로몰라: 이다경
+    <comment ref="I703" authorId="0" shapeId="0" xr:uid="{A221FF7C-4E46-1745-BDAA-297DE78F6BCB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>니진스키: 박준휘
+디아길레프: 조성윤
+스트라빈스키: 박선영
+로몰라: 이다경
 한스 / 분신: 이지명</t>
         </r>
       </text>
     </comment>
-    <comment ref="I704" authorId="0" shapeId="0" xr:uid="{BD695DA6-1858-534E-91A9-A6C48B33D0EC}">
+    <comment ref="I704" authorId="0" shapeId="0" xr:uid="{FE7E6419-54F2-3D47-AEE8-59F0FD90AAB8}">
       <text>
         <r>
           <rPr>
@@ -15345,7 +15760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I705" authorId="0" shapeId="0" xr:uid="{6E023EE2-0105-EC4D-9B41-E3F7B77A3D21}">
+    <comment ref="I705" authorId="0" shapeId="0" xr:uid="{AFE07691-DFD1-064E-8FAB-97F8A3798EE4}">
       <text>
         <r>
           <rPr>
@@ -15361,7 +15776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I706" authorId="0" shapeId="0" xr:uid="{A2F0EFDD-5695-3F41-8010-21F99CEA11C5}">
+    <comment ref="I706" authorId="0" shapeId="0" xr:uid="{BD23C901-3D28-014D-B23E-FD16A6CFF900}">
       <text>
         <r>
           <rPr>
@@ -15377,37 +15792,660 @@
         </r>
       </text>
     </comment>
-    <comment ref="I707" authorId="0" shapeId="0" xr:uid="{E9CC24E7-1BDD-6A49-A83F-060589C5B932}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>제이크 스터디: 배수빈
-조이 스터디: 최석진
-로빈 디토나: 전익령
-트와일라 스터디: 김지혜
-라우디 에이커스: 허영손</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I708" authorId="0" shapeId="0" xr:uid="{A5D72318-2D9B-5F42-8BBA-3820BDF63170}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>지나(지나이다 알렉산드로브나 자시에키나) : 최연우
-빅토르 세르게예비치 투르게네프: 조성윤
-이반 빅토로비치 투르게네프: 한상훈</t>
+    <comment ref="I707" authorId="0" shapeId="0" xr:uid="{20D884D1-CE9A-E542-B90F-967E6C1E67D6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>제이크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스터디</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>배수빈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스터디</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최석진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>로빈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>디토나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전익령</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>트와일라</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스터디</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지혜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>라우디</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에이커스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>허영손</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I708" authorId="0" shapeId="0" xr:uid="{F449E6FF-3BF2-4C46-B1AA-7E3F0414B982}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지나이다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>알렉산드로브나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>자시에키나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) : </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최연우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>빅토르</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>세르게예비치</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>투르게네프</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조성윤</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이반</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>빅토로비치</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>투르게네프</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>한상훈</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I709" authorId="1" shapeId="0" xr:uid="{E8670081-ED86-B94B-A2C9-8D55C2D07149}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>차미호</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재림</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>차미</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>정우연</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>김고대</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>정욱진</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>오진혁</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준영</t>
         </r>
       </text>
     </comment>
@@ -15416,7 +16454,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8500" uniqueCount="3972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8512" uniqueCount="3977">
   <si>
     <t>시즌</t>
   </si>
@@ -27332,6 +28370,21 @@
   </si>
   <si>
     <t>https://blog.naver.com/playnmu/223909211648</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 이재림 정우연 정욱진 김준영 </t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/151p6Aup0qZki6hvL_E73D-XKB7jHAqBNW0_aKy_5m9w/edit?tab=t.0#heading=h.w1scvyj1ovhr</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OJGv2IED-NzNkIASfP9G-3dWfR2G56P2/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/258400</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/223917877555</t>
   </si>
 </sst>
 </file>
@@ -27343,7 +28396,7 @@
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -27452,6 +28505,13 @@
       <name val="굴림"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -28560,7 +29620,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:P708" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:P709" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -28886,7 +29946,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T708"/>
+  <dimension ref="A1:T709"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="13" customWidth="1"/>
@@ -67134,9 +68194,60 @@
         <v>16</v>
       </c>
     </row>
+    <row r="709" spans="1:20" ht="17" customHeight="1">
+      <c r="A709" s="56">
+        <f>N(A708)+1</f>
+        <v>708</v>
+      </c>
+      <c r="B709" s="57">
+        <v>45838</v>
+      </c>
+      <c r="C709" s="58">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D709" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E709" s="59" t="s">
+        <v>164</v>
+      </c>
+      <c r="F709" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G709" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="H709" s="59" t="s">
+        <v>824</v>
+      </c>
+      <c r="I709" s="61" t="s">
+        <v>3972</v>
+      </c>
+      <c r="J709" s="52">
+        <v>0</v>
+      </c>
+      <c r="K709" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="L709" s="72" t="s">
+        <v>3974</v>
+      </c>
+      <c r="M709" s="72" t="s">
+        <v>3976</v>
+      </c>
+      <c r="N709" s="48" t="s">
+        <v>3973</v>
+      </c>
+      <c r="O709" s="48" t="s">
+        <v>3975</v>
+      </c>
+      <c r="P709" s="49" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="B2:B708">
+  <conditionalFormatting sqref="B2:B709">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8239FF8-E36E-0D49-8EAC-EB2BCD1C3E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6810418E-89D1-4C49-83B8-116462D3D458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="14400" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -42,10 +42,9 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>System</author>
-    <author>Jie-Soo Lee</author>
   </authors>
   <commentList>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{F241879F-2CEA-D541-B33D-4CE3AA78DF2D}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{657E1917-2003-BE4E-8046-19AE6F65E430}">
       <text>
         <r>
           <rPr>
@@ -79,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{D6B0BAA5-F3A5-5542-9D22-3BD36F2CD692}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{AF5899F9-3B42-244E-90E6-F93C3A03BBBB}">
       <text>
         <r>
           <rPr>
@@ -107,868 +106,37 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{F5F43810-9820-E142-B8E4-A4D18A1D3135}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>지킬</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>&amp;</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>하이드</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>홍광호</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루시</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윤공주</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>엠마</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이정화</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>댄버스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>경</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김봉환</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>어터슨</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김도형</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>새비지</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>/</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>풀</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>강상범</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>비컨스필드</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>/</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>기네비어</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>홍금단</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>글로솝</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이창완</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>주교</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이상훈</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스트라이드</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>/</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스파이더</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이용진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>프룹스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김이삭</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>앙상블</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이재현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>신재희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>장은희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>맹원태</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이호진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김도현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김준희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>남궁혜윤</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>허윤혜</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김도하</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김지훈</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">) </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이다경</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>정귀희</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스윙</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: 
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>유환</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>권오현</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윤나영</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{679A1A29-C802-FC45-B663-CB1B4E773B32}">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{8B85A0FE-67E5-6D45-B07B-3D109D3EFA9B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>지킬&amp;하이드: 홍광호
+루시: 윤공주
+엠마: 이정화
+댄버스 경: 김봉환
+어터슨: 김도형
+새비지/풀: 강상범
+비컨스필드/기네비어: 홍금단
+글로솝: 이창완
+주교: 이상훈
+스트라이드/스파이더: 이용진
+프룹스: 김이삭
+앙상블: 
+이재현 신재희 장은희 맹원태 
+이호진 김도현 김준희 남궁혜윤 
+허윤혜 김도하(김지훈) 이다경 정귀희
+스윙: 
+유환 권오현 윤나영</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{128AD696-DCEE-B14A-82BD-FEAF622B2F48}">
       <text>
         <r>
           <rPr>
@@ -1002,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{D6046E75-224C-D74E-8CA1-AA7830C8CBCB}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{24C91627-7101-D242-83AE-D42FE39F738C}">
       <text>
         <r>
           <rPr>
@@ -1036,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{6429579C-6F02-FA4A-A904-83305B30EE23}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{DEA7C4DF-4E3F-4144-A8E6-E985FDA071DE}">
       <text>
         <r>
           <rPr>
@@ -1066,7 +234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{F88A2CFD-7027-714A-9B9A-0D79174FC116}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{D724B00B-C4FF-3643-A0D9-8248BDA05F4B}">
       <text>
         <r>
           <rPr>
@@ -1096,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{F112996B-AD6E-E047-AFCC-16B052C25307}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{7FDBD52B-E654-724A-AD30-DBDA74809F52}">
       <text>
         <r>
           <rPr>
@@ -1127,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{60946D83-AF99-BC47-89A3-B815C936DFD9}">
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{2B963D28-18CE-3F43-809B-D2DB9F67D403}">
       <text>
         <r>
           <rPr>
@@ -1158,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{1DB826E8-1C96-BC40-91BD-03E3962B1D96}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{650088D4-AEED-8A4A-9287-4B2E65D1744A}">
       <text>
         <r>
           <rPr>
@@ -1189,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{1CF0D8AB-C22A-8A4F-869E-C0467FC18C49}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{3AD3CE2F-8749-0342-860E-E1C41E27B302}">
       <text>
         <r>
           <rPr>
@@ -1220,7 +388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{710890DC-AE3A-5F42-9D51-1EF9F68BC27B}">
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{D98BFF85-E221-8542-9713-8991530C2821}">
       <text>
         <r>
           <rPr>
@@ -1250,7 +418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{AF863A0E-963C-1446-A964-750A165575B0}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{F38D3B1A-BCC8-824E-959A-0E7C0B31C4AA}">
       <text>
         <r>
           <rPr>
@@ -1281,7 +449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{6A2BC204-B745-8040-B088-9DA110ECC7EE}">
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{A3B4ED2F-8A43-494E-A4D2-156AA45A0AC1}">
       <text>
         <r>
           <rPr>
@@ -1312,7 +480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{85305F9D-5786-EB45-A40C-CA8C31CEB6F2}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{2F267C96-5D7A-3F47-8BAF-D2BE672CF255}">
       <text>
         <r>
           <rPr>
@@ -1343,7 +511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{43EB95C4-DD81-974C-97EE-22C9B88293D7}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{C75EAC0B-4CDF-7F4A-A59B-DED913812FF9}">
       <text>
         <r>
           <rPr>
@@ -1374,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{2FFF2CB9-CC10-6C4C-B38A-B4E9420984A9}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{46BE4FD3-8B8D-3F40-8CAF-DD72B624D9AC}">
       <text>
         <r>
           <rPr>
@@ -1405,38 +573,841 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{853386D7-D3C4-234B-B1F5-510E90F8C740}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>아더: ㅅㅂ
-귀네비어: 임정희
-랜슬롯: 임병근
-모르간: 리사
-멜레아강: 김찬호
-멀린: 지혜근
-케이: 김지욱
-레이아: 정다영
-늑대: 이기흥
-사슴: 이영호
-가웨인: 이종찬
-앙상블: 
-주홍균 최민준 이재범 권기중 
-노해영 오홍학 임동섭 이승현 
-김정민 이보슬 남궁민희 황보주성 
-고샛별 우미나 홍윤영 김재희 임상희
-스윙: 
-전성혜 하웅환 이윤환</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00A46DBB-9AAF-364C-B1B3-165575704896}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{AE5F7961-A9E4-5B4F-8737-BD33C84079E3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아더</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ㅅㅂ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>귀네비어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임정희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>랜슬롯</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임병근</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>모르간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>리사</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>멜레아강</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김찬호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>멀린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지혜근</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레이아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정다영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>늑대</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이기흥</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>사슴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이영호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>가웨인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이종찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앙상블</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주홍균</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최민준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재범</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>권기중</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>노해영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>오홍학</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임동섭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이승현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김정민</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이보슬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>남궁민희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황보주성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>고샛별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>우미나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍윤영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김재희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임상희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스윙</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전성혜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>하웅환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이윤환</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{52A9E8AE-74E4-BA4A-959C-017A2684091F}">
       <text>
         <r>
           <rPr>
@@ -1454,7 +1425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{024AFD6A-FE69-E940-91B2-DA9F8A3D4B74}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{E168D125-5447-1443-BEE4-C4D0225B080D}">
       <text>
         <r>
           <rPr>
@@ -1472,7 +1443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{E5E2013F-AF04-8B4B-A0C8-EC717BF36DE9}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{35103124-AA39-6443-8508-ECEDF183A0A6}">
       <text>
         <r>
           <rPr>
@@ -1489,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{D5CC1712-3806-9A4D-A480-B544E6CAC04D}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{223F1A10-B78D-3A46-A3A7-50B07542EE6B}">
       <text>
         <r>
           <rPr>
@@ -1506,7 +1477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{C0EDC518-5CE9-7B4E-B6EE-6FFCB89AA9BF}">
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{05EF4FFB-933D-124C-A693-590786A7B27F}">
       <text>
         <r>
           <rPr>
@@ -1522,7 +1493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{AE21ABC5-2E5B-4442-8F6A-93AD8F9D5F06}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{1134705A-93EF-5748-B853-7DFA55D1EA45}">
       <text>
         <r>
           <rPr>
@@ -1546,7 +1517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{EF58C723-FBE9-4549-9416-39FABE1C5D70}">
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{58DD59C1-927E-E04A-8BBA-7BE5F981B5F8}">
       <text>
         <r>
           <rPr>
@@ -1564,7 +1535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{AA638651-B2F4-AF4C-B9A1-3A39BEBBC402}">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{AC25EE6C-F3C2-EA43-9EC0-27921B54C698}">
       <text>
         <r>
           <rPr>
@@ -1580,7 +1551,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{01AE70F3-1186-0E44-B34F-4E6ED05A6F9A}">
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{AB0C9DDE-580D-FC4A-8BEF-0DA6C3541E87}">
       <text>
         <r>
           <rPr>
@@ -1609,7 +1580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{09D09F2D-14DF-414B-B69F-4B66CED0B6B6}">
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{44FF7671-5728-EB4A-9C1C-A35C9EBE9838}">
       <text>
         <r>
           <rPr>
@@ -1625,7 +1596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{7E82B788-B12D-784F-AF25-B3D53056A86A}">
+    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{A175FE71-55E1-4240-B340-E445953AA81D}">
       <text>
         <r>
           <rPr>
@@ -1654,7 +1625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{9A3A6D99-A9FC-FE49-BE46-FB2E21986E08}">
+    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{9B624174-5AC3-F64F-BCB8-CFF79EC00469}">
       <text>
         <r>
           <rPr>
@@ -1683,7 +1654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{EA55C0F2-6DF0-7740-9282-23869585F59A}">
+    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{F40FF39E-E986-CF42-8AF0-BB1C0B5932DF}">
       <text>
         <r>
           <rPr>
@@ -1707,7 +1678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{B5AAF0D3-6DCF-5B44-8A61-84E3B4DB1791}">
+    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{8A6D7E6B-777A-5848-9170-29041B35304B}">
       <text>
         <r>
           <rPr>
@@ -1723,7 +1694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{E6FCB3C2-E368-5D4F-92BA-5568A9541F5F}">
+    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{672E1809-9AE7-C949-9611-6EB6B32E6E4D}">
       <text>
         <r>
           <rPr>
@@ -1752,7 +1723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{84F657B9-E031-B14F-BC7E-1B1808ADA6FD}">
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{B8E4A6FD-A778-704F-9EAC-6E71A98F664D}">
       <text>
         <r>
           <rPr>
@@ -1769,7 +1740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{3B2F671C-EE0B-3D4F-8E0A-FF37747060A8}">
+    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{B9A8F79D-4C66-284E-A287-6313B3027793}">
       <text>
         <r>
           <rPr>
@@ -1798,7 +1769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{8EEBF8DC-832D-9C4D-B0AC-BC1D9D737C63}">
+    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{85D1D955-A0D7-BB4F-8ADC-FF1569020C9D}">
       <text>
         <r>
           <rPr>
@@ -1814,7 +1785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{CB503437-8718-284E-A7CA-E993DE56E5D0}">
+    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{17CA612E-52E6-E044-BF6A-9D71926F0D19}">
       <text>
         <r>
           <rPr>
@@ -1840,7 +1811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{8335AF87-4D18-B141-A1AD-664AE765BFFF}">
+    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{700BE64B-C22C-9046-8F55-93AE35EE0F1A}">
       <text>
         <r>
           <rPr>
@@ -1856,7 +1827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I40" authorId="0" shapeId="0" xr:uid="{774D8452-C118-1445-9C9B-F228D7B1398E}">
+    <comment ref="I40" authorId="0" shapeId="0" xr:uid="{3C76D509-A99C-D347-BF64-6BC33F724D37}">
       <text>
         <r>
           <rPr>
@@ -1872,7 +1843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{87DB4414-D027-EB43-8FBE-E70E2F24A248}">
+    <comment ref="I41" authorId="0" shapeId="0" xr:uid="{DCA54E03-8F60-BA48-AB36-A88F9CC8EA60}">
       <text>
         <r>
           <rPr>
@@ -1889,7 +1860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{11906F85-85CD-CA49-A089-72A9A3112843}">
+    <comment ref="I42" authorId="0" shapeId="0" xr:uid="{C76F54AF-63BD-A740-9239-38E92F2D822F}">
       <text>
         <r>
           <rPr>
@@ -1905,7 +1876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{53642EC4-D884-0042-8D62-508558A1C790}">
+    <comment ref="I43" authorId="0" shapeId="0" xr:uid="{8E2790D7-8377-3F4B-A6E9-C190152F28AC}">
       <text>
         <r>
           <rPr>
@@ -1921,7 +1892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I44" authorId="0" shapeId="0" xr:uid="{E82C5067-42EB-CC41-9C60-93CA9C28B3E4}">
+    <comment ref="I44" authorId="0" shapeId="0" xr:uid="{4C0D6D13-5607-A94C-8670-29D8185C0B11}">
       <text>
         <r>
           <rPr>
@@ -1937,7 +1908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I45" authorId="0" shapeId="0" xr:uid="{FCBA8920-BAF3-6A45-8E79-C9A30C55E3A1}">
+    <comment ref="I45" authorId="0" shapeId="0" xr:uid="{E1154616-8A4A-0140-A548-9687DE36D173}">
       <text>
         <r>
           <rPr>
@@ -1964,7 +1935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I46" authorId="0" shapeId="0" xr:uid="{A5A089FF-D727-1E49-BCEA-5DE8896FF100}">
+    <comment ref="I46" authorId="0" shapeId="0" xr:uid="{5EF87225-D2E7-7F48-ABA6-006E9D5F0DB7}">
       <text>
         <r>
           <rPr>
@@ -1993,7 +1964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{BE53CE3D-119E-BD43-BB60-83FA223445A1}">
+    <comment ref="I47" authorId="0" shapeId="0" xr:uid="{D6704989-67EE-4348-B8EF-B244CD526C65}">
       <text>
         <r>
           <rPr>
@@ -2009,7 +1980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{AB039D0E-E07A-934F-A338-763E5898DF5B}">
+    <comment ref="I48" authorId="0" shapeId="0" xr:uid="{DB51F173-8B1F-0A42-B703-3B6DD5468785}">
       <text>
         <r>
           <rPr>
@@ -2025,7 +1996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{FE013450-1C47-0843-8B66-92C2C14E5FFB}">
+    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{2A2AD8FF-58A1-4A42-9CC1-C7DFD1824509}">
       <text>
         <r>
           <rPr>
@@ -2040,7 +2011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{2063074F-0B3B-FC44-AFC9-59EED48C8F96}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{2E1C8CA2-427B-B943-B30A-60DB87839A23}">
       <text>
         <r>
           <rPr>
@@ -2067,7 +2038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{55954392-5C0D-2248-B496-D8C1F6C9F93C}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{28AEADF4-B1C6-844A-BAB6-6B6A23A405F4}">
       <text>
         <r>
           <rPr>
@@ -2083,7 +2054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{43D76953-9312-8E4B-AA55-EBB5C24E09AA}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{344444E9-2C04-D14A-BB15-FFFF98F9AC89}">
       <text>
         <r>
           <rPr>
@@ -2099,7 +2070,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{A49B2986-229F-EC40-95AD-F040EE5D9201}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{ABB8A8B4-686F-2E45-9774-DD96F629A07F}">
       <text>
         <r>
           <rPr>
@@ -2123,7 +2094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I54" authorId="0" shapeId="0" xr:uid="{7C5A286C-3D82-0B41-9C86-1FF54881CEF4}">
+    <comment ref="I54" authorId="0" shapeId="0" xr:uid="{C97867E8-95A0-5444-9EF7-99E2C5F6263D}">
       <text>
         <r>
           <rPr>
@@ -2139,7 +2110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I55" authorId="0" shapeId="0" xr:uid="{161EFF59-16A6-F646-9564-34134EE1CAB4}">
+    <comment ref="I55" authorId="0" shapeId="0" xr:uid="{22817B6C-BAE3-5743-8B16-ECA935F0165D}">
       <text>
         <r>
           <rPr>
@@ -2155,7 +2126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{87735BA0-D752-054D-B52D-16A1B360EE6C}">
+    <comment ref="I56" authorId="0" shapeId="0" xr:uid="{B7F5144B-6BF5-A949-A3DC-F77F330E36EB}">
       <text>
         <r>
           <rPr>
@@ -2180,7 +2151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I57" authorId="0" shapeId="0" xr:uid="{A01490E5-1413-EF45-8BB3-D7F6F745671D}">
+    <comment ref="I57" authorId="0" shapeId="0" xr:uid="{2DE0A4D1-4E8F-504B-A8CA-B492C75E0064}">
       <text>
         <r>
           <rPr>
@@ -2205,7 +2176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{1A4BAEA6-C93C-F64C-8EBC-FAD2D15D0296}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{725E2608-BCF7-574A-BBA9-519A26E5A0EA}">
       <text>
         <r>
           <rPr>
@@ -2225,7 +2196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{CD93AECA-6586-C241-AC7D-6328006480E3}">
+    <comment ref="I59" authorId="0" shapeId="0" xr:uid="{AB1EC335-99AD-C743-9204-9773FEB8C6CB}">
       <text>
         <r>
           <rPr>
@@ -2240,7 +2211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I60" authorId="0" shapeId="0" xr:uid="{DD38654A-DE46-DF43-9858-A9EAFA8541F6}">
+    <comment ref="I60" authorId="0" shapeId="0" xr:uid="{B13EA97A-E89D-FC43-8D4F-7EA986E6A6CD}">
       <text>
         <r>
           <rPr>
@@ -2260,7 +2231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I61" authorId="0" shapeId="0" xr:uid="{D3D8BC99-1A40-094B-8B1C-D6D743E13974}">
+    <comment ref="I61" authorId="0" shapeId="0" xr:uid="{A43A2B78-6780-3A4B-B654-7F186E80C967}">
       <text>
         <r>
           <rPr>
@@ -2276,7 +2247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I62" authorId="0" shapeId="0" xr:uid="{944D6A2E-F73C-BE42-ABB5-DDE9449D1AB9}">
+    <comment ref="I62" authorId="0" shapeId="0" xr:uid="{33B4B297-A306-9E4A-A880-2727F61316CF}">
       <text>
         <r>
           <rPr>
@@ -2292,7 +2263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I63" authorId="0" shapeId="0" xr:uid="{26462BC6-F9E7-BC40-9FE1-E1A1BCBECAC7}">
+    <comment ref="I63" authorId="0" shapeId="0" xr:uid="{66B89189-B977-2943-B13C-5B028CBC8899}">
       <text>
         <r>
           <rPr>
@@ -2307,7 +2278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I64" authorId="0" shapeId="0" xr:uid="{D67D3806-C7B0-254B-B6A4-2D5F6FCE6D23}">
+    <comment ref="I64" authorId="0" shapeId="0" xr:uid="{AEA9AFF2-9DE8-FC4C-89B2-C6E74604364F}">
       <text>
         <r>
           <rPr>
@@ -2323,7 +2294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I65" authorId="0" shapeId="0" xr:uid="{9126337A-6691-A64B-919A-A0283A86178F}">
+    <comment ref="I65" authorId="0" shapeId="0" xr:uid="{0DC80350-5562-FD43-9002-F8E4AB8A0A44}">
       <text>
         <r>
           <rPr>
@@ -2352,7 +2323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I66" authorId="0" shapeId="0" xr:uid="{07780261-FBDA-464E-B735-7E2FEE0817B5}">
+    <comment ref="I66" authorId="0" shapeId="0" xr:uid="{B0597EE8-26F7-6E47-AE98-A09F7C351444}">
       <text>
         <r>
           <rPr>
@@ -2367,7 +2338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{039BC6E1-A0BC-4944-A20E-38ED08882DD7}">
+    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{B4791254-BC13-2E42-BB3F-03AB8F63E5FF}">
       <text>
         <r>
           <rPr>
@@ -2387,7 +2358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{01921435-8C22-7149-A61B-0F1307F51CA9}">
+    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{5DA5CA13-1ABC-2140-931A-B69761D40341}">
       <text>
         <r>
           <rPr>
@@ -2407,7 +2378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{D00419A2-8BE6-D948-BC05-BEF88A283BAC}">
+    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{CF0DFD7F-86B5-8E4F-BC68-0EC8A83590CA}">
       <text>
         <r>
           <rPr>
@@ -2427,7 +2398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I70" authorId="0" shapeId="0" xr:uid="{8C525EA1-FA2B-1A4E-BCB8-7E328A25C5D8}">
+    <comment ref="I70" authorId="0" shapeId="0" xr:uid="{B311D1A3-6D7E-9A47-90D8-E663D76E6BDA}">
       <text>
         <r>
           <rPr>
@@ -2450,7 +2421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I71" authorId="0" shapeId="0" xr:uid="{30342D18-073C-8D47-81B1-8E6E13DD94D9}">
+    <comment ref="I71" authorId="0" shapeId="0" xr:uid="{8A02F9AD-BEC0-5E46-B5C5-6CD71547CFDF}">
       <text>
         <r>
           <rPr>
@@ -2462,11 +2433,12 @@
           </rPr>
           <t>마이클: 강승호
 그린버그: 양승리
-피터슨: 박지아</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{CFE4033D-0A0D-3241-993C-87C30EFC93AA}">
+피터슨: 박지아
+안소니: 안소니</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I72" authorId="0" shapeId="0" xr:uid="{D56ED220-D68C-5440-A595-D21D3253F237}">
       <text>
         <r>
           <rPr>
@@ -2495,7 +2467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I73" authorId="0" shapeId="0" xr:uid="{44EFD821-70C7-1340-89E3-A1F0B109531C}">
+    <comment ref="I73" authorId="0" shapeId="0" xr:uid="{46A075EE-6175-A543-ADB1-A795009D2B51}">
       <text>
         <r>
           <rPr>
@@ -2510,7 +2482,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I74" authorId="0" shapeId="0" xr:uid="{9724BD29-B5A8-474B-A926-FB6BDE267669}">
+    <comment ref="I74" authorId="0" shapeId="0" xr:uid="{7B22F5A2-8D05-7849-8453-B3DD86248FF8}">
       <text>
         <r>
           <rPr>
@@ -2530,7 +2502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I75" authorId="0" shapeId="0" xr:uid="{29C5BAF2-3C06-A24D-9041-4010363EF2AC}">
+    <comment ref="I75" authorId="0" shapeId="0" xr:uid="{E9D0B6B6-CC42-314C-9C3D-24748688D872}">
       <text>
         <r>
           <rPr>
@@ -2550,7 +2522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I76" authorId="0" shapeId="0" xr:uid="{4354588A-AFB6-CB48-B13A-E9D51EF78BC8}">
+    <comment ref="I76" authorId="0" shapeId="0" xr:uid="{8117ECDC-0086-CC42-BAAC-FA304F1C13CF}">
       <text>
         <r>
           <rPr>
@@ -2570,7 +2542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I77" authorId="0" shapeId="0" xr:uid="{8812F474-87A8-E448-82F8-367B63670671}">
+    <comment ref="I77" authorId="0" shapeId="0" xr:uid="{4075B2FD-66B5-4248-8D0F-40AF6779E187}">
       <text>
         <r>
           <rPr>
@@ -2590,7 +2562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I78" authorId="0" shapeId="0" xr:uid="{4F339964-9B17-9149-94BC-04693862EF9D}">
+    <comment ref="I78" authorId="0" shapeId="0" xr:uid="{21135CCA-944D-5146-BF79-3ECCA896E8E7}">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I79" authorId="0" shapeId="0" xr:uid="{920E6B95-D187-734C-8FC9-22EB071BF11F}">
+    <comment ref="I79" authorId="0" shapeId="0" xr:uid="{F28F3C3F-A9CB-264D-B6AC-1EE060CB8EB6}">
       <text>
         <r>
           <rPr>
@@ -2621,7 +2593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I80" authorId="0" shapeId="0" xr:uid="{E2373000-4E3F-FF49-97C4-A9A467EC6273}">
+    <comment ref="I80" authorId="0" shapeId="0" xr:uid="{C3C8A327-3088-5845-A547-22E453FFD85A}">
       <text>
         <r>
           <rPr>
@@ -2641,7 +2613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I81" authorId="0" shapeId="0" xr:uid="{E0773EF7-7484-E940-BB33-07971FFA3CA6}">
+    <comment ref="I81" authorId="0" shapeId="0" xr:uid="{0DEFD275-FEA6-E443-8A77-A045FDAD872D}">
       <text>
         <r>
           <rPr>
@@ -2661,7 +2633,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I82" authorId="0" shapeId="0" xr:uid="{62C6FB66-597B-6647-AED9-4064CC7E985D}">
+    <comment ref="I82" authorId="0" shapeId="0" xr:uid="{0FED1E77-225B-E140-9D3F-25919FBBDC37}">
       <text>
         <r>
           <rPr>
@@ -2688,7 +2660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I83" authorId="0" shapeId="0" xr:uid="{EA80ABF8-9776-9B49-99BF-F629B0D8558E}">
+    <comment ref="I83" authorId="0" shapeId="0" xr:uid="{8A1CEB2E-AB25-B04A-89C9-B6F102D09985}">
       <text>
         <r>
           <rPr>
@@ -2706,7 +2678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I84" authorId="0" shapeId="0" xr:uid="{06D7A474-F9E2-BB44-8317-9C7D96F15756}">
+    <comment ref="I84" authorId="0" shapeId="0" xr:uid="{AB523EC3-A4AF-B142-AEF6-646CA3BC1019}">
       <text>
         <r>
           <rPr>
@@ -2735,7 +2707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{E93CFABC-FBAD-2140-823E-C77AEA71D8A1}">
+    <comment ref="I85" authorId="0" shapeId="0" xr:uid="{097D1C5D-424A-1C4B-A7CB-55C7BE8F9C1A}">
       <text>
         <r>
           <rPr>
@@ -2755,7 +2727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{564FE5E7-91A7-F743-A512-57A67B2E2DDE}">
+    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{FFE5EA5E-F629-5644-8FC1-9750F63F050E}">
       <text>
         <r>
           <rPr>
@@ -2770,7 +2742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{166CE5E6-E44C-7844-8B1D-E99B8EF96C8F}">
+    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{35519A2A-F9BA-2F49-9511-4BCE80C319AF}">
       <text>
         <r>
           <rPr>
@@ -2782,11 +2754,12 @@
           </rPr>
           <t>마이클: 강승호
 그린버그: 고영빈
-피터슨: 고수희</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{C5F81559-1732-5342-BBD2-75E4D083B7F6}">
+피터슨: 고수희
+안소니: 안소니</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I88" authorId="0" shapeId="0" xr:uid="{F744A6E6-C497-FA42-AE5D-4446A25994D4}">
       <text>
         <r>
           <rPr>
@@ -2804,7 +2777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{200158D0-CEA4-394B-8EBD-AADEB4F27900}">
+    <comment ref="I89" authorId="0" shapeId="0" xr:uid="{56092B8A-E3B2-F546-B0C0-8129AE4936FA}">
       <text>
         <r>
           <rPr>
@@ -2823,7 +2796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{5112E077-D346-4940-82E4-340DC91C9A3F}">
+    <comment ref="I90" authorId="0" shapeId="0" xr:uid="{54D95139-D757-754E-BA16-9FB757B233E3}">
       <text>
         <r>
           <rPr>
@@ -2843,7 +2816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I91" authorId="0" shapeId="0" xr:uid="{122943B9-1A1D-ED4E-BD41-2CF019C6F691}">
+    <comment ref="I91" authorId="0" shapeId="0" xr:uid="{F947AC30-3786-0A42-B9AF-77D4F70874E6}">
       <text>
         <r>
           <rPr>
@@ -2871,7 +2844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I92" authorId="0" shapeId="0" xr:uid="{122FDA04-1CEC-FF4D-AC99-F398E6D42EA5}">
+    <comment ref="I92" authorId="0" shapeId="0" xr:uid="{047B7E55-B3C3-C643-BC54-E60139F12DF5}">
       <text>
         <r>
           <rPr>
@@ -2886,7 +2859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I93" authorId="0" shapeId="0" xr:uid="{DA3CB83E-2E83-8949-B8D7-55767B019D22}">
+    <comment ref="I93" authorId="0" shapeId="0" xr:uid="{B0DB9B36-E1E4-094A-979E-D64F96A3C605}">
       <text>
         <r>
           <rPr>
@@ -2901,7 +2874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I94" authorId="0" shapeId="0" xr:uid="{DFF5DBC4-E077-F143-9B4E-8DFE2DA606D2}">
+    <comment ref="I94" authorId="0" shapeId="0" xr:uid="{D37BB9C0-3C47-124A-A4F3-2BCAEC1AC3EF}">
       <text>
         <r>
           <rPr>
@@ -2917,7 +2890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I95" authorId="0" shapeId="0" xr:uid="{AE7A2981-690A-DF49-B8DE-1ABA509EE4E3}">
+    <comment ref="I95" authorId="0" shapeId="0" xr:uid="{A6AFDE7A-8453-874E-B49C-E45F187972CA}">
       <text>
         <r>
           <rPr>
@@ -2946,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I96" authorId="0" shapeId="0" xr:uid="{71D9C317-3673-EF4F-AE4E-0AA254962EC1}">
+    <comment ref="I96" authorId="0" shapeId="0" xr:uid="{A44AE9C0-8D7A-4446-930A-839D2D30ABAB}">
       <text>
         <r>
           <rPr>
@@ -2966,7 +2939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I97" authorId="0" shapeId="0" xr:uid="{5B514A54-6A80-3E48-A6ED-8F46B5C78EC3}">
+    <comment ref="I97" authorId="0" shapeId="0" xr:uid="{383D8280-60F1-B349-92B9-39853E201482}">
       <text>
         <r>
           <rPr>
@@ -2985,7 +2958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I98" authorId="0" shapeId="0" xr:uid="{EBD49A71-F84F-2643-A409-3A0420049B2F}">
+    <comment ref="I98" authorId="0" shapeId="0" xr:uid="{1658AC09-2292-7D4C-B499-0C781C7B270A}">
       <text>
         <r>
           <rPr>
@@ -3005,7 +2978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{35D6A9EB-692D-9F41-9129-72A2A1701AD6}">
+    <comment ref="I99" authorId="0" shapeId="0" xr:uid="{1C1BC6C9-B13F-9C46-ACB8-C346E0676B52}">
       <text>
         <r>
           <rPr>
@@ -3025,7 +2998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{6DDD74D2-65C9-AF49-87D1-BE7DAB1B43BB}">
+    <comment ref="I100" authorId="0" shapeId="0" xr:uid="{27DCC503-E6C7-7B4D-8F86-7352140A02B3}">
       <text>
         <r>
           <rPr>
@@ -3040,7 +3013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{16441AEF-89CA-FE4B-80F8-DF79C04D7529}">
+    <comment ref="I101" authorId="0" shapeId="0" xr:uid="{00CC79BD-6626-AE44-9272-F100358461C9}">
       <text>
         <r>
           <rPr>
@@ -3069,7 +3042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I102" authorId="0" shapeId="0" xr:uid="{BACE25D9-344F-B948-844C-61FCB6981AF3}">
+    <comment ref="I102" authorId="0" shapeId="0" xr:uid="{5D5F5087-4120-E24D-95EA-8CA88540858D}">
       <text>
         <r>
           <rPr>
@@ -3087,7 +3060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I103" authorId="0" shapeId="0" xr:uid="{7B0CD44B-E2E3-FB40-8172-677E09817684}">
+    <comment ref="I103" authorId="0" shapeId="0" xr:uid="{1AA655C3-172A-DB43-91FF-58E2F8370191}">
       <text>
         <r>
           <rPr>
@@ -3107,7 +3080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I104" authorId="0" shapeId="0" xr:uid="{B1B720FA-F825-B746-8CCF-11E96A2986BF}">
+    <comment ref="I104" authorId="0" shapeId="0" xr:uid="{189186F6-FBB7-FE4D-9795-2FCB2B539257}">
       <text>
         <r>
           <rPr>
@@ -3125,7 +3098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I105" authorId="0" shapeId="0" xr:uid="{AB2B49FE-DF11-6146-B512-2C440EB42875}">
+    <comment ref="I105" authorId="0" shapeId="0" xr:uid="{4E4AE5DB-7A7C-1645-BB54-BA471E5B2417}">
       <text>
         <r>
           <rPr>
@@ -3143,7 +3116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I106" authorId="0" shapeId="0" xr:uid="{D78B0419-7DC6-9847-AB46-AE5769696648}">
+    <comment ref="I106" authorId="0" shapeId="0" xr:uid="{7FBF3554-CB73-0F48-88B1-29F6CC08B337}">
       <text>
         <r>
           <rPr>
@@ -3163,7 +3136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I107" authorId="0" shapeId="0" xr:uid="{890420D5-FA9F-2F43-B1F9-C59CF3530119}">
+    <comment ref="I107" authorId="0" shapeId="0" xr:uid="{784023CB-34CD-9C4F-8FE9-55AD24AB11C0}">
       <text>
         <r>
           <rPr>
@@ -3178,7 +3151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I108" authorId="0" shapeId="0" xr:uid="{2B236E1F-7A48-F240-9F8B-88B745F694A4}">
+    <comment ref="I108" authorId="0" shapeId="0" xr:uid="{8CA4D3C0-6308-D04A-801E-DEEF1FD37576}">
       <text>
         <r>
           <rPr>
@@ -3201,7 +3174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I109" authorId="0" shapeId="0" xr:uid="{8880574D-A041-1746-9020-F217E9789F66}">
+    <comment ref="I109" authorId="0" shapeId="0" xr:uid="{4B1CB286-9F60-984C-9892-1373FD73A9BF}">
       <text>
         <r>
           <rPr>
@@ -3216,7 +3189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I110" authorId="0" shapeId="0" xr:uid="{DA24B8AB-BA36-6647-B21F-CDBFEAA88371}">
+    <comment ref="I110" authorId="0" shapeId="0" xr:uid="{65F05878-00FE-6F4A-AB14-3C10AFDBD376}">
       <text>
         <r>
           <rPr>
@@ -3231,7 +3204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I111" authorId="0" shapeId="0" xr:uid="{9A0725F9-3D96-B44E-93AE-29449FF0DD0D}">
+    <comment ref="I111" authorId="0" shapeId="0" xr:uid="{C6F03916-5D04-5343-B8C2-97A5938323AF}">
       <text>
         <r>
           <rPr>
@@ -3246,7 +3219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I112" authorId="0" shapeId="0" xr:uid="{99506EC8-21D8-444B-A574-BF299E41C528}">
+    <comment ref="I112" authorId="0" shapeId="0" xr:uid="{8C0C8565-A6F1-BE49-8456-82E0F1F681F9}">
       <text>
         <r>
           <rPr>
@@ -3267,7 +3240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I113" authorId="0" shapeId="0" xr:uid="{8F315B8A-0FED-FA4B-86FA-DACFCF07704A}">
+    <comment ref="I113" authorId="0" shapeId="0" xr:uid="{C8535261-B761-484E-815E-E368A596B54C}">
       <text>
         <r>
           <rPr>
@@ -3284,7 +3257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I114" authorId="0" shapeId="0" xr:uid="{8C3F68B2-F6A7-9A47-80F2-7382D073DF8C}">
+    <comment ref="I114" authorId="0" shapeId="0" xr:uid="{3E49A43E-AC14-AF47-85E3-4D55B3B12838}">
       <text>
         <r>
           <rPr>
@@ -3299,7 +3272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I115" authorId="0" shapeId="0" xr:uid="{D2688350-D62A-AB44-86A1-6C0B3055FDF6}">
+    <comment ref="I115" authorId="0" shapeId="0" xr:uid="{9539DD0C-1F4E-8442-B93F-5FD22BC39CD6}">
       <text>
         <r>
           <rPr>
@@ -3318,7 +3291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I116" authorId="0" shapeId="0" xr:uid="{41C16B57-3B7B-1B4C-B622-A88B1BE2C6CD}">
+    <comment ref="I116" authorId="0" shapeId="0" xr:uid="{7167D220-3851-7F4A-BE4B-A550FB57575E}">
       <text>
         <r>
           <rPr>
@@ -3335,7 +3308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I117" authorId="0" shapeId="0" xr:uid="{F2A33C47-C2D3-B340-B3E0-98750A60E1E1}">
+    <comment ref="I117" authorId="0" shapeId="0" xr:uid="{174CF797-F6C7-0141-A29A-99C16B2524C6}">
       <text>
         <r>
           <rPr>
@@ -3361,7 +3334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I118" authorId="0" shapeId="0" xr:uid="{7A4E0879-9493-8744-94DF-6A6A51931CDD}">
+    <comment ref="I118" authorId="0" shapeId="0" xr:uid="{99951C86-B0AE-BB41-A14E-E6EE24EDE4EE}">
       <text>
         <r>
           <rPr>
@@ -3378,7 +3351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I119" authorId="0" shapeId="0" xr:uid="{88BF1485-D8A7-994B-AE44-4833DDCABC45}">
+    <comment ref="I119" authorId="0" shapeId="0" xr:uid="{384E77E1-5DB5-4E40-AEE0-DDC5ADC31406}">
       <text>
         <r>
           <rPr>
@@ -3406,7 +3379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I120" authorId="0" shapeId="0" xr:uid="{04F445C0-B843-324F-AF08-8F1D70C3758C}">
+    <comment ref="I120" authorId="0" shapeId="0" xr:uid="{093F9542-6FF2-B745-8212-7936255DD667}">
       <text>
         <r>
           <rPr>
@@ -3422,7 +3395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I121" authorId="0" shapeId="0" xr:uid="{C8DFFB88-0C57-DD4B-ABC4-7728AE0AD202}">
+    <comment ref="I121" authorId="0" shapeId="0" xr:uid="{DEE2D1E5-FF1D-6047-A846-1D0EFD5B20B2}">
       <text>
         <r>
           <rPr>
@@ -3439,7 +3412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I122" authorId="0" shapeId="0" xr:uid="{C44A74CF-772B-E041-BFE3-0CEECFB0F3B7}">
+    <comment ref="I122" authorId="0" shapeId="0" xr:uid="{EEBAA932-8C4A-6144-8126-7A730D23D9FB}">
       <text>
         <r>
           <rPr>
@@ -3455,7 +3428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I123" authorId="0" shapeId="0" xr:uid="{ADF05674-6ECF-404D-944B-C71486F896AB}">
+    <comment ref="I123" authorId="0" shapeId="0" xr:uid="{82EC46DB-7B6F-B249-9EA0-91160C968491}">
       <text>
         <r>
           <rPr>
@@ -3472,7 +3445,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I124" authorId="0" shapeId="0" xr:uid="{A9D81B34-12C0-BD4E-A670-53C2245D12BB}">
+    <comment ref="I124" authorId="0" shapeId="0" xr:uid="{990E6FA9-7590-864B-A8EF-07879D6EA678}">
       <text>
         <r>
           <rPr>
@@ -3504,7 +3477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I125" authorId="0" shapeId="0" xr:uid="{7FB9270C-46CF-AD46-965A-E4F0D97C0C6F}">
+    <comment ref="I125" authorId="0" shapeId="0" xr:uid="{D61D8D0E-35D1-AF46-B650-2638332FB527}">
       <text>
         <r>
           <rPr>
@@ -3523,7 +3496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I126" authorId="0" shapeId="0" xr:uid="{D0F85AA8-0416-1C40-95F9-088E9E3FFBE9}">
+    <comment ref="I126" authorId="0" shapeId="0" xr:uid="{B7ADDC76-4A4C-1544-A362-E2CD34039693}">
       <text>
         <r>
           <rPr>
@@ -3541,7 +3514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I127" authorId="0" shapeId="0" xr:uid="{EDEDB30C-55AE-AF46-9EB8-795F9ED00126}">
+    <comment ref="I127" authorId="0" shapeId="0" xr:uid="{A5E7A4ED-BBE7-C044-8C1A-739660CFB58D}">
       <text>
         <r>
           <rPr>
@@ -3556,7 +3529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I128" authorId="0" shapeId="0" xr:uid="{6248E1C1-BE06-2046-89FA-467CE61C5117}">
+    <comment ref="I128" authorId="0" shapeId="0" xr:uid="{3E4465E0-F6C0-0E42-ABD6-9B1833A1AE56}">
       <text>
         <r>
           <rPr>
@@ -3573,7 +3546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I129" authorId="0" shapeId="0" xr:uid="{14FA2F63-40BD-5D4E-8757-72C05E82C6B8}">
+    <comment ref="I129" authorId="0" shapeId="0" xr:uid="{68B99014-1261-8847-ABBE-C6CE8DB5D197}">
       <text>
         <r>
           <rPr>
@@ -3590,7 +3563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I130" authorId="0" shapeId="0" xr:uid="{C9E08B14-CB59-3247-B9F3-7B107408C140}">
+    <comment ref="I130" authorId="0" shapeId="0" xr:uid="{587E2538-1884-524A-B2AA-77938B38BAD8}">
       <text>
         <r>
           <rPr>
@@ -3605,7 +3578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I131" authorId="0" shapeId="0" xr:uid="{CC0F1275-534F-BA4C-810A-BB3711BAF564}">
+    <comment ref="I131" authorId="0" shapeId="0" xr:uid="{401A6E36-D509-FE4A-A76E-C058437C14F9}">
       <text>
         <r>
           <rPr>
@@ -3624,7 +3597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I132" authorId="0" shapeId="0" xr:uid="{91DF5060-C04C-F348-B5CD-043E8053F35C}">
+    <comment ref="I132" authorId="0" shapeId="0" xr:uid="{E2737A62-08AD-754A-9B60-96D026C7E28E}">
       <text>
         <r>
           <rPr>
@@ -3643,7 +3616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I133" authorId="0" shapeId="0" xr:uid="{B83E1DE9-348E-904C-BB00-72CA6CE8CC91}">
+    <comment ref="I133" authorId="0" shapeId="0" xr:uid="{D8C623C2-1156-084C-AC6A-FE689E765E6A}">
       <text>
         <r>
           <rPr>
@@ -3660,7 +3633,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I134" authorId="0" shapeId="0" xr:uid="{B0939CFC-6F65-E545-AF70-132339CE42BA}">
+    <comment ref="I134" authorId="0" shapeId="0" xr:uid="{E9C00511-A878-A143-9C49-5200E6B14605}">
       <text>
         <r>
           <rPr>
@@ -3675,7 +3648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I135" authorId="0" shapeId="0" xr:uid="{25AEF7A7-638D-F047-B743-81E21A087D2B}">
+    <comment ref="I135" authorId="0" shapeId="0" xr:uid="{B2D058E8-1EB2-AF4F-A4FD-39B015EAF565}">
       <text>
         <r>
           <rPr>
@@ -3691,7 +3664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I136" authorId="0" shapeId="0" xr:uid="{ABEF14D4-06B9-0E40-ABA2-5EF0C586E411}">
+    <comment ref="I136" authorId="0" shapeId="0" xr:uid="{932A8E9B-F458-494B-BA25-28AE0DC4CA3B}">
       <text>
         <r>
           <rPr>
@@ -3708,7 +3681,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I137" authorId="0" shapeId="0" xr:uid="{B53809DE-3A38-5140-9C9A-7832D470A749}">
+    <comment ref="I137" authorId="0" shapeId="0" xr:uid="{0047A67E-D3AA-6344-9B05-42290CC2D6FC}">
       <text>
         <r>
           <rPr>
@@ -3736,7 +3709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I138" authorId="0" shapeId="0" xr:uid="{034311FC-AA7E-3946-AC4B-C90C5757FDC1}">
+    <comment ref="I138" authorId="0" shapeId="0" xr:uid="{929EB407-767B-2847-B968-24E1DF4F56CE}">
       <text>
         <r>
           <rPr>
@@ -3753,7 +3726,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I139" authorId="0" shapeId="0" xr:uid="{1CBF530E-2F10-7E48-AE26-A2590302F6AF}">
+    <comment ref="I139" authorId="0" shapeId="0" xr:uid="{07B8B7CD-421E-8E43-B67A-C0F172030AD2}">
       <text>
         <r>
           <rPr>
@@ -3769,7 +3742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I140" authorId="0" shapeId="0" xr:uid="{A310F016-98A4-634B-BEC3-FCC11F946B41}">
+    <comment ref="I140" authorId="0" shapeId="0" xr:uid="{8D4A6EA8-AE78-C54B-A3E3-3539B7124287}">
       <text>
         <r>
           <rPr>
@@ -3785,7 +3758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I141" authorId="0" shapeId="0" xr:uid="{191ED7C9-87D9-3946-8436-4EF6B5AAF606}">
+    <comment ref="I141" authorId="0" shapeId="0" xr:uid="{098239A8-DAC9-9449-8D7B-ED426F320C6C}">
       <text>
         <r>
           <rPr>
@@ -3803,7 +3776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I142" authorId="0" shapeId="0" xr:uid="{788CBBD8-7241-DB48-AC2E-2A926805C572}">
+    <comment ref="I142" authorId="0" shapeId="0" xr:uid="{F26F5C2E-0BC3-9F4F-97DB-6BBCAB993526}">
       <text>
         <r>
           <rPr>
@@ -3821,7 +3794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I143" authorId="0" shapeId="0" xr:uid="{EB9FCDDA-077E-5742-BBAE-108E757BF446}">
+    <comment ref="I143" authorId="0" shapeId="0" xr:uid="{A05532F1-BE99-1D47-B1A0-197DD2939747}">
       <text>
         <r>
           <rPr>
@@ -3837,7 +3810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I144" authorId="0" shapeId="0" xr:uid="{B8F5D2C2-8A5D-854A-A1FF-A63B579B25CA}">
+    <comment ref="I144" authorId="0" shapeId="0" xr:uid="{4E03670A-5402-DA4F-8B05-026793DD8258}">
       <text>
         <r>
           <rPr>
@@ -3854,7 +3827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I145" authorId="0" shapeId="0" xr:uid="{79724995-0C87-D048-AC3A-AFE88864430B}">
+    <comment ref="I145" authorId="0" shapeId="0" xr:uid="{5F14FD86-A81B-8640-8A33-58EC393E2799}">
       <text>
         <r>
           <rPr>
@@ -3870,7 +3843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I146" authorId="0" shapeId="0" xr:uid="{A981FF28-0EA2-F643-BF65-3DB4AC2CEF80}">
+    <comment ref="I146" authorId="0" shapeId="0" xr:uid="{923F0EEA-3AC7-3041-955F-4AD697F1EA2E}">
       <text>
         <r>
           <rPr>
@@ -3887,7 +3860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I147" authorId="0" shapeId="0" xr:uid="{2C834151-9AB7-0344-82CA-5DC271EFC789}">
+    <comment ref="I147" authorId="0" shapeId="0" xr:uid="{DFC43001-198E-9B4E-9777-E500AB1D8CFD}">
       <text>
         <r>
           <rPr>
@@ -3907,7 +3880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I148" authorId="0" shapeId="0" xr:uid="{BAA73ECE-EA32-9C4D-B9B8-D34D541614DE}">
+    <comment ref="I148" authorId="0" shapeId="0" xr:uid="{5DD9F1D0-9785-E74F-91F4-96F5760E2278}">
       <text>
         <r>
           <rPr>
@@ -3942,7 +3915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I149" authorId="0" shapeId="0" xr:uid="{6DCB4D26-3FF3-9147-B19B-53BDB03C03FE}">
+    <comment ref="I149" authorId="0" shapeId="0" xr:uid="{81D96665-1A9F-2C42-A04A-1FE623C67B8F}">
       <text>
         <r>
           <rPr>
@@ -3958,7 +3931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I150" authorId="0" shapeId="0" xr:uid="{36DA116B-F6C6-2A48-87F4-FC625A5111DE}">
+    <comment ref="I150" authorId="0" shapeId="0" xr:uid="{620A2B73-ED39-C741-88B4-52FB003D2BAF}">
       <text>
         <r>
           <rPr>
@@ -3980,7 +3953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I151" authorId="0" shapeId="0" xr:uid="{B7BAC43B-750B-8243-8296-4A286D2B159A}">
+    <comment ref="I151" authorId="0" shapeId="0" xr:uid="{EB4B88AA-75B3-5642-86A2-BA144217FA41}">
       <text>
         <r>
           <rPr>
@@ -4004,7 +3977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I152" authorId="0" shapeId="0" xr:uid="{E6D38539-35E5-8D48-BF75-D9C81C980904}">
+    <comment ref="I152" authorId="0" shapeId="0" xr:uid="{28B67E08-C8E4-0E4E-A56F-7E45FEB49E6A}">
       <text>
         <r>
           <rPr>
@@ -4022,7 +3995,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I153" authorId="0" shapeId="0" xr:uid="{0231BC5A-BF67-2744-A124-B0E08EEA99BB}">
+    <comment ref="I153" authorId="0" shapeId="0" xr:uid="{6158DC3D-6CC5-2840-BE0D-57F6D363387B}">
       <text>
         <r>
           <rPr>
@@ -4038,7 +4011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I154" authorId="0" shapeId="0" xr:uid="{B8AD17CA-D92F-B34D-B2C7-C21703B01921}">
+    <comment ref="I154" authorId="0" shapeId="0" xr:uid="{45F67E7E-BD5B-614B-A965-188F68619847}">
       <text>
         <r>
           <rPr>
@@ -4062,7 +4035,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I155" authorId="0" shapeId="0" xr:uid="{D5C1827E-7935-1440-8DC8-7291810AA447}">
+    <comment ref="I155" authorId="0" shapeId="0" xr:uid="{C0471EFD-6D27-184D-AFE4-297E77D758EE}">
       <text>
         <r>
           <rPr>
@@ -4081,7 +4054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I156" authorId="0" shapeId="0" xr:uid="{5BA36180-8DDA-9743-8459-F808DA6FC7E6}">
+    <comment ref="I156" authorId="0" shapeId="0" xr:uid="{41D6F970-0334-2B46-A561-40B22E6033D0}">
       <text>
         <r>
           <rPr>
@@ -4101,7 +4074,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I157" authorId="0" shapeId="0" xr:uid="{8C01E368-07BF-C548-81F9-8A10568F4F9D}">
+    <comment ref="I157" authorId="0" shapeId="0" xr:uid="{2EDABC0A-598A-AB47-A418-C0609F72ABC1}">
       <text>
         <r>
           <rPr>
@@ -4121,7 +4094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I158" authorId="0" shapeId="0" xr:uid="{F56F6525-87F5-464A-947F-E3EADCE792B7}">
+    <comment ref="I158" authorId="0" shapeId="0" xr:uid="{F6DB31E9-1A5C-5F45-B7A9-E7F165053218}">
       <text>
         <r>
           <rPr>
@@ -4141,7 +4114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I159" authorId="0" shapeId="0" xr:uid="{60F748A4-28DB-BC4E-B9E9-A28D792E439A}">
+    <comment ref="I159" authorId="0" shapeId="0" xr:uid="{5E0DD253-57FA-4444-BEF9-8048B7E8F8CF}">
       <text>
         <r>
           <rPr>
@@ -4157,7 +4130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I160" authorId="0" shapeId="0" xr:uid="{F7BC204E-145F-1F44-989E-718FEE9ED871}">
+    <comment ref="I160" authorId="0" shapeId="0" xr:uid="{5E80B726-BA36-2A40-ADE1-E49ACC440A7D}">
       <text>
         <r>
           <rPr>
@@ -4181,7 +4154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I161" authorId="0" shapeId="0" xr:uid="{534E5985-221E-C749-B873-DDD574BEDC96}">
+    <comment ref="I161" authorId="0" shapeId="0" xr:uid="{EEBF5A44-26C8-4745-956F-8E26E7179F27}">
       <text>
         <r>
           <rPr>
@@ -4205,7 +4178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I162" authorId="0" shapeId="0" xr:uid="{6960C695-3011-BF43-89DE-2586ED228399}">
+    <comment ref="I162" authorId="0" shapeId="0" xr:uid="{3F0DE024-ACD9-8840-AE15-254E074073B4}">
       <text>
         <r>
           <rPr>
@@ -4229,7 +4202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I163" authorId="0" shapeId="0" xr:uid="{E063ACA4-1EC2-0A4C-BB82-3A0253F4C45A}">
+    <comment ref="I163" authorId="0" shapeId="0" xr:uid="{10E5D833-AC75-064A-B789-870D25EDD4B1}">
       <text>
         <r>
           <rPr>
@@ -4247,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I164" authorId="0" shapeId="0" xr:uid="{517F47E7-7C21-8848-8360-375AC2999E46}">
+    <comment ref="I164" authorId="0" shapeId="0" xr:uid="{B0CBBA3B-FD95-274C-B135-E58934CE0C08}">
       <text>
         <r>
           <rPr>
@@ -4269,7 +4242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I165" authorId="0" shapeId="0" xr:uid="{6594536E-D697-0C4D-B138-230873098102}">
+    <comment ref="I165" authorId="0" shapeId="0" xr:uid="{911BDFF8-366B-9543-9393-7A98CE2D4376}">
       <text>
         <r>
           <rPr>
@@ -4287,7 +4260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I166" authorId="0" shapeId="0" xr:uid="{4A527715-4F86-8140-9D08-4EE23774D1FE}">
+    <comment ref="I166" authorId="0" shapeId="0" xr:uid="{3E29C5F3-18B6-044B-BD00-759EE1386804}">
       <text>
         <r>
           <rPr>
@@ -4303,7 +4276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I167" authorId="0" shapeId="0" xr:uid="{258FA360-8073-454D-850B-F8F6DC30B26B}">
+    <comment ref="I167" authorId="0" shapeId="0" xr:uid="{3E7080FF-1C1A-5444-86B8-E3EA93CE6681}">
       <text>
         <r>
           <rPr>
@@ -4330,7 +4303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I168" authorId="0" shapeId="0" xr:uid="{F3D3AA81-6D87-CD49-9892-441342AE8BCC}">
+    <comment ref="I168" authorId="0" shapeId="0" xr:uid="{F5778DEF-994E-C940-8302-F0E964EE2EA6}">
       <text>
         <r>
           <rPr>
@@ -4351,7 +4324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I169" authorId="0" shapeId="0" xr:uid="{EF5BCBD2-40A2-5042-BBB1-16FDED9811ED}">
+    <comment ref="I169" authorId="0" shapeId="0" xr:uid="{C5C58D5D-2E6E-0342-B3BC-5672D969FF53}">
       <text>
         <r>
           <rPr>
@@ -4375,7 +4348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I170" authorId="0" shapeId="0" xr:uid="{6FBE1B88-EF7D-A74D-A731-84D93CAB42E4}">
+    <comment ref="I170" authorId="0" shapeId="0" xr:uid="{CF91B13B-47A2-CC48-BC62-357EA7C3EB02}">
       <text>
         <r>
           <rPr>
@@ -4395,7 +4368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I171" authorId="0" shapeId="0" xr:uid="{85FCAFDA-848F-7B4C-8F6E-610D10B36B72}">
+    <comment ref="I171" authorId="0" shapeId="0" xr:uid="{8EE37F87-D8FC-7E4E-91AD-644AF5B4D29B}">
       <text>
         <r>
           <rPr>
@@ -4410,7 +4383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I172" authorId="0" shapeId="0" xr:uid="{44605528-B46F-024F-8081-F2F26D042E6A}">
+    <comment ref="I172" authorId="0" shapeId="0" xr:uid="{68841A0A-5365-AF4E-AA42-E2F0939ECF0D}">
       <text>
         <r>
           <rPr>
@@ -4425,7 +4398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I173" authorId="0" shapeId="0" xr:uid="{5CC02FDD-CD2F-2C48-B2F1-72618F981B1D}">
+    <comment ref="I173" authorId="0" shapeId="0" xr:uid="{0325751D-E718-7E4F-8894-F2CF4D031521}">
       <text>
         <r>
           <rPr>
@@ -4441,7 +4414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I174" authorId="0" shapeId="0" xr:uid="{85639E0E-DBBD-FE40-ADE5-62581A6F384C}">
+    <comment ref="I174" authorId="0" shapeId="0" xr:uid="{8AADAC41-662C-BE44-8F26-6BC002932E42}">
       <text>
         <r>
           <rPr>
@@ -4460,7 +4433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I175" authorId="0" shapeId="0" xr:uid="{E20B1C67-B11C-7A45-9F21-C4805EEB7092}">
+    <comment ref="I175" authorId="0" shapeId="0" xr:uid="{06075F1E-E9E2-BA44-8319-0CC4D249D3D7}">
       <text>
         <r>
           <rPr>
@@ -4484,7 +4457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I176" authorId="0" shapeId="0" xr:uid="{4CC3F33B-57F8-9E46-B0C6-2906C55617BB}">
+    <comment ref="I176" authorId="0" shapeId="0" xr:uid="{BE901D96-80F7-A24E-9B25-06B3F40E6C98}">
       <text>
         <r>
           <rPr>
@@ -4502,7 +4475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I177" authorId="0" shapeId="0" xr:uid="{D548183E-F4A1-8A41-95BF-FA1C1664B427}">
+    <comment ref="I177" authorId="0" shapeId="0" xr:uid="{0BE561EE-6392-6749-ABB4-C3F85A72B1D6}">
       <text>
         <r>
           <rPr>
@@ -4520,7 +4493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I178" authorId="0" shapeId="0" xr:uid="{FBE2FE42-840B-7842-A686-4B9DDC71DA29}">
+    <comment ref="I178" authorId="0" shapeId="0" xr:uid="{959BC77A-2826-1644-9057-3416026A9D09}">
       <text>
         <r>
           <rPr>
@@ -4537,7 +4510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I179" authorId="0" shapeId="0" xr:uid="{E341A0B0-68E8-7545-8088-0D17265E74E9}">
+    <comment ref="I179" authorId="0" shapeId="0" xr:uid="{CC2F2E8D-2587-5448-8F2C-8148A8B1756E}">
       <text>
         <r>
           <rPr>
@@ -4556,7 +4529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I180" authorId="0" shapeId="0" xr:uid="{19933615-2C42-4E4C-8195-E5C5E5F87649}">
+    <comment ref="I180" authorId="0" shapeId="0" xr:uid="{70C722CE-F062-244F-AC7D-5E3E20C26EED}">
       <text>
         <r>
           <rPr>
@@ -4580,7 +4553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I181" authorId="0" shapeId="0" xr:uid="{C842AF1F-A155-AE45-9A8A-AED1728E15A6}">
+    <comment ref="I181" authorId="0" shapeId="0" xr:uid="{1E3B51DC-3441-0C45-AB5C-48A5F8BCCDE2}">
       <text>
         <r>
           <rPr>
@@ -4615,7 +4588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I182" authorId="0" shapeId="0" xr:uid="{38929870-C132-C045-97DB-DAACD2B67E8F}">
+    <comment ref="I182" authorId="0" shapeId="0" xr:uid="{249C59C6-79EA-C944-8C24-5416A02E2BBD}">
       <text>
         <r>
           <rPr>
@@ -4630,7 +4603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I183" authorId="0" shapeId="0" xr:uid="{A8D12412-7F02-3F41-AFFA-FEA4633A2BC0}">
+    <comment ref="I183" authorId="0" shapeId="0" xr:uid="{4D017E42-6D0F-854C-B28A-8529B4122E38}">
       <text>
         <r>
           <rPr>
@@ -4645,7 +4618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I184" authorId="0" shapeId="0" xr:uid="{6B90F7D3-2E6F-3A4C-8F71-6D0CADDA8E17}">
+    <comment ref="I184" authorId="0" shapeId="0" xr:uid="{3C729A30-0A64-9143-987C-BA2AA7339C7F}">
       <text>
         <r>
           <rPr>
@@ -4660,7 +4633,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I185" authorId="0" shapeId="0" xr:uid="{B435F3D8-F8DC-6245-92D1-219AF8F60861}">
+    <comment ref="I185" authorId="0" shapeId="0" xr:uid="{21B8666E-0AE2-1F49-804A-3E6BC502912F}">
       <text>
         <r>
           <rPr>
@@ -4675,7 +4648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I186" authorId="0" shapeId="0" xr:uid="{863ED2C9-7F3E-064A-821E-24F65156540C}">
+    <comment ref="I186" authorId="0" shapeId="0" xr:uid="{5BEA4FFC-50C6-FC49-86D1-367123951656}">
       <text>
         <r>
           <rPr>
@@ -4695,7 +4668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I187" authorId="0" shapeId="0" xr:uid="{77CE9ADC-27FF-1B49-91B5-0D675F153267}">
+    <comment ref="I187" authorId="0" shapeId="0" xr:uid="{D8A9109C-63AE-7843-A819-E489E484C778}">
       <text>
         <r>
           <rPr>
@@ -4715,7 +4688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I188" authorId="0" shapeId="0" xr:uid="{A722F798-3DB5-E942-9807-DE50CE0298C0}">
+    <comment ref="I188" authorId="0" shapeId="0" xr:uid="{75BC98DC-D971-744D-B767-76086B469B7A}">
       <text>
         <r>
           <rPr>
@@ -4748,7 +4721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I189" authorId="0" shapeId="0" xr:uid="{5D40908C-BC6C-4046-8F81-779BF1FDD3DF}">
+    <comment ref="I189" authorId="0" shapeId="0" xr:uid="{EA1C40C8-A51A-5342-979F-E37C490408D8}">
       <text>
         <r>
           <rPr>
@@ -4764,7 +4737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I190" authorId="0" shapeId="0" xr:uid="{857F76EE-0D48-E945-9EE5-828FFC4A56AE}">
+    <comment ref="I190" authorId="0" shapeId="0" xr:uid="{8069496F-1B83-A24D-8ED6-E22FAD741E01}">
       <text>
         <r>
           <rPr>
@@ -4779,7 +4752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I191" authorId="0" shapeId="0" xr:uid="{62BBD6C4-B450-AD41-A81F-7440F994DB6A}">
+    <comment ref="I191" authorId="0" shapeId="0" xr:uid="{014282B0-906B-B047-AA7C-D0FAFA350A58}">
       <text>
         <r>
           <rPr>
@@ -4794,7 +4767,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I192" authorId="0" shapeId="0" xr:uid="{79900091-25D9-ED4F-9E79-B61BE967281F}">
+    <comment ref="I192" authorId="0" shapeId="0" xr:uid="{E67B2F4E-5BE1-6346-9D06-44A36AF68267}">
       <text>
         <r>
           <rPr>
@@ -4809,7 +4782,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I193" authorId="0" shapeId="0" xr:uid="{A6255798-48FC-5148-A086-D307434D6C9E}">
+    <comment ref="I193" authorId="0" shapeId="0" xr:uid="{0EAED50E-1935-A947-AAA7-5050D626816C}">
       <text>
         <r>
           <rPr>
@@ -4825,7 +4798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I194" authorId="0" shapeId="0" xr:uid="{F1B66C5C-34E0-0546-ADE8-EC9FE8FEF077}">
+    <comment ref="I194" authorId="0" shapeId="0" xr:uid="{F58AF4B6-AC3E-6D48-B3EE-3002FAD8ADBC}">
       <text>
         <r>
           <rPr>
@@ -4840,7 +4813,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I195" authorId="0" shapeId="0" xr:uid="{92F8AF71-4319-4D44-AF96-35C205958D37}">
+    <comment ref="I195" authorId="0" shapeId="0" xr:uid="{91A1A853-DBF5-5441-BF5F-BFE3917ED0C0}">
       <text>
         <r>
           <rPr>
@@ -4856,7 +4829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I196" authorId="0" shapeId="0" xr:uid="{95844CAF-C71B-B74E-A789-22B3457C9012}">
+    <comment ref="I196" authorId="0" shapeId="0" xr:uid="{A0298B70-8609-E144-8606-5AD1FA54E992}">
       <text>
         <r>
           <rPr>
@@ -4877,7 +4850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I197" authorId="0" shapeId="0" xr:uid="{59C73CB7-58C9-2F4E-A094-954843BF73F7}">
+    <comment ref="I197" authorId="0" shapeId="0" xr:uid="{B160A9EE-092B-4740-84A1-291B18675B9E}">
       <text>
         <r>
           <rPr>
@@ -4895,7 +4868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I198" authorId="0" shapeId="0" xr:uid="{AB8B2C39-6A1F-644F-8626-E8733F67E8D6}">
+    <comment ref="I198" authorId="0" shapeId="0" xr:uid="{132CB594-0B1A-7344-AF22-C48D844B0327}">
       <text>
         <r>
           <rPr>
@@ -4913,7 +4886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I199" authorId="0" shapeId="0" xr:uid="{9C1BB033-C1A6-564B-88C0-21CF3675C9E7}">
+    <comment ref="I199" authorId="0" shapeId="0" xr:uid="{3A7030B8-9E0F-F44B-AE51-0F6F3BE4DBBB}">
       <text>
         <r>
           <rPr>
@@ -4934,7 +4907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I200" authorId="0" shapeId="0" xr:uid="{05575B7B-C9DF-4441-A0CC-6CDE0121D6AF}">
+    <comment ref="I200" authorId="0" shapeId="0" xr:uid="{877AC9E6-7512-804D-86C5-B07608BE7B25}">
       <text>
         <r>
           <rPr>
@@ -4949,7 +4922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I201" authorId="0" shapeId="0" xr:uid="{5A53B5AE-8D4B-E347-AEE8-27825D4F95E4}">
+    <comment ref="I201" authorId="0" shapeId="0" xr:uid="{1A48B216-B53A-854B-B765-F449272BF3CF}">
       <text>
         <r>
           <rPr>
@@ -4977,7 +4950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I202" authorId="0" shapeId="0" xr:uid="{AC6C0EC8-7BDB-DD45-B937-6BE44445D0C5}">
+    <comment ref="I202" authorId="0" shapeId="0" xr:uid="{527BD9E8-6E43-414B-B801-336BE8C3806E}">
       <text>
         <r>
           <rPr>
@@ -4994,7 +4967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I203" authorId="0" shapeId="0" xr:uid="{1B99C76D-8E89-1440-870D-2A686D18EE39}">
+    <comment ref="I203" authorId="0" shapeId="0" xr:uid="{B868F0CF-175D-E14E-98FC-FA769EAF81DE}">
       <text>
         <r>
           <rPr>
@@ -5014,7 +4987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I204" authorId="0" shapeId="0" xr:uid="{ABD9CD8B-088B-6347-BDC2-EA74C866526E}">
+    <comment ref="I204" authorId="0" shapeId="0" xr:uid="{F146F031-F847-5A48-8038-CF57283CC10C}">
       <text>
         <r>
           <rPr>
@@ -5030,7 +5003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I205" authorId="0" shapeId="0" xr:uid="{E2C90B49-F7CF-F54E-B523-5EAB214A1AA6}">
+    <comment ref="I205" authorId="0" shapeId="0" xr:uid="{AE2F862F-C2EB-7A43-98F2-58376B74CA76}">
       <text>
         <r>
           <rPr>
@@ -5046,7 +5019,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I206" authorId="0" shapeId="0" xr:uid="{1F9D63F3-11F7-C748-95F8-F94A5DE8F77C}">
+    <comment ref="I206" authorId="0" shapeId="0" xr:uid="{2E36E897-4CA8-3349-8C4F-CA22343E4066}">
       <text>
         <r>
           <rPr>
@@ -5071,7 +5044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I207" authorId="0" shapeId="0" xr:uid="{4702335D-6B46-2648-9F0D-85835D180D12}">
+    <comment ref="I207" authorId="0" shapeId="0" xr:uid="{E66B4D3D-041D-6040-B6D4-3F7882CDF72C}">
       <text>
         <r>
           <rPr>
@@ -5090,7 +5063,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I208" authorId="0" shapeId="0" xr:uid="{D77C350F-FAC9-4B48-B5DF-40461DFF012E}">
+    <comment ref="I208" authorId="0" shapeId="0" xr:uid="{D6D6ECC9-5B97-D240-B9DE-D04ABDD6B867}">
       <text>
         <r>
           <rPr>
@@ -5109,7 +5082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I209" authorId="0" shapeId="0" xr:uid="{E181A851-067A-8A49-85B8-1B6ACC021E95}">
+    <comment ref="I209" authorId="0" shapeId="0" xr:uid="{2F9F0190-1775-F042-A22E-CA94D2E0E900}">
       <text>
         <r>
           <rPr>
@@ -5126,7 +5099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I210" authorId="0" shapeId="0" xr:uid="{B922EAAD-9A01-5249-B885-910EE5B22B4A}">
+    <comment ref="I210" authorId="0" shapeId="0" xr:uid="{2E15DD2D-27E7-7D45-97EF-5E23AE831A51}">
       <text>
         <r>
           <rPr>
@@ -5146,7 +5119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I211" authorId="0" shapeId="0" xr:uid="{5A178D29-DF9F-0C46-B4D8-D0F510BEBCD6}">
+    <comment ref="I211" authorId="0" shapeId="0" xr:uid="{51A32568-1B32-6648-ACD9-9400385B4B5E}">
       <text>
         <r>
           <rPr>
@@ -5168,7 +5141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I212" authorId="0" shapeId="0" xr:uid="{499D6B92-5AAB-B549-B8F8-6341C820B0BF}">
+    <comment ref="I212" authorId="0" shapeId="0" xr:uid="{6B2D303C-0984-E948-AE5C-82B72C366455}">
       <text>
         <r>
           <rPr>
@@ -5184,7 +5157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I213" authorId="0" shapeId="0" xr:uid="{8D269498-4C2D-764D-AB24-EA8C372DBD91}">
+    <comment ref="I213" authorId="0" shapeId="0" xr:uid="{1AE2AF5D-C05D-A449-B209-D91FCC354307}">
       <text>
         <r>
           <rPr>
@@ -5200,7 +5173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I214" authorId="0" shapeId="0" xr:uid="{D5B65371-578D-0340-9874-23DB06FFBD15}">
+    <comment ref="I214" authorId="0" shapeId="0" xr:uid="{7DB7075B-55A2-D047-A7B3-04B772F848AF}">
       <text>
         <r>
           <rPr>
@@ -5222,7 +5195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I215" authorId="0" shapeId="0" xr:uid="{DCEFEA34-B503-C141-BC2B-30777EC7D943}">
+    <comment ref="I215" authorId="0" shapeId="0" xr:uid="{532FB2E1-A7BC-1E42-A4E0-79E935090276}">
       <text>
         <r>
           <rPr>
@@ -5242,7 +5215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I216" authorId="0" shapeId="0" xr:uid="{BF9EC3C5-2120-B549-944E-E8F2904123BE}">
+    <comment ref="I216" authorId="0" shapeId="0" xr:uid="{A51A8196-8E68-9F41-AA15-0C8EF505EC52}">
       <text>
         <r>
           <rPr>
@@ -5258,7 +5231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I217" authorId="0" shapeId="0" xr:uid="{B1E79E58-BAC0-4543-8C4D-5A87FB0946ED}">
+    <comment ref="I217" authorId="0" shapeId="0" xr:uid="{B64188B4-0370-404C-ABF3-459DDFB093CC}">
       <text>
         <r>
           <rPr>
@@ -5275,7 +5248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I218" authorId="0" shapeId="0" xr:uid="{3D126290-0DCF-8543-8A00-FEF0717BF526}">
+    <comment ref="I218" authorId="0" shapeId="0" xr:uid="{D4B1D317-50AB-6944-9919-301765B36107}">
       <text>
         <r>
           <rPr>
@@ -5295,7 +5268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I219" authorId="0" shapeId="0" xr:uid="{1276DB85-34C9-CF43-8030-B1D7A42D458E}">
+    <comment ref="I219" authorId="0" shapeId="0" xr:uid="{96BF9212-9EFD-684D-B174-D2594E867532}">
       <text>
         <r>
           <rPr>
@@ -5310,7 +5283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I220" authorId="0" shapeId="0" xr:uid="{DA2E4A88-2CA4-2149-A45C-09A4156D31C0}">
+    <comment ref="I220" authorId="0" shapeId="0" xr:uid="{FEC2D49E-A9E4-524E-8B86-702137BA9238}">
       <text>
         <r>
           <rPr>
@@ -5332,7 +5305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I221" authorId="0" shapeId="0" xr:uid="{CDADD7A0-9B42-EF42-89D7-F4A82B781071}">
+    <comment ref="I221" authorId="0" shapeId="0" xr:uid="{E404A53A-F486-1742-855B-AEBDA284F7D5}">
       <text>
         <r>
           <rPr>
@@ -5354,7 +5327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I222" authorId="0" shapeId="0" xr:uid="{6AE17AF7-79E2-7A4A-AB2F-BED9028531C0}">
+    <comment ref="I222" authorId="0" shapeId="0" xr:uid="{7F5046D7-85A7-1349-ADB0-745FDB2BB6D0}">
       <text>
         <r>
           <rPr>
@@ -5387,7 +5360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I223" authorId="0" shapeId="0" xr:uid="{7BB493D1-1C28-B243-B4FC-143CED981E30}">
+    <comment ref="I223" authorId="0" shapeId="0" xr:uid="{DF4E7BA8-E742-2D48-96B6-BD1A33956D4A}">
       <text>
         <r>
           <rPr>
@@ -5417,7 +5390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I224" authorId="0" shapeId="0" xr:uid="{F603BB0B-8777-0D4F-AAB9-D20CB5D807AE}">
+    <comment ref="I224" authorId="0" shapeId="0" xr:uid="{0185699F-14F9-2749-A4E2-89B38CAC184E}">
       <text>
         <r>
           <rPr>
@@ -5432,7 +5405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I225" authorId="0" shapeId="0" xr:uid="{C2D75DBB-155C-0347-B910-8A06BEB4DDFA}">
+    <comment ref="I225" authorId="0" shapeId="0" xr:uid="{45108B27-0104-E746-AC7A-DA327EFFA799}">
       <text>
         <r>
           <rPr>
@@ -5451,7 +5424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I226" authorId="0" shapeId="0" xr:uid="{3E781C2F-A3D7-0342-AC54-0590A3035916}">
+    <comment ref="I226" authorId="0" shapeId="0" xr:uid="{2BB9D81C-1F4B-1242-99AB-C6596BB1E5F2}">
       <text>
         <r>
           <rPr>
@@ -5469,7 +5442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I227" authorId="0" shapeId="0" xr:uid="{91BB57EC-35D1-AC40-A3CC-D28997AF1331}">
+    <comment ref="I227" authorId="0" shapeId="0" xr:uid="{E48D7C71-2909-DC40-8F8A-1E4F8928D24A}">
       <text>
         <r>
           <rPr>
@@ -5495,7 +5468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I228" authorId="0" shapeId="0" xr:uid="{875A7EC0-7F2C-AF42-ACAE-CE8DB71F1E9D}">
+    <comment ref="I228" authorId="0" shapeId="0" xr:uid="{EE8A9FA2-D13C-F94D-9D47-C98C81EE2365}">
       <text>
         <r>
           <rPr>
@@ -5510,7 +5483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I229" authorId="0" shapeId="0" xr:uid="{4E2B6038-334C-5F4A-9E72-32C5F4A34AC2}">
+    <comment ref="I229" authorId="0" shapeId="0" xr:uid="{57924368-C8CC-F049-8FEF-9C714FE71062}">
       <text>
         <r>
           <rPr>
@@ -5529,7 +5502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I230" authorId="0" shapeId="0" xr:uid="{5707B953-345B-904A-A9CE-55E853DB46E7}">
+    <comment ref="I230" authorId="0" shapeId="0" xr:uid="{64935531-1923-E948-BFCE-4F348A873B10}">
       <text>
         <r>
           <rPr>
@@ -5545,7 +5518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I231" authorId="0" shapeId="0" xr:uid="{5489B042-FCED-6A43-A357-3651CDB27940}">
+    <comment ref="I231" authorId="0" shapeId="0" xr:uid="{D207E0BB-AB36-D546-9270-3F401D7A4769}">
       <text>
         <r>
           <rPr>
@@ -5573,7 +5546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I232" authorId="0" shapeId="0" xr:uid="{BB615D1F-67EB-0B4B-9B4D-BF60A9C77C97}">
+    <comment ref="I232" authorId="0" shapeId="0" xr:uid="{F24E2FEA-41D5-3F49-B733-1F205E42A20C}">
       <text>
         <r>
           <rPr>
@@ -5593,7 +5566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I233" authorId="0" shapeId="0" xr:uid="{15E01AAB-8D60-E44D-81EA-FD552DD934B5}">
+    <comment ref="I233" authorId="0" shapeId="0" xr:uid="{52A97494-3208-124D-B41F-979CA7B114B8}">
       <text>
         <r>
           <rPr>
@@ -5618,7 +5591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I234" authorId="0" shapeId="0" xr:uid="{0AD3A748-DAB6-754C-A26E-8BEDA6F12D6E}">
+    <comment ref="I234" authorId="0" shapeId="0" xr:uid="{B299C3F0-62AC-5246-8A7D-04518551BFD2}">
       <text>
         <r>
           <rPr>
@@ -5634,7 +5607,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I235" authorId="0" shapeId="0" xr:uid="{1A4B7505-7A7D-2B48-A7E9-1FFB7FD04323}">
+    <comment ref="I235" authorId="0" shapeId="0" xr:uid="{338341B1-A65C-5343-91EE-9ACE07A564C2}">
       <text>
         <r>
           <rPr>
@@ -5650,7 +5623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I236" authorId="0" shapeId="0" xr:uid="{603284CF-0E46-8E44-BA5B-FF864DA732F4}">
+    <comment ref="I236" authorId="0" shapeId="0" xr:uid="{DCE720B6-085E-1B46-8E9C-B29D39E5B1B6}">
       <text>
         <r>
           <rPr>
@@ -5666,7 +5639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I237" authorId="0" shapeId="0" xr:uid="{C75D8A67-BC3A-A146-88FE-139E85EF6433}">
+    <comment ref="I237" authorId="0" shapeId="0" xr:uid="{055AEB3A-D3A6-B445-A9AA-80156E8EA531}">
       <text>
         <r>
           <rPr>
@@ -5685,7 +5658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I238" authorId="0" shapeId="0" xr:uid="{11857B4F-463D-7E49-9249-8C23ABD9216C}">
+    <comment ref="I238" authorId="0" shapeId="0" xr:uid="{EA06FD64-1497-2C47-A168-8C4F747FE6A2}">
       <text>
         <r>
           <rPr>
@@ -5700,7 +5673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I239" authorId="0" shapeId="0" xr:uid="{B83170C7-6BD3-FB43-ACE0-4B3BDD4D282A}">
+    <comment ref="I239" authorId="0" shapeId="0" xr:uid="{139DFD3B-4041-2547-B3A9-D91E503D9DAD}">
       <text>
         <r>
           <rPr>
@@ -5722,7 +5695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I240" authorId="0" shapeId="0" xr:uid="{DDE824A3-693A-014A-88B4-1F8E9F418063}">
+    <comment ref="I240" authorId="0" shapeId="0" xr:uid="{0AF76D7C-2CDC-3649-A380-7E27607724CD}">
       <text>
         <r>
           <rPr>
@@ -5738,7 +5711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I241" authorId="0" shapeId="0" xr:uid="{E71D9C9D-5598-7E44-9B9A-C4C8091B720F}">
+    <comment ref="I241" authorId="0" shapeId="0" xr:uid="{B85B95E5-572F-6D45-9249-74907374D2EE}">
       <text>
         <r>
           <rPr>
@@ -5756,7 +5729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I242" authorId="0" shapeId="0" xr:uid="{E6B467C3-E1DF-9543-B012-315C190D640F}">
+    <comment ref="I242" authorId="0" shapeId="0" xr:uid="{536A4E64-4718-6D4F-AFFB-843637582A88}">
       <text>
         <r>
           <rPr>
@@ -5772,7 +5745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I243" authorId="0" shapeId="0" xr:uid="{B987477B-1928-F44C-AE06-C76940CCF418}">
+    <comment ref="I243" authorId="0" shapeId="0" xr:uid="{56E06DB1-565A-7E48-B561-E6584EC64C26}">
       <text>
         <r>
           <rPr>
@@ -5788,7 +5761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I244" authorId="0" shapeId="0" xr:uid="{9199F696-7DE9-4340-BA5F-0DC5FA076866}">
+    <comment ref="I244" authorId="0" shapeId="0" xr:uid="{CC15C872-481A-A246-9441-DBB04BF48AD6}">
       <text>
         <r>
           <rPr>
@@ -5804,7 +5777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I245" authorId="0" shapeId="0" xr:uid="{3054F03F-C0AD-AC4F-990C-D17A7ADCD911}">
+    <comment ref="I245" authorId="0" shapeId="0" xr:uid="{A87B0F4D-B0A6-1F4A-BE6A-7AE0C9DEB249}">
       <text>
         <r>
           <rPr>
@@ -5820,7 +5793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I246" authorId="0" shapeId="0" xr:uid="{007DF422-3FFC-7F4B-80D5-F4E2C91D3165}">
+    <comment ref="I246" authorId="0" shapeId="0" xr:uid="{992216BA-8A38-AA43-8BD8-7A018789ECC4}">
       <text>
         <r>
           <rPr>
@@ -5835,7 +5808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I247" authorId="0" shapeId="0" xr:uid="{822164AA-6599-9545-B4B1-CCABE57771ED}">
+    <comment ref="I247" authorId="0" shapeId="0" xr:uid="{61820918-BE5D-9C4C-8B51-4253BA24304F}">
       <text>
         <r>
           <rPr>
@@ -5851,7 +5824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I248" authorId="0" shapeId="0" xr:uid="{30CF8857-A146-464D-A68B-9040FADE2142}">
+    <comment ref="I248" authorId="0" shapeId="0" xr:uid="{42BB81A4-1A3C-8D47-9781-3806B27C3805}">
       <text>
         <r>
           <rPr>
@@ -5866,7 +5839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I249" authorId="0" shapeId="0" xr:uid="{ED3ECEDE-92E6-7E49-B57C-9EE7CDD16A52}">
+    <comment ref="I249" authorId="0" shapeId="0" xr:uid="{54E59F4E-46B9-8B4D-8541-EE998E576990}">
       <text>
         <r>
           <rPr>
@@ -5885,7 +5858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I250" authorId="0" shapeId="0" xr:uid="{7713CDCB-5416-9145-A9C9-662B95936045}">
+    <comment ref="I250" authorId="0" shapeId="0" xr:uid="{76085807-433B-5943-84FF-9B8BE38C7407}">
       <text>
         <r>
           <rPr>
@@ -5901,7 +5874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I251" authorId="0" shapeId="0" xr:uid="{C1C35909-EAA4-EF45-8EB5-CE6D0EF5998C}">
+    <comment ref="I251" authorId="0" shapeId="0" xr:uid="{292D2B96-6A6B-F04F-9908-D0D91550AB83}">
       <text>
         <r>
           <rPr>
@@ -5920,7 +5893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I252" authorId="0" shapeId="0" xr:uid="{126D6761-2F34-1549-A842-9AAF14288C74}">
+    <comment ref="I252" authorId="0" shapeId="0" xr:uid="{C413FDD1-187D-0E4C-911D-D3112F865324}">
       <text>
         <r>
           <rPr>
@@ -5948,7 +5921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I253" authorId="0" shapeId="0" xr:uid="{D32E4AA5-91FF-304A-A1B6-A24543032D00}">
+    <comment ref="I253" authorId="0" shapeId="0" xr:uid="{41AE9292-4167-AC43-873A-604DB6430D90}">
       <text>
         <r>
           <rPr>
@@ -5964,7 +5937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I254" authorId="0" shapeId="0" xr:uid="{59817223-1821-D943-AE3E-8F2B62A44DD1}">
+    <comment ref="I254" authorId="0" shapeId="0" xr:uid="{C2D70BF2-FE89-AF48-9757-8C918DEDF948}">
       <text>
         <r>
           <rPr>
@@ -5991,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I255" authorId="0" shapeId="0" xr:uid="{EE82321A-EE04-2F42-ABB3-1C9000961906}">
+    <comment ref="I255" authorId="0" shapeId="0" xr:uid="{766994BC-FF61-3A4C-AFC0-689AF588D489}">
       <text>
         <r>
           <rPr>
@@ -6007,7 +5980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I256" authorId="0" shapeId="0" xr:uid="{BCC2B9AF-B6F0-0B43-9CAE-987654FAC515}">
+    <comment ref="I256" authorId="0" shapeId="0" xr:uid="{8DFDBD7D-964F-B24F-AA9D-81D05C8D2CCE}">
       <text>
         <r>
           <rPr>
@@ -6022,7 +5995,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I257" authorId="0" shapeId="0" xr:uid="{FCB7BD37-3C24-D245-95C7-016434A957FC}">
+    <comment ref="I257" authorId="0" shapeId="0" xr:uid="{F75124A7-3F04-C94E-B096-40291DEF3D50}">
       <text>
         <r>
           <rPr>
@@ -6038,7 +6011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I258" authorId="0" shapeId="0" xr:uid="{D89C5216-DB94-2B46-B0D8-3289B75561BF}">
+    <comment ref="I258" authorId="0" shapeId="0" xr:uid="{5021C1C2-9D3F-D349-8AFD-D52C7F447176}">
       <text>
         <r>
           <rPr>
@@ -6057,7 +6030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I259" authorId="0" shapeId="0" xr:uid="{D8676727-0E1A-9040-8503-362961BD36BD}">
+    <comment ref="I259" authorId="0" shapeId="0" xr:uid="{80D50D37-C01F-F543-91EB-5579E27D2A9B}">
       <text>
         <r>
           <rPr>
@@ -6072,7 +6045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I260" authorId="0" shapeId="0" xr:uid="{49A0D2CA-4F6A-954E-89C1-91985863659B}">
+    <comment ref="I260" authorId="0" shapeId="0" xr:uid="{0FA27827-1A4C-1B4B-9937-D7386FA9F082}">
       <text>
         <r>
           <rPr>
@@ -6088,7 +6061,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I261" authorId="0" shapeId="0" xr:uid="{E7694C46-6187-0440-AF15-B4E5AA7DB60A}">
+    <comment ref="I261" authorId="0" shapeId="0" xr:uid="{26775054-807E-6445-B060-C8E1BA199DE2}">
       <text>
         <r>
           <rPr>
@@ -6106,7 +6079,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I262" authorId="0" shapeId="0" xr:uid="{E1CEBF6E-2ACE-4243-A7BC-58DD21D12393}">
+    <comment ref="I262" authorId="0" shapeId="0" xr:uid="{D1845D61-BC98-984D-806F-52693E9A548A}">
       <text>
         <r>
           <rPr>
@@ -6122,7 +6095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I263" authorId="0" shapeId="0" xr:uid="{CA3FFF3F-94AB-8A40-A471-0757BFA32C17}">
+    <comment ref="I263" authorId="0" shapeId="0" xr:uid="{B8CFB3FB-9064-A640-8386-71DB3CFB27B5}">
       <text>
         <r>
           <rPr>
@@ -6141,7 +6114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I264" authorId="0" shapeId="0" xr:uid="{34936AB9-DCE0-844D-9D43-6E6161062632}">
+    <comment ref="I264" authorId="0" shapeId="0" xr:uid="{A026A8FC-1140-8F45-B1B8-9EA6CACB1803}">
       <text>
         <r>
           <rPr>
@@ -6157,7 +6130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I265" authorId="0" shapeId="0" xr:uid="{0B6170B7-FC81-A94E-9957-1476962534BB}">
+    <comment ref="I265" authorId="0" shapeId="0" xr:uid="{9BD40E55-A45F-194D-B5DA-54093960A8B8}">
       <text>
         <r>
           <rPr>
@@ -6175,7 +6148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I266" authorId="0" shapeId="0" xr:uid="{CDF88906-7F8C-4A49-8F8A-89F86DA617AF}">
+    <comment ref="I266" authorId="0" shapeId="0" xr:uid="{E5CD4770-7E1F-1F4D-BCB8-CA108EE27091}">
       <text>
         <r>
           <rPr>
@@ -6193,7 +6166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I267" authorId="0" shapeId="0" xr:uid="{BC6A6B55-3520-344C-8A46-6F53F217F073}">
+    <comment ref="I267" authorId="0" shapeId="0" xr:uid="{17EE59C0-793C-F642-9652-B32839CEC28B}">
       <text>
         <r>
           <rPr>
@@ -6211,7 +6184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I268" authorId="0" shapeId="0" xr:uid="{75EEB886-C097-304F-94C4-387671F7BFCF}">
+    <comment ref="I268" authorId="0" shapeId="0" xr:uid="{97377130-48F7-6642-A68D-5CA7F7C3CB00}">
       <text>
         <r>
           <rPr>
@@ -6226,7 +6199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I269" authorId="0" shapeId="0" xr:uid="{C8A3F29D-FB42-AE41-8C50-C2CC0DDF9AC0}">
+    <comment ref="I269" authorId="0" shapeId="0" xr:uid="{717AA2FC-3DDA-254B-972B-4B046565A6A4}">
       <text>
         <r>
           <rPr>
@@ -6245,7 +6218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I270" authorId="0" shapeId="0" xr:uid="{FFDAA77A-02A0-C041-B65B-7D22D4F37B6D}">
+    <comment ref="I270" authorId="0" shapeId="0" xr:uid="{629D3FD1-A27B-8B44-AFEA-666BEEDC266C}">
       <text>
         <r>
           <rPr>
@@ -6261,7 +6234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I271" authorId="0" shapeId="0" xr:uid="{E96B6831-0F09-AD4C-91E5-C2709024D177}">
+    <comment ref="I271" authorId="0" shapeId="0" xr:uid="{EFDDBBF7-9557-0F40-AA1D-873421B529A6}">
       <text>
         <r>
           <rPr>
@@ -6279,7 +6252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I272" authorId="0" shapeId="0" xr:uid="{D15AAC17-25A8-EE47-8E9C-910C6366CCB3}">
+    <comment ref="I272" authorId="0" shapeId="0" xr:uid="{879DBB77-EC5A-4A47-BCFA-07F061CF7898}">
       <text>
         <r>
           <rPr>
@@ -6295,7 +6268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I273" authorId="0" shapeId="0" xr:uid="{707872CA-14B8-9047-9610-17F8A740BB7C}">
+    <comment ref="I273" authorId="0" shapeId="0" xr:uid="{C840FAAB-2619-B34B-9F2A-B50398714095}">
       <text>
         <r>
           <rPr>
@@ -6314,7 +6287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I274" authorId="0" shapeId="0" xr:uid="{CAE70F3A-6AD5-0E43-AB89-1B5CFA40744A}">
+    <comment ref="I274" authorId="0" shapeId="0" xr:uid="{FF09DD3D-47A9-324A-BE3C-702E66F2DDE5}">
       <text>
         <r>
           <rPr>
@@ -6330,7 +6303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I275" authorId="0" shapeId="0" xr:uid="{B569FD6A-C118-F544-BB8A-5C6242A4AC50}">
+    <comment ref="I275" authorId="0" shapeId="0" xr:uid="{25BB7670-E69E-6F42-B22C-B82D97900FEA}">
       <text>
         <r>
           <rPr>
@@ -6346,7 +6319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I276" authorId="0" shapeId="0" xr:uid="{8507B332-DA9A-B240-AA53-E3B0FC4413EB}">
+    <comment ref="I276" authorId="0" shapeId="0" xr:uid="{17E90BFD-8850-DD48-A717-136EE49B4FAF}">
       <text>
         <r>
           <rPr>
@@ -6364,7 +6337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I277" authorId="0" shapeId="0" xr:uid="{D750ADB1-8C16-3D40-B5A6-EC14B044F718}">
+    <comment ref="I277" authorId="0" shapeId="0" xr:uid="{80743AD3-7C0B-9D4C-93EC-92ED36F6F971}">
       <text>
         <r>
           <rPr>
@@ -6380,7 +6353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I278" authorId="0" shapeId="0" xr:uid="{3B7BD0F5-85BC-5847-BA85-8F8A1E8A1701}">
+    <comment ref="I278" authorId="0" shapeId="0" xr:uid="{7AB7BCDD-99D6-B04B-9B9E-C46187A95803}">
       <text>
         <r>
           <rPr>
@@ -6396,7 +6369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I279" authorId="0" shapeId="0" xr:uid="{C4683E4D-EA94-F949-BF46-9BCBA08967B6}">
+    <comment ref="I279" authorId="0" shapeId="0" xr:uid="{901FB44D-8ADA-C24F-A07D-CD249939202B}">
       <text>
         <r>
           <rPr>
@@ -6412,7 +6385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I280" authorId="0" shapeId="0" xr:uid="{4A8D99F1-1D51-5342-91B9-2050AB6F9123}">
+    <comment ref="I280" authorId="0" shapeId="0" xr:uid="{A7F6F47B-57C7-2D4F-BEE1-22D1D6FBE3BE}">
       <text>
         <r>
           <rPr>
@@ -6432,7 +6405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I281" authorId="0" shapeId="0" xr:uid="{D9B229F4-1E91-784C-9F62-2475FABC5BFB}">
+    <comment ref="I281" authorId="0" shapeId="0" xr:uid="{2D6C60E1-867D-8045-8A3D-114C07755CF0}">
       <text>
         <r>
           <rPr>
@@ -6450,7 +6423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I282" authorId="0" shapeId="0" xr:uid="{BDADAC3E-074C-EC46-8E30-102FE0BC9647}">
+    <comment ref="I282" authorId="0" shapeId="0" xr:uid="{A7DEEF78-B5C3-9F49-969D-65E8DEB9EE75}">
       <text>
         <r>
           <rPr>
@@ -6478,7 +6451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I283" authorId="0" shapeId="0" xr:uid="{294DCC3A-A99C-884D-B42C-859829A2777C}">
+    <comment ref="I283" authorId="0" shapeId="0" xr:uid="{23586F8F-28F8-5B4A-8BC2-A887C3C734FA}">
       <text>
         <r>
           <rPr>
@@ -6507,7 +6480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I284" authorId="0" shapeId="0" xr:uid="{B8E3533E-089A-6347-B923-18FF3F0909A1}">
+    <comment ref="I284" authorId="0" shapeId="0" xr:uid="{F7465765-5701-C243-99AA-F1E680AB8D29}">
       <text>
         <r>
           <rPr>
@@ -6524,7 +6497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I285" authorId="0" shapeId="0" xr:uid="{9E912087-25D8-F44D-89F2-3C2FEA356A61}">
+    <comment ref="I285" authorId="0" shapeId="0" xr:uid="{B3B85D1E-BD86-A948-A008-9677F473F6AF}">
       <text>
         <r>
           <rPr>
@@ -6553,7 +6526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I286" authorId="0" shapeId="0" xr:uid="{4D457188-CEB8-D24A-A11E-14A86AE74994}">
+    <comment ref="I286" authorId="0" shapeId="0" xr:uid="{5BE4BFA7-4FD0-0D42-9DF3-E00A27F1E30B}">
       <text>
         <r>
           <rPr>
@@ -6582,7 +6555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I287" authorId="0" shapeId="0" xr:uid="{9402037A-572F-E74A-B579-C404BC590F34}">
+    <comment ref="I287" authorId="0" shapeId="0" xr:uid="{0422919E-2D1D-CA48-BE3B-8BFAA93EA659}">
       <text>
         <r>
           <rPr>
@@ -6597,7 +6570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I288" authorId="0" shapeId="0" xr:uid="{238CCC8F-97A2-7F4A-94D0-0E4E2BE4B363}">
+    <comment ref="I288" authorId="0" shapeId="0" xr:uid="{BF42C738-ABB4-5A43-B71A-1E4D0DECAFA5}">
       <text>
         <r>
           <rPr>
@@ -6615,7 +6588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I289" authorId="0" shapeId="0" xr:uid="{31EDD7BF-2A67-044B-A656-1102CB6D25E5}">
+    <comment ref="I289" authorId="0" shapeId="0" xr:uid="{EFD25815-01EC-EF49-9CE7-D0BAC175D384}">
       <text>
         <r>
           <rPr>
@@ -6635,7 +6608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I290" authorId="0" shapeId="0" xr:uid="{4C567587-3CAD-6242-B5C1-190C2AE06422}">
+    <comment ref="I290" authorId="0" shapeId="0" xr:uid="{F7B8C5B1-66CB-A246-A848-3D7BF3FBD14F}">
       <text>
         <r>
           <rPr>
@@ -6654,7 +6627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I291" authorId="0" shapeId="0" xr:uid="{E6B0B248-B7EC-784D-ACFF-4C6DBBDCD5B0}">
+    <comment ref="I291" authorId="0" shapeId="0" xr:uid="{BBCA3482-AC7B-4E49-BF46-5B7A6F876230}">
       <text>
         <r>
           <rPr>
@@ -6673,7 +6646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I292" authorId="0" shapeId="0" xr:uid="{762CCB2B-CA6C-C34C-82E5-D3AA041DA5BE}">
+    <comment ref="I292" authorId="0" shapeId="0" xr:uid="{11866E7F-0D6E-3645-8879-4EB494195066}">
       <text>
         <r>
           <rPr>
@@ -6693,7 +6666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I293" authorId="0" shapeId="0" xr:uid="{52B78231-59AE-1E46-BD4F-68A49C062E88}">
+    <comment ref="I293" authorId="0" shapeId="0" xr:uid="{36239CD3-91D1-CE4A-8A37-C81373A1AC2F}">
       <text>
         <r>
           <rPr>
@@ -6722,7 +6695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I294" authorId="0" shapeId="0" xr:uid="{F254CE40-C2AD-C640-94D8-0BE14BB82384}">
+    <comment ref="I294" authorId="0" shapeId="0" xr:uid="{06506B74-3F39-184E-8E6C-491F96F27C42}">
       <text>
         <r>
           <rPr>
@@ -6743,7 +6716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I295" authorId="0" shapeId="0" xr:uid="{4F0B15B8-C7E3-F048-B659-BECDDB14E3E1}">
+    <comment ref="I295" authorId="0" shapeId="0" xr:uid="{C21F5F4C-4CF6-3445-B730-7B9CF1B869D2}">
       <text>
         <r>
           <rPr>
@@ -6758,7 +6731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I296" authorId="0" shapeId="0" xr:uid="{A780D1D1-C7F6-F74E-926E-AD16D62B62BE}">
+    <comment ref="I296" authorId="0" shapeId="0" xr:uid="{B5535D10-6A30-9645-85D6-36329BAC7F38}">
       <text>
         <r>
           <rPr>
@@ -6778,7 +6751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I297" authorId="0" shapeId="0" xr:uid="{D697DC4B-626F-CB42-A30E-041534EC809D}">
+    <comment ref="I297" authorId="0" shapeId="0" xr:uid="{2BF93938-048A-BC48-AD27-E240E50CB64E}">
       <text>
         <r>
           <rPr>
@@ -6797,7 +6770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I298" authorId="0" shapeId="0" xr:uid="{10D181C3-4A74-D24C-A0E7-24A9A34306F8}">
+    <comment ref="I298" authorId="0" shapeId="0" xr:uid="{57FA49F2-C6A7-1C4E-A877-84B8454B782D}">
       <text>
         <r>
           <rPr>
@@ -6817,7 +6790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I299" authorId="0" shapeId="0" xr:uid="{FAED49EB-8719-2148-A4D9-EBF20B313E37}">
+    <comment ref="I299" authorId="0" shapeId="0" xr:uid="{55043794-5556-1C40-A043-956C951B21E6}">
       <text>
         <r>
           <rPr>
@@ -6841,7 +6814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I300" authorId="0" shapeId="0" xr:uid="{B705384C-D315-0F47-9752-67EFA1A3AF80}">
+    <comment ref="I300" authorId="0" shapeId="0" xr:uid="{281B8020-08BF-704F-BB47-1E7783B374E5}">
       <text>
         <r>
           <rPr>
@@ -6856,7 +6829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I301" authorId="0" shapeId="0" xr:uid="{D97BC0BE-7580-104B-A9D4-A9826F1DED78}">
+    <comment ref="I301" authorId="0" shapeId="0" xr:uid="{D97F9DE5-C72E-6E43-A637-AC55F1CE15A9}">
       <text>
         <r>
           <rPr>
@@ -6872,7 +6845,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I302" authorId="0" shapeId="0" xr:uid="{0C46EDFA-74A0-154B-B480-105827AA2403}">
+    <comment ref="I302" authorId="0" shapeId="0" xr:uid="{B1A78507-DDB7-4F4C-9DF9-0E66A12E99A7}">
       <text>
         <r>
           <rPr>
@@ -6888,7 +6861,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I303" authorId="0" shapeId="0" xr:uid="{F071D1CC-CC1B-954C-A757-01801760B922}">
+    <comment ref="I303" authorId="0" shapeId="0" xr:uid="{3D3A6B93-3B0F-E54A-92F1-76ACA489E11B}">
       <text>
         <r>
           <rPr>
@@ -6906,7 +6879,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I304" authorId="0" shapeId="0" xr:uid="{069718CC-FD0F-A541-9885-A39CED86812D}">
+    <comment ref="I304" authorId="0" shapeId="0" xr:uid="{C2A2D0C5-D920-1B4F-851A-23F92DE0B035}">
       <text>
         <r>
           <rPr>
@@ -6923,7 +6896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I305" authorId="0" shapeId="0" xr:uid="{FADF5F13-6D5D-DC43-92DE-1D94F40A71F9}">
+    <comment ref="I305" authorId="0" shapeId="0" xr:uid="{772A0424-C80B-DB4D-B013-2F18B0A2F7A5}">
       <text>
         <r>
           <rPr>
@@ -6939,7 +6912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I306" authorId="0" shapeId="0" xr:uid="{EA164EF4-69CA-014F-9D29-9F470C2FAC62}">
+    <comment ref="I306" authorId="0" shapeId="0" xr:uid="{DA62D858-7A87-CE4B-AF0A-708FDC04436E}">
       <text>
         <r>
           <rPr>
@@ -6955,7 +6928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I307" authorId="0" shapeId="0" xr:uid="{F1CC2CC7-D833-144E-80CE-11D3C509F1D2}">
+    <comment ref="I307" authorId="0" shapeId="0" xr:uid="{997E6248-AB58-4645-8C2C-60F18F20E424}">
       <text>
         <r>
           <rPr>
@@ -6977,7 +6950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I308" authorId="0" shapeId="0" xr:uid="{BA88B69D-A5F7-1D43-B843-A8D63C774A89}">
+    <comment ref="I308" authorId="0" shapeId="0" xr:uid="{4FF98175-F43E-4640-993F-47C53C78D2CA}">
       <text>
         <r>
           <rPr>
@@ -6993,7 +6966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I309" authorId="0" shapeId="0" xr:uid="{B1051356-77CE-C040-98E7-3A139BDB21F1}">
+    <comment ref="I309" authorId="0" shapeId="0" xr:uid="{F4D9348D-DE96-F64F-9D66-373965CE1210}">
       <text>
         <r>
           <rPr>
@@ -7009,7 +6982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I310" authorId="0" shapeId="0" xr:uid="{91BC1D89-B2BE-6F4C-B8FF-910AFE19F2A4}">
+    <comment ref="I310" authorId="0" shapeId="0" xr:uid="{AD6B0E44-86F6-8E4C-B467-1D2EF8A6A4BA}">
       <text>
         <r>
           <rPr>
@@ -7029,7 +7002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I311" authorId="0" shapeId="0" xr:uid="{441CAC05-AC5A-214D-9860-94C91B52BAC3}">
+    <comment ref="I311" authorId="0" shapeId="0" xr:uid="{4CBC10A2-9159-1549-9D4A-60B27DBCAFF7}">
       <text>
         <r>
           <rPr>
@@ -7053,7 +7026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I312" authorId="0" shapeId="0" xr:uid="{4A9C8FB5-4DCE-544C-81A5-2E9B4820EA93}">
+    <comment ref="I312" authorId="0" shapeId="0" xr:uid="{BCADDB75-86B9-EE49-B69D-B899357AC045}">
       <text>
         <r>
           <rPr>
@@ -7075,7 +7048,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I313" authorId="0" shapeId="0" xr:uid="{8D3C3500-80BB-E44B-A4E4-21D9C59A7294}">
+    <comment ref="I313" authorId="0" shapeId="0" xr:uid="{5BC9C343-4C73-0649-97B5-40790D269C81}">
       <text>
         <r>
           <rPr>
@@ -7097,7 +7070,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I314" authorId="0" shapeId="0" xr:uid="{A7BE04AD-0E36-C04B-A488-F85498DB7E55}">
+    <comment ref="I314" authorId="0" shapeId="0" xr:uid="{049C4C12-A6E9-8746-B5C5-8134F99C6D29}">
       <text>
         <r>
           <rPr>
@@ -7125,7 +7098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I315" authorId="0" shapeId="0" xr:uid="{B6269AF0-2B3A-0847-AC6E-7C87A6B3C8C6}">
+    <comment ref="I315" authorId="0" shapeId="0" xr:uid="{F34206C4-4F69-0C4E-8640-B9C5A1851FF0}">
       <text>
         <r>
           <rPr>
@@ -7144,7 +7117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I316" authorId="0" shapeId="0" xr:uid="{4CB33A19-ADFE-B949-9651-E80760F86AB8}">
+    <comment ref="I316" authorId="0" shapeId="0" xr:uid="{359E191C-42ED-7C43-875F-F0D67C0E0160}">
       <text>
         <r>
           <rPr>
@@ -7164,7 +7137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I317" authorId="0" shapeId="0" xr:uid="{4E438ED6-45CD-8F46-B5D6-3707901372FE}">
+    <comment ref="I317" authorId="0" shapeId="0" xr:uid="{EA89FB0A-5FB1-CC44-A5B5-3EC4D3F3A8A6}">
       <text>
         <r>
           <rPr>
@@ -7182,7 +7155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I318" authorId="0" shapeId="0" xr:uid="{CE54E930-FB04-C341-9C51-151D6A2F18D3}">
+    <comment ref="I318" authorId="0" shapeId="0" xr:uid="{074C0DE9-57CE-7C4D-A6B2-AEFDF8205F87}">
       <text>
         <r>
           <rPr>
@@ -7197,7 +7170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I319" authorId="0" shapeId="0" xr:uid="{73B85D92-3E8A-3841-AC7A-E2D2C7F02541}">
+    <comment ref="I319" authorId="0" shapeId="0" xr:uid="{6C4F23AA-17D4-2843-9C7C-27F0D2D5E93B}">
       <text>
         <r>
           <rPr>
@@ -7214,14 +7187,14 @@
 하데스: 김우형
 운명의 여신: 
 이지숙 이아름솔 박가람
-앙상블=일꾼: 
+일꾼: 
 김주영 남궁혜인 양병철 정호준 권상석
 스윙: 
 박주희 신은총 박우빈 김성정</t>
         </r>
       </text>
     </comment>
-    <comment ref="I320" authorId="0" shapeId="0" xr:uid="{6A08117A-D460-4E43-8DF0-8A59470FBC44}">
+    <comment ref="I320" authorId="0" shapeId="0" xr:uid="{2C18902A-193E-F941-9BAF-141DDC642B48}">
       <text>
         <r>
           <rPr>
@@ -7240,7 +7213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I321" authorId="0" shapeId="0" xr:uid="{54B0DA6D-4A9E-A84D-8266-A7794C57301C}">
+    <comment ref="I321" authorId="0" shapeId="0" xr:uid="{ED4D41AC-5D92-5344-84AD-D9779F1D33A8}">
       <text>
         <r>
           <rPr>
@@ -7256,7 +7229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I322" authorId="0" shapeId="0" xr:uid="{739FF6F8-AE7A-934D-981A-4C7349854D7D}">
+    <comment ref="I322" authorId="0" shapeId="0" xr:uid="{F93A7F76-55F0-C643-8861-D71CA34E2547}">
       <text>
         <r>
           <rPr>
@@ -7274,7 +7247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I323" authorId="0" shapeId="0" xr:uid="{A6E350EA-BCF8-FD40-BB54-B1E93FE5B88A}">
+    <comment ref="I323" authorId="0" shapeId="0" xr:uid="{9AD74D91-7AE6-3E44-B275-6BC10017F486}">
       <text>
         <r>
           <rPr>
@@ -7289,7 +7262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I324" authorId="0" shapeId="0" xr:uid="{BDAC4BE4-B82F-034F-B4AB-29060C34DF22}">
+    <comment ref="I324" authorId="0" shapeId="0" xr:uid="{B9378048-B72E-904C-ADCF-EEEE35A4D7AF}">
       <text>
         <r>
           <rPr>
@@ -7308,7 +7281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I325" authorId="0" shapeId="0" xr:uid="{EB54B8DF-2CEE-D240-9F27-97207B743166}">
+    <comment ref="I325" authorId="0" shapeId="0" xr:uid="{D0E1ECDF-6FBB-4C45-A261-454332FC54D0}">
       <text>
         <r>
           <rPr>
@@ -7337,7 +7310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I326" authorId="0" shapeId="0" xr:uid="{F09BA5BA-1852-4C4C-9896-253100D27EF9}">
+    <comment ref="I326" authorId="0" shapeId="0" xr:uid="{D3E533CA-CE8B-084D-A194-78AE1FA7F0F4}">
       <text>
         <r>
           <rPr>
@@ -7355,7 +7328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I327" authorId="0" shapeId="0" xr:uid="{213ED458-3BF5-5444-BDDD-5273D5422B7D}">
+    <comment ref="I327" authorId="0" shapeId="0" xr:uid="{3DFC3488-0DB4-8E4F-93C2-598A044EB0A7}">
       <text>
         <r>
           <rPr>
@@ -7384,7 +7357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I328" authorId="0" shapeId="0" xr:uid="{3DEAFA99-95F0-0047-B23F-1D7A6361C21F}">
+    <comment ref="I328" authorId="0" shapeId="0" xr:uid="{8F158CF6-CAA6-4C4C-938B-506228370E2F}">
       <text>
         <r>
           <rPr>
@@ -7396,11 +7369,12 @@
           </rPr>
           <t>마이클: 김현진
 그린버그: 이석준
-피터슨: 이현진</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I329" authorId="0" shapeId="0" xr:uid="{584B6D46-22E4-004E-8B66-091E1CF8C6D7}">
+피터슨: 이현진
+안소니: 안소니</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I329" authorId="0" shapeId="0" xr:uid="{8A329A5F-B830-9248-9B46-3895BC64E9E7}">
       <text>
         <r>
           <rPr>
@@ -7416,7 +7390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I330" authorId="0" shapeId="0" xr:uid="{7EA63503-0D69-EE40-88A4-AE4412BF6255}">
+    <comment ref="I330" authorId="0" shapeId="0" xr:uid="{04DE51CF-4689-254A-86CC-7CC67469327F}">
       <text>
         <r>
           <rPr>
@@ -7445,7 +7419,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I331" authorId="0" shapeId="0" xr:uid="{C45B3B4A-AB5F-194C-9345-6F463683AFC1}">
+    <comment ref="I331" authorId="0" shapeId="0" xr:uid="{74E6BB96-033C-824F-874B-3032DA99F8CD}">
       <text>
         <r>
           <rPr>
@@ -7470,7 +7444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I332" authorId="0" shapeId="0" xr:uid="{ECB7B9A8-A606-AA47-8E1D-190BD6E43593}">
+    <comment ref="I332" authorId="0" shapeId="0" xr:uid="{2AA0C239-702C-BB4E-8D8B-90376753C344}">
       <text>
         <r>
           <rPr>
@@ -7489,7 +7463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I333" authorId="0" shapeId="0" xr:uid="{5CFF66C0-CBE0-4642-9D25-3BA053BCC668}">
+    <comment ref="I333" authorId="0" shapeId="0" xr:uid="{65406216-482C-9946-8778-C2C4623EF6E0}">
       <text>
         <r>
           <rPr>
@@ -7513,7 +7487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I334" authorId="0" shapeId="0" xr:uid="{8E1F3995-23C3-9347-8DC5-552B8FC25FCB}">
+    <comment ref="I334" authorId="0" shapeId="0" xr:uid="{EC98B9EB-D98A-2446-96AE-2069B8894F06}">
       <text>
         <r>
           <rPr>
@@ -7532,7 +7506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I335" authorId="0" shapeId="0" xr:uid="{77392464-6CC4-F442-B416-E1243B789C97}">
+    <comment ref="I335" authorId="0" shapeId="0" xr:uid="{70ACCD9D-E82A-EE4D-922E-C92676777DEB}">
       <text>
         <r>
           <rPr>
@@ -7551,7 +7525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I336" authorId="0" shapeId="0" xr:uid="{E116FD34-2D62-2443-9C1D-5CD173CB761B}">
+    <comment ref="I336" authorId="0" shapeId="0" xr:uid="{8F148C53-8A2E-114D-9E47-31A551958C1B}">
       <text>
         <r>
           <rPr>
@@ -7570,7 +7544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I337" authorId="0" shapeId="0" xr:uid="{84CBB1BD-DEA3-7A44-A697-ACB51ABAC997}">
+    <comment ref="I337" authorId="0" shapeId="0" xr:uid="{5EC43776-A33F-1D41-BB1E-FFC8D7C5D201}">
       <text>
         <r>
           <rPr>
@@ -7598,7 +7572,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I338" authorId="0" shapeId="0" xr:uid="{7DCB2D7D-AC6D-004B-8BEA-6B6F7EBB7E6D}">
+    <comment ref="I338" authorId="0" shapeId="0" xr:uid="{CB5DBDA6-7EDF-CC49-9790-B69B22E51F3E}">
       <text>
         <r>
           <rPr>
@@ -7617,7 +7591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I339" authorId="0" shapeId="0" xr:uid="{EFCFE2E8-0426-D540-B5EA-C39A04B62C7B}">
+    <comment ref="I339" authorId="0" shapeId="0" xr:uid="{8D44F17B-782B-F34A-B3EA-58CCF3E38D11}">
       <text>
         <r>
           <rPr>
@@ -7647,7 +7621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I340" authorId="0" shapeId="0" xr:uid="{6EFCD771-F87E-854E-B0BF-30B836D6E1B3}">
+    <comment ref="I340" authorId="0" shapeId="0" xr:uid="{F1B1CA46-F9C6-0D4D-967D-ADEFD95EBFE8}">
       <text>
         <r>
           <rPr>
@@ -7666,7 +7640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I341" authorId="0" shapeId="0" xr:uid="{2164C086-E1D6-5B48-984C-8C40C58D5692}">
+    <comment ref="I341" authorId="0" shapeId="0" xr:uid="{AF9CF734-8581-C945-899C-FE5B12AE4388}">
       <text>
         <r>
           <rPr>
@@ -7682,7 +7656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I342" authorId="0" shapeId="0" xr:uid="{197FC39B-C9F8-094F-9ECB-73894C8F25BD}">
+    <comment ref="I342" authorId="0" shapeId="0" xr:uid="{505644CB-29A0-274F-836B-BEE104572A4C}">
       <text>
         <r>
           <rPr>
@@ -7701,7 +7675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I343" authorId="0" shapeId="0" xr:uid="{BC91C05A-A910-B04C-9FBD-5AEACE9B9B1A}">
+    <comment ref="I343" authorId="0" shapeId="0" xr:uid="{D8459571-5316-5946-AE72-1AB9911A427B}">
       <text>
         <r>
           <rPr>
@@ -7730,7 +7704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I344" authorId="0" shapeId="0" xr:uid="{C334D55C-5000-4E45-8076-93F63CF63DDA}">
+    <comment ref="I344" authorId="0" shapeId="0" xr:uid="{4A44AEDF-741B-834C-84DF-50AAE4A16162}">
       <text>
         <r>
           <rPr>
@@ -7749,7 +7723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I345" authorId="0" shapeId="0" xr:uid="{08099C3F-D499-A04B-B6D4-D353CD8BC820}">
+    <comment ref="I345" authorId="0" shapeId="0" xr:uid="{640D39EE-47A2-0B47-84F9-5D7C2E662B8C}">
       <text>
         <r>
           <rPr>
@@ -7765,7 +7739,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I346" authorId="0" shapeId="0" xr:uid="{474EF982-D1AB-2C4F-875D-70EEA34CCD15}">
+    <comment ref="I346" authorId="0" shapeId="0" xr:uid="{F225C36C-1DEA-6F4D-AE72-EA8781992871}">
       <text>
         <r>
           <rPr>
@@ -7784,7 +7758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I347" authorId="0" shapeId="0" xr:uid="{20AD4FC5-BE41-1545-9C3D-FBED6F73995D}">
+    <comment ref="I347" authorId="0" shapeId="0" xr:uid="{B39E0339-D6B7-404E-921F-55CABE95BE72}">
       <text>
         <r>
           <rPr>
@@ -7813,7 +7787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I348" authorId="0" shapeId="0" xr:uid="{17AD7F34-6BC3-3C45-87B3-BCB8DCEB22DD}">
+    <comment ref="I348" authorId="0" shapeId="0" xr:uid="{FE21B0FC-EC1D-504C-920F-2242FA329170}">
       <text>
         <r>
           <rPr>
@@ -7829,7 +7803,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I349" authorId="0" shapeId="0" xr:uid="{21159CCD-31B3-274A-8C53-E0F405FCDF24}">
+    <comment ref="I349" authorId="0" shapeId="0" xr:uid="{72CB8A8F-BE98-CB4D-87B2-08FAD50ACA34}">
       <text>
         <r>
           <rPr>
@@ -7844,7 +7818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I350" authorId="0" shapeId="0" xr:uid="{D4285962-A75B-4B4D-9687-11FEE56624BD}">
+    <comment ref="I350" authorId="0" shapeId="0" xr:uid="{C2609B76-C541-4D4A-A8B4-835911C327B2}">
       <text>
         <r>
           <rPr>
@@ -7863,7 +7837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I351" authorId="0" shapeId="0" xr:uid="{9E1A647E-6653-0F47-81F6-63E6C352115B}">
+    <comment ref="I351" authorId="0" shapeId="0" xr:uid="{86606252-4728-5944-8439-7F2137E2C223}">
       <text>
         <r>
           <rPr>
@@ -7882,7 +7856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I352" authorId="0" shapeId="0" xr:uid="{C170AE85-5F1E-B441-BCDA-EF047C703FDB}">
+    <comment ref="I352" authorId="0" shapeId="0" xr:uid="{E7F7195E-06E7-7140-8785-33FEEE7B9918}">
       <text>
         <r>
           <rPr>
@@ -7903,7 +7877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I353" authorId="0" shapeId="0" xr:uid="{38E50066-D7C3-DE49-8673-E942DC0B5375}">
+    <comment ref="I353" authorId="0" shapeId="0" xr:uid="{A4D88ACC-1D95-1E47-B046-F3F5768CAB3C}">
       <text>
         <r>
           <rPr>
@@ -7918,7 +7892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I354" authorId="0" shapeId="0" xr:uid="{44FBB1D0-5C00-DD49-B3D7-FC71AFE20D2A}">
+    <comment ref="I354" authorId="0" shapeId="0" xr:uid="{D83DE277-96A6-3148-A0C3-2A451909BC72}">
       <text>
         <r>
           <rPr>
@@ -7934,7 +7908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I355" authorId="0" shapeId="0" xr:uid="{35CF5966-AD1D-F243-8E0B-1F3EAA5FE982}">
+    <comment ref="I355" authorId="0" shapeId="0" xr:uid="{B99934C0-5471-E448-8279-E705B2D2E718}">
       <text>
         <r>
           <rPr>
@@ -7951,7 +7925,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I356" authorId="0" shapeId="0" xr:uid="{351C2317-709B-974E-ABB2-4646A462C9E2}">
+    <comment ref="I356" authorId="0" shapeId="0" xr:uid="{78721247-5511-8A4E-A3F7-119035A340FA}">
       <text>
         <r>
           <rPr>
@@ -7967,7 +7941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I357" authorId="0" shapeId="0" xr:uid="{711756CB-8C15-014F-A6E6-1AF592577E18}">
+    <comment ref="I357" authorId="0" shapeId="0" xr:uid="{3B0A879A-C366-4A4A-A4D6-AB6FE492463D}">
       <text>
         <r>
           <rPr>
@@ -7986,7 +7960,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I358" authorId="0" shapeId="0" xr:uid="{286EC909-860D-2140-808B-104A30F3C545}">
+    <comment ref="I358" authorId="0" shapeId="0" xr:uid="{C0D65163-D1F9-BD40-A5EB-3130E004F970}">
       <text>
         <r>
           <rPr>
@@ -8003,7 +7977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I359" authorId="0" shapeId="0" xr:uid="{AFF87048-BC64-E240-A258-B8D8422D7C30}">
+    <comment ref="I359" authorId="0" shapeId="0" xr:uid="{30751843-BDB4-4E48-AA58-63C31980037B}">
       <text>
         <r>
           <rPr>
@@ -8022,7 +7996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I360" authorId="0" shapeId="0" xr:uid="{00863649-15A3-6C4F-9139-768123618A2B}">
+    <comment ref="I360" authorId="0" shapeId="0" xr:uid="{0BA43BB2-83A3-704D-81A0-936868551C3B}">
       <text>
         <r>
           <rPr>
@@ -8039,7 +8013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I361" authorId="0" shapeId="0" xr:uid="{D4687ADE-EA77-7344-A21F-AAC0AF3C8E1D}">
+    <comment ref="I361" authorId="0" shapeId="0" xr:uid="{9AAFB6A2-89A6-DE42-ADC2-A84AA4CAC7AA}">
       <text>
         <r>
           <rPr>
@@ -8056,7 +8030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I362" authorId="0" shapeId="0" xr:uid="{22688EFB-FF20-414B-B8FB-D32527EDECC7}">
+    <comment ref="I362" authorId="0" shapeId="0" xr:uid="{E5FA2F05-50A6-B843-9D24-F46615B7D85C}">
       <text>
         <r>
           <rPr>
@@ -8073,7 +8047,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I363" authorId="0" shapeId="0" xr:uid="{E331C90D-AEDB-BA4B-9D6F-AEDADC5608D6}">
+    <comment ref="I363" authorId="0" shapeId="0" xr:uid="{DBFEF93E-AB97-B540-943E-18851114F996}">
       <text>
         <r>
           <rPr>
@@ -8098,7 +8072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I364" authorId="0" shapeId="0" xr:uid="{E4B377F1-CD05-334C-A37A-0D7D2D36F0EE}">
+    <comment ref="I364" authorId="0" shapeId="0" xr:uid="{13FD0CE8-EE04-D148-A175-27993FD9EB03}">
       <text>
         <r>
           <rPr>
@@ -8115,7 +8089,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I365" authorId="0" shapeId="0" xr:uid="{F18CF403-FF77-3B41-B904-C51EE13B6106}">
+    <comment ref="I365" authorId="0" shapeId="0" xr:uid="{D1361EB9-FFDB-A445-9DDF-CAC3FFA987F4}">
       <text>
         <r>
           <rPr>
@@ -8132,7 +8106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I366" authorId="0" shapeId="0" xr:uid="{CE253AD8-4F90-7648-B1DD-A6AD388B1BFD}">
+    <comment ref="I366" authorId="0" shapeId="0" xr:uid="{4AFB6FCF-7853-3445-92D0-33EB16587031}">
       <text>
         <r>
           <rPr>
@@ -8149,7 +8123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I367" authorId="0" shapeId="0" xr:uid="{3B45BF28-EE17-4C43-81C0-FE9925EAEAAA}">
+    <comment ref="I367" authorId="0" shapeId="0" xr:uid="{3A4539A4-507D-2B46-8098-E5CFBD09B05E}">
       <text>
         <r>
           <rPr>
@@ -8166,7 +8140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I368" authorId="0" shapeId="0" xr:uid="{4A3E0464-A9E7-D143-8C99-C45C73C4EE61}">
+    <comment ref="I368" authorId="0" shapeId="0" xr:uid="{F4596871-27DF-6B44-A9AE-6B47682ED218}">
       <text>
         <r>
           <rPr>
@@ -8183,7 +8157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I369" authorId="0" shapeId="0" xr:uid="{F809BA46-2C30-EC49-989C-C21E2982A2D8}">
+    <comment ref="I369" authorId="0" shapeId="0" xr:uid="{A3273B74-2446-9D41-8609-EFD07199BE7C}">
       <text>
         <r>
           <rPr>
@@ -8201,7 +8175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I370" authorId="0" shapeId="0" xr:uid="{693A4184-A1D9-C643-8CDB-C8044246DD75}">
+    <comment ref="I370" authorId="0" shapeId="0" xr:uid="{06E18ADA-FEAC-B946-8C33-D12F630B927A}">
       <text>
         <r>
           <rPr>
@@ -8218,7 +8192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I371" authorId="0" shapeId="0" xr:uid="{0B0D3E26-DF98-9148-9AEA-C2F597B2B1FB}">
+    <comment ref="I371" authorId="0" shapeId="0" xr:uid="{0C3E300D-F509-B643-BCA7-372709CFF285}">
       <text>
         <r>
           <rPr>
@@ -8236,7 +8210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I372" authorId="0" shapeId="0" xr:uid="{823467D8-FE6D-4940-9D58-D35D86285E4F}">
+    <comment ref="I372" authorId="0" shapeId="0" xr:uid="{7D2684D5-0C15-E84F-AA7F-B2E16B0B8975}">
       <text>
         <r>
           <rPr>
@@ -8260,7 +8234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I373" authorId="0" shapeId="0" xr:uid="{6D5D2DE4-AC2F-7749-B9BE-D520CE2C5162}">
+    <comment ref="I373" authorId="0" shapeId="0" xr:uid="{93FFEF49-BEF8-A741-ADBB-D09EC193B88C}">
       <text>
         <r>
           <rPr>
@@ -8279,7 +8253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I374" authorId="0" shapeId="0" xr:uid="{34F70CEE-83EA-BC49-B175-D38D8F46ACC5}">
+    <comment ref="I374" authorId="0" shapeId="0" xr:uid="{5991BEAD-85C7-E240-A3F5-CAA6BC1DBFD0}">
       <text>
         <r>
           <rPr>
@@ -8297,7 +8271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I375" authorId="0" shapeId="0" xr:uid="{AD70CB1C-7F54-6146-86FB-B64FAA1A8016}">
+    <comment ref="I375" authorId="0" shapeId="0" xr:uid="{D9542C02-5420-7C43-A880-C843E2E04EF8}">
       <text>
         <r>
           <rPr>
@@ -8314,7 +8288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I376" authorId="0" shapeId="0" xr:uid="{39EB5C82-C3CE-084A-B500-0FBC0E0F5E17}">
+    <comment ref="I376" authorId="0" shapeId="0" xr:uid="{7B8B3AF8-5E62-9649-AE9B-E1E355569174}">
       <text>
         <r>
           <rPr>
@@ -8331,7 +8305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I377" authorId="0" shapeId="0" xr:uid="{1EA8BD7B-06AD-A747-833E-48E1F44123B2}">
+    <comment ref="I377" authorId="0" shapeId="0" xr:uid="{5324691B-B4E4-574A-8887-655F09DE5B64}">
       <text>
         <r>
           <rPr>
@@ -8348,7 +8322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I378" authorId="0" shapeId="0" xr:uid="{8E1DF46E-E227-704A-B138-5AF9BA40A72C}">
+    <comment ref="I378" authorId="0" shapeId="0" xr:uid="{E4C359FB-6786-5A41-A46D-972A0B62B2F8}">
       <text>
         <r>
           <rPr>
@@ -8368,7 +8342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I379" authorId="0" shapeId="0" xr:uid="{00D556C1-5C2D-6441-ACB2-D5AFD26C5A46}">
+    <comment ref="I379" authorId="0" shapeId="0" xr:uid="{48958966-6C3C-ED48-BDC2-E32C0D45F024}">
       <text>
         <r>
           <rPr>
@@ -8385,7 +8359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I380" authorId="0" shapeId="0" xr:uid="{92A93FE3-71DC-F34B-B9AF-A5D94F674D1A}">
+    <comment ref="I380" authorId="0" shapeId="0" xr:uid="{BEA334EF-84C7-6B43-BAFE-A50F7340B717}">
       <text>
         <r>
           <rPr>
@@ -8402,7 +8376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I381" authorId="0" shapeId="0" xr:uid="{8F7FE5A2-D66E-2348-B56B-8F1503CA1707}">
+    <comment ref="I381" authorId="0" shapeId="0" xr:uid="{8B7DF301-2750-2F4C-9723-4D4CD7DC4AFB}">
       <text>
         <r>
           <rPr>
@@ -8419,7 +8393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I382" authorId="0" shapeId="0" xr:uid="{88945F33-1D56-8C43-B414-95B3AB18CD34}">
+    <comment ref="I382" authorId="0" shapeId="0" xr:uid="{29A62076-BC45-5C42-BDAF-D87FAD9A938E}">
       <text>
         <r>
           <rPr>
@@ -8436,7 +8410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I383" authorId="0" shapeId="0" xr:uid="{A44890B6-5C05-0F40-A11B-4CACF83A637F}">
+    <comment ref="I383" authorId="0" shapeId="0" xr:uid="{7AC88146-EB6C-9E4B-AF68-5E3005AF621E}">
       <text>
         <r>
           <rPr>
@@ -8453,7 +8427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I384" authorId="0" shapeId="0" xr:uid="{3B8DB17D-864B-CB41-8A77-3E07F86EAD3F}">
+    <comment ref="I384" authorId="0" shapeId="0" xr:uid="{B544566B-5FEB-4F43-B2E0-552F75B5DC41}">
       <text>
         <r>
           <rPr>
@@ -8470,7 +8444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I385" authorId="0" shapeId="0" xr:uid="{48103161-84B6-824E-BF4C-B56A600FEA0D}">
+    <comment ref="I385" authorId="0" shapeId="0" xr:uid="{99F4CF30-C6D7-0644-A88D-7A4C4E1DB2CB}">
       <text>
         <r>
           <rPr>
@@ -8503,7 +8477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I386" authorId="0" shapeId="0" xr:uid="{D410E63B-42C8-3841-98C5-6FC191B330EA}">
+    <comment ref="I386" authorId="0" shapeId="0" xr:uid="{AA1ED94C-667F-094B-8E18-EA6D614B0380}">
       <text>
         <r>
           <rPr>
@@ -8518,7 +8492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I387" authorId="0" shapeId="0" xr:uid="{A6DE13DA-BD9A-7244-9DAF-4DEFC3597D75}">
+    <comment ref="I387" authorId="0" shapeId="0" xr:uid="{43896481-75A3-3340-A2F6-92B9773AE824}">
       <text>
         <r>
           <rPr>
@@ -8538,7 +8512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I388" authorId="0" shapeId="0" xr:uid="{A1B86E64-CCFC-9A4C-8384-1D5FF3275ED9}">
+    <comment ref="I388" authorId="0" shapeId="0" xr:uid="{2FDAAD7D-4768-8D44-A125-A1C62DDCA755}">
       <text>
         <r>
           <rPr>
@@ -8558,7 +8532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I389" authorId="0" shapeId="0" xr:uid="{A63A6C56-D6BD-1443-B0EC-AB5BF0D7CE7E}">
+    <comment ref="I389" authorId="0" shapeId="0" xr:uid="{055AA037-E73B-5C4D-AAE6-9BD882831690}">
       <text>
         <r>
           <rPr>
@@ -8576,7 +8550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I390" authorId="0" shapeId="0" xr:uid="{E43C493E-90D6-B849-8889-75D4FFBD57A7}">
+    <comment ref="I390" authorId="0" shapeId="0" xr:uid="{47CC1697-3974-494B-8D6A-3050160BAE62}">
       <text>
         <r>
           <rPr>
@@ -8594,7 +8568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I391" authorId="0" shapeId="0" xr:uid="{02530C73-BF06-5B48-8B68-84F62196A226}">
+    <comment ref="I391" authorId="0" shapeId="0" xr:uid="{9CBB8675-9412-B143-BFB7-CA6E92F1DABD}">
       <text>
         <r>
           <rPr>
@@ -8611,7 +8585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I392" authorId="0" shapeId="0" xr:uid="{783E52D0-7512-B041-9E37-9E1703D3F72E}">
+    <comment ref="I392" authorId="0" shapeId="0" xr:uid="{F2202A7E-BA96-9444-BF80-CE0C3D40D701}">
       <text>
         <r>
           <rPr>
@@ -8628,7 +8602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I393" authorId="0" shapeId="0" xr:uid="{CD0DEE07-F092-F44C-8D09-307F44935E31}">
+    <comment ref="I393" authorId="0" shapeId="0" xr:uid="{3FC63A55-E2EA-F343-A979-B239FCB1DC6D}">
       <text>
         <r>
           <rPr>
@@ -8657,7 +8631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I394" authorId="0" shapeId="0" xr:uid="{D2DA3317-993B-1842-8EFC-7137BB317956}">
+    <comment ref="I394" authorId="0" shapeId="0" xr:uid="{CB4A3699-9CE5-5C40-8B68-98B7C94C9AF1}">
       <text>
         <r>
           <rPr>
@@ -8679,7 +8653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I395" authorId="0" shapeId="0" xr:uid="{B3C37DCE-7A03-474E-B9C2-9CB19F23E00B}">
+    <comment ref="I395" authorId="0" shapeId="0" xr:uid="{9784E5B4-EDB2-2846-A038-99AD2737B6A8}">
       <text>
         <r>
           <rPr>
@@ -8695,7 +8669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I396" authorId="0" shapeId="0" xr:uid="{ADA554D5-B62A-0A4E-AE52-4CC75477AB60}">
+    <comment ref="I396" authorId="0" shapeId="0" xr:uid="{18F0C863-A70D-4E4B-BD02-260D9A984C7A}">
       <text>
         <r>
           <rPr>
@@ -8714,7 +8688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I397" authorId="0" shapeId="0" xr:uid="{04BC9BCB-E43D-4A48-9178-82EC5BB8BD0C}">
+    <comment ref="I397" authorId="0" shapeId="0" xr:uid="{E77EBADC-E552-F347-BF9C-87F1820698F8}">
       <text>
         <r>
           <rPr>
@@ -8736,7 +8710,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I398" authorId="0" shapeId="0" xr:uid="{55DA0408-64AD-5746-BFA1-59A6978BB330}">
+    <comment ref="I398" authorId="0" shapeId="0" xr:uid="{BCAFDCE1-4A35-6D46-9B28-A879B285EC73}">
       <text>
         <r>
           <rPr>
@@ -8754,7 +8728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I399" authorId="0" shapeId="0" xr:uid="{F274200A-E41C-D740-88B2-FFCDF40E4C79}">
+    <comment ref="I399" authorId="0" shapeId="0" xr:uid="{FA1F03AE-3AC6-5940-B102-D7DAF0DDEB69}">
       <text>
         <r>
           <rPr>
@@ -8772,7 +8746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I400" authorId="0" shapeId="0" xr:uid="{548F211D-1ED9-234B-B7BF-CF72B1A89019}">
+    <comment ref="I400" authorId="0" shapeId="0" xr:uid="{01A319DE-2B26-3143-A4E5-70E537507749}">
       <text>
         <r>
           <rPr>
@@ -8788,7 +8762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I401" authorId="0" shapeId="0" xr:uid="{184DBF28-2590-1041-8FD6-2000F2E10EA7}">
+    <comment ref="I401" authorId="0" shapeId="0" xr:uid="{D90FD009-E803-D943-9020-FC34FE8D1B8B}">
       <text>
         <r>
           <rPr>
@@ -8811,7 +8785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I402" authorId="0" shapeId="0" xr:uid="{E53AAC39-278E-1C46-87B7-3F720905B5C1}">
+    <comment ref="I402" authorId="0" shapeId="0" xr:uid="{2788C9C8-5084-AE45-AC41-75448A3AFB40}">
       <text>
         <r>
           <rPr>
@@ -8829,7 +8803,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I403" authorId="0" shapeId="0" xr:uid="{821E5E81-E1A5-1848-A8CC-600D0F43F4BE}">
+    <comment ref="I403" authorId="0" shapeId="0" xr:uid="{71711A38-5EDB-CD46-92E7-4E8230BF9F9B}">
       <text>
         <r>
           <rPr>
@@ -8847,7 +8821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I404" authorId="0" shapeId="0" xr:uid="{CF74A982-9BDF-6849-BE44-BDA8563D56D8}">
+    <comment ref="I404" authorId="0" shapeId="0" xr:uid="{4925D346-6B03-EA49-BFE1-BB1A4F370C5D}">
       <text>
         <r>
           <rPr>
@@ -8865,7 +8839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I405" authorId="0" shapeId="0" xr:uid="{7AAB8EBB-2E3E-9F43-96E4-766800A20784}">
+    <comment ref="I405" authorId="0" shapeId="0" xr:uid="{B2969376-89AE-BD44-B0AF-B4519E1847B9}">
       <text>
         <r>
           <rPr>
@@ -8888,7 +8862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I406" authorId="0" shapeId="0" xr:uid="{B999BECC-8833-044B-8EDF-D3EEEE152306}">
+    <comment ref="I406" authorId="0" shapeId="0" xr:uid="{472508D5-7D7B-F549-9742-207E3878CD94}">
       <text>
         <r>
           <rPr>
@@ -8906,7 +8880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I407" authorId="0" shapeId="0" xr:uid="{4ED74A6E-D383-614A-B4AE-D395DE4CD32D}">
+    <comment ref="I407" authorId="0" shapeId="0" xr:uid="{D356B396-62A5-C94F-A07E-5B9B8660D716}">
       <text>
         <r>
           <rPr>
@@ -8929,7 +8903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I408" authorId="0" shapeId="0" xr:uid="{183E45FF-C801-AE4E-98DA-57E762B21F38}">
+    <comment ref="I408" authorId="0" shapeId="0" xr:uid="{CED8FB91-390E-5A4E-B2DB-FBCE533AD736}">
       <text>
         <r>
           <rPr>
@@ -8947,7 +8921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I409" authorId="0" shapeId="0" xr:uid="{B1213E9D-9E81-9441-AE17-64A73AD915EB}">
+    <comment ref="I409" authorId="0" shapeId="0" xr:uid="{41169B03-1E70-CF49-96E1-137A53E27703}">
       <text>
         <r>
           <rPr>
@@ -8965,7 +8939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I410" authorId="0" shapeId="0" xr:uid="{0AC6BD87-351E-0847-A16C-937DCC59786D}">
+    <comment ref="I410" authorId="0" shapeId="0" xr:uid="{B81DF8E6-F628-3548-992A-8DBB72651F98}">
       <text>
         <r>
           <rPr>
@@ -8984,7 +8958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I411" authorId="0" shapeId="0" xr:uid="{6AF283DA-F4E0-D744-830A-81540973DC30}">
+    <comment ref="I411" authorId="0" shapeId="0" xr:uid="{E379B071-DCF8-B748-9B0A-5CD799A19F43}">
       <text>
         <r>
           <rPr>
@@ -9007,7 +8981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I412" authorId="0" shapeId="0" xr:uid="{DABDB5CF-7439-DD46-A8DF-43146B8D3747}">
+    <comment ref="I412" authorId="0" shapeId="0" xr:uid="{C979677C-9AC3-C448-B3CD-DA8049C2EE72}">
       <text>
         <r>
           <rPr>
@@ -9025,7 +8999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I413" authorId="0" shapeId="0" xr:uid="{27ABB536-F02E-5D46-8C71-75B7BDACB7A3}">
+    <comment ref="I413" authorId="0" shapeId="0" xr:uid="{A7C4B9F7-833D-6746-8B12-A4C03652749B}">
       <text>
         <r>
           <rPr>
@@ -9041,7 +9015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I414" authorId="0" shapeId="0" xr:uid="{ECB50423-A9EB-9541-9AC5-2BB6567B2A39}">
+    <comment ref="I414" authorId="0" shapeId="0" xr:uid="{13DC9D6E-AF18-F84D-BFF7-8A217A8A1877}">
       <text>
         <r>
           <rPr>
@@ -9064,7 +9038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I415" authorId="0" shapeId="0" xr:uid="{70DD5B8C-CB33-2745-8D71-35D9B0780301}">
+    <comment ref="I415" authorId="0" shapeId="0" xr:uid="{0D024D7C-5613-3941-A115-83A4CF1A0B24}">
       <text>
         <r>
           <rPr>
@@ -9082,7 +9056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I416" authorId="0" shapeId="0" xr:uid="{55C926C7-170D-7548-975A-7921AAD9CC4D}">
+    <comment ref="I416" authorId="0" shapeId="0" xr:uid="{B16D45EA-F1EA-6343-828E-454C45210FC3}">
       <text>
         <r>
           <rPr>
@@ -9097,7 +9071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I417" authorId="0" shapeId="0" xr:uid="{4AC3D76E-471F-B141-9E62-F1F8316413E7}">
+    <comment ref="I417" authorId="0" shapeId="0" xr:uid="{E55E753F-F59D-7B4D-AFC9-E680C205C962}">
       <text>
         <r>
           <rPr>
@@ -9120,7 +9094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I418" authorId="0" shapeId="0" xr:uid="{E93E9C93-580F-1C49-90CF-D1B6F8FBD915}">
+    <comment ref="I418" authorId="0" shapeId="0" xr:uid="{F9669E01-4276-664F-9ED6-F4279AE85C9E}">
       <text>
         <r>
           <rPr>
@@ -9139,7 +9113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I419" authorId="0" shapeId="0" xr:uid="{BA4D9641-8E8D-7F45-8229-CB774F597F05}">
+    <comment ref="I419" authorId="0" shapeId="0" xr:uid="{C4497C8E-CE58-524E-98C9-8499D033CE0A}">
       <text>
         <r>
           <rPr>
@@ -9162,7 +9136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I420" authorId="0" shapeId="0" xr:uid="{AD93E3FC-E14F-894F-BE1C-1A27C1B443C1}">
+    <comment ref="I420" authorId="0" shapeId="0" xr:uid="{D4EA8CB9-6AF5-C242-8448-B2592AC5C9AD}">
       <text>
         <r>
           <rPr>
@@ -9180,7 +9154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I421" authorId="0" shapeId="0" xr:uid="{3FC9997E-5E36-C747-9126-C6F4B15D7CB4}">
+    <comment ref="I421" authorId="0" shapeId="0" xr:uid="{F664518E-984C-894A-B526-843E0DBD3C42}">
       <text>
         <r>
           <rPr>
@@ -9203,7 +9177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I422" authorId="0" shapeId="0" xr:uid="{499829D3-52BF-9348-9795-9B1B0873939A}">
+    <comment ref="I422" authorId="0" shapeId="0" xr:uid="{A8AD15DB-0461-D14F-BB2E-AE8DA0628490}">
       <text>
         <r>
           <rPr>
@@ -9226,7 +9200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I423" authorId="0" shapeId="0" xr:uid="{7169E8F3-99FD-D545-B68C-2BA6732196EE}">
+    <comment ref="I423" authorId="0" shapeId="0" xr:uid="{65F2ACF1-C9A6-144B-8DC3-6B11127D58B2}">
       <text>
         <r>
           <rPr>
@@ -9249,7 +9223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I424" authorId="0" shapeId="0" xr:uid="{69DE4FF4-C55D-1346-8AD7-456C5F6B4870}">
+    <comment ref="I424" authorId="0" shapeId="0" xr:uid="{B813B6A0-6E72-8545-BACD-431104C422CC}">
       <text>
         <r>
           <rPr>
@@ -9272,7 +9246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I425" authorId="0" shapeId="0" xr:uid="{F8F088CD-6E59-1247-9D71-6EABFC86CC44}">
+    <comment ref="I425" authorId="0" shapeId="0" xr:uid="{FDEB1FDF-21F4-5540-8A48-166701078485}">
       <text>
         <r>
           <rPr>
@@ -9290,7 +9264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I426" authorId="0" shapeId="0" xr:uid="{F0EFB85C-883D-A94D-A45C-846CB04952BB}">
+    <comment ref="I426" authorId="0" shapeId="0" xr:uid="{D7B2B45F-B0FD-444E-9C88-20B1B5B47B69}">
       <text>
         <r>
           <rPr>
@@ -9313,7 +9287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I427" authorId="0" shapeId="0" xr:uid="{BD8BBC17-B1C3-BF43-B774-0692322C7AD6}">
+    <comment ref="I427" authorId="0" shapeId="0" xr:uid="{118ED0F8-52B7-B449-B7F5-246B3DC877B0}">
       <text>
         <r>
           <rPr>
@@ -9336,7 +9310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I428" authorId="0" shapeId="0" xr:uid="{C3C9CE05-FE4E-C241-A095-30B3F8C396A9}">
+    <comment ref="I428" authorId="0" shapeId="0" xr:uid="{2A6830E0-EA70-EE40-9A5B-B1488C45BC5E}">
       <text>
         <r>
           <rPr>
@@ -9359,7 +9333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I429" authorId="0" shapeId="0" xr:uid="{8BBF7758-9781-E547-9FC7-74E657A145C6}">
+    <comment ref="I429" authorId="0" shapeId="0" xr:uid="{7B9DD2C8-40B0-FD43-BD15-75B6AD2F6641}">
       <text>
         <r>
           <rPr>
@@ -9382,7 +9356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I430" authorId="0" shapeId="0" xr:uid="{896DFC0D-AF9C-DA4E-8646-6D7F3E2FB600}">
+    <comment ref="I430" authorId="0" shapeId="0" xr:uid="{62F56BE9-EB5B-034E-AF72-7A3B90950DFA}">
       <text>
         <r>
           <rPr>
@@ -9405,7 +9379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I431" authorId="0" shapeId="0" xr:uid="{AA3F9C77-C772-444F-A7ED-8AA97673AA9A}">
+    <comment ref="I431" authorId="0" shapeId="0" xr:uid="{F7E24A3C-CF5E-3743-A53D-C071B2AFE99A}">
       <text>
         <r>
           <rPr>
@@ -9428,7 +9402,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I432" authorId="0" shapeId="0" xr:uid="{D409EB21-B3F1-EF49-9856-5ABDB8404E78}">
+    <comment ref="I432" authorId="0" shapeId="0" xr:uid="{85C0AD54-8449-8D44-A232-C1BD2CBE8231}">
       <text>
         <r>
           <rPr>
@@ -9443,7 +9417,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I433" authorId="0" shapeId="0" xr:uid="{CC2F6A80-9444-CE49-9F59-2BA7A77F191E}">
+    <comment ref="I433" authorId="0" shapeId="0" xr:uid="{709B3892-26EE-B54A-B951-9BE19F5A7A29}">
       <text>
         <r>
           <rPr>
@@ -9473,7 +9447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I434" authorId="0" shapeId="0" xr:uid="{63A96FE4-80C7-5E42-99BC-BF8CAB44CFAB}">
+    <comment ref="I434" authorId="0" shapeId="0" xr:uid="{8B492E5D-19AE-E440-B3FE-F2883B198692}">
       <text>
         <r>
           <rPr>
@@ -9502,7 +9476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I435" authorId="0" shapeId="0" xr:uid="{660FD3BE-055A-DC4F-8A70-C8E0373F1939}">
+    <comment ref="I435" authorId="0" shapeId="0" xr:uid="{700C58CB-84FE-CE48-BC65-7F086FE3A45C}">
       <text>
         <r>
           <rPr>
@@ -9518,7 +9492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I436" authorId="0" shapeId="0" xr:uid="{B51CF53C-4E5E-D641-8967-C18A1BEEE077}">
+    <comment ref="I436" authorId="0" shapeId="0" xr:uid="{D5DEA28E-5BC6-E543-A6F1-D80DA5D1ECED}">
       <text>
         <r>
           <rPr>
@@ -9537,7 +9511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I437" authorId="0" shapeId="0" xr:uid="{2C931645-E2CE-CA48-A4E9-DD42AC61A1AB}">
+    <comment ref="I437" authorId="0" shapeId="0" xr:uid="{A0E830CD-A663-B649-B8A6-EF14603FA050}">
       <text>
         <r>
           <rPr>
@@ -9557,7 +9531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I438" authorId="0" shapeId="0" xr:uid="{0496E561-D77C-5149-819F-D65E3C2A597E}">
+    <comment ref="I438" authorId="0" shapeId="0" xr:uid="{83BA98E1-35CC-FB4D-9023-DD5153075DC0}">
       <text>
         <r>
           <rPr>
@@ -9577,7 +9551,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I439" authorId="0" shapeId="0" xr:uid="{495DD6C2-398B-AC44-8E24-BECF7C8D7F1A}">
+    <comment ref="I439" authorId="0" shapeId="0" xr:uid="{A6270537-1B23-C04D-BC26-164EA474285B}">
       <text>
         <r>
           <rPr>
@@ -9593,7 +9567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I440" authorId="0" shapeId="0" xr:uid="{80E71F84-C777-A44A-AE7E-2260C7F68EB0}">
+    <comment ref="I440" authorId="0" shapeId="0" xr:uid="{3DF37484-FC52-3D47-AEB0-48585C4299CA}">
       <text>
         <r>
           <rPr>
@@ -9613,7 +9587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I441" authorId="0" shapeId="0" xr:uid="{28FFB1CF-6EB6-2A43-90F8-FB82DB0A5A82}">
+    <comment ref="I441" authorId="0" shapeId="0" xr:uid="{3A3D6593-A970-F843-891C-BA689010CB98}">
       <text>
         <r>
           <rPr>
@@ -9632,7 +9606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I442" authorId="0" shapeId="0" xr:uid="{4C260DF8-B605-6443-80CD-B7008BFD3E64}">
+    <comment ref="I442" authorId="0" shapeId="0" xr:uid="{06CFC007-300A-5943-92ED-5AAFF406D241}">
       <text>
         <r>
           <rPr>
@@ -9652,7 +9626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I443" authorId="0" shapeId="0" xr:uid="{C1884AD5-6EE1-544A-AC55-FE7B27041660}">
+    <comment ref="I443" authorId="0" shapeId="0" xr:uid="{FFEA7B9A-E365-8F49-8F1F-10998D54EF1E}">
       <text>
         <r>
           <rPr>
@@ -9672,7 +9646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I444" authorId="0" shapeId="0" xr:uid="{FEDEE016-09BE-6A4A-87D2-073273D7D9CF}">
+    <comment ref="I444" authorId="0" shapeId="0" xr:uid="{8EED36FB-7CA6-D14B-A3C0-323B2308C29F}">
       <text>
         <r>
           <rPr>
@@ -9691,7 +9665,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I445" authorId="0" shapeId="0" xr:uid="{11B4025D-E2A8-DE4B-AEE7-D283C691CBD1}">
+    <comment ref="I445" authorId="0" shapeId="0" xr:uid="{5BC2DC66-3F53-A145-A4C0-55BA5E52DBFF}">
       <text>
         <r>
           <rPr>
@@ -9717,7 +9691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I446" authorId="0" shapeId="0" xr:uid="{A40040C8-393A-2C4C-9C73-5D1A45EF5A59}">
+    <comment ref="I446" authorId="0" shapeId="0" xr:uid="{95A364C8-6BBF-484A-B93D-79289D261349}">
       <text>
         <r>
           <rPr>
@@ -9743,7 +9717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I447" authorId="0" shapeId="0" xr:uid="{E53CA82B-46DE-9E41-A4F7-E91B4BCB1503}">
+    <comment ref="I447" authorId="0" shapeId="0" xr:uid="{EBB93C19-58EE-3F4D-92DA-949CFBAC6EFF}">
       <text>
         <r>
           <rPr>
@@ -9769,7 +9743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I448" authorId="0" shapeId="0" xr:uid="{98F76995-4BE6-584B-9827-CDE83CBDAB66}">
+    <comment ref="I448" authorId="0" shapeId="0" xr:uid="{309AAC35-7501-7B4A-B90C-5983F75F24BB}">
       <text>
         <r>
           <rPr>
@@ -9789,7 +9763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I449" authorId="0" shapeId="0" xr:uid="{7B94F910-D83D-D741-B652-07D8030D7F65}">
+    <comment ref="I449" authorId="0" shapeId="0" xr:uid="{38B2E341-5898-6346-8F58-9BA00CF42555}">
       <text>
         <r>
           <rPr>
@@ -9812,7 +9786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I450" authorId="0" shapeId="0" xr:uid="{E6731921-BB23-3345-9199-E477C90C22F8}">
+    <comment ref="I450" authorId="0" shapeId="0" xr:uid="{B2CAEF47-EAA2-3C4E-B8E3-FAEF094AD21D}">
       <text>
         <r>
           <rPr>
@@ -9838,7 +9812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I451" authorId="0" shapeId="0" xr:uid="{86912B04-DE90-6D43-A530-A4D22B3396DC}">
+    <comment ref="I451" authorId="0" shapeId="0" xr:uid="{07F988D3-5A1A-4743-9C4B-C80882D54D32}">
       <text>
         <r>
           <rPr>
@@ -9858,7 +9832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I452" authorId="0" shapeId="0" xr:uid="{A71A225A-4984-2B44-A293-6E4D2DEDA351}">
+    <comment ref="I452" authorId="0" shapeId="0" xr:uid="{DA8D7482-F41A-D642-AD5F-7287A8DD7369}">
       <text>
         <r>
           <rPr>
@@ -9884,7 +9858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I453" authorId="0" shapeId="0" xr:uid="{841D12E7-0F19-984B-B338-E1DB73C559E0}">
+    <comment ref="I453" authorId="0" shapeId="0" xr:uid="{36CB5D37-5028-3E49-B5C2-A1B6C65B3C28}">
       <text>
         <r>
           <rPr>
@@ -9910,7 +9884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I454" authorId="0" shapeId="0" xr:uid="{CD5B4EF4-B9B3-BB4E-B053-BA724D394C3A}">
+    <comment ref="I454" authorId="0" shapeId="0" xr:uid="{6C72B2A2-669A-0443-A156-8912D6095B4F}">
       <text>
         <r>
           <rPr>
@@ -9930,7 +9904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I455" authorId="0" shapeId="0" xr:uid="{9A594232-91BB-4F4B-A49F-49FF95EC17E3}">
+    <comment ref="I455" authorId="0" shapeId="0" xr:uid="{725866F3-3ADE-6C4F-8E67-554A9D5BB253}">
       <text>
         <r>
           <rPr>
@@ -9953,7 +9927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I456" authorId="0" shapeId="0" xr:uid="{023B903E-6841-F648-B101-B0413F4C25FB}">
+    <comment ref="I456" authorId="0" shapeId="0" xr:uid="{B201B061-52B6-3240-9999-B5D7F9EDF7ED}">
       <text>
         <r>
           <rPr>
@@ -9976,7 +9950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I457" authorId="0" shapeId="0" xr:uid="{69F6CA35-B508-0B43-B071-DD4DA1FCFB40}">
+    <comment ref="I457" authorId="0" shapeId="0" xr:uid="{2FEE9A25-D0C7-514F-A73C-2FC3B15396B3}">
       <text>
         <r>
           <rPr>
@@ -9996,7 +9970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I458" authorId="0" shapeId="0" xr:uid="{E544DB34-CB22-6749-94A6-52129F690CF5}">
+    <comment ref="I458" authorId="0" shapeId="0" xr:uid="{9079DD3A-8064-9840-8B58-187ECDCA2C3E}">
       <text>
         <r>
           <rPr>
@@ -10022,7 +9996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I459" authorId="0" shapeId="0" xr:uid="{8EE463BC-777C-0A47-875E-EEDD77D252A0}">
+    <comment ref="I459" authorId="0" shapeId="0" xr:uid="{104EC9F3-1409-5949-A29D-2A96885451CA}">
       <text>
         <r>
           <rPr>
@@ -10042,7 +10016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I460" authorId="0" shapeId="0" xr:uid="{6EA77256-B734-5743-B86A-9A6BA09DCE1C}">
+    <comment ref="I460" authorId="0" shapeId="0" xr:uid="{8F8AD645-FAD1-BE42-9B7D-4C94A4CFC43C}">
       <text>
         <r>
           <rPr>
@@ -10062,7 +10036,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I461" authorId="0" shapeId="0" xr:uid="{77158EA5-2975-9543-81EF-4A29FEB82478}">
+    <comment ref="I461" authorId="0" shapeId="0" xr:uid="{F32ADFFF-7518-4C4D-A874-0C356C057BBD}">
       <text>
         <r>
           <rPr>
@@ -10088,7 +10062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I462" authorId="0" shapeId="0" xr:uid="{94B60FF6-320C-4942-B533-A93CE235105E}">
+    <comment ref="I462" authorId="0" shapeId="0" xr:uid="{62E06C8A-E525-1748-991F-E7446B27ADB3}">
       <text>
         <r>
           <rPr>
@@ -10108,7 +10082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I463" authorId="0" shapeId="0" xr:uid="{0A22ADFF-8C8D-1845-ADD8-7D89CF9FB1EC}">
+    <comment ref="I463" authorId="0" shapeId="0" xr:uid="{B076105C-2872-314D-B2B6-33592425A587}">
       <text>
         <r>
           <rPr>
@@ -10134,7 +10108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I464" authorId="0" shapeId="0" xr:uid="{36C0A501-A125-7E42-8173-E977A5CB804A}">
+    <comment ref="I464" authorId="0" shapeId="0" xr:uid="{378DFC10-1BBB-B044-93E4-DA1446CB547B}">
       <text>
         <r>
           <rPr>
@@ -10160,7 +10134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I465" authorId="0" shapeId="0" xr:uid="{40ECCF90-A5B0-F14A-B192-9E98A6041A0C}">
+    <comment ref="I465" authorId="0" shapeId="0" xr:uid="{D144D42A-7BDA-1B49-BEEC-220858B54296}">
       <text>
         <r>
           <rPr>
@@ -10180,7 +10154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I466" authorId="0" shapeId="0" xr:uid="{AD3EBD9C-482C-8242-B7C0-FA9AC5231823}">
+    <comment ref="I466" authorId="0" shapeId="0" xr:uid="{18FA5562-3FC6-5447-80EB-E73938656A0E}">
       <text>
         <r>
           <rPr>
@@ -10200,7 +10174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I467" authorId="0" shapeId="0" xr:uid="{98D23B2C-C0AD-A845-9C47-EA4FF915A8B7}">
+    <comment ref="I467" authorId="0" shapeId="0" xr:uid="{7B99D00A-6C22-7E4A-985C-55E0E9270D56}">
       <text>
         <r>
           <rPr>
@@ -10226,7 +10200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I468" authorId="0" shapeId="0" xr:uid="{668FD319-3692-F54E-A09D-13BF6CEE999B}">
+    <comment ref="I468" authorId="0" shapeId="0" xr:uid="{80C711E7-822E-B943-802E-EE80F254C9EA}">
       <text>
         <r>
           <rPr>
@@ -10246,7 +10220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I469" authorId="0" shapeId="0" xr:uid="{0D3A92F2-91D8-D241-85CA-3B2540EDF91E}">
+    <comment ref="I469" authorId="0" shapeId="0" xr:uid="{C43D8728-9ECF-F248-B536-0060E984E4BA}">
       <text>
         <r>
           <rPr>
@@ -10272,7 +10246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I470" authorId="0" shapeId="0" xr:uid="{88DF22AA-CB44-6E49-AA22-F663AEDC018F}">
+    <comment ref="I470" authorId="0" shapeId="0" xr:uid="{2E9955F9-EAE3-0746-AA4D-2A6D03A7CC6E}">
       <text>
         <r>
           <rPr>
@@ -10298,7 +10272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I471" authorId="0" shapeId="0" xr:uid="{950838F2-19F3-AD4C-8A89-4203F9E4571D}">
+    <comment ref="I471" authorId="0" shapeId="0" xr:uid="{16A21F6F-F16B-C045-889C-80608807AD7C}">
       <text>
         <r>
           <rPr>
@@ -10318,7 +10292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I472" authorId="0" shapeId="0" xr:uid="{D94AA941-2C64-224A-A549-B354BDEA7471}">
+    <comment ref="I472" authorId="0" shapeId="0" xr:uid="{592FECF5-E8CB-0C4D-9516-8888E752CD2F}">
       <text>
         <r>
           <rPr>
@@ -10336,7 +10310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I473" authorId="0" shapeId="0" xr:uid="{5168916A-4F26-6B43-8848-1D1E7DE0AE13}">
+    <comment ref="I473" authorId="0" shapeId="0" xr:uid="{A6970223-C277-7C4D-856B-0DAB925EAD79}">
       <text>
         <r>
           <rPr>
@@ -10365,7 +10339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I474" authorId="0" shapeId="0" xr:uid="{A4FC76E8-1A91-FB49-86D2-25D0883D4386}">
+    <comment ref="I474" authorId="0" shapeId="0" xr:uid="{FE0E727F-7777-4A45-B384-65FDE3C662E7}">
       <text>
         <r>
           <rPr>
@@ -10381,7 +10355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I475" authorId="0" shapeId="0" xr:uid="{CE7D1CBD-DD0D-D246-89E3-80F442CC7C66}">
+    <comment ref="I475" authorId="0" shapeId="0" xr:uid="{621A2856-1AC7-984E-B1C5-9AA07886CF7E}">
       <text>
         <r>
           <rPr>
@@ -10397,7 +10371,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I476" authorId="0" shapeId="0" xr:uid="{04636EDF-A157-C942-9129-EE6A0C9A49F1}">
+    <comment ref="I476" authorId="0" shapeId="0" xr:uid="{578FB428-CE42-4F45-B40D-ED2199DFF2D3}">
       <text>
         <r>
           <rPr>
@@ -10417,7 +10391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I477" authorId="0" shapeId="0" xr:uid="{86C7F3A3-21F9-9041-B0AA-034EFC9AE6C6}">
+    <comment ref="I477" authorId="0" shapeId="0" xr:uid="{485F163B-DC6D-EA41-8646-786782873BB0}">
       <text>
         <r>
           <rPr>
@@ -10443,7 +10417,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I478" authorId="0" shapeId="0" xr:uid="{84678152-0C60-7849-97F2-DE505AB23902}">
+    <comment ref="I478" authorId="0" shapeId="0" xr:uid="{C2DBF854-1D17-0B4B-B1C8-D091DBC56138}">
       <text>
         <r>
           <rPr>
@@ -10459,7 +10433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I479" authorId="0" shapeId="0" xr:uid="{95A6FF2D-B860-AA4A-9AD5-F270F3EF029D}">
+    <comment ref="I479" authorId="0" shapeId="0" xr:uid="{5D261A89-FB5C-EF4A-883E-6A5F33294D57}">
       <text>
         <r>
           <rPr>
@@ -10479,7 +10453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I480" authorId="0" shapeId="0" xr:uid="{90A9E2B9-7F67-054B-80DD-E4C04429F208}">
+    <comment ref="I480" authorId="0" shapeId="0" xr:uid="{5526E422-417F-7C40-A72A-55B86EE47952}">
       <text>
         <r>
           <rPr>
@@ -10495,7 +10469,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I481" authorId="0" shapeId="0" xr:uid="{00E53211-5952-AA4C-A64D-11F772081CC9}">
+    <comment ref="I481" authorId="0" shapeId="0" xr:uid="{6FBC4E35-7E19-124F-9A61-43738E5075E7}">
       <text>
         <r>
           <rPr>
@@ -10521,7 +10495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I482" authorId="0" shapeId="0" xr:uid="{F004A8CD-ACE5-5A40-956D-587FEEF8951C}">
+    <comment ref="I482" authorId="0" shapeId="0" xr:uid="{88E4892A-4AFF-9E4B-91A9-B8F3B88C6410}">
       <text>
         <r>
           <rPr>
@@ -10544,7 +10518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I483" authorId="0" shapeId="0" xr:uid="{897AA9EA-11C8-1E42-B9BB-5CC9A6542636}">
+    <comment ref="I483" authorId="0" shapeId="0" xr:uid="{37D99255-4473-C04F-AF12-44221A3C8020}">
       <text>
         <r>
           <rPr>
@@ -10564,7 +10538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I484" authorId="0" shapeId="0" xr:uid="{3857718F-3C8A-174B-BB0D-115B2CCC33C8}">
+    <comment ref="I484" authorId="0" shapeId="0" xr:uid="{8A6D6AB3-5C12-4647-A40C-64FF56A6635B}">
       <text>
         <r>
           <rPr>
@@ -10580,7 +10554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I485" authorId="0" shapeId="0" xr:uid="{52276DE7-2862-EA48-A20F-00881AD326F4}">
+    <comment ref="I485" authorId="0" shapeId="0" xr:uid="{1DC51DDE-F93D-DA42-A175-1E693E1AF6B6}">
       <text>
         <r>
           <rPr>
@@ -10606,7 +10580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I486" authorId="0" shapeId="0" xr:uid="{4C3DB519-C3D0-3242-BF2D-0B6C24756860}">
+    <comment ref="I486" authorId="0" shapeId="0" xr:uid="{0F8822D5-48B5-0D43-8993-4B2AEC4D548C}">
       <text>
         <r>
           <rPr>
@@ -10622,7 +10596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I487" authorId="0" shapeId="0" xr:uid="{49A93E11-BFE8-0F43-80F9-B347E296864C}">
+    <comment ref="I487" authorId="0" shapeId="0" xr:uid="{5E2BC7E8-E1C0-8743-A2AF-4CEC02CB5F36}">
       <text>
         <r>
           <rPr>
@@ -10642,7 +10616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I488" authorId="0" shapeId="0" xr:uid="{AB16B213-A145-C841-A2C8-FBDE0F3AC833}">
+    <comment ref="I488" authorId="0" shapeId="0" xr:uid="{47333A77-AD0F-C24C-ACB4-61BE5A6E9B19}">
       <text>
         <r>
           <rPr>
@@ -10662,7 +10636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I489" authorId="0" shapeId="0" xr:uid="{BB2C1A6E-847D-D240-8843-C4C7601B0315}">
+    <comment ref="I489" authorId="0" shapeId="0" xr:uid="{58A792BA-1DD7-FE44-B3AD-4FD990ADD097}">
       <text>
         <r>
           <rPr>
@@ -10682,7 +10656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I490" authorId="0" shapeId="0" xr:uid="{268F339C-8D34-BE43-9BFC-B5CE68ED4E46}">
+    <comment ref="I490" authorId="0" shapeId="0" xr:uid="{90F80621-F276-6649-85F4-4FA82D2D970F}">
       <text>
         <r>
           <rPr>
@@ -10702,7 +10676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I491" authorId="0" shapeId="0" xr:uid="{E5AF521F-492F-1345-99C6-6AABCB07CF5A}">
+    <comment ref="I491" authorId="0" shapeId="0" xr:uid="{A2367C18-C807-8741-9672-68979630D3CD}">
       <text>
         <r>
           <rPr>
@@ -10728,7 +10702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I492" authorId="0" shapeId="0" xr:uid="{96A39834-F35A-DA42-8C44-DA96DB992A5C}">
+    <comment ref="I492" authorId="0" shapeId="0" xr:uid="{ADBF35F4-1754-924D-9697-97A81F94B8ED}">
       <text>
         <r>
           <rPr>
@@ -10751,7 +10725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I493" authorId="0" shapeId="0" xr:uid="{019C5520-6B7F-8A47-B7A1-3D6A8CC38713}">
+    <comment ref="I493" authorId="0" shapeId="0" xr:uid="{1238A312-FFBA-7345-BA1A-4FAB0302B484}">
       <text>
         <r>
           <rPr>
@@ -10777,7 +10751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I494" authorId="0" shapeId="0" xr:uid="{103DB91A-F442-354D-B5CD-ADCD6B2DD221}">
+    <comment ref="I494" authorId="0" shapeId="0" xr:uid="{8DC6EEED-7CB8-9348-B2CF-2348D909650A}">
       <text>
         <r>
           <rPr>
@@ -10797,7 +10771,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I495" authorId="0" shapeId="0" xr:uid="{27E32BB8-41BB-A94E-B811-002612BED525}">
+    <comment ref="I495" authorId="0" shapeId="0" xr:uid="{683DDA20-BC0A-F949-B67B-755287C9C145}">
       <text>
         <r>
           <rPr>
@@ -10817,7 +10791,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I496" authorId="0" shapeId="0" xr:uid="{B174D313-E312-544A-A195-7BB66C54B7EA}">
+    <comment ref="I496" authorId="0" shapeId="0" xr:uid="{EA522D50-D485-1A49-8C4D-DA691F75F978}">
       <text>
         <r>
           <rPr>
@@ -10837,7 +10811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I497" authorId="0" shapeId="0" xr:uid="{4EA54391-7B8C-CC49-A265-F726CDD4F5C9}">
+    <comment ref="I497" authorId="0" shapeId="0" xr:uid="{83FC8CD4-13F4-6F47-AF63-A7DF665F7678}">
       <text>
         <r>
           <rPr>
@@ -10857,7 +10831,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I498" authorId="0" shapeId="0" xr:uid="{9FFE8671-D78E-7040-867E-3DE37C998A6B}">
+    <comment ref="I498" authorId="0" shapeId="0" xr:uid="{1C2B3B68-FE5C-BD4D-9F1E-96676CFC06C1}">
       <text>
         <r>
           <rPr>
@@ -10877,7 +10851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I499" authorId="0" shapeId="0" xr:uid="{877093EE-B8E3-3E42-B250-299B76DBBE4C}">
+    <comment ref="I499" authorId="0" shapeId="0" xr:uid="{5DBCFFA6-CF1B-B648-84A6-B9539AC2FDFA}">
       <text>
         <r>
           <rPr>
@@ -10898,7 +10872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I500" authorId="0" shapeId="0" xr:uid="{B688D7AF-AF03-E14F-A853-86CA681638B1}">
+    <comment ref="I500" authorId="0" shapeId="0" xr:uid="{06314B8B-CC64-1F4D-BE38-F6FA22227D5B}">
       <text>
         <r>
           <rPr>
@@ -10918,7 +10892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I501" authorId="0" shapeId="0" xr:uid="{5AB3F8F7-5765-4744-ADCD-1592A23C3BCC}">
+    <comment ref="I501" authorId="0" shapeId="0" xr:uid="{92D57C0E-9E49-2B41-B267-3C168811FECB}">
       <text>
         <r>
           <rPr>
@@ -10936,7 +10910,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I502" authorId="0" shapeId="0" xr:uid="{6F891F55-3B81-6149-8160-47AE790CEBEE}">
+    <comment ref="I502" authorId="0" shapeId="0" xr:uid="{2A1F4690-A94E-8740-BBAC-13E07FEA0837}">
       <text>
         <r>
           <rPr>
@@ -10956,7 +10930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I503" authorId="0" shapeId="0" xr:uid="{29115A4D-7641-1643-8FAA-80534CC2D884}">
+    <comment ref="I503" authorId="0" shapeId="0" xr:uid="{A3D41A21-BD7F-194B-8961-7832A7D1AB37}">
       <text>
         <r>
           <rPr>
@@ -10971,7 +10945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I504" authorId="0" shapeId="0" xr:uid="{BFDBA3C5-3527-094C-A280-59C1E701ED68}">
+    <comment ref="I504" authorId="0" shapeId="0" xr:uid="{1DBE696C-A943-4A41-A335-7537F6F0079D}">
       <text>
         <r>
           <rPr>
@@ -10991,7 +10965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I505" authorId="0" shapeId="0" xr:uid="{B3EB2621-99A4-064E-959E-89B148CE0939}">
+    <comment ref="I505" authorId="0" shapeId="0" xr:uid="{A95A45A1-A89D-1543-BDFA-8C9CE936887E}">
       <text>
         <r>
           <rPr>
@@ -11011,7 +10985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I506" authorId="0" shapeId="0" xr:uid="{A7370203-1FEA-8B4D-9BEF-B394CFFADF8C}">
+    <comment ref="I506" authorId="0" shapeId="0" xr:uid="{6D8FD2CA-0865-154B-B0FB-BC908F5E97D7}">
       <text>
         <r>
           <rPr>
@@ -11031,7 +11005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I507" authorId="0" shapeId="0" xr:uid="{D9D5EED4-0899-6E42-9158-CC89495D4A0C}">
+    <comment ref="I507" authorId="0" shapeId="0" xr:uid="{8A89F831-92E4-0A45-BCA4-AB2B8981AE95}">
       <text>
         <r>
           <rPr>
@@ -11051,7 +11025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I508" authorId="0" shapeId="0" xr:uid="{8B9BA080-F775-C244-B9D3-ECE7D6D4C112}">
+    <comment ref="I508" authorId="0" shapeId="0" xr:uid="{AD2A8E95-1F0B-7248-83B0-5D60E2DABBB9}">
       <text>
         <r>
           <rPr>
@@ -11068,7 +11042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I509" authorId="0" shapeId="0" xr:uid="{AFD250B9-B919-0A4C-BB0C-DEEEF4D2A495}">
+    <comment ref="I509" authorId="0" shapeId="0" xr:uid="{6FC678E9-B34E-B443-B18E-E31D5588C218}">
       <text>
         <r>
           <rPr>
@@ -11088,7 +11062,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I510" authorId="0" shapeId="0" xr:uid="{41FEEE6F-574F-8D4F-BF53-C8AC1D01D3E5}">
+    <comment ref="I510" authorId="0" shapeId="0" xr:uid="{69E12D0E-D78B-854F-AF52-FB4BC1572F76}">
       <text>
         <r>
           <rPr>
@@ -11108,7 +11082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I511" authorId="0" shapeId="0" xr:uid="{E6487B68-C16C-914E-9253-C14EA372EC85}">
+    <comment ref="I511" authorId="0" shapeId="0" xr:uid="{0FDA66C3-D4CA-1B45-9870-5C6872F4F477}">
       <text>
         <r>
           <rPr>
@@ -11126,7 +11100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I512" authorId="0" shapeId="0" xr:uid="{1A661793-6F37-894D-A3A3-AF0411E70BCA}">
+    <comment ref="I512" authorId="0" shapeId="0" xr:uid="{79FD902C-FC88-134F-8D12-92732774C466}">
       <text>
         <r>
           <rPr>
@@ -11149,7 +11123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I513" authorId="0" shapeId="0" xr:uid="{1113C9C3-E685-734B-9EE7-856359EA7A3F}">
+    <comment ref="I513" authorId="0" shapeId="0" xr:uid="{5DD43104-F217-1A47-8B2F-7F34732E769B}">
       <text>
         <r>
           <rPr>
@@ -11165,7 +11139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I514" authorId="0" shapeId="0" xr:uid="{134B4A3D-CB7F-A945-AAD3-1AC2EB823966}">
+    <comment ref="I514" authorId="0" shapeId="0" xr:uid="{2399F6CC-5C5C-0440-84E3-584BE1406314}">
       <text>
         <r>
           <rPr>
@@ -11191,7 +11165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I515" authorId="0" shapeId="0" xr:uid="{3C6CD736-C6B6-B545-B3A7-29EBE247D651}">
+    <comment ref="I515" authorId="0" shapeId="0" xr:uid="{129E9519-9340-C646-AB58-03E123FAEFC7}">
       <text>
         <r>
           <rPr>
@@ -11217,7 +11191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I516" authorId="0" shapeId="0" xr:uid="{14BDA5F3-4ED9-9048-983A-ED560D3747DC}">
+    <comment ref="I516" authorId="0" shapeId="0" xr:uid="{9A588BCA-C455-5548-A95A-7B00F23F27DB}">
       <text>
         <r>
           <rPr>
@@ -11233,7 +11207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I517" authorId="0" shapeId="0" xr:uid="{2BF818D3-466F-AA4C-8CF0-3B0D31C6452E}">
+    <comment ref="I517" authorId="0" shapeId="0" xr:uid="{71939D31-9C0A-6B42-9A85-F24E3D729D39}">
       <text>
         <r>
           <rPr>
@@ -11249,7 +11223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I518" authorId="0" shapeId="0" xr:uid="{681EFC1E-35CD-F542-B63B-6055B4BE29F7}">
+    <comment ref="I518" authorId="0" shapeId="0" xr:uid="{D3A0C4D5-CF5C-B24F-A4D0-F9A76939061C}">
       <text>
         <r>
           <rPr>
@@ -11265,7 +11239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I519" authorId="0" shapeId="0" xr:uid="{A06D4EDD-3EBD-3949-887B-621A9F98881C}">
+    <comment ref="I519" authorId="0" shapeId="0" xr:uid="{6BC784E7-001E-D045-B658-A5A83B1CE506}">
       <text>
         <r>
           <rPr>
@@ -11282,7 +11256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I520" authorId="0" shapeId="0" xr:uid="{9F35AF5D-D792-2945-A937-34937B751668}">
+    <comment ref="I520" authorId="0" shapeId="0" xr:uid="{9E1C74F2-7EF6-DE47-A1F9-3805A4247885}">
       <text>
         <r>
           <rPr>
@@ -11299,7 +11273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I521" authorId="0" shapeId="0" xr:uid="{5B196590-D2E6-354C-8F31-5803F743A38B}">
+    <comment ref="I521" authorId="0" shapeId="0" xr:uid="{A1A50018-6299-A149-8FDC-0752CCC5A899}">
       <text>
         <r>
           <rPr>
@@ -11318,7 +11292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I522" authorId="0" shapeId="0" xr:uid="{8C1685AE-E6A8-5041-8A65-CCA6E8380921}">
+    <comment ref="I522" authorId="0" shapeId="0" xr:uid="{4A757BE3-21E1-D343-8F1F-31D7E20C386D}">
       <text>
         <r>
           <rPr>
@@ -11338,7 +11312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I523" authorId="0" shapeId="0" xr:uid="{75A89B74-16C8-694D-A66E-70B44CCE6ABD}">
+    <comment ref="I523" authorId="0" shapeId="0" xr:uid="{7F5B4418-BF81-524D-AFD4-FE9C73811AB9}">
       <text>
         <r>
           <rPr>
@@ -11354,7 +11328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I524" authorId="0" shapeId="0" xr:uid="{471876C4-DB14-FB41-A7FC-75F98BD61511}">
+    <comment ref="I524" authorId="0" shapeId="0" xr:uid="{030B5A23-1E8D-E74E-BB9C-76D46DF2841B}">
       <text>
         <r>
           <rPr>
@@ -11370,7 +11344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I525" authorId="0" shapeId="0" xr:uid="{F25FC5B2-DB9E-7244-B664-F5AB79C303C3}">
+    <comment ref="I525" authorId="0" shapeId="0" xr:uid="{6EDB9CF4-D385-1A49-8C9B-B665FF1FD7B6}">
       <text>
         <r>
           <rPr>
@@ -11387,7 +11361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I526" authorId="0" shapeId="0" xr:uid="{82CC9EE3-7842-5844-980F-E66D4D2ED737}">
+    <comment ref="I526" authorId="0" shapeId="0" xr:uid="{1C028080-92C1-6344-90EA-E7A253EC73DD}">
       <text>
         <r>
           <rPr>
@@ -11403,7 +11377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I527" authorId="0" shapeId="0" xr:uid="{371B328A-BD25-0147-8FCE-B3DE5C212A4C}">
+    <comment ref="I527" authorId="0" shapeId="0" xr:uid="{3F1D27DD-6731-D744-9D66-0844B0908C1A}">
       <text>
         <r>
           <rPr>
@@ -11420,7 +11394,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I528" authorId="0" shapeId="0" xr:uid="{619BAF2A-9A32-0B45-8A2B-828F77E1C0E3}">
+    <comment ref="I528" authorId="0" shapeId="0" xr:uid="{3EB2841D-2064-8549-B917-9C910628EBF1}">
       <text>
         <r>
           <rPr>
@@ -11440,7 +11414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I529" authorId="0" shapeId="0" xr:uid="{68B4890B-332B-2249-A54E-0079937E79A7}">
+    <comment ref="I529" authorId="0" shapeId="0" xr:uid="{A16E4BCC-BAF7-284D-BB3F-333029624BFC}">
       <text>
         <r>
           <rPr>
@@ -11456,7 +11430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I530" authorId="0" shapeId="0" xr:uid="{204066FC-D346-7642-AFB8-64036A7F8586}">
+    <comment ref="I530" authorId="0" shapeId="0" xr:uid="{AA2A3ED3-3028-CA48-9A02-3160B287C421}">
       <text>
         <r>
           <rPr>
@@ -11472,7 +11446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I531" authorId="0" shapeId="0" xr:uid="{6C9F618A-98E0-6E4C-B150-F445EBDBFCA3}">
+    <comment ref="I531" authorId="0" shapeId="0" xr:uid="{AB6B9870-69A8-1D48-97DB-ED59E6C824C3}">
       <text>
         <r>
           <rPr>
@@ -11489,7 +11463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I532" authorId="0" shapeId="0" xr:uid="{5E7B9178-A075-D14B-9584-45FFDF201B7C}">
+    <comment ref="I532" authorId="0" shapeId="0" xr:uid="{EADB94A3-6F4E-3847-BA00-3E081E36373C}">
       <text>
         <r>
           <rPr>
@@ -11505,7 +11479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I533" authorId="0" shapeId="0" xr:uid="{A4BA99E3-A412-EB44-B365-534B8CEDE3B2}">
+    <comment ref="I533" authorId="0" shapeId="0" xr:uid="{D380A77A-E70E-E74A-8C07-6795CBD6EA6F}">
       <text>
         <r>
           <rPr>
@@ -11524,7 +11498,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I534" authorId="0" shapeId="0" xr:uid="{D79E0660-D424-784D-B6D6-9506ADFCA956}">
+    <comment ref="I534" authorId="0" shapeId="0" xr:uid="{00A0EE41-B064-8A40-9392-4D2B9EBFED30}">
       <text>
         <r>
           <rPr>
@@ -11541,7 +11515,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I535" authorId="0" shapeId="0" xr:uid="{EDD423CE-A8F0-BC46-BA75-E43E8FD4D5A1}">
+    <comment ref="I535" authorId="0" shapeId="0" xr:uid="{54D34692-393B-3040-A367-5EB9E718224E}">
       <text>
         <r>
           <rPr>
@@ -11557,7 +11531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I536" authorId="0" shapeId="0" xr:uid="{E06F720B-CE98-6A48-A056-0BBCB30FDBFB}">
+    <comment ref="I536" authorId="0" shapeId="0" xr:uid="{88F9414F-5DD4-F24A-8695-13C6D97FEE5C}">
       <text>
         <r>
           <rPr>
@@ -11573,7 +11547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I537" authorId="0" shapeId="0" xr:uid="{9FE11772-049E-CC4B-A44D-89A5C0000905}">
+    <comment ref="I537" authorId="0" shapeId="0" xr:uid="{C60FA3F3-8D34-1049-A830-5C5D418649D3}">
       <text>
         <r>
           <rPr>
@@ -11589,7 +11563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I538" authorId="0" shapeId="0" xr:uid="{ECCB8ED9-4B64-7246-AA45-88106ED5E9C1}">
+    <comment ref="I538" authorId="0" shapeId="0" xr:uid="{E8F25083-7DCC-BB45-B2D0-088A3CC618E9}">
       <text>
         <r>
           <rPr>
@@ -11608,7 +11582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I539" authorId="0" shapeId="0" xr:uid="{1F44F5AC-F003-3A4F-9497-291AA6CE7BC5}">
+    <comment ref="I539" authorId="0" shapeId="0" xr:uid="{820D5F77-8DC3-0240-806B-67C3F66D1B33}">
       <text>
         <r>
           <rPr>
@@ -11624,7 +11598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I540" authorId="0" shapeId="0" xr:uid="{10EA17B3-6834-D047-BA20-5F9E29A97794}">
+    <comment ref="I540" authorId="0" shapeId="0" xr:uid="{DD27A4BF-0818-2042-8299-BFE505AA1096}">
       <text>
         <r>
           <rPr>
@@ -11639,7 +11613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I541" authorId="0" shapeId="0" xr:uid="{511EAAB5-4B8C-4A4C-BF8E-748D78C18F69}">
+    <comment ref="I541" authorId="0" shapeId="0" xr:uid="{3DA50265-086B-194D-AF43-77FA77FEDE7A}">
       <text>
         <r>
           <rPr>
@@ -11663,7 +11637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I542" authorId="0" shapeId="0" xr:uid="{D706887B-DB68-ED4A-8F27-8AC5B61AB95A}">
+    <comment ref="I542" authorId="0" shapeId="0" xr:uid="{6A33A614-FE73-684A-B823-7E1381E1F86B}">
       <text>
         <r>
           <rPr>
@@ -11679,7 +11653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I543" authorId="0" shapeId="0" xr:uid="{9367EE3A-B443-6343-B287-AE8EBFA83B43}">
+    <comment ref="I543" authorId="0" shapeId="0" xr:uid="{E591415E-6532-9C4A-9339-46354CAC2B91}">
       <text>
         <r>
           <rPr>
@@ -11696,7 +11670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I544" authorId="0" shapeId="0" xr:uid="{6BC90581-113D-FB48-8601-53BB12B9C44C}">
+    <comment ref="I544" authorId="0" shapeId="0" xr:uid="{342900AD-5EB9-2043-9CC5-9510B20F656D}">
       <text>
         <r>
           <rPr>
@@ -11712,7 +11686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I545" authorId="0" shapeId="0" xr:uid="{AA790FF3-5ADF-ED4E-AA34-A9B862A47F19}">
+    <comment ref="I545" authorId="0" shapeId="0" xr:uid="{EA6DAEAA-5835-1647-B0EE-96A159032118}">
       <text>
         <r>
           <rPr>
@@ -11728,7 +11702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I546" authorId="0" shapeId="0" xr:uid="{CEFA9CFF-9E31-4740-A09D-C18397AAEE6F}">
+    <comment ref="I546" authorId="0" shapeId="0" xr:uid="{823E3BF3-E174-FB42-88AA-9CB8614CC4B1}">
       <text>
         <r>
           <rPr>
@@ -11744,7 +11718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I547" authorId="0" shapeId="0" xr:uid="{487AA2DA-5D88-F84F-BFF5-7858AD45C998}">
+    <comment ref="I547" authorId="0" shapeId="0" xr:uid="{C09F49F0-05FE-FB42-B220-2712D9A7D388}">
       <text>
         <r>
           <rPr>
@@ -11758,7 +11732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I548" authorId="0" shapeId="0" xr:uid="{66896341-9868-E94E-8533-D156B8111C3D}">
+    <comment ref="I548" authorId="0" shapeId="0" xr:uid="{7EFC27D5-A315-014A-BB18-E3F1254E0EDE}">
       <text>
         <r>
           <rPr>
@@ -11774,7 +11748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I549" authorId="0" shapeId="0" xr:uid="{874D3025-0707-F04B-A98D-8D7912444396}">
+    <comment ref="I549" authorId="0" shapeId="0" xr:uid="{98AE239D-CCF2-3E4E-B350-E3B7BB187FAE}">
       <text>
         <r>
           <rPr>
@@ -11789,7 +11763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I550" authorId="0" shapeId="0" xr:uid="{D439E06D-D2FC-4A44-A179-20D191499BA5}">
+    <comment ref="I550" authorId="0" shapeId="0" xr:uid="{30EA3AA7-5EB9-4147-BB36-9FC196DD4B45}">
       <text>
         <r>
           <rPr>
@@ -11805,7 +11779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I551" authorId="0" shapeId="0" xr:uid="{71F279A9-91C4-2D4C-8561-A15083D394B6}">
+    <comment ref="I551" authorId="0" shapeId="0" xr:uid="{ED00C3E7-FAF3-544A-8509-AA1B3DF70DA5}">
       <text>
         <r>
           <rPr>
@@ -11821,7 +11795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I552" authorId="0" shapeId="0" xr:uid="{D61F443A-155A-AB4F-8373-7E913F97DC2E}">
+    <comment ref="I552" authorId="0" shapeId="0" xr:uid="{70742516-008E-6447-9C24-C908A070C2C5}">
       <text>
         <r>
           <rPr>
@@ -11850,7 +11824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I553" authorId="0" shapeId="0" xr:uid="{44049E61-5B78-9546-955B-236AA761BE1E}">
+    <comment ref="I553" authorId="0" shapeId="0" xr:uid="{173DFB88-C532-1D47-8C62-72ED582B4817}">
       <text>
         <r>
           <rPr>
@@ -11865,7 +11839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I554" authorId="0" shapeId="0" xr:uid="{2B5B5424-48B2-6748-B445-B1CA8A78863E}">
+    <comment ref="I554" authorId="0" shapeId="0" xr:uid="{EE6D733E-727D-E04E-B251-63B797A93B02}">
       <text>
         <r>
           <rPr>
@@ -11880,7 +11854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I555" authorId="0" shapeId="0" xr:uid="{FF4FA113-81E2-0249-9FCD-6A048BEDEE3C}">
+    <comment ref="I555" authorId="0" shapeId="0" xr:uid="{442C943C-934C-394D-A6A8-4692A7E5E321}">
       <text>
         <r>
           <rPr>
@@ -11897,7 +11871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I556" authorId="0" shapeId="0" xr:uid="{17BE3D0A-82DB-F644-A7F6-8180B191CADF}">
+    <comment ref="I556" authorId="0" shapeId="0" xr:uid="{1ED0F925-BC95-E843-BF7C-D0C68150AC25}">
       <text>
         <r>
           <rPr>
@@ -11916,7 +11890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I557" authorId="0" shapeId="0" xr:uid="{0CD404E0-8128-1243-BFB4-A4677B6618CD}">
+    <comment ref="I557" authorId="0" shapeId="0" xr:uid="{1F560C46-FBD0-C74C-BA9F-9DA9785F4D96}">
       <text>
         <r>
           <rPr>
@@ -11935,7 +11909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I558" authorId="0" shapeId="0" xr:uid="{14278096-6C01-B048-8A6B-FEDA80F72206}">
+    <comment ref="I558" authorId="0" shapeId="0" xr:uid="{E59A265E-CA2D-4849-B8DA-B9E6BD01C552}">
       <text>
         <r>
           <rPr>
@@ -11954,7 +11928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I559" authorId="0" shapeId="0" xr:uid="{A0CD808C-24DD-4849-A2B5-D2C221FFC95C}">
+    <comment ref="I559" authorId="0" shapeId="0" xr:uid="{943D3DD5-5E06-AC4D-BBB2-75F2506C4665}">
       <text>
         <r>
           <rPr>
@@ -11973,7 +11947,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I560" authorId="0" shapeId="0" xr:uid="{7898ED51-38B3-0147-BE75-2A99250A59CD}">
+    <comment ref="I560" authorId="0" shapeId="0" xr:uid="{E643AD35-FE5A-2742-B514-2D1436AD4F82}">
       <text>
         <r>
           <rPr>
@@ -11992,7 +11966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I561" authorId="0" shapeId="0" xr:uid="{DD75F448-176E-0742-A012-D5EEFA4BF4DB}">
+    <comment ref="I561" authorId="0" shapeId="0" xr:uid="{47EFDB7F-E7EB-654B-A9FB-2EA35CACEB53}">
       <text>
         <r>
           <rPr>
@@ -12007,7 +11981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I562" authorId="0" shapeId="0" xr:uid="{61635A94-8B33-A24D-A2B4-2670CF24D4DF}">
+    <comment ref="I562" authorId="0" shapeId="0" xr:uid="{B7679447-6566-3942-A842-B5E7739B590A}">
       <text>
         <r>
           <rPr>
@@ -12026,7 +12000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I563" authorId="0" shapeId="0" xr:uid="{58C8CBF1-9C27-0040-B0B6-DE1448D594CF}">
+    <comment ref="I563" authorId="0" shapeId="0" xr:uid="{5B3CDA61-2146-AE4F-9A90-06A1E712DAFF}">
       <text>
         <r>
           <rPr>
@@ -12043,7 +12017,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I564" authorId="0" shapeId="0" xr:uid="{7446774B-D39C-A841-938B-A43447A55C73}">
+    <comment ref="I564" authorId="0" shapeId="0" xr:uid="{37FE1A8D-2651-684F-9D36-7D4F235DE7A4}">
       <text>
         <r>
           <rPr>
@@ -12062,7 +12036,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I565" authorId="0" shapeId="0" xr:uid="{A9F246B3-773C-684D-86E3-4ABD1EF0540A}">
+    <comment ref="I565" authorId="0" shapeId="0" xr:uid="{B3388182-CDFE-5347-9379-0D36D0DABF5C}">
       <text>
         <r>
           <rPr>
@@ -12081,7 +12055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I566" authorId="0" shapeId="0" xr:uid="{BA9EDC49-62E4-5244-9BC7-29C35B8D5288}">
+    <comment ref="I566" authorId="0" shapeId="0" xr:uid="{D01456A0-B03D-EF46-9956-98E4249CE17A}">
       <text>
         <r>
           <rPr>
@@ -12099,7 +12073,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I567" authorId="0" shapeId="0" xr:uid="{F4402495-6D3A-B74D-8730-680BD54F2C0E}">
+    <comment ref="I567" authorId="0" shapeId="0" xr:uid="{DB6EA2BF-2915-4940-A528-BA1526A4E806}">
       <text>
         <r>
           <rPr>
@@ -12129,7 +12103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I568" authorId="0" shapeId="0" xr:uid="{903C28F0-550F-A846-8EB9-41B6CC13A6BF}">
+    <comment ref="I568" authorId="0" shapeId="0" xr:uid="{F96B0343-2AFF-B648-A45C-DB23A8DA3467}">
       <text>
         <r>
           <rPr>
@@ -12148,7 +12122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I569" authorId="0" shapeId="0" xr:uid="{E8ACC8C2-8756-3948-8BDF-2FDC564CF7E3}">
+    <comment ref="I569" authorId="0" shapeId="0" xr:uid="{0ACB2760-AB7B-EC4A-8081-AA804872F6D6}">
       <text>
         <r>
           <rPr>
@@ -12167,7 +12141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I570" authorId="0" shapeId="0" xr:uid="{36DAF9EC-0902-9341-AE06-2A64FC757EDD}">
+    <comment ref="I570" authorId="0" shapeId="0" xr:uid="{5F3CECDC-372A-9E47-833D-C04BF53BDA63}">
       <text>
         <r>
           <rPr>
@@ -12186,7 +12160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I571" authorId="0" shapeId="0" xr:uid="{C08D1A6D-395A-A64C-9B73-C7E7674DDEDA}">
+    <comment ref="I571" authorId="0" shapeId="0" xr:uid="{6F471997-7AE1-B44D-8ABC-F10FF8F10329}">
       <text>
         <r>
           <rPr>
@@ -12216,7 +12190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I572" authorId="0" shapeId="0" xr:uid="{CA3E5238-E27D-FB4A-A0F2-281524E027F0}">
+    <comment ref="I572" authorId="0" shapeId="0" xr:uid="{ADFFCDB4-D6AB-D24A-A92C-B1362428EAA4}">
       <text>
         <r>
           <rPr>
@@ -12232,7 +12206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I573" authorId="0" shapeId="0" xr:uid="{432B7F45-00B1-DE4B-B539-ADA2CC31DBBB}">
+    <comment ref="I573" authorId="0" shapeId="0" xr:uid="{4521ACD2-D1B6-6041-A053-5F3C51055FF6}">
       <text>
         <r>
           <rPr>
@@ -12251,7 +12225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I574" authorId="0" shapeId="0" xr:uid="{B30D1F27-13D9-FB4F-AD0C-0CC7B5439892}">
+    <comment ref="I574" authorId="0" shapeId="0" xr:uid="{2A5E6F22-FBF6-384D-9CEA-07F3EAB1F4D8}">
       <text>
         <r>
           <rPr>
@@ -12281,7 +12255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I575" authorId="0" shapeId="0" xr:uid="{BE602DC9-BEF2-9347-B8A1-463DBEFD33C3}">
+    <comment ref="I575" authorId="0" shapeId="0" xr:uid="{3C4C9EF6-73B0-E64C-AC12-116EAA9C5991}">
       <text>
         <r>
           <rPr>
@@ -12300,7 +12274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I576" authorId="0" shapeId="0" xr:uid="{88B1B0B9-5485-9A4E-91C8-3C09FBE88F5D}">
+    <comment ref="I576" authorId="0" shapeId="0" xr:uid="{AAF4DF6F-591F-334A-A470-F487CC22545D}">
       <text>
         <r>
           <rPr>
@@ -12316,7 +12290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I577" authorId="0" shapeId="0" xr:uid="{4A816C83-A057-234B-8E3C-0FD3236404EC}">
+    <comment ref="I577" authorId="0" shapeId="0" xr:uid="{3790ED83-1F94-0C42-AE1C-9A722C51D3BD}">
       <text>
         <r>
           <rPr>
@@ -12335,7 +12309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I578" authorId="0" shapeId="0" xr:uid="{08402326-FA3B-C042-801C-2C41FC142DDE}">
+    <comment ref="I578" authorId="0" shapeId="0" xr:uid="{288E6CDA-838A-964B-A242-A41D78816E13}">
       <text>
         <r>
           <rPr>
@@ -12365,7 +12339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I579" authorId="0" shapeId="0" xr:uid="{89D6D04A-C41D-DA44-AC12-4E42C6BE53F7}">
+    <comment ref="I579" authorId="0" shapeId="0" xr:uid="{B5A9C01E-A3EC-1049-8546-A7102EE80705}">
       <text>
         <r>
           <rPr>
@@ -12384,7 +12358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I580" authorId="0" shapeId="0" xr:uid="{21C27946-7171-3E4F-8AB0-E7034640B74F}">
+    <comment ref="I580" authorId="0" shapeId="0" xr:uid="{FFBFA3C8-49D8-9E41-9C10-2D796410D675}">
       <text>
         <r>
           <rPr>
@@ -12403,7 +12377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I581" authorId="0" shapeId="0" xr:uid="{C64F0D92-B5D3-E64D-8D30-16946C3BAA6F}">
+    <comment ref="I581" authorId="0" shapeId="0" xr:uid="{77E91C43-B875-FA41-B9B5-D51FB2A6ED55}">
       <text>
         <r>
           <rPr>
@@ -12422,7 +12396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I582" authorId="0" shapeId="0" xr:uid="{2A6AA9A8-A931-A14E-84AC-8CE98E79D812}">
+    <comment ref="I582" authorId="0" shapeId="0" xr:uid="{CB3A0473-848B-5D44-B67B-07F8E43B5E8D}">
       <text>
         <r>
           <rPr>
@@ -12441,7 +12415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I583" authorId="0" shapeId="0" xr:uid="{31C31942-F538-984C-A975-62A78585830E}">
+    <comment ref="I583" authorId="0" shapeId="0" xr:uid="{FBF18085-F259-4746-8C56-C6C1BB00D303}">
       <text>
         <r>
           <rPr>
@@ -12473,7 +12447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I584" authorId="0" shapeId="0" xr:uid="{A35F52E6-FDB3-6547-BE60-EBF3BB642C1B}">
+    <comment ref="I584" authorId="0" shapeId="0" xr:uid="{AAEA5F62-1074-7946-AE9D-4CD2923D0E95}">
       <text>
         <r>
           <rPr>
@@ -12490,7 +12464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I585" authorId="0" shapeId="0" xr:uid="{17878D83-07B5-0245-86DE-0E9B5A016066}">
+    <comment ref="I585" authorId="0" shapeId="0" xr:uid="{E320104D-1C98-1044-8761-4C45335C8B5C}">
       <text>
         <r>
           <rPr>
@@ -12520,7 +12494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I586" authorId="0" shapeId="0" xr:uid="{ED74EE8A-AF60-EC49-BB51-4BEB98BCA7EF}">
+    <comment ref="I586" authorId="0" shapeId="0" xr:uid="{F2862F75-2C5F-5045-9E4D-381DFD26664A}">
       <text>
         <r>
           <rPr>
@@ -12548,7 +12522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I587" authorId="0" shapeId="0" xr:uid="{66A0F166-FF36-4547-BA60-2BAA003AF1EC}">
+    <comment ref="I587" authorId="0" shapeId="0" xr:uid="{968440BD-8052-6E42-9D7C-33A30AAD7A0E}">
       <text>
         <r>
           <rPr>
@@ -12569,7 +12543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I588" authorId="0" shapeId="0" xr:uid="{16BA1152-D6A1-3441-954F-E62D5F6071CB}">
+    <comment ref="I588" authorId="0" shapeId="0" xr:uid="{19D37D28-5DE0-5045-8A1F-84C2984F414F}">
       <text>
         <r>
           <rPr>
@@ -12597,7 +12571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I589" authorId="0" shapeId="0" xr:uid="{D66497E2-1F79-3D40-B225-A13AEBA14471}">
+    <comment ref="I589" authorId="0" shapeId="0" xr:uid="{E6440A89-BC95-6B4D-88ED-0E6C5CDF9266}">
       <text>
         <r>
           <rPr>
@@ -12614,7 +12588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I590" authorId="0" shapeId="0" xr:uid="{5886FBF5-C07D-9E4C-A76C-6F1086C724BE}">
+    <comment ref="I590" authorId="0" shapeId="0" xr:uid="{8E9E1580-0A71-9E44-9E31-B78174F6675C}">
       <text>
         <r>
           <rPr>
@@ -12634,7 +12608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I591" authorId="0" shapeId="0" xr:uid="{39962BBC-CEBC-C547-9AA2-0C42B35E0854}">
+    <comment ref="I591" authorId="0" shapeId="0" xr:uid="{EF444A1F-C053-F24C-BC47-0D8BF1AFE40A}">
       <text>
         <r>
           <rPr>
@@ -12656,7 +12630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I592" authorId="0" shapeId="0" xr:uid="{09330405-396E-A248-8F3E-D35DA9B202A9}">
+    <comment ref="I592" authorId="0" shapeId="0" xr:uid="{71F1A8E0-2D2A-B648-B302-23F8660C94A1}">
       <text>
         <r>
           <rPr>
@@ -12673,7 +12647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I593" authorId="0" shapeId="0" xr:uid="{520F7532-198B-C446-9185-0564D588A84D}">
+    <comment ref="I593" authorId="0" shapeId="0" xr:uid="{6940373B-C801-0945-AD48-821426982E9F}">
       <text>
         <r>
           <rPr>
@@ -12689,7 +12663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I594" authorId="0" shapeId="0" xr:uid="{5D82BE74-9A8E-AC46-B0C8-C030CD91695D}">
+    <comment ref="I594" authorId="0" shapeId="0" xr:uid="{D79A3965-4A3F-BE46-8FCC-82A7B78F11B1}">
       <text>
         <r>
           <rPr>
@@ -12712,7 +12686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I595" authorId="0" shapeId="0" xr:uid="{2981B63A-3DC2-A745-806B-65AF231FEC4A}">
+    <comment ref="I595" authorId="0" shapeId="0" xr:uid="{EAD6E589-69AC-4240-BFB3-517628CAEBDB}">
       <text>
         <r>
           <rPr>
@@ -12743,7 +12717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I596" authorId="0" shapeId="0" xr:uid="{C2BF535A-A3AB-6142-87E2-0D947152E7FA}">
+    <comment ref="I596" authorId="0" shapeId="0" xr:uid="{4784C07E-ED8C-FD49-8F49-53CD85EF5E90}">
       <text>
         <r>
           <rPr>
@@ -12784,7 +12758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I597" authorId="0" shapeId="0" xr:uid="{23FF9160-D15A-B24C-AD75-4FF1D37E62FF}">
+    <comment ref="I597" authorId="0" shapeId="0" xr:uid="{1E8AC700-B7F3-4E41-81F2-6F6D58E5A14A}">
       <text>
         <r>
           <rPr>
@@ -12804,7 +12778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I598" authorId="0" shapeId="0" xr:uid="{686FB4FC-865E-674D-A854-B3279FB8159D}">
+    <comment ref="I598" authorId="0" shapeId="0" xr:uid="{EB87BEA1-FB3E-804A-BB7A-03B2E9009EB5}">
       <text>
         <r>
           <rPr>
@@ -12844,7 +12818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I599" authorId="0" shapeId="0" xr:uid="{B547E0DD-5893-DE45-8E1A-CD65D4CB5E09}">
+    <comment ref="I599" authorId="0" shapeId="0" xr:uid="{2517EDCC-2587-F540-A279-DA307066243C}">
       <text>
         <r>
           <rPr>
@@ -12884,7 +12858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I600" authorId="0" shapeId="0" xr:uid="{96C8E188-A2E6-5D4D-81CB-9550B50D982D}">
+    <comment ref="I600" authorId="0" shapeId="0" xr:uid="{45D7B568-A801-8B40-8590-62D5F712C15A}">
       <text>
         <r>
           <rPr>
@@ -12911,7 +12885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I601" authorId="0" shapeId="0" xr:uid="{31BD34EB-681F-8A4C-80B2-D9ABA91FF36F}">
+    <comment ref="I601" authorId="0" shapeId="0" xr:uid="{2FA14F1C-2445-BA4E-B53F-25136B44B47F}">
       <text>
         <r>
           <rPr>
@@ -12940,7 +12914,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I602" authorId="0" shapeId="0" xr:uid="{26DB159F-0452-864D-ACEF-DAEA461794CC}">
+    <comment ref="I602" authorId="0" shapeId="0" xr:uid="{A34B5555-CD0E-C242-8980-43D9B282708A}">
       <text>
         <r>
           <rPr>
@@ -12956,7 +12930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I603" authorId="0" shapeId="0" xr:uid="{EFCC04BC-1515-1148-88AE-E23BECF0700D}">
+    <comment ref="I603" authorId="0" shapeId="0" xr:uid="{64B62FDF-4D97-0B48-8AF2-503B3CD9519E}">
       <text>
         <r>
           <rPr>
@@ -12979,7 +12953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I604" authorId="0" shapeId="0" xr:uid="{13D2454C-6115-1549-B1B8-AE965ABC651C}">
+    <comment ref="I604" authorId="0" shapeId="0" xr:uid="{4EB7B056-BA30-2548-979C-AA23F224C8C2}">
       <text>
         <r>
           <rPr>
@@ -13004,7 +12978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I605" authorId="0" shapeId="0" xr:uid="{F236D4FB-6F06-6C4A-AA44-B5B36F54C2EA}">
+    <comment ref="I605" authorId="0" shapeId="0" xr:uid="{0D350000-4099-BB49-941D-4DF4F70BB078}">
       <text>
         <r>
           <rPr>
@@ -13036,7 +13010,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I606" authorId="0" shapeId="0" xr:uid="{DB9CD3AD-7730-5545-9740-1E33A73D0C5B}">
+    <comment ref="I606" authorId="0" shapeId="0" xr:uid="{2C1C355A-5442-AA43-898D-B75BC51E82A7}">
       <text>
         <r>
           <rPr>
@@ -13071,7 +13045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I607" authorId="0" shapeId="0" xr:uid="{277BDC98-6D4C-2D4D-A0E5-B8447A4E0EAB}">
+    <comment ref="I607" authorId="0" shapeId="0" xr:uid="{00411241-1EE4-E44B-9B92-A2DB1489D957}">
       <text>
         <r>
           <rPr>
@@ -13093,7 +13067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I608" authorId="0" shapeId="0" xr:uid="{7B7AA93C-4999-CC47-9033-987AAF33CC2E}">
+    <comment ref="I608" authorId="0" shapeId="0" xr:uid="{FDBBD43F-6E16-0344-910F-4AA09D7F0EE3}">
       <text>
         <r>
           <rPr>
@@ -13123,7 +13097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I609" authorId="0" shapeId="0" xr:uid="{A8164643-304F-A74E-B045-E4441049F0C7}">
+    <comment ref="I609" authorId="0" shapeId="0" xr:uid="{7A337FF5-364D-194B-8B62-24773E9C13EB}">
       <text>
         <r>
           <rPr>
@@ -13138,7 +13112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I610" authorId="0" shapeId="0" xr:uid="{25BB3796-5CF1-5A42-BCD3-0343193957EB}">
+    <comment ref="I610" authorId="0" shapeId="0" xr:uid="{0FDEA6B7-6903-2247-83B4-FB4E76D82EEB}">
       <text>
         <r>
           <rPr>
@@ -13166,7 +13140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I611" authorId="0" shapeId="0" xr:uid="{1FB1886F-5A6E-1548-AA79-7085D87325BB}">
+    <comment ref="I611" authorId="0" shapeId="0" xr:uid="{0806B639-3069-BD42-840B-29F3383D7603}">
       <text>
         <r>
           <rPr>
@@ -13187,7 +13161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I612" authorId="0" shapeId="0" xr:uid="{0E622974-E7CE-B74D-989D-D59C623915A5}">
+    <comment ref="I612" authorId="0" shapeId="0" xr:uid="{32C5A619-9863-2B4E-9565-A4BC142E1925}">
       <text>
         <r>
           <rPr>
@@ -13228,7 +13202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I613" authorId="0" shapeId="0" xr:uid="{0EC98399-2252-7749-896C-022AE027A958}">
+    <comment ref="I613" authorId="0" shapeId="0" xr:uid="{461868E8-0139-CE4B-AF32-9662B37D128E}">
       <text>
         <r>
           <rPr>
@@ -13269,7 +13243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I614" authorId="0" shapeId="0" xr:uid="{983A296A-F14E-6444-B01C-60B2401B8902}">
+    <comment ref="I614" authorId="0" shapeId="0" xr:uid="{0F5F9550-788C-6F41-8513-4D8AE9AF9F45}">
       <text>
         <r>
           <rPr>
@@ -13301,7 +13275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I615" authorId="0" shapeId="0" xr:uid="{C6ACAC23-2F43-E141-8049-080EC50F4A42}">
+    <comment ref="I615" authorId="0" shapeId="0" xr:uid="{8BB8B164-BE37-3946-8FEC-A419DD77AF5B}">
       <text>
         <r>
           <rPr>
@@ -13320,7 +13294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I616" authorId="0" shapeId="0" xr:uid="{710334E1-8286-1249-AB8D-A418A8F95CB6}">
+    <comment ref="I616" authorId="0" shapeId="0" xr:uid="{F3BBC2AE-7760-3B49-B544-3F8BEC1D0D09}">
       <text>
         <r>
           <rPr>
@@ -13336,7 +13310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I617" authorId="0" shapeId="0" xr:uid="{5D7CA182-3EFF-F445-9AF3-F070BCD1313B}">
+    <comment ref="I617" authorId="0" shapeId="0" xr:uid="{2F272782-1798-224C-8F60-66FB80A680B3}">
       <text>
         <r>
           <rPr>
@@ -13355,7 +13329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I618" authorId="0" shapeId="0" xr:uid="{67AC4783-1123-9049-9DC0-16B11A987838}">
+    <comment ref="I618" authorId="0" shapeId="0" xr:uid="{9482FA0E-5924-294B-95D0-2B70AE0B8851}">
       <text>
         <r>
           <rPr>
@@ -13394,7 +13368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I619" authorId="0" shapeId="0" xr:uid="{3B7EF804-A1CA-D549-A792-1839CEA1C9FC}">
+    <comment ref="I619" authorId="0" shapeId="0" xr:uid="{ABBB6E8F-9E58-2544-BFC9-7ED6FAC0FDFA}">
       <text>
         <r>
           <rPr>
@@ -13421,7 +13395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I620" authorId="0" shapeId="0" xr:uid="{20D87EF8-F519-5C40-A846-B55691CE5D67}">
+    <comment ref="I620" authorId="0" shapeId="0" xr:uid="{FDF87274-26B3-CA49-8F77-B383D8874A63}">
       <text>
         <r>
           <rPr>
@@ -13450,7 +13424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I621" authorId="0" shapeId="0" xr:uid="{73FE9198-C9CE-FA41-B87F-BF81464AF689}">
+    <comment ref="I621" authorId="0" shapeId="0" xr:uid="{DC70A93A-428F-9B4C-B79F-B7D4A0A8FC41}">
       <text>
         <r>
           <rPr>
@@ -13489,7 +13463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I622" authorId="0" shapeId="0" xr:uid="{6F87ED15-D57A-384D-8C9A-7B6430807389}">
+    <comment ref="I622" authorId="0" shapeId="0" xr:uid="{96F0A046-CD75-FE42-A383-03C0A4EF9695}">
       <text>
         <r>
           <rPr>
@@ -13516,7 +13490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I623" authorId="0" shapeId="0" xr:uid="{9452E8EA-E4DD-1F4F-AA82-54B6CAE36EE9}">
+    <comment ref="I623" authorId="0" shapeId="0" xr:uid="{C3D1B1B9-7C5E-334E-9FAB-2E93A804C6E9}">
       <text>
         <r>
           <rPr>
@@ -13543,7 +13517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I624" authorId="0" shapeId="0" xr:uid="{C9E906BB-EB08-8C47-8912-6921AC44E132}">
+    <comment ref="I624" authorId="0" shapeId="0" xr:uid="{293C648D-0FDD-C04F-B8E2-CD3F71429F2E}">
       <text>
         <r>
           <rPr>
@@ -13584,7 +13558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I625" authorId="0" shapeId="0" xr:uid="{2EEF9D5F-C3C1-DB4C-A013-8B08BD3D22A3}">
+    <comment ref="I625" authorId="0" shapeId="0" xr:uid="{4CA83747-10D8-7B4A-95C7-0B99AF35497A}">
       <text>
         <r>
           <rPr>
@@ -13625,7 +13599,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I626" authorId="0" shapeId="0" xr:uid="{EA980E7E-2587-874A-9D41-98EB57C19B7E}">
+    <comment ref="I626" authorId="0" shapeId="0" xr:uid="{2EA65996-D460-4F45-A673-B18720E4D172}">
       <text>
         <r>
           <rPr>
@@ -13648,7 +13622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I627" authorId="0" shapeId="0" xr:uid="{FA53D03B-057C-644D-8D75-65AD905B26AA}">
+    <comment ref="I627" authorId="0" shapeId="0" xr:uid="{5A45F404-2FC4-C64F-80A4-494E5C785FA8}">
       <text>
         <r>
           <rPr>
@@ -13675,7 +13649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I628" authorId="0" shapeId="0" xr:uid="{766733FA-82C2-5C43-A5C1-4E2FCBD01870}">
+    <comment ref="I628" authorId="0" shapeId="0" xr:uid="{F70D278D-B2E3-AA40-996C-B2384258670E}">
       <text>
         <r>
           <rPr>
@@ -13702,7 +13676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I629" authorId="0" shapeId="0" xr:uid="{43F2E400-0676-7740-80CE-EC3A4EB2A9D6}">
+    <comment ref="I629" authorId="0" shapeId="0" xr:uid="{19A0F31A-4DAE-8741-9E7C-395E0DBE57F2}">
       <text>
         <r>
           <rPr>
@@ -13735,7 +13709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I630" authorId="0" shapeId="0" xr:uid="{570F715B-65D9-2140-9754-75523FC8DD6C}">
+    <comment ref="I630" authorId="0" shapeId="0" xr:uid="{E1303BD6-E300-484C-A2D5-21B65E28163D}">
       <text>
         <r>
           <rPr>
@@ -13754,7 +13728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I631" authorId="0" shapeId="0" xr:uid="{701849ED-D5DC-A748-AE2A-161C9246DC46}">
+    <comment ref="I631" authorId="0" shapeId="0" xr:uid="{21AD0DCD-B4AA-114E-8001-B21E1A59F0C0}">
       <text>
         <r>
           <rPr>
@@ -13790,7 +13764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I632" authorId="0" shapeId="0" xr:uid="{3C6A48A7-E57D-BB4E-9801-608E81DA930C}">
+    <comment ref="I632" authorId="0" shapeId="0" xr:uid="{DC6820F7-7373-AF4C-BCFD-4B2F894CC988}">
       <text>
         <r>
           <rPr>
@@ -13831,7 +13805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I633" authorId="0" shapeId="0" xr:uid="{E19605E3-77F1-4D43-A068-1A559986740D}">
+    <comment ref="I633" authorId="0" shapeId="0" xr:uid="{30FE8FB1-B686-5944-9C1B-9EFED8B7D227}">
       <text>
         <r>
           <rPr>
@@ -13863,7 +13837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I634" authorId="0" shapeId="0" xr:uid="{4211EEC8-3427-F440-B9E5-1E2EAF2B890C}">
+    <comment ref="I634" authorId="0" shapeId="0" xr:uid="{4B232623-C218-7442-ABAE-6D581F25CB7E}">
       <text>
         <r>
           <rPr>
@@ -13904,7 +13878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I635" authorId="0" shapeId="0" xr:uid="{39721C71-A384-BF45-95FA-9C9EA7B5FAC0}">
+    <comment ref="I635" authorId="0" shapeId="0" xr:uid="{65C92D37-182E-8949-A8BC-45C6FF125D42}">
       <text>
         <r>
           <rPr>
@@ -13945,7 +13919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I636" authorId="0" shapeId="0" xr:uid="{881F5E36-2D72-2F4B-BC02-AFD522821971}">
+    <comment ref="I636" authorId="0" shapeId="0" xr:uid="{A2CC5F39-D1BB-184F-927E-C89097662061}">
       <text>
         <r>
           <rPr>
@@ -13986,7 +13960,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I637" authorId="0" shapeId="0" xr:uid="{ED1361EA-7A2C-AB43-9BBA-22178F03141A}">
+    <comment ref="I637" authorId="0" shapeId="0" xr:uid="{F713FF56-7589-1642-81D4-15E6F6A2982E}">
       <text>
         <r>
           <rPr>
@@ -14018,7 +13992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I638" authorId="0" shapeId="0" xr:uid="{E2FFA344-4DBD-D244-8576-F00FBF5D733D}">
+    <comment ref="I638" authorId="0" shapeId="0" xr:uid="{F13D9A2E-6CB9-9241-B99F-900E03AC03EA}">
       <text>
         <r>
           <rPr>
@@ -14044,7 +14018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I639" authorId="0" shapeId="0" xr:uid="{BC53FD0D-AE0B-FE46-88D9-6D9445C962FB}">
+    <comment ref="I639" authorId="0" shapeId="0" xr:uid="{B34ABDEF-FAF5-1F4C-9A40-5107BE4D5610}">
       <text>
         <r>
           <rPr>
@@ -14077,7 +14051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I640" authorId="0" shapeId="0" xr:uid="{477FA2C5-2156-4641-9E20-721C990DAC70}">
+    <comment ref="I640" authorId="0" shapeId="0" xr:uid="{66699144-5F79-9444-97C1-45ADE2B54AF7}">
       <text>
         <r>
           <rPr>
@@ -14118,7 +14092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I641" authorId="0" shapeId="0" xr:uid="{20BB0B49-7C95-6247-9C98-929DD2A9A742}">
+    <comment ref="I641" authorId="0" shapeId="0" xr:uid="{1C6E6055-86EE-CF4C-9D43-54274EFA80D8}">
       <text>
         <r>
           <rPr>
@@ -14135,7 +14109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I642" authorId="0" shapeId="0" xr:uid="{32BA6181-A3BA-7F40-8C5B-6F2B4D0F476D}">
+    <comment ref="I642" authorId="0" shapeId="0" xr:uid="{AD4AE0CD-4B1A-734F-8D0A-3AFC1054D57F}">
       <text>
         <r>
           <rPr>
@@ -14165,7 +14139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I643" authorId="0" shapeId="0" xr:uid="{BB869905-0224-014E-910C-87CB2F2D6151}">
+    <comment ref="I643" authorId="0" shapeId="0" xr:uid="{825997A2-ECCB-5C43-BB20-10323461B67D}">
       <text>
         <r>
           <rPr>
@@ -14181,7 +14155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I644" authorId="0" shapeId="0" xr:uid="{7075EA8C-BA93-394B-B79A-C0EADE1115EB}">
+    <comment ref="I644" authorId="0" shapeId="0" xr:uid="{EBD53EF0-DA67-854F-BDA6-4A225355E422}">
       <text>
         <r>
           <rPr>
@@ -14202,7 +14176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I645" authorId="0" shapeId="0" xr:uid="{0F134B70-353D-FD43-B9C4-4C4DCBD558E0}">
+    <comment ref="I645" authorId="0" shapeId="0" xr:uid="{D490BA35-ED3D-3945-8C43-6C4A8C2724BD}">
       <text>
         <r>
           <rPr>
@@ -14219,7 +14193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I646" authorId="0" shapeId="0" xr:uid="{A761C2CF-0E0B-1F45-8589-F92DAF02541B}">
+    <comment ref="I646" authorId="0" shapeId="0" xr:uid="{E60E920A-F4EB-B44D-819A-E08C0385FA87}">
       <text>
         <r>
           <rPr>
@@ -14247,7 +14221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I647" authorId="0" shapeId="0" xr:uid="{BB18D1F4-C8D1-D04B-A634-3ABDB9E86C59}">
+    <comment ref="I647" authorId="0" shapeId="0" xr:uid="{F0822DFB-16AF-3B4D-96D5-A19AFF523242}">
       <text>
         <r>
           <rPr>
@@ -14275,7 +14249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I648" authorId="0" shapeId="0" xr:uid="{11D0894E-2A64-644D-A6C3-602B54505CB8}">
+    <comment ref="I648" authorId="0" shapeId="0" xr:uid="{721F986B-F1A2-434B-9BC1-4EF5C980A03A}">
       <text>
         <r>
           <rPr>
@@ -14292,7 +14266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I649" authorId="0" shapeId="0" xr:uid="{EBDB1BE5-EEF5-3742-ACE1-12B506DCDD49}">
+    <comment ref="I649" authorId="0" shapeId="0" xr:uid="{598B31EF-50A4-C346-8435-A3901F80FA71}">
       <text>
         <r>
           <rPr>
@@ -14307,7 +14281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I650" authorId="0" shapeId="0" xr:uid="{2EEB9C26-DF52-354A-9765-057EAF5B99A8}">
+    <comment ref="I650" authorId="0" shapeId="0" xr:uid="{D0518BBE-46A3-1240-BEC0-7ABA8A889C12}">
       <text>
         <r>
           <rPr>
@@ -14327,7 +14301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I651" authorId="0" shapeId="0" xr:uid="{9D2C7DA8-FCC7-6842-844E-6442B8532E16}">
+    <comment ref="I651" authorId="0" shapeId="0" xr:uid="{DA3248A2-BEF4-464E-8155-91562A169E5A}">
       <text>
         <r>
           <rPr>
@@ -14349,7 +14323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I652" authorId="0" shapeId="0" xr:uid="{1A93EBC6-B0FD-E44E-8497-FCF131C05327}">
+    <comment ref="I652" authorId="0" shapeId="0" xr:uid="{3C1A971B-8833-D646-94D7-49E373AAE4FD}">
       <text>
         <r>
           <rPr>
@@ -14371,7 +14345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I653" authorId="0" shapeId="0" xr:uid="{FEA1924E-E195-114C-9C68-E627E92BBCA3}">
+    <comment ref="I653" authorId="0" shapeId="0" xr:uid="{667837CB-00A6-8049-9930-FA4D337A987F}">
       <text>
         <r>
           <rPr>
@@ -14387,7 +14361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I654" authorId="0" shapeId="0" xr:uid="{D0544D85-A2E8-264F-999A-DBFDCD8B02ED}">
+    <comment ref="I654" authorId="0" shapeId="0" xr:uid="{1F322E75-25D7-5C44-8714-F98FA1460211}">
       <text>
         <r>
           <rPr>
@@ -14403,7 +14377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I655" authorId="0" shapeId="0" xr:uid="{237909DC-D1AB-9246-88D0-588C63655658}">
+    <comment ref="I655" authorId="0" shapeId="0" xr:uid="{05F94E4A-3264-C24C-8037-5CCEA2921E85}">
       <text>
         <r>
           <rPr>
@@ -14421,7 +14395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I656" authorId="0" shapeId="0" xr:uid="{82652164-5C8B-F140-B74A-1F98F884EC2E}">
+    <comment ref="I656" authorId="0" shapeId="0" xr:uid="{E11A0F30-B35A-2646-9C72-D95720EE0184}">
       <text>
         <r>
           <rPr>
@@ -14437,7 +14411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I657" authorId="0" shapeId="0" xr:uid="{7ADBA39D-2C37-DD4C-87D5-41D3F4C0BD64}">
+    <comment ref="I657" authorId="0" shapeId="0" xr:uid="{48879DD9-E261-0944-878C-024C934FCCBB}">
       <text>
         <r>
           <rPr>
@@ -14455,7 +14429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I658" authorId="0" shapeId="0" xr:uid="{3A6C0413-E61A-4547-90B3-DAEC9A01B04F}">
+    <comment ref="I658" authorId="0" shapeId="0" xr:uid="{F9F0A5EE-17A0-344C-8A7A-71C715F13990}">
       <text>
         <r>
           <rPr>
@@ -14477,7 +14451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I659" authorId="0" shapeId="0" xr:uid="{31F63E9A-539E-064B-8B71-D6D15F1FDD3C}">
+    <comment ref="I659" authorId="0" shapeId="0" xr:uid="{76513C47-FD23-2A4B-94E5-56F62E35B5B1}">
       <text>
         <r>
           <rPr>
@@ -14501,7 +14475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I660" authorId="0" shapeId="0" xr:uid="{8BA525F3-E790-C541-8383-257364E1A701}">
+    <comment ref="I660" authorId="0" shapeId="0" xr:uid="{C9A7EFCF-2EAB-BE4E-BECC-18D288690078}">
       <text>
         <r>
           <rPr>
@@ -14519,7 +14493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I661" authorId="0" shapeId="0" xr:uid="{46474E5B-84AC-C048-9A4B-53DBCEF9FDEB}">
+    <comment ref="I661" authorId="0" shapeId="0" xr:uid="{6021F1C9-1DF0-874B-B0FB-47B5171EF5D0}">
       <text>
         <r>
           <rPr>
@@ -14543,7 +14517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I662" authorId="0" shapeId="0" xr:uid="{FC1ECBF8-2DD3-F244-A17A-2A7590389396}">
+    <comment ref="I662" authorId="0" shapeId="0" xr:uid="{81548D95-D776-5D4F-90E4-2620FB301FC9}">
       <text>
         <r>
           <rPr>
@@ -14559,7 +14533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I663" authorId="0" shapeId="0" xr:uid="{A4C66D65-A816-B84F-B6C4-D607B3B1BA06}">
+    <comment ref="I663" authorId="0" shapeId="0" xr:uid="{A1D547E4-CD94-B243-8C92-847D580207D2}">
       <text>
         <r>
           <rPr>
@@ -14575,7 +14549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I664" authorId="0" shapeId="0" xr:uid="{CD0D63CF-6382-4B49-A0D9-35A866BF41D5}">
+    <comment ref="I664" authorId="0" shapeId="0" xr:uid="{A497505F-98B6-4048-8598-A533B0987F8E}">
       <text>
         <r>
           <rPr>
@@ -14591,7 +14565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I665" authorId="0" shapeId="0" xr:uid="{86BFBFCB-CD3F-CC4F-94C0-AA57FDBFCE85}">
+    <comment ref="I665" authorId="0" shapeId="0" xr:uid="{EFCE30FD-0CAB-A34D-B1C0-155583CF1FC6}">
       <text>
         <r>
           <rPr>
@@ -14607,7 +14581,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I666" authorId="0" shapeId="0" xr:uid="{23C6FE18-DE50-D84E-A8A0-F18E0F6A942E}">
+    <comment ref="I666" authorId="0" shapeId="0" xr:uid="{6FBD262C-5353-E34D-92C4-87A3A8860333}">
       <text>
         <r>
           <rPr>
@@ -14636,7 +14610,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I667" authorId="0" shapeId="0" xr:uid="{3606F3EF-ACA6-D14E-A924-3D1CC257BB77}">
+    <comment ref="I667" authorId="0" shapeId="0" xr:uid="{62B8CDD3-F243-7648-A889-AC3AD323C872}">
       <text>
         <r>
           <rPr>
@@ -14653,7 +14627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I668" authorId="0" shapeId="0" xr:uid="{B6835CE5-55D6-F54E-8E16-C19CC3A171F8}">
+    <comment ref="I668" authorId="0" shapeId="0" xr:uid="{C0F23E04-D436-EE48-BC5B-0D6FC0DC8998}">
       <text>
         <r>
           <rPr>
@@ -14668,7 +14642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I669" authorId="0" shapeId="0" xr:uid="{7A995559-FC5B-C747-9F08-C92FFE18AE81}">
+    <comment ref="I669" authorId="0" shapeId="0" xr:uid="{5CD3955C-53BF-5845-A2D6-3DDD3B1E7104}">
       <text>
         <r>
           <rPr>
@@ -14683,7 +14657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I670" authorId="0" shapeId="0" xr:uid="{DD8A15B9-749D-AE43-8FF6-4D13CDA32B23}">
+    <comment ref="I670" authorId="0" shapeId="0" xr:uid="{FE4889DA-E4C8-A143-8D80-ED4C69E16D40}">
       <text>
         <r>
           <rPr>
@@ -14699,7 +14673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I671" authorId="0" shapeId="0" xr:uid="{99E93C0A-9C38-7B44-A0D9-1BDF6CCD24EF}">
+    <comment ref="I671" authorId="0" shapeId="0" xr:uid="{96308C31-79A3-DF47-9A0F-99AEB6461011}">
       <text>
         <r>
           <rPr>
@@ -14728,7 +14702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I672" authorId="0" shapeId="0" xr:uid="{7BABFBAE-E8B2-D44D-B62E-E5B7CF10748C}">
+    <comment ref="I672" authorId="0" shapeId="0" xr:uid="{19ED4D91-CE34-D042-9D36-BB6950BB063A}">
       <text>
         <r>
           <rPr>
@@ -14757,7 +14731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I673" authorId="0" shapeId="0" xr:uid="{3B32DAEC-3AA2-B448-9F6B-FBCBDC9E7913}">
+    <comment ref="I673" authorId="0" shapeId="0" xr:uid="{593E2B8C-61EE-7C44-AB75-67449A6F3B8B}">
       <text>
         <r>
           <rPr>
@@ -14781,7 +14755,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I674" authorId="0" shapeId="0" xr:uid="{01CDDD1D-8AD4-7A43-8E08-4F7A3043E822}">
+    <comment ref="I674" authorId="0" shapeId="0" xr:uid="{A8936223-D9AF-464F-997F-9CA75B5FA165}">
       <text>
         <r>
           <rPr>
@@ -14798,7 +14772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I675" authorId="0" shapeId="0" xr:uid="{D2A697AF-96E7-0541-80F4-36B527E9917E}">
+    <comment ref="I675" authorId="0" shapeId="0" xr:uid="{0F1BC628-A67B-604E-AEAE-5649DB7DC2E6}">
       <text>
         <r>
           <rPr>
@@ -14827,7 +14801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I676" authorId="0" shapeId="0" xr:uid="{1BEAE932-5ECD-C44F-A9F9-124AB027B20E}">
+    <comment ref="I676" authorId="0" shapeId="0" xr:uid="{A99DD91D-77CA-5A45-9766-6009AA9B02D9}">
       <text>
         <r>
           <rPr>
@@ -14863,7 +14837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I677" authorId="0" shapeId="0" xr:uid="{3C67899E-3A76-6E4A-B70B-AEE008A0D37F}">
+    <comment ref="I677" authorId="0" shapeId="0" xr:uid="{609D9485-6D0C-4549-B501-669A8BAF5F6B}">
       <text>
         <r>
           <rPr>
@@ -14898,7 +14872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I678" authorId="0" shapeId="0" xr:uid="{FCB50A92-44B2-424B-9DB5-D696B533495A}">
+    <comment ref="I678" authorId="0" shapeId="0" xr:uid="{36AF581A-888A-6749-BB0C-86D1391B8F6E}">
       <text>
         <r>
           <rPr>
@@ -14913,7 +14887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I679" authorId="0" shapeId="0" xr:uid="{DA647732-AEA0-8541-9988-871049975F25}">
+    <comment ref="I679" authorId="0" shapeId="0" xr:uid="{4324CB11-B7D1-BD40-B34E-21EB6E2BE043}">
       <text>
         <r>
           <rPr>
@@ -14931,7 +14905,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I680" authorId="0" shapeId="0" xr:uid="{B207843F-C069-0B4E-8C3E-0FCD1801FF40}">
+    <comment ref="I680" authorId="0" shapeId="0" xr:uid="{16705C22-A435-F442-A73E-AB842662D267}">
       <text>
         <r>
           <rPr>
@@ -14946,7 +14920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I681" authorId="0" shapeId="0" xr:uid="{0D1C082E-F066-8348-8A65-0E623C14442E}">
+    <comment ref="I681" authorId="0" shapeId="0" xr:uid="{3EC668F5-1825-A440-B9B7-21B8753E6820}">
       <text>
         <r>
           <rPr>
@@ -14964,7 +14938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I682" authorId="0" shapeId="0" xr:uid="{1CD47A58-0A9C-4D48-B13A-B1186744BA91}">
+    <comment ref="I682" authorId="0" shapeId="0" xr:uid="{E691800A-181E-8D42-AC42-5E9291CCEC5F}">
       <text>
         <r>
           <rPr>
@@ -14981,7 +14955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I683" authorId="0" shapeId="0" xr:uid="{8447B169-F392-6D44-97BD-74B81AC8E5B5}">
+    <comment ref="I683" authorId="0" shapeId="0" xr:uid="{DBE2D4DA-7374-6B4F-B6CA-338184323422}">
       <text>
         <r>
           <rPr>
@@ -14997,7 +14971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I684" authorId="0" shapeId="0" xr:uid="{5C03A259-2BAB-E345-A620-163826C85B53}">
+    <comment ref="I684" authorId="0" shapeId="0" xr:uid="{C668D76D-7E03-284A-AA5B-0504634620BA}">
       <text>
         <r>
           <rPr>
@@ -15013,7 +14987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I685" authorId="0" shapeId="0" xr:uid="{B69B8EC8-5BF3-D246-B989-CE355D8FF9F3}">
+    <comment ref="I685" authorId="0" shapeId="0" xr:uid="{A02A340B-2BC8-314C-A47F-692CB9119C15}">
       <text>
         <r>
           <rPr>
@@ -15029,7 +15003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I686" authorId="0" shapeId="0" xr:uid="{6A47F435-B5CC-934A-B627-7866C5F90E49}">
+    <comment ref="I686" authorId="0" shapeId="0" xr:uid="{3BD0AE8E-789F-6843-BEBD-7A7B6D5B92B3}">
       <text>
         <r>
           <rPr>
@@ -15049,7 +15023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I687" authorId="0" shapeId="0" xr:uid="{FD9FAA42-22F3-0244-A57A-85FBEC4C7328}">
+    <comment ref="I687" authorId="0" shapeId="0" xr:uid="{FFFAC09A-752B-7247-890F-2AC667FE43E0}">
       <text>
         <r>
           <rPr>
@@ -15067,7 +15041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I688" authorId="0" shapeId="0" xr:uid="{D3995A77-1FD9-6B44-838C-E30FED575BB1}">
+    <comment ref="I688" authorId="0" shapeId="0" xr:uid="{AC2F752E-197F-1C42-87D5-716F5F0C1EF7}">
       <text>
         <r>
           <rPr>
@@ -15084,7 +15058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I689" authorId="0" shapeId="0" xr:uid="{1B927980-DE54-5240-A023-DF5C3001E92C}">
+    <comment ref="I689" authorId="0" shapeId="0" xr:uid="{E1D90A9D-9D62-424B-AB01-3C5E9057FB30}">
       <text>
         <r>
           <rPr>
@@ -15098,7 +15072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I690" authorId="0" shapeId="0" xr:uid="{6CCFD22A-86B2-1E4F-BBDE-FDE2494F6A2C}">
+    <comment ref="I690" authorId="0" shapeId="0" xr:uid="{3B81BBB1-D737-CE4B-8497-1A03B8BB7773}">
       <text>
         <r>
           <rPr>
@@ -15116,7 +15090,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I691" authorId="0" shapeId="0" xr:uid="{11ABFCA2-2F31-1F4C-958B-D2EEED6C027A}">
+    <comment ref="I691" authorId="0" shapeId="0" xr:uid="{D83B6257-2631-7448-ACAF-A118C9E00B6A}">
       <text>
         <r>
           <rPr>
@@ -15134,7 +15108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I692" authorId="0" shapeId="0" xr:uid="{6DDD2BE0-E23F-B940-BCC0-1AFB87FBEDA7}">
+    <comment ref="I692" authorId="0" shapeId="0" xr:uid="{7F7906A4-9FBB-8E4C-BAD3-27363A2296A8}">
       <text>
         <r>
           <rPr>
@@ -15152,7 +15126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I693" authorId="0" shapeId="0" xr:uid="{6E2E78D3-A4D3-FE47-87CE-C4E25B409A91}">
+    <comment ref="I693" authorId="0" shapeId="0" xr:uid="{8E21FE6D-3830-1C4D-B6ED-D3215CF4125C}">
       <text>
         <r>
           <rPr>
@@ -15172,7 +15146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I694" authorId="0" shapeId="0" xr:uid="{50B9023D-782E-9B46-AC26-2033432159F0}">
+    <comment ref="I694" authorId="0" shapeId="0" xr:uid="{98067023-D440-2A4A-BEC4-AA98EF4B0802}">
       <text>
         <r>
           <rPr>
@@ -15189,7 +15163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I695" authorId="0" shapeId="0" xr:uid="{0604CB0E-B8D8-B74B-8DD7-97296BF8C962}">
+    <comment ref="I695" authorId="0" shapeId="0" xr:uid="{1547D158-750A-5047-A151-03FB3BAA3C9F}">
       <text>
         <r>
           <rPr>
@@ -15206,7 +15180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I696" authorId="0" shapeId="0" xr:uid="{71F36FFB-AC31-A04D-A759-31D323CBBCBB}">
+    <comment ref="I696" authorId="0" shapeId="0" xr:uid="{6598E97F-71AE-B44D-96DA-E0EAC8951B6F}">
       <text>
         <r>
           <rPr>
@@ -15223,413 +15197,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="I697" authorId="0" shapeId="0" xr:uid="{6C4FCAA3-3AA0-BF42-A1B7-0FA10D9BD21A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>엘리자베스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>제인</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>코크런</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>주다온</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>에라스무스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>윌슨</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최민우</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>조지</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>매든</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>유성재</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>콜드웰</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>&amp;</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>공장부장</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>나현진</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>도로시</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>&amp;</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>에이프릴</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>시민지</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>밀라</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>임바로미</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>루나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>&amp;</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>소피아</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이준혁</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>넬</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I698" authorId="0" shapeId="0" xr:uid="{70DDE62C-5C47-634F-827F-83A24D43D3FF}">
+    <comment ref="I697" authorId="0" shapeId="0" xr:uid="{F24CA69C-2FE6-F649-9F6B-30446F2A6C28}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>엘리자베스 제인 코크런: 주다온
+에라스무스 윌슨: 최민우
+조지 매든: 유성재
+콜드웰&amp;공장부장: 나현진
+도로시&amp;에이프릴: 시민지
+밀라: 임바로미
+루나&amp;소피아: 이준혁(넬)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I698" authorId="0" shapeId="0" xr:uid="{03AFDD9F-7CB2-364B-A7EA-C7209B26AFFE}">
       <text>
         <r>
           <rPr>
@@ -15647,7 +15235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I699" authorId="0" shapeId="0" xr:uid="{221D3F93-CACC-AF4C-AEEC-E1CAA5A18790}">
+    <comment ref="I699" authorId="0" shapeId="0" xr:uid="{2A1D5D06-EB93-F640-AB02-A655AD0650FF}">
       <text>
         <r>
           <rPr>
@@ -15663,7 +15251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I700" authorId="0" shapeId="0" xr:uid="{AED1D80C-4B31-A94D-AAF9-7CB77CB87AFD}">
+    <comment ref="I700" authorId="0" shapeId="0" xr:uid="{A40BEFFC-0932-4F49-B2A4-E4C6DC2CAA24}">
       <text>
         <r>
           <rPr>
@@ -15681,7 +15269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I701" authorId="0" shapeId="0" xr:uid="{A7C70930-05F8-184E-B364-7C9C7AAA242D}">
+    <comment ref="I701" authorId="0" shapeId="0" xr:uid="{284CD4D3-A65C-9B4A-8E21-A0B27CDE2A32}">
       <text>
         <r>
           <rPr>
@@ -15700,7 +15288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I702" authorId="0" shapeId="0" xr:uid="{F70962D0-CA49-B44C-BF47-AF679AB8AFC8}">
+    <comment ref="I702" authorId="0" shapeId="0" xr:uid="{E9BD1A52-F4AE-C94F-9C50-1F4C23534391}">
       <text>
         <r>
           <rPr>
@@ -15715,7 +15303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I703" authorId="0" shapeId="0" xr:uid="{A221FF7C-4E46-1745-BDAA-297DE78F6BCB}">
+    <comment ref="I703" authorId="0" shapeId="0" xr:uid="{1342A30B-E119-F346-81AF-62B172657641}">
       <text>
         <r>
           <rPr>
@@ -15733,7 +15321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I704" authorId="0" shapeId="0" xr:uid="{FE7E6419-54F2-3D47-AEE8-59F0FD90AAB8}">
+    <comment ref="I704" authorId="0" shapeId="0" xr:uid="{2F1C49C9-878A-6B42-9BF0-4E2A9F914CAF}">
       <text>
         <r>
           <rPr>
@@ -15760,7 +15348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I705" authorId="0" shapeId="0" xr:uid="{AFE07691-DFD1-064E-8FAB-97F8A3798EE4}">
+    <comment ref="I705" authorId="0" shapeId="0" xr:uid="{D21F75B3-6D0C-7E4A-9CB7-A3600D311C75}">
       <text>
         <r>
           <rPr>
@@ -15776,7 +15364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I706" authorId="0" shapeId="0" xr:uid="{BD23C901-3D28-014D-B23E-FD16A6CFF900}">
+    <comment ref="I706" authorId="0" shapeId="0" xr:uid="{D9C1DFB2-6F74-6C47-9C9C-15B5254216C2}">
       <text>
         <r>
           <rPr>
@@ -15792,7 +15380,41 @@
         </r>
       </text>
     </comment>
-    <comment ref="I707" authorId="0" shapeId="0" xr:uid="{20D884D1-CE9A-E542-B90F-967E6C1E67D6}">
+    <comment ref="I707" authorId="0" shapeId="0" xr:uid="{87490B6D-FA6E-2049-8A05-BDE337D360DB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>제이크 스터디: 배수빈
+조이 스터디: 최석진
+로빈 디토나: 전익령
+트와일라 스터디: 김지혜
+라우디 에이커스: 허영손</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I708" authorId="0" shapeId="0" xr:uid="{602B9F1A-F7E3-BE49-9906-9E316CCCDD5E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>지나(지나이다 알렉산드로브나 자시에키나) : 최연우
+빅토르 세르게예비치 투르게네프: 조성윤
+이반 빅토로비치 투르게네프: 한상훈</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I709" authorId="0" shapeId="0" xr:uid="{48D81CDF-C251-8C40-8862-45935093F0C4}">
       <text>
         <r>
           <rPr>
@@ -15801,7 +15423,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>제이크</t>
+          <t>차미호</t>
         </r>
         <r>
           <rPr>
@@ -15810,7 +15432,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">: </t>
         </r>
         <r>
           <rPr>
@@ -15819,25 +15441,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>스터디</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>배수빈</t>
+          <t>이재림</t>
         </r>
         <r>
           <rPr>
@@ -15856,7 +15460,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>조이</t>
+          <t>차미</t>
         </r>
         <r>
           <rPr>
@@ -15865,7 +15469,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">: </t>
         </r>
         <r>
           <rPr>
@@ -15874,25 +15478,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>스터디</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최석진</t>
+          <t>정우연</t>
         </r>
         <r>
           <rPr>
@@ -15911,7 +15497,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>로빈</t>
+          <t>김고대</t>
         </r>
         <r>
           <rPr>
@@ -15920,7 +15506,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">: </t>
         </r>
         <r>
           <rPr>
@@ -15929,25 +15515,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>디토나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>전익령</t>
+          <t>정욱진</t>
         </r>
         <r>
           <rPr>
@@ -15966,7 +15534,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>트와일라</t>
+          <t>오진혁</t>
         </r>
         <r>
           <rPr>
@@ -15975,474 +15543,13 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> </t>
+          <t xml:space="preserve">: </t>
         </r>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>스터디</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>김지혜</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>라우디</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>에이커스</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>허영손</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I708" authorId="0" shapeId="0" xr:uid="{F449E6FF-3BF2-4C46-B1AA-7E3F0414B982}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>지나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>지나이다</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>알렉산드로브나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>자시에키나</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">) : </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>최연우</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>빅토르</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>세르게예비치</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>투르게네프</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>조성윤</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>이반</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>빅토로비치</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>투르게네프</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>한상훈</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I709" authorId="1" shapeId="0" xr:uid="{E8670081-ED86-B94B-A2C9-8D55C2D07149}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>차미호</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>이재림</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>차미</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>정우연</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>김고대</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>정욱진</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>오진혁</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t>김준영</t>
@@ -28396,7 +27503,7 @@
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28505,13 +27612,6 @@
       <name val="굴림"/>
       <family val="2"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5FA791-659F-6243-9CD7-BC9771FB8181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA02B66-1CF3-9D42-9B44-A9C30E81B1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -27082,9 +27082,6 @@
     <t>https://drive.google.com/file/d/1yx61mnhbjGZwIxiHTw68qFckk36i0zMI/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/16oBWleCgYIXTk069uDvfZR6tZoIY5QU3/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1cBL-9PLFLcQC2mwD8xYgeugPoAXVYEUd/view?usp=drive_link</t>
   </si>
   <si>
@@ -27286,9 +27283,6 @@
     <t>https://drive.google.com/file/d/1kgMiy6aRGbpac0leeuRxhAobFmDAgRd7/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1jrkRLngtbf3s-U2FoLlCx4hoADKKngg2/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1x0YYEIc41ztm-KX1SglVlR1NsNg_pMLS/view?usp=drive_link</t>
   </si>
   <si>
@@ -27301,15 +27295,9 @@
     <t>https://drive.google.com/file/d/1gCZIiauDZpJLFHTPYgz1_HF4NO-hINSk/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1j50C5WoxyV4_bG5gIrhY0qagbD8rss-s/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1b2T_YNRAmtFBGvwjLTVPdDS_yN7BoyFd/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1uE5fFdwVD77OTNs2j5RBv68SQFpd34Vc/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1rdx4Vw6sGPNEjdWVKTKpmJdpNe9Gngd8/view?usp=drive_link</t>
   </si>
   <si>
@@ -27337,18 +27325,9 @@
     <t>https://drive.google.com/file/d/1Ud6dOpl52ARt56zGNHvGYXtfbLKZhmoW/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1e4fGA8bM7usagPS0cr7LsCD8yJQyMB4D/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1DDRd2uovkbNiPyQoLfynrrA-YRzAEf1C/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1dFW5A_2WGxHc_3kCj6I_H-ZfpGnYfDo9/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1wTiBPaS2lTmHRgMrhBoF28VZfZfixTVn/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1uKpyfDlJTXLC1WXt9IiBWttsnOaDDkFY/view?usp=drive_link</t>
   </si>
   <si>
@@ -27358,21 +27337,9 @@
     <t>https://drive.google.com/file/d/1xSF3yozEodINi6QUH10uq9Ju7U0BSvCl/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1zgqgIQ2sq28ReR8A3LcFBCrB0ntDUI32/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/17sFcLh_gTrO5oO8nV9k8r8iIegNbvJhy/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1jvFboWV2a8Gd6g2Uxm65wr9STRkDRY9G/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1L2YDgYqVVYKZ9cba75WGFiQJc6fvmeOD/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1iKC_YTupFtvPcB6wVHkL1YqYY7e0XtHa/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1PR6BFFvnFBIfXOLVyRUTPmZpXkR6lUJz/view?usp=drive_link</t>
   </si>
   <si>
@@ -27391,24 +27358,12 @@
     <t>https://drive.google.com/file/d/11RrUe6EJsWra1Upt8rzadkkbKreIKgqR/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1FRKMmXEwehuPphcwJJ3SxBSAZOSKGcp4/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1ew-ZN3-HH_tZK22KnAukbcvE6hMdWdJu/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1kUpl-DGu644QYO-3uXeEcCIdX3Aln0Lr/view?usp=drive_link</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1KzbL5NVj3X-4T2so262NbZ8Ee01ieFQh/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1YFauelyEhpBYbtwVO772JuCdj_LFkHtb/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Zazo2OYT55F6dzIorr5xh-xmNbcWltAI/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1mPfhRtn4Z8rk7HteERSZneUer11_z5-Y/view?usp=drive_link</t>
   </si>
   <si>
@@ -27421,9 +27376,6 @@
     <t>https://drive.google.com/file/d/1StQRGZyGNEdj2Muvf0AC5w5-8UPpG_JH/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1668r6A526tXELxab3thESeg3I1IAQbYK/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/11_fuazd_g1kWo1my8DOq3jLtNT-gLwk9/view?usp=drive_link</t>
   </si>
   <si>
@@ -27475,9 +27427,6 @@
     <t>https://m.dcinside.com/mini/musicalplay/257489</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1V3GzyFMWcIbzp_vsYdcramyiG5DuhSSl/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://blog.naver.com/playnmu/223909211648</t>
   </si>
   <si>
@@ -27487,9 +27436,6 @@
     <t>https://docs.google.com/document/d/151p6Aup0qZki6hvL_E73D-XKB7jHAqBNW0_aKy_5m9w/edit?tab=t.0#heading=h.w1scvyj1ovhr</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1OJGv2IED-NzNkIASfP9G-3dWfR2G56P2/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>https://m.dcinside.com/mini/musicalplay/258400</t>
   </si>
   <si>
@@ -27542,6 +27488,60 @@
   </si>
   <si>
     <t>https://blog.naver.com/playnmu/223921039919</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IkWylIii7MSCs3xxXhanTzK1UElMBKlE/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mBSfZBovXTQdjPdSLLAW2xce7QLMmGNW/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15sf_PKkhq7VUtNqBpfvciAN1fzLln5m1/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/132twMn7s_5iA63BfO-gSDlDCJ3-fXx3f/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1U3oWRXnk5i6CijTQEf-d7ZST4uzBmowQ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1I4IgKxh03QVfjtWV-jIUUNqFoWxJS5Ei/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1b4_REOtKllPFwffUXF3RIyKxLAFYxP5-/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SITjfF3Zv5Kya5UIsN7lCZeP-EU3sI9X/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bLB-p5Upm7EcKpnj4WO9Fca5Q9YfkX0l/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tXUjcSCQaThJScvAy852rxKRhYhwbAUz/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jRKqXsOtiW4rYZrjSDjiBCSazNwKRq3c/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XCPAi48n7_lpfUeYKsEHKyU9BNE85lBV/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OQkV--t23aKrENnPux7PxcMghRx3zhPD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RtSuUhGI59BHqAKvZpHbwCzFdmZHMwUV/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Qs9RlTEFqiBaapG_vZ1VcYig2a0dqMrP/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pft4ssTWZWSc4NI0pcz-krzec4Ey_PSW/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_v8Tu2uzBP94E-X_ejwinwu5sBGKv-Zh/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pDx1tTLUdvzhnTuerVGaCRrHsvBuHdD0/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -27773,7 +27773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -27922,19 +27922,16 @@
     <xf numFmtId="166" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -29214,7 +29211,7 @@
         <v>1210</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>3977</v>
+        <v>3959</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>1211</v>
@@ -29223,7 +29220,7 @@
         <v>1212</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>3983</v>
+        <v>3965</v>
       </c>
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
@@ -29279,7 +29276,7 @@
         <v>16</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R2" s="12"/>
       <c r="T2" s="11"/>
@@ -29335,7 +29332,7 @@
         <v>16</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R3" s="12"/>
       <c r="T3" s="11"/>
@@ -29391,7 +29388,7 @@
         <v>2979</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R4" s="12"/>
       <c r="T4" s="11"/>
@@ -29447,7 +29444,7 @@
         <v>16</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R5" s="12"/>
       <c r="T5" s="11"/>
@@ -29503,7 +29500,7 @@
         <v>16</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R6" s="12"/>
       <c r="T6" s="11"/>
@@ -29559,7 +29556,7 @@
         <v>2980</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R7" s="12"/>
       <c r="T7" s="11"/>
@@ -29615,7 +29612,7 @@
         <v>2981</v>
       </c>
       <c r="Q8" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R8" s="12"/>
       <c r="T8" s="11"/>
@@ -29671,7 +29668,7 @@
         <v>2982</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R9" s="12"/>
       <c r="T9" s="11"/>
@@ -29727,7 +29724,7 @@
         <v>2983</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R10" s="12"/>
       <c r="T10" s="11"/>
@@ -29783,7 +29780,7 @@
         <v>2984</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R11" s="12"/>
       <c r="T11" s="11"/>
@@ -29839,7 +29836,7 @@
         <v>2985</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R12" s="12"/>
       <c r="T12" s="11"/>
@@ -29895,7 +29892,7 @@
         <v>2986</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R13" s="12"/>
       <c r="T13" s="11"/>
@@ -29951,7 +29948,7 @@
         <v>2987</v>
       </c>
       <c r="Q14" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R14" s="12"/>
       <c r="T14" s="11"/>
@@ -30007,7 +30004,7 @@
         <v>2988</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R15" s="12"/>
       <c r="T15" s="11"/>
@@ -30063,7 +30060,7 @@
         <v>2989</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R16" s="12"/>
       <c r="T16" s="11"/>
@@ -30119,7 +30116,7 @@
         <v>2990</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R17" s="12"/>
       <c r="T17" s="11"/>
@@ -30175,7 +30172,7 @@
         <v>2991</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R18" s="12"/>
       <c r="T18" s="11"/>
@@ -30231,7 +30228,7 @@
         <v>2992</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R19" s="12"/>
       <c r="T19" s="11"/>
@@ -30287,7 +30284,7 @@
         <v>16</v>
       </c>
       <c r="Q20" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R20" s="12"/>
       <c r="T20" s="11"/>
@@ -30343,7 +30340,7 @@
         <v>16</v>
       </c>
       <c r="Q21" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R21" s="12"/>
       <c r="T21" s="11"/>
@@ -30399,7 +30396,7 @@
         <v>16</v>
       </c>
       <c r="Q22" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R22" s="12"/>
       <c r="T22" s="11"/>
@@ -30455,7 +30452,7 @@
         <v>16</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R23" s="12"/>
       <c r="T23" s="11"/>
@@ -30511,7 +30508,7 @@
         <v>16</v>
       </c>
       <c r="Q24" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R24" s="12"/>
       <c r="T24" s="11"/>
@@ -30567,7 +30564,7 @@
         <v>16</v>
       </c>
       <c r="Q25" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R25" s="12"/>
       <c r="T25" s="11"/>
@@ -30623,7 +30620,7 @@
         <v>16</v>
       </c>
       <c r="Q26" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R26" s="12"/>
       <c r="T26" s="11"/>
@@ -30679,7 +30676,7 @@
         <v>16</v>
       </c>
       <c r="Q27" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R27" s="12"/>
       <c r="T27" s="11"/>
@@ -30735,7 +30732,7 @@
         <v>3001</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R28" s="12"/>
       <c r="T28" s="11"/>
@@ -30791,7 +30788,7 @@
         <v>16</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R29" s="12"/>
       <c r="T29" s="11"/>
@@ -30847,7 +30844,7 @@
         <v>3003</v>
       </c>
       <c r="Q30" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R30" s="12"/>
       <c r="T30" s="11"/>
@@ -30903,7 +30900,7 @@
         <v>3004</v>
       </c>
       <c r="Q31" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R31" s="12"/>
       <c r="T31" s="11"/>
@@ -30959,7 +30956,7 @@
         <v>16</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R32" s="12"/>
       <c r="T32" s="11"/>
@@ -31015,7 +31012,7 @@
         <v>16</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R33" s="12"/>
       <c r="T33" s="11"/>
@@ -31071,7 +31068,7 @@
         <v>3007</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R34" s="12"/>
       <c r="T34" s="11"/>
@@ -31127,7 +31124,7 @@
         <v>16</v>
       </c>
       <c r="Q35" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R35" s="12"/>
       <c r="T35" s="11"/>
@@ -31183,7 +31180,7 @@
         <v>3009</v>
       </c>
       <c r="Q36" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R36" s="12"/>
       <c r="T36" s="11"/>
@@ -31239,7 +31236,7 @@
         <v>16</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R37" s="12"/>
       <c r="T37" s="11"/>
@@ -31295,7 +31292,7 @@
         <v>3011</v>
       </c>
       <c r="Q38" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R38" s="12"/>
       <c r="T38" s="11"/>
@@ -31351,7 +31348,7 @@
         <v>16</v>
       </c>
       <c r="Q39" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R39" s="12"/>
       <c r="T39" s="11"/>
@@ -31407,7 +31404,7 @@
         <v>16</v>
       </c>
       <c r="Q40" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R40" s="12"/>
       <c r="T40" s="11"/>
@@ -31463,7 +31460,7 @@
         <v>3014</v>
       </c>
       <c r="Q41" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R41" s="12"/>
       <c r="T41" s="11"/>
@@ -31519,7 +31516,7 @@
         <v>16</v>
       </c>
       <c r="Q42" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R42" s="12"/>
       <c r="T42" s="11"/>
@@ -31575,7 +31572,7 @@
         <v>16</v>
       </c>
       <c r="Q43" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R43" s="12"/>
       <c r="T43" s="11"/>
@@ -31631,7 +31628,7 @@
         <v>16</v>
       </c>
       <c r="Q44" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R44" s="12"/>
       <c r="T44" s="11"/>
@@ -31663,7 +31660,7 @@
         <v>824</v>
       </c>
       <c r="I45" s="26" t="s">
-        <v>3964</v>
+        <v>3948</v>
       </c>
       <c r="J45" s="41">
         <v>71000</v>
@@ -31687,7 +31684,7 @@
         <v>3018</v>
       </c>
       <c r="Q45" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R45" s="12"/>
       <c r="T45" s="11"/>
@@ -31743,7 +31740,7 @@
         <v>3019</v>
       </c>
       <c r="Q46" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R46" s="12"/>
       <c r="T46" s="11"/>
@@ -31799,7 +31796,7 @@
         <v>16</v>
       </c>
       <c r="Q47" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R47" s="12"/>
       <c r="T47" s="11"/>
@@ -31855,7 +31852,7 @@
         <v>16</v>
       </c>
       <c r="Q48" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R48" s="12"/>
       <c r="T48" s="11"/>
@@ -31911,7 +31908,7 @@
         <v>3022</v>
       </c>
       <c r="Q49" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R49" s="12"/>
       <c r="T49" s="11"/>
@@ -31943,7 +31940,7 @@
         <v>825</v>
       </c>
       <c r="I50" s="26" t="s">
-        <v>3965</v>
+        <v>3949</v>
       </c>
       <c r="J50" s="41">
         <v>44000</v>
@@ -31967,7 +31964,7 @@
         <v>3023</v>
       </c>
       <c r="Q50" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R50" s="12"/>
       <c r="T50" s="11"/>
@@ -32023,7 +32020,7 @@
         <v>16</v>
       </c>
       <c r="Q51" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R51" s="12"/>
       <c r="T51" s="11"/>
@@ -32079,7 +32076,7 @@
         <v>16</v>
       </c>
       <c r="Q52" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R52" s="12"/>
       <c r="T52" s="11"/>
@@ -32135,7 +32132,7 @@
         <v>16</v>
       </c>
       <c r="Q53" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R53" s="12"/>
       <c r="T53" s="11"/>
@@ -32191,7 +32188,7 @@
         <v>16</v>
       </c>
       <c r="Q54" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R54" s="12"/>
       <c r="T54" s="11"/>
@@ -32247,7 +32244,7 @@
         <v>16</v>
       </c>
       <c r="Q55" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R55" s="12"/>
       <c r="T55" s="11"/>
@@ -32303,7 +32300,7 @@
         <v>16</v>
       </c>
       <c r="Q56" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R56" s="12"/>
       <c r="T56" s="11"/>
@@ -32359,7 +32356,7 @@
         <v>3029</v>
       </c>
       <c r="Q57" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R57" s="12"/>
       <c r="T57" s="11"/>
@@ -32415,7 +32412,7 @@
         <v>16</v>
       </c>
       <c r="Q58" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R58" s="12"/>
       <c r="T58" s="11"/>
@@ -32471,7 +32468,7 @@
         <v>16</v>
       </c>
       <c r="Q59" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R59" s="12"/>
       <c r="T59" s="11"/>
@@ -32527,7 +32524,7 @@
         <v>16</v>
       </c>
       <c r="Q60" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R60" s="12"/>
       <c r="T60" s="11"/>
@@ -32583,7 +32580,7 @@
         <v>16</v>
       </c>
       <c r="Q61" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R61" s="12"/>
       <c r="T61" s="11"/>
@@ -32639,7 +32636,7 @@
         <v>16</v>
       </c>
       <c r="Q62" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R62" s="12"/>
       <c r="T62" s="11"/>
@@ -32695,7 +32692,7 @@
         <v>16</v>
       </c>
       <c r="Q63" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R63" s="12"/>
       <c r="T63" s="11"/>
@@ -32751,7 +32748,7 @@
         <v>16</v>
       </c>
       <c r="Q64" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R64" s="12"/>
       <c r="T64" s="11"/>
@@ -32807,7 +32804,7 @@
         <v>16</v>
       </c>
       <c r="Q65" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R65" s="12"/>
       <c r="T65" s="11"/>
@@ -32863,7 +32860,7 @@
         <v>16</v>
       </c>
       <c r="Q66" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R66" s="12"/>
       <c r="T66" s="11"/>
@@ -32919,7 +32916,7 @@
         <v>16</v>
       </c>
       <c r="Q67" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R67" s="12"/>
       <c r="T67" s="11"/>
@@ -32975,7 +32972,7 @@
         <v>16</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R68" s="12"/>
       <c r="T68" s="11"/>
@@ -33031,7 +33028,7 @@
         <v>16</v>
       </c>
       <c r="Q69" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R69" s="12"/>
       <c r="T69" s="11"/>
@@ -33087,7 +33084,7 @@
         <v>3040</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R70" s="12"/>
       <c r="T70" s="11"/>
@@ -33143,7 +33140,7 @@
         <v>16</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R71" s="12"/>
       <c r="T71" s="11"/>
@@ -33199,7 +33196,7 @@
         <v>3042</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R72" s="12"/>
       <c r="T72" s="11"/>
@@ -33255,7 +33252,7 @@
         <v>16</v>
       </c>
       <c r="Q73" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R73" s="12"/>
       <c r="T73" s="11"/>
@@ -33311,7 +33308,7 @@
         <v>16</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R74" s="12"/>
       <c r="T74" s="11"/>
@@ -33367,7 +33364,7 @@
         <v>16</v>
       </c>
       <c r="Q75" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R75" s="12"/>
       <c r="T75" s="11"/>
@@ -33423,7 +33420,7 @@
         <v>16</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R76" s="12"/>
       <c r="T76" s="11"/>
@@ -33479,7 +33476,7 @@
         <v>3047</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R77" s="12"/>
       <c r="T77" s="11"/>
@@ -33535,7 +33532,7 @@
         <v>16</v>
       </c>
       <c r="Q78" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R78" s="12"/>
       <c r="T78" s="11"/>
@@ -33591,7 +33588,7 @@
         <v>16</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R79" s="12"/>
       <c r="T79" s="11"/>
@@ -33647,7 +33644,7 @@
         <v>16</v>
       </c>
       <c r="Q80" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R80" s="12"/>
       <c r="T80" s="11"/>
@@ -33703,7 +33700,7 @@
         <v>3051</v>
       </c>
       <c r="Q81" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R81" s="12"/>
       <c r="T81" s="11"/>
@@ -33735,7 +33732,7 @@
         <v>826</v>
       </c>
       <c r="I82" s="26" t="s">
-        <v>3966</v>
+        <v>3950</v>
       </c>
       <c r="J82" s="41">
         <v>61000</v>
@@ -33759,7 +33756,7 @@
         <v>3052</v>
       </c>
       <c r="Q82" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R82" s="12"/>
       <c r="T82" s="11"/>
@@ -33815,7 +33812,7 @@
         <v>16</v>
       </c>
       <c r="Q83" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R83" s="12"/>
       <c r="T83" s="11"/>
@@ -33871,7 +33868,7 @@
         <v>16</v>
       </c>
       <c r="Q84" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R84" s="12"/>
       <c r="T84" s="11"/>
@@ -33927,7 +33924,7 @@
         <v>16</v>
       </c>
       <c r="Q85" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R85" s="12"/>
       <c r="T85" s="11"/>
@@ -33983,7 +33980,7 @@
         <v>16</v>
       </c>
       <c r="Q86" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R86" s="12"/>
       <c r="T86" s="11"/>
@@ -34039,7 +34036,7 @@
         <v>16</v>
       </c>
       <c r="Q87" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R87" s="12"/>
       <c r="T87" s="11"/>
@@ -34095,7 +34092,7 @@
         <v>16</v>
       </c>
       <c r="Q88" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R88" s="12"/>
       <c r="T88" s="11"/>
@@ -34151,7 +34148,7 @@
         <v>16</v>
       </c>
       <c r="Q89" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R89" s="12"/>
       <c r="T89" s="11"/>
@@ -34207,7 +34204,7 @@
         <v>16</v>
       </c>
       <c r="Q90" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R90" s="12"/>
       <c r="T90" s="11"/>
@@ -34263,7 +34260,7 @@
         <v>16</v>
       </c>
       <c r="Q91" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R91" s="12"/>
       <c r="T91" s="11"/>
@@ -34319,7 +34316,7 @@
         <v>16</v>
       </c>
       <c r="Q92" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R92" s="12"/>
       <c r="T92" s="11"/>
@@ -34375,7 +34372,7 @@
         <v>16</v>
       </c>
       <c r="Q93" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R93" s="12"/>
       <c r="T93" s="11"/>
@@ -34431,7 +34428,7 @@
         <v>16</v>
       </c>
       <c r="Q94" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R94" s="12"/>
       <c r="T94" s="11"/>
@@ -34487,7 +34484,7 @@
         <v>3063</v>
       </c>
       <c r="Q95" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R95" s="12"/>
       <c r="T95" s="11"/>
@@ -34543,7 +34540,7 @@
         <v>16</v>
       </c>
       <c r="Q96" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R96" s="12"/>
       <c r="T96" s="11"/>
@@ -34599,7 +34596,7 @@
         <v>16</v>
       </c>
       <c r="Q97" s="20" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R97" s="12"/>
       <c r="T97" s="11"/>
@@ -34655,7 +34652,7 @@
         <v>16</v>
       </c>
       <c r="Q98" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R98" s="12"/>
       <c r="T98" s="11"/>
@@ -34711,7 +34708,7 @@
         <v>16</v>
       </c>
       <c r="Q99" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R99" s="12"/>
       <c r="T99" s="11"/>
@@ -34767,7 +34764,7 @@
         <v>16</v>
       </c>
       <c r="Q100" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R100" s="12"/>
       <c r="T100" s="11"/>
@@ -34823,7 +34820,7 @@
         <v>16</v>
       </c>
       <c r="Q101" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R101" s="12"/>
       <c r="T101" s="11"/>
@@ -34879,7 +34876,7 @@
         <v>16</v>
       </c>
       <c r="Q102" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R102" s="12"/>
       <c r="T102" s="11"/>
@@ -34935,7 +34932,7 @@
         <v>16</v>
       </c>
       <c r="Q103" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R103" s="12"/>
       <c r="T103" s="11"/>
@@ -34991,7 +34988,7 @@
         <v>16</v>
       </c>
       <c r="Q104" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R104" s="12"/>
       <c r="T104" s="11"/>
@@ -35047,7 +35044,7 @@
         <v>16</v>
       </c>
       <c r="Q105" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R105" s="12"/>
       <c r="T105" s="11"/>
@@ -35103,7 +35100,7 @@
         <v>16</v>
       </c>
       <c r="Q106" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R106" s="12"/>
       <c r="T106" s="11"/>
@@ -35159,7 +35156,7 @@
         <v>16</v>
       </c>
       <c r="Q107" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R107" s="12"/>
       <c r="T107" s="11"/>
@@ -35215,7 +35212,7 @@
         <v>16</v>
       </c>
       <c r="Q108" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R108" s="12"/>
       <c r="T108" s="11"/>
@@ -35271,7 +35268,7 @@
         <v>16</v>
       </c>
       <c r="Q109" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R109" s="12"/>
       <c r="T109" s="11"/>
@@ -35327,7 +35324,7 @@
         <v>16</v>
       </c>
       <c r="Q110" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R110" s="12"/>
       <c r="T110" s="11"/>
@@ -35383,7 +35380,7 @@
         <v>16</v>
       </c>
       <c r="Q111" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R111" s="12"/>
       <c r="T111" s="11"/>
@@ -35439,7 +35436,7 @@
         <v>16</v>
       </c>
       <c r="Q112" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R112" s="12"/>
       <c r="T112" s="11"/>
@@ -35495,7 +35492,7 @@
         <v>16</v>
       </c>
       <c r="Q113" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R113" s="12"/>
       <c r="T113" s="11"/>
@@ -35551,7 +35548,7 @@
         <v>16</v>
       </c>
       <c r="Q114" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R114" s="12"/>
       <c r="T114" s="11"/>
@@ -35607,7 +35604,7 @@
         <v>16</v>
       </c>
       <c r="Q115" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R115" s="12"/>
       <c r="T115" s="11"/>
@@ -35663,7 +35660,7 @@
         <v>16</v>
       </c>
       <c r="Q116" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R116" s="12"/>
       <c r="T116" s="11"/>
@@ -35719,7 +35716,7 @@
         <v>3085</v>
       </c>
       <c r="Q117" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R117" s="12"/>
       <c r="T117" s="11"/>
@@ -35775,7 +35772,7 @@
         <v>16</v>
       </c>
       <c r="Q118" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R118" s="12"/>
       <c r="T118" s="11"/>
@@ -35831,7 +35828,7 @@
         <v>3087</v>
       </c>
       <c r="Q119" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R119" s="12"/>
       <c r="T119" s="11"/>
@@ -35887,7 +35884,7 @@
         <v>16</v>
       </c>
       <c r="Q120" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R120" s="12"/>
       <c r="T120" s="11"/>
@@ -35943,7 +35940,7 @@
         <v>16</v>
       </c>
       <c r="Q121" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R121" s="12"/>
       <c r="T121" s="11"/>
@@ -35999,7 +35996,7 @@
         <v>16</v>
       </c>
       <c r="Q122" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R122" s="12"/>
       <c r="T122" s="11"/>
@@ -36055,7 +36052,7 @@
         <v>16</v>
       </c>
       <c r="Q123" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R123" s="12"/>
       <c r="T123" s="11"/>
@@ -36111,7 +36108,7 @@
         <v>16</v>
       </c>
       <c r="Q124" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R124" s="12"/>
       <c r="T124" s="11"/>
@@ -36167,7 +36164,7 @@
         <v>16</v>
       </c>
       <c r="Q125" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R125" s="12"/>
       <c r="T125" s="11"/>
@@ -36223,7 +36220,7 @@
         <v>3093</v>
       </c>
       <c r="Q126" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R126" s="12"/>
       <c r="T126" s="11"/>
@@ -36279,7 +36276,7 @@
         <v>16</v>
       </c>
       <c r="Q127" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R127" s="12"/>
       <c r="T127" s="11"/>
@@ -36335,7 +36332,7 @@
         <v>16</v>
       </c>
       <c r="Q128" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R128" s="12"/>
       <c r="T128" s="11"/>
@@ -36391,7 +36388,7 @@
         <v>16</v>
       </c>
       <c r="Q129" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R129" s="12"/>
       <c r="T129" s="11"/>
@@ -36447,7 +36444,7 @@
         <v>16</v>
       </c>
       <c r="Q130" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R130" s="12"/>
       <c r="T130" s="11"/>
@@ -36503,7 +36500,7 @@
         <v>16</v>
       </c>
       <c r="Q131" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R131" s="12"/>
       <c r="T131" s="11"/>
@@ -36559,7 +36556,7 @@
         <v>16</v>
       </c>
       <c r="Q132" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R132" s="12"/>
       <c r="T132" s="11"/>
@@ -36615,7 +36612,7 @@
         <v>16</v>
       </c>
       <c r="Q133" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R133" s="12"/>
       <c r="T133" s="11"/>
@@ -36671,7 +36668,7 @@
         <v>16</v>
       </c>
       <c r="Q134" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R134" s="12"/>
       <c r="T134" s="11"/>
@@ -36727,7 +36724,7 @@
         <v>16</v>
       </c>
       <c r="Q135" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R135" s="12"/>
       <c r="T135" s="11"/>
@@ -36783,7 +36780,7 @@
         <v>16</v>
       </c>
       <c r="Q136" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R136" s="12"/>
       <c r="T136" s="11"/>
@@ -36839,7 +36836,7 @@
         <v>3103</v>
       </c>
       <c r="Q137" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R137" s="12"/>
       <c r="T137" s="11"/>
@@ -36895,7 +36892,7 @@
         <v>16</v>
       </c>
       <c r="Q138" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R138" s="12"/>
       <c r="T138" s="11"/>
@@ -36951,7 +36948,7 @@
         <v>16</v>
       </c>
       <c r="Q139" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R139" s="12"/>
       <c r="T139" s="11"/>
@@ -37007,7 +37004,7 @@
         <v>16</v>
       </c>
       <c r="Q140" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R140" s="12"/>
       <c r="T140" s="11"/>
@@ -37063,7 +37060,7 @@
         <v>16</v>
       </c>
       <c r="Q141" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R141" s="12"/>
       <c r="T141" s="11"/>
@@ -37119,7 +37116,7 @@
         <v>16</v>
       </c>
       <c r="Q142" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R142" s="12"/>
       <c r="T142" s="11"/>
@@ -37175,7 +37172,7 @@
         <v>16</v>
       </c>
       <c r="Q143" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R143" s="12"/>
       <c r="T143" s="11"/>
@@ -37231,7 +37228,7 @@
         <v>16</v>
       </c>
       <c r="Q144" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R144" s="12"/>
       <c r="T144" s="11"/>
@@ -37287,7 +37284,7 @@
         <v>16</v>
       </c>
       <c r="Q145" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R145" s="12"/>
       <c r="T145" s="11"/>
@@ -37325,7 +37322,7 @@
         <v>18390</v>
       </c>
       <c r="K146" s="44" t="s">
-        <v>3975</v>
+        <v>3957</v>
       </c>
       <c r="L146" s="27" t="s">
         <v>3396</v>
@@ -37343,7 +37340,7 @@
         <v>16</v>
       </c>
       <c r="Q146" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R146" s="12"/>
       <c r="T146" s="11"/>
@@ -37399,7 +37396,7 @@
         <v>16</v>
       </c>
       <c r="Q147" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R147" s="12"/>
       <c r="T147" s="11"/>
@@ -37455,7 +37452,7 @@
         <v>16</v>
       </c>
       <c r="Q148" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R148" s="12"/>
       <c r="T148" s="11"/>
@@ -37511,7 +37508,7 @@
         <v>16</v>
       </c>
       <c r="Q149" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R149" s="12"/>
       <c r="T149" s="11"/>
@@ -37567,7 +37564,7 @@
         <v>16</v>
       </c>
       <c r="Q150" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R150" s="12"/>
       <c r="T150" s="11"/>
@@ -37623,7 +37620,7 @@
         <v>16</v>
       </c>
       <c r="Q151" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R151" s="12"/>
       <c r="T151" s="11"/>
@@ -37679,7 +37676,7 @@
         <v>16</v>
       </c>
       <c r="Q152" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R152" s="12"/>
       <c r="T152" s="11"/>
@@ -37735,7 +37732,7 @@
         <v>16</v>
       </c>
       <c r="Q153" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R153" s="12"/>
       <c r="T153" s="11"/>
@@ -37791,7 +37788,7 @@
         <v>16</v>
       </c>
       <c r="Q154" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R154" s="12"/>
       <c r="T154" s="11"/>
@@ -37847,7 +37844,7 @@
         <v>16</v>
       </c>
       <c r="Q155" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R155" s="12"/>
       <c r="T155" s="11"/>
@@ -37903,7 +37900,7 @@
         <v>16</v>
       </c>
       <c r="Q156" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R156" s="12"/>
       <c r="T156" s="11"/>
@@ -37959,7 +37956,7 @@
         <v>16</v>
       </c>
       <c r="Q157" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R157" s="12"/>
       <c r="T157" s="11"/>
@@ -38015,7 +38012,7 @@
         <v>16</v>
       </c>
       <c r="Q158" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R158" s="12"/>
       <c r="T158" s="11"/>
@@ -38071,7 +38068,7 @@
         <v>16</v>
       </c>
       <c r="Q159" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R159" s="12"/>
       <c r="T159" s="11"/>
@@ -38127,7 +38124,7 @@
         <v>16</v>
       </c>
       <c r="Q160" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R160" s="12"/>
       <c r="T160" s="11"/>
@@ -38183,7 +38180,7 @@
         <v>16</v>
       </c>
       <c r="Q161" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R161" s="12"/>
       <c r="T161" s="11"/>
@@ -38239,7 +38236,7 @@
         <v>16</v>
       </c>
       <c r="Q162" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R162" s="12"/>
       <c r="T162" s="11"/>
@@ -38295,7 +38292,7 @@
         <v>16</v>
       </c>
       <c r="Q163" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R163" s="12"/>
       <c r="T163" s="11"/>
@@ -38351,7 +38348,7 @@
         <v>16</v>
       </c>
       <c r="Q164" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R164" s="12"/>
       <c r="T164" s="11"/>
@@ -38407,7 +38404,7 @@
         <v>16</v>
       </c>
       <c r="Q165" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R165" s="12"/>
       <c r="T165" s="11"/>
@@ -38463,7 +38460,7 @@
         <v>16</v>
       </c>
       <c r="Q166" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R166" s="12"/>
       <c r="T166" s="11"/>
@@ -38519,7 +38516,7 @@
         <v>16</v>
       </c>
       <c r="Q167" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R167" s="12"/>
       <c r="T167" s="11"/>
@@ -38575,7 +38572,7 @@
         <v>1552</v>
       </c>
       <c r="Q168" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R168" s="12"/>
       <c r="T168" s="11"/>
@@ -38631,7 +38628,7 @@
         <v>16</v>
       </c>
       <c r="Q169" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R169" s="12"/>
       <c r="T169" s="11"/>
@@ -38687,7 +38684,7 @@
         <v>16</v>
       </c>
       <c r="Q170" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R170" s="12"/>
       <c r="T170" s="11"/>
@@ -38743,7 +38740,7 @@
         <v>16</v>
       </c>
       <c r="Q171" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R171" s="12"/>
       <c r="T171" s="11"/>
@@ -38799,7 +38796,7 @@
         <v>16</v>
       </c>
       <c r="Q172" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R172" s="12"/>
       <c r="T172" s="11"/>
@@ -38855,7 +38852,7 @@
         <v>16</v>
       </c>
       <c r="Q173" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R173" s="12"/>
       <c r="T173" s="11"/>
@@ -38911,7 +38908,7 @@
         <v>16</v>
       </c>
       <c r="Q174" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R174" s="12"/>
       <c r="T174" s="11"/>
@@ -38967,7 +38964,7 @@
         <v>2972</v>
       </c>
       <c r="Q175" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R175" s="12"/>
       <c r="T175" s="11"/>
@@ -39023,7 +39020,7 @@
         <v>16</v>
       </c>
       <c r="Q176" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R176" s="12"/>
       <c r="T176" s="11"/>
@@ -39079,7 +39076,7 @@
         <v>16</v>
       </c>
       <c r="Q177" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R177" s="12"/>
       <c r="T177" s="11"/>
@@ -39135,7 +39132,7 @@
         <v>16</v>
       </c>
       <c r="Q178" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R178" s="12"/>
       <c r="T178" s="11"/>
@@ -39191,7 +39188,7 @@
         <v>16</v>
       </c>
       <c r="Q179" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R179" s="12"/>
       <c r="T179" s="11"/>
@@ -39247,7 +39244,7 @@
         <v>16</v>
       </c>
       <c r="Q180" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R180" s="12"/>
       <c r="T180" s="11"/>
@@ -39303,7 +39300,7 @@
         <v>16</v>
       </c>
       <c r="Q181" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R181" s="12"/>
       <c r="T181" s="11"/>
@@ -39359,7 +39356,7 @@
         <v>16</v>
       </c>
       <c r="Q182" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R182" s="12"/>
       <c r="T182" s="11"/>
@@ -39415,7 +39412,7 @@
         <v>16</v>
       </c>
       <c r="Q183" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R183" s="12"/>
       <c r="T183" s="11"/>
@@ -39471,7 +39468,7 @@
         <v>16</v>
       </c>
       <c r="Q184" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R184" s="12"/>
       <c r="T184" s="11"/>
@@ -39527,7 +39524,7 @@
         <v>16</v>
       </c>
       <c r="Q185" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R185" s="12"/>
       <c r="T185" s="11"/>
@@ -39583,7 +39580,7 @@
         <v>16</v>
       </c>
       <c r="Q186" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R186" s="12"/>
       <c r="T186" s="11"/>
@@ -39639,7 +39636,7 @@
         <v>3120</v>
       </c>
       <c r="Q187" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R187" s="12"/>
       <c r="T187" s="11"/>
@@ -39695,7 +39692,7 @@
         <v>16</v>
       </c>
       <c r="Q188" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R188" s="12"/>
       <c r="T188" s="11"/>
@@ -39751,7 +39748,7 @@
         <v>16</v>
       </c>
       <c r="Q189" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R189" s="12"/>
       <c r="T189" s="11"/>
@@ -39807,7 +39804,7 @@
         <v>16</v>
       </c>
       <c r="Q190" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R190" s="12"/>
       <c r="T190" s="11"/>
@@ -39863,7 +39860,7 @@
         <v>16</v>
       </c>
       <c r="Q191" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R191" s="12"/>
       <c r="T191" s="11"/>
@@ -39919,7 +39916,7 @@
         <v>16</v>
       </c>
       <c r="Q192" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R192" s="12"/>
       <c r="T192" s="11"/>
@@ -39975,7 +39972,7 @@
         <v>16</v>
       </c>
       <c r="Q193" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R193" s="12"/>
       <c r="T193" s="11"/>
@@ -40031,7 +40028,7 @@
         <v>16</v>
       </c>
       <c r="Q194" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R194" s="12"/>
       <c r="T194" s="11"/>
@@ -40087,7 +40084,7 @@
         <v>16</v>
       </c>
       <c r="Q195" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R195" s="12"/>
       <c r="T195" s="11"/>
@@ -40143,7 +40140,7 @@
         <v>16</v>
       </c>
       <c r="Q196" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R196" s="12"/>
       <c r="T196" s="11"/>
@@ -40199,7 +40196,7 @@
         <v>16</v>
       </c>
       <c r="Q197" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R197" s="12"/>
       <c r="T197" s="11"/>
@@ -40255,7 +40252,7 @@
         <v>16</v>
       </c>
       <c r="Q198" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R198" s="12"/>
       <c r="T198" s="11"/>
@@ -40311,7 +40308,7 @@
         <v>16</v>
       </c>
       <c r="Q199" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R199" s="12"/>
       <c r="T199" s="11"/>
@@ -40367,7 +40364,7 @@
         <v>16</v>
       </c>
       <c r="Q200" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R200" s="12"/>
       <c r="T200" s="11"/>
@@ -40423,7 +40420,7 @@
         <v>1640</v>
       </c>
       <c r="Q201" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R201" s="12"/>
       <c r="T201" s="11"/>
@@ -40479,7 +40476,7 @@
         <v>16</v>
       </c>
       <c r="Q202" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R202" s="12"/>
       <c r="T202" s="11"/>
@@ -40535,7 +40532,7 @@
         <v>16</v>
       </c>
       <c r="Q203" s="20" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R203" s="12"/>
       <c r="T203" s="11"/>
@@ -40591,7 +40588,7 @@
         <v>16</v>
       </c>
       <c r="Q204" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R204" s="12"/>
       <c r="T204" s="11"/>
@@ -40647,7 +40644,7 @@
         <v>16</v>
       </c>
       <c r="Q205" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R205" s="12"/>
       <c r="T205" s="11"/>
@@ -40703,7 +40700,7 @@
         <v>1653</v>
       </c>
       <c r="Q206" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R206" s="12"/>
       <c r="T206" s="11"/>
@@ -40759,7 +40756,7 @@
         <v>16</v>
       </c>
       <c r="Q207" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R207" s="12"/>
       <c r="T207" s="11"/>
@@ -40815,7 +40812,7 @@
         <v>16</v>
       </c>
       <c r="Q208" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R208" s="12"/>
       <c r="T208" s="11"/>
@@ -40871,7 +40868,7 @@
         <v>16</v>
       </c>
       <c r="Q209" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R209" s="12"/>
       <c r="T209" s="11"/>
@@ -40927,7 +40924,7 @@
         <v>16</v>
       </c>
       <c r="Q210" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R210" s="12"/>
       <c r="T210" s="11"/>
@@ -40983,7 +40980,7 @@
         <v>16</v>
       </c>
       <c r="Q211" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R211" s="12"/>
       <c r="T211" s="11"/>
@@ -41039,7 +41036,7 @@
         <v>16</v>
       </c>
       <c r="Q212" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R212" s="12"/>
       <c r="T212" s="11"/>
@@ -41095,7 +41092,7 @@
         <v>16</v>
       </c>
       <c r="Q213" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R213" s="12"/>
       <c r="T213" s="11"/>
@@ -41151,7 +41148,7 @@
         <v>1674</v>
       </c>
       <c r="Q214" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R214" s="12"/>
       <c r="T214" s="11"/>
@@ -41207,7 +41204,7 @@
         <v>16</v>
       </c>
       <c r="Q215" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R215" s="12"/>
       <c r="T215" s="11"/>
@@ -41263,7 +41260,7 @@
         <v>16</v>
       </c>
       <c r="Q216" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R216" s="12"/>
       <c r="T216" s="11"/>
@@ -41319,7 +41316,7 @@
         <v>16</v>
       </c>
       <c r="Q217" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R217" s="12"/>
       <c r="T217" s="11"/>
@@ -41375,7 +41372,7 @@
         <v>16</v>
       </c>
       <c r="Q218" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R218" s="12"/>
       <c r="T218" s="11"/>
@@ -41431,7 +41428,7 @@
         <v>16</v>
       </c>
       <c r="Q219" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R219" s="12"/>
       <c r="T219" s="11"/>
@@ -41487,7 +41484,7 @@
         <v>16</v>
       </c>
       <c r="Q220" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R220" s="12"/>
       <c r="T220" s="11"/>
@@ -41543,7 +41540,7 @@
         <v>16</v>
       </c>
       <c r="Q221" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R221" s="12"/>
       <c r="T221" s="11"/>
@@ -41599,7 +41596,7 @@
         <v>16</v>
       </c>
       <c r="Q222" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R222" s="12"/>
       <c r="T222" s="11"/>
@@ -41655,7 +41652,7 @@
         <v>16</v>
       </c>
       <c r="Q223" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R223" s="12"/>
       <c r="T223" s="11"/>
@@ -41711,7 +41708,7 @@
         <v>16</v>
       </c>
       <c r="Q224" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R224" s="12"/>
       <c r="T224" s="11"/>
@@ -41767,7 +41764,7 @@
         <v>16</v>
       </c>
       <c r="Q225" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R225" s="12"/>
       <c r="T225" s="11"/>
@@ -41823,7 +41820,7 @@
         <v>16</v>
       </c>
       <c r="Q226" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R226" s="12"/>
       <c r="T226" s="11"/>
@@ -41879,7 +41876,7 @@
         <v>16</v>
       </c>
       <c r="Q227" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R227" s="12"/>
       <c r="T227" s="11"/>
@@ -41935,7 +41932,7 @@
         <v>16</v>
       </c>
       <c r="Q228" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R228" s="12"/>
       <c r="T228" s="11"/>
@@ -41991,7 +41988,7 @@
         <v>16</v>
       </c>
       <c r="Q229" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R229" s="12"/>
       <c r="T229" s="11"/>
@@ -42047,7 +42044,7 @@
         <v>16</v>
       </c>
       <c r="Q230" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R230" s="12"/>
       <c r="T230" s="11"/>
@@ -42103,7 +42100,7 @@
         <v>16</v>
       </c>
       <c r="Q231" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R231" s="12"/>
       <c r="T231" s="11"/>
@@ -42159,7 +42156,7 @@
         <v>16</v>
       </c>
       <c r="Q232" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R232" s="12"/>
       <c r="T232" s="11"/>
@@ -42215,7 +42212,7 @@
         <v>16</v>
       </c>
       <c r="Q233" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R233" s="12"/>
       <c r="T233" s="11"/>
@@ -42271,7 +42268,7 @@
         <v>16</v>
       </c>
       <c r="Q234" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R234" s="12"/>
       <c r="T234" s="11"/>
@@ -42327,7 +42324,7 @@
         <v>16</v>
       </c>
       <c r="Q235" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R235" s="12"/>
       <c r="T235" s="11"/>
@@ -42383,7 +42380,7 @@
         <v>16</v>
       </c>
       <c r="Q236" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R236" s="12"/>
       <c r="T236" s="11"/>
@@ -42439,7 +42436,7 @@
         <v>16</v>
       </c>
       <c r="Q237" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R237" s="12"/>
       <c r="T237" s="11"/>
@@ -42495,7 +42492,7 @@
         <v>16</v>
       </c>
       <c r="Q238" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R238" s="12"/>
       <c r="T238" s="11"/>
@@ -42551,7 +42548,7 @@
         <v>16</v>
       </c>
       <c r="Q239" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R239" s="12"/>
       <c r="T239" s="11"/>
@@ -42607,7 +42604,7 @@
         <v>16</v>
       </c>
       <c r="Q240" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R240" s="12"/>
       <c r="T240" s="11"/>
@@ -42663,7 +42660,7 @@
         <v>16</v>
       </c>
       <c r="Q241" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R241" s="12"/>
       <c r="T241" s="11"/>
@@ -42719,7 +42716,7 @@
         <v>16</v>
       </c>
       <c r="Q242" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R242" s="12"/>
       <c r="T242" s="11"/>
@@ -42775,7 +42772,7 @@
         <v>16</v>
       </c>
       <c r="Q243" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R243" s="12"/>
       <c r="T243" s="11"/>
@@ -42831,7 +42828,7 @@
         <v>16</v>
       </c>
       <c r="Q244" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R244" s="12"/>
       <c r="T244" s="11"/>
@@ -42887,7 +42884,7 @@
         <v>16</v>
       </c>
       <c r="Q245" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R245" s="12"/>
       <c r="T245" s="11"/>
@@ -42943,7 +42940,7 @@
         <v>16</v>
       </c>
       <c r="Q246" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R246" s="12"/>
       <c r="T246" s="11"/>
@@ -42999,7 +42996,7 @@
         <v>16</v>
       </c>
       <c r="Q247" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R247" s="12"/>
       <c r="T247" s="11"/>
@@ -43055,7 +43052,7 @@
         <v>16</v>
       </c>
       <c r="Q248" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R248" s="12"/>
       <c r="T248" s="11"/>
@@ -43111,7 +43108,7 @@
         <v>16</v>
       </c>
       <c r="Q249" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R249" s="12"/>
       <c r="T249" s="11"/>
@@ -43167,7 +43164,7 @@
         <v>16</v>
       </c>
       <c r="Q250" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R250" s="12"/>
       <c r="T250" s="11"/>
@@ -43223,7 +43220,7 @@
         <v>16</v>
       </c>
       <c r="Q251" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R251" s="12"/>
       <c r="T251" s="11"/>
@@ -43279,7 +43276,7 @@
         <v>16</v>
       </c>
       <c r="Q252" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R252" s="12"/>
       <c r="T252" s="11"/>
@@ -43335,7 +43332,7 @@
         <v>16</v>
       </c>
       <c r="Q253" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R253" s="12"/>
       <c r="T253" s="11"/>
@@ -43391,7 +43388,7 @@
         <v>1776</v>
       </c>
       <c r="Q254" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R254" s="12"/>
       <c r="T254" s="11"/>
@@ -43447,7 +43444,7 @@
         <v>16</v>
       </c>
       <c r="Q255" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R255" s="12"/>
       <c r="T255" s="11"/>
@@ -43503,7 +43500,7 @@
         <v>16</v>
       </c>
       <c r="Q256" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R256" s="12"/>
       <c r="T256" s="11"/>
@@ -43559,7 +43556,7 @@
         <v>16</v>
       </c>
       <c r="Q257" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R257" s="12"/>
       <c r="T257" s="11"/>
@@ -43615,7 +43612,7 @@
         <v>16</v>
       </c>
       <c r="Q258" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R258" s="12"/>
       <c r="T258" s="11"/>
@@ -43671,7 +43668,7 @@
         <v>16</v>
       </c>
       <c r="Q259" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R259" s="12"/>
       <c r="T259" s="11"/>
@@ -43727,7 +43724,7 @@
         <v>16</v>
       </c>
       <c r="Q260" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R260" s="12"/>
       <c r="T260" s="11"/>
@@ -43783,7 +43780,7 @@
         <v>16</v>
       </c>
       <c r="Q261" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R261" s="12"/>
       <c r="T261" s="11"/>
@@ -43839,7 +43836,7 @@
         <v>16</v>
       </c>
       <c r="Q262" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R262" s="12"/>
       <c r="T262" s="11"/>
@@ -43895,7 +43892,7 @@
         <v>16</v>
       </c>
       <c r="Q263" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R263" s="12"/>
       <c r="T263" s="11"/>
@@ -43951,7 +43948,7 @@
         <v>16</v>
       </c>
       <c r="Q264" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R264" s="12"/>
       <c r="T264" s="11"/>
@@ -44007,7 +44004,7 @@
         <v>16</v>
       </c>
       <c r="Q265" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R265" s="12"/>
       <c r="T265" s="11"/>
@@ -44063,7 +44060,7 @@
         <v>16</v>
       </c>
       <c r="Q266" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R266" s="12"/>
       <c r="T266" s="11"/>
@@ -44119,7 +44116,7 @@
         <v>16</v>
       </c>
       <c r="Q267" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R267" s="12"/>
       <c r="T267" s="11"/>
@@ -44175,7 +44172,7 @@
         <v>16</v>
       </c>
       <c r="Q268" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R268" s="12"/>
       <c r="T268" s="11"/>
@@ -44231,7 +44228,7 @@
         <v>16</v>
       </c>
       <c r="Q269" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R269" s="12"/>
       <c r="T269" s="11"/>
@@ -44287,7 +44284,7 @@
         <v>16</v>
       </c>
       <c r="Q270" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R270" s="12"/>
       <c r="T270" s="11"/>
@@ -44343,7 +44340,7 @@
         <v>16</v>
       </c>
       <c r="Q271" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R271" s="12"/>
       <c r="T271" s="11"/>
@@ -44384,7 +44381,7 @@
         <v>16</v>
       </c>
       <c r="L272" s="27" t="s">
-        <v>3956</v>
+        <v>3940</v>
       </c>
       <c r="M272" s="27" t="s">
         <v>1822</v>
@@ -44399,7 +44396,7 @@
         <v>16</v>
       </c>
       <c r="Q272" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R272" s="12"/>
       <c r="T272" s="11"/>
@@ -44455,7 +44452,7 @@
         <v>16</v>
       </c>
       <c r="Q273" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R273" s="12"/>
       <c r="T273" s="11"/>
@@ -44511,7 +44508,7 @@
         <v>16</v>
       </c>
       <c r="Q274" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R274" s="12"/>
       <c r="T274" s="11"/>
@@ -44567,7 +44564,7 @@
         <v>16</v>
       </c>
       <c r="Q275" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R275" s="12"/>
       <c r="T275" s="11"/>
@@ -44623,7 +44620,7 @@
         <v>16</v>
       </c>
       <c r="Q276" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R276" s="12"/>
       <c r="T276" s="11"/>
@@ -44679,7 +44676,7 @@
         <v>16</v>
       </c>
       <c r="Q277" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R277" s="12"/>
       <c r="T277" s="11"/>
@@ -44735,7 +44732,7 @@
         <v>16</v>
       </c>
       <c r="Q278" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R278" s="12"/>
       <c r="T278" s="11"/>
@@ -44791,7 +44788,7 @@
         <v>16</v>
       </c>
       <c r="Q279" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R279" s="12"/>
       <c r="T279" s="11"/>
@@ -44847,7 +44844,7 @@
         <v>16</v>
       </c>
       <c r="Q280" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R280" s="12"/>
       <c r="T280" s="11"/>
@@ -44903,7 +44900,7 @@
         <v>16</v>
       </c>
       <c r="Q281" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R281" s="12"/>
       <c r="T281" s="11"/>
@@ -44959,7 +44956,7 @@
         <v>1850</v>
       </c>
       <c r="Q282" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R282" s="12"/>
       <c r="T282" s="11"/>
@@ -45015,7 +45012,7 @@
         <v>3140</v>
       </c>
       <c r="Q283" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R283" s="12"/>
       <c r="T283" s="11"/>
@@ -45071,7 +45068,7 @@
         <v>16</v>
       </c>
       <c r="Q284" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R284" s="12"/>
       <c r="T284" s="11"/>
@@ -45127,7 +45124,7 @@
         <v>1860</v>
       </c>
       <c r="Q285" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R285" s="12"/>
       <c r="T285" s="11"/>
@@ -45183,7 +45180,7 @@
         <v>1864</v>
       </c>
       <c r="Q286" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R286" s="12"/>
       <c r="T286" s="11"/>
@@ -45239,7 +45236,7 @@
         <v>16</v>
       </c>
       <c r="Q287" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R287" s="12"/>
       <c r="T287" s="11"/>
@@ -45295,7 +45292,7 @@
         <v>16</v>
       </c>
       <c r="Q288" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R288" s="12"/>
       <c r="T288" s="11"/>
@@ -45351,7 +45348,7 @@
         <v>16</v>
       </c>
       <c r="Q289" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R289" s="12"/>
       <c r="T289" s="11"/>
@@ -45407,7 +45404,7 @@
         <v>1876</v>
       </c>
       <c r="Q290" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R290" s="12"/>
       <c r="T290" s="11"/>
@@ -45463,7 +45460,7 @@
         <v>16</v>
       </c>
       <c r="Q291" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R291" s="12"/>
       <c r="T291" s="11"/>
@@ -45519,7 +45516,7 @@
         <v>16</v>
       </c>
       <c r="Q292" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R292" s="12"/>
       <c r="T292" s="11"/>
@@ -45575,7 +45572,7 @@
         <v>1885</v>
       </c>
       <c r="Q293" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R293" s="12"/>
       <c r="T293" s="11"/>
@@ -45631,7 +45628,7 @@
         <v>16</v>
       </c>
       <c r="Q294" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R294" s="12"/>
       <c r="T294" s="11"/>
@@ -45687,7 +45684,7 @@
         <v>16</v>
       </c>
       <c r="Q295" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R295" s="12"/>
       <c r="T295" s="11"/>
@@ -45743,7 +45740,7 @@
         <v>16</v>
       </c>
       <c r="Q296" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R296" s="12"/>
       <c r="T296" s="11"/>
@@ -45799,7 +45796,7 @@
         <v>16</v>
       </c>
       <c r="Q297" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R297" s="12"/>
       <c r="T297" s="11"/>
@@ -45855,7 +45852,7 @@
         <v>16</v>
       </c>
       <c r="Q298" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R298" s="12"/>
       <c r="T298" s="11"/>
@@ -45911,7 +45908,7 @@
         <v>3144</v>
       </c>
       <c r="Q299" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R299" s="12"/>
       <c r="T299" s="11"/>
@@ -45967,7 +45964,7 @@
         <v>16</v>
       </c>
       <c r="Q300" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R300" s="12"/>
       <c r="T300" s="11"/>
@@ -46023,7 +46020,7 @@
         <v>16</v>
       </c>
       <c r="Q301" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R301" s="12"/>
       <c r="T301" s="11"/>
@@ -46079,7 +46076,7 @@
         <v>16</v>
       </c>
       <c r="Q302" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R302" s="12"/>
       <c r="T302" s="11"/>
@@ -46135,7 +46132,7 @@
         <v>16</v>
       </c>
       <c r="Q303" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R303" s="12"/>
       <c r="T303" s="11"/>
@@ -46191,7 +46188,7 @@
         <v>16</v>
       </c>
       <c r="Q304" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R304" s="12"/>
       <c r="T304" s="11"/>
@@ -46247,7 +46244,7 @@
         <v>16</v>
       </c>
       <c r="Q305" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R305" s="12"/>
       <c r="T305" s="11"/>
@@ -46303,7 +46300,7 @@
         <v>16</v>
       </c>
       <c r="Q306" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R306" s="12"/>
       <c r="T306" s="11"/>
@@ -46359,7 +46356,7 @@
         <v>16</v>
       </c>
       <c r="Q307" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R307" s="12"/>
       <c r="T307" s="11"/>
@@ -46415,7 +46412,7 @@
         <v>16</v>
       </c>
       <c r="Q308" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R308" s="12"/>
       <c r="T308" s="11"/>
@@ -46471,7 +46468,7 @@
         <v>16</v>
       </c>
       <c r="Q309" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R309" s="12"/>
       <c r="T309" s="11"/>
@@ -46527,7 +46524,7 @@
         <v>16</v>
       </c>
       <c r="Q310" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R310" s="12"/>
       <c r="T310" s="11"/>
@@ -46583,7 +46580,7 @@
         <v>16</v>
       </c>
       <c r="Q311" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R311" s="12"/>
       <c r="T311" s="11"/>
@@ -46639,7 +46636,7 @@
         <v>16</v>
       </c>
       <c r="Q312" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R312" s="12"/>
       <c r="T312" s="11"/>
@@ -46695,7 +46692,7 @@
         <v>16</v>
       </c>
       <c r="Q313" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R313" s="12"/>
       <c r="T313" s="11"/>
@@ -46751,7 +46748,7 @@
         <v>16</v>
       </c>
       <c r="Q314" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R314" s="12"/>
       <c r="T314" s="11"/>
@@ -46807,7 +46804,7 @@
         <v>16</v>
       </c>
       <c r="Q315" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R315" s="12"/>
       <c r="T315" s="11"/>
@@ -46863,7 +46860,7 @@
         <v>16</v>
       </c>
       <c r="Q316" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R316" s="12"/>
       <c r="T316" s="11"/>
@@ -46919,7 +46916,7 @@
         <v>16</v>
       </c>
       <c r="Q317" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R317" s="12"/>
       <c r="T317" s="11"/>
@@ -46975,7 +46972,7 @@
         <v>16</v>
       </c>
       <c r="Q318" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R318" s="12"/>
       <c r="T318" s="11"/>
@@ -47031,7 +47028,7 @@
         <v>1953</v>
       </c>
       <c r="Q319" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R319" s="12"/>
       <c r="T319" s="11"/>
@@ -47087,7 +47084,7 @@
         <v>16</v>
       </c>
       <c r="Q320" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R320" s="12"/>
       <c r="T320" s="11"/>
@@ -47143,7 +47140,7 @@
         <v>16</v>
       </c>
       <c r="Q321" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R321" s="12"/>
       <c r="T321" s="11"/>
@@ -47199,7 +47196,7 @@
         <v>16</v>
       </c>
       <c r="Q322" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R322" s="12"/>
       <c r="T322" s="11"/>
@@ -47255,7 +47252,7 @@
         <v>16</v>
       </c>
       <c r="Q323" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R323" s="12"/>
       <c r="T323" s="11"/>
@@ -47311,7 +47308,7 @@
         <v>16</v>
       </c>
       <c r="Q324" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R324" s="12"/>
       <c r="T324" s="11"/>
@@ -47367,7 +47364,7 @@
         <v>16</v>
       </c>
       <c r="Q325" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R325" s="12"/>
       <c r="T325" s="11"/>
@@ -47423,7 +47420,7 @@
         <v>16</v>
       </c>
       <c r="Q326" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R326" s="12"/>
       <c r="T326" s="11"/>
@@ -47479,7 +47476,7 @@
         <v>1975</v>
       </c>
       <c r="Q327" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R327" s="12"/>
       <c r="T327" s="11"/>
@@ -47535,7 +47532,7 @@
         <v>16</v>
       </c>
       <c r="Q328" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R328" s="12"/>
       <c r="T328" s="11"/>
@@ -47591,7 +47588,7 @@
         <v>16</v>
       </c>
       <c r="Q329" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R329" s="12"/>
       <c r="T329" s="11"/>
@@ -47647,7 +47644,7 @@
         <v>1985</v>
       </c>
       <c r="Q330" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R330" s="12"/>
       <c r="T330" s="11"/>
@@ -47703,7 +47700,7 @@
         <v>16</v>
       </c>
       <c r="Q331" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R331" s="12"/>
       <c r="T331" s="11"/>
@@ -47759,7 +47756,7 @@
         <v>16</v>
       </c>
       <c r="Q332" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R332" s="12"/>
       <c r="T332" s="11"/>
@@ -47815,7 +47812,7 @@
         <v>16</v>
       </c>
       <c r="Q333" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R333" s="12"/>
       <c r="T333" s="11"/>
@@ -47871,7 +47868,7 @@
         <v>16</v>
       </c>
       <c r="Q334" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R334" s="12"/>
       <c r="T334" s="11"/>
@@ -47927,7 +47924,7 @@
         <v>16</v>
       </c>
       <c r="Q335" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R335" s="12"/>
       <c r="T335" s="11"/>
@@ -47983,7 +47980,7 @@
         <v>16</v>
       </c>
       <c r="Q336" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R336" s="12"/>
       <c r="T336" s="11"/>
@@ -48039,7 +48036,7 @@
         <v>16</v>
       </c>
       <c r="Q337" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R337" s="12"/>
       <c r="T337" s="11"/>
@@ -48095,7 +48092,7 @@
         <v>16</v>
       </c>
       <c r="Q338" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R338" s="12"/>
       <c r="T338" s="11"/>
@@ -48151,7 +48148,7 @@
         <v>16</v>
       </c>
       <c r="Q339" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R339" s="12"/>
       <c r="T339" s="11"/>
@@ -48207,7 +48204,7 @@
         <v>16</v>
       </c>
       <c r="Q340" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R340" s="12"/>
       <c r="T340" s="11"/>
@@ -48263,7 +48260,7 @@
         <v>16</v>
       </c>
       <c r="Q341" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R341" s="12"/>
       <c r="T341" s="11"/>
@@ -48319,7 +48316,7 @@
         <v>16</v>
       </c>
       <c r="Q342" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R342" s="12"/>
       <c r="T342" s="11"/>
@@ -48375,7 +48372,7 @@
         <v>16</v>
       </c>
       <c r="Q343" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R343" s="12"/>
       <c r="T343" s="11"/>
@@ -48431,7 +48428,7 @@
         <v>16</v>
       </c>
       <c r="Q344" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R344" s="12"/>
       <c r="T344" s="11"/>
@@ -48469,7 +48466,7 @@
         <v>24000</v>
       </c>
       <c r="K345" s="44" t="s">
-        <v>3975</v>
+        <v>3957</v>
       </c>
       <c r="L345" s="27" t="s">
         <v>3594</v>
@@ -48487,7 +48484,7 @@
         <v>16</v>
       </c>
       <c r="Q345" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R345" s="12"/>
       <c r="T345" s="11"/>
@@ -48543,7 +48540,7 @@
         <v>16</v>
       </c>
       <c r="Q346" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R346" s="12"/>
       <c r="T346" s="11"/>
@@ -48599,7 +48596,7 @@
         <v>16</v>
       </c>
       <c r="Q347" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R347" s="12"/>
       <c r="T347" s="11"/>
@@ -48655,7 +48652,7 @@
         <v>16</v>
       </c>
       <c r="Q348" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R348" s="12"/>
       <c r="T348" s="11"/>
@@ -48711,7 +48708,7 @@
         <v>2031</v>
       </c>
       <c r="Q349" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R349" s="12"/>
       <c r="T349" s="11"/>
@@ -48767,7 +48764,7 @@
         <v>16</v>
       </c>
       <c r="Q350" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R350" s="12"/>
       <c r="T350" s="11"/>
@@ -48823,7 +48820,7 @@
         <v>16</v>
       </c>
       <c r="Q351" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R351" s="12"/>
       <c r="T351" s="11"/>
@@ -48879,7 +48876,7 @@
         <v>16</v>
       </c>
       <c r="Q352" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R352" s="12"/>
       <c r="T352" s="11"/>
@@ -48935,7 +48932,7 @@
         <v>16</v>
       </c>
       <c r="Q353" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R353" s="12"/>
       <c r="T353" s="11"/>
@@ -48991,7 +48988,7 @@
         <v>16</v>
       </c>
       <c r="Q354" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R354" s="12"/>
       <c r="T354" s="11"/>
@@ -49047,7 +49044,7 @@
         <v>16</v>
       </c>
       <c r="Q355" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R355" s="12"/>
       <c r="T355" s="11"/>
@@ -49103,7 +49100,7 @@
         <v>16</v>
       </c>
       <c r="Q356" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R356" s="12"/>
       <c r="T356" s="11"/>
@@ -49159,7 +49156,7 @@
         <v>16</v>
       </c>
       <c r="Q357" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R357" s="12"/>
       <c r="T357" s="11"/>
@@ -49215,7 +49212,7 @@
         <v>16</v>
       </c>
       <c r="Q358" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R358" s="12"/>
       <c r="T358" s="11"/>
@@ -49271,7 +49268,7 @@
         <v>16</v>
       </c>
       <c r="Q359" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R359" s="12"/>
       <c r="T359" s="11"/>
@@ -49327,7 +49324,7 @@
         <v>16</v>
       </c>
       <c r="Q360" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R360" s="12"/>
       <c r="T360" s="11"/>
@@ -49383,7 +49380,7 @@
         <v>16</v>
       </c>
       <c r="Q361" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R361" s="12"/>
       <c r="T361" s="11"/>
@@ -49439,7 +49436,7 @@
         <v>16</v>
       </c>
       <c r="Q362" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R362" s="12"/>
       <c r="T362" s="11"/>
@@ -49495,7 +49492,7 @@
         <v>16</v>
       </c>
       <c r="Q363" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R363" s="12"/>
       <c r="T363" s="11"/>
@@ -49551,7 +49548,7 @@
         <v>16</v>
       </c>
       <c r="Q364" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R364" s="12"/>
       <c r="T364" s="11"/>
@@ -49607,7 +49604,7 @@
         <v>16</v>
       </c>
       <c r="Q365" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R365" s="12"/>
       <c r="T365" s="11"/>
@@ -49663,7 +49660,7 @@
         <v>16</v>
       </c>
       <c r="Q366" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R366" s="12"/>
       <c r="T366" s="11"/>
@@ -49719,7 +49716,7 @@
         <v>16</v>
       </c>
       <c r="Q367" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R367" s="12"/>
       <c r="T367" s="11"/>
@@ -49775,7 +49772,7 @@
         <v>16</v>
       </c>
       <c r="Q368" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R368" s="12"/>
       <c r="T368" s="11"/>
@@ -49831,7 +49828,7 @@
         <v>16</v>
       </c>
       <c r="Q369" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R369" s="12"/>
       <c r="T369" s="11"/>
@@ -49887,7 +49884,7 @@
         <v>16</v>
       </c>
       <c r="Q370" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R370" s="12"/>
       <c r="T370" s="11"/>
@@ -49943,7 +49940,7 @@
         <v>16</v>
       </c>
       <c r="Q371" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R371" s="12"/>
       <c r="T371" s="11"/>
@@ -49999,7 +49996,7 @@
         <v>16</v>
       </c>
       <c r="Q372" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R372" s="12"/>
       <c r="T372" s="11"/>
@@ -50055,7 +50052,7 @@
         <v>16</v>
       </c>
       <c r="Q373" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R373" s="12"/>
       <c r="T373" s="11"/>
@@ -50111,7 +50108,7 @@
         <v>16</v>
       </c>
       <c r="Q374" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R374" s="12"/>
       <c r="T374" s="11"/>
@@ -50167,7 +50164,7 @@
         <v>16</v>
       </c>
       <c r="Q375" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R375" s="12"/>
       <c r="T375" s="11"/>
@@ -50223,7 +50220,7 @@
         <v>16</v>
       </c>
       <c r="Q376" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R376" s="12"/>
       <c r="T376" s="11"/>
@@ -50279,7 +50276,7 @@
         <v>16</v>
       </c>
       <c r="Q377" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R377" s="12"/>
       <c r="T377" s="11"/>
@@ -50320,7 +50317,7 @@
         <v>60</v>
       </c>
       <c r="L378" s="27" t="s">
-        <v>3955</v>
+        <v>3939</v>
       </c>
       <c r="M378" s="27" t="s">
         <v>2108</v>
@@ -50335,7 +50332,7 @@
         <v>3157</v>
       </c>
       <c r="Q378" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R378" s="12"/>
       <c r="T378" s="11"/>
@@ -50391,7 +50388,7 @@
         <v>16</v>
       </c>
       <c r="Q379" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R379" s="12"/>
       <c r="T379" s="11"/>
@@ -50447,7 +50444,7 @@
         <v>16</v>
       </c>
       <c r="Q380" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R380" s="12"/>
       <c r="T380" s="11"/>
@@ -50503,7 +50500,7 @@
         <v>16</v>
       </c>
       <c r="Q381" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R381" s="12"/>
       <c r="T381" s="11"/>
@@ -50559,7 +50556,7 @@
         <v>16</v>
       </c>
       <c r="Q382" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R382" s="12"/>
       <c r="T382" s="11"/>
@@ -50615,7 +50612,7 @@
         <v>16</v>
       </c>
       <c r="Q383" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R383" s="12"/>
       <c r="T383" s="11"/>
@@ -50671,7 +50668,7 @@
         <v>16</v>
       </c>
       <c r="Q384" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R384" s="12"/>
       <c r="T384" s="11"/>
@@ -50727,7 +50724,7 @@
         <v>16</v>
       </c>
       <c r="Q385" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R385" s="12"/>
       <c r="T385" s="11"/>
@@ -50783,7 +50780,7 @@
         <v>16</v>
       </c>
       <c r="Q386" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R386" s="12"/>
       <c r="T386" s="11"/>
@@ -50839,7 +50836,7 @@
         <v>16</v>
       </c>
       <c r="Q387" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R387" s="12"/>
       <c r="T387" s="11"/>
@@ -50895,7 +50892,7 @@
         <v>16</v>
       </c>
       <c r="Q388" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R388" s="12"/>
       <c r="T388" s="11"/>
@@ -50951,7 +50948,7 @@
         <v>16</v>
       </c>
       <c r="Q389" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R389" s="12"/>
       <c r="T389" s="11"/>
@@ -51007,7 +51004,7 @@
         <v>2141</v>
       </c>
       <c r="Q390" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R390" s="12"/>
       <c r="T390" s="11"/>
@@ -51063,7 +51060,7 @@
         <v>3201</v>
       </c>
       <c r="Q391" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R391" s="12"/>
       <c r="T391" s="11"/>
@@ -51119,7 +51116,7 @@
         <v>16</v>
       </c>
       <c r="Q392" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R392" s="12"/>
       <c r="T392" s="11"/>
@@ -51175,7 +51172,7 @@
         <v>2149</v>
       </c>
       <c r="Q393" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R393" s="12"/>
       <c r="T393" s="11"/>
@@ -51231,7 +51228,7 @@
         <v>16</v>
       </c>
       <c r="Q394" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R394" s="12"/>
       <c r="T394" s="11"/>
@@ -51287,7 +51284,7 @@
         <v>16</v>
       </c>
       <c r="Q395" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R395" s="12"/>
       <c r="T395" s="11"/>
@@ -51343,7 +51340,7 @@
         <v>16</v>
       </c>
       <c r="Q396" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R396" s="12"/>
       <c r="T396" s="11"/>
@@ -51399,7 +51396,7 @@
         <v>16</v>
       </c>
       <c r="Q397" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R397" s="12"/>
       <c r="T397" s="11"/>
@@ -51455,7 +51452,7 @@
         <v>16</v>
       </c>
       <c r="Q398" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R398" s="12"/>
       <c r="T398" s="11"/>
@@ -51511,7 +51508,7 @@
         <v>16</v>
       </c>
       <c r="Q399" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R399" s="12"/>
       <c r="T399" s="11"/>
@@ -51567,7 +51564,7 @@
         <v>16</v>
       </c>
       <c r="Q400" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R400" s="12"/>
       <c r="T400" s="11"/>
@@ -51623,7 +51620,7 @@
         <v>2174</v>
       </c>
       <c r="Q401" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R401" s="12"/>
       <c r="T401" s="11"/>
@@ -51679,7 +51676,7 @@
         <v>16</v>
       </c>
       <c r="Q402" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R402" s="12"/>
       <c r="T402" s="11"/>
@@ -51735,7 +51732,7 @@
         <v>16</v>
       </c>
       <c r="Q403" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R403" s="12"/>
       <c r="T403" s="11"/>
@@ -51791,7 +51788,7 @@
         <v>16</v>
       </c>
       <c r="Q404" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R404" s="12"/>
       <c r="T404" s="11"/>
@@ -51847,7 +51844,7 @@
         <v>16</v>
       </c>
       <c r="Q405" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R405" s="12"/>
       <c r="T405" s="11"/>
@@ -51903,7 +51900,7 @@
         <v>16</v>
       </c>
       <c r="Q406" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R406" s="12"/>
       <c r="T406" s="11"/>
@@ -51959,7 +51956,7 @@
         <v>16</v>
       </c>
       <c r="Q407" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R407" s="12"/>
       <c r="T407" s="11"/>
@@ -52015,7 +52012,7 @@
         <v>16</v>
       </c>
       <c r="Q408" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R408" s="12"/>
       <c r="T408" s="11"/>
@@ -52071,7 +52068,7 @@
         <v>16</v>
       </c>
       <c r="Q409" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R409" s="12"/>
       <c r="T409" s="11"/>
@@ -52127,7 +52124,7 @@
         <v>16</v>
       </c>
       <c r="Q410" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R410" s="12"/>
       <c r="T410" s="11"/>
@@ -52183,7 +52180,7 @@
         <v>2205</v>
       </c>
       <c r="Q411" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R411" s="12"/>
       <c r="T411" s="11"/>
@@ -52239,7 +52236,7 @@
         <v>16</v>
       </c>
       <c r="Q412" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R412" s="12"/>
       <c r="T412" s="11"/>
@@ -52295,7 +52292,7 @@
         <v>16</v>
       </c>
       <c r="Q413" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R413" s="12"/>
       <c r="T413" s="11"/>
@@ -52351,7 +52348,7 @@
         <v>2215</v>
       </c>
       <c r="Q414" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R414" s="12"/>
       <c r="T414" s="11"/>
@@ -52407,7 +52404,7 @@
         <v>16</v>
       </c>
       <c r="Q415" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R415" s="12"/>
       <c r="T415" s="11"/>
@@ -52463,7 +52460,7 @@
         <v>16</v>
       </c>
       <c r="Q416" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R416" s="12"/>
       <c r="T416" s="11"/>
@@ -52519,7 +52516,7 @@
         <v>16</v>
       </c>
       <c r="Q417" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R417" s="12"/>
       <c r="T417" s="11"/>
@@ -52575,7 +52572,7 @@
         <v>16</v>
       </c>
       <c r="Q418" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R418" s="12"/>
       <c r="T418" s="11"/>
@@ -52631,7 +52628,7 @@
         <v>3203</v>
       </c>
       <c r="Q419" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R419" s="12"/>
       <c r="T419" s="11"/>
@@ -52687,7 +52684,7 @@
         <v>16</v>
       </c>
       <c r="Q420" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R420" s="12"/>
       <c r="T420" s="11"/>
@@ -52743,7 +52740,7 @@
         <v>16</v>
       </c>
       <c r="Q421" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R421" s="12"/>
       <c r="T421" s="11"/>
@@ -52799,7 +52796,7 @@
         <v>16</v>
       </c>
       <c r="Q422" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R422" s="12"/>
       <c r="T422" s="11"/>
@@ -52855,7 +52852,7 @@
         <v>16</v>
       </c>
       <c r="Q423" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R423" s="12"/>
       <c r="T423" s="11"/>
@@ -52911,7 +52908,7 @@
         <v>3206</v>
       </c>
       <c r="Q424" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R424" s="12"/>
       <c r="T424" s="11"/>
@@ -52967,7 +52964,7 @@
         <v>16</v>
       </c>
       <c r="Q425" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R425" s="12"/>
       <c r="T425" s="11"/>
@@ -53023,7 +53020,7 @@
         <v>2245</v>
       </c>
       <c r="Q426" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R426" s="12"/>
       <c r="T426" s="11"/>
@@ -53079,7 +53076,7 @@
         <v>16</v>
       </c>
       <c r="Q427" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R427" s="12"/>
       <c r="T427" s="11"/>
@@ -53135,7 +53132,7 @@
         <v>16</v>
       </c>
       <c r="Q428" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R428" s="12"/>
       <c r="T428" s="11"/>
@@ -53191,7 +53188,7 @@
         <v>16</v>
       </c>
       <c r="Q429" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R429" s="12"/>
       <c r="T429" s="11"/>
@@ -53247,7 +53244,7 @@
         <v>16</v>
       </c>
       <c r="Q430" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R430" s="12"/>
       <c r="T430" s="11"/>
@@ -53303,7 +53300,7 @@
         <v>16</v>
       </c>
       <c r="Q431" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R431" s="12"/>
       <c r="T431" s="11"/>
@@ -53359,7 +53356,7 @@
         <v>16</v>
       </c>
       <c r="Q432" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R432" s="12"/>
       <c r="T432" s="11"/>
@@ -53415,7 +53412,7 @@
         <v>16</v>
       </c>
       <c r="Q433" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R433" s="12"/>
       <c r="T433" s="11"/>
@@ -53471,7 +53468,7 @@
         <v>16</v>
       </c>
       <c r="Q434" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R434" s="12"/>
       <c r="T434" s="11"/>
@@ -53527,7 +53524,7 @@
         <v>16</v>
       </c>
       <c r="Q435" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R435" s="12"/>
       <c r="T435" s="11"/>
@@ -53583,7 +53580,7 @@
         <v>16</v>
       </c>
       <c r="Q436" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R436" s="12"/>
       <c r="T436" s="11"/>
@@ -53639,7 +53636,7 @@
         <v>16</v>
       </c>
       <c r="Q437" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R437" s="12"/>
       <c r="T437" s="11"/>
@@ -53695,7 +53692,7 @@
         <v>16</v>
       </c>
       <c r="Q438" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R438" s="12"/>
       <c r="T438" s="11"/>
@@ -53751,7 +53748,7 @@
         <v>16</v>
       </c>
       <c r="Q439" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R439" s="12"/>
       <c r="T439" s="11"/>
@@ -53807,7 +53804,7 @@
         <v>16</v>
       </c>
       <c r="Q440" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R440" s="12"/>
       <c r="T440" s="11"/>
@@ -53863,7 +53860,7 @@
         <v>16</v>
       </c>
       <c r="Q441" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R441" s="12"/>
       <c r="T441" s="11"/>
@@ -53919,7 +53916,7 @@
         <v>16</v>
       </c>
       <c r="Q442" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R442" s="12"/>
       <c r="T442" s="11"/>
@@ -53975,7 +53972,7 @@
         <v>16</v>
       </c>
       <c r="Q443" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R443" s="12"/>
       <c r="T443" s="11"/>
@@ -54031,7 +54028,7 @@
         <v>16</v>
       </c>
       <c r="Q444" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R444" s="12"/>
       <c r="T444" s="11"/>
@@ -54087,7 +54084,7 @@
         <v>16</v>
       </c>
       <c r="Q445" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R445" s="12"/>
       <c r="T445" s="11"/>
@@ -54143,7 +54140,7 @@
         <v>16</v>
       </c>
       <c r="Q446" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R446" s="12"/>
       <c r="T446" s="11"/>
@@ -54199,7 +54196,7 @@
         <v>16</v>
       </c>
       <c r="Q447" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R447" s="12"/>
       <c r="T447" s="11"/>
@@ -54255,7 +54252,7 @@
         <v>16</v>
       </c>
       <c r="Q448" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R448" s="12"/>
       <c r="T448" s="11"/>
@@ -54311,7 +54308,7 @@
         <v>16</v>
       </c>
       <c r="Q449" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R449" s="12"/>
       <c r="T449" s="11"/>
@@ -54367,7 +54364,7 @@
         <v>16</v>
       </c>
       <c r="Q450" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R450" s="12"/>
       <c r="T450" s="11"/>
@@ -54423,7 +54420,7 @@
         <v>16</v>
       </c>
       <c r="Q451" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R451" s="12"/>
       <c r="T451" s="11"/>
@@ -54479,7 +54476,7 @@
         <v>16</v>
       </c>
       <c r="Q452" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R452" s="12"/>
       <c r="T452" s="11"/>
@@ -54535,7 +54532,7 @@
         <v>16</v>
       </c>
       <c r="Q453" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R453" s="12"/>
       <c r="T453" s="11"/>
@@ -54591,7 +54588,7 @@
         <v>16</v>
       </c>
       <c r="Q454" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R454" s="12"/>
       <c r="T454" s="11"/>
@@ -54647,7 +54644,7 @@
         <v>16</v>
       </c>
       <c r="Q455" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R455" s="12"/>
       <c r="T455" s="11"/>
@@ -54703,7 +54700,7 @@
         <v>16</v>
       </c>
       <c r="Q456" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R456" s="12"/>
       <c r="T456" s="11"/>
@@ -54759,7 +54756,7 @@
         <v>16</v>
       </c>
       <c r="Q457" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R457" s="12"/>
       <c r="T457" s="11"/>
@@ -54815,7 +54812,7 @@
         <v>16</v>
       </c>
       <c r="Q458" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R458" s="12"/>
       <c r="T458" s="11"/>
@@ -54871,7 +54868,7 @@
         <v>16</v>
       </c>
       <c r="Q459" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R459" s="12"/>
       <c r="T459" s="11"/>
@@ -54927,7 +54924,7 @@
         <v>16</v>
       </c>
       <c r="Q460" s="21" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R460" s="12"/>
       <c r="T460" s="11"/>
@@ -54983,7 +54980,7 @@
         <v>16</v>
       </c>
       <c r="Q461" s="21" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R461" s="12"/>
       <c r="T461" s="11"/>
@@ -55039,7 +55036,7 @@
         <v>16</v>
       </c>
       <c r="Q462" s="21" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R462" s="12"/>
       <c r="T462" s="11"/>
@@ -55095,7 +55092,7 @@
         <v>16</v>
       </c>
       <c r="Q463" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R463" s="12"/>
       <c r="T463" s="11"/>
@@ -55151,7 +55148,7 @@
         <v>3217</v>
       </c>
       <c r="Q464" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R464" s="12"/>
       <c r="T464" s="11"/>
@@ -55207,7 +55204,7 @@
         <v>16</v>
       </c>
       <c r="Q465" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R465" s="12"/>
       <c r="T465" s="11"/>
@@ -55263,7 +55260,7 @@
         <v>16</v>
       </c>
       <c r="Q466" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R466" s="12"/>
       <c r="T466" s="11"/>
@@ -55319,7 +55316,7 @@
         <v>16</v>
       </c>
       <c r="Q467" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R467" s="12"/>
       <c r="T467" s="11"/>
@@ -55375,7 +55372,7 @@
         <v>16</v>
       </c>
       <c r="Q468" s="21" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R468" s="12"/>
       <c r="T468" s="11"/>
@@ -55431,7 +55428,7 @@
         <v>2359</v>
       </c>
       <c r="Q469" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R469" s="12"/>
       <c r="T469" s="11"/>
@@ -55487,7 +55484,7 @@
         <v>16</v>
       </c>
       <c r="Q470" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R470" s="12"/>
       <c r="T470" s="11"/>
@@ -55543,7 +55540,7 @@
         <v>16</v>
       </c>
       <c r="Q471" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R471" s="12"/>
       <c r="T471" s="11"/>
@@ -55599,7 +55596,7 @@
         <v>16</v>
       </c>
       <c r="Q472" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R472" s="12"/>
       <c r="T472" s="11"/>
@@ -55655,7 +55652,7 @@
         <v>2372</v>
       </c>
       <c r="Q473" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R473" s="12"/>
       <c r="T473" s="11"/>
@@ -55711,7 +55708,7 @@
         <v>16</v>
       </c>
       <c r="Q474" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R474" s="12"/>
       <c r="T474" s="11"/>
@@ -55767,7 +55764,7 @@
         <v>16</v>
       </c>
       <c r="Q475" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R475" s="12"/>
       <c r="T475" s="11"/>
@@ -55823,7 +55820,7 @@
         <v>16</v>
       </c>
       <c r="Q476" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R476" s="12"/>
       <c r="T476" s="11"/>
@@ -55879,7 +55876,7 @@
         <v>16</v>
       </c>
       <c r="Q477" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R477" s="12"/>
       <c r="T477" s="11"/>
@@ -55935,7 +55932,7 @@
         <v>16</v>
       </c>
       <c r="Q478" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R478" s="12"/>
       <c r="T478" s="11"/>
@@ -55991,7 +55988,7 @@
         <v>16</v>
       </c>
       <c r="Q479" s="21" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R479" s="12"/>
       <c r="T479" s="11"/>
@@ -56047,7 +56044,7 @@
         <v>16</v>
       </c>
       <c r="Q480" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R480" s="12"/>
       <c r="T480" s="11"/>
@@ -56103,7 +56100,7 @@
         <v>16</v>
       </c>
       <c r="Q481" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R481" s="12"/>
       <c r="T481" s="11"/>
@@ -56159,7 +56156,7 @@
         <v>16</v>
       </c>
       <c r="Q482" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R482" s="12"/>
       <c r="T482" s="11"/>
@@ -56215,7 +56212,7 @@
         <v>16</v>
       </c>
       <c r="Q483" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R483" s="12"/>
       <c r="T483" s="11"/>
@@ -56271,7 +56268,7 @@
         <v>16</v>
       </c>
       <c r="Q484" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R484" s="12"/>
       <c r="T484" s="11"/>
@@ -56327,7 +56324,7 @@
         <v>16</v>
       </c>
       <c r="Q485" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R485" s="12"/>
       <c r="T485" s="11"/>
@@ -56383,7 +56380,7 @@
         <v>16</v>
       </c>
       <c r="Q486" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R486" s="12"/>
       <c r="T486" s="11"/>
@@ -56439,7 +56436,7 @@
         <v>16</v>
       </c>
       <c r="Q487" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R487" s="12"/>
       <c r="T487" s="11"/>
@@ -56495,7 +56492,7 @@
         <v>16</v>
       </c>
       <c r="Q488" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R488" s="12"/>
       <c r="T488" s="11"/>
@@ -56551,7 +56548,7 @@
         <v>16</v>
       </c>
       <c r="Q489" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R489" s="12"/>
       <c r="T489" s="11"/>
@@ -56607,7 +56604,7 @@
         <v>16</v>
       </c>
       <c r="Q490" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R490" s="12"/>
       <c r="T490" s="11"/>
@@ -56663,7 +56660,7 @@
         <v>16</v>
       </c>
       <c r="Q491" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R491" s="12"/>
       <c r="T491" s="11"/>
@@ -56719,7 +56716,7 @@
         <v>16</v>
       </c>
       <c r="Q492" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R492" s="12"/>
       <c r="T492" s="11"/>
@@ -56775,7 +56772,7 @@
         <v>16</v>
       </c>
       <c r="Q493" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R493" s="12"/>
       <c r="T493" s="11"/>
@@ -56831,7 +56828,7 @@
         <v>16</v>
       </c>
       <c r="Q494" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R494" s="12"/>
       <c r="T494" s="11"/>
@@ -56887,7 +56884,7 @@
         <v>16</v>
       </c>
       <c r="Q495" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R495" s="12"/>
       <c r="T495" s="11"/>
@@ -56943,7 +56940,7 @@
         <v>16</v>
       </c>
       <c r="Q496" s="20" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R496" s="12"/>
       <c r="T496" s="11"/>
@@ -56999,7 +56996,7 @@
         <v>16</v>
       </c>
       <c r="Q497" s="20" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R497" s="12"/>
       <c r="T497" s="11"/>
@@ -57055,7 +57052,7 @@
         <v>16</v>
       </c>
       <c r="Q498" s="20" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R498" s="12"/>
       <c r="T498" s="11"/>
@@ -57111,7 +57108,7 @@
         <v>16</v>
       </c>
       <c r="Q499" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R499" s="12"/>
       <c r="T499" s="11"/>
@@ -57167,7 +57164,7 @@
         <v>16</v>
       </c>
       <c r="Q500" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R500" s="12"/>
       <c r="T500" s="11"/>
@@ -57223,7 +57220,7 @@
         <v>16</v>
       </c>
       <c r="Q501" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R501" s="12"/>
       <c r="T501" s="11"/>
@@ -57279,7 +57276,7 @@
         <v>16</v>
       </c>
       <c r="Q502" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R502" s="12"/>
       <c r="T502" s="11"/>
@@ -57335,7 +57332,7 @@
         <v>16</v>
       </c>
       <c r="Q503" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R503" s="12"/>
       <c r="T503" s="11"/>
@@ -57391,7 +57388,7 @@
         <v>16</v>
       </c>
       <c r="Q504" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R504" s="12"/>
       <c r="T504" s="11"/>
@@ -57447,7 +57444,7 @@
         <v>16</v>
       </c>
       <c r="Q505" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R505" s="12"/>
       <c r="T505" s="11"/>
@@ -57503,7 +57500,7 @@
         <v>16</v>
       </c>
       <c r="Q506" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R506" s="12"/>
       <c r="T506" s="11"/>
@@ -57559,7 +57556,7 @@
         <v>16</v>
       </c>
       <c r="Q507" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R507" s="12"/>
       <c r="T507" s="11"/>
@@ -57615,7 +57612,7 @@
         <v>16</v>
       </c>
       <c r="Q508" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R508" s="12"/>
       <c r="T508" s="11"/>
@@ -57671,7 +57668,7 @@
         <v>16</v>
       </c>
       <c r="Q509" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R509" s="12"/>
       <c r="T509" s="11"/>
@@ -57727,7 +57724,7 @@
         <v>16</v>
       </c>
       <c r="Q510" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R510" s="12"/>
       <c r="T510" s="11"/>
@@ -57783,7 +57780,7 @@
         <v>16</v>
       </c>
       <c r="Q511" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R511" s="12"/>
       <c r="T511" s="11"/>
@@ -57839,7 +57836,7 @@
         <v>2483</v>
       </c>
       <c r="Q512" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R512" s="12"/>
       <c r="T512" s="11"/>
@@ -57895,7 +57892,7 @@
         <v>16</v>
       </c>
       <c r="Q513" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R513" s="12"/>
       <c r="T513" s="11"/>
@@ -57951,7 +57948,7 @@
         <v>16</v>
       </c>
       <c r="Q514" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R514" s="12"/>
       <c r="T514" s="11"/>
@@ -58007,7 +58004,7 @@
         <v>16</v>
       </c>
       <c r="Q515" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R515" s="12"/>
       <c r="T515" s="11"/>
@@ -58063,7 +58060,7 @@
         <v>16</v>
       </c>
       <c r="Q516" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R516" s="12"/>
       <c r="T516" s="11"/>
@@ -58119,7 +58116,7 @@
         <v>16</v>
       </c>
       <c r="Q517" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R517" s="12"/>
       <c r="T517" s="11"/>
@@ -58175,7 +58172,7 @@
         <v>16</v>
       </c>
       <c r="Q518" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R518" s="12"/>
       <c r="T518" s="11"/>
@@ -58231,7 +58228,7 @@
         <v>16</v>
       </c>
       <c r="Q519" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R519" s="12"/>
       <c r="T519" s="11"/>
@@ -58287,7 +58284,7 @@
         <v>16</v>
       </c>
       <c r="Q520" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R520" s="12"/>
       <c r="T520" s="11"/>
@@ -58343,7 +58340,7 @@
         <v>16</v>
       </c>
       <c r="Q521" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R521" s="12"/>
       <c r="T521" s="11"/>
@@ -58399,7 +58396,7 @@
         <v>16</v>
       </c>
       <c r="Q522" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R522" s="12"/>
       <c r="T522" s="11"/>
@@ -58455,7 +58452,7 @@
         <v>16</v>
       </c>
       <c r="Q523" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R523" s="12"/>
       <c r="T523" s="11"/>
@@ -58511,7 +58508,7 @@
         <v>16</v>
       </c>
       <c r="Q524" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R524" s="12"/>
       <c r="T524" s="11"/>
@@ -58567,7 +58564,7 @@
         <v>16</v>
       </c>
       <c r="Q525" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R525" s="12"/>
       <c r="T525" s="11"/>
@@ -58623,7 +58620,7 @@
         <v>16</v>
       </c>
       <c r="Q526" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R526" s="12"/>
       <c r="T526" s="11"/>
@@ -58679,7 +58676,7 @@
         <v>16</v>
       </c>
       <c r="Q527" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R527" s="12"/>
       <c r="T527" s="11"/>
@@ -58735,7 +58732,7 @@
         <v>16</v>
       </c>
       <c r="Q528" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R528" s="12"/>
       <c r="T528" s="11"/>
@@ -58773,7 +58770,7 @@
         <v>0</v>
       </c>
       <c r="K529" s="44" t="s">
-        <v>3975</v>
+        <v>3957</v>
       </c>
       <c r="L529" s="27" t="s">
         <v>3777</v>
@@ -58791,7 +58788,7 @@
         <v>16</v>
       </c>
       <c r="Q529" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R529" s="12"/>
       <c r="T529" s="11"/>
@@ -58847,7 +58844,7 @@
         <v>16</v>
       </c>
       <c r="Q530" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R530" s="12"/>
       <c r="T530" s="11"/>
@@ -58903,7 +58900,7 @@
         <v>16</v>
       </c>
       <c r="Q531" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R531" s="12"/>
       <c r="T531" s="11"/>
@@ -58959,7 +58956,7 @@
         <v>16</v>
       </c>
       <c r="Q532" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R532" s="12"/>
       <c r="T532" s="11"/>
@@ -59015,7 +59012,7 @@
         <v>16</v>
       </c>
       <c r="Q533" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R533" s="12"/>
       <c r="T533" s="11"/>
@@ -59071,7 +59068,7 @@
         <v>16</v>
       </c>
       <c r="Q534" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R534" s="12"/>
       <c r="T534" s="11"/>
@@ -59127,7 +59124,7 @@
         <v>16</v>
       </c>
       <c r="Q535" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R535" s="12"/>
       <c r="T535" s="11"/>
@@ -59183,7 +59180,7 @@
         <v>16</v>
       </c>
       <c r="Q536" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R536" s="12"/>
       <c r="T536" s="11"/>
@@ -59239,7 +59236,7 @@
         <v>16</v>
       </c>
       <c r="Q537" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R537" s="12"/>
       <c r="T537" s="11"/>
@@ -59295,7 +59292,7 @@
         <v>16</v>
       </c>
       <c r="Q538" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R538" s="12"/>
       <c r="T538" s="11"/>
@@ -59351,7 +59348,7 @@
         <v>16</v>
       </c>
       <c r="Q539" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R539" s="12"/>
       <c r="T539" s="11"/>
@@ -59407,7 +59404,7 @@
         <v>16</v>
       </c>
       <c r="Q540" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R540" s="12"/>
       <c r="T540" s="11"/>
@@ -59463,7 +59460,7 @@
         <v>16</v>
       </c>
       <c r="Q541" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R541" s="12"/>
       <c r="T541" s="11"/>
@@ -59519,7 +59516,7 @@
         <v>16</v>
       </c>
       <c r="Q542" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R542" s="12"/>
       <c r="T542" s="11"/>
@@ -59575,7 +59572,7 @@
         <v>16</v>
       </c>
       <c r="Q543" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R543" s="12"/>
       <c r="T543" s="11"/>
@@ -59631,7 +59628,7 @@
         <v>16</v>
       </c>
       <c r="Q544" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R544" s="12"/>
       <c r="T544" s="11"/>
@@ -59687,7 +59684,7 @@
         <v>16</v>
       </c>
       <c r="Q545" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R545" s="12"/>
       <c r="T545" s="11"/>
@@ -59743,7 +59740,7 @@
         <v>16</v>
       </c>
       <c r="Q546" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R546" s="12"/>
       <c r="T546" s="11"/>
@@ -59799,7 +59796,7 @@
         <v>16</v>
       </c>
       <c r="Q547" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R547" s="12"/>
       <c r="T547" s="11"/>
@@ -59855,7 +59852,7 @@
         <v>16</v>
       </c>
       <c r="Q548" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R548" s="12"/>
       <c r="T548" s="11"/>
@@ -59911,7 +59908,7 @@
         <v>16</v>
       </c>
       <c r="Q549" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R549" s="12"/>
       <c r="T549" s="11"/>
@@ -59967,7 +59964,7 @@
         <v>16</v>
       </c>
       <c r="Q550" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R550" s="12"/>
       <c r="T550" s="11"/>
@@ -60023,7 +60020,7 @@
         <v>16</v>
       </c>
       <c r="Q551" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R551" s="12"/>
       <c r="T551" s="11"/>
@@ -60079,7 +60076,7 @@
         <v>16</v>
       </c>
       <c r="Q552" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R552" s="12"/>
       <c r="T552" s="11"/>
@@ -60135,7 +60132,7 @@
         <v>16</v>
       </c>
       <c r="Q553" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R553" s="12"/>
       <c r="T553" s="11"/>
@@ -60191,7 +60188,7 @@
         <v>16</v>
       </c>
       <c r="Q554" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R554" s="12"/>
       <c r="T554" s="11"/>
@@ -60247,7 +60244,7 @@
         <v>16</v>
       </c>
       <c r="Q555" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R555" s="12"/>
       <c r="T555" s="11"/>
@@ -60303,7 +60300,7 @@
         <v>16</v>
       </c>
       <c r="Q556" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R556" s="12"/>
       <c r="T556" s="11"/>
@@ -60359,7 +60356,7 @@
         <v>16</v>
       </c>
       <c r="Q557" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R557" s="12"/>
       <c r="T557" s="11"/>
@@ -60415,7 +60412,7 @@
         <v>16</v>
       </c>
       <c r="Q558" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R558" s="12"/>
       <c r="T558" s="11"/>
@@ -60471,7 +60468,7 @@
         <v>16</v>
       </c>
       <c r="Q559" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R559" s="12"/>
       <c r="T559" s="11"/>
@@ -60527,7 +60524,7 @@
         <v>16</v>
       </c>
       <c r="Q560" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R560" s="12"/>
       <c r="T560" s="11"/>
@@ -60583,7 +60580,7 @@
         <v>16</v>
       </c>
       <c r="Q561" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R561" s="12"/>
       <c r="T561" s="11"/>
@@ -60639,7 +60636,7 @@
         <v>16</v>
       </c>
       <c r="Q562" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R562" s="12"/>
       <c r="T562" s="11"/>
@@ -60695,7 +60692,7 @@
         <v>16</v>
       </c>
       <c r="Q563" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R563" s="12"/>
       <c r="T563" s="11"/>
@@ -60751,7 +60748,7 @@
         <v>16</v>
       </c>
       <c r="Q564" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R564" s="12"/>
       <c r="T564" s="11"/>
@@ -60807,7 +60804,7 @@
         <v>16</v>
       </c>
       <c r="Q565" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R565" s="12"/>
       <c r="T565" s="11"/>
@@ -60863,7 +60860,7 @@
         <v>16</v>
       </c>
       <c r="Q566" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R566" s="12"/>
       <c r="T566" s="11"/>
@@ -60919,7 +60916,7 @@
         <v>16</v>
       </c>
       <c r="Q567" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R567" s="12"/>
       <c r="T567" s="11"/>
@@ -60975,7 +60972,7 @@
         <v>16</v>
       </c>
       <c r="Q568" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R568" s="12"/>
       <c r="T568" s="11"/>
@@ -61031,7 +61028,7 @@
         <v>16</v>
       </c>
       <c r="Q569" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R569" s="12"/>
       <c r="T569" s="11"/>
@@ -61087,7 +61084,7 @@
         <v>16</v>
       </c>
       <c r="Q570" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R570" s="12"/>
       <c r="T570" s="11"/>
@@ -61143,7 +61140,7 @@
         <v>16</v>
       </c>
       <c r="Q571" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R571" s="12"/>
       <c r="T571" s="11"/>
@@ -61199,7 +61196,7 @@
         <v>16</v>
       </c>
       <c r="Q572" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R572" s="12"/>
       <c r="T572" s="11"/>
@@ -61255,7 +61252,7 @@
         <v>16</v>
       </c>
       <c r="Q573" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R573" s="12"/>
       <c r="T573" s="11"/>
@@ -61311,7 +61308,7 @@
         <v>16</v>
       </c>
       <c r="Q574" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R574" s="12"/>
       <c r="T574" s="11"/>
@@ -61367,7 +61364,7 @@
         <v>16</v>
       </c>
       <c r="Q575" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R575" s="12"/>
       <c r="T575" s="11"/>
@@ -61423,7 +61420,7 @@
         <v>16</v>
       </c>
       <c r="Q576" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R576" s="12"/>
       <c r="T576" s="11"/>
@@ -61479,7 +61476,7 @@
         <v>16</v>
       </c>
       <c r="Q577" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R577" s="12"/>
       <c r="T577" s="11"/>
@@ -61535,7 +61532,7 @@
         <v>16</v>
       </c>
       <c r="Q578" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R578" s="12"/>
       <c r="T578" s="11"/>
@@ -61591,7 +61588,7 @@
         <v>2671</v>
       </c>
       <c r="Q579" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R579" s="12"/>
       <c r="T579" s="11"/>
@@ -61647,7 +61644,7 @@
         <v>16</v>
       </c>
       <c r="Q580" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R580" s="12"/>
       <c r="T580" s="11"/>
@@ -61703,7 +61700,7 @@
         <v>16</v>
       </c>
       <c r="Q581" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R581" s="12"/>
       <c r="T581" s="11"/>
@@ -61759,7 +61756,7 @@
         <v>16</v>
       </c>
       <c r="Q582" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R582" s="12"/>
       <c r="T582" s="11"/>
@@ -61815,7 +61812,7 @@
         <v>16</v>
       </c>
       <c r="Q583" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R583" s="12"/>
       <c r="T583" s="11"/>
@@ -61871,7 +61868,7 @@
         <v>16</v>
       </c>
       <c r="Q584" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R584" s="12"/>
       <c r="T584" s="11"/>
@@ -61927,7 +61924,7 @@
         <v>16</v>
       </c>
       <c r="Q585" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R585" s="12"/>
       <c r="T585" s="11"/>
@@ -61983,7 +61980,7 @@
         <v>16</v>
       </c>
       <c r="Q586" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R586" s="12"/>
       <c r="T586" s="11"/>
@@ -62039,7 +62036,7 @@
         <v>16</v>
       </c>
       <c r="Q587" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R587" s="12"/>
       <c r="T587" s="11"/>
@@ -62095,7 +62092,7 @@
         <v>16</v>
       </c>
       <c r="Q588" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R588" s="12"/>
       <c r="T588" s="11"/>
@@ -62136,7 +62133,7 @@
         <v>16</v>
       </c>
       <c r="L589" s="27" t="s">
-        <v>3837</v>
+        <v>3973</v>
       </c>
       <c r="M589" s="27" t="s">
         <v>2690</v>
@@ -62151,7 +62148,7 @@
         <v>16</v>
       </c>
       <c r="Q589" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R589" s="12"/>
       <c r="T589" s="11"/>
@@ -62192,7 +62189,7 @@
         <v>16</v>
       </c>
       <c r="L590" s="27" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="M590" s="27" t="s">
         <v>2693</v>
@@ -62207,7 +62204,7 @@
         <v>16</v>
       </c>
       <c r="Q590" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R590" s="12"/>
       <c r="T590" s="11"/>
@@ -62248,7 +62245,7 @@
         <v>16</v>
       </c>
       <c r="L591" s="27" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="M591" s="27" t="s">
         <v>2696</v>
@@ -62263,7 +62260,7 @@
         <v>16</v>
       </c>
       <c r="Q591" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R591" s="12"/>
       <c r="T591" s="11"/>
@@ -62304,7 +62301,7 @@
         <v>16</v>
       </c>
       <c r="L592" s="27" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="M592" s="27" t="s">
         <v>2699</v>
@@ -62319,7 +62316,7 @@
         <v>16</v>
       </c>
       <c r="Q592" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R592" s="12"/>
       <c r="T592" s="11"/>
@@ -62360,7 +62357,7 @@
         <v>16</v>
       </c>
       <c r="L593" s="27" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="M593" s="27" t="s">
         <v>2701</v>
@@ -62375,7 +62372,7 @@
         <v>16</v>
       </c>
       <c r="Q593" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R593" s="12"/>
       <c r="T593" s="11"/>
@@ -62416,7 +62413,7 @@
         <v>16</v>
       </c>
       <c r="L594" s="27" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="M594" s="27" t="s">
         <v>2703</v>
@@ -62431,7 +62428,7 @@
         <v>16</v>
       </c>
       <c r="Q594" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R594" s="12"/>
       <c r="T594" s="11"/>
@@ -62472,7 +62469,7 @@
         <v>934</v>
       </c>
       <c r="L595" s="27" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="M595" s="27" t="s">
         <v>2706</v>
@@ -62487,7 +62484,7 @@
         <v>16</v>
       </c>
       <c r="Q595" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R595" s="12"/>
       <c r="T595" s="11"/>
@@ -62528,7 +62525,7 @@
         <v>16</v>
       </c>
       <c r="L596" s="27" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="M596" s="27" t="s">
         <v>2708</v>
@@ -62543,7 +62540,7 @@
         <v>16</v>
       </c>
       <c r="Q596" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R596" s="12"/>
       <c r="T596" s="11"/>
@@ -62584,7 +62581,7 @@
         <v>16</v>
       </c>
       <c r="L597" s="27" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="M597" s="27" t="s">
         <v>2710</v>
@@ -62599,7 +62596,7 @@
         <v>16</v>
       </c>
       <c r="Q597" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R597" s="12"/>
       <c r="T597" s="11"/>
@@ -62640,7 +62637,7 @@
         <v>1058</v>
       </c>
       <c r="L598" s="27" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="M598" s="27" t="s">
         <v>2712</v>
@@ -62655,7 +62652,7 @@
         <v>16</v>
       </c>
       <c r="Q598" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R598" s="12"/>
       <c r="T598" s="11"/>
@@ -62696,7 +62693,7 @@
         <v>1058</v>
       </c>
       <c r="L599" s="27" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="M599" s="27" t="s">
         <v>2714</v>
@@ -62711,7 +62708,7 @@
         <v>16</v>
       </c>
       <c r="Q599" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R599" s="12"/>
       <c r="T599" s="11"/>
@@ -62752,7 +62749,7 @@
         <v>1059</v>
       </c>
       <c r="L600" s="27" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="M600" s="27" t="s">
         <v>2716</v>
@@ -62767,7 +62764,7 @@
         <v>16</v>
       </c>
       <c r="Q600" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R600" s="12"/>
       <c r="T600" s="11"/>
@@ -62808,7 +62805,7 @@
         <v>1060</v>
       </c>
       <c r="L601" s="27" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="M601" s="27" t="s">
         <v>2718</v>
@@ -62823,7 +62820,7 @@
         <v>16</v>
       </c>
       <c r="Q601" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R601" s="12"/>
       <c r="T601" s="11"/>
@@ -62864,7 +62861,7 @@
         <v>16</v>
       </c>
       <c r="L602" s="27" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="M602" s="27" t="s">
         <v>2720</v>
@@ -62879,7 +62876,7 @@
         <v>16</v>
       </c>
       <c r="Q602" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R602" s="12"/>
       <c r="T602" s="11"/>
@@ -62920,7 +62917,7 @@
         <v>16</v>
       </c>
       <c r="L603" s="27" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="M603" s="27" t="s">
         <v>2722</v>
@@ -62935,7 +62932,7 @@
         <v>16</v>
       </c>
       <c r="Q603" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R603" s="12"/>
       <c r="T603" s="11"/>
@@ -62976,7 +62973,7 @@
         <v>16</v>
       </c>
       <c r="L604" s="27" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="M604" s="27" t="s">
         <v>2724</v>
@@ -62991,7 +62988,7 @@
         <v>16</v>
       </c>
       <c r="Q604" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R604" s="12"/>
       <c r="T604" s="11"/>
@@ -63032,7 +63029,7 @@
         <v>1061</v>
       </c>
       <c r="L605" s="27" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="M605" s="27" t="s">
         <v>2726</v>
@@ -63047,7 +63044,7 @@
         <v>16</v>
       </c>
       <c r="Q605" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R605" s="12"/>
       <c r="T605" s="11"/>
@@ -63088,7 +63085,7 @@
         <v>1062</v>
       </c>
       <c r="L606" s="27" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="M606" s="27" t="s">
         <v>2728</v>
@@ -63103,7 +63100,7 @@
         <v>16</v>
       </c>
       <c r="Q606" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R606" s="12"/>
       <c r="T606" s="11"/>
@@ -63144,7 +63141,7 @@
         <v>1063</v>
       </c>
       <c r="L607" s="27" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="M607" s="27" t="s">
         <v>2730</v>
@@ -63159,7 +63156,7 @@
         <v>16</v>
       </c>
       <c r="Q607" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R607" s="12"/>
       <c r="T607" s="11"/>
@@ -63200,7 +63197,7 @@
         <v>1064</v>
       </c>
       <c r="L608" s="27" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="M608" s="27" t="s">
         <v>2732</v>
@@ -63215,7 +63212,7 @@
         <v>16</v>
       </c>
       <c r="Q608" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R608" s="12"/>
       <c r="T608" s="11"/>
@@ -63256,7 +63253,7 @@
         <v>1065</v>
       </c>
       <c r="L609" s="27" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="M609" s="27" t="s">
         <v>2734</v>
@@ -63271,7 +63268,7 @@
         <v>16</v>
       </c>
       <c r="Q609" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R609" s="12"/>
       <c r="T609" s="11"/>
@@ -63312,7 +63309,7 @@
         <v>1081</v>
       </c>
       <c r="L610" s="27" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="M610" s="27" t="s">
         <v>2736</v>
@@ -63327,7 +63324,7 @@
         <v>16</v>
       </c>
       <c r="Q610" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R610" s="12"/>
       <c r="T610" s="11"/>
@@ -63368,7 +63365,7 @@
         <v>1066</v>
       </c>
       <c r="L611" s="27" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="M611" s="27" t="s">
         <v>2738</v>
@@ -63383,7 +63380,7 @@
         <v>16</v>
       </c>
       <c r="Q611" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R611" s="12"/>
       <c r="T611" s="11"/>
@@ -63424,7 +63421,7 @@
         <v>1067</v>
       </c>
       <c r="L612" s="27" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="M612" s="27" t="s">
         <v>2740</v>
@@ -63439,7 +63436,7 @@
         <v>16</v>
       </c>
       <c r="Q612" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R612" s="12"/>
       <c r="T612" s="11"/>
@@ -63480,7 +63477,7 @@
         <v>1067</v>
       </c>
       <c r="L613" s="27" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="M613" s="27" t="s">
         <v>2742</v>
@@ -63495,7 +63492,7 @@
         <v>16</v>
       </c>
       <c r="Q613" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R613" s="12"/>
       <c r="T613" s="11"/>
@@ -63536,7 +63533,7 @@
         <v>920</v>
       </c>
       <c r="L614" s="27" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="M614" s="27" t="s">
         <v>2744</v>
@@ -63551,7 +63548,7 @@
         <v>16</v>
       </c>
       <c r="Q614" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R614" s="12"/>
       <c r="T614" s="11"/>
@@ -63592,7 +63589,7 @@
         <v>1068</v>
       </c>
       <c r="L615" s="27" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="M615" s="27" t="s">
         <v>2746</v>
@@ -63607,7 +63604,7 @@
         <v>16</v>
       </c>
       <c r="Q615" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R615" s="12"/>
       <c r="T615" s="11"/>
@@ -63648,7 +63645,7 @@
         <v>16</v>
       </c>
       <c r="L616" s="27" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="M616" s="27" t="s">
         <v>2748</v>
@@ -63663,7 +63660,7 @@
         <v>16</v>
       </c>
       <c r="Q616" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R616" s="12"/>
       <c r="T616" s="11"/>
@@ -63704,7 +63701,7 @@
         <v>1068</v>
       </c>
       <c r="L617" s="27" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="M617" s="27" t="s">
         <v>2750</v>
@@ -63719,7 +63716,7 @@
         <v>16</v>
       </c>
       <c r="Q617" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R617" s="12"/>
       <c r="T617" s="11"/>
@@ -63760,7 +63757,7 @@
         <v>1069</v>
       </c>
       <c r="L618" s="27" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="M618" s="27" t="s">
         <v>2752</v>
@@ -63775,7 +63772,7 @@
         <v>16</v>
       </c>
       <c r="Q618" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R618" s="12"/>
       <c r="T618" s="11"/>
@@ -63816,7 +63813,7 @@
         <v>1070</v>
       </c>
       <c r="L619" s="27" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="M619" s="27" t="s">
         <v>2754</v>
@@ -63831,7 +63828,7 @@
         <v>16</v>
       </c>
       <c r="Q619" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R619" s="12"/>
       <c r="T619" s="11"/>
@@ -63872,7 +63869,7 @@
         <v>1071</v>
       </c>
       <c r="L620" s="27" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="M620" s="27" t="s">
         <v>2756</v>
@@ -63887,7 +63884,7 @@
         <v>16</v>
       </c>
       <c r="Q620" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R620" s="12"/>
       <c r="T620" s="11"/>
@@ -63928,7 +63925,7 @@
         <v>1069</v>
       </c>
       <c r="L621" s="27" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="M621" s="27" t="s">
         <v>2758</v>
@@ -63943,7 +63940,7 @@
         <v>16</v>
       </c>
       <c r="Q621" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R621" s="12"/>
       <c r="T621" s="11"/>
@@ -63984,7 +63981,7 @@
         <v>1072</v>
       </c>
       <c r="L622" s="27" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="M622" s="27" t="s">
         <v>2760</v>
@@ -63999,7 +63996,7 @@
         <v>16</v>
       </c>
       <c r="Q622" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R622" s="12"/>
       <c r="T622" s="11"/>
@@ -64040,7 +64037,7 @@
         <v>1073</v>
       </c>
       <c r="L623" s="27" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="M623" s="27" t="s">
         <v>2762</v>
@@ -64055,7 +64052,7 @@
         <v>16</v>
       </c>
       <c r="Q623" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R623" s="12"/>
       <c r="T623" s="11"/>
@@ -64096,7 +64093,7 @@
         <v>1067</v>
       </c>
       <c r="L624" s="27" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="M624" s="27" t="s">
         <v>2764</v>
@@ -64111,7 +64108,7 @@
         <v>16</v>
       </c>
       <c r="Q624" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R624" s="12"/>
       <c r="T624" s="11"/>
@@ -64152,7 +64149,7 @@
         <v>1067</v>
       </c>
       <c r="L625" s="27" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="M625" s="27" t="s">
         <v>2766</v>
@@ -64167,7 +64164,7 @@
         <v>16</v>
       </c>
       <c r="Q625" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R625" s="12"/>
       <c r="T625" s="11"/>
@@ -64208,7 +64205,7 @@
         <v>16</v>
       </c>
       <c r="L626" s="27" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="M626" s="27" t="s">
         <v>2768</v>
@@ -64223,7 +64220,7 @@
         <v>16</v>
       </c>
       <c r="Q626" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R626" s="12"/>
       <c r="T626" s="11"/>
@@ -64264,7 +64261,7 @@
         <v>1072</v>
       </c>
       <c r="L627" s="27" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="M627" s="27" t="s">
         <v>2770</v>
@@ -64279,7 +64276,7 @@
         <v>16</v>
       </c>
       <c r="Q627" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R627" s="12"/>
       <c r="T627" s="11"/>
@@ -64320,7 +64317,7 @@
         <v>1074</v>
       </c>
       <c r="L628" s="27" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="M628" s="27" t="s">
         <v>2772</v>
@@ -64335,7 +64332,7 @@
         <v>16</v>
       </c>
       <c r="Q628" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R628" s="12"/>
       <c r="T628" s="11"/>
@@ -64376,7 +64373,7 @@
         <v>1061</v>
       </c>
       <c r="L629" s="27" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="M629" s="27" t="s">
         <v>2774</v>
@@ -64391,7 +64388,7 @@
         <v>16</v>
       </c>
       <c r="Q629" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R629" s="12"/>
       <c r="T629" s="11"/>
@@ -64432,7 +64429,7 @@
         <v>1075</v>
       </c>
       <c r="L630" s="27" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="M630" s="27" t="s">
         <v>2776</v>
@@ -64447,7 +64444,7 @@
         <v>16</v>
       </c>
       <c r="Q630" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R630" s="12"/>
       <c r="T630" s="11"/>
@@ -64488,7 +64485,7 @@
         <v>1076</v>
       </c>
       <c r="L631" s="27" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="M631" s="27" t="s">
         <v>2778</v>
@@ -64503,7 +64500,7 @@
         <v>16</v>
       </c>
       <c r="Q631" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R631" s="12"/>
       <c r="T631" s="11"/>
@@ -64544,7 +64541,7 @@
         <v>1067</v>
       </c>
       <c r="L632" s="27" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="M632" s="27" t="s">
         <v>2780</v>
@@ -64559,7 +64556,7 @@
         <v>16</v>
       </c>
       <c r="Q632" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R632" s="12"/>
       <c r="T632" s="11"/>
@@ -64600,7 +64597,7 @@
         <v>1077</v>
       </c>
       <c r="L633" s="27" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="M633" s="27" t="s">
         <v>2782</v>
@@ -64615,7 +64612,7 @@
         <v>16</v>
       </c>
       <c r="Q633" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R633" s="12"/>
       <c r="T633" s="11"/>
@@ -64656,7 +64653,7 @@
         <v>1067</v>
       </c>
       <c r="L634" s="27" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="M634" s="27" t="s">
         <v>2784</v>
@@ -64671,7 +64668,7 @@
         <v>16</v>
       </c>
       <c r="Q634" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R634" s="12"/>
       <c r="T634" s="11"/>
@@ -64712,7 +64709,7 @@
         <v>1067</v>
       </c>
       <c r="L635" s="27" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="M635" s="27" t="s">
         <v>2786</v>
@@ -64727,7 +64724,7 @@
         <v>16</v>
       </c>
       <c r="Q635" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R635" s="12"/>
       <c r="T635" s="11"/>
@@ -64768,7 +64765,7 @@
         <v>1067</v>
       </c>
       <c r="L636" s="27" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="M636" s="27" t="s">
         <v>2788</v>
@@ -64783,7 +64780,7 @@
         <v>16</v>
       </c>
       <c r="Q636" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R636" s="12"/>
       <c r="T636" s="11"/>
@@ -64824,7 +64821,7 @@
         <v>1078</v>
       </c>
       <c r="L637" s="27" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="M637" s="27" t="s">
         <v>2790</v>
@@ -64839,7 +64836,7 @@
         <v>16</v>
       </c>
       <c r="Q637" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R637" s="12"/>
       <c r="T637" s="11"/>
@@ -64880,7 +64877,7 @@
         <v>1079</v>
       </c>
       <c r="L638" s="27" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="M638" s="27" t="s">
         <v>2792</v>
@@ -64895,7 +64892,7 @@
         <v>16</v>
       </c>
       <c r="Q638" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R638" s="12"/>
       <c r="T638" s="11"/>
@@ -64936,7 +64933,7 @@
         <v>1080</v>
       </c>
       <c r="L639" s="27" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="M639" s="27" t="s">
         <v>2794</v>
@@ -64951,7 +64948,7 @@
         <v>16</v>
       </c>
       <c r="Q639" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R639" s="12"/>
       <c r="T639" s="11"/>
@@ -64992,7 +64989,7 @@
         <v>1067</v>
       </c>
       <c r="L640" s="27" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="M640" s="27" t="s">
         <v>2796</v>
@@ -65007,7 +65004,7 @@
         <v>16</v>
       </c>
       <c r="Q640" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R640" s="12"/>
       <c r="T640" s="11"/>
@@ -65048,7 +65045,7 @@
         <v>46</v>
       </c>
       <c r="L641" s="27" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="M641" s="27" t="s">
         <v>2798</v>
@@ -65063,7 +65060,7 @@
         <v>16</v>
       </c>
       <c r="Q641" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R641" s="12"/>
       <c r="T641" s="11"/>
@@ -65104,7 +65101,7 @@
         <v>148</v>
       </c>
       <c r="L642" s="27" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="M642" s="27" t="s">
         <v>2800</v>
@@ -65119,7 +65116,7 @@
         <v>16</v>
       </c>
       <c r="Q642" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R642" s="12"/>
       <c r="T642" s="11"/>
@@ -65160,7 +65157,7 @@
         <v>63</v>
       </c>
       <c r="L643" s="27" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="M643" s="27" t="s">
         <v>2802</v>
@@ -65175,7 +65172,7 @@
         <v>16</v>
       </c>
       <c r="Q643" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R643" s="12"/>
       <c r="T643" s="11"/>
@@ -65216,7 +65213,7 @@
         <v>31</v>
       </c>
       <c r="L644" s="27" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="M644" s="27" t="s">
         <v>2804</v>
@@ -65231,7 +65228,7 @@
         <v>16</v>
       </c>
       <c r="Q644" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R644" s="12"/>
       <c r="T644" s="11"/>
@@ -65272,7 +65269,7 @@
         <v>46</v>
       </c>
       <c r="L645" s="27" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="M645" s="27" t="s">
         <v>2806</v>
@@ -65287,7 +65284,7 @@
         <v>16</v>
       </c>
       <c r="Q645" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R645" s="12"/>
       <c r="T645" s="11"/>
@@ -65328,7 +65325,7 @@
         <v>1082</v>
       </c>
       <c r="L646" s="27" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="M646" s="27" t="s">
         <v>2809</v>
@@ -65343,7 +65340,7 @@
         <v>16</v>
       </c>
       <c r="Q646" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R646" s="12"/>
       <c r="T646" s="11"/>
@@ -65384,7 +65381,7 @@
         <v>1082</v>
       </c>
       <c r="L647" s="27" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="M647" s="27" t="s">
         <v>2811</v>
@@ -65399,7 +65396,7 @@
         <v>16</v>
       </c>
       <c r="Q647" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R647" s="12"/>
       <c r="T647" s="11"/>
@@ -65440,7 +65437,7 @@
         <v>46</v>
       </c>
       <c r="L648" s="27" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="M648" s="27" t="s">
         <v>2813</v>
@@ -65455,7 +65452,7 @@
         <v>16</v>
       </c>
       <c r="Q648" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R648" s="12"/>
       <c r="T648" s="11"/>
@@ -65496,7 +65493,7 @@
         <v>229</v>
       </c>
       <c r="L649" s="27" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="M649" s="27" t="s">
         <v>2816</v>
@@ -65511,7 +65508,7 @@
         <v>16</v>
       </c>
       <c r="Q649" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R649" s="12"/>
       <c r="T649" s="11"/>
@@ -65552,7 +65549,7 @@
         <v>22</v>
       </c>
       <c r="L650" s="27" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="M650" s="27" t="s">
         <v>2819</v>
@@ -65567,7 +65564,7 @@
         <v>16</v>
       </c>
       <c r="Q650" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R650" s="12"/>
       <c r="T650" s="11"/>
@@ -65608,7 +65605,7 @@
         <v>74</v>
       </c>
       <c r="L651" s="27" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="M651" s="27" t="s">
         <v>2821</v>
@@ -65623,7 +65620,7 @@
         <v>16</v>
       </c>
       <c r="Q651" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R651" s="12"/>
       <c r="T651" s="11"/>
@@ -65664,7 +65661,7 @@
         <v>74</v>
       </c>
       <c r="L652" s="27" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="M652" s="27" t="s">
         <v>2823</v>
@@ -65679,7 +65676,7 @@
         <v>16</v>
       </c>
       <c r="Q652" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R652" s="12"/>
       <c r="T652" s="11"/>
@@ -65720,7 +65717,7 @@
         <v>806</v>
       </c>
       <c r="L653" s="27" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="M653" s="27" t="s">
         <v>2826</v>
@@ -65735,7 +65732,7 @@
         <v>16</v>
       </c>
       <c r="Q653" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R653" s="12"/>
       <c r="T653" s="11"/>
@@ -65776,7 +65773,7 @@
         <v>711</v>
       </c>
       <c r="L654" s="27" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="M654" s="27" t="s">
         <v>2829</v>
@@ -65791,7 +65788,7 @@
         <v>16</v>
       </c>
       <c r="Q654" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R654" s="12"/>
       <c r="T654" s="11"/>
@@ -65832,7 +65829,7 @@
         <v>106</v>
       </c>
       <c r="L655" s="27" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="M655" s="27" t="s">
         <v>2831</v>
@@ -65847,7 +65844,7 @@
         <v>16</v>
       </c>
       <c r="Q655" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R655" s="12"/>
       <c r="T655" s="11"/>
@@ -65888,7 +65885,7 @@
         <v>711</v>
       </c>
       <c r="L656" s="27" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="M656" s="27" t="s">
         <v>2834</v>
@@ -65903,7 +65900,7 @@
         <v>16</v>
       </c>
       <c r="Q656" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R656" s="12"/>
       <c r="T656" s="11"/>
@@ -65944,7 +65941,7 @@
         <v>16</v>
       </c>
       <c r="L657" s="27" t="s">
-        <v>3905</v>
+        <v>3974</v>
       </c>
       <c r="M657" s="27" t="s">
         <v>2837</v>
@@ -65959,7 +65956,7 @@
         <v>16</v>
       </c>
       <c r="Q657" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R657" s="12"/>
       <c r="T657" s="11"/>
@@ -66000,7 +65997,7 @@
         <v>46</v>
       </c>
       <c r="L658" s="27" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
       <c r="M658" s="27" t="s">
         <v>2840</v>
@@ -66015,7 +66012,7 @@
         <v>16</v>
       </c>
       <c r="Q658" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R658" s="12"/>
       <c r="T658" s="11"/>
@@ -66056,7 +66053,7 @@
         <v>524</v>
       </c>
       <c r="L659" s="27" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="M659" s="27" t="s">
         <v>2843</v>
@@ -66071,7 +66068,7 @@
         <v>2846</v>
       </c>
       <c r="Q659" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R659" s="12"/>
       <c r="T659" s="11"/>
@@ -66112,7 +66109,7 @@
         <v>91</v>
       </c>
       <c r="L660" s="27" t="s">
-        <v>3908</v>
+        <v>3906</v>
       </c>
       <c r="M660" s="27" t="s">
         <v>2847</v>
@@ -66127,7 +66124,7 @@
         <v>16</v>
       </c>
       <c r="Q660" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R660" s="12"/>
       <c r="T660" s="11"/>
@@ -66168,7 +66165,7 @@
         <v>22</v>
       </c>
       <c r="L661" s="27" t="s">
-        <v>3909</v>
+        <v>3907</v>
       </c>
       <c r="M661" s="27" t="s">
         <v>2850</v>
@@ -66183,7 +66180,7 @@
         <v>16</v>
       </c>
       <c r="Q661" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R661" s="12"/>
       <c r="T661" s="11"/>
@@ -66224,7 +66221,7 @@
         <v>16</v>
       </c>
       <c r="L662" s="27" t="s">
-        <v>3910</v>
+        <v>3975</v>
       </c>
       <c r="M662" s="27" t="s">
         <v>2852</v>
@@ -66239,7 +66236,7 @@
         <v>16</v>
       </c>
       <c r="Q662" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R662" s="12"/>
       <c r="T662" s="11"/>
@@ -66280,7 +66277,7 @@
         <v>472</v>
       </c>
       <c r="L663" s="27" t="s">
-        <v>3911</v>
+        <v>3908</v>
       </c>
       <c r="M663" s="27" t="s">
         <v>2855</v>
@@ -66295,7 +66292,7 @@
         <v>16</v>
       </c>
       <c r="Q663" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R663" s="12"/>
       <c r="T663" s="11"/>
@@ -66336,7 +66333,7 @@
         <v>16</v>
       </c>
       <c r="L664" s="27" t="s">
-        <v>3912</v>
+        <v>3976</v>
       </c>
       <c r="M664" s="27" t="s">
         <v>2857</v>
@@ -66351,7 +66348,7 @@
         <v>16</v>
       </c>
       <c r="Q664" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R664" s="12"/>
       <c r="T664" s="11"/>
@@ -66392,7 +66389,7 @@
         <v>152</v>
       </c>
       <c r="L665" s="27" t="s">
-        <v>3913</v>
+        <v>3909</v>
       </c>
       <c r="M665" s="27" t="s">
         <v>2860</v>
@@ -66407,7 +66404,7 @@
         <v>16</v>
       </c>
       <c r="Q665" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R665" s="12"/>
       <c r="T665" s="11"/>
@@ -66448,7 +66445,7 @@
         <v>339</v>
       </c>
       <c r="L666" s="27" t="s">
-        <v>3914</v>
+        <v>3910</v>
       </c>
       <c r="M666" s="27" t="s">
         <v>2862</v>
@@ -66463,7 +66460,7 @@
         <v>16</v>
       </c>
       <c r="Q666" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R666" s="12"/>
       <c r="T666" s="11"/>
@@ -66504,7 +66501,7 @@
         <v>16</v>
       </c>
       <c r="L667" s="27" t="s">
-        <v>3915</v>
+        <v>3911</v>
       </c>
       <c r="M667" s="27" t="s">
         <v>2864</v>
@@ -66519,7 +66516,7 @@
         <v>16</v>
       </c>
       <c r="Q667" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R667" s="12"/>
       <c r="T667" s="11"/>
@@ -66560,7 +66557,7 @@
         <v>16</v>
       </c>
       <c r="L668" s="27" t="s">
-        <v>3916</v>
+        <v>3912</v>
       </c>
       <c r="M668" s="27" t="s">
         <v>2867</v>
@@ -66575,7 +66572,7 @@
         <v>16</v>
       </c>
       <c r="Q668" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R668" s="12"/>
       <c r="T668" s="11"/>
@@ -66613,10 +66610,10 @@
         <v>0</v>
       </c>
       <c r="K669" s="44" t="s">
-        <v>3975</v>
+        <v>3957</v>
       </c>
       <c r="L669" s="27" t="s">
-        <v>3917</v>
+        <v>3913</v>
       </c>
       <c r="M669" s="27" t="s">
         <v>2869</v>
@@ -66631,7 +66628,7 @@
         <v>16</v>
       </c>
       <c r="Q669" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R669" s="12"/>
       <c r="T669" s="11"/>
@@ -66672,7 +66669,7 @@
         <v>152</v>
       </c>
       <c r="L670" s="27" t="s">
-        <v>3918</v>
+        <v>3914</v>
       </c>
       <c r="M670" s="27" t="s">
         <v>2872</v>
@@ -66687,7 +66684,7 @@
         <v>16</v>
       </c>
       <c r="Q670" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R670" s="12"/>
       <c r="T670" s="11"/>
@@ -66728,7 +66725,7 @@
         <v>74</v>
       </c>
       <c r="L671" s="27" t="s">
-        <v>3919</v>
+        <v>3915</v>
       </c>
       <c r="M671" s="27" t="s">
         <v>2874</v>
@@ -66743,7 +66740,7 @@
         <v>2877</v>
       </c>
       <c r="Q671" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R671" s="12"/>
       <c r="T671" s="11"/>
@@ -66784,7 +66781,7 @@
         <v>74</v>
       </c>
       <c r="L672" s="27" t="s">
-        <v>3920</v>
+        <v>3916</v>
       </c>
       <c r="M672" s="27" t="s">
         <v>2878</v>
@@ -66799,7 +66796,7 @@
         <v>16</v>
       </c>
       <c r="Q672" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R672" s="12"/>
       <c r="T672" s="11"/>
@@ -66840,7 +66837,7 @@
         <v>148</v>
       </c>
       <c r="L673" s="27" t="s">
-        <v>3921</v>
+        <v>3917</v>
       </c>
       <c r="M673" s="27" t="s">
         <v>2881</v>
@@ -66855,7 +66852,7 @@
         <v>16</v>
       </c>
       <c r="Q673" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R673" s="12"/>
       <c r="T673" s="11"/>
@@ -66896,7 +66893,7 @@
         <v>16</v>
       </c>
       <c r="L674" s="27" t="s">
-        <v>3922</v>
+        <v>3977</v>
       </c>
       <c r="M674" s="27" t="s">
         <v>2883</v>
@@ -66911,7 +66908,7 @@
         <v>16</v>
       </c>
       <c r="Q674" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R674" s="12"/>
       <c r="T674" s="11"/>
@@ -66952,7 +66949,7 @@
         <v>74</v>
       </c>
       <c r="L675" s="27" t="s">
-        <v>3923</v>
+        <v>3918</v>
       </c>
       <c r="M675" s="27" t="s">
         <v>2886</v>
@@ -66967,7 +66964,7 @@
         <v>16</v>
       </c>
       <c r="Q675" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R675" s="12"/>
       <c r="T675" s="11"/>
@@ -67008,7 +67005,7 @@
         <v>16</v>
       </c>
       <c r="L676" s="27" t="s">
-        <v>3924</v>
+        <v>3978</v>
       </c>
       <c r="M676" s="27" t="s">
         <v>2889</v>
@@ -67023,7 +67020,7 @@
         <v>16</v>
       </c>
       <c r="Q676" s="19" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
       <c r="R676" s="12"/>
       <c r="T676" s="11"/>
@@ -67064,7 +67061,7 @@
         <v>16</v>
       </c>
       <c r="L677" s="27" t="s">
-        <v>3925</v>
+        <v>3979</v>
       </c>
       <c r="M677" s="27" t="s">
         <v>2891</v>
@@ -67079,7 +67076,7 @@
         <v>16</v>
       </c>
       <c r="Q677" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R677" s="12"/>
       <c r="T677" s="11"/>
@@ -67120,7 +67117,7 @@
         <v>16</v>
       </c>
       <c r="L678" s="27" t="s">
-        <v>3926</v>
+        <v>3919</v>
       </c>
       <c r="M678" s="27" t="s">
         <v>2893</v>
@@ -67135,7 +67132,7 @@
         <v>16</v>
       </c>
       <c r="Q678" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R678" s="12"/>
       <c r="T678" s="11"/>
@@ -67176,7 +67173,7 @@
         <v>1097</v>
       </c>
       <c r="L679" s="27" t="s">
-        <v>3927</v>
+        <v>3920</v>
       </c>
       <c r="M679" s="27" t="s">
         <v>2895</v>
@@ -67191,7 +67188,7 @@
         <v>16</v>
       </c>
       <c r="Q679" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R679" s="12"/>
       <c r="T679" s="11"/>
@@ -67232,7 +67229,7 @@
         <v>16</v>
       </c>
       <c r="L680" s="27" t="s">
-        <v>3928</v>
+        <v>3921</v>
       </c>
       <c r="M680" s="27" t="s">
         <v>2897</v>
@@ -67247,7 +67244,7 @@
         <v>16</v>
       </c>
       <c r="Q680" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R680" s="12"/>
       <c r="T680" s="11"/>
@@ -67288,7 +67285,7 @@
         <v>16</v>
       </c>
       <c r="L681" s="27" t="s">
-        <v>3929</v>
+        <v>3980</v>
       </c>
       <c r="M681" s="27" t="s">
         <v>2899</v>
@@ -67303,7 +67300,7 @@
         <v>16</v>
       </c>
       <c r="Q681" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R681" s="12"/>
       <c r="T681" s="11"/>
@@ -67344,7 +67341,7 @@
         <v>16</v>
       </c>
       <c r="L682" s="27" t="s">
-        <v>3930</v>
+        <v>3981</v>
       </c>
       <c r="M682" s="27" t="s">
         <v>2902</v>
@@ -67359,7 +67356,7 @@
         <v>16</v>
       </c>
       <c r="Q682" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R682" s="12"/>
       <c r="T682" s="11"/>
@@ -67400,7 +67397,7 @@
         <v>16</v>
       </c>
       <c r="L683" s="27" t="s">
-        <v>3931</v>
+        <v>3982</v>
       </c>
       <c r="M683" s="27" t="s">
         <v>2905</v>
@@ -67415,7 +67412,7 @@
         <v>16</v>
       </c>
       <c r="Q683" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R683" s="12"/>
       <c r="T683" s="11"/>
@@ -67456,7 +67453,7 @@
         <v>152</v>
       </c>
       <c r="L684" s="27" t="s">
-        <v>3932</v>
+        <v>3922</v>
       </c>
       <c r="M684" s="27" t="s">
         <v>2908</v>
@@ -67471,7 +67468,7 @@
         <v>16</v>
       </c>
       <c r="Q684" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R684" s="12"/>
       <c r="T684" s="11"/>
@@ -67512,7 +67509,7 @@
         <v>16</v>
       </c>
       <c r="L685" s="27" t="s">
-        <v>3933</v>
+        <v>3983</v>
       </c>
       <c r="M685" s="27" t="s">
         <v>2911</v>
@@ -67527,7 +67524,7 @@
         <v>16</v>
       </c>
       <c r="Q685" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R685" s="12"/>
       <c r="T685" s="11"/>
@@ -67568,7 +67565,7 @@
         <v>60</v>
       </c>
       <c r="L686" s="27" t="s">
-        <v>3934</v>
+        <v>3923</v>
       </c>
       <c r="M686" s="27" t="s">
         <v>2913</v>
@@ -67583,7 +67580,7 @@
         <v>16</v>
       </c>
       <c r="Q686" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R686" s="12"/>
       <c r="T686" s="11"/>
@@ -67624,7 +67621,7 @@
         <v>229</v>
       </c>
       <c r="L687" s="27" t="s">
-        <v>3935</v>
+        <v>3924</v>
       </c>
       <c r="M687" s="27" t="s">
         <v>2915</v>
@@ -67639,7 +67636,7 @@
         <v>16</v>
       </c>
       <c r="Q687" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R687" s="12"/>
       <c r="T687" s="11"/>
@@ -67680,7 +67677,7 @@
         <v>1159</v>
       </c>
       <c r="L688" s="27" t="s">
-        <v>3936</v>
+        <v>3925</v>
       </c>
       <c r="M688" s="27" t="s">
         <v>2917</v>
@@ -67695,7 +67692,7 @@
         <v>16</v>
       </c>
       <c r="Q688" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R688" s="12"/>
       <c r="T688" s="11"/>
@@ -67736,7 +67733,7 @@
         <v>472</v>
       </c>
       <c r="L689" s="27" t="s">
-        <v>3937</v>
+        <v>3926</v>
       </c>
       <c r="M689" s="27" t="s">
         <v>2920</v>
@@ -67751,7 +67748,7 @@
         <v>16</v>
       </c>
       <c r="Q689" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R689" s="12"/>
       <c r="T689" s="11"/>
@@ -67792,7 +67789,7 @@
         <v>1097</v>
       </c>
       <c r="L690" s="27" t="s">
-        <v>3938</v>
+        <v>3927</v>
       </c>
       <c r="M690" s="27" t="s">
         <v>2923</v>
@@ -67807,7 +67804,7 @@
         <v>16</v>
       </c>
       <c r="Q690" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R690" s="12"/>
       <c r="T690" s="11"/>
@@ -67848,7 +67845,7 @@
         <v>1097</v>
       </c>
       <c r="L691" s="27" t="s">
-        <v>3939</v>
+        <v>3928</v>
       </c>
       <c r="M691" s="27" t="s">
         <v>2926</v>
@@ -67863,7 +67860,7 @@
         <v>16</v>
       </c>
       <c r="Q691" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R691" s="12"/>
       <c r="T691" s="11"/>
@@ -67904,7 +67901,7 @@
         <v>16</v>
       </c>
       <c r="L692" s="27" t="s">
-        <v>3940</v>
+        <v>3984</v>
       </c>
       <c r="M692" s="27" t="s">
         <v>2928</v>
@@ -67919,7 +67916,7 @@
         <v>16</v>
       </c>
       <c r="Q692" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R692" s="12"/>
       <c r="T692" s="11"/>
@@ -67960,7 +67957,7 @@
         <v>16</v>
       </c>
       <c r="L693" s="27" t="s">
-        <v>3941</v>
+        <v>3985</v>
       </c>
       <c r="M693" s="27" t="s">
         <v>2930</v>
@@ -67975,7 +67972,7 @@
         <v>16</v>
       </c>
       <c r="Q693" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R693" s="12"/>
       <c r="T693" s="11"/>
@@ -68016,7 +68013,7 @@
         <v>229</v>
       </c>
       <c r="L694" s="27" t="s">
-        <v>3942</v>
+        <v>3929</v>
       </c>
       <c r="M694" s="27" t="s">
         <v>2932</v>
@@ -68031,7 +68028,7 @@
         <v>16</v>
       </c>
       <c r="Q694" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R694" s="12"/>
       <c r="T694" s="11"/>
@@ -68072,7 +68069,7 @@
         <v>229</v>
       </c>
       <c r="L695" s="27" t="s">
-        <v>3943</v>
+        <v>3930</v>
       </c>
       <c r="M695" s="27" t="s">
         <v>2934</v>
@@ -68087,7 +68084,7 @@
         <v>16</v>
       </c>
       <c r="Q695" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R695" s="12"/>
       <c r="T695" s="11"/>
@@ -68128,7 +68125,7 @@
         <v>16</v>
       </c>
       <c r="L696" s="27" t="s">
-        <v>3944</v>
+        <v>3986</v>
       </c>
       <c r="M696" s="27" t="s">
         <v>2936</v>
@@ -68143,7 +68140,7 @@
         <v>16</v>
       </c>
       <c r="Q696" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R696" s="12"/>
       <c r="T696" s="11"/>
@@ -68184,7 +68181,7 @@
         <v>16</v>
       </c>
       <c r="L697" s="27" t="s">
-        <v>3945</v>
+        <v>3987</v>
       </c>
       <c r="M697" s="27" t="s">
         <v>2938</v>
@@ -68199,7 +68196,7 @@
         <v>16</v>
       </c>
       <c r="Q697" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R697" s="12"/>
       <c r="T697" s="11"/>
@@ -68240,7 +68237,7 @@
         <v>46</v>
       </c>
       <c r="L698" s="27" t="s">
-        <v>3946</v>
+        <v>3931</v>
       </c>
       <c r="M698" s="27" t="s">
         <v>2940</v>
@@ -68255,7 +68252,7 @@
         <v>16</v>
       </c>
       <c r="Q698" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R698" s="12"/>
       <c r="T698" s="11"/>
@@ -68296,7 +68293,7 @@
         <v>263</v>
       </c>
       <c r="L699" s="27" t="s">
-        <v>3947</v>
+        <v>3932</v>
       </c>
       <c r="M699" s="27" t="s">
         <v>2942</v>
@@ -68311,7 +68308,7 @@
         <v>16</v>
       </c>
       <c r="Q699" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R699" s="12"/>
       <c r="T699" s="11"/>
@@ -68352,7 +68349,7 @@
         <v>1180</v>
       </c>
       <c r="L700" s="27" t="s">
-        <v>3948</v>
+        <v>3933</v>
       </c>
       <c r="M700" s="27" t="s">
         <v>2944</v>
@@ -68367,7 +68364,7 @@
         <v>16</v>
       </c>
       <c r="Q700" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
       <c r="R700" s="12"/>
       <c r="T700" s="11"/>
@@ -68408,7 +68405,7 @@
         <v>16</v>
       </c>
       <c r="L701" s="27" t="s">
-        <v>3949</v>
+        <v>3934</v>
       </c>
       <c r="M701" s="27" t="s">
         <v>2946</v>
@@ -68423,7 +68420,7 @@
         <v>16</v>
       </c>
       <c r="Q701" s="19" t="s">
-        <v>3981</v>
+        <v>3963</v>
       </c>
       <c r="R701" s="12"/>
       <c r="T701" s="11"/>
@@ -68464,7 +68461,7 @@
         <v>16</v>
       </c>
       <c r="L702" s="27" t="s">
-        <v>3950</v>
+        <v>3988</v>
       </c>
       <c r="M702" s="27" t="s">
         <v>2948</v>
@@ -68479,7 +68476,7 @@
         <v>16</v>
       </c>
       <c r="Q702" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R702" s="12"/>
       <c r="T702" s="11"/>
@@ -68520,7 +68517,7 @@
         <v>46</v>
       </c>
       <c r="L703" s="27" t="s">
-        <v>3951</v>
+        <v>3935</v>
       </c>
       <c r="M703" s="27" t="s">
         <v>2951</v>
@@ -68535,7 +68532,7 @@
         <v>16</v>
       </c>
       <c r="Q703" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R703" s="12"/>
       <c r="T703" s="11"/>
@@ -68576,7 +68573,7 @@
         <v>74</v>
       </c>
       <c r="L704" s="27" t="s">
-        <v>3952</v>
+        <v>3936</v>
       </c>
       <c r="M704" s="27" t="s">
         <v>2954</v>
@@ -68591,7 +68588,7 @@
         <v>16</v>
       </c>
       <c r="Q704" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R704" s="12"/>
       <c r="T704" s="11"/>
@@ -68632,7 +68629,7 @@
         <v>263</v>
       </c>
       <c r="L705" s="27" t="s">
-        <v>3953</v>
+        <v>3937</v>
       </c>
       <c r="M705" s="27" t="s">
         <v>3245</v>
@@ -68647,7 +68644,7 @@
         <v>16</v>
       </c>
       <c r="Q705" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
       <c r="R705" s="12"/>
       <c r="T705" s="11"/>
@@ -68688,7 +68685,7 @@
         <v>263</v>
       </c>
       <c r="L706" s="27" t="s">
-        <v>3954</v>
+        <v>3938</v>
       </c>
       <c r="M706" s="27" t="s">
         <v>3246</v>
@@ -68703,7 +68700,7 @@
         <v>16</v>
       </c>
       <c r="Q706" s="19" t="s">
-        <v>3978</v>
+        <v>3960</v>
       </c>
       <c r="R706" s="12"/>
       <c r="T706" s="11"/>
@@ -68729,37 +68726,37 @@
         <v>49</v>
       </c>
       <c r="G707" s="25" t="s">
-        <v>3957</v>
+        <v>3941</v>
       </c>
       <c r="H707" s="22" t="s">
         <v>824</v>
       </c>
       <c r="I707" s="26" t="s">
-        <v>3958</v>
+        <v>3942</v>
       </c>
       <c r="J707" s="41">
         <v>30000</v>
       </c>
       <c r="K707" s="44" t="s">
-        <v>3976</v>
+        <v>3958</v>
       </c>
       <c r="L707" s="27" t="s">
+        <v>3944</v>
+      </c>
+      <c r="M707" s="27" t="s">
+        <v>3945</v>
+      </c>
+      <c r="N707" s="27" t="s">
+        <v>3946</v>
+      </c>
+      <c r="O707" s="27" t="s">
+        <v>3943</v>
+      </c>
+      <c r="P707" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q707" s="19" t="s">
         <v>3960</v>
-      </c>
-      <c r="M707" s="27" t="s">
-        <v>3961</v>
-      </c>
-      <c r="N707" s="27" t="s">
-        <v>3962</v>
-      </c>
-      <c r="O707" s="27" t="s">
-        <v>3959</v>
-      </c>
-      <c r="P707" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q707" s="19" t="s">
-        <v>3978</v>
       </c>
     </row>
     <row r="708" spans="1:20" ht="17" customHeight="1">
@@ -68798,22 +68795,22 @@
         <v>16</v>
       </c>
       <c r="L708" s="27" t="s">
-        <v>3968</v>
+        <v>3989</v>
       </c>
       <c r="M708" s="27" t="s">
-        <v>3969</v>
+        <v>3952</v>
       </c>
       <c r="N708" s="27" t="s">
-        <v>3963</v>
+        <v>3947</v>
       </c>
       <c r="O708" s="27" t="s">
-        <v>3967</v>
+        <v>3951</v>
       </c>
       <c r="P708" s="39" t="s">
         <v>16</v>
       </c>
       <c r="Q708" s="19" t="s">
-        <v>3980</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="709" spans="1:20" ht="17" customHeight="1">
@@ -68843,7 +68840,7 @@
         <v>824</v>
       </c>
       <c r="I709" s="26" t="s">
-        <v>3970</v>
+        <v>3953</v>
       </c>
       <c r="J709" s="41">
         <v>0</v>
@@ -68852,22 +68849,22 @@
         <v>16</v>
       </c>
       <c r="L709" s="27" t="s">
-        <v>3972</v>
+        <v>3990</v>
       </c>
       <c r="M709" s="27" t="s">
-        <v>3974</v>
+        <v>3956</v>
       </c>
       <c r="N709" s="27" t="s">
-        <v>3971</v>
+        <v>3954</v>
       </c>
       <c r="O709" s="27" t="s">
-        <v>3973</v>
+        <v>3955</v>
       </c>
       <c r="P709" s="39" t="s">
         <v>16</v>
       </c>
       <c r="Q709" s="19" t="s">
-        <v>3979</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="710" spans="1:20" ht="17" customHeight="1">
@@ -68881,47 +68878,47 @@
       <c r="C710" s="53">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D710" s="54" t="s">
-        <v>3984</v>
-      </c>
-      <c r="E710" s="54" t="s">
+      <c r="D710" s="51" t="s">
+        <v>3966</v>
+      </c>
+      <c r="E710" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="F710" s="54" t="s">
+      <c r="F710" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G710" s="55" t="s">
-        <v>3985</v>
-      </c>
-      <c r="H710" s="54" t="s">
+      <c r="G710" s="54" t="s">
+        <v>3967</v>
+      </c>
+      <c r="H710" s="51" t="s">
         <v>824</v>
       </c>
-      <c r="I710" s="56" t="s">
-        <v>3986</v>
+      <c r="I710" s="55" t="s">
+        <v>3968</v>
       </c>
       <c r="J710" s="50">
         <v>10000</v>
       </c>
-      <c r="K710" s="57" t="s">
+      <c r="K710" s="56" t="s">
         <v>711</v>
       </c>
-      <c r="L710" s="58" t="s">
-        <v>3987</v>
-      </c>
-      <c r="M710" s="58" t="s">
-        <v>3990</v>
-      </c>
-      <c r="N710" s="58" t="s">
-        <v>3988</v>
-      </c>
-      <c r="O710" s="58" t="s">
-        <v>3989</v>
-      </c>
-      <c r="P710" s="59" t="s">
+      <c r="L710" s="57" t="s">
+        <v>3969</v>
+      </c>
+      <c r="M710" s="57" t="s">
+        <v>3972</v>
+      </c>
+      <c r="N710" s="57" t="s">
+        <v>3970</v>
+      </c>
+      <c r="O710" s="57" t="s">
+        <v>3971</v>
+      </c>
+      <c r="P710" s="58" t="s">
         <v>16</v>
       </c>
       <c r="Q710" s="49" t="s">
-        <v>3982</v>
+        <v>3964</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239BE955-18C7-D74D-9A86-1A748FE424DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976BFB27-7C3E-C940-A139-56F8A1A81FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17530,13 +17530,66 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>박사: 박민성
-괴물: 문태유</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박사</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박민성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>괴물</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>문태유</t>
         </r>
       </text>
     </comment>
@@ -19448,13 +19501,138 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>마이클 (행크 클리프트): 윤석원
-데이 (잭 터너): 정동화</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마이클</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>행크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>클리프트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>윤석원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>잭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>터너</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정동화</t>
         </r>
       </text>
     </comment>
@@ -20567,7 +20745,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10319" uniqueCount="4205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10350" uniqueCount="4216">
   <si>
     <t>시즌</t>
   </si>
@@ -33182,6 +33360,39 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.1bu81oay04sf</t>
+  </si>
+  <si>
+    <t>라이프 오브 파이</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 박강현 황만익 송인성 정호준 김지혜 김형준 신진경 한규정 전걸 이상아 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 박은석 박정복 정재은(엘) </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fANwmSfUP2fDszlTxazN-RKSC7eaMFiU/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224205681579</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.82o5w47amdc6</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/theatergoing/125238</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kQ0H7PFvADAe-AI2Uc_N3T4v-dglmnL4/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224205688407</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.vk0bcqck0omr</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/285455</t>
   </si>
 </sst>
 </file>
@@ -33413,7 +33624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -33605,6 +33816,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -34535,7 +34776,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R737" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R739" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34861,7 +35102,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U737"/>
+  <dimension ref="A1:U739"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77452,7 +77693,9 @@
       <c r="Q735" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="R735" s="51"/>
+      <c r="R735" s="51" t="s">
+        <v>4098</v>
+      </c>
     </row>
     <row r="736" spans="1:18" ht="17" customHeight="1">
       <c r="A736" s="54">
@@ -77506,61 +77749,177 @@
       <c r="Q736" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="R736" s="51"/>
+      <c r="R736" s="51" t="s">
+        <v>4095</v>
+      </c>
     </row>
     <row r="737" spans="1:18" ht="17" customHeight="1">
-      <c r="A737" s="65">
+      <c r="A737" s="54">
         <v>736</v>
       </c>
-      <c r="B737" s="66">
+      <c r="B737" s="55">
         <v>46074</v>
       </c>
-      <c r="C737" s="67">
+      <c r="C737" s="56">
         <v>0.625</v>
       </c>
-      <c r="D737" s="68" t="s">
+      <c r="D737" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="E737" s="68" t="s">
+      <c r="E737" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="F737" s="68" t="s">
+      <c r="F737" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="G737" s="69" t="s">
+      <c r="G737" s="58" t="s">
         <v>4200</v>
       </c>
-      <c r="H737" s="68" t="s">
+      <c r="H737" s="57" t="s">
         <v>815</v>
       </c>
-      <c r="I737" s="70" t="s">
+      <c r="I737" s="59" t="s">
         <v>4201</v>
       </c>
-      <c r="J737" s="71">
+      <c r="J737" s="64">
         <v>0</v>
       </c>
-      <c r="K737" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="L737" s="73" t="s">
+      <c r="K737" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L737" s="60" t="s">
         <v>4202</v>
       </c>
       <c r="M737" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="N737" s="73" t="s">
+      <c r="N737" s="60" t="s">
         <v>4203</v>
       </c>
-      <c r="O737" s="73" t="s">
+      <c r="O737" s="60" t="s">
         <v>4204</v>
       </c>
-      <c r="P737" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q737" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="R737" s="74"/>
+      <c r="P737" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q737" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="R737" s="51" t="s">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="738" spans="1:18" ht="17" customHeight="1">
+      <c r="A738" s="65">
+        <v>737</v>
+      </c>
+      <c r="B738" s="66">
+        <v>46083</v>
+      </c>
+      <c r="C738" s="67">
+        <v>0.625</v>
+      </c>
+      <c r="D738" s="68" t="s">
+        <v>551</v>
+      </c>
+      <c r="E738" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F738" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="G738" s="69" t="s">
+        <v>4205</v>
+      </c>
+      <c r="H738" s="68" t="s">
+        <v>815</v>
+      </c>
+      <c r="I738" s="70" t="s">
+        <v>4206</v>
+      </c>
+      <c r="J738" s="71">
+        <v>33500</v>
+      </c>
+      <c r="K738" s="72" t="s">
+        <v>554</v>
+      </c>
+      <c r="L738" s="73" t="s">
+        <v>4208</v>
+      </c>
+      <c r="M738" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N738" s="73" t="s">
+        <v>4209</v>
+      </c>
+      <c r="O738" s="73" t="s">
+        <v>4210</v>
+      </c>
+      <c r="P738" s="73" t="s">
+        <v>4211</v>
+      </c>
+      <c r="Q738" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="R738" s="74" t="s">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="739" spans="1:18" ht="17" customHeight="1">
+      <c r="A739" s="75">
+        <v>738</v>
+      </c>
+      <c r="B739" s="76">
+        <v>46085</v>
+      </c>
+      <c r="C739" s="77">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D739" s="78" t="s">
+        <v>148</v>
+      </c>
+      <c r="E739" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="F739" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="G739" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="H739" s="78" t="s">
+        <v>821</v>
+      </c>
+      <c r="I739" s="80" t="s">
+        <v>4207</v>
+      </c>
+      <c r="J739" s="81">
+        <v>33000</v>
+      </c>
+      <c r="K739" s="82" t="s">
+        <v>151</v>
+      </c>
+      <c r="L739" s="83" t="s">
+        <v>4212</v>
+      </c>
+      <c r="M739" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="N739" s="83" t="s">
+        <v>4213</v>
+      </c>
+      <c r="O739" s="83" t="s">
+        <v>4214</v>
+      </c>
+      <c r="P739" s="83" t="s">
+        <v>4215</v>
+      </c>
+      <c r="Q739" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="R739" s="84" t="s">
+        <v>4095</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21633113-8693-A44C-87EA-39FD482878A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC284DFB-CA6D-3D44-846B-6D91AFCA78CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -1247,29 +1247,822 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>아더: ㅅㅂ
-귀네비어: 이지수
-랜슬롯: 장지후
-모르간: 박혜나
-멜레아강: 강홍석
-멀린: 지혜근
-케이: 김지욱
-레이아: 정다영
-늑대: 이기흥
-사슴: 이영호
-가웨인: 이종찬
-앙상블: 
-주홍균 최민준 이재범 권기중 
-노해영 오홍학 임동섭 이승현 
-김정민 이보슬 남궁민희 황보주성 
-고샛별 우미나 홍윤영 김재희 임상희
-스윙: 
-전성혜 하웅환 이윤환</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아더</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ㅅㅂ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>귀네비어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이지수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>랜슬롯</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장지후</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>모르간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박혜나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>멜레아강</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강홍석</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>멀린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지혜근</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레이아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정다영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>늑대</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이기흥</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>사슴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이영호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>가웨인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이종찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앙상블</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주홍균</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최민준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재범</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>권기중</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>노해영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>오홍학</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임동섭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이승현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김정민</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이보슬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>남궁민희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황보주성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>고샛별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>우미나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍윤영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김재희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임상희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스윙</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전성혜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>하웅환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이윤환</t>
         </r>
       </text>
     </comment>
@@ -1591,27 +2384,900 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>유다 벤허: 민우혁
-메셀라: 박민성
-에스더: 린아
-퀸터스: 이정열
-미리암: 임선애
-시모니테스: 홍경수
-빌라도: 이정수
-티토: 선한국
-티르자: 문은수
-어린티토: 이윤우
-앙상블: 
-조상현 백시호 선재 최도진 박종배 
-김선 정민찬(정설웅) 유효진 이민재 정종락 
-권기중 이한울 백승리 권성일 김원빈 
-이재웅 박선영 신영찬 임태현 서종원 
-김재현 진대웅 정찬우 현익창 이우진 황성훈</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>유다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>벤허</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>민우혁</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>메셀라</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박민성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에스더</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>린아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>퀸터스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이정열</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>미리암</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임선애</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>시모니테스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍경수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>빌라도</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이정수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>티토</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>선한국</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>티르자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>문은수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>어린티토</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이윤우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앙상블</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조상현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>백시호</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>선재</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최도진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박종배</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김선</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정민찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정설웅</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>유효진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이민재</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정종락</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>권기중</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이한울</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>백승리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>권성일</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김원빈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재웅</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박선영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신영찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임태현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>서종원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김재현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>진대웅</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정찬우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>현익창</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이우진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황성훈</t>
         </r>
       </text>
     </comment>
@@ -17839,12 +19505,245 @@
         </r>
       </text>
     </comment>
+    <comment ref="I740" authorId="0" shapeId="0" xr:uid="{B35B2110-06CA-4E4C-AF3C-6F1A6A81CC74}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Franklin Shepard: Jonathan Groff
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mary Flynn: Lindsay Mendez
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Charley Kringas: Daniel Radcliffe
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Gussie Carnegie: Krystal Joy Brown
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Beth Shepard: Katie Rose Clarke
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Joe Josephson: Reg Rogers
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Frank Jr.: Max Rackenberg
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Scotty / Mrs. Spencer / Auditionee #1: Sherz Aletaha
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Chorus 1/ Make-Up Artist / Swing: Brianna Stoute
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Waitress / Newscaster / Auditionee #2: Leana Rae Concepcion
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bunker / Newscaster / Photographer: Coby Getzug
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tyler: Corey Mach
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Meg Kincaid: Talia Simone Robinson
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dory / Evelyn: Jamila Sabares-Klemm
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Chorus 2 / Swing: Brian Sears
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ru / Reverend: Christian Strange
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jerome: Vishal Vaidya
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">KT: Natalie Wachen
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Terry / Mr. Spencer: Jacob Keith Watson
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Swing / Dance Captain: Morgan Kirner
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Swing / Fight Captain: Koray Tarhan
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Swing: Amanda Rose
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Swing: David Purdy</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10350" uniqueCount="4197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10364" uniqueCount="4204">
   <si>
     <t>시즌</t>
   </si>
@@ -30435,6 +32334,27 @@
   </si>
   <si>
     <t>GS아트센터(구 엘아센)</t>
+  </si>
+  <si>
+    <t>Merrily We Roll Along</t>
+  </si>
+  <si>
+    <t>(US 중계)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jonathan_Groff Lindsay_Mendez Daniel_Radcliffe Krystal_Brown Katie_Clarke Reg_Rogers </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G7wxLRIPnTu8iv7GOIpkC1EZtdTfu6Oz/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1yhrsEA841c8uXJq2TfsYYZtPAMcsrhds/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224211821646</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.ik3eqlxcxspr</t>
   </si>
 </sst>
 </file>
@@ -30666,7 +32586,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -30858,6 +32778,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -31758,7 +33708,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R739" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R740" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32084,7 +34034,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U739"/>
+  <dimension ref="A1:U740"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -74903,6 +76853,62 @@
         <v>4065</v>
       </c>
     </row>
+    <row r="740" spans="1:18" ht="17" customHeight="1">
+      <c r="A740" s="65">
+        <v>739</v>
+      </c>
+      <c r="B740" s="66">
+        <v>46091</v>
+      </c>
+      <c r="C740" s="67">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D740" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E740" s="68" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F740" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="G740" s="69" t="s">
+        <v>4197</v>
+      </c>
+      <c r="H740" s="68" t="s">
+        <v>4198</v>
+      </c>
+      <c r="I740" s="70" t="s">
+        <v>4199</v>
+      </c>
+      <c r="J740" s="71">
+        <v>21971</v>
+      </c>
+      <c r="K740" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="L740" s="73" t="s">
+        <v>4200</v>
+      </c>
+      <c r="M740" s="61" t="s">
+        <v>4201</v>
+      </c>
+      <c r="N740" s="73" t="s">
+        <v>4202</v>
+      </c>
+      <c r="O740" s="73" t="s">
+        <v>4203</v>
+      </c>
+      <c r="P740" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q740" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="R740" s="74" t="s">
+        <v>4065</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC284DFB-CA6D-3D44-846B-6D91AFCA78CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687EE05A-773F-8044-BE50-D3315BE06784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -19321,27 +19321,938 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>파이: 박강현
-아버지: 황만익
-엄마 / 간호사 / 오렌지주스: 송인성
-오카모토 / 선장: 정호준
-루루 첸: 김지혜 
-요리사 / 리차드 파커 목소리: 김형준
-쿠마르 / 자이다 칸: 신진경 
-마마지 / 판딧지: 한규정 
-그랜트 존스 중령 / 마틴 신부 / 러시아 선원: 전걸
-라니: 이상아 
-리차드 파커: 
-박재춘, 김예진, 임우영
-퍼펫티어: 
-김시영, 최은별, 이지용
-퍼펫티어 스탠바이: 
-임원, 강은나, 강장군</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>파이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박강현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아버지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황만익</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>엄마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>간호사</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>오렌지주스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>송인성</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>오카모토</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>선장</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정호준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루루</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>첸</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지혜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>요리사</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>리차드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>파커</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>목소리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김형준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>쿠마르</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>자이다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>칸</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신진경</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마마지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>판딧지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>한규정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>그랜트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>존스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>중령</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마틴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신부</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>러시아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>선원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전걸</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>라니</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이상아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>리차드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>파커</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박재춘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김예진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임우영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>퍼펫티어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김시영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최은별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이지용</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>퍼펫티어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스탠바이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>임원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강은나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강장군</t>
         </r>
       </text>
     </comment>
@@ -19505,7 +20416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I740" authorId="0" shapeId="0" xr:uid="{B35B2110-06CA-4E4C-AF3C-6F1A6A81CC74}">
+    <comment ref="I740" authorId="0" shapeId="0" xr:uid="{C8C8900C-45DA-E542-8181-DA3B5BF30241}">
       <text>
         <r>
           <rPr>
@@ -19514,7 +20425,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Franklin Shepard: Jonathan Groff
+          <t xml:space="preserve">Franklin Shepard: JONATHAN GROFF
 </t>
         </r>
         <r>
@@ -19524,7 +20435,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Mary Flynn: Lindsay Mendez
+          <t xml:space="preserve">Mary Flynn: LINDSAY MENDEZ
 </t>
         </r>
         <r>
@@ -19534,7 +20445,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Charley Kringas: Daniel Radcliffe
+          <t xml:space="preserve">Charley Kringas: DANIEL RADCLIFFE
 </t>
         </r>
         <r>
@@ -19544,7 +20455,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Gussie Carnegie: Krystal Joy Brown
+          <t xml:space="preserve">Gussie Carnegie: KRYSTAL JOY BROWN
 </t>
         </r>
         <r>
@@ -19554,7 +20465,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Beth Shepard: Katie Rose Clarke
+          <t xml:space="preserve">Beth Shepard: KATIE ROSE CLARKE
 </t>
         </r>
         <r>
@@ -19564,7 +20475,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Joe Josephson: Reg Rogers
+          <t xml:space="preserve">Joe Josephson: REG ROGERS
 </t>
         </r>
         <r>
@@ -19574,7 +20485,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Frank Jr.: Max Rackenberg
+          <t xml:space="preserve">Frank Jr.: MAX RACKENBERG
 </t>
         </r>
         <r>
@@ -19584,7 +20495,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Scotty / Mrs. Spencer / Auditionee #1: Sherz Aletaha
+          <t xml:space="preserve">Scotty / Mrs. Spencer / Auditionee #1: SHERZ ALETAHA
 </t>
         </r>
         <r>
@@ -19594,7 +20505,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Chorus 1/ Make-Up Artist / Swing: Brianna Stoute
+          <t xml:space="preserve">Chorus 1/ Make-Up Artist / Swing: BRIANNA STOUTE
 </t>
         </r>
         <r>
@@ -19604,7 +20515,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Waitress / Newscaster / Auditionee #2: Leana Rae Concepcion
+          <t xml:space="preserve">Waitress / Newscaster / Auditionee #2: LEANA RAE CONCEPCION
 </t>
         </r>
         <r>
@@ -19614,7 +20525,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Bunker / Newscaster / Photographer: Coby Getzug
+          <t xml:space="preserve">Bunker / Newscaster / Photographer: COBY GETZUG
 </t>
         </r>
         <r>
@@ -19624,7 +20535,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Tyler: Corey Mach
+          <t xml:space="preserve">Tyler: COREY MACH
 </t>
         </r>
         <r>
@@ -19634,7 +20545,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Meg Kincaid: Talia Simone Robinson
+          <t xml:space="preserve">Meg Kincaid: TALIA SIMONE ROBINSON
 </t>
         </r>
         <r>
@@ -19644,7 +20555,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Dory / Evelyn: Jamila Sabares-Klemm
+          <t xml:space="preserve">Dory / Evelyn: JAMILA SABARES-KLEMM
 </t>
         </r>
         <r>
@@ -19654,7 +20565,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Chorus 2 / Swing: Brian Sears
+          <t xml:space="preserve">Chorus 2 / Swing: BRIAN SEARS
 </t>
         </r>
         <r>
@@ -19664,7 +20575,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ru / Reverend: Christian Strange
+          <t xml:space="preserve">Ru / Reverend: CHRISTIAN STRANGE
 </t>
         </r>
         <r>
@@ -19674,7 +20585,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Jerome: Vishal Vaidya
+          <t xml:space="preserve">Jerome: VISHAL VAIDYA
 </t>
         </r>
         <r>
@@ -19684,7 +20595,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">KT: Natalie Wachen
+          <t xml:space="preserve">KT: NATALIE WACHEN
 </t>
         </r>
         <r>
@@ -19694,7 +20605,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Terry / Mr. Spencer: Jacob Keith Watson
+          <t xml:space="preserve">Terry / Mr. Spencer: JACOB KEITH WATSON
 </t>
         </r>
         <r>
@@ -19704,7 +20615,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Swing / Dance Captain: Morgan Kirner
+          <t xml:space="preserve">Swing / Dance Captain: MORGAN KIRNER
 </t>
         </r>
         <r>
@@ -19714,7 +20625,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Swing / Fight Captain: Koray Tarhan
+          <t xml:space="preserve">Swing / Fight Captain: KORAY TARHAN
 </t>
         </r>
         <r>
@@ -19724,7 +20635,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Swing: Amanda Rose
+          <t xml:space="preserve">Swing: AMANDA ROSE
 </t>
         </r>
         <r>
@@ -19734,7 +20645,37 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>Swing: David Purdy</t>
+          <t>Swing: DAVID PURDY</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I741" authorId="0" shapeId="0" xr:uid="{07423F1D-2A57-E943-B9D8-86E5733F7E2C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Alexander Hamilton: LIN-MANUEL MIRANDA
+Aaron Burr: LESLIE ODOM JR.
+King George: JONATHAN GROFF
+Eliza Hamilton: PHILLIPA SOO
+George Washington: CHRIS JACKSON
+Angelica Schuyler: RENÉE ELISE GOLDSBERRY
+Marquis de Lafayette/Thomas Jefferson: DAVEED DIGGS
+John Laurens/Philip Hamilton: ANTHONY RAMOS
+Hercules Mulligan/James Madison: OKIERIETE ONAODOWAN
+Peggy Schuyler/Maria Reynolds: JASMINE CEPHAS JONES
+Philip Schuyler/James Reynolds/Doctor/Ensemble: SYDNEY JAMES HARCOURT
+Samuel Seabury/Ensemble: THAYNE JASPERSON
+Charles Lee/Ensemble: JON RUA
+George Eacker/Ensemble: EPHRAIM SYKES
+Ensemble:
+CARLEIGH BETTIOL, ARIANA DEBOSE, HOPE EASTERBROOK, 
+SASHA HUTCHINGS, ELIZABETH JUDD, AUSTIN SMITH, SETH STEWART</t>
         </r>
       </text>
     </comment>
@@ -19743,7 +20684,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10364" uniqueCount="4204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10378" uniqueCount="4212">
   <si>
     <t>시즌</t>
   </si>
@@ -32355,6 +33296,30 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.ik3eqlxcxspr</t>
+  </si>
+  <si>
+    <t>GS아트센터(엘아센)</t>
+  </si>
+  <si>
+    <t>라센 16</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lin-Manuel_Miranda Leslie_Odom_Jr. Jonathan_Groff Phillipa_Soo Chris_Jackson Renée_Goldsberry Daveed_Diggs Anthony_Ramos Okieriete_Onaodowan Jasmine_Jones </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qkY_eahOG0Dq89v-M6_rWxuTlYLpiGRY/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EJIZJ2vMggq_KdJm5NLnRnWVNQ3YiRwP/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224213072967</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.bnc0vq81etez</t>
   </si>
 </sst>
 </file>
@@ -32586,7 +33551,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32774,40 +33739,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -33708,7 +34640,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R740" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R741" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34034,7 +34966,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U740"/>
+  <dimension ref="A1:U741"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -40295,7 +41227,7 @@
         <v>55000</v>
       </c>
       <c r="K108" s="45" t="s">
-        <v>4196</v>
+        <v>4204</v>
       </c>
       <c r="L108" s="16" t="s">
         <v>3327</v>
@@ -52533,7 +53465,7 @@
         <v>49000</v>
       </c>
       <c r="K319" s="45" t="s">
-        <v>4196</v>
+        <v>4204</v>
       </c>
       <c r="L319" s="16" t="s">
         <v>3537</v>
@@ -76545,7 +77477,7 @@
       <c r="I734" s="43" t="s">
         <v>4151</v>
       </c>
-      <c r="J734" s="63">
+      <c r="J734" s="28">
         <v>0</v>
       </c>
       <c r="K734" s="50" t="s">
@@ -76601,7 +77533,7 @@
       <c r="I735" s="43" t="s">
         <v>4195</v>
       </c>
-      <c r="J735" s="63">
+      <c r="J735" s="28">
         <v>52000</v>
       </c>
       <c r="K735" s="50" t="s">
@@ -76657,7 +77589,7 @@
       <c r="I736" s="59" t="s">
         <v>4158</v>
       </c>
-      <c r="J736" s="64">
+      <c r="J736" s="62">
         <v>0</v>
       </c>
       <c r="K736" s="54" t="s">
@@ -76713,7 +77645,7 @@
       <c r="I737" s="59" t="s">
         <v>4169</v>
       </c>
-      <c r="J737" s="64">
+      <c r="J737" s="62">
         <v>0</v>
       </c>
       <c r="K737" s="54" t="s">
@@ -76769,7 +77701,7 @@
       <c r="I738" s="43" t="s">
         <v>4174</v>
       </c>
-      <c r="J738" s="63">
+      <c r="J738" s="28">
         <v>33500</v>
       </c>
       <c r="K738" s="50" t="s">
@@ -76825,7 +77757,7 @@
       <c r="I739" s="59" t="s">
         <v>4175</v>
       </c>
-      <c r="J739" s="64">
+      <c r="J739" s="62">
         <v>33000</v>
       </c>
       <c r="K739" s="54" t="s">
@@ -76854,58 +77786,114 @@
       </c>
     </row>
     <row r="740" spans="1:18" ht="17" customHeight="1">
-      <c r="A740" s="65">
+      <c r="A740" s="54">
         <v>739</v>
       </c>
-      <c r="B740" s="66">
+      <c r="B740" s="55">
         <v>46091</v>
       </c>
-      <c r="C740" s="67">
+      <c r="C740" s="56">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D740" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="E740" s="68" t="s">
+      <c r="D740" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E740" s="57" t="s">
         <v>1124</v>
       </c>
-      <c r="F740" s="68" t="s">
+      <c r="F740" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="G740" s="69" t="s">
+      <c r="G740" s="58" t="s">
         <v>4197</v>
       </c>
-      <c r="H740" s="68" t="s">
+      <c r="H740" s="57" t="s">
         <v>4198</v>
       </c>
-      <c r="I740" s="70" t="s">
+      <c r="I740" s="59" t="s">
         <v>4199</v>
       </c>
-      <c r="J740" s="71">
+      <c r="J740" s="62">
         <v>21971</v>
       </c>
-      <c r="K740" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="L740" s="73" t="s">
+      <c r="K740" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L740" s="60" t="s">
         <v>4200</v>
       </c>
       <c r="M740" s="61" t="s">
         <v>4201</v>
       </c>
-      <c r="N740" s="73" t="s">
+      <c r="N740" s="60" t="s">
         <v>4202</v>
       </c>
-      <c r="O740" s="73" t="s">
+      <c r="O740" s="60" t="s">
         <v>4203</v>
       </c>
-      <c r="P740" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q740" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="R740" s="74" t="s">
+      <c r="P740" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q740" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="R740" s="51" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="741" spans="1:18" ht="17" customHeight="1">
+      <c r="A741" s="54">
+        <v>740</v>
+      </c>
+      <c r="B741" s="55">
+        <v>46092</v>
+      </c>
+      <c r="C741" s="56">
+        <v>0.75</v>
+      </c>
+      <c r="D741" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E741" s="57" t="s">
+        <v>4205</v>
+      </c>
+      <c r="F741" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="G741" s="58" t="s">
+        <v>4206</v>
+      </c>
+      <c r="H741" s="57" t="s">
+        <v>4198</v>
+      </c>
+      <c r="I741" s="59" t="s">
+        <v>4207</v>
+      </c>
+      <c r="J741" s="63">
+        <v>0</v>
+      </c>
+      <c r="K741" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L741" s="60" t="s">
+        <v>4208</v>
+      </c>
+      <c r="M741" s="61" t="s">
+        <v>4209</v>
+      </c>
+      <c r="N741" s="60" t="s">
+        <v>4210</v>
+      </c>
+      <c r="O741" s="60" t="s">
+        <v>4211</v>
+      </c>
+      <c r="P741" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q741" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="R741" s="51" t="s">
         <v>4065</v>
       </c>
     </row>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687EE05A-773F-8044-BE50-D3315BE06784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F5503-A49F-A442-8726-15C36CAC16D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -20654,28 +20654,314 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Alexander Hamilton: LIN-MANUEL MIRANDA
-Aaron Burr: LESLIE ODOM JR.
-King George: JONATHAN GROFF
-Eliza Hamilton: PHILLIPA SOO
-George Washington: CHRIS JACKSON
-Angelica Schuyler: RENÉE ELISE GOLDSBERRY
-Marquis de Lafayette/Thomas Jefferson: DAVEED DIGGS
-John Laurens/Philip Hamilton: ANTHONY RAMOS
-Hercules Mulligan/James Madison: OKIERIETE ONAODOWAN
-Peggy Schuyler/Maria Reynolds: JASMINE CEPHAS JONES
-Philip Schuyler/James Reynolds/Doctor/Ensemble: SYDNEY JAMES HARCOURT
-Samuel Seabury/Ensemble: THAYNE JASPERSON
-Charles Lee/Ensemble: JON RUA
-George Eacker/Ensemble: EPHRAIM SYKES
-Ensemble:
-CARLEIGH BETTIOL, ARIANA DEBOSE, HOPE EASTERBROOK, 
-SASHA HUTCHINGS, ELIZABETH JUDD, AUSTIN SMITH, SETH STEWART</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Alexander Hamilton: LIN-MANUEL MIRANDA
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Aaron Burr: LESLIE ODOM JR.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">King George: JONATHAN GROFF
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eliza Hamilton: PHILLIPA SOO
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">George Washington: CHRIS JACKSON
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Angelica Schuyler: RENÉE ELISE GOLDSBERRY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Marquis de Lafayette/Thomas Jefferson: DAVEED DIGGS
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">John Laurens/Philip Hamilton: ANTHONY RAMOS
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hercules Mulligan/James Madison: OKIERIETE ONAODOWAN
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Peggy Schuyler/Maria Reynolds: JASMINE CEPHAS JONES
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Philip Schuyler/James Reynolds/Doctor/Ensemble: SYDNEY JAMES HARCOURT
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Samuel Seabury/Ensemble: THAYNE JASPERSON
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Charles Lee/Ensemble: JON RUA
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">George Eacker/Ensemble: EPHRAIM SYKES
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ensemble:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">CARLEIGH BETTIOL, ARIANA DEBOSE, HOPE EASTERBROOK, 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>SASHA HUTCHINGS, ELIZABETH JUDD, AUSTIN SMITH, SETH STEWART</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I742" authorId="0" shapeId="0" xr:uid="{DC8B9932-05BC-524E-B20C-0EF8AEFAB8DE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bonnie Harris / Others : PETRINA BROMLEY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Beverley Bass / Annette / Others : JENN COLELLA
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bob / Others : DE'LON GRANT
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Claude Elliott / Others : JOEL HATCH
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Kevin Tuerff / Garth / Others : TONY LEPAGE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Kevin Jung / Ali / Others : CAESAR SAMAYOA
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hannah O'Rourke / Others : Q. SMITH
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Janice Mosher / Others : EMILY WALTON
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Marson / Doug / Others : JIM WALTON
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Diane Gray / Others : SHARON WHEATLEY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Oz Fudge / Others : PAUL WHITTY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Beulah Davis / Others : ASTRID VAN WIEREN</t>
         </r>
       </text>
     </comment>
@@ -20684,7 +20970,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10378" uniqueCount="4212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10392" uniqueCount="4219">
   <si>
     <t>시즌</t>
   </si>
@@ -33320,6 +33606,27 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.bnc0vq81etez</t>
+  </si>
+  <si>
+    <t>라센 21</t>
+  </si>
+  <si>
+    <t>Come From Away</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Petrina_Bromley Jenn_Colella De'Lon_Grant Joel_Hatch Tony_LePage Caesar_Samayoa Q._Smith Emily_Walton Jim_Walton Sharon_Wheatley Paul_Whitty Astrid_Wieren </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mlzcb8C5oqWQTDU1yPwgSPN4YTi1USDy/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K4mXwCtJppdHpU9LCpHN4cMmTCGxbc_X/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224214371034</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.jsqp0xeill50</t>
   </si>
 </sst>
 </file>
@@ -33551,7 +33858,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -33740,6 +34047,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -34640,7 +34977,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R741" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R742" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34966,7 +35303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U741"/>
+  <dimension ref="A1:U742"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77897,6 +78234,62 @@
         <v>4065</v>
       </c>
     </row>
+    <row r="742" spans="1:18" ht="17" customHeight="1">
+      <c r="A742" s="64">
+        <v>741</v>
+      </c>
+      <c r="B742" s="65">
+        <v>46093</v>
+      </c>
+      <c r="C742" s="66">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D742" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E742" s="67" t="s">
+        <v>4212</v>
+      </c>
+      <c r="F742" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="G742" s="68" t="s">
+        <v>4213</v>
+      </c>
+      <c r="H742" s="67" t="s">
+        <v>4198</v>
+      </c>
+      <c r="I742" s="69" t="s">
+        <v>4214</v>
+      </c>
+      <c r="J742" s="70">
+        <v>0</v>
+      </c>
+      <c r="K742" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="L742" s="72" t="s">
+        <v>4215</v>
+      </c>
+      <c r="M742" s="61" t="s">
+        <v>4216</v>
+      </c>
+      <c r="N742" s="72" t="s">
+        <v>4217</v>
+      </c>
+      <c r="O742" s="72" t="s">
+        <v>4218</v>
+      </c>
+      <c r="P742" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q742" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="R742" s="73" t="s">
+        <v>4067</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F5503-A49F-A442-8726-15C36CAC16D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE154F13-5408-5A4F-9FBF-11F2C2146CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -20965,12 +20965,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="I743" authorId="0" shapeId="0" xr:uid="{26164D98-E902-BC49-B742-63A7D80424B6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>토적토: 조민호
+절영/해설: 최수형
+아버지/군마: 오찬우
+군마: 정민희
+조조/군마: 서광섭
+호적토/군마: 전우형
+군마: 김종헌
+관우/군마: 김동현
+유비/군마: 지승민
+군마: 김도연
+여포/군마: 권강민
+동탁/군마: 류다휘</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10392" uniqueCount="4219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10406" uniqueCount="4226">
   <si>
     <t>시즌</t>
   </si>
@@ -33627,6 +33652,27 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.jsqp0xeill50</t>
+  </si>
+  <si>
+    <t>죽도록달린다</t>
+  </si>
+  <si>
+    <t>적토</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 조민호 최수형 </t>
+  </si>
+  <si>
+    <t>SH아트홀</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hysuk8jfQZlBdf4i8kwY0dAJHyePpkcA/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224217153775</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.c7lqjg5zpdjc</t>
   </si>
 </sst>
 </file>
@@ -34977,7 +35023,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R742" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R743" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -35303,7 +35349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U742"/>
+  <dimension ref="A1:U743"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -78235,59 +78281,115 @@
       </c>
     </row>
     <row r="742" spans="1:18" ht="17" customHeight="1">
-      <c r="A742" s="64">
+      <c r="A742" s="54">
         <v>741</v>
       </c>
-      <c r="B742" s="65">
+      <c r="B742" s="55">
         <v>46093</v>
       </c>
-      <c r="C742" s="66">
+      <c r="C742" s="56">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D742" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="E742" s="67" t="s">
+      <c r="D742" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E742" s="57" t="s">
         <v>4212</v>
       </c>
-      <c r="F742" s="67" t="s">
+      <c r="F742" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="G742" s="68" t="s">
+      <c r="G742" s="58" t="s">
         <v>4213</v>
       </c>
-      <c r="H742" s="67" t="s">
+      <c r="H742" s="57" t="s">
         <v>4198</v>
       </c>
-      <c r="I742" s="69" t="s">
+      <c r="I742" s="59" t="s">
         <v>4214</v>
       </c>
-      <c r="J742" s="70">
+      <c r="J742" s="63">
         <v>0</v>
       </c>
-      <c r="K742" s="71" t="s">
-        <v>15</v>
-      </c>
-      <c r="L742" s="72" t="s">
+      <c r="K742" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L742" s="60" t="s">
         <v>4215</v>
       </c>
       <c r="M742" s="61" t="s">
         <v>4216</v>
       </c>
-      <c r="N742" s="72" t="s">
+      <c r="N742" s="60" t="s">
         <v>4217</v>
       </c>
-      <c r="O742" s="72" t="s">
+      <c r="O742" s="60" t="s">
         <v>4218</v>
       </c>
-      <c r="P742" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q742" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="R742" s="73" t="s">
+      <c r="P742" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q742" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="R742" s="51" t="s">
         <v>4067</v>
+      </c>
+    </row>
+    <row r="743" spans="1:18" ht="17" customHeight="1">
+      <c r="A743" s="64">
+        <v>742</v>
+      </c>
+      <c r="B743" s="65">
+        <v>46095</v>
+      </c>
+      <c r="C743" s="66">
+        <v>0.625</v>
+      </c>
+      <c r="D743" s="67" t="s">
+        <v>4219</v>
+      </c>
+      <c r="E743" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F743" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G743" s="68" t="s">
+        <v>4220</v>
+      </c>
+      <c r="H743" s="67" t="s">
+        <v>810</v>
+      </c>
+      <c r="I743" s="69" t="s">
+        <v>4221</v>
+      </c>
+      <c r="J743" s="70">
+        <v>0</v>
+      </c>
+      <c r="K743" s="71" t="s">
+        <v>4222</v>
+      </c>
+      <c r="L743" s="72" t="s">
+        <v>4223</v>
+      </c>
+      <c r="M743" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="N743" s="72" t="s">
+        <v>4224</v>
+      </c>
+      <c r="O743" s="72" t="s">
+        <v>4225</v>
+      </c>
+      <c r="P743" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q743" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="R743" s="73" t="s">
+        <v>4065</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63F588C-6C2B-8141-B305-4EF813B3A5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2E8229-B41A-084C-8891-136DFDB54A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -26798,12 +26798,228 @@
         </r>
       </text>
     </comment>
+    <comment ref="I750" authorId="0" shapeId="0" xr:uid="{2989461E-9534-E246-A14D-36792F28E499}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>영란</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김아영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>춘심</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박채원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>인순</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>허순미</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>분한</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이예지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>석구</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지철</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>가을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>하은주</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10490" uniqueCount="4274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10504" uniqueCount="4280">
   <si>
     <t>시즌</t>
   </si>
@@ -39625,6 +39841,24 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/293009</t>
+  </si>
+  <si>
+    <t>오지게 재밌는 가시나들</t>
+  </si>
+  <si>
+    <t>김아영, 박채원, 허순미, 이예지, 김지철, 하은주</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pPqOmgwZK5Dl37OyYzFI2JiDg3Ig6G93/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224289468960</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.ev4zrquirwo5</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/293452</t>
   </si>
 </sst>
 </file>
@@ -40969,7 +41203,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R749" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R750" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -41295,7 +41529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U749"/>
+  <dimension ref="A1:U750"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -84619,59 +84853,115 @@
       </c>
     </row>
     <row r="749" spans="1:18" ht="17" customHeight="1">
-      <c r="A749" s="64">
+      <c r="A749" s="50">
         <v>748</v>
       </c>
-      <c r="B749" s="65">
+      <c r="B749" s="51">
         <v>46156</v>
       </c>
-      <c r="C749" s="66">
+      <c r="C749" s="52">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D749" s="67" t="s">
+      <c r="D749" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="E749" s="67" t="s">
+      <c r="E749" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="F749" s="67" t="s">
+      <c r="F749" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G749" s="68" t="s">
+      <c r="G749" s="54" t="s">
         <v>4267</v>
       </c>
-      <c r="H749" s="67" t="s">
+      <c r="H749" s="53" t="s">
         <v>358</v>
       </c>
-      <c r="I749" s="69" t="s">
+      <c r="I749" s="63" t="s">
         <v>4268</v>
       </c>
-      <c r="J749" s="70">
+      <c r="J749" s="58">
         <v>0</v>
       </c>
-      <c r="K749" s="71" t="s">
+      <c r="K749" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="L749" s="72" t="s">
+      <c r="L749" s="55" t="s">
         <v>4269</v>
       </c>
       <c r="M749" s="56" t="s">
         <v>4270</v>
       </c>
-      <c r="N749" s="72" t="s">
+      <c r="N749" s="55" t="s">
         <v>4271</v>
       </c>
-      <c r="O749" s="72" t="s">
+      <c r="O749" s="55" t="s">
         <v>4272</v>
       </c>
-      <c r="P749" s="72" t="s">
+      <c r="P749" s="55" t="s">
         <v>4273</v>
       </c>
-      <c r="Q749" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R749" s="73" t="s">
+      <c r="Q749" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="R749" s="47" t="s">
         <v>3409</v>
+      </c>
+    </row>
+    <row r="750" spans="1:18" ht="17" customHeight="1">
+      <c r="A750" s="64">
+        <v>749</v>
+      </c>
+      <c r="B750" s="65">
+        <v>46160</v>
+      </c>
+      <c r="C750" s="66">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D750" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E750" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F750" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G750" s="68" t="s">
+        <v>4274</v>
+      </c>
+      <c r="H750" s="67" t="s">
+        <v>358</v>
+      </c>
+      <c r="I750" s="69" t="s">
+        <v>4275</v>
+      </c>
+      <c r="J750" s="70">
+        <v>0</v>
+      </c>
+      <c r="K750" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L750" s="72" t="s">
+        <v>4276</v>
+      </c>
+      <c r="M750" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="N750" s="72" t="s">
+        <v>4277</v>
+      </c>
+      <c r="O750" s="72" t="s">
+        <v>4278</v>
+      </c>
+      <c r="P750" s="72" t="s">
+        <v>4279</v>
+      </c>
+      <c r="Q750" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R750" s="73" t="s">
+        <v>3413</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2E8229-B41A-084C-8891-136DFDB54A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5403461-1BD8-BB40-882D-ABC2EA519B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -26798,16 +26798,35 @@
         </r>
       </text>
     </comment>
-    <comment ref="I750" authorId="0" shapeId="0" xr:uid="{2989461E-9534-E246-A14D-36792F28E499}">
+    <comment ref="I750" authorId="0" shapeId="0" xr:uid="{CEFE388D-3815-5148-B33A-30C4A4D6DF10}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>영란</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>영란: 김아영
+춘심: 박채원
+인순: 허순미
+분한: 이예지
+석구: 김지철
+가을: 하은주</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I751" authorId="0" shapeId="0" xr:uid="{08305B0C-6495-1249-B3FE-B26C154EA30C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>엠마</t>
         </r>
         <r>
           <rPr>
@@ -26825,7 +26844,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>김아영</t>
+          <t>랑연</t>
         </r>
         <r>
           <rPr>
@@ -26844,7 +26863,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>춘심</t>
+          <t>제인</t>
         </r>
         <r>
           <rPr>
@@ -26862,7 +26881,38 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>박채원</t>
+          <t>최수현</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I752" authorId="0" shapeId="0" xr:uid="{A7401A0B-63CC-C94D-A995-DF327C4DAA15}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>디아길레프</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>안재영</t>
         </r>
         <r>
           <rPr>
@@ -26881,7 +26931,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>인순</t>
+          <t>브누아</t>
         </r>
         <r>
           <rPr>
@@ -26899,7 +26949,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>허순미</t>
+          <t>김수호</t>
         </r>
         <r>
           <rPr>
@@ -26918,7 +26968,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>분한</t>
+          <t>니진스키</t>
         </r>
         <r>
           <rPr>
@@ -26936,7 +26986,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>이예지</t>
+          <t>김태연</t>
         </r>
         <r>
           <rPr>
@@ -26955,7 +27005,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>석구</t>
+          <t>스트라빈스키</t>
         </r>
         <r>
           <rPr>
@@ -26973,44 +27023,34 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>김지철</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>가을</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>하은주</t>
+          <t>김도하</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지훈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
         </r>
       </text>
     </comment>
@@ -27019,7 +27059,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10504" uniqueCount="4280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10539" uniqueCount="4293">
   <si>
     <t>시즌</t>
   </si>
@@ -39859,6 +39899,45 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/293452</t>
+  </si>
+  <si>
+    <t>앤유컴퍼니</t>
+  </si>
+  <si>
+    <t>더 펜</t>
+  </si>
+  <si>
+    <t>랑연, 최수현</t>
+  </si>
+  <si>
+    <t>안재영, 김수호, 김태연, 김도하(김지훈)</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1dImYrmSOw5FHccYa-Owb2xbUyazV_wkv/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1O0CxU7BAZApAHZK8oDgFMN-9LB1NsS6g/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224299116880</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.wvdqm2w4d6r7</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/294298</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qraLbg3O9fjyc6FTprDxaPi5O_ZLeo22/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224299120494</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.es2fvfqzcyy8</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/294398</t>
   </si>
 </sst>
 </file>
@@ -40281,34 +40360,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -41203,7 +41282,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R750" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R753" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -41529,7 +41608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U750"/>
+  <dimension ref="A1:U753"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -84909,59 +84988,205 @@
       </c>
     </row>
     <row r="750" spans="1:18" ht="17" customHeight="1">
-      <c r="A750" s="64">
+      <c r="A750" s="50">
         <v>749</v>
       </c>
-      <c r="B750" s="65">
+      <c r="B750" s="51">
         <v>46160</v>
       </c>
-      <c r="C750" s="66">
+      <c r="C750" s="52">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D750" s="67" t="s">
+      <c r="D750" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="E750" s="67" t="s">
+      <c r="E750" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="F750" s="67" t="s">
+      <c r="F750" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="G750" s="68" t="s">
+      <c r="G750" s="54" t="s">
         <v>4274</v>
       </c>
-      <c r="H750" s="67" t="s">
+      <c r="H750" s="53" t="s">
         <v>358</v>
       </c>
-      <c r="I750" s="69" t="s">
+      <c r="I750" s="63" t="s">
         <v>4275</v>
       </c>
-      <c r="J750" s="70">
+      <c r="J750" s="58">
         <v>0</v>
       </c>
-      <c r="K750" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L750" s="72" t="s">
+      <c r="K750" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L750" s="55" t="s">
         <v>4276</v>
       </c>
       <c r="M750" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="N750" s="72" t="s">
+      <c r="N750" s="55" t="s">
         <v>4277</v>
       </c>
-      <c r="O750" s="72" t="s">
+      <c r="O750" s="55" t="s">
         <v>4278</v>
       </c>
-      <c r="P750" s="72" t="s">
+      <c r="P750" s="55" t="s">
         <v>4279</v>
       </c>
-      <c r="Q750" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R750" s="73" t="s">
+      <c r="Q750" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="R750" s="47" t="s">
         <v>3413</v>
+      </c>
+    </row>
+    <row r="751" spans="1:18" ht="17" customHeight="1">
+      <c r="A751" s="64">
+        <v>750</v>
+      </c>
+      <c r="B751" s="65">
+        <v>46168</v>
+      </c>
+      <c r="C751" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D751" s="67" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E751" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F751" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G751" s="68" t="s">
+        <v>4281</v>
+      </c>
+      <c r="H751" s="67" t="s">
+        <v>358</v>
+      </c>
+      <c r="I751" s="69" t="s">
+        <v>4282</v>
+      </c>
+      <c r="J751" s="70">
+        <v>0</v>
+      </c>
+      <c r="K751" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L751" s="72" t="s">
+        <v>4276</v>
+      </c>
+      <c r="M751" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N751" s="72" t="s">
+        <v>4277</v>
+      </c>
+      <c r="O751" s="72" t="s">
+        <v>4278</v>
+      </c>
+      <c r="P751" s="72" t="s">
+        <v>4279</v>
+      </c>
+      <c r="Q751" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R751" s="73" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="752" spans="1:18" ht="17" customHeight="1">
+      <c r="A752" s="64">
+        <v>751</v>
+      </c>
+      <c r="B752" s="65">
+        <v>46169</v>
+      </c>
+      <c r="C752" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D752" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E752" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="F752" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G752" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="H752" s="67" t="s">
+        <v>359</v>
+      </c>
+      <c r="I752" s="69" t="s">
+        <v>4283</v>
+      </c>
+      <c r="J752" s="70">
+        <v>10000</v>
+      </c>
+      <c r="K752" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="L752" s="72" t="s">
+        <v>4284</v>
+      </c>
+      <c r="M752" s="15" t="s">
+        <v>4285</v>
+      </c>
+      <c r="N752" s="72" t="s">
+        <v>4286</v>
+      </c>
+      <c r="O752" s="72" t="s">
+        <v>4287</v>
+      </c>
+      <c r="P752" s="72" t="s">
+        <v>4288</v>
+      </c>
+      <c r="Q752" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R752" s="73" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="753" spans="1:18" ht="17" customHeight="1">
+      <c r="A753" s="64"/>
+      <c r="B753" s="65"/>
+      <c r="C753" s="66"/>
+      <c r="D753" s="67"/>
+      <c r="E753" s="67"/>
+      <c r="F753" s="67"/>
+      <c r="G753" s="68"/>
+      <c r="H753" s="67"/>
+      <c r="I753" s="69"/>
+      <c r="J753" s="70"/>
+      <c r="K753" s="71"/>
+      <c r="L753" s="72" t="s">
+        <v>4289</v>
+      </c>
+      <c r="M753" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N753" s="72" t="s">
+        <v>4290</v>
+      </c>
+      <c r="O753" s="72" t="s">
+        <v>4291</v>
+      </c>
+      <c r="P753" s="72" t="s">
+        <v>4292</v>
+      </c>
+      <c r="Q753" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R753" s="73" t="s">
+        <v>3409</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5403461-1BD8-BB40-882D-ABC2EA519B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC734D3-F49A-3E4F-9FFB-36490543B11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27059,7 +27059,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10539" uniqueCount="4293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10532" uniqueCount="4293">
   <si>
     <t>시즌</t>
   </si>
@@ -40169,7 +40169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -40360,35 +40360,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -41282,7 +41255,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R753" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R752" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -41608,7 +41581,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U753"/>
+  <dimension ref="A1:U752"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -85044,148 +85017,114 @@
       </c>
     </row>
     <row r="751" spans="1:18" ht="17" customHeight="1">
-      <c r="A751" s="64">
+      <c r="A751" s="46">
         <v>750</v>
       </c>
-      <c r="B751" s="65">
+      <c r="B751" s="37">
         <v>46168</v>
       </c>
-      <c r="C751" s="66">
+      <c r="C751" s="38">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D751" s="67" t="s">
+      <c r="D751" s="36" t="s">
         <v>4280</v>
       </c>
-      <c r="E751" s="67" t="s">
+      <c r="E751" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="F751" s="67" t="s">
+      <c r="F751" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="G751" s="68" t="s">
+      <c r="G751" s="39" t="s">
         <v>4281</v>
       </c>
-      <c r="H751" s="67" t="s">
+      <c r="H751" s="36" t="s">
         <v>358</v>
       </c>
-      <c r="I751" s="69" t="s">
+      <c r="I751" s="64" t="s">
         <v>4282</v>
       </c>
-      <c r="J751" s="70">
+      <c r="J751" s="62">
         <v>0</v>
       </c>
-      <c r="K751" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L751" s="72" t="s">
-        <v>4276</v>
+      <c r="K751" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L751" s="40" t="s">
+        <v>4284</v>
       </c>
       <c r="M751" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="N751" s="72" t="s">
-        <v>4277</v>
-      </c>
-      <c r="O751" s="72" t="s">
-        <v>4278</v>
-      </c>
-      <c r="P751" s="72" t="s">
-        <v>4279</v>
-      </c>
-      <c r="Q751" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R751" s="73" t="s">
-        <v>3413</v>
+        <v>4285</v>
+      </c>
+      <c r="N751" s="40" t="s">
+        <v>4286</v>
+      </c>
+      <c r="O751" s="40" t="s">
+        <v>4287</v>
+      </c>
+      <c r="P751" s="40" t="s">
+        <v>4288</v>
+      </c>
+      <c r="Q751" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R751" s="47" t="s">
+        <v>3409</v>
       </c>
     </row>
     <row r="752" spans="1:18" ht="17" customHeight="1">
-      <c r="A752" s="64">
+      <c r="A752" s="46">
         <v>751</v>
       </c>
-      <c r="B752" s="65">
+      <c r="B752" s="37">
         <v>46169</v>
       </c>
-      <c r="C752" s="66">
+      <c r="C752" s="38">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D752" s="67" t="s">
+      <c r="D752" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="E752" s="67" t="s">
+      <c r="E752" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F752" s="67" t="s">
+      <c r="F752" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="G752" s="68" t="s">
+      <c r="G752" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="H752" s="67" t="s">
+      <c r="H752" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="I752" s="69" t="s">
+      <c r="I752" s="64" t="s">
         <v>4283</v>
       </c>
-      <c r="J752" s="70">
+      <c r="J752" s="62">
         <v>10000</v>
       </c>
-      <c r="K752" s="71" t="s">
+      <c r="K752" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="L752" s="72" t="s">
-        <v>4284</v>
+      <c r="L752" s="40" t="s">
+        <v>4289</v>
       </c>
       <c r="M752" s="15" t="s">
-        <v>4285</v>
-      </c>
-      <c r="N752" s="72" t="s">
-        <v>4286</v>
-      </c>
-      <c r="O752" s="72" t="s">
-        <v>4287</v>
-      </c>
-      <c r="P752" s="72" t="s">
-        <v>4288</v>
-      </c>
-      <c r="Q752" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R752" s="73" t="s">
-        <v>3409</v>
-      </c>
-    </row>
-    <row r="753" spans="1:18" ht="17" customHeight="1">
-      <c r="A753" s="64"/>
-      <c r="B753" s="65"/>
-      <c r="C753" s="66"/>
-      <c r="D753" s="67"/>
-      <c r="E753" s="67"/>
-      <c r="F753" s="67"/>
-      <c r="G753" s="68"/>
-      <c r="H753" s="67"/>
-      <c r="I753" s="69"/>
-      <c r="J753" s="70"/>
-      <c r="K753" s="71"/>
-      <c r="L753" s="72" t="s">
-        <v>4289</v>
-      </c>
-      <c r="M753" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="N753" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="N752" s="40" t="s">
         <v>4290</v>
       </c>
-      <c r="O753" s="72" t="s">
+      <c r="O752" s="40" t="s">
         <v>4291</v>
       </c>
-      <c r="P753" s="72" t="s">
+      <c r="P752" s="40" t="s">
         <v>4292</v>
       </c>
-      <c r="Q753" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R753" s="73" t="s">
+      <c r="Q752" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R752" s="47" t="s">
         <v>3409</v>
       </c>
     </row>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4E7A77-12A2-164B-B1A8-1AE1033ADA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99376BAD-CC7D-2E40-9C6C-0A593526C9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17730,7 +17730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I757" authorId="0" shapeId="0" xr:uid="{107222E2-90CF-9E4D-A4CB-BBDB450BA4BA}">
+    <comment ref="I757" authorId="0" shapeId="0" xr:uid="{28C7C55E-DDA1-6645-8DE0-8DFB7B007FE3}">
       <text>
         <r>
           <rPr>
@@ -17798,7 +17798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I758" authorId="0" shapeId="0" xr:uid="{8A67D142-F58B-CD41-93BB-5510A06DF4FE}">
+    <comment ref="I758" authorId="0" shapeId="0" xr:uid="{D7E86292-FE08-354B-8DB3-7BE1393AA871}">
       <text>
         <r>
           <rPr>
@@ -17826,6 +17826,142 @@
             <family val="2"/>
           </rPr>
           <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I759" authorId="0" shapeId="0" xr:uid="{312EE6E9-37FC-B84D-BC3E-41198F122E93}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이주원</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I760" authorId="0" shapeId="0" xr:uid="{2030B9B5-B339-EC42-8FD7-E243BE61C261}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지상윤</t>
         </r>
         <r>
           <rPr>
@@ -17871,7 +18007,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10616" uniqueCount="4322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10644" uniqueCount="4329">
   <si>
     <t>시즌</t>
   </si>
@@ -30837,6 +30973,27 @@
   </si>
   <si>
     <t>지상윤, 김준우</t>
+  </si>
+  <si>
+    <t>주이진, 이주원</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rRPV-PskR5X0QRmaY4PGC3M6tJ5_S9AK/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224309505078</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.zapgpimrc5ek</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19peCwiE1KJ_bV6VxuZLoUQkARbR-Wibb/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224309511011</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.m9nhdfb9ws88</t>
   </si>
 </sst>
 </file>
@@ -31068,7 +31225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31261,6 +31418,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -32154,7 +32341,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R758" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R760" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32480,7 +32667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U758"/>
+  <dimension ref="A1:U760"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -76363,6 +76550,118 @@
         <v>3409</v>
       </c>
     </row>
+    <row r="759" spans="1:18" ht="17" customHeight="1">
+      <c r="A759" s="65">
+        <v>758</v>
+      </c>
+      <c r="B759" s="66">
+        <v>46179</v>
+      </c>
+      <c r="C759" s="67">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D759" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E759" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F759" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G759" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H759" s="68" t="s">
+        <v>362</v>
+      </c>
+      <c r="I759" s="70" t="s">
+        <v>4322</v>
+      </c>
+      <c r="J759" s="71">
+        <v>19320</v>
+      </c>
+      <c r="K759" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L759" s="73" t="s">
+        <v>4323</v>
+      </c>
+      <c r="M759" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N759" s="73" t="s">
+        <v>4324</v>
+      </c>
+      <c r="O759" s="73" t="s">
+        <v>4325</v>
+      </c>
+      <c r="P759" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q759" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R759" s="74" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="760" spans="1:18" ht="17" customHeight="1">
+      <c r="A760" s="65">
+        <v>759</v>
+      </c>
+      <c r="B760" s="66">
+        <v>46180</v>
+      </c>
+      <c r="C760" s="67">
+        <v>0.75</v>
+      </c>
+      <c r="D760" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E760" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F760" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G760" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H760" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="I760" s="70" t="s">
+        <v>4321</v>
+      </c>
+      <c r="J760" s="71">
+        <v>19320</v>
+      </c>
+      <c r="K760" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L760" s="73" t="s">
+        <v>4326</v>
+      </c>
+      <c r="M760" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N760" s="73" t="s">
+        <v>4327</v>
+      </c>
+      <c r="O760" s="73" t="s">
+        <v>4328</v>
+      </c>
+      <c r="P760" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q760" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R760" s="74" t="s">
+        <v>3410</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99376BAD-CC7D-2E40-9C6C-0A593526C9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CC5DAF-A28B-684F-9B79-26D5A8FE6099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18002,12 +18002,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="I761" authorId="0" shapeId="0" xr:uid="{A0441A8F-9148-6C4F-BC7D-EB399F5A5305}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 고주희
+루이: 김평화</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10644" uniqueCount="4329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10658" uniqueCount="4334">
   <si>
     <t>시즌</t>
   </si>
@@ -30994,6 +31009,21 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.m9nhdfb9ws88</t>
+  </si>
+  <si>
+    <t>고주희, 김평화</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oLA64MffMxed3T1mnS08URiqJJTk-GNJ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224312911646</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.jv3ytc81crxz</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/295766</t>
   </si>
 </sst>
 </file>
@@ -31419,34 +31449,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -32341,7 +32371,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R760" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R761" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32667,7 +32697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U760"/>
+  <dimension ref="A1:U761"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -76551,115 +76581,171 @@
       </c>
     </row>
     <row r="759" spans="1:18" ht="17" customHeight="1">
-      <c r="A759" s="65">
+      <c r="A759" s="46">
         <v>758</v>
       </c>
-      <c r="B759" s="66">
+      <c r="B759" s="37">
         <v>46179</v>
       </c>
-      <c r="C759" s="67">
+      <c r="C759" s="38">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D759" s="68" t="s">
+      <c r="D759" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E759" s="68" t="s">
+      <c r="E759" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="F759" s="68" t="s">
+      <c r="F759" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G759" s="69" t="s">
+      <c r="G759" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H759" s="68" t="s">
+      <c r="H759" s="36" t="s">
         <v>362</v>
       </c>
-      <c r="I759" s="70" t="s">
+      <c r="I759" s="64" t="s">
         <v>4322</v>
       </c>
-      <c r="J759" s="71">
+      <c r="J759" s="62">
         <v>19320</v>
       </c>
-      <c r="K759" s="72" t="s">
+      <c r="K759" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L759" s="73" t="s">
+      <c r="L759" s="40" t="s">
         <v>4323</v>
       </c>
       <c r="M759" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N759" s="73" t="s">
+      <c r="N759" s="40" t="s">
         <v>4324</v>
       </c>
-      <c r="O759" s="73" t="s">
+      <c r="O759" s="40" t="s">
         <v>4325</v>
       </c>
-      <c r="P759" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q759" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R759" s="74" t="s">
+      <c r="P759" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q759" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R759" s="47" t="s">
         <v>3409</v>
       </c>
     </row>
     <row r="760" spans="1:18" ht="17" customHeight="1">
-      <c r="A760" s="65">
+      <c r="A760" s="46">
         <v>759</v>
       </c>
-      <c r="B760" s="66">
+      <c r="B760" s="37">
         <v>46180</v>
       </c>
-      <c r="C760" s="67">
+      <c r="C760" s="38">
         <v>0.75</v>
       </c>
-      <c r="D760" s="68" t="s">
+      <c r="D760" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E760" s="68" t="s">
+      <c r="E760" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="F760" s="68" t="s">
+      <c r="F760" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G760" s="69" t="s">
+      <c r="G760" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H760" s="68" t="s">
+      <c r="H760" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="I760" s="70" t="s">
+      <c r="I760" s="64" t="s">
         <v>4321</v>
       </c>
-      <c r="J760" s="71">
+      <c r="J760" s="62">
         <v>19320</v>
       </c>
-      <c r="K760" s="72" t="s">
+      <c r="K760" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L760" s="73" t="s">
+      <c r="L760" s="40" t="s">
         <v>4326</v>
       </c>
       <c r="M760" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N760" s="73" t="s">
+      <c r="N760" s="40" t="s">
         <v>4327</v>
       </c>
-      <c r="O760" s="73" t="s">
+      <c r="O760" s="40" t="s">
         <v>4328</v>
       </c>
-      <c r="P760" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q760" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R760" s="74" t="s">
+      <c r="P760" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q760" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R760" s="47" t="s">
         <v>3410</v>
+      </c>
+    </row>
+    <row r="761" spans="1:18" ht="17" customHeight="1">
+      <c r="A761" s="65">
+        <v>760</v>
+      </c>
+      <c r="B761" s="66">
+        <v>46183</v>
+      </c>
+      <c r="C761" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D761" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E761" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F761" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G761" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H761" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="I761" s="70" t="s">
+        <v>4329</v>
+      </c>
+      <c r="J761" s="71">
+        <v>20000</v>
+      </c>
+      <c r="K761" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L761" s="73" t="s">
+        <v>4330</v>
+      </c>
+      <c r="M761" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="N761" s="73" t="s">
+        <v>4331</v>
+      </c>
+      <c r="O761" s="73" t="s">
+        <v>4332</v>
+      </c>
+      <c r="P761" s="73" t="s">
+        <v>4333</v>
+      </c>
+      <c r="Q761" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R761" s="74" t="s">
+        <v>3412</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CC5DAF-A28B-684F-9B79-26D5A8FE6099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C974F8-8032-0441-BE53-D88E87D3DF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18002,7 +18002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I761" authorId="0" shapeId="0" xr:uid="{A0441A8F-9148-6C4F-BC7D-EB399F5A5305}">
+    <comment ref="I761" authorId="0" shapeId="0" xr:uid="{15A78E2D-2A83-2942-A51E-673E8BD7595C}">
       <text>
         <r>
           <rPr>
@@ -18014,6 +18014,157 @@
           </rPr>
           <t>마크: 고주희
 루이: 김평화</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I762" authorId="0" shapeId="0" xr:uid="{02CFF90F-CD71-F243-A8CE-FD5C2E7F57B4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 지상윤
+루이: 김준우</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I763" authorId="0" shapeId="0" xr:uid="{3C649050-CA00-6A47-AE28-C7ECCCFE4383}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>고주희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이주원</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I764" authorId="0" shapeId="0" xr:uid="{CB78BE8C-6DE9-EF46-92BA-1D19A35634CA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
         </r>
       </text>
     </comment>
@@ -18022,7 +18173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10658" uniqueCount="4334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10700" uniqueCount="4345">
   <si>
     <t>시즌</t>
   </si>
@@ -31024,6 +31175,39 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/295766</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15XjxC2odL5kgHYawHN81tjZb3Qw9K5JZ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224316660589</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.sbppqhoh70u9</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vgQUWo5c9Smw8mgZOU2d7N6fNzb-Qo_Q/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224316667032</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.nhtf81md54i7</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/296037</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1J-iLTcPOeQc5HsJjY9We-soA00larJ7Q/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224317659970</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.d53t22o29ud</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/296207</t>
   </si>
 </sst>
 </file>
@@ -31449,34 +31633,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -32371,7 +32555,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R761" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R764" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32697,7 +32881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U761"/>
+  <dimension ref="A1:U764"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -76409,7 +76593,7 @@
         <v>14</v>
       </c>
       <c r="R755" s="47" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="756" spans="1:18" ht="17" customHeight="1">
@@ -76693,58 +76877,226 @@
       </c>
     </row>
     <row r="761" spans="1:18" ht="17" customHeight="1">
-      <c r="A761" s="65">
+      <c r="A761" s="50">
         <v>760</v>
       </c>
-      <c r="B761" s="66">
+      <c r="B761" s="51">
         <v>46183</v>
       </c>
-      <c r="C761" s="67">
+      <c r="C761" s="52">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D761" s="68" t="s">
+      <c r="D761" s="53" t="s">
         <v>4292</v>
       </c>
-      <c r="E761" s="68" t="s">
+      <c r="E761" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="F761" s="68" t="s">
+      <c r="F761" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="G761" s="69" t="s">
+      <c r="G761" s="54" t="s">
         <v>4293</v>
       </c>
-      <c r="H761" s="68" t="s">
+      <c r="H761" s="53" t="s">
         <v>364</v>
       </c>
-      <c r="I761" s="70" t="s">
+      <c r="I761" s="63" t="s">
         <v>4329</v>
       </c>
-      <c r="J761" s="71">
-        <v>20000</v>
-      </c>
-      <c r="K761" s="72" t="s">
+      <c r="J761" s="58">
+        <v>19180</v>
+      </c>
+      <c r="K761" s="50" t="s">
         <v>4294</v>
       </c>
-      <c r="L761" s="73" t="s">
+      <c r="L761" s="55" t="s">
         <v>4330</v>
       </c>
       <c r="M761" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="N761" s="73" t="s">
+      <c r="N761" s="55" t="s">
         <v>4331</v>
       </c>
-      <c r="O761" s="73" t="s">
+      <c r="O761" s="55" t="s">
         <v>4332</v>
       </c>
-      <c r="P761" s="73" t="s">
+      <c r="P761" s="55" t="s">
         <v>4333</v>
       </c>
-      <c r="Q761" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R761" s="74" t="s">
+      <c r="Q761" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="R761" s="47" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="762" spans="1:18" ht="17" customHeight="1">
+      <c r="A762" s="65">
+        <v>761</v>
+      </c>
+      <c r="B762" s="66">
+        <v>46185</v>
+      </c>
+      <c r="C762" s="67">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D762" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E762" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F762" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G762" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H762" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="I762" s="70" t="s">
+        <v>4321</v>
+      </c>
+      <c r="J762" s="71">
+        <v>21700</v>
+      </c>
+      <c r="K762" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L762" s="73" t="s">
+        <v>4334</v>
+      </c>
+      <c r="M762" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N762" s="73" t="s">
+        <v>4335</v>
+      </c>
+      <c r="O762" s="73" t="s">
+        <v>4336</v>
+      </c>
+      <c r="P762" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q762" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R762" s="74" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="763" spans="1:18" ht="17" customHeight="1">
+      <c r="A763" s="65">
+        <v>762</v>
+      </c>
+      <c r="B763" s="66">
+        <v>46186</v>
+      </c>
+      <c r="C763" s="67">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D763" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E763" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F763" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G763" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H763" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="I763" s="70" t="s">
+        <v>4303</v>
+      </c>
+      <c r="J763" s="71">
+        <v>14600</v>
+      </c>
+      <c r="K763" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L763" s="73" t="s">
+        <v>4337</v>
+      </c>
+      <c r="M763" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N763" s="73" t="s">
+        <v>4338</v>
+      </c>
+      <c r="O763" s="73" t="s">
+        <v>4339</v>
+      </c>
+      <c r="P763" s="73" t="s">
+        <v>4340</v>
+      </c>
+      <c r="Q763" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R763" s="74" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="764" spans="1:18" ht="17" customHeight="1">
+      <c r="A764" s="65">
+        <v>763</v>
+      </c>
+      <c r="B764" s="66">
+        <v>46188</v>
+      </c>
+      <c r="C764" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D764" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E764" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F764" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G764" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H764" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="I764" s="70" t="s">
+        <v>4309</v>
+      </c>
+      <c r="J764" s="71">
+        <v>19680</v>
+      </c>
+      <c r="K764" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L764" s="73" t="s">
+        <v>4341</v>
+      </c>
+      <c r="M764" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N764" s="73" t="s">
+        <v>4342</v>
+      </c>
+      <c r="O764" s="73" t="s">
+        <v>4343</v>
+      </c>
+      <c r="P764" s="73" t="s">
+        <v>4344</v>
+      </c>
+      <c r="Q764" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R764" s="74" t="s">
         <v>3412</v>
       </c>
     </row>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C974F8-8032-0441-BE53-D88E87D3DF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0244D00-CE9A-5640-AE18-8680BEF94D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -31439,7 +31439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31632,36 +31632,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -76442,7 +76412,7 @@
         <v>4292</v>
       </c>
       <c r="E753" s="36" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F753" s="36" t="s">
         <v>30</v>
@@ -76554,7 +76524,7 @@
         <v>4292</v>
       </c>
       <c r="E755" s="53" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F755" s="53" t="s">
         <v>30</v>
@@ -76666,7 +76636,7 @@
         <v>4292</v>
       </c>
       <c r="E757" s="36" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F757" s="36" t="s">
         <v>30</v>
@@ -76722,7 +76692,7 @@
         <v>4292</v>
       </c>
       <c r="E758" s="36" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F758" s="36" t="s">
         <v>30</v>
@@ -76778,7 +76748,7 @@
         <v>4292</v>
       </c>
       <c r="E759" s="36" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F759" s="36" t="s">
         <v>30</v>
@@ -76834,7 +76804,7 @@
         <v>4292</v>
       </c>
       <c r="E760" s="36" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F760" s="36" t="s">
         <v>30</v>
@@ -76890,7 +76860,7 @@
         <v>4292</v>
       </c>
       <c r="E761" s="53" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F761" s="53" t="s">
         <v>30</v>
@@ -76933,170 +76903,170 @@
       </c>
     </row>
     <row r="762" spans="1:18" ht="17" customHeight="1">
-      <c r="A762" s="65">
+      <c r="A762" s="46">
         <v>761</v>
       </c>
-      <c r="B762" s="66">
+      <c r="B762" s="37">
         <v>46185</v>
       </c>
-      <c r="C762" s="67">
+      <c r="C762" s="38">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D762" s="68" t="s">
+      <c r="D762" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E762" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F762" s="68" t="s">
+      <c r="E762" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F762" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G762" s="69" t="s">
+      <c r="G762" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H762" s="68" t="s">
+      <c r="H762" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="I762" s="70" t="s">
+      <c r="I762" s="64" t="s">
         <v>4321</v>
       </c>
-      <c r="J762" s="71">
+      <c r="J762" s="62">
         <v>21700</v>
       </c>
-      <c r="K762" s="72" t="s">
+      <c r="K762" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L762" s="73" t="s">
+      <c r="L762" s="40" t="s">
         <v>4334</v>
       </c>
       <c r="M762" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N762" s="73" t="s">
+      <c r="N762" s="40" t="s">
         <v>4335</v>
       </c>
-      <c r="O762" s="73" t="s">
+      <c r="O762" s="40" t="s">
         <v>4336</v>
       </c>
-      <c r="P762" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q762" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R762" s="74" t="s">
+      <c r="P762" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q762" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R762" s="47" t="s">
         <v>3411</v>
       </c>
     </row>
     <row r="763" spans="1:18" ht="17" customHeight="1">
-      <c r="A763" s="65">
+      <c r="A763" s="46">
         <v>762</v>
       </c>
-      <c r="B763" s="66">
+      <c r="B763" s="37">
         <v>46186</v>
       </c>
-      <c r="C763" s="67">
+      <c r="C763" s="38">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D763" s="68" t="s">
+      <c r="D763" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E763" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F763" s="68" t="s">
+      <c r="E763" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F763" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G763" s="69" t="s">
+      <c r="G763" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H763" s="68" t="s">
+      <c r="H763" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="I763" s="70" t="s">
+      <c r="I763" s="64" t="s">
         <v>4303</v>
       </c>
-      <c r="J763" s="71">
+      <c r="J763" s="62">
         <v>14600</v>
       </c>
-      <c r="K763" s="72" t="s">
+      <c r="K763" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L763" s="73" t="s">
+      <c r="L763" s="40" t="s">
         <v>4337</v>
       </c>
       <c r="M763" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N763" s="73" t="s">
+      <c r="N763" s="40" t="s">
         <v>4338</v>
       </c>
-      <c r="O763" s="73" t="s">
+      <c r="O763" s="40" t="s">
         <v>4339</v>
       </c>
-      <c r="P763" s="73" t="s">
+      <c r="P763" s="40" t="s">
         <v>4340</v>
       </c>
-      <c r="Q763" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R763" s="74" t="s">
+      <c r="Q763" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R763" s="47" t="s">
         <v>3409</v>
       </c>
     </row>
     <row r="764" spans="1:18" ht="17" customHeight="1">
-      <c r="A764" s="65">
+      <c r="A764" s="46">
         <v>763</v>
       </c>
-      <c r="B764" s="66">
+      <c r="B764" s="37">
         <v>46188</v>
       </c>
-      <c r="C764" s="67">
+      <c r="C764" s="38">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D764" s="68" t="s">
+      <c r="D764" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E764" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F764" s="68" t="s">
+      <c r="E764" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F764" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G764" s="69" t="s">
+      <c r="G764" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H764" s="68" t="s">
+      <c r="H764" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="I764" s="70" t="s">
+      <c r="I764" s="64" t="s">
         <v>4309</v>
       </c>
-      <c r="J764" s="71">
+      <c r="J764" s="62">
         <v>19680</v>
       </c>
-      <c r="K764" s="72" t="s">
+      <c r="K764" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L764" s="73" t="s">
+      <c r="L764" s="40" t="s">
         <v>4341</v>
       </c>
       <c r="M764" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N764" s="73" t="s">
+      <c r="N764" s="40" t="s">
         <v>4342</v>
       </c>
-      <c r="O764" s="73" t="s">
+      <c r="O764" s="40" t="s">
         <v>4343</v>
       </c>
-      <c r="P764" s="73" t="s">
+      <c r="P764" s="40" t="s">
         <v>4344</v>
       </c>
-      <c r="Q764" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R764" s="74" t="s">
+      <c r="Q764" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R764" s="47" t="s">
         <v>3412</v>
       </c>
     </row>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0244D00-CE9A-5640-AE18-8680BEF94D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CACF232-0FD8-444A-8467-8AED3FAC6FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18100,7 +18100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I764" authorId="0" shapeId="0" xr:uid="{CB78BE8C-6DE9-EF46-92BA-1D19A35634CA}">
+    <comment ref="I764" authorId="0" shapeId="0" xr:uid="{5CB322F1-764D-8E42-8F94-7E51DEC03539}">
       <text>
         <r>
           <rPr>
@@ -18165,6 +18165,104 @@
             <family val="2"/>
           </rPr>
           <t>김준우</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I765" authorId="0" shapeId="0" xr:uid="{0FE6FC5E-B7E7-D548-8A87-C6B41EECAA1C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>손유동</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>싱어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최석진</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I766" authorId="0" shapeId="0" xr:uid="{82D9D994-96D7-9441-8ADE-A21FB59BD556}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 지준형
+루이: 장수지</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I767" authorId="0" shapeId="0" xr:uid="{8C1A9B65-30BD-F043-A9D3-F84F3376D7E8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 주이진
+루이: 이주원</t>
         </r>
       </text>
     </comment>
@@ -18173,7 +18271,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10700" uniqueCount="4345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10742" uniqueCount="4357">
   <si>
     <t>시즌</t>
   </si>
@@ -31208,6 +31306,42 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/296207</t>
+  </si>
+  <si>
+    <t>손유동, 최석진</t>
+  </si>
+  <si>
+    <t>지준형, 장수지</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UKD3DtkyTgedi9ZNJ_Y3zrZE68T-x_oh/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224319881877</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.mpcsggnzchjw</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/296274</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jXh2mYxw5xUHGY6eQxCFshXSTs_9EWRs/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224319884748</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.a72wownxvrka</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KO1D7ez57GYscrqtQ24cwFqOmpWg2FMD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224319888621</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.iomx9qz4nrep</t>
   </si>
 </sst>
 </file>
@@ -32525,7 +32659,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R764" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R767" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32851,7 +32985,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U764"/>
+  <dimension ref="A1:U767"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77070,6 +77204,174 @@
         <v>3412</v>
       </c>
     </row>
+    <row r="765" spans="1:18" ht="17" customHeight="1">
+      <c r="A765" s="46">
+        <v>764</v>
+      </c>
+      <c r="B765" s="37">
+        <v>46189</v>
+      </c>
+      <c r="C765" s="38">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D765" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="E765" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F765" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G765" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H765" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="I765" s="64" t="s">
+        <v>4345</v>
+      </c>
+      <c r="J765" s="62">
+        <v>18104</v>
+      </c>
+      <c r="K765" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="L765" s="40" t="s">
+        <v>4347</v>
+      </c>
+      <c r="M765" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N765" s="40" t="s">
+        <v>4348</v>
+      </c>
+      <c r="O765" s="40" t="s">
+        <v>4349</v>
+      </c>
+      <c r="P765" s="40" t="s">
+        <v>4350</v>
+      </c>
+      <c r="Q765" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R765" s="47" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="766" spans="1:18" ht="17" customHeight="1">
+      <c r="A766" s="46">
+        <v>765</v>
+      </c>
+      <c r="B766" s="37">
+        <v>46190</v>
+      </c>
+      <c r="C766" s="38">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D766" s="36" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E766" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F766" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G766" s="39" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H766" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="I766" s="64" t="s">
+        <v>4346</v>
+      </c>
+      <c r="J766" s="62">
+        <v>8500</v>
+      </c>
+      <c r="K766" s="46" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L766" s="40" t="s">
+        <v>4351</v>
+      </c>
+      <c r="M766" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N766" s="40" t="s">
+        <v>4352</v>
+      </c>
+      <c r="O766" s="40" t="s">
+        <v>4353</v>
+      </c>
+      <c r="P766" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q766" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R766" s="47" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="767" spans="1:18" ht="17" customHeight="1">
+      <c r="A767" s="46">
+        <v>766</v>
+      </c>
+      <c r="B767" s="37">
+        <v>46190</v>
+      </c>
+      <c r="C767" s="38">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D767" s="36" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E767" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F767" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G767" s="39" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H767" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="I767" s="64" t="s">
+        <v>4322</v>
+      </c>
+      <c r="J767" s="62">
+        <v>9480</v>
+      </c>
+      <c r="K767" s="46" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L767" s="40" t="s">
+        <v>4354</v>
+      </c>
+      <c r="M767" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N767" s="40" t="s">
+        <v>4355</v>
+      </c>
+      <c r="O767" s="40" t="s">
+        <v>4356</v>
+      </c>
+      <c r="P767" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q767" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R767" s="47" t="s">
+        <v>3411</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CACF232-0FD8-444A-8467-8AED3FAC6FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB324D0-C1EE-0F47-B4AB-BF82DC04D179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18266,12 +18266,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="I768" authorId="0" shapeId="0" xr:uid="{4F4FC22B-DDBE-B944-85B9-07929D37E1C3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 정성일
+싱어: 최석진</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10742" uniqueCount="4357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10756" uniqueCount="4361">
   <si>
     <t>시즌</t>
   </si>
@@ -31342,6 +31357,18 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.iomx9qz4nrep</t>
+  </si>
+  <si>
+    <t>CD2 자셋</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OzxYi_Wr7UY37wlGreRI6nms2u3TXiLL/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224320306996</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.w8ujce5gn37s</t>
   </si>
 </sst>
 </file>
@@ -31573,7 +31600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31766,6 +31793,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -32659,7 +32716,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R767" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R768" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32985,7 +33042,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U767"/>
+  <dimension ref="A1:U768"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77372,6 +77429,62 @@
         <v>3411</v>
       </c>
     </row>
+    <row r="768" spans="1:18" ht="17" customHeight="1">
+      <c r="A768" s="65">
+        <v>767</v>
+      </c>
+      <c r="B768" s="66">
+        <v>46191</v>
+      </c>
+      <c r="C768" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D768" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="E768" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="F768" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="G768" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H768" s="68" t="s">
+        <v>4357</v>
+      </c>
+      <c r="I768" s="70" t="s">
+        <v>3732</v>
+      </c>
+      <c r="J768" s="71">
+        <v>0</v>
+      </c>
+      <c r="K768" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="L768" s="73" t="s">
+        <v>4358</v>
+      </c>
+      <c r="M768" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="N768" s="73" t="s">
+        <v>4359</v>
+      </c>
+      <c r="O768" s="73" t="s">
+        <v>4360</v>
+      </c>
+      <c r="P768" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q768" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R768" s="74" t="s">
+        <v>3411</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB324D0-C1EE-0F47-B4AB-BF82DC04D179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317B71E0-4D8D-104F-984C-DD9202D3DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18266,7 +18266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I768" authorId="0" shapeId="0" xr:uid="{4F4FC22B-DDBE-B944-85B9-07929D37E1C3}">
+    <comment ref="I768" authorId="0" shapeId="0" xr:uid="{289198E9-61D9-3041-B7FB-2B4CACD1B5AB}">
       <text>
         <r>
           <rPr>
@@ -18278,6 +18278,157 @@
           </rPr>
           <t>마크: 정성일
 싱어: 최석진</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I769" authorId="0" shapeId="0" xr:uid="{D5587B01-AC44-E940-AC15-1085F084DC1A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 주이진
+루이: 이주원</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I770" authorId="0" shapeId="0" xr:uid="{96E2F8BC-EF4D-2B4C-913B-B654B70621E7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>고주희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이주원</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I771" authorId="0" shapeId="0" xr:uid="{8361772B-3B54-3944-B48B-A3BD8F56041E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
         </r>
       </text>
     </comment>
@@ -18286,7 +18437,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10756" uniqueCount="4361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10798" uniqueCount="4371">
   <si>
     <t>시즌</t>
   </si>
@@ -31369,6 +31520,36 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.w8ujce5gn37s</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UQ8uGb8vcvYIKv9vbwsGnVbHs7XfqJV8/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224321702745</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.bu19e9i9h5gs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1C84zkbNz_SKW0IQFYhL0x5JOlrw-rlB5/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224323489076</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.8g81x017lsoc</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jUJgirLdfRAbotRylSDH5KRlxo0PvYWc/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224323492704</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.wy14egin9dmv</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/296748</t>
   </si>
 </sst>
 </file>
@@ -31794,34 +31975,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -32716,7 +32897,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R768" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R771" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33042,7 +33223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U768"/>
+  <dimension ref="A1:U771"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77430,59 +77611,227 @@
       </c>
     </row>
     <row r="768" spans="1:18" ht="17" customHeight="1">
-      <c r="A768" s="65">
+      <c r="A768" s="50">
         <v>767</v>
       </c>
-      <c r="B768" s="66">
+      <c r="B768" s="51">
         <v>46191</v>
       </c>
-      <c r="C768" s="67">
+      <c r="C768" s="52">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D768" s="68" t="s">
+      <c r="D768" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="E768" s="68" t="s">
+      <c r="E768" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="F768" s="68" t="s">
+      <c r="F768" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="G768" s="69" t="s">
+      <c r="G768" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="H768" s="68" t="s">
+      <c r="H768" s="53" t="s">
         <v>4357</v>
       </c>
-      <c r="I768" s="70" t="s">
+      <c r="I768" s="63" t="s">
         <v>3732</v>
       </c>
-      <c r="J768" s="71">
+      <c r="J768" s="58">
         <v>0</v>
       </c>
-      <c r="K768" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="L768" s="73" t="s">
+      <c r="K768" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L768" s="55" t="s">
         <v>4358</v>
       </c>
       <c r="M768" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="N768" s="73" t="s">
+      <c r="N768" s="55" t="s">
         <v>4359</v>
       </c>
-      <c r="O768" s="73" t="s">
+      <c r="O768" s="55" t="s">
         <v>4360</v>
       </c>
-      <c r="P768" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q768" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R768" s="74" t="s">
+      <c r="P768" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q768" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="R768" s="47" t="s">
         <v>3411</v>
+      </c>
+    </row>
+    <row r="769" spans="1:18" ht="17" customHeight="1">
+      <c r="A769" s="65">
+        <v>768</v>
+      </c>
+      <c r="B769" s="66">
+        <v>46192</v>
+      </c>
+      <c r="C769" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D769" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E769" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F769" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G769" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H769" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="I769" s="70" t="s">
+        <v>4322</v>
+      </c>
+      <c r="J769" s="71">
+        <v>9480</v>
+      </c>
+      <c r="K769" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L769" s="73" t="s">
+        <v>4361</v>
+      </c>
+      <c r="M769" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N769" s="73" t="s">
+        <v>4362</v>
+      </c>
+      <c r="O769" s="73" t="s">
+        <v>4363</v>
+      </c>
+      <c r="P769" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q769" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R769" s="74" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="770" spans="1:18" ht="17" customHeight="1">
+      <c r="A770" s="65">
+        <v>769</v>
+      </c>
+      <c r="B770" s="66">
+        <v>46194</v>
+      </c>
+      <c r="C770" s="67">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D770" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E770" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F770" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G770" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H770" s="68" t="s">
+        <v>370</v>
+      </c>
+      <c r="I770" s="70" t="s">
+        <v>4303</v>
+      </c>
+      <c r="J770" s="71">
+        <v>6400</v>
+      </c>
+      <c r="K770" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L770" s="73" t="s">
+        <v>4364</v>
+      </c>
+      <c r="M770" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N770" s="73" t="s">
+        <v>4365</v>
+      </c>
+      <c r="O770" s="73" t="s">
+        <v>4366</v>
+      </c>
+      <c r="P770" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q770" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R770" s="74" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="771" spans="1:18" ht="17" customHeight="1">
+      <c r="A771" s="65">
+        <v>770</v>
+      </c>
+      <c r="B771" s="66">
+        <v>46194</v>
+      </c>
+      <c r="C771" s="67">
+        <v>0.75</v>
+      </c>
+      <c r="D771" s="68" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E771" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F771" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G771" s="69" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H771" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="I771" s="70" t="s">
+        <v>4309</v>
+      </c>
+      <c r="J771" s="71">
+        <v>14600</v>
+      </c>
+      <c r="K771" s="72" t="s">
+        <v>4294</v>
+      </c>
+      <c r="L771" s="73" t="s">
+        <v>4367</v>
+      </c>
+      <c r="M771" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N771" s="73" t="s">
+        <v>4368</v>
+      </c>
+      <c r="O771" s="73" t="s">
+        <v>4369</v>
+      </c>
+      <c r="P771" s="73" t="s">
+        <v>4370</v>
+      </c>
+      <c r="Q771" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R771" s="74" t="s">
+        <v>3412</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317B71E0-4D8D-104F-984C-DD9202D3DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECDDFC5-1144-894F-8571-A67B01C9F81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18432,12 +18432,172 @@
         </r>
       </text>
     </comment>
+    <comment ref="I772" authorId="0" shapeId="0" xr:uid="{3DBE1E50-5DD9-D149-9FDA-50B0D7FD8838}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데미안</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김도빈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>싱클레어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김기택</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>크나우어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김서환</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>알폰스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>벡</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>안창용</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10798" uniqueCount="4371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10812" uniqueCount="4375">
   <si>
     <t>시즌</t>
   </si>
@@ -31550,6 +31710,18 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/296748</t>
+  </si>
+  <si>
+    <t>김도빈, 김기택, 김서환, 안창용</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hh5jCzxqkxgbjHhhkiFwtliwA_pZ1b_g/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224325775064</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.ih8lon35oa1t</t>
   </si>
 </sst>
 </file>
@@ -31781,7 +31953,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31974,36 +32146,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -32897,7 +33039,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R771" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R772" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33223,7 +33365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U771"/>
+  <dimension ref="A1:U772"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77667,171 +77809,227 @@
       </c>
     </row>
     <row r="769" spans="1:18" ht="17" customHeight="1">
-      <c r="A769" s="65">
+      <c r="A769" s="46">
         <v>768</v>
       </c>
-      <c r="B769" s="66">
+      <c r="B769" s="37">
         <v>46192</v>
       </c>
-      <c r="C769" s="67">
+      <c r="C769" s="38">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D769" s="68" t="s">
+      <c r="D769" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E769" s="68" t="s">
+      <c r="E769" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F769" s="68" t="s">
+      <c r="F769" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G769" s="69" t="s">
+      <c r="G769" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H769" s="68" t="s">
+      <c r="H769" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="I769" s="70" t="s">
+      <c r="I769" s="64" t="s">
         <v>4322</v>
       </c>
-      <c r="J769" s="71">
+      <c r="J769" s="62">
         <v>9480</v>
       </c>
-      <c r="K769" s="72" t="s">
+      <c r="K769" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L769" s="73" t="s">
+      <c r="L769" s="40" t="s">
         <v>4361</v>
       </c>
       <c r="M769" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N769" s="73" t="s">
+      <c r="N769" s="40" t="s">
         <v>4362</v>
       </c>
-      <c r="O769" s="73" t="s">
+      <c r="O769" s="40" t="s">
         <v>4363</v>
       </c>
-      <c r="P769" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q769" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R769" s="74" t="s">
+      <c r="P769" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q769" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R769" s="47" t="s">
         <v>3411</v>
       </c>
     </row>
     <row r="770" spans="1:18" ht="17" customHeight="1">
-      <c r="A770" s="65">
+      <c r="A770" s="46">
         <v>769</v>
       </c>
-      <c r="B770" s="66">
+      <c r="B770" s="37">
         <v>46194</v>
       </c>
-      <c r="C770" s="67">
+      <c r="C770" s="38">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D770" s="68" t="s">
+      <c r="D770" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E770" s="68" t="s">
+      <c r="E770" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F770" s="68" t="s">
+      <c r="F770" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G770" s="69" t="s">
+      <c r="G770" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H770" s="68" t="s">
+      <c r="H770" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="I770" s="70" t="s">
+      <c r="I770" s="64" t="s">
         <v>4303</v>
       </c>
-      <c r="J770" s="71">
+      <c r="J770" s="62">
         <v>6400</v>
       </c>
-      <c r="K770" s="72" t="s">
+      <c r="K770" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L770" s="73" t="s">
+      <c r="L770" s="40" t="s">
         <v>4364</v>
       </c>
       <c r="M770" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N770" s="73" t="s">
+      <c r="N770" s="40" t="s">
         <v>4365</v>
       </c>
-      <c r="O770" s="73" t="s">
+      <c r="O770" s="40" t="s">
         <v>4366</v>
       </c>
-      <c r="P770" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q770" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R770" s="74" t="s">
+      <c r="P770" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q770" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R770" s="47" t="s">
         <v>3409</v>
       </c>
     </row>
     <row r="771" spans="1:18" ht="17" customHeight="1">
-      <c r="A771" s="65">
+      <c r="A771" s="46">
         <v>770</v>
       </c>
-      <c r="B771" s="66">
+      <c r="B771" s="37">
         <v>46194</v>
       </c>
-      <c r="C771" s="67">
+      <c r="C771" s="38">
         <v>0.75</v>
       </c>
-      <c r="D771" s="68" t="s">
+      <c r="D771" s="36" t="s">
         <v>4292</v>
       </c>
-      <c r="E771" s="68" t="s">
+      <c r="E771" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F771" s="68" t="s">
+      <c r="F771" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G771" s="69" t="s">
+      <c r="G771" s="39" t="s">
         <v>4293</v>
       </c>
-      <c r="H771" s="68" t="s">
+      <c r="H771" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="I771" s="70" t="s">
+      <c r="I771" s="64" t="s">
         <v>4309</v>
       </c>
-      <c r="J771" s="71">
+      <c r="J771" s="62">
         <v>14600</v>
       </c>
-      <c r="K771" s="72" t="s">
+      <c r="K771" s="46" t="s">
         <v>4294</v>
       </c>
-      <c r="L771" s="73" t="s">
+      <c r="L771" s="40" t="s">
         <v>4367</v>
       </c>
       <c r="M771" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N771" s="73" t="s">
+      <c r="N771" s="40" t="s">
         <v>4368</v>
       </c>
-      <c r="O771" s="73" t="s">
+      <c r="O771" s="40" t="s">
         <v>4369</v>
       </c>
-      <c r="P771" s="73" t="s">
+      <c r="P771" s="40" t="s">
         <v>4370</v>
       </c>
-      <c r="Q771" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R771" s="74" t="s">
+      <c r="Q771" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R771" s="47" t="s">
         <v>3412</v>
+      </c>
+    </row>
+    <row r="772" spans="1:18" ht="17" customHeight="1">
+      <c r="A772" s="46">
+        <v>771</v>
+      </c>
+      <c r="B772" s="37">
+        <v>46196</v>
+      </c>
+      <c r="C772" s="38">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D772" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="E772" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F772" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G772" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="H772" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="I772" s="64" t="s">
+        <v>4371</v>
+      </c>
+      <c r="J772" s="62">
+        <v>0</v>
+      </c>
+      <c r="K772" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="L772" s="40" t="s">
+        <v>4372</v>
+      </c>
+      <c r="M772" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N772" s="40" t="s">
+        <v>4373</v>
+      </c>
+      <c r="O772" s="40" t="s">
+        <v>4374</v>
+      </c>
+      <c r="P772" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q772" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R772" s="47" t="s">
+        <v>3411</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECDDFC5-1144-894F-8571-A67B01C9F81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A6D263-7CA8-384C-AAD6-F9DB78D49B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18597,7 +18597,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10812" uniqueCount="4375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10826" uniqueCount="4379">
   <si>
     <t>시즌</t>
   </si>
@@ -31722,6 +31722,18 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.ih8lon35oa1t</t>
+  </si>
+  <si>
+    <t>양지원, 박정혁</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Der9N8kTDomNCL5Xve78p7nquX2dsl8J/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224327133120</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.cuueccia07hz</t>
   </si>
 </sst>
 </file>
@@ -31953,7 +31965,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32146,6 +32158,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33039,7 +33081,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R772" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R773" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33365,7 +33407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U772"/>
+  <dimension ref="A1:U773"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -78032,6 +78074,62 @@
         <v>3411</v>
       </c>
     </row>
+    <row r="773" spans="1:18" ht="17" customHeight="1">
+      <c r="A773" s="65">
+        <v>772</v>
+      </c>
+      <c r="B773" s="66">
+        <v>46197</v>
+      </c>
+      <c r="C773" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D773" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="E773" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="F773" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G773" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H773" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="I773" s="70" t="s">
+        <v>4375</v>
+      </c>
+      <c r="J773" s="71">
+        <v>33000</v>
+      </c>
+      <c r="K773" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="L773" s="73" t="s">
+        <v>4376</v>
+      </c>
+      <c r="M773" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N773" s="73" t="s">
+        <v>4377</v>
+      </c>
+      <c r="O773" s="73" t="s">
+        <v>4378</v>
+      </c>
+      <c r="P773" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q773" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R773" s="74" t="s">
+        <v>3409</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A6D263-7CA8-384C-AAD6-F9DB78D49B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A28ACC-2B96-264E-9A2D-20EFBC31E599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18592,12 +18592,436 @@
         </r>
       </text>
     </comment>
+    <comment ref="I773" authorId="0" shapeId="0" xr:uid="{5E0BECFB-97E4-474A-8980-98C11814CFBE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>양지원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>싱어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박정혁</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I774" authorId="0" shapeId="0" xr:uid="{E7AAB728-69E1-8647-85C3-1BFEE64AE25A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>중년</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에니스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이상홍</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에니스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>델마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍승안</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>잭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>트위스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정휘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>알마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전재희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아구이레</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>민성욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>볼라디어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>문혜원</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I775" authorId="0" shapeId="0" xr:uid="{CF94F4F0-1E27-414A-860E-CFD3ABA0698E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>양지원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>싱어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최석진</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10826" uniqueCount="4379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10854" uniqueCount="4390">
   <si>
     <t>시즌</t>
   </si>
@@ -31734,6 +32158,39 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.cuueccia07hz</t>
+  </si>
+  <si>
+    <t>브로크백 마운틴</t>
+  </si>
+  <si>
+    <t>이상홍, 홍승안, 정휘, 전재희, 민성욱, 문혜원</t>
+  </si>
+  <si>
+    <t>양지원, 최석진</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11W2atEXiRdsrSL9GRCzPWcIPJ1TmSmRP/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224329764958</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.qupadfeskihp</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/297156</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Q6zSp4xGONbuHBZ3vaEDYFhuVEqtn5Tb/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224329766765</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.ba1wqc14qrt6</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/297211</t>
   </si>
 </sst>
 </file>
@@ -33081,7 +33538,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R773" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R775" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33407,7 +33864,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U773"/>
+  <dimension ref="A1:U775"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -78075,58 +78532,170 @@
       </c>
     </row>
     <row r="773" spans="1:18" ht="17" customHeight="1">
-      <c r="A773" s="65">
+      <c r="A773" s="46">
         <v>772</v>
       </c>
-      <c r="B773" s="66">
+      <c r="B773" s="37">
         <v>46197</v>
       </c>
-      <c r="C773" s="67">
+      <c r="C773" s="38">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D773" s="68" t="s">
+      <c r="D773" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="E773" s="68" t="s">
+      <c r="E773" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="F773" s="68" t="s">
+      <c r="F773" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G773" s="69" t="s">
+      <c r="G773" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H773" s="68" t="s">
+      <c r="H773" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="I773" s="70" t="s">
+      <c r="I773" s="64" t="s">
         <v>4375</v>
       </c>
-      <c r="J773" s="71">
+      <c r="J773" s="62">
         <v>33000</v>
       </c>
-      <c r="K773" s="72" t="s">
+      <c r="K773" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="L773" s="73" t="s">
+      <c r="L773" s="40" t="s">
         <v>4376</v>
       </c>
       <c r="M773" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N773" s="73" t="s">
+      <c r="N773" s="40" t="s">
         <v>4377</v>
       </c>
-      <c r="O773" s="73" t="s">
+      <c r="O773" s="40" t="s">
         <v>4378</v>
       </c>
-      <c r="P773" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q773" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R773" s="74" t="s">
+      <c r="P773" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q773" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R773" s="47" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="774" spans="1:18" ht="17" customHeight="1">
+      <c r="A774" s="65">
+        <v>773</v>
+      </c>
+      <c r="B774" s="66">
+        <v>46199</v>
+      </c>
+      <c r="C774" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D774" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E774" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F774" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G774" s="69" t="s">
+        <v>4379</v>
+      </c>
+      <c r="H774" s="68" t="s">
+        <v>353</v>
+      </c>
+      <c r="I774" s="70" t="s">
+        <v>4380</v>
+      </c>
+      <c r="J774" s="71">
+        <v>30000</v>
+      </c>
+      <c r="K774" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="L774" s="73" t="s">
+        <v>4382</v>
+      </c>
+      <c r="M774" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N774" s="73" t="s">
+        <v>4383</v>
+      </c>
+      <c r="O774" s="73" t="s">
+        <v>4384</v>
+      </c>
+      <c r="P774" s="73" t="s">
+        <v>4385</v>
+      </c>
+      <c r="Q774" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R774" s="74" t="s">
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="775" spans="1:18" ht="17" customHeight="1">
+      <c r="A775" s="65">
+        <v>774</v>
+      </c>
+      <c r="B775" s="66">
+        <v>46200</v>
+      </c>
+      <c r="C775" s="67">
+        <v>0.625</v>
+      </c>
+      <c r="D775" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="E775" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="F775" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G775" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H775" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="I775" s="70" t="s">
+        <v>4381</v>
+      </c>
+      <c r="J775" s="71">
+        <v>38100</v>
+      </c>
+      <c r="K775" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="L775" s="73" t="s">
+        <v>4386</v>
+      </c>
+      <c r="M775" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N775" s="73" t="s">
+        <v>4387</v>
+      </c>
+      <c r="O775" s="73" t="s">
+        <v>4388</v>
+      </c>
+      <c r="P775" s="73" t="s">
+        <v>4389</v>
+      </c>
+      <c r="Q775" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R775" s="74" t="s">
         <v>3409</v>
       </c>
     </row>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85732A9A-636E-2E4B-890F-59A5B3AE4521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7F1E23-63D0-D849-BDD9-0556058D4FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17662,17 +17662,286 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>중년 에니스: 이상홍
-에니스 델마: 홍승안
-잭 트위스트: 정휘
-알마: 전재희
-조 아구이레: 민성욱
-볼라디어: 문혜원</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>중년</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에니스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이상홍</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에니스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>델마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍승안</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>잭</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>트위스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정휘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>알마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전재희</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아구이레</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>민성욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>볼라디어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>문혜원</t>
         </r>
       </text>
     </comment>
@@ -17771,6 +18040,74 @@
             <family val="2"/>
           </rPr>
           <t>이동연</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I778" authorId="0" shapeId="0" xr:uid="{9AFA5130-D535-0244-A175-70A56B759544}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>어둑시니</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>소문</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신주협</t>
         </r>
       </text>
     </comment>
@@ -17779,7 +18116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10882" uniqueCount="4403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10896" uniqueCount="4410">
   <si>
     <t>시즌</t>
   </si>
@@ -30988,6 +31325,27 @@
   </si>
   <si>
     <t>https://blog.naver.com/playnmu/224335450284</t>
+  </si>
+  <si>
+    <t>어둑시니</t>
+  </si>
+  <si>
+    <t>강찬, 신주협</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sFHMGo67LZw30RfFffMLj7I6qnTsLrai/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QTgr_zCRl0vHDXPNtajUYyh-aL05L6B2/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224338498458</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.umiqun3j9y46</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/297992</t>
   </si>
 </sst>
 </file>
@@ -31219,7 +31577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31395,12 +31753,438 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2E081884-2A09-B448-BF80-BA6986B8AEF0}"/>
   </cellStyles>
   <dxfs count="20">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="1"/>
+        <color theme="0"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="1"/>
+        <color theme="0"/>
+        <name val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </left>
+        <right style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="6" tint="0.59996337778862885"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -31828,402 +32612,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="1"/>
-        <color theme="0"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical/>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical/>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="1"/>
-        <color theme="0"/>
-        <name val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </left>
-        <right style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="6" tint="0.59996337778862885"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
         <name val="굴림"/>
@@ -32295,29 +32683,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R777" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R778" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{DC85AE02-0EA8-42E3-87F8-D865EFA4C2E6}" name="횟수" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{B48C796F-E8C4-41A8-BCBF-8301C4ACBAA1}" name="날짜" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{0982F33A-F661-4470-82DC-9010353F0976}" name="시간" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{36F5BE2E-308F-4A12-B91B-50C9A00FBDFC}" name="제작사" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{9EBAAD07-3822-40DC-8509-3824D2EA9ECB}" name="시즌" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{13EC2912-E34E-496D-A727-7E5D62D23C1C}" name="장르" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{F6BCF58A-D337-4D1E-9C37-8C8EE7094378}" name="극" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{F9A57261-368E-4D7A-A8FB-E2D256003A37}" name="자n" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{D2D74C4D-6259-4846-847D-4CDCDA777F11}" name="캐슷" dataDxfId="0"/>
-    <tableColumn id="12" xr3:uid="{33891BFD-5636-4885-9C06-9FDF54A496F7}" name="가격" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{C87BCB63-7DDA-47D4-896C-AA919F4BD984}" name="극장" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{BCB3F920-9D4A-7741-8D5F-63E4E1EE292F}" name="CB" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{B5E83DAF-333E-BF4E-9765-4291CA09D193}" name="CB2" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{D0C2394A-0151-764C-8473-A40EBB50F95D}" name="캐보" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{2AC81BF4-8913-FE47-A8CF-DB8AF6BF5947}" name="후기" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{13FCC05F-283B-FF40-AFF3-973A3EC7C428}" name="L1" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{6C402620-F383-6846-A38C-7174940478F8}" name="L2" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{F99FBB31-0EF1-6645-9A28-C8E3DFE613DF}" name="RV" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{DC85AE02-0EA8-42E3-87F8-D865EFA4C2E6}" name="횟수" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{B48C796F-E8C4-41A8-BCBF-8301C4ACBAA1}" name="날짜" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{0982F33A-F661-4470-82DC-9010353F0976}" name="시간" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{36F5BE2E-308F-4A12-B91B-50C9A00FBDFC}" name="제작사" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{9EBAAD07-3822-40DC-8509-3824D2EA9ECB}" name="시즌" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{13EC2912-E34E-496D-A727-7E5D62D23C1C}" name="장르" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{F6BCF58A-D337-4D1E-9C37-8C8EE7094378}" name="극" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{F9A57261-368E-4D7A-A8FB-E2D256003A37}" name="자n" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{D2D74C4D-6259-4846-847D-4CDCDA777F11}" name="캐슷" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{33891BFD-5636-4885-9C06-9FDF54A496F7}" name="가격" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{C87BCB63-7DDA-47D4-896C-AA919F4BD984}" name="극장" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{BCB3F920-9D4A-7741-8D5F-63E4E1EE292F}" name="CB" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{B5E83DAF-333E-BF4E-9765-4291CA09D193}" name="CB2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{D0C2394A-0151-764C-8473-A40EBB50F95D}" name="캐보" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{2AC81BF4-8913-FE47-A8CF-DB8AF6BF5947}" name="후기" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{13FCC05F-283B-FF40-AFF3-973A3EC7C428}" name="L1" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{6C402620-F383-6846-A38C-7174940478F8}" name="L2" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{F99FBB31-0EF1-6645-9A28-C8E3DFE613DF}" name="RV" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -32621,7 +33009,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U777"/>
+  <dimension ref="A1:U778"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77568,6 +77956,62 @@
         <v>3409</v>
       </c>
     </row>
+    <row r="778" spans="1:18" ht="17" customHeight="1">
+      <c r="A778" s="59">
+        <v>777</v>
+      </c>
+      <c r="B778" s="60">
+        <v>46209</v>
+      </c>
+      <c r="C778" s="61">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D778" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="E778" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F778" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G778" s="63" t="s">
+        <v>4403</v>
+      </c>
+      <c r="H778" s="62" t="s">
+        <v>358</v>
+      </c>
+      <c r="I778" s="64" t="s">
+        <v>4404</v>
+      </c>
+      <c r="J778" s="65">
+        <v>0</v>
+      </c>
+      <c r="K778" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="L778" s="67" t="s">
+        <v>4405</v>
+      </c>
+      <c r="M778" s="52" t="s">
+        <v>4406</v>
+      </c>
+      <c r="N778" s="67" t="s">
+        <v>4407</v>
+      </c>
+      <c r="O778" s="67" t="s">
+        <v>4408</v>
+      </c>
+      <c r="P778" s="67" t="s">
+        <v>4409</v>
+      </c>
+      <c r="Q778" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="R778" s="68" t="s">
+        <v>3409</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7F1E23-63D0-D849-BDD9-0556058D4FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DD0F3C-D35A-214B-9FEF-DA4021D699FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18111,12 +18111,148 @@
         </r>
       </text>
     </comment>
+    <comment ref="I779" authorId="0" shapeId="0" xr:uid="{D109AEA4-5D1C-614F-B3A2-D6327A3AFF7C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>양지원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>싱어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김기택</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I780" authorId="0" shapeId="0" xr:uid="{BD61076A-15C9-7746-A90D-8BF57D6AB6DA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이강우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>싱어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍승안</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10896" uniqueCount="4410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10924" uniqueCount="4418">
   <si>
     <t>시즌</t>
   </si>
@@ -31346,6 +31482,30 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/297992</t>
+  </si>
+  <si>
+    <t>양지원, 김기택</t>
+  </si>
+  <si>
+    <t>CD4 자넷</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vVk2W6M24hjvhKLBKqYpLDLzVnHfsWot/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224340405846</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.y6scay6u5v0q</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1j-zJX_0O2wO4jt8tRwbIH5viUBjB8MTu/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224340407755</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.j36u5jdp02dm</t>
   </si>
 </sst>
 </file>
@@ -31577,7 +31737,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31752,6 +31912,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32683,7 +32888,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R778" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R780" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33009,7 +33214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U778"/>
+  <dimension ref="A1:U780"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77966,50 +78171,162 @@
       <c r="C778" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D778" s="62" t="s">
+      <c r="D778" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="E778" s="62" t="s">
+      <c r="E778" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="F778" s="62" t="s">
+      <c r="F778" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="G778" s="63" t="s">
+      <c r="G778" s="62" t="s">
         <v>4403</v>
       </c>
-      <c r="H778" s="62" t="s">
+      <c r="H778" s="59" t="s">
         <v>358</v>
       </c>
-      <c r="I778" s="64" t="s">
+      <c r="I778" s="63" t="s">
         <v>4404</v>
       </c>
-      <c r="J778" s="65">
+      <c r="J778" s="54">
         <v>0</v>
       </c>
-      <c r="K778" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="L778" s="67" t="s">
+      <c r="K778" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L778" s="51" t="s">
         <v>4405</v>
       </c>
       <c r="M778" s="52" t="s">
         <v>4406</v>
       </c>
-      <c r="N778" s="67" t="s">
+      <c r="N778" s="51" t="s">
         <v>4407</v>
       </c>
-      <c r="O778" s="67" t="s">
+      <c r="O778" s="51" t="s">
         <v>4408</v>
       </c>
-      <c r="P778" s="67" t="s">
+      <c r="P778" s="51" t="s">
         <v>4409</v>
       </c>
-      <c r="Q778" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="R778" s="68" t="s">
+      <c r="Q778" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R778" s="47" t="s">
         <v>3409</v>
+      </c>
+    </row>
+    <row r="779" spans="1:18" ht="17" customHeight="1">
+      <c r="A779" s="64">
+        <v>778</v>
+      </c>
+      <c r="B779" s="65">
+        <v>46210</v>
+      </c>
+      <c r="C779" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D779" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="E779" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="F779" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="G779" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="H779" s="67" t="s">
+        <v>361</v>
+      </c>
+      <c r="I779" s="69" t="s">
+        <v>4410</v>
+      </c>
+      <c r="J779" s="70">
+        <v>11700</v>
+      </c>
+      <c r="K779" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="L779" s="72" t="s">
+        <v>4412</v>
+      </c>
+      <c r="M779" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N779" s="72" t="s">
+        <v>4413</v>
+      </c>
+      <c r="O779" s="72" t="s">
+        <v>4414</v>
+      </c>
+      <c r="P779" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q779" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R779" s="73" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="780" spans="1:18" ht="17" customHeight="1">
+      <c r="A780" s="74">
+        <v>779</v>
+      </c>
+      <c r="B780" s="75">
+        <v>46211</v>
+      </c>
+      <c r="C780" s="76">
+        <v>0</v>
+      </c>
+      <c r="D780" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="E780" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="F780" s="77" t="s">
+        <v>186</v>
+      </c>
+      <c r="G780" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="H780" s="77" t="s">
+        <v>4411</v>
+      </c>
+      <c r="I780" s="79" t="s">
+        <v>3728</v>
+      </c>
+      <c r="J780" s="80">
+        <v>0</v>
+      </c>
+      <c r="K780" s="81" t="s">
+        <v>14</v>
+      </c>
+      <c r="L780" s="82" t="s">
+        <v>4415</v>
+      </c>
+      <c r="M780" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N780" s="82" t="s">
+        <v>4416</v>
+      </c>
+      <c r="O780" s="82" t="s">
+        <v>4417</v>
+      </c>
+      <c r="P780" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q780" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="R780" s="83" t="s">
+        <v>3412</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F6DCD9-A97A-7A49-845C-E9618F21CA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F654E87-B6E7-B343-B0AB-A21D6BA3AD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -20225,12 +20225,95 @@
         </r>
       </text>
     </comment>
+    <comment ref="I782" authorId="0" shapeId="0" xr:uid="{E36ACD57-EB1E-0243-B8E2-5CEB21A3DF54}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 김유진
+싱어: 신재범</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I783" authorId="0" shapeId="0" xr:uid="{1F3A3D1C-1B02-4843-91BD-6D8300EE7220}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>노아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>곽민수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조슬린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박영수</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10938" uniqueCount="4421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10966" uniqueCount="4430">
   <si>
     <t>시즌</t>
   </si>
@@ -33493,6 +33576,33 @@
   </si>
   <si>
     <t>조성윤, 한재원(김민성), 김청아, 이기현</t>
+  </si>
+  <si>
+    <t>CD3 자둘</t>
+  </si>
+  <si>
+    <t>곽민수, 박영수</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14e1RGzz51uNwpuFsnoy8128uICRb-Noj/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224343668587</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.l0oxelxje7rj</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EOYoxvTtP2mG1giphX1JFzRtXg79fHRD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224343670018</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.eh085cr3foke</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/298447</t>
   </si>
 </sst>
 </file>
@@ -33724,7 +33834,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -33914,6 +34024,66 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -34815,7 +34985,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R781" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R783" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -35141,7 +35311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U781"/>
+  <dimension ref="A1:U783"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -80312,6 +80482,118 @@
         <v>3409</v>
       </c>
     </row>
+    <row r="782" spans="1:18" ht="17" customHeight="1">
+      <c r="A782" s="64">
+        <v>781</v>
+      </c>
+      <c r="B782" s="65">
+        <v>46213</v>
+      </c>
+      <c r="C782" s="66">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D782" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="E782" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="F782" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="G782" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="H782" s="67" t="s">
+        <v>4421</v>
+      </c>
+      <c r="I782" s="69" t="s">
+        <v>3730</v>
+      </c>
+      <c r="J782" s="70">
+        <v>0</v>
+      </c>
+      <c r="K782" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L782" s="72" t="s">
+        <v>4423</v>
+      </c>
+      <c r="M782" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N782" s="72" t="s">
+        <v>4424</v>
+      </c>
+      <c r="O782" s="72" t="s">
+        <v>4425</v>
+      </c>
+      <c r="P782" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q782" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R782" s="73" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="783" spans="1:18" ht="17" customHeight="1">
+      <c r="A783" s="74">
+        <v>782</v>
+      </c>
+      <c r="B783" s="75">
+        <v>46214</v>
+      </c>
+      <c r="C783" s="76">
+        <v>0.625</v>
+      </c>
+      <c r="D783" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="E783" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="F783" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="G783" s="78" t="s">
+        <v>4389</v>
+      </c>
+      <c r="H783" s="77" t="s">
+        <v>359</v>
+      </c>
+      <c r="I783" s="79" t="s">
+        <v>4422</v>
+      </c>
+      <c r="J783" s="80">
+        <v>0</v>
+      </c>
+      <c r="K783" s="81" t="s">
+        <v>60</v>
+      </c>
+      <c r="L783" s="82" t="s">
+        <v>4426</v>
+      </c>
+      <c r="M783" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N783" s="82" t="s">
+        <v>4427</v>
+      </c>
+      <c r="O783" s="82" t="s">
+        <v>4428</v>
+      </c>
+      <c r="P783" s="82" t="s">
+        <v>4429</v>
+      </c>
+      <c r="Q783" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="R783" s="83" t="s">
+        <v>3411</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F654E87-B6E7-B343-B0AB-A21D6BA3AD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A464F1C-8780-F44F-8CBB-6EABA5014F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -20308,12 +20308,195 @@
         </r>
       </text>
     </comment>
+    <comment ref="I784" authorId="0" shapeId="0" xr:uid="{958EC3E7-3997-9644-A2AB-B0113D1DB4FD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Clyde Barrow : JEREMY JORDAN
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bonnie Parker : FRANCES MCCANN
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Clyde Ivan 'Buck' Barrow : GEORGE MAGUIRE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Blanche Barrow : NATALIE MCQUEEN
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Preacher : TREVOR NICHOLAS
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ted : LIAM TAMNE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cumie Barrow : GILLIAN BEVAN
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Emma Parker : JULIE YAMMANEE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Trish : ELOISE DAVIES
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Govenor Miriam Ferguson / Eleanore : DEBBIE KURUP
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Stella : CASEY AL-SHAQSY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Captain Frank Hamer : RUSSELL WILCOX
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sherriff Schmid : JEREMY SECOMB
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bob Alcorn : MATTHEW MALTHOUSE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bud / Archie : SIMON ANTHONY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Henry Barrow : ADRIAN GROVE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Young Bonnie : BEA WARD
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Young Clyde : ALBERT ATACK</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10966" uniqueCount="4430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10980" uniqueCount="4436">
   <si>
     <t>시즌</t>
   </si>
@@ -33603,6 +33786,24 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/298447</t>
+  </si>
+  <si>
+    <t>Bonnie &amp; Clyde</t>
+  </si>
+  <si>
+    <t>Jeremy Jordan, Frances McCann, George Maguire, Natalie McQueen, Trevor Nicholas, Liam Tamne</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14ZEhNVVsqeut1B9SbsdXfaqanqW0NMAE/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224345536935</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.cmh8droqm8ug</t>
+  </si>
+  <si>
+    <t>https://bonnieclydelive.com/</t>
   </si>
 </sst>
 </file>
@@ -33834,7 +34035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -34024,36 +34225,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -34985,7 +35156,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R783" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R784" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -35311,7 +35482,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U783"/>
+  <dimension ref="A1:U784"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -80483,115 +80654,171 @@
       </c>
     </row>
     <row r="782" spans="1:18" ht="17" customHeight="1">
-      <c r="A782" s="64">
+      <c r="A782" s="36">
         <v>781</v>
       </c>
-      <c r="B782" s="65">
+      <c r="B782" s="37">
         <v>46213</v>
       </c>
-      <c r="C782" s="66">
+      <c r="C782" s="38">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D782" s="67" t="s">
+      <c r="D782" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="E782" s="67" t="s">
+      <c r="E782" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F782" s="67" t="s">
+      <c r="F782" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="G782" s="68" t="s">
+      <c r="G782" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H782" s="67" t="s">
+      <c r="H782" s="36" t="s">
         <v>4421</v>
       </c>
-      <c r="I782" s="69" t="s">
+      <c r="I782" s="56" t="s">
         <v>3730</v>
       </c>
-      <c r="J782" s="70">
+      <c r="J782" s="55">
         <v>0</v>
       </c>
-      <c r="K782" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L782" s="72" t="s">
+      <c r="K782" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L782" s="40" t="s">
         <v>4423</v>
       </c>
       <c r="M782" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="N782" s="72" t="s">
+      <c r="N782" s="40" t="s">
         <v>4424</v>
       </c>
-      <c r="O782" s="72" t="s">
+      <c r="O782" s="40" t="s">
         <v>4425</v>
       </c>
-      <c r="P782" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q782" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R782" s="73" t="s">
+      <c r="P782" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q782" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R782" s="47" t="s">
         <v>3411</v>
       </c>
     </row>
     <row r="783" spans="1:18" ht="17" customHeight="1">
-      <c r="A783" s="74">
+      <c r="A783" s="59">
         <v>782</v>
       </c>
-      <c r="B783" s="75">
+      <c r="B783" s="60">
         <v>46214</v>
       </c>
-      <c r="C783" s="76">
+      <c r="C783" s="61">
         <v>0.625</v>
       </c>
-      <c r="D783" s="77" t="s">
+      <c r="D783" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="E783" s="77" t="s">
+      <c r="E783" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="F783" s="77" t="s">
+      <c r="F783" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G783" s="78" t="s">
+      <c r="G783" s="62" t="s">
         <v>4389</v>
       </c>
-      <c r="H783" s="77" t="s">
+      <c r="H783" s="59" t="s">
         <v>359</v>
       </c>
-      <c r="I783" s="79" t="s">
+      <c r="I783" s="63" t="s">
         <v>4422</v>
       </c>
-      <c r="J783" s="80">
+      <c r="J783" s="54">
         <v>0</v>
       </c>
-      <c r="K783" s="81" t="s">
+      <c r="K783" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="L783" s="82" t="s">
+      <c r="L783" s="51" t="s">
         <v>4426</v>
       </c>
       <c r="M783" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="N783" s="82" t="s">
+      <c r="N783" s="51" t="s">
         <v>4427</v>
       </c>
-      <c r="O783" s="82" t="s">
+      <c r="O783" s="51" t="s">
         <v>4428</v>
       </c>
-      <c r="P783" s="82" t="s">
+      <c r="P783" s="51" t="s">
         <v>4429</v>
       </c>
-      <c r="Q783" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="R783" s="83" t="s">
+      <c r="Q783" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R783" s="47" t="s">
         <v>3411</v>
+      </c>
+    </row>
+    <row r="784" spans="1:18" ht="17" customHeight="1">
+      <c r="A784" s="64">
+        <v>783</v>
+      </c>
+      <c r="B784" s="65">
+        <v>46216</v>
+      </c>
+      <c r="C784" s="66">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D784" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E784" s="67" t="s">
+        <v>3553</v>
+      </c>
+      <c r="F784" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="G784" s="68" t="s">
+        <v>4430</v>
+      </c>
+      <c r="H784" s="67" t="s">
+        <v>3472</v>
+      </c>
+      <c r="I784" s="69" t="s">
+        <v>4431</v>
+      </c>
+      <c r="J784" s="70">
+        <v>22386</v>
+      </c>
+      <c r="K784" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L784" s="72" t="s">
+        <v>4432</v>
+      </c>
+      <c r="M784" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N784" s="72" t="s">
+        <v>4433</v>
+      </c>
+      <c r="O784" s="72" t="s">
+        <v>4434</v>
+      </c>
+      <c r="P784" s="72" t="s">
+        <v>4435</v>
+      </c>
+      <c r="Q784" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R784" s="73" t="s">
+        <v>3409</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C80EEC-89C7-CD4A-BBB5-444FD41F14CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A213DDF8-6C8F-AA44-8BD1-FC245B67D08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -16627,13 +16627,66 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>마크: 주이진
-루이: 김준우</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마크</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
         </r>
       </text>
     </comment>
@@ -17111,12 +17164,80 @@
         </r>
       </text>
     </comment>
+    <comment ref="I785" authorId="0" shapeId="0" xr:uid="{21A202C1-471B-CC4D-ABD4-AECB3DC3E1B3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>노아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조환지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조슬린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>조성윤</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10980" uniqueCount="4436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10994" uniqueCount="4441">
   <si>
     <t>시즌</t>
   </si>
@@ -30424,6 +30545,21 @@
   </si>
   <si>
     <t>https://bonnieclydelive.com/</t>
+  </si>
+  <si>
+    <t>조환지, 조성윤</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bWrLCWRdnR6Di0v0Rjyl-BgB9Dwn4s5q/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224348542211</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.n741s969aze5</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/298832</t>
   </si>
 </sst>
 </file>
@@ -30655,7 +30791,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -30845,6 +30981,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -31746,7 +31912,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R784" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R785" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32072,7 +32238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U784"/>
+  <dimension ref="A1:U785"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77411,6 +77577,62 @@
         <v>3409</v>
       </c>
     </row>
+    <row r="785" spans="1:18" ht="17" customHeight="1">
+      <c r="A785" s="64">
+        <v>784</v>
+      </c>
+      <c r="B785" s="65">
+        <v>46218</v>
+      </c>
+      <c r="C785" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D785" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="E785" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="F785" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G785" s="68" t="s">
+        <v>4389</v>
+      </c>
+      <c r="H785" s="67" t="s">
+        <v>360</v>
+      </c>
+      <c r="I785" s="69" t="s">
+        <v>4436</v>
+      </c>
+      <c r="J785" s="70">
+        <v>27000</v>
+      </c>
+      <c r="K785" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="L785" s="72" t="s">
+        <v>4437</v>
+      </c>
+      <c r="M785" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N785" s="72" t="s">
+        <v>4438</v>
+      </c>
+      <c r="O785" s="72" t="s">
+        <v>4439</v>
+      </c>
+      <c r="P785" s="72" t="s">
+        <v>4440</v>
+      </c>
+      <c r="Q785" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R785" s="73" t="s">
+        <v>3411</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A213DDF8-6C8F-AA44-8BD1-FC245B67D08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210BCB54-1348-D943-A2B2-3EB3A070D3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17232,12 +17232,42 @@
         </r>
       </text>
     </comment>
+    <comment ref="I786" authorId="0" shapeId="0" xr:uid="{6BAE2FF2-196F-DF46-889D-E770893712B3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>마크: 최호승
+싱어: 최석진</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I787" authorId="0" shapeId="0" xr:uid="{5FF807C4-9F1B-A849-97D1-D60CCCA0572B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>조너스 보튼: 박건형
+존 조우: 고상호</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10994" uniqueCount="4441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11022" uniqueCount="4452">
   <si>
     <t>시즌</t>
   </si>
@@ -30560,6 +30590,39 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/298832</t>
+  </si>
+  <si>
+    <t>최호승, 최석진</t>
+  </si>
+  <si>
+    <t>트위스트1971</t>
+  </si>
+  <si>
+    <t>댄포스가 옳았다</t>
+  </si>
+  <si>
+    <t>박건형, 고상호</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZnRJ2WRGS-SsNsRADZNPZrKwfQow4kND/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224350262600</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.mg0it9to6oc6</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bsdrPEWDIdqP1ZOewhZ0FbgY6QU3m5EQ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224350264254</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.v4ojb7iwprwo</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/299056</t>
   </si>
 </sst>
 </file>
@@ -30791,7 +30854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -30981,6 +31044,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -31912,7 +32005,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R785" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:R787" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -32238,7 +32331,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U785"/>
+  <dimension ref="A1:U787"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -77578,59 +77671,171 @@
       </c>
     </row>
     <row r="785" spans="1:18" ht="17" customHeight="1">
-      <c r="A785" s="64">
+      <c r="A785" s="59">
         <v>784</v>
       </c>
-      <c r="B785" s="65">
+      <c r="B785" s="60">
         <v>46218</v>
       </c>
-      <c r="C785" s="66">
+      <c r="C785" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D785" s="67" t="s">
+      <c r="D785" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="E785" s="67" t="s">
+      <c r="E785" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="F785" s="67" t="s">
+      <c r="F785" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G785" s="68" t="s">
+      <c r="G785" s="62" t="s">
         <v>4389</v>
       </c>
-      <c r="H785" s="67" t="s">
+      <c r="H785" s="59" t="s">
         <v>360</v>
       </c>
-      <c r="I785" s="69" t="s">
+      <c r="I785" s="63" t="s">
         <v>4436</v>
       </c>
-      <c r="J785" s="70">
+      <c r="J785" s="54">
         <v>27000</v>
       </c>
-      <c r="K785" s="71" t="s">
+      <c r="K785" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="L785" s="72" t="s">
+      <c r="L785" s="51" t="s">
         <v>4437</v>
       </c>
       <c r="M785" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="N785" s="72" t="s">
+      <c r="N785" s="51" t="s">
         <v>4438</v>
       </c>
-      <c r="O785" s="72" t="s">
+      <c r="O785" s="51" t="s">
         <v>4439</v>
       </c>
-      <c r="P785" s="72" t="s">
+      <c r="P785" s="51" t="s">
         <v>4440</v>
       </c>
-      <c r="Q785" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R785" s="73" t="s">
+      <c r="Q785" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R785" s="47" t="s">
         <v>3411</v>
+      </c>
+    </row>
+    <row r="786" spans="1:18" ht="17" customHeight="1">
+      <c r="A786" s="64">
+        <v>785</v>
+      </c>
+      <c r="B786" s="65">
+        <v>46220</v>
+      </c>
+      <c r="C786" s="66">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D786" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="E786" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="F786" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="G786" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="H786" s="67" t="s">
+        <v>362</v>
+      </c>
+      <c r="I786" s="69" t="s">
+        <v>4441</v>
+      </c>
+      <c r="J786" s="70">
+        <v>17400</v>
+      </c>
+      <c r="K786" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="L786" s="72" t="s">
+        <v>4445</v>
+      </c>
+      <c r="M786" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N786" s="72" t="s">
+        <v>4446</v>
+      </c>
+      <c r="O786" s="72" t="s">
+        <v>4447</v>
+      </c>
+      <c r="P786" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q786" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R786" s="73" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="787" spans="1:18" ht="17" customHeight="1">
+      <c r="A787" s="74">
+        <v>786</v>
+      </c>
+      <c r="B787" s="75">
+        <v>46220</v>
+      </c>
+      <c r="C787" s="76">
+        <v>0.75</v>
+      </c>
+      <c r="D787" s="77" t="s">
+        <v>4442</v>
+      </c>
+      <c r="E787" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F787" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="G787" s="78" t="s">
+        <v>4443</v>
+      </c>
+      <c r="H787" s="77" t="s">
+        <v>358</v>
+      </c>
+      <c r="I787" s="79" t="s">
+        <v>4444</v>
+      </c>
+      <c r="J787" s="80">
+        <v>25000</v>
+      </c>
+      <c r="K787" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="L787" s="82" t="s">
+        <v>4448</v>
+      </c>
+      <c r="M787" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N787" s="82" t="s">
+        <v>4449</v>
+      </c>
+      <c r="O787" s="82" t="s">
+        <v>4450</v>
+      </c>
+      <c r="P787" s="82" t="s">
+        <v>4451</v>
+      </c>
+      <c r="Q787" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="R787" s="83" t="s">
+        <v>3410</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFA02CE-B306-A44D-B5B6-3E1F9C7EB101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D50FC3E-A3D4-824A-A631-3B7A6E36BF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17929,12 +17929,43 @@
         </r>
       </text>
     </comment>
+    <comment ref="I790" authorId="0" shapeId="0" xr:uid="{BC38B764-E615-5C42-92C5-756FCFBF9397}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>생존자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>홍나현</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11839" uniqueCount="4615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11854" uniqueCount="4621">
   <si>
     <t>시즌</t>
   </si>
@@ -31779,6 +31810,24 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/299649</t>
+  </si>
+  <si>
+    <t>홍나현</t>
+  </si>
+  <si>
+    <t>더스페이스 1관</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mKJd_7KhWKil7Qi95pUZ0XGVFcoSxLrT/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EgLfzpCsJ7_-5afOfVzovZRWk303iKXO/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224358310666</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.4w7btzv0w00k</t>
   </si>
 </sst>
 </file>
@@ -32010,7 +32059,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32200,6 +32249,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33142,7 +33221,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S789" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S790" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33469,7 +33548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V789"/>
+  <dimension ref="A1:V790"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -81455,6 +81534,65 @@
         <v>3410</v>
       </c>
     </row>
+    <row r="790" spans="1:19" ht="17" customHeight="1">
+      <c r="A790" s="64">
+        <v>789</v>
+      </c>
+      <c r="B790" s="65">
+        <v>46228</v>
+      </c>
+      <c r="C790" s="66">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D790" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="E790" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="F790" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G790" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="H790" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I790" s="69" t="s">
+        <v>4615</v>
+      </c>
+      <c r="J790" s="70">
+        <v>0</v>
+      </c>
+      <c r="K790" s="71" t="s">
+        <v>4616</v>
+      </c>
+      <c r="L790" s="72" t="s">
+        <v>4617</v>
+      </c>
+      <c r="M790" s="52" t="s">
+        <v>4618</v>
+      </c>
+      <c r="N790" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O790" s="72" t="s">
+        <v>4619</v>
+      </c>
+      <c r="P790" s="72" t="s">
+        <v>4620</v>
+      </c>
+      <c r="Q790" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R790" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="S790" s="73" t="s">
+        <v>3412</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D50FC3E-A3D4-824A-A631-3B7A6E36BF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8C0CF6-49A4-BF42-AC86-BB866CFC3DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17960,12 +17960,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="I791" authorId="0" shapeId="0" xr:uid="{8AB8C1F9-8D37-164A-B7A8-9976CD440048}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>유견: 정민
+이산: 홍성원</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11854" uniqueCount="4621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11869" uniqueCount="4628">
   <si>
     <t>시즌</t>
   </si>
@@ -31828,6 +31843,27 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.4w7btzv0w00k</t>
+  </si>
+  <si>
+    <t>해몽가</t>
+  </si>
+  <si>
+    <t>정민, 홍성원</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1atjCbk60LdqTs3i3EgC0KpyVfVhJWDkg/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-CTQ25D-N4zWDHbZMuUhqKh7nJezPSk5/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224359766992</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.8zuhnmu6wo7t</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/300063</t>
   </si>
 </sst>
 </file>
@@ -33221,7 +33257,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S790" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S791" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33548,7 +33584,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V790"/>
+  <dimension ref="A1:V791"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -81535,40 +81571,40 @@
       </c>
     </row>
     <row r="790" spans="1:19" ht="17" customHeight="1">
-      <c r="A790" s="64">
+      <c r="A790" s="59">
         <v>789</v>
       </c>
-      <c r="B790" s="65">
+      <c r="B790" s="60">
         <v>46228</v>
       </c>
-      <c r="C790" s="66">
+      <c r="C790" s="61">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D790" s="67" t="s">
+      <c r="D790" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="E790" s="67" t="s">
+      <c r="E790" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="F790" s="67" t="s">
+      <c r="F790" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G790" s="68" t="s">
+      <c r="G790" s="62" t="s">
         <v>237</v>
       </c>
-      <c r="H790" s="67" t="s">
+      <c r="H790" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="I790" s="69" t="s">
+      <c r="I790" s="63" t="s">
         <v>4615</v>
       </c>
-      <c r="J790" s="70">
+      <c r="J790" s="54">
         <v>0</v>
       </c>
-      <c r="K790" s="71" t="s">
+      <c r="K790" s="50" t="s">
         <v>4616</v>
       </c>
-      <c r="L790" s="72" t="s">
+      <c r="L790" s="51" t="s">
         <v>4617</v>
       </c>
       <c r="M790" s="52" t="s">
@@ -81577,20 +81613,79 @@
       <c r="N790" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O790" s="72" t="s">
+      <c r="O790" s="51" t="s">
         <v>4619</v>
       </c>
-      <c r="P790" s="72" t="s">
+      <c r="P790" s="51" t="s">
         <v>4620</v>
       </c>
-      <c r="Q790" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R790" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="S790" s="73" t="s">
+      <c r="Q790" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R790" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S790" s="47" t="s">
         <v>3412</v>
+      </c>
+    </row>
+    <row r="791" spans="1:19" ht="17" customHeight="1">
+      <c r="A791" s="64">
+        <v>790</v>
+      </c>
+      <c r="B791" s="65">
+        <v>46230</v>
+      </c>
+      <c r="C791" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D791" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="E791" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F791" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G791" s="68" t="s">
+        <v>4621</v>
+      </c>
+      <c r="H791" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I791" s="69" t="s">
+        <v>4622</v>
+      </c>
+      <c r="J791" s="70">
+        <v>0</v>
+      </c>
+      <c r="K791" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L791" s="72" t="s">
+        <v>4623</v>
+      </c>
+      <c r="M791" s="52" t="s">
+        <v>4624</v>
+      </c>
+      <c r="N791" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O791" s="72" t="s">
+        <v>4625</v>
+      </c>
+      <c r="P791" s="72" t="s">
+        <v>4626</v>
+      </c>
+      <c r="Q791" s="72" t="s">
+        <v>4627</v>
+      </c>
+      <c r="R791" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="S791" s="73" t="s">
+        <v>3409</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8C0CF6-49A4-BF42-AC86-BB866CFC3DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CBC4E4-FFE3-FC4B-AC08-66BAB50FD965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -17975,12 +17975,117 @@
         </r>
       </text>
     </comment>
+    <comment ref="I792" authorId="0" shapeId="0" xr:uid="{D2C4E63D-DFE4-FE44-8372-D4EC6B130067}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>갈릴레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김지철</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케플러</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강병훈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>마리아</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>유낙원</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11869" uniqueCount="4628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11884" uniqueCount="4634">
   <si>
     <t>시즌</t>
   </si>
@@ -31864,6 +31969,24 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/300063</t>
+  </si>
+  <si>
+    <t>김지철, 강병훈, 유낙원</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kDefAObLLPkZSoqtFVVo1xRdnd0QZa3o/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/176gVHOQunfSIpnhwpxFJFh5wcc9fK7V3/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224367131329</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.sll8ffflqk2l</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/300679</t>
   </si>
 </sst>
 </file>
@@ -33257,7 +33380,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S791" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S792" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33584,7 +33707,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V791"/>
+  <dimension ref="A1:V792"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -81630,40 +81753,40 @@
       </c>
     </row>
     <row r="791" spans="1:19" ht="17" customHeight="1">
-      <c r="A791" s="64">
+      <c r="A791" s="59">
         <v>790</v>
       </c>
-      <c r="B791" s="65">
+      <c r="B791" s="60">
         <v>46230</v>
       </c>
-      <c r="C791" s="66">
+      <c r="C791" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D791" s="67" t="s">
+      <c r="D791" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="E791" s="67" t="s">
+      <c r="E791" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="F791" s="67" t="s">
+      <c r="F791" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="G791" s="68" t="s">
+      <c r="G791" s="62" t="s">
         <v>4621</v>
       </c>
-      <c r="H791" s="67" t="s">
+      <c r="H791" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="I791" s="69" t="s">
+      <c r="I791" s="63" t="s">
         <v>4622</v>
       </c>
-      <c r="J791" s="70">
+      <c r="J791" s="54">
         <v>0</v>
       </c>
-      <c r="K791" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L791" s="72" t="s">
+      <c r="K791" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L791" s="51" t="s">
         <v>4623</v>
       </c>
       <c r="M791" s="52" t="s">
@@ -81672,20 +81795,79 @@
       <c r="N791" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O791" s="72" t="s">
+      <c r="O791" s="51" t="s">
         <v>4625</v>
       </c>
-      <c r="P791" s="72" t="s">
+      <c r="P791" s="51" t="s">
         <v>4626</v>
       </c>
-      <c r="Q791" s="72" t="s">
+      <c r="Q791" s="51" t="s">
         <v>4627</v>
       </c>
-      <c r="R791" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="S791" s="73" t="s">
+      <c r="R791" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S791" s="47" t="s">
         <v>3409</v>
+      </c>
+    </row>
+    <row r="792" spans="1:19" ht="17" customHeight="1">
+      <c r="A792" s="64">
+        <v>791</v>
+      </c>
+      <c r="B792" s="65">
+        <v>46237</v>
+      </c>
+      <c r="C792" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D792" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="E792" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="F792" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G792" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="H792" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I792" s="69" t="s">
+        <v>4628</v>
+      </c>
+      <c r="J792" s="70">
+        <v>0</v>
+      </c>
+      <c r="K792" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L792" s="72" t="s">
+        <v>4629</v>
+      </c>
+      <c r="M792" s="52" t="s">
+        <v>4630</v>
+      </c>
+      <c r="N792" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O792" s="72" t="s">
+        <v>4631</v>
+      </c>
+      <c r="P792" s="72" t="s">
+        <v>4632</v>
+      </c>
+      <c r="Q792" s="72" t="s">
+        <v>4633</v>
+      </c>
+      <c r="R792" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="S792" s="73" t="s">
+        <v>3410</v>
       </c>
     </row>
   </sheetData>
